--- a/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -586,82 +586,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.61477315892319</v>
+        <v>22.6147731589231</v>
       </c>
       <c r="C2" t="n">
         <v>16.23337825937018</v>
       </c>
       <c r="D2" t="n">
-        <v>21.92729669313043</v>
+        <v>21.92729669313035</v>
       </c>
       <c r="E2" t="n">
-        <v>21.92665257161315</v>
+        <v>21.92665257161309</v>
       </c>
       <c r="F2" t="n">
-        <v>22.02082685606891</v>
+        <v>22.02082685606884</v>
       </c>
       <c r="G2" t="n">
-        <v>23.27655556849007</v>
+        <v>23.27655556849001</v>
       </c>
       <c r="H2" t="n">
-        <v>21.89999850345955</v>
+        <v>21.89999850345947</v>
       </c>
       <c r="I2" t="n">
-        <v>22.02419281090001</v>
+        <v>22.02419281090002</v>
       </c>
       <c r="J2" t="n">
         <v>22.57822349481856</v>
       </c>
       <c r="K2" t="n">
-        <v>22.00433042658873</v>
+        <v>22.00433042658867</v>
       </c>
       <c r="L2" t="n">
-        <v>22.15981429290733</v>
+        <v>22.15981429290735</v>
       </c>
       <c r="M2" t="n">
         <v>23.39668971328538</v>
       </c>
       <c r="N2" t="n">
-        <v>21.95623376304405</v>
+        <v>21.956233763044</v>
       </c>
       <c r="O2" t="n">
-        <v>29.66886044214731</v>
+        <v>29.66886044214729</v>
       </c>
       <c r="P2" t="n">
-        <v>22.19423053043054</v>
+        <v>22.19423053043051</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.94790900823237</v>
+        <v>21.94790900823231</v>
       </c>
       <c r="R2" t="n">
-        <v>21.89110733347468</v>
+        <v>21.8911073334746</v>
       </c>
       <c r="S2" t="n">
-        <v>22.30843954009045</v>
+        <v>22.3084395400904</v>
       </c>
       <c r="T2" t="n">
-        <v>21.9669178571324</v>
+        <v>21.96691785713237</v>
       </c>
       <c r="U2" t="n">
-        <v>26.01165911328459</v>
+        <v>26.01165911328462</v>
       </c>
       <c r="V2" t="n">
-        <v>22.03485293227233</v>
+        <v>22.0348529322723</v>
       </c>
       <c r="W2" t="n">
-        <v>27.91110240491919</v>
+        <v>27.91110240491925</v>
       </c>
       <c r="X2" t="n">
-        <v>22.09839910382852</v>
+        <v>22.09839910382856</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.10147707701697</v>
+        <v>22.1014770770169</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.88881025542882</v>
+        <v>28.8888102554288</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.20679830386463</v>
+        <v>22.20679830386469</v>
       </c>
       <c r="AB2" t="n">
         <v>23.09174124460817</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.71177048427277</v>
+        <v>26.71177048427282</v>
       </c>
       <c r="C3" t="n">
         <v>11.62216093548261</v>
       </c>
       <c r="D3" t="n">
-        <v>21.83451298643323</v>
+        <v>21.83451298643324</v>
       </c>
       <c r="E3" t="n">
-        <v>21.8100404391753</v>
+        <v>21.81004043917533</v>
       </c>
       <c r="F3" t="n">
-        <v>22.50770937486345</v>
+        <v>22.50770937486349</v>
       </c>
       <c r="G3" t="n">
-        <v>31.43155124971206</v>
+        <v>31.43155124971207</v>
       </c>
       <c r="H3" t="n">
-        <v>21.6432736820209</v>
+        <v>21.64327368202101</v>
       </c>
       <c r="I3" t="n">
-        <v>22.5297792548418</v>
+        <v>22.52977925484184</v>
       </c>
       <c r="J3" t="n">
-        <v>26.46783852432714</v>
+        <v>26.46783852432716</v>
       </c>
       <c r="K3" t="n">
-        <v>22.38492243794071</v>
+        <v>22.38492243794064</v>
       </c>
       <c r="L3" t="n">
-        <v>23.48832928080676</v>
+        <v>23.48832928080673</v>
       </c>
       <c r="M3" t="n">
         <v>33.15985594668322</v>
       </c>
       <c r="N3" t="n">
-        <v>22.03868393429905</v>
+        <v>22.03868393429902</v>
       </c>
       <c r="O3" t="n">
         <v>35.72306562219285</v>
       </c>
       <c r="P3" t="n">
-        <v>23.72390220807925</v>
+        <v>23.72390220807924</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.9801184211196</v>
+        <v>21.98011842111961</v>
       </c>
       <c r="R3" t="n">
-        <v>21.57751330739041</v>
+        <v>21.57751330739046</v>
       </c>
       <c r="S3" t="n">
-        <v>24.5405499566811</v>
+        <v>24.54054995668109</v>
       </c>
       <c r="T3" t="n">
         <v>22.11860275220802</v>
       </c>
       <c r="U3" t="n">
-        <v>31.25636540436968</v>
+        <v>31.25636540436967</v>
       </c>
       <c r="V3" t="n">
-        <v>22.59123944629638</v>
+        <v>22.59123944629648</v>
       </c>
       <c r="W3" t="n">
         <v>32.81455243936725</v>
       </c>
       <c r="X3" t="n">
-        <v>23.05751999970947</v>
+        <v>23.05751999970946</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.0742913929306</v>
+        <v>23.07429139293061</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.72282764271559</v>
+        <v>35.7228276427156</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.82668102121089</v>
+        <v>23.82668102121088</v>
       </c>
       <c r="AB3" t="n">
-        <v>30.17014824359541</v>
+        <v>30.17014824359538</v>
       </c>
     </row>
     <row r="4">
@@ -765,10 +765,10 @@
         <v>23.88524247260246</v>
       </c>
       <c r="C4" t="n">
-        <v>14.44660498580766</v>
+        <v>14.44660498580765</v>
       </c>
       <c r="D4" t="n">
-        <v>16.11987953667443</v>
+        <v>16.11987953667442</v>
       </c>
       <c r="E4" t="n">
         <v>16.11260388782603</v>
@@ -777,40 +777,40 @@
         <v>17.17634575306527</v>
       </c>
       <c r="G4" t="n">
-        <v>31.36037922360949</v>
+        <v>31.36037922360951</v>
       </c>
       <c r="H4" t="n">
-        <v>15.81153392655415</v>
+        <v>15.81153392655414</v>
       </c>
       <c r="I4" t="n">
-        <v>17.21436576129872</v>
+        <v>17.21436576129871</v>
       </c>
       <c r="J4" t="n">
-        <v>23.4388639095203</v>
+        <v>23.43886390952029</v>
       </c>
       <c r="K4" t="n">
-        <v>16.99001099335419</v>
+        <v>16.99001099335418</v>
       </c>
       <c r="L4" t="n">
-        <v>18.74627278953601</v>
+        <v>18.74627278953602</v>
       </c>
       <c r="M4" t="n">
-        <v>34.1781788261836</v>
+        <v>34.17817882618359</v>
       </c>
       <c r="N4" t="n">
-        <v>16.4467370530587</v>
+        <v>16.44673705305869</v>
       </c>
       <c r="O4" t="n">
-        <v>18.44119112747805</v>
+        <v>18.44119112747803</v>
       </c>
       <c r="P4" t="n">
-        <v>19.13502002461161</v>
+        <v>19.13502002461162</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.35270511788413</v>
+        <v>16.35270511788411</v>
       </c>
       <c r="R4" t="n">
-        <v>15.71110407143467</v>
+        <v>15.71110407143465</v>
       </c>
       <c r="S4" t="n">
         <v>20.42506332745985</v>
@@ -819,28 +819,28 @@
         <v>16.56741881071277</v>
       </c>
       <c r="U4" t="n">
-        <v>21.28592765514769</v>
+        <v>21.28592765514766</v>
       </c>
       <c r="V4" t="n">
-        <v>17.11938812198759</v>
+        <v>17.11938812198757</v>
       </c>
       <c r="W4" t="n">
-        <v>18.39844638386725</v>
+        <v>18.39844638386723</v>
       </c>
       <c r="X4" t="n">
-        <v>18.05255997650793</v>
+        <v>18.05255997650791</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.85304539766678</v>
+        <v>17.85304539766675</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.08880950389306</v>
+        <v>21.08880950389305</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.27697880701183</v>
+        <v>19.27697880701184</v>
       </c>
       <c r="AB4" t="n">
-        <v>29.22406090092806</v>
+        <v>29.22406090092803</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212.2826639206138</v>
+        <v>212.2826639206133</v>
       </c>
       <c r="C5" t="n">
         <v>37.78545271724875</v>
       </c>
       <c r="D5" t="n">
-        <v>73.3172109729686</v>
+        <v>73.31721097296864</v>
       </c>
       <c r="E5" t="n">
-        <v>61.35774502076631</v>
+        <v>61.35774502076619</v>
       </c>
       <c r="F5" t="n">
-        <v>97.96031996290273</v>
+        <v>97.96031996290229</v>
       </c>
       <c r="G5" t="n">
-        <v>360.7990428075383</v>
+        <v>360.7990428075389</v>
       </c>
       <c r="H5" t="n">
-        <v>69.24105507676734</v>
+        <v>69.24105507676735</v>
       </c>
       <c r="I5" t="n">
-        <v>97.56513230321187</v>
+        <v>97.5651323032117</v>
       </c>
       <c r="J5" t="n">
-        <v>213.9945736905798</v>
+        <v>213.99457369058</v>
       </c>
       <c r="K5" t="n">
-        <v>91.20582045932491</v>
+        <v>91.20582045932483</v>
       </c>
       <c r="L5" t="n">
-        <v>122.8351342270928</v>
+        <v>122.835134227093</v>
       </c>
       <c r="M5" t="n">
-        <v>463.4293699861493</v>
+        <v>463.4293699861497</v>
       </c>
       <c r="N5" t="n">
-        <v>170.7592119567205</v>
+        <v>170.7592119567201</v>
       </c>
       <c r="O5" t="n">
-        <v>109.4781357312707</v>
+        <v>109.4781357312708</v>
       </c>
       <c r="P5" t="n">
-        <v>124.6860096352356</v>
+        <v>124.6860096352355</v>
       </c>
       <c r="Q5" t="n">
-        <v>77.11091348807673</v>
+        <v>77.11091348807646</v>
       </c>
       <c r="R5" t="n">
         <v>65.84943938861259</v>
       </c>
       <c r="S5" t="n">
-        <v>151.5754605672236</v>
+        <v>151.5754605672234</v>
       </c>
       <c r="T5" t="n">
-        <v>83.10920457861937</v>
+        <v>83.10920457861906</v>
       </c>
       <c r="U5" t="n">
-        <v>175.8326842607508</v>
+        <v>175.8326842607502</v>
       </c>
       <c r="V5" t="n">
-        <v>91.08420248491856</v>
+        <v>91.08420248491848</v>
       </c>
       <c r="W5" t="n">
-        <v>116.7896480374108</v>
+        <v>116.7896480374106</v>
       </c>
       <c r="X5" t="n">
-        <v>113.3311851320155</v>
+        <v>113.3311851320153</v>
       </c>
       <c r="Y5" t="n">
-        <v>110.9429276373041</v>
+        <v>110.9429276373035</v>
       </c>
       <c r="Z5" t="n">
-        <v>163.6224978350549</v>
+        <v>163.6224978350546</v>
       </c>
       <c r="AA5" t="n">
         <v>135.3200297008274</v>
       </c>
       <c r="AB5" t="n">
-        <v>367.7724391777465</v>
+        <v>367.7724391777456</v>
       </c>
     </row>
     <row r="6">
@@ -938,55 +938,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.86943489929286</v>
+        <v>59.06110183717151</v>
       </c>
       <c r="C6" t="n">
         <v>49.6224643503767</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10407196336483</v>
+        <v>36.10407196336482</v>
       </c>
       <c r="E6" t="n">
-        <v>51.28846325239507</v>
+        <v>36.09679631451638</v>
       </c>
       <c r="F6" t="n">
-        <v>37.16053817975566</v>
+        <v>52.35220511763428</v>
       </c>
       <c r="G6" t="n">
-        <v>51.34457165029999</v>
+        <v>66.53623858817859</v>
       </c>
       <c r="H6" t="n">
         <v>50.98739329112315</v>
       </c>
       <c r="I6" t="n">
-        <v>52.39022512586774</v>
+        <v>37.19855818798908</v>
       </c>
       <c r="J6" t="n">
-        <v>43.42305633621072</v>
+        <v>58.61472327408934</v>
       </c>
       <c r="K6" t="n">
-        <v>36.97420342004462</v>
+        <v>36.97420342004461</v>
       </c>
       <c r="L6" t="n">
-        <v>53.92213215410514</v>
+        <v>38.73046521622641</v>
       </c>
       <c r="M6" t="n">
-        <v>54.16237125287397</v>
+        <v>54.162371252874</v>
       </c>
       <c r="N6" t="n">
-        <v>36.44736787333213</v>
+        <v>36.44736787333219</v>
       </c>
       <c r="O6" t="n">
-        <v>53.26927127824352</v>
+        <v>53.26927127824355</v>
       </c>
       <c r="P6" t="n">
         <v>53.96308812198394</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.33689754457457</v>
+        <v>36.33689754457455</v>
       </c>
       <c r="R6" t="n">
-        <v>50.88696343600367</v>
+        <v>35.69529649812505</v>
       </c>
       <c r="S6" t="n">
         <v>55.60092269202892</v>
@@ -995,28 +995,28 @@
         <v>36.55161123740316</v>
       </c>
       <c r="U6" t="n">
-        <v>41.50440178377949</v>
+        <v>41.50440178377946</v>
       </c>
       <c r="V6" t="n">
-        <v>52.29524748655663</v>
+        <v>52.2952474865566</v>
       </c>
       <c r="W6" t="n">
-        <v>39.46042981701883</v>
+        <v>53.22651936474031</v>
       </c>
       <c r="X6" t="n">
-        <v>53.22841934107697</v>
+        <v>53.22841934107699</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.97462804207832</v>
+        <v>38.97462804207835</v>
       </c>
       <c r="Z6" t="n">
-        <v>41.07300193058349</v>
+        <v>41.07300193058347</v>
       </c>
       <c r="AA6" t="n">
-        <v>54.45283817158086</v>
+        <v>39.2611712337022</v>
       </c>
       <c r="AB6" t="n">
-        <v>49.29256513660557</v>
+        <v>49.29256513660556</v>
       </c>
     </row>
     <row r="7">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.31002914318194</v>
+        <v>29.31002914318184</v>
       </c>
       <c r="C7" t="n">
         <v>19.87139165638716</v>
@@ -1035,16 +1035,16 @@
         <v>21.54466620725393</v>
       </c>
       <c r="E7" t="n">
-        <v>21.53739055840555</v>
+        <v>21.53739055840554</v>
       </c>
       <c r="F7" t="n">
         <v>22.60113242364477</v>
       </c>
       <c r="G7" t="n">
-        <v>36.78516589418899</v>
+        <v>36.78516589418902</v>
       </c>
       <c r="H7" t="n">
-        <v>21.23632059713364</v>
+        <v>21.23632059713365</v>
       </c>
       <c r="I7" t="n">
         <v>22.63915243187822</v>
@@ -1053,13 +1053,13 @@
         <v>28.86365058009979</v>
       </c>
       <c r="K7" t="n">
-        <v>22.4147976639337</v>
+        <v>22.41479766393369</v>
       </c>
       <c r="L7" t="n">
-        <v>24.17105946011552</v>
+        <v>24.17105946011554</v>
       </c>
       <c r="M7" t="n">
-        <v>39.60296549676308</v>
+        <v>39.60296549676309</v>
       </c>
       <c r="N7" t="n">
         <v>21.87152372363821</v>
@@ -1071,40 +1071,40 @@
         <v>24.55970568301199</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.77749178846361</v>
+        <v>21.77749178846362</v>
       </c>
       <c r="R7" t="n">
         <v>21.13589074201418</v>
       </c>
       <c r="S7" t="n">
-        <v>25.84984999803936</v>
+        <v>25.84984999803935</v>
       </c>
       <c r="T7" t="n">
-        <v>21.99220548129227</v>
+        <v>21.99220548129226</v>
       </c>
       <c r="U7" t="n">
-        <v>26.94002247478686</v>
+        <v>26.94002247478684</v>
       </c>
       <c r="V7" t="n">
-        <v>22.54417479256708</v>
+        <v>22.54417479256707</v>
       </c>
       <c r="W7" t="n">
         <v>23.82323305444675</v>
       </c>
       <c r="X7" t="n">
-        <v>23.47734664708742</v>
+        <v>23.47734664708741</v>
       </c>
       <c r="Y7" t="n">
-        <v>23.51211377018767</v>
+        <v>23.51211377018766</v>
       </c>
       <c r="Z7" t="n">
-        <v>26.51359617447256</v>
+        <v>26.51359617447257</v>
       </c>
       <c r="AA7" t="n">
         <v>24.70176547759134</v>
       </c>
       <c r="AB7" t="n">
-        <v>34.64884757150752</v>
+        <v>34.6488475715075</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.58721287853877</v>
+        <v>43.58721287853874</v>
       </c>
       <c r="C8" t="n">
-        <v>47.28428631267646</v>
+        <v>47.28428631267651</v>
       </c>
       <c r="D8" t="n">
-        <v>48.95756086354321</v>
+        <v>48.95756086354328</v>
       </c>
       <c r="E8" t="n">
-        <v>48.95028521469482</v>
+        <v>41.95590662839572</v>
       </c>
       <c r="F8" t="n">
-        <v>38.92470640027041</v>
+        <v>38.92470640027043</v>
       </c>
       <c r="G8" t="n">
-        <v>64.19806055047826</v>
+        <v>66.92183578118077</v>
       </c>
       <c r="H8" t="n">
-        <v>48.64921525342291</v>
+        <v>48.64921525342301</v>
       </c>
       <c r="I8" t="n">
-        <v>50.05204708816752</v>
+        <v>50.05204708816755</v>
       </c>
       <c r="J8" t="n">
-        <v>56.27654523638908</v>
+        <v>56.27654523638913</v>
       </c>
       <c r="K8" t="n">
-        <v>49.82769232022298</v>
+        <v>49.82769232022304</v>
       </c>
       <c r="L8" t="n">
-        <v>51.58395411640482</v>
+        <v>51.58395411640488</v>
       </c>
       <c r="M8" t="n">
-        <v>67.01586015305234</v>
+        <v>67.01586015305259</v>
       </c>
       <c r="N8" t="n">
-        <v>39.10204485981946</v>
+        <v>39.10204485981949</v>
       </c>
       <c r="O8" t="n">
-        <v>43.89470359000315</v>
+        <v>43.89470359000318</v>
       </c>
       <c r="P8" t="n">
-        <v>43.90262491186355</v>
+        <v>43.9026249118636</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.47320851971389</v>
+        <v>33.47320851971391</v>
       </c>
       <c r="R8" t="n">
-        <v>48.54878539830342</v>
+        <v>48.54878539830351</v>
       </c>
       <c r="S8" t="n">
-        <v>53.26274465432863</v>
+        <v>53.26274465432871</v>
       </c>
       <c r="T8" t="n">
-        <v>49.40510013758151</v>
+        <v>49.40510013758163</v>
       </c>
       <c r="U8" t="n">
-        <v>46.27131243078654</v>
+        <v>47.94274940480065</v>
       </c>
       <c r="V8" t="n">
-        <v>49.95706944885636</v>
+        <v>46.36271666486422</v>
       </c>
       <c r="W8" t="n">
         <v>51.23870925500425</v>
       </c>
       <c r="X8" t="n">
-        <v>36.37697738571627</v>
+        <v>36.37697738571631</v>
       </c>
       <c r="Y8" t="n">
-        <v>63.97908699974063</v>
+        <v>63.97908699974066</v>
       </c>
       <c r="Z8" t="n">
-        <v>53.92649083076186</v>
+        <v>40.54677733553581</v>
       </c>
       <c r="AA8" t="n">
-        <v>52.11466013388065</v>
+        <v>52.11466013388069</v>
       </c>
       <c r="AB8" t="n">
-        <v>75.78309067562481</v>
+        <v>75.78309067562478</v>
       </c>
     </row>
     <row r="9">
@@ -1202,37 +1202,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45.36419901995757</v>
+        <v>45.36419901995767</v>
       </c>
       <c r="C9" t="n">
-        <v>42.13436087162809</v>
+        <v>42.13436087162808</v>
       </c>
       <c r="D9" t="n">
         <v>43.80763542249485</v>
       </c>
       <c r="E9" t="n">
-        <v>43.80035977364647</v>
+        <v>42.36739429305322</v>
       </c>
       <c r="F9" t="n">
-        <v>44.86410163888571</v>
+        <v>30.55112448332007</v>
       </c>
       <c r="G9" t="n">
-        <v>59.04813510942991</v>
+        <v>59.04813521537672</v>
       </c>
       <c r="H9" t="n">
-        <v>43.49928981237457</v>
+        <v>43.49928981237454</v>
       </c>
       <c r="I9" t="n">
-        <v>44.90212164711913</v>
+        <v>44.90212164711912</v>
       </c>
       <c r="J9" t="n">
-        <v>51.12661979534069</v>
+        <v>51.12661979534067</v>
       </c>
       <c r="K9" t="n">
         <v>44.67776687917461</v>
       </c>
       <c r="L9" t="n">
-        <v>46.43402867535646</v>
+        <v>46.43402867535642</v>
       </c>
       <c r="M9" t="n">
         <v>61.86593471200401</v>
@@ -1241,28 +1241,28 @@
         <v>44.13449293887913</v>
       </c>
       <c r="O9" t="n">
-        <v>48.18653512540022</v>
+        <v>48.18653512540016</v>
       </c>
       <c r="P9" t="n">
         <v>49.32785411160245</v>
       </c>
       <c r="Q9" t="n">
-        <v>44.04046110965137</v>
+        <v>44.04046110965136</v>
       </c>
       <c r="R9" t="n">
-        <v>43.39885995725506</v>
+        <v>43.39885995725508</v>
       </c>
       <c r="S9" t="n">
-        <v>48.11281921328028</v>
+        <v>48.11281921328029</v>
       </c>
       <c r="T9" t="n">
         <v>44.25517469653315</v>
       </c>
       <c r="U9" t="n">
-        <v>49.20796524290952</v>
+        <v>49.20796524290949</v>
       </c>
       <c r="V9" t="n">
-        <v>44.80714400780801</v>
+        <v>51.97195962461829</v>
       </c>
       <c r="W9" t="n">
         <v>46.08620226968767</v>
@@ -1271,16 +1271,16 @@
         <v>45.74031586232834</v>
       </c>
       <c r="Y9" t="n">
-        <v>45.7750829854286</v>
+        <v>45.77508298542857</v>
       </c>
       <c r="Z9" t="n">
-        <v>48.77656538971347</v>
+        <v>45.03321153866818</v>
       </c>
       <c r="AA9" t="n">
-        <v>46.96473469283225</v>
+        <v>46.96473469283222</v>
       </c>
       <c r="AB9" t="n">
-        <v>56.91181678674845</v>
+        <v>56.9118167867484</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.1036544242189</v>
+        <v>20.10365442421887</v>
       </c>
       <c r="C2" t="n">
-        <v>14.44776792041824</v>
+        <v>14.44776792041822</v>
       </c>
       <c r="D2" t="n">
-        <v>20.01765429086689</v>
+        <v>20.01765429086684</v>
       </c>
       <c r="E2" t="n">
-        <v>19.98427164334047</v>
+        <v>19.98427164334042</v>
       </c>
       <c r="F2" t="n">
-        <v>20.03192603936758</v>
+        <v>20.03192603936754</v>
       </c>
       <c r="G2" t="n">
-        <v>20.09519499973444</v>
+        <v>20.09519499973437</v>
       </c>
       <c r="H2" t="n">
-        <v>20.07466747798644</v>
+        <v>20.0746674779864</v>
       </c>
       <c r="I2" t="n">
-        <v>20.11849011388141</v>
+        <v>20.11849011388137</v>
       </c>
       <c r="J2" t="n">
         <v>20.07858439440225</v>
       </c>
       <c r="K2" t="n">
-        <v>20.10046986276372</v>
+        <v>20.10046986276369</v>
       </c>
       <c r="L2" t="n">
-        <v>20.06313781352832</v>
+        <v>20.06313781352827</v>
       </c>
       <c r="M2" t="n">
-        <v>19.92226634415955</v>
+        <v>19.92226634415952</v>
       </c>
       <c r="N2" t="n">
-        <v>20.05394106591798</v>
+        <v>20.05394106591794</v>
       </c>
       <c r="O2" t="n">
         <v>26.80124736790884</v>
       </c>
       <c r="P2" t="n">
-        <v>20.08180943582524</v>
+        <v>20.08180943582521</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.08063450491165</v>
+        <v>20.0806345049116</v>
       </c>
       <c r="R2" t="n">
-        <v>20.09840674134296</v>
+        <v>20.09840674134291</v>
       </c>
       <c r="S2" t="n">
-        <v>20.07244612788932</v>
+        <v>20.0724461278893</v>
       </c>
       <c r="T2" t="n">
-        <v>20.03123022188863</v>
+        <v>20.03123022188858</v>
       </c>
       <c r="U2" t="n">
         <v>23.33169710427291</v>
       </c>
       <c r="V2" t="n">
-        <v>20.0733274367459</v>
+        <v>20.07332743674587</v>
       </c>
       <c r="W2" t="n">
-        <v>25.53927450371261</v>
+        <v>25.53927450371254</v>
       </c>
       <c r="X2" t="n">
         <v>20.29810715758065</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.26926682687694</v>
+        <v>20.26926682687691</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.22018571330788</v>
+        <v>26.22018571330784</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.12986716815426</v>
+        <v>20.12986716815421</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.03278547027456</v>
+        <v>20.03278547027455</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.08083389370512</v>
+        <v>20.08083389370513</v>
       </c>
       <c r="C3" t="n">
-        <v>10.18427035860092</v>
+        <v>10.18427035860091</v>
       </c>
       <c r="D3" t="n">
-        <v>19.4743498621009</v>
+        <v>19.47434986210089</v>
       </c>
       <c r="E3" t="n">
-        <v>19.22045624224207</v>
+        <v>19.22045624224205</v>
       </c>
       <c r="F3" t="n">
-        <v>19.57621415320088</v>
+        <v>19.57621415320087</v>
       </c>
       <c r="G3" t="n">
-        <v>20.02153701921726</v>
+        <v>20.02153701921722</v>
       </c>
       <c r="H3" t="n">
-        <v>19.88400294750159</v>
+        <v>19.88400294750157</v>
       </c>
       <c r="I3" t="n">
         <v>20.195001026603</v>
       </c>
       <c r="J3" t="n">
-        <v>19.90560746028061</v>
+        <v>19.90560746028057</v>
       </c>
       <c r="K3" t="n">
-        <v>20.06387039924553</v>
+        <v>20.06387039924552</v>
       </c>
       <c r="L3" t="n">
-        <v>19.7959144140805</v>
+        <v>19.79591441408052</v>
       </c>
       <c r="M3" t="n">
         <v>19.64546354886047</v>
       </c>
       <c r="N3" t="n">
-        <v>19.73122115607155</v>
+        <v>19.73122115607154</v>
       </c>
       <c r="O3" t="n">
-        <v>30.93758395818488</v>
+        <v>30.93758395818487</v>
       </c>
       <c r="P3" t="n">
-        <v>19.92528173857637</v>
+        <v>19.92528173857638</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.9209665260981</v>
+        <v>19.92096652609811</v>
       </c>
       <c r="R3" t="n">
-        <v>20.05253435956116</v>
+        <v>20.05253435956117</v>
       </c>
       <c r="S3" t="n">
-        <v>19.859654087034</v>
+        <v>19.85965408703403</v>
       </c>
       <c r="T3" t="n">
-        <v>19.57042601262635</v>
+        <v>19.57042601262631</v>
       </c>
       <c r="U3" t="n">
         <v>25.51027960713052</v>
       </c>
       <c r="V3" t="n">
-        <v>19.86685942069394</v>
+        <v>19.86685942069395</v>
       </c>
       <c r="W3" t="n">
-        <v>29.50793293609662</v>
+        <v>29.50793293609661</v>
       </c>
       <c r="X3" t="n">
-        <v>21.47201688571538</v>
+        <v>21.47201688571535</v>
       </c>
       <c r="Y3" t="n">
         <v>21.26883236969733</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.8722646396893</v>
+        <v>29.87226463968932</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.27262447005727</v>
+        <v>20.27262447005728</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.60214602975987</v>
+        <v>19.60214602975991</v>
       </c>
     </row>
     <row r="4">
@@ -1622,58 +1622,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.86425445933664</v>
+        <v>12.86425445933666</v>
       </c>
       <c r="C4" t="n">
-        <v>11.701909214053</v>
+        <v>11.70190921405299</v>
       </c>
       <c r="D4" t="n">
-        <v>11.89284339110961</v>
+        <v>11.89284339110963</v>
       </c>
       <c r="E4" t="n">
-        <v>11.51577103052222</v>
+        <v>11.51577103052226</v>
       </c>
       <c r="F4" t="n">
-        <v>12.05404935575375</v>
+        <v>12.05404935575377</v>
       </c>
       <c r="G4" t="n">
-        <v>12.76870136825684</v>
+        <v>12.76870136825688</v>
       </c>
       <c r="H4" t="n">
-        <v>12.53683356698682</v>
+        <v>12.53683356698684</v>
       </c>
       <c r="I4" t="n">
-        <v>13.0318303988291</v>
+        <v>13.03183039882912</v>
       </c>
       <c r="J4" t="n">
-        <v>12.55309244563924</v>
+        <v>12.55309244563925</v>
       </c>
       <c r="K4" t="n">
-        <v>12.82828337272975</v>
+        <v>12.82828337272978</v>
       </c>
       <c r="L4" t="n">
-        <v>12.40660070302479</v>
+        <v>12.40660070302481</v>
       </c>
       <c r="M4" t="n">
-        <v>12.38118195130361</v>
+        <v>12.38118195130363</v>
       </c>
       <c r="N4" t="n">
-        <v>40.77114717237073</v>
+        <v>40.77114717237048</v>
       </c>
       <c r="O4" t="n">
-        <v>12.45191807146756</v>
+        <v>12.45191807146758</v>
       </c>
       <c r="P4" t="n">
-        <v>12.61750526623918</v>
+        <v>12.61750526623919</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.60423388107528</v>
+        <v>12.60423388107527</v>
       </c>
       <c r="R4" t="n">
-        <v>12.80497946719952</v>
+        <v>12.80497946719954</v>
       </c>
       <c r="S4" t="n">
-        <v>12.51174239576838</v>
+        <v>12.5117423957684</v>
       </c>
       <c r="T4" t="n">
         <v>12.04618977723706</v>
@@ -1682,25 +1682,25 @@
         <v>12.85829330732556</v>
       </c>
       <c r="V4" t="n">
-        <v>12.34385727782682</v>
+        <v>12.34385727782685</v>
       </c>
       <c r="W4" t="n">
-        <v>13.79184962436071</v>
+        <v>13.79184962436073</v>
       </c>
       <c r="X4" t="n">
-        <v>15.06068753533444</v>
+        <v>15.06068753533449</v>
       </c>
       <c r="Y4" t="n">
         <v>14.66362193873909</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.23213239929779</v>
+        <v>12.23213239929782</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.16033946054459</v>
+        <v>13.16033946054463</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.09733958031454</v>
+        <v>12.09733958031458</v>
       </c>
     </row>
     <row r="5">
@@ -1710,31 +1710,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.0111766717056</v>
+        <v>48.01117667170563</v>
       </c>
       <c r="C5" t="n">
-        <v>31.32728141296067</v>
+        <v>31.32728141296068</v>
       </c>
       <c r="D5" t="n">
-        <v>34.61487127967553</v>
+        <v>34.61487127967557</v>
       </c>
       <c r="E5" t="n">
-        <v>19.84069026029007</v>
+        <v>19.84069026029011</v>
       </c>
       <c r="F5" t="n">
         <v>37.46923142650299</v>
       </c>
       <c r="G5" t="n">
-        <v>46.88004705132794</v>
+        <v>46.88004705132833</v>
       </c>
       <c r="H5" t="n">
-        <v>47.42852906216175</v>
+        <v>47.42852906216176</v>
       </c>
       <c r="I5" t="n">
-        <v>55.26804639832538</v>
+        <v>55.26804639832531</v>
       </c>
       <c r="J5" t="n">
-        <v>44.89196441525627</v>
+        <v>44.89196441525623</v>
       </c>
       <c r="K5" t="n">
         <v>50.36247141968825</v>
@@ -1743,52 +1743,52 @@
         <v>42.11905757791187</v>
       </c>
       <c r="M5" t="n">
-        <v>43.86215657924336</v>
+        <v>43.86215657924338</v>
       </c>
       <c r="N5" t="n">
-        <v>40.77114717237073</v>
+        <v>40.77114717237048</v>
       </c>
       <c r="O5" t="n">
-        <v>41.45652499996925</v>
+        <v>41.45652499996928</v>
       </c>
       <c r="P5" t="n">
-        <v>43.83181726216059</v>
+        <v>43.8318172621605</v>
       </c>
       <c r="Q5" t="n">
         <v>45.70643534556238</v>
       </c>
       <c r="R5" t="n">
-        <v>51.70633919719788</v>
+        <v>51.70633919719791</v>
       </c>
       <c r="S5" t="n">
-        <v>42.58244508598291</v>
+        <v>42.58244508598287</v>
       </c>
       <c r="T5" t="n">
-        <v>36.90421182576385</v>
+        <v>36.90421182576389</v>
       </c>
       <c r="U5" t="n">
         <v>50.14302167850035</v>
       </c>
       <c r="V5" t="n">
-        <v>43.05504893421217</v>
+        <v>43.05504893421226</v>
       </c>
       <c r="W5" t="n">
-        <v>66.52471249046515</v>
+        <v>66.52471249046508</v>
       </c>
       <c r="X5" t="n">
-        <v>88.60210047204957</v>
+        <v>88.60210047204959</v>
       </c>
       <c r="Y5" t="n">
-        <v>84.21389535898847</v>
+        <v>84.21389535898848</v>
       </c>
       <c r="Z5" t="n">
         <v>37.8710499716893</v>
       </c>
       <c r="AA5" t="n">
-        <v>55.68820504116387</v>
+        <v>55.68820504116391</v>
       </c>
       <c r="AB5" t="n">
-        <v>39.03917460198859</v>
+        <v>39.03917460198872</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.28878810646076</v>
+        <v>30.1734988888291</v>
       </c>
       <c r="C6" t="n">
-        <v>41.12644286117711</v>
+        <v>29.01115364354546</v>
       </c>
       <c r="D6" t="n">
-        <v>41.31737703823372</v>
+        <v>41.31737703823377</v>
       </c>
       <c r="E6" t="n">
-        <v>40.94030467764639</v>
+        <v>28.82501546001468</v>
       </c>
       <c r="F6" t="n">
-        <v>41.47858300287784</v>
+        <v>29.36329378524621</v>
       </c>
       <c r="G6" t="n">
-        <v>30.07794579774928</v>
+        <v>42.19323501538088</v>
       </c>
       <c r="H6" t="n">
-        <v>29.84607799647922</v>
+        <v>41.96136721411096</v>
       </c>
       <c r="I6" t="n">
-        <v>30.34107482832149</v>
+        <v>42.45636404595325</v>
       </c>
       <c r="J6" t="n">
-        <v>29.8623368751317</v>
+        <v>41.97762609276339</v>
       </c>
       <c r="K6" t="n">
-        <v>42.25281701985386</v>
+        <v>30.13752780222216</v>
       </c>
       <c r="L6" t="n">
-        <v>29.71584513251723</v>
+        <v>41.83113435014897</v>
       </c>
       <c r="M6" t="n">
-        <v>29.69042638079608</v>
+        <v>41.80571559842778</v>
       </c>
       <c r="N6" t="n">
-        <v>40.77114717237073</v>
+        <v>40.77114717237048</v>
       </c>
       <c r="O6" t="n">
-        <v>41.55833288693232</v>
+        <v>41.55833288693233</v>
       </c>
       <c r="P6" t="n">
-        <v>28.90632313026905</v>
+        <v>41.72382723499217</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.02876752819937</v>
+        <v>42.02876752819939</v>
       </c>
       <c r="R6" t="n">
-        <v>30.11422389669193</v>
+        <v>42.22951311432369</v>
       </c>
       <c r="S6" t="n">
-        <v>29.82098682526082</v>
+        <v>41.93627604289251</v>
       </c>
       <c r="T6" t="n">
-        <v>41.47072342436121</v>
+        <v>29.35543420672952</v>
       </c>
       <c r="U6" t="n">
-        <v>30.23883853090741</v>
+        <v>42.35412774853906</v>
       </c>
       <c r="V6" t="n">
-        <v>29.65310170731929</v>
+        <v>41.76839092495104</v>
       </c>
       <c r="W6" t="n">
-        <v>32.01896970341328</v>
+        <v>32.01896970341326</v>
       </c>
       <c r="X6" t="n">
-        <v>32.36993196482691</v>
+        <v>32.36993196482697</v>
       </c>
       <c r="Y6" t="n">
-        <v>32.82994199896459</v>
+        <v>32.82994199896462</v>
       </c>
       <c r="Z6" t="n">
-        <v>41.65666604642188</v>
+        <v>29.54137682879026</v>
       </c>
       <c r="AA6" t="n">
-        <v>30.469583890037</v>
+        <v>30.46958389003706</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.41076195267394</v>
+        <v>29.41076195267397</v>
       </c>
     </row>
     <row r="7">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.78808433016162</v>
+        <v>16.78808433016163</v>
       </c>
       <c r="C7" t="n">
-        <v>15.62573908487798</v>
+        <v>15.62573908487796</v>
       </c>
       <c r="D7" t="n">
-        <v>15.81667326193459</v>
+        <v>15.8166732619346</v>
       </c>
       <c r="E7" t="n">
         <v>15.4396009013472</v>
@@ -1901,10 +1901,10 @@
         <v>15.97787922657874</v>
       </c>
       <c r="G7" t="n">
-        <v>16.6925312390818</v>
+        <v>16.69253123908183</v>
       </c>
       <c r="H7" t="n">
-        <v>16.46066343781181</v>
+        <v>16.4606634378118</v>
       </c>
       <c r="I7" t="n">
         <v>16.95566026965408</v>
@@ -1913,34 +1913,34 @@
         <v>16.47692231646419</v>
       </c>
       <c r="K7" t="n">
-        <v>16.75211324355472</v>
+        <v>16.75211324355474</v>
       </c>
       <c r="L7" t="n">
-        <v>16.33043057384976</v>
+        <v>16.33043057384977</v>
       </c>
       <c r="M7" t="n">
-        <v>16.30501182212859</v>
+        <v>16.30501182212858</v>
       </c>
       <c r="N7" t="n">
-        <v>40.77114717237073</v>
+        <v>40.77114717237048</v>
       </c>
       <c r="O7" t="n">
         <v>16.37566711006179</v>
       </c>
       <c r="P7" t="n">
-        <v>16.54125430483341</v>
+        <v>16.54125430483344</v>
       </c>
       <c r="Q7" t="n">
         <v>16.52806375190023</v>
       </c>
       <c r="R7" t="n">
-        <v>16.7288093380245</v>
+        <v>16.72880933802449</v>
       </c>
       <c r="S7" t="n">
         <v>16.43557226659335</v>
       </c>
       <c r="T7" t="n">
-        <v>15.97001964806203</v>
+        <v>15.97001964806202</v>
       </c>
       <c r="U7" t="n">
         <v>16.8513680272207</v>
@@ -1952,19 +1952,19 @@
         <v>17.71567949518568</v>
       </c>
       <c r="X7" t="n">
-        <v>18.98451740615944</v>
+        <v>18.98451740615945</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.65875260365347</v>
+        <v>18.65875260365346</v>
       </c>
       <c r="Z7" t="n">
         <v>16.15596227012277</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.08416933136957</v>
+        <v>17.08416933136958</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.02116945113953</v>
+        <v>16.02116945113956</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.61815641593124</v>
+        <v>28.61815641593129</v>
       </c>
       <c r="C8" t="n">
-        <v>37.79616441570198</v>
+        <v>37.79616441570202</v>
       </c>
       <c r="D8" t="n">
-        <v>37.98709859275852</v>
+        <v>37.98709859275861</v>
       </c>
       <c r="E8" t="n">
-        <v>37.6100262321712</v>
+        <v>32.10409315034363</v>
       </c>
       <c r="F8" t="n">
-        <v>29.41885749776658</v>
+        <v>29.41885749776663</v>
       </c>
       <c r="G8" t="n">
-        <v>38.86295656990579</v>
+        <v>41.00709617646689</v>
       </c>
       <c r="H8" t="n">
-        <v>38.63108876863572</v>
+        <v>38.63108876863579</v>
       </c>
       <c r="I8" t="n">
-        <v>39.12608560047804</v>
+        <v>39.12608560047808</v>
       </c>
       <c r="J8" t="n">
         <v>38.64734764728821</v>
       </c>
       <c r="K8" t="n">
-        <v>38.92253857437871</v>
+        <v>38.92253857437876</v>
       </c>
       <c r="L8" t="n">
-        <v>38.5008559046737</v>
+        <v>38.50085590467374</v>
       </c>
       <c r="M8" t="n">
-        <v>38.47543715295258</v>
+        <v>38.47543715295249</v>
       </c>
       <c r="N8" t="n">
-        <v>40.77114717237073</v>
+        <v>40.77114717237048</v>
       </c>
       <c r="O8" t="n">
-        <v>32.73339961091698</v>
+        <v>32.73339961091703</v>
       </c>
       <c r="P8" t="n">
-        <v>32.35904445577009</v>
+        <v>32.35904445577016</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.32602041774186</v>
+        <v>26.3260204177419</v>
       </c>
       <c r="R8" t="n">
-        <v>38.89923466884848</v>
+        <v>38.89923466884853</v>
       </c>
       <c r="S8" t="n">
-        <v>38.60599759741734</v>
+        <v>38.60599759741736</v>
       </c>
       <c r="T8" t="n">
-        <v>38.14044497888593</v>
+        <v>38.14044497888604</v>
       </c>
       <c r="U8" t="n">
-        <v>32.65949704640759</v>
+        <v>33.97533023189278</v>
       </c>
       <c r="V8" t="n">
-        <v>38.43811247947574</v>
+        <v>35.61024974694475</v>
       </c>
       <c r="W8" t="n">
-        <v>39.88813700257474</v>
+        <v>39.88813700257481</v>
       </c>
       <c r="X8" t="n">
-        <v>29.73018799403684</v>
+        <v>29.73018799403687</v>
       </c>
       <c r="Y8" t="n">
-        <v>51.10773728398033</v>
+        <v>51.1077372839804</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.32638760094673</v>
+        <v>27.79395698554524</v>
       </c>
       <c r="AA8" t="n">
-        <v>39.25459466219355</v>
+        <v>39.2545946621936</v>
       </c>
       <c r="AB8" t="n">
-        <v>48.9929583935055</v>
+        <v>48.99295839350556</v>
       </c>
     </row>
     <row r="9">
@@ -2062,67 +2062,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.21252517263301</v>
+        <v>23.21252517263299</v>
       </c>
       <c r="C9" t="n">
         <v>25.05589973587912</v>
       </c>
       <c r="D9" t="n">
-        <v>25.24683391293572</v>
+        <v>25.24683391293573</v>
       </c>
       <c r="E9" t="n">
-        <v>24.86976155234835</v>
+        <v>24.17605442041413</v>
       </c>
       <c r="F9" t="n">
-        <v>25.40803987757987</v>
+        <v>18.47903412482736</v>
       </c>
       <c r="G9" t="n">
-        <v>26.12269189008295</v>
+        <v>26.12269285181463</v>
       </c>
       <c r="H9" t="n">
-        <v>25.89082408881294</v>
+        <v>25.89082408881293</v>
       </c>
       <c r="I9" t="n">
-        <v>26.38582092065521</v>
+        <v>26.38582092065518</v>
       </c>
       <c r="J9" t="n">
         <v>25.90708296746535</v>
       </c>
       <c r="K9" t="n">
-        <v>26.18227389455588</v>
+        <v>26.18227389455587</v>
       </c>
       <c r="L9" t="n">
-        <v>25.7605912248509</v>
+        <v>25.76059122485091</v>
       </c>
       <c r="M9" t="n">
-        <v>25.73517247312973</v>
+        <v>25.73517247312974</v>
       </c>
       <c r="N9" t="n">
-        <v>40.77114717237073</v>
+        <v>40.77114717237048</v>
       </c>
       <c r="O9" t="n">
-        <v>26.80200148263987</v>
+        <v>26.80200148263988</v>
       </c>
       <c r="P9" t="n">
         <v>27.18422158160364</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.95822536463309</v>
+        <v>25.95822536463308</v>
       </c>
       <c r="R9" t="n">
-        <v>26.15896998902566</v>
+        <v>26.15896998902564</v>
       </c>
       <c r="S9" t="n">
-        <v>25.8657329175945</v>
+        <v>25.86573291759451</v>
       </c>
       <c r="T9" t="n">
         <v>25.40018029906317</v>
       </c>
       <c r="U9" t="n">
-        <v>26.28358462324108</v>
+        <v>26.28358462324106</v>
       </c>
       <c r="V9" t="n">
-        <v>25.69784779965295</v>
+        <v>29.1663846265564</v>
       </c>
       <c r="W9" t="n">
         <v>27.14584014618684</v>
@@ -2131,10 +2131,10 @@
         <v>28.41467805716056</v>
       </c>
       <c r="Y9" t="n">
-        <v>28.08891325465459</v>
+        <v>28.08891325465461</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.58612292112389</v>
+        <v>23.77394153750739</v>
       </c>
       <c r="AA9" t="n">
         <v>26.51432998237073</v>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.39446511724634</v>
+        <v>22.39446511724639</v>
       </c>
       <c r="C2" t="n">
         <v>16.09308793579301</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8883953982062</v>
+        <v>21.88839539820625</v>
       </c>
       <c r="E2" t="n">
-        <v>21.77745485788708</v>
+        <v>21.77745485788709</v>
       </c>
       <c r="F2" t="n">
-        <v>21.87593666865842</v>
+        <v>21.87593666865846</v>
       </c>
       <c r="G2" t="n">
-        <v>23.12598691323156</v>
+        <v>23.12598691323161</v>
       </c>
       <c r="H2" t="n">
-        <v>21.68246563292087</v>
+        <v>21.68246563292092</v>
       </c>
       <c r="I2" t="n">
-        <v>21.78864063717811</v>
+        <v>21.78864063717815</v>
       </c>
       <c r="J2" t="n">
-        <v>22.47832265689216</v>
+        <v>22.47832265689217</v>
       </c>
       <c r="K2" t="n">
-        <v>21.89154616760288</v>
+        <v>21.89154616760286</v>
       </c>
       <c r="L2" t="n">
-        <v>22.01442195297517</v>
+        <v>22.01442195297522</v>
       </c>
       <c r="M2" t="n">
-        <v>23.17502193099647</v>
+        <v>23.17502193099648</v>
       </c>
       <c r="N2" t="n">
-        <v>21.82089059981832</v>
+        <v>21.82089059981837</v>
       </c>
       <c r="O2" t="n">
-        <v>29.46530248409873</v>
+        <v>29.4653024840987</v>
       </c>
       <c r="P2" t="n">
-        <v>22.16528679081731</v>
+        <v>22.16528679081736</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.83275390741478</v>
+        <v>21.83275390741482</v>
       </c>
       <c r="R2" t="n">
-        <v>21.74118239734817</v>
+        <v>21.74118239734821</v>
       </c>
       <c r="S2" t="n">
-        <v>22.1910165424478</v>
+        <v>22.19101654244786</v>
       </c>
       <c r="T2" t="n">
-        <v>21.84998198809047</v>
+        <v>21.84998198809051</v>
       </c>
       <c r="U2" t="n">
-        <v>25.75588674705896</v>
+        <v>25.75588674705895</v>
       </c>
       <c r="V2" t="n">
-        <v>21.82246973775663</v>
+        <v>21.82246973775669</v>
       </c>
       <c r="W2" t="n">
-        <v>27.68478654071355</v>
+        <v>27.68478654071352</v>
       </c>
       <c r="X2" t="n">
-        <v>22.00026880027269</v>
+        <v>22.00026880027274</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.96349682758791</v>
+        <v>21.96349682758798</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.58525878450689</v>
+        <v>28.58525878450701</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.95465714284017</v>
+        <v>21.95465714284027</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.94955509472949</v>
+        <v>22.94955509472935</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.91993649738986</v>
+        <v>25.91993649739</v>
       </c>
       <c r="C3" t="n">
-        <v>11.4201891685796</v>
+        <v>11.42018916857961</v>
       </c>
       <c r="D3" t="n">
-        <v>22.33796695715368</v>
+        <v>22.33796695715382</v>
       </c>
       <c r="E3" t="n">
-        <v>21.52451781644565</v>
+        <v>21.52451781644578</v>
       </c>
       <c r="F3" t="n">
-        <v>22.25047521417832</v>
+        <v>22.25047521417834</v>
       </c>
       <c r="G3" t="n">
-        <v>31.13183961100768</v>
+        <v>31.13183961100776</v>
       </c>
       <c r="H3" t="n">
-        <v>20.86640490718006</v>
+        <v>20.86640490718017</v>
       </c>
       <c r="I3" t="n">
-        <v>21.62491355600457</v>
+        <v>21.6249135560047</v>
       </c>
       <c r="J3" t="n">
-        <v>26.53303921478384</v>
+        <v>26.53303921478389</v>
       </c>
       <c r="K3" t="n">
-        <v>22.35578815890584</v>
+        <v>22.35578815890602</v>
       </c>
       <c r="L3" t="n">
-        <v>23.2299990178019</v>
+        <v>23.22999901780201</v>
       </c>
       <c r="M3" t="n">
-        <v>32.35165376049452</v>
+        <v>32.35165376049455</v>
       </c>
       <c r="N3" t="n">
-        <v>21.85189300847071</v>
+        <v>21.85189300847085</v>
       </c>
       <c r="O3" t="n">
-        <v>35.36962769954651</v>
+        <v>35.36962769954649</v>
       </c>
       <c r="P3" t="n">
-        <v>24.29417637222998</v>
+        <v>24.29417637223016</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.9373214712376</v>
+        <v>21.93732147123759</v>
       </c>
       <c r="R3" t="n">
-        <v>21.28588623577907</v>
+        <v>21.28588623577918</v>
       </c>
       <c r="S3" t="n">
-        <v>24.47997172220409</v>
+        <v>24.47997172220412</v>
       </c>
       <c r="T3" t="n">
-        <v>22.06322536170012</v>
+        <v>22.06322536170023</v>
       </c>
       <c r="U3" t="n">
-        <v>30.62968104127167</v>
+        <v>30.62968104127162</v>
       </c>
       <c r="V3" t="n">
-        <v>21.85628975551506</v>
+        <v>21.85628975551521</v>
       </c>
       <c r="W3" t="n">
-        <v>32.43209634926641</v>
+        <v>32.43209634926644</v>
       </c>
       <c r="X3" t="n">
-        <v>23.13623307781235</v>
+        <v>23.13623307781236</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.86789358847394</v>
+        <v>22.86789358847402</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.80710487426596</v>
+        <v>34.80710487426599</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.80518409843287</v>
+        <v>22.80518409843285</v>
       </c>
       <c r="AB3" t="n">
-        <v>29.9297279247118</v>
+        <v>29.92972792471181</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.64449632835852</v>
+        <v>22.64449632835854</v>
       </c>
       <c r="C4" t="n">
-        <v>14.14973849853231</v>
+        <v>14.14973849853232</v>
       </c>
       <c r="D4" t="n">
-        <v>16.92820604822766</v>
+        <v>16.9282060482277</v>
       </c>
       <c r="E4" t="n">
-        <v>15.67508161015316</v>
+        <v>15.67508161015317</v>
       </c>
       <c r="F4" t="n">
-        <v>16.78747896668654</v>
+        <v>16.78747896668655</v>
       </c>
       <c r="G4" t="n">
-        <v>30.90737153066354</v>
+        <v>30.90737153066349</v>
       </c>
       <c r="H4" t="n">
-        <v>14.60213461695756</v>
+        <v>14.60213461695758</v>
       </c>
       <c r="I4" t="n">
         <v>15.80143013295788</v>
       </c>
       <c r="J4" t="n">
-        <v>23.55786340915508</v>
+        <v>23.5578634091551</v>
       </c>
       <c r="K4" t="n">
-        <v>16.96379543798857</v>
+        <v>16.96379543798858</v>
       </c>
       <c r="L4" t="n">
-        <v>18.35173395942271</v>
+        <v>18.35173395942274</v>
       </c>
       <c r="M4" t="n">
-        <v>32.92341028122028</v>
+        <v>32.9234102812203</v>
       </c>
       <c r="N4" t="n">
         <v>16.16570829669514</v>
       </c>
       <c r="O4" t="n">
-        <v>18.04853644286688</v>
+        <v>18.0485364428669</v>
       </c>
       <c r="P4" t="n">
-        <v>20.05582170410381</v>
+        <v>20.05582170410384</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.29970981338813</v>
+        <v>16.29970981338814</v>
       </c>
       <c r="R4" t="n">
-        <v>15.26536748220984</v>
+        <v>15.26536748220986</v>
       </c>
       <c r="S4" t="n">
-        <v>20.34645108504076</v>
+        <v>20.3464510850408</v>
       </c>
       <c r="T4" t="n">
-        <v>16.49430890992871</v>
+        <v>16.49430890992873</v>
       </c>
       <c r="U4" t="n">
-        <v>20.51285734616012</v>
+        <v>20.51285734616016</v>
       </c>
       <c r="V4" t="n">
-        <v>15.96605302892518</v>
+        <v>15.9660530289252</v>
       </c>
       <c r="W4" t="n">
-        <v>18.02351865322558</v>
+        <v>18.02351865322559</v>
       </c>
       <c r="X4" t="n">
-        <v>18.19186758887612</v>
+        <v>18.19186758887614</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.54706702167969</v>
+        <v>17.54706702167972</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.87742731972378</v>
+        <v>19.8774273197238</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.67666293577719</v>
+        <v>17.6766629357772</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.85743100855263</v>
+        <v>28.85743100855262</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>179.6202175490477</v>
+        <v>179.6202175490478</v>
       </c>
       <c r="C5" t="n">
-        <v>33.48141907231209</v>
+        <v>33.48141907231208</v>
       </c>
       <c r="D5" t="n">
-        <v>88.15234721742456</v>
+        <v>88.15234721742446</v>
       </c>
       <c r="E5" t="n">
-        <v>52.41159062588096</v>
+        <v>52.41159062588102</v>
       </c>
       <c r="F5" t="n">
-        <v>86.28502821564334</v>
+        <v>86.28502821564338</v>
       </c>
       <c r="G5" t="n">
-        <v>330.8460487481327</v>
+        <v>330.8460487481331</v>
       </c>
       <c r="H5" t="n">
-        <v>43.15286862193823</v>
+        <v>43.15286862193832</v>
       </c>
       <c r="I5" t="n">
-        <v>66.23633204299193</v>
+        <v>66.23633204299203</v>
       </c>
       <c r="J5" t="n">
-        <v>205.6199913717034</v>
+        <v>205.6199913717037</v>
       </c>
       <c r="K5" t="n">
         <v>86.23026353798241</v>
       </c>
       <c r="L5" t="n">
-        <v>110.9384331072374</v>
+        <v>110.9384331072377</v>
       </c>
       <c r="M5" t="n">
-        <v>410.9128261673352</v>
+        <v>410.9128261673363</v>
       </c>
       <c r="N5" t="n">
-        <v>148.9140949209067</v>
+        <v>148.9140949209065</v>
       </c>
       <c r="O5" t="n">
-        <v>98.45041720006176</v>
+        <v>98.45041720006189</v>
       </c>
       <c r="P5" t="n">
-        <v>136.178052439876</v>
+        <v>136.1780524398766</v>
       </c>
       <c r="Q5" t="n">
-        <v>74.30592095074824</v>
+        <v>74.30592095074829</v>
       </c>
       <c r="R5" t="n">
-        <v>55.92504644777051</v>
+        <v>55.9250464477706</v>
       </c>
       <c r="S5" t="n">
-        <v>142.8749954409558</v>
+        <v>142.8749954409563</v>
       </c>
       <c r="T5" t="n">
-        <v>79.62392887615775</v>
+        <v>79.62392887615768</v>
       </c>
       <c r="U5" t="n">
-        <v>153.4906881901506</v>
+        <v>153.4906881901505</v>
       </c>
       <c r="V5" t="n">
-        <v>67.64684578794197</v>
+        <v>67.64684578794176</v>
       </c>
       <c r="W5" t="n">
         <v>105.5898129644405</v>
       </c>
       <c r="X5" t="n">
-        <v>111.9454721518445</v>
+        <v>111.945472151845</v>
       </c>
       <c r="Y5" t="n">
-        <v>100.8128318630906</v>
+        <v>100.8128318630909</v>
       </c>
       <c r="Z5" t="n">
-        <v>134.049729923178</v>
+        <v>134.0497299231778</v>
       </c>
       <c r="AA5" t="n">
-        <v>99.13612551388505</v>
+        <v>99.1361255138853</v>
       </c>
       <c r="AB5" t="n">
-        <v>341.0795953457668</v>
+        <v>341.0795953457664</v>
       </c>
     </row>
     <row r="6">
@@ -2658,82 +2658,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55.44966253718022</v>
+        <v>41.29102193827808</v>
       </c>
       <c r="C6" t="n">
-        <v>46.95490470735395</v>
+        <v>46.95490470735396</v>
       </c>
       <c r="D6" t="n">
-        <v>35.57473165814733</v>
+        <v>49.73337225704934</v>
       </c>
       <c r="E6" t="n">
         <v>34.32160722007279</v>
       </c>
       <c r="F6" t="n">
-        <v>49.59264517550823</v>
+        <v>35.43400457660616</v>
       </c>
       <c r="G6" t="n">
-        <v>63.71253773948519</v>
+        <v>49.55389714058309</v>
       </c>
       <c r="H6" t="n">
-        <v>33.24866022687715</v>
+        <v>47.40730082577915</v>
       </c>
       <c r="I6" t="n">
-        <v>34.4479557428775</v>
+        <v>34.44795574287754</v>
       </c>
       <c r="J6" t="n">
-        <v>56.36302961797678</v>
+        <v>56.36302961797673</v>
       </c>
       <c r="K6" t="n">
-        <v>35.6103210479082</v>
+        <v>49.76896164681021</v>
       </c>
       <c r="L6" t="n">
-        <v>36.99825956934234</v>
+        <v>36.99825956934238</v>
       </c>
       <c r="M6" t="n">
-        <v>51.56993589113988</v>
+        <v>51.56993589113989</v>
       </c>
       <c r="N6" t="n">
-        <v>34.82452376048666</v>
+        <v>34.82452376048676</v>
       </c>
       <c r="O6" t="n">
-        <v>50.52904353405518</v>
+        <v>50.52904353405521</v>
       </c>
       <c r="P6" t="n">
-        <v>52.53632568553805</v>
+        <v>52.53632568553816</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.94623542330775</v>
+        <v>49.10487602220975</v>
       </c>
       <c r="R6" t="n">
-        <v>33.91189309212946</v>
+        <v>48.07053369103154</v>
       </c>
       <c r="S6" t="n">
-        <v>38.99297669496042</v>
+        <v>53.1516172938624</v>
       </c>
       <c r="T6" t="n">
-        <v>49.29947511875034</v>
+        <v>35.14083451984837</v>
       </c>
       <c r="U6" t="n">
-        <v>53.54746777476076</v>
+        <v>39.38882717585868</v>
       </c>
       <c r="V6" t="n">
-        <v>48.77121923774683</v>
+        <v>48.77121923774686</v>
       </c>
       <c r="W6" t="n">
-        <v>50.5039538225763</v>
+        <v>50.50395382257634</v>
       </c>
       <c r="X6" t="n">
-        <v>36.83839319879576</v>
+        <v>50.99703379769773</v>
       </c>
       <c r="Y6" t="n">
-        <v>37.26050063654422</v>
+        <v>37.26050063654436</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.52395292964339</v>
+        <v>52.68259352854544</v>
       </c>
       <c r="AA6" t="n">
-        <v>50.48182914459882</v>
+        <v>36.32318854569684</v>
       </c>
       <c r="AB6" t="n">
         <v>47.5832519978597</v>
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.65072851681854</v>
+        <v>27.65072851681856</v>
       </c>
       <c r="C7" t="n">
         <v>19.15597068699233</v>
       </c>
       <c r="D7" t="n">
-        <v>21.93443823668769</v>
+        <v>21.9344382366877</v>
       </c>
       <c r="E7" t="n">
-        <v>20.68131379861317</v>
+        <v>20.68131379861318</v>
       </c>
       <c r="F7" t="n">
         <v>21.79371115514655</v>
       </c>
       <c r="G7" t="n">
-        <v>35.91360371912354</v>
+        <v>35.91360371912353</v>
       </c>
       <c r="H7" t="n">
-        <v>19.60836680541761</v>
+        <v>19.60836680541762</v>
       </c>
       <c r="I7" t="n">
-        <v>20.80766232141789</v>
+        <v>20.80766232141792</v>
       </c>
       <c r="J7" t="n">
-        <v>28.5640955976151</v>
+        <v>28.56409559761511</v>
       </c>
       <c r="K7" t="n">
-        <v>21.97002762644859</v>
+        <v>21.9700276264486</v>
       </c>
       <c r="L7" t="n">
-        <v>23.35796614788274</v>
+        <v>23.35796614788276</v>
       </c>
       <c r="M7" t="n">
-        <v>37.92964246968032</v>
+        <v>37.92964246968033</v>
       </c>
       <c r="N7" t="n">
-        <v>21.17194048515516</v>
+        <v>21.17194048515517</v>
       </c>
       <c r="O7" t="n">
-        <v>23.05467538210287</v>
+        <v>23.05467538210288</v>
       </c>
       <c r="P7" t="n">
-        <v>25.06196064333981</v>
+        <v>25.06196064333986</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.30594200184816</v>
+        <v>21.30594200184815</v>
       </c>
       <c r="R7" t="n">
-        <v>20.2715996706699</v>
+        <v>20.27159967066991</v>
       </c>
       <c r="S7" t="n">
-        <v>25.35268327350078</v>
+        <v>25.35268327350082</v>
       </c>
       <c r="T7" t="n">
-        <v>21.50054109838872</v>
+        <v>21.50054109838874</v>
       </c>
       <c r="U7" t="n">
-        <v>25.74358746353116</v>
+        <v>25.7435874635312</v>
       </c>
       <c r="V7" t="n">
-        <v>20.97228521738519</v>
+        <v>20.97228521738522</v>
       </c>
       <c r="W7" t="n">
-        <v>23.02975084168561</v>
+        <v>23.0297508416856</v>
       </c>
       <c r="X7" t="n">
-        <v>23.19809977733614</v>
+        <v>23.19809977733616</v>
       </c>
       <c r="Y7" t="n">
         <v>22.78274342991867</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.88365950818378</v>
+        <v>24.8836595081838</v>
       </c>
       <c r="AA7" t="n">
         <v>22.68289512423719</v>
       </c>
       <c r="AB7" t="n">
-        <v>33.86366319701263</v>
+        <v>33.86366319701264</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40.99041147122053</v>
+        <v>40.99041147122054</v>
       </c>
       <c r="C8" t="n">
-        <v>44.71971193882125</v>
+        <v>44.71971193882129</v>
       </c>
       <c r="D8" t="n">
-        <v>47.49817948851661</v>
+        <v>47.49817948851664</v>
       </c>
       <c r="E8" t="n">
-        <v>46.24505505044208</v>
+        <v>39.73610459409497</v>
       </c>
       <c r="F8" t="n">
-        <v>37.03775952677999</v>
+        <v>37.03775952678001</v>
       </c>
       <c r="G8" t="n">
-        <v>61.47734497095247</v>
+        <v>64.01208309130436</v>
       </c>
       <c r="H8" t="n">
-        <v>45.1721080572465</v>
+        <v>45.17210805724652</v>
       </c>
       <c r="I8" t="n">
         <v>46.37140357324682</v>
       </c>
       <c r="J8" t="n">
-        <v>54.12783684944399</v>
+        <v>54.12783684944401</v>
       </c>
       <c r="K8" t="n">
-        <v>47.53376887827748</v>
+        <v>47.53376887827753</v>
       </c>
       <c r="L8" t="n">
-        <v>48.92170739971166</v>
+        <v>48.92170739971168</v>
       </c>
       <c r="M8" t="n">
-        <v>63.49338372150922</v>
+        <v>63.49338372150905</v>
       </c>
       <c r="N8" t="n">
-        <v>37.25999151624516</v>
+        <v>37.25999151624517</v>
       </c>
       <c r="O8" t="n">
-        <v>41.74682161147018</v>
+        <v>41.74682161147022</v>
       </c>
       <c r="P8" t="n">
-        <v>43.11580307344643</v>
+        <v>43.11580307344649</v>
       </c>
       <c r="Q8" t="n">
         <v>32.24331850012496</v>
       </c>
       <c r="R8" t="n">
-        <v>45.83534092249877</v>
+        <v>45.83534092249882</v>
       </c>
       <c r="S8" t="n">
-        <v>50.91642452532967</v>
+        <v>50.9164245253297</v>
       </c>
       <c r="T8" t="n">
-        <v>47.06428235021765</v>
+        <v>47.06428235021761</v>
       </c>
       <c r="U8" t="n">
-        <v>43.78669449892227</v>
+        <v>45.34211431618625</v>
       </c>
       <c r="V8" t="n">
-        <v>46.5360264692141</v>
+        <v>43.19085876057834</v>
       </c>
       <c r="W8" t="n">
         <v>48.5958944718888</v>
       </c>
       <c r="X8" t="n">
-        <v>35.25583550854756</v>
+        <v>35.25583550854762</v>
       </c>
       <c r="Y8" t="n">
-        <v>60.49415365303147</v>
+        <v>60.49415365303155</v>
       </c>
       <c r="Z8" t="n">
-        <v>50.44740076001271</v>
+        <v>37.99627430381861</v>
       </c>
       <c r="AA8" t="n">
-        <v>48.24663637606611</v>
+        <v>48.24663637606608</v>
       </c>
       <c r="AB8" t="n">
-        <v>72.19645550023813</v>
+        <v>72.19645550023812</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40.87817701585087</v>
+        <v>40.87817701585088</v>
       </c>
       <c r="C9" t="n">
-        <v>37.67294492833412</v>
+        <v>37.67294492833415</v>
       </c>
       <c r="D9" t="n">
-        <v>40.45141247802947</v>
+        <v>40.45141247802957</v>
       </c>
       <c r="E9" t="n">
-        <v>39.19828803995497</v>
+        <v>37.97748715700209</v>
       </c>
       <c r="F9" t="n">
-        <v>40.31068539648838</v>
+        <v>28.11688477143053</v>
       </c>
       <c r="G9" t="n">
-        <v>54.43057796046531</v>
+        <v>54.43057806809725</v>
       </c>
       <c r="H9" t="n">
-        <v>38.1253410467594</v>
+        <v>38.12534104675945</v>
       </c>
       <c r="I9" t="n">
-        <v>39.32463656275969</v>
+        <v>39.32463656275975</v>
       </c>
       <c r="J9" t="n">
-        <v>47.08106983895688</v>
+        <v>47.08106983895694</v>
       </c>
       <c r="K9" t="n">
-        <v>40.48700186779038</v>
+        <v>40.48700186779045</v>
       </c>
       <c r="L9" t="n">
-        <v>41.87494038922452</v>
+        <v>41.87494038922461</v>
       </c>
       <c r="M9" t="n">
-        <v>56.4466167110221</v>
+        <v>56.44661671102213</v>
       </c>
       <c r="N9" t="n">
-        <v>39.68891472649698</v>
+        <v>39.68891472649702</v>
       </c>
       <c r="O9" t="n">
-        <v>43.32468492093372</v>
+        <v>43.32468492093378</v>
       </c>
       <c r="P9" t="n">
-        <v>45.7132049788348</v>
+        <v>45.71320497883491</v>
       </c>
       <c r="Q9" t="n">
-        <v>39.82291635082183</v>
+        <v>39.82291635082185</v>
       </c>
       <c r="R9" t="n">
-        <v>38.78857391201169</v>
+        <v>38.7885739120117</v>
       </c>
       <c r="S9" t="n">
-        <v>43.86965751484258</v>
+        <v>43.86965751484264</v>
       </c>
       <c r="T9" t="n">
-        <v>40.01751533973054</v>
+        <v>40.01751533973056</v>
       </c>
       <c r="U9" t="n">
-        <v>44.2655079957409</v>
+        <v>44.26550799574097</v>
       </c>
       <c r="V9" t="n">
-        <v>39.48925945872705</v>
+        <v>45.59325352574176</v>
       </c>
       <c r="W9" t="n">
-        <v>41.54672508302739</v>
+        <v>41.54672508302742</v>
       </c>
       <c r="X9" t="n">
-        <v>41.71507401867795</v>
+        <v>41.71507401867802</v>
       </c>
       <c r="Y9" t="n">
-        <v>41.2997176712605</v>
+        <v>41.29971767126054</v>
       </c>
       <c r="Z9" t="n">
-        <v>43.40063374952559</v>
+        <v>40.21152013263379</v>
       </c>
       <c r="AA9" t="n">
-        <v>41.19986936557901</v>
+        <v>41.19986936557905</v>
       </c>
       <c r="AB9" t="n">
-        <v>52.38063743835446</v>
+        <v>52.38063743835452</v>
       </c>
     </row>
   </sheetData>
@@ -3166,55 +3166,55 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.22731956354763</v>
+        <v>22.22731956354762</v>
       </c>
       <c r="C2" t="n">
-        <v>16.02634909711895</v>
+        <v>16.02634909711896</v>
       </c>
       <c r="D2" t="n">
-        <v>21.87379396157976</v>
+        <v>21.87379396157974</v>
       </c>
       <c r="E2" t="n">
-        <v>21.68255061804165</v>
+        <v>21.68255061804164</v>
       </c>
       <c r="F2" t="n">
-        <v>21.90861466389748</v>
+        <v>21.90861466389747</v>
       </c>
       <c r="G2" t="n">
         <v>22.98094866793745</v>
       </c>
       <c r="H2" t="n">
-        <v>21.60959230106945</v>
+        <v>21.60959230106946</v>
       </c>
       <c r="I2" t="n">
-        <v>21.89050491770539</v>
+        <v>21.89050491770537</v>
       </c>
       <c r="J2" t="n">
-        <v>22.3769424580073</v>
+        <v>22.37694245800728</v>
       </c>
       <c r="K2" t="n">
-        <v>21.95207422295144</v>
+        <v>21.95207422295143</v>
       </c>
       <c r="L2" t="n">
-        <v>21.90051200673834</v>
+        <v>21.90051200673835</v>
       </c>
       <c r="M2" t="n">
         <v>22.91331009691455</v>
       </c>
       <c r="N2" t="n">
-        <v>21.72689741053538</v>
+        <v>21.72689741053535</v>
       </c>
       <c r="O2" t="n">
-        <v>29.27709524608087</v>
+        <v>29.27709524608085</v>
       </c>
       <c r="P2" t="n">
-        <v>22.09585447607938</v>
+        <v>22.0958544760794</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.78782012967634</v>
+        <v>21.78782012967632</v>
       </c>
       <c r="R2" t="n">
-        <v>21.65112937484127</v>
+        <v>21.65112937484129</v>
       </c>
       <c r="S2" t="n">
         <v>22.08611280507033</v>
@@ -3223,28 +3223,28 @@
         <v>21.78181820959704</v>
       </c>
       <c r="U2" t="n">
-        <v>25.49757417356388</v>
+        <v>25.49757417356391</v>
       </c>
       <c r="V2" t="n">
-        <v>21.82829068953011</v>
+        <v>21.8282906895301</v>
       </c>
       <c r="W2" t="n">
         <v>27.54626420566812</v>
       </c>
       <c r="X2" t="n">
-        <v>21.99865268453365</v>
+        <v>21.99865268453366</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.13993369053794</v>
+        <v>22.13993369053797</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.50648724665731</v>
+        <v>28.50648724665728</v>
       </c>
       <c r="AA2" t="n">
         <v>21.87744329968901</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.8087639603508</v>
+        <v>22.80876396035079</v>
       </c>
     </row>
     <row r="3">
@@ -3257,82 +3257,82 @@
         <v>25.16439979209642</v>
       </c>
       <c r="C3" t="n">
-        <v>11.41292410527208</v>
+        <v>11.41292410527209</v>
       </c>
       <c r="D3" t="n">
-        <v>22.66485966749203</v>
+        <v>22.66485966749205</v>
       </c>
       <c r="E3" t="n">
-        <v>21.27801181370207</v>
+        <v>21.27801181370205</v>
       </c>
       <c r="F3" t="n">
-        <v>22.91480519930438</v>
+        <v>22.91480519930439</v>
       </c>
       <c r="G3" t="n">
-        <v>30.52135060548563</v>
+        <v>30.52135060548566</v>
       </c>
       <c r="H3" t="n">
-        <v>20.77654990506707</v>
+        <v>20.7765499050671</v>
       </c>
       <c r="I3" t="n">
-        <v>22.78676798094309</v>
+        <v>22.78676798094313</v>
       </c>
       <c r="J3" t="n">
-        <v>26.23832606727687</v>
+        <v>26.23832606727692</v>
       </c>
       <c r="K3" t="n">
-        <v>23.21243538349031</v>
+        <v>23.21243538349032</v>
       </c>
       <c r="L3" t="n">
-        <v>22.8474125712352</v>
+        <v>22.84741257123522</v>
       </c>
       <c r="M3" t="n">
-        <v>30.92404175016098</v>
+        <v>30.924041750161</v>
       </c>
       <c r="N3" t="n">
-        <v>21.61162709888321</v>
+        <v>21.6116270988832</v>
       </c>
       <c r="O3" t="n">
-        <v>34.94724692118081</v>
+        <v>34.94724692118086</v>
       </c>
       <c r="P3" t="n">
-        <v>24.22753054796633</v>
+        <v>24.22753054796636</v>
       </c>
       <c r="Q3" t="n">
         <v>22.04619513363546</v>
       </c>
       <c r="R3" t="n">
-        <v>21.07315611378362</v>
+        <v>21.07315611378358</v>
       </c>
       <c r="S3" t="n">
-        <v>24.16132329725093</v>
+        <v>24.16132329725099</v>
       </c>
       <c r="T3" t="n">
         <v>22.00752408648701</v>
       </c>
       <c r="U3" t="n">
-        <v>29.58203139532202</v>
+        <v>29.58203139532204</v>
       </c>
       <c r="V3" t="n">
-        <v>22.32490956737722</v>
+        <v>22.32490956737723</v>
       </c>
       <c r="W3" t="n">
-        <v>32.25537186306239</v>
+        <v>32.2553718630624</v>
       </c>
       <c r="X3" t="n">
-        <v>23.55561268006644</v>
+        <v>23.55561268006642</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.55772974026849</v>
+        <v>24.55772974026853</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.75862720966523</v>
+        <v>34.75862720966525</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.68502776288641</v>
+        <v>22.6850277628864</v>
       </c>
       <c r="AB3" t="n">
-        <v>29.36065951176948</v>
+        <v>29.36065951176951</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.32929635066694</v>
+        <v>21.32929635066695</v>
       </c>
       <c r="C4" t="n">
         <v>14.04493786712146</v>
       </c>
       <c r="D4" t="n">
-        <v>17.33606204662803</v>
+        <v>17.33606204662806</v>
       </c>
       <c r="E4" t="n">
-        <v>15.1758805050807</v>
+        <v>15.17588050508071</v>
       </c>
       <c r="F4" t="n">
         <v>17.72937789762127</v>
       </c>
       <c r="G4" t="n">
-        <v>29.84188377126637</v>
+        <v>29.84188377126638</v>
       </c>
       <c r="H4" t="n">
         <v>14.35178275239582</v>
       </c>
       <c r="I4" t="n">
-        <v>17.52481998348669</v>
+        <v>17.52481998348672</v>
       </c>
       <c r="J4" t="n">
         <v>22.9862217584018</v>
       </c>
       <c r="K4" t="n">
-        <v>18.22027360952057</v>
+        <v>18.22027360952058</v>
       </c>
       <c r="L4" t="n">
-        <v>17.63785465760233</v>
+        <v>17.63785465760234</v>
       </c>
       <c r="M4" t="n">
-        <v>30.56434675942558</v>
+        <v>30.56434675942559</v>
       </c>
       <c r="N4" t="n">
-        <v>15.67679792682968</v>
+        <v>15.67679792682967</v>
       </c>
       <c r="O4" t="n">
-        <v>17.50344033569894</v>
+        <v>17.50344033569898</v>
       </c>
       <c r="P4" t="n">
-        <v>19.84433771078515</v>
+        <v>19.84433771078518</v>
       </c>
       <c r="Q4" t="n">
         <v>16.36494806536227</v>
       </c>
       <c r="R4" t="n">
-        <v>14.82096310864663</v>
+        <v>14.82096310864664</v>
       </c>
       <c r="S4" t="n">
         <v>19.73430105534774</v>
       </c>
       <c r="T4" t="n">
-        <v>16.29715361704715</v>
+        <v>16.29715361704718</v>
       </c>
       <c r="U4" t="n">
-        <v>18.95231332519633</v>
+        <v>18.95231332519639</v>
       </c>
       <c r="V4" t="n">
-        <v>16.60938792360472</v>
+        <v>16.60938792360473</v>
       </c>
       <c r="W4" t="n">
-        <v>17.81633942994448</v>
+        <v>17.81633942994447</v>
       </c>
       <c r="X4" t="n">
-        <v>18.74639876024263</v>
+        <v>18.74639876024268</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.14459745967998</v>
+        <v>20.14459745967999</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.7520226750295</v>
+        <v>19.75202267502952</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.37728299935054</v>
+        <v>17.37728299935056</v>
       </c>
       <c r="AB4" t="n">
-        <v>27.85118127584713</v>
+        <v>27.85118127584715</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>152.0412169342693</v>
+        <v>152.0412169342697</v>
       </c>
       <c r="C5" t="n">
-        <v>33.92148571459467</v>
+        <v>33.9214857145947</v>
       </c>
       <c r="D5" t="n">
-        <v>93.63905426050354</v>
+        <v>93.6390542605038</v>
       </c>
       <c r="E5" t="n">
-        <v>44.06563996191889</v>
+        <v>44.06563996191903</v>
       </c>
       <c r="F5" t="n">
-        <v>101.3357487756487</v>
+        <v>101.3357487756486</v>
       </c>
       <c r="G5" t="n">
-        <v>291.3353729685884</v>
+        <v>291.3353729685878</v>
       </c>
       <c r="H5" t="n">
-        <v>39.46346793232074</v>
+        <v>39.46346793232073</v>
       </c>
       <c r="I5" t="n">
-        <v>98.34638152172604</v>
+        <v>98.34638152172636</v>
       </c>
       <c r="J5" t="n">
-        <v>185.0401273739149</v>
+        <v>185.0401273739148</v>
       </c>
       <c r="K5" t="n">
-        <v>103.5180323211415</v>
+        <v>103.5180323211417</v>
       </c>
       <c r="L5" t="n">
-        <v>94.76093645456653</v>
+        <v>94.76093645456658</v>
       </c>
       <c r="M5" t="n">
-        <v>344.4317690176385</v>
+        <v>344.4317690176389</v>
       </c>
       <c r="N5" t="n">
-        <v>115.5569834851775</v>
+        <v>115.5569834851782</v>
       </c>
       <c r="O5" t="n">
-        <v>86.53814964762847</v>
+        <v>86.53814964762869</v>
       </c>
       <c r="P5" t="n">
-        <v>126.5046733407924</v>
+        <v>126.5046733407932</v>
       </c>
       <c r="Q5" t="n">
-        <v>73.83848806932488</v>
+        <v>73.83848806932508</v>
       </c>
       <c r="R5" t="n">
-        <v>47.84152536773576</v>
+        <v>47.84152536773579</v>
       </c>
       <c r="S5" t="n">
-        <v>126.2787615374054</v>
+        <v>126.2787615374059</v>
       </c>
       <c r="T5" t="n">
-        <v>74.79781418908829</v>
+        <v>74.79781418908865</v>
       </c>
       <c r="U5" t="n">
-        <v>119.0301341393991</v>
+        <v>119.0301341394002</v>
       </c>
       <c r="V5" t="n">
-        <v>76.46342899736251</v>
+        <v>76.46342899736064</v>
       </c>
       <c r="W5" t="n">
-        <v>98.91226341268788</v>
+        <v>98.91226341268771</v>
       </c>
       <c r="X5" t="n">
-        <v>118.3914858518263</v>
+        <v>118.3914858518269</v>
       </c>
       <c r="Y5" t="n">
-        <v>143.3969600661707</v>
+        <v>143.3969600661715</v>
       </c>
       <c r="Z5" t="n">
         <v>121.7690152321436</v>
       </c>
       <c r="AA5" t="n">
-        <v>91.3222945684377</v>
+        <v>91.32229456843775</v>
       </c>
       <c r="AB5" t="n">
-        <v>304.3639992343215</v>
+        <v>304.3639992343212</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.87807959298053</v>
+        <v>38.75206016963478</v>
       </c>
       <c r="C6" t="n">
-        <v>31.46770168608921</v>
+        <v>31.46770168608924</v>
       </c>
       <c r="D6" t="n">
-        <v>47.88484528894169</v>
+        <v>47.88484528894177</v>
       </c>
       <c r="E6" t="n">
-        <v>32.59864432404844</v>
+        <v>32.59864432404848</v>
       </c>
       <c r="F6" t="n">
-        <v>35.15214171658905</v>
+        <v>48.27816113993494</v>
       </c>
       <c r="G6" t="n">
-        <v>60.39066701358004</v>
+        <v>47.26464759023417</v>
       </c>
       <c r="H6" t="n">
-        <v>31.7745465713636</v>
+        <v>31.77454657136363</v>
       </c>
       <c r="I6" t="n">
-        <v>48.07360322580028</v>
+        <v>34.94758380245447</v>
       </c>
       <c r="J6" t="n">
-        <v>53.53500500071549</v>
+        <v>53.5350050007155</v>
       </c>
       <c r="K6" t="n">
-        <v>35.64303742848831</v>
+        <v>48.76905685183424</v>
       </c>
       <c r="L6" t="n">
-        <v>48.18663789991602</v>
+        <v>35.06061847657009</v>
       </c>
       <c r="M6" t="n">
-        <v>61.11313000173929</v>
+        <v>61.1131300017393</v>
       </c>
       <c r="N6" t="n">
-        <v>33.11369695891423</v>
+        <v>33.11369695891425</v>
       </c>
       <c r="O6" t="n">
-        <v>47.74786912365661</v>
+        <v>34.94033936778357</v>
       </c>
       <c r="P6" t="n">
-        <v>50.08874728996163</v>
+        <v>50.08874728996172</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.91373130767592</v>
+        <v>46.913731307676</v>
       </c>
       <c r="R6" t="n">
-        <v>45.36974635096027</v>
+        <v>45.36974635096028</v>
       </c>
       <c r="S6" t="n">
-        <v>37.15706487431547</v>
+        <v>37.15706487431552</v>
       </c>
       <c r="T6" t="n">
-        <v>33.71991743601497</v>
+        <v>33.719917436015</v>
       </c>
       <c r="U6" t="n">
-        <v>49.69873182336524</v>
+        <v>36.57271240001938</v>
       </c>
       <c r="V6" t="n">
-        <v>47.15817116591834</v>
+        <v>47.15817116591835</v>
       </c>
       <c r="W6" t="n">
-        <v>48.06071540573873</v>
+        <v>36.17842140236897</v>
       </c>
       <c r="X6" t="n">
-        <v>36.16916257921038</v>
+        <v>36.16916257921046</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.55193459322758</v>
+        <v>38.55193459322763</v>
       </c>
       <c r="Z6" t="n">
-        <v>50.30080591734317</v>
+        <v>37.17478649399726</v>
       </c>
       <c r="AA6" t="n">
-        <v>34.80004681831833</v>
+        <v>47.92606624166424</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.34500524614681</v>
+        <v>45.34500524614689</v>
       </c>
     </row>
     <row r="7">
@@ -3606,82 +3606,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.89246617489253</v>
+        <v>25.89246617489259</v>
       </c>
       <c r="C7" t="n">
-        <v>18.60810769134709</v>
+        <v>18.6081076913471</v>
       </c>
       <c r="D7" t="n">
-        <v>21.89923187085367</v>
+        <v>21.89923187085369</v>
       </c>
       <c r="E7" t="n">
-        <v>19.73905032930632</v>
+        <v>19.73905032930633</v>
       </c>
       <c r="F7" t="n">
-        <v>22.29254772184687</v>
+        <v>22.29254772184689</v>
       </c>
       <c r="G7" t="n">
         <v>34.40505359549199</v>
       </c>
       <c r="H7" t="n">
-        <v>18.91495257662144</v>
+        <v>18.91495257662147</v>
       </c>
       <c r="I7" t="n">
-        <v>22.08798980771232</v>
+        <v>22.08798980771234</v>
       </c>
       <c r="J7" t="n">
-        <v>27.54939158262742</v>
+        <v>27.54939158262741</v>
       </c>
       <c r="K7" t="n">
-        <v>22.78344343374619</v>
+        <v>22.78344343374623</v>
       </c>
       <c r="L7" t="n">
-        <v>22.20102448182795</v>
+        <v>22.20102448182798</v>
       </c>
       <c r="M7" t="n">
-        <v>35.12751658365119</v>
+        <v>35.12751658365117</v>
       </c>
       <c r="N7" t="n">
-        <v>20.23996775105531</v>
+        <v>20.23996775105533</v>
       </c>
       <c r="O7" t="n">
-        <v>22.06652318243709</v>
+        <v>22.06652318243711</v>
       </c>
       <c r="P7" t="n">
-        <v>24.4074205575232</v>
+        <v>24.40742055752329</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.92811788958788</v>
+        <v>20.92811788958791</v>
       </c>
       <c r="R7" t="n">
-        <v>19.38413293287227</v>
+        <v>19.38413293287228</v>
       </c>
       <c r="S7" t="n">
-        <v>24.29747087957332</v>
+        <v>24.29747087957338</v>
       </c>
       <c r="T7" t="n">
-        <v>20.86032344127281</v>
+        <v>20.86032344127284</v>
       </c>
       <c r="U7" t="n">
-        <v>23.70863755024973</v>
+        <v>23.7086375502498</v>
       </c>
       <c r="V7" t="n">
-        <v>21.17255774783036</v>
+        <v>21.17255774783034</v>
       </c>
       <c r="W7" t="n">
-        <v>22.3795092541701</v>
+        <v>22.37950925417012</v>
       </c>
       <c r="X7" t="n">
-        <v>23.30956858446827</v>
+        <v>23.30956858446828</v>
       </c>
       <c r="Y7" t="n">
-        <v>24.90540253976086</v>
+        <v>24.90540253976091</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.31519249925512</v>
+        <v>24.31519249925513</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.94045282357618</v>
+        <v>21.9404528235762</v>
       </c>
       <c r="AB7" t="n">
         <v>32.41435110007281</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.27385580434168</v>
+        <v>38.27385580434171</v>
       </c>
       <c r="C8" t="n">
-        <v>42.26334077878352</v>
+        <v>42.26334077878353</v>
       </c>
       <c r="D8" t="n">
-        <v>45.55446495829018</v>
+        <v>45.55446495829013</v>
       </c>
       <c r="E8" t="n">
-        <v>43.39428341674279</v>
+        <v>37.39129433282316</v>
       </c>
       <c r="F8" t="n">
-        <v>36.43027040193091</v>
+        <v>36.4302704019309</v>
       </c>
       <c r="G8" t="n">
-        <v>58.06028668292842</v>
+        <v>60.39799156624537</v>
       </c>
       <c r="H8" t="n">
-        <v>42.5701856640579</v>
+        <v>42.57018566405792</v>
       </c>
       <c r="I8" t="n">
-        <v>45.7432228951488</v>
+        <v>45.74322289514879</v>
       </c>
       <c r="J8" t="n">
-        <v>51.20462467006388</v>
+        <v>51.20462467006382</v>
       </c>
       <c r="K8" t="n">
-        <v>46.43867652118264</v>
+        <v>46.43867652118269</v>
       </c>
       <c r="L8" t="n">
-        <v>45.85625756926434</v>
+        <v>45.8562575692644</v>
       </c>
       <c r="M8" t="n">
-        <v>58.78274967108769</v>
+        <v>58.78274967108747</v>
       </c>
       <c r="N8" t="n">
         <v>35.15608608578346</v>
       </c>
       <c r="O8" t="n">
-        <v>39.38431310948502</v>
+        <v>39.38431310948506</v>
       </c>
       <c r="P8" t="n">
-        <v>41.13652406501964</v>
+        <v>41.1365240650197</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.09393996646932</v>
+        <v>31.09393996646934</v>
       </c>
       <c r="R8" t="n">
-        <v>43.03936602030872</v>
+        <v>43.03936602030873</v>
       </c>
       <c r="S8" t="n">
-        <v>47.95270396700973</v>
+        <v>47.95270396700981</v>
       </c>
       <c r="T8" t="n">
-        <v>44.51555652870925</v>
+        <v>44.51555652870928</v>
       </c>
       <c r="U8" t="n">
-        <v>40.42781785126599</v>
+        <v>41.86233382430346</v>
       </c>
       <c r="V8" t="n">
-        <v>44.82779083526673</v>
+        <v>41.74272365183204</v>
       </c>
       <c r="W8" t="n">
-        <v>46.03695797548454</v>
+        <v>46.0369579754846</v>
       </c>
       <c r="X8" t="n">
-        <v>34.50866081611154</v>
+        <v>34.50866081611159</v>
       </c>
       <c r="Y8" t="n">
-        <v>59.7641363521664</v>
+        <v>59.76413635216654</v>
       </c>
       <c r="Z8" t="n">
-        <v>47.97042558669163</v>
+        <v>36.48716469842383</v>
       </c>
       <c r="AA8" t="n">
-        <v>45.59568591101265</v>
+        <v>45.59568591101263</v>
       </c>
       <c r="AB8" t="n">
-        <v>67.84605638339123</v>
+        <v>67.84605638339121</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.14262727504946</v>
+        <v>37.1426272750495</v>
       </c>
       <c r="C9" t="n">
-        <v>34.45240180190229</v>
+        <v>34.45240180190228</v>
       </c>
       <c r="D9" t="n">
-        <v>37.74352598140879</v>
+        <v>37.74352598140887</v>
       </c>
       <c r="E9" t="n">
-        <v>35.58334443986148</v>
+        <v>34.52303763879429</v>
       </c>
       <c r="F9" t="n">
-        <v>38.13684183240208</v>
+        <v>27.54611077704723</v>
       </c>
       <c r="G9" t="n">
-        <v>50.24934770604722</v>
+        <v>50.24934817225198</v>
       </c>
       <c r="H9" t="n">
-        <v>34.75924668717668</v>
+        <v>34.75924668717666</v>
       </c>
       <c r="I9" t="n">
-        <v>37.93228391826753</v>
+        <v>37.93228391826752</v>
       </c>
       <c r="J9" t="n">
-        <v>43.39368569318262</v>
+        <v>43.39368569318263</v>
       </c>
       <c r="K9" t="n">
         <v>38.62773754430143</v>
       </c>
       <c r="L9" t="n">
-        <v>38.0453185923832</v>
+        <v>38.04531859238317</v>
       </c>
       <c r="M9" t="n">
-        <v>50.9718106942064</v>
+        <v>50.97181069420642</v>
       </c>
       <c r="N9" t="n">
         <v>36.08426186161051</v>
       </c>
       <c r="O9" t="n">
-        <v>39.43339455533177</v>
+        <v>39.43339455533179</v>
       </c>
       <c r="P9" t="n">
-        <v>42.10540734444297</v>
+        <v>42.10540734444301</v>
       </c>
       <c r="Q9" t="n">
         <v>36.77241246634789</v>
       </c>
       <c r="R9" t="n">
-        <v>35.22842704342746</v>
+        <v>35.22842704342747</v>
       </c>
       <c r="S9" t="n">
-        <v>40.14176499012855</v>
+        <v>40.14176499012859</v>
       </c>
       <c r="T9" t="n">
-        <v>36.70461755182802</v>
+        <v>36.70461755182801</v>
       </c>
       <c r="U9" t="n">
-        <v>39.5574125158323</v>
+        <v>39.55741251583245</v>
       </c>
       <c r="V9" t="n">
-        <v>37.01685185838556</v>
+        <v>42.31837896706988</v>
       </c>
       <c r="W9" t="n">
-        <v>38.22380336472526</v>
+        <v>38.22380336472531</v>
       </c>
       <c r="X9" t="n">
-        <v>39.15386269502348</v>
+        <v>39.15386269502349</v>
       </c>
       <c r="Y9" t="n">
-        <v>40.74969665031607</v>
+        <v>40.74969665031608</v>
       </c>
       <c r="Z9" t="n">
-        <v>40.15948660981028</v>
+        <v>37.3896331159119</v>
       </c>
       <c r="AA9" t="n">
-        <v>37.78474693413136</v>
+        <v>37.78474693413138</v>
       </c>
       <c r="AB9" t="n">
-        <v>48.25864521062796</v>
+        <v>48.25864521062802</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.02268472976975</v>
+        <v>22.02268472976972</v>
       </c>
       <c r="C2" t="n">
-        <v>15.89437438478415</v>
+        <v>15.89437438478413</v>
       </c>
       <c r="D2" t="n">
-        <v>21.67315593412564</v>
+        <v>21.67315593412568</v>
       </c>
       <c r="E2" t="n">
-        <v>21.51057442984344</v>
+        <v>21.51057442984349</v>
       </c>
       <c r="F2" t="n">
-        <v>21.84065768993073</v>
+        <v>21.84065768993079</v>
       </c>
       <c r="G2" t="n">
-        <v>22.66256344278442</v>
+        <v>22.66256344278447</v>
       </c>
       <c r="H2" t="n">
-        <v>21.49315564351141</v>
+        <v>21.49315564351139</v>
       </c>
       <c r="I2" t="n">
-        <v>21.79655986511381</v>
+        <v>21.79655986511385</v>
       </c>
       <c r="J2" t="n">
-        <v>22.15364110547528</v>
+        <v>22.15364110547526</v>
       </c>
       <c r="K2" t="n">
-        <v>21.88141762430095</v>
+        <v>21.88141762430092</v>
       </c>
       <c r="L2" t="n">
-        <v>21.73624062522801</v>
+        <v>21.73624062522806</v>
       </c>
       <c r="M2" t="n">
-        <v>22.55174524981183</v>
+        <v>22.55174524981182</v>
       </c>
       <c r="N2" t="n">
-        <v>21.56825213461815</v>
+        <v>21.56825213461818</v>
       </c>
       <c r="O2" t="n">
-        <v>28.93293419049875</v>
+        <v>28.93293419049865</v>
       </c>
       <c r="P2" t="n">
-        <v>21.91968178819863</v>
+        <v>21.91968178819866</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.66136020698361</v>
+        <v>21.66136020698365</v>
       </c>
       <c r="R2" t="n">
-        <v>21.62650207510058</v>
+        <v>21.62650207510062</v>
       </c>
       <c r="S2" t="n">
-        <v>21.9252551794809</v>
+        <v>21.92525517948095</v>
       </c>
       <c r="T2" t="n">
-        <v>21.68439265008359</v>
+        <v>21.68439265008365</v>
       </c>
       <c r="U2" t="n">
-        <v>25.34303654521343</v>
+        <v>25.34303654521349</v>
       </c>
       <c r="V2" t="n">
-        <v>21.82640601188898</v>
+        <v>21.82640601188903</v>
       </c>
       <c r="W2" t="n">
-        <v>27.40174652955776</v>
+        <v>27.40174652955777</v>
       </c>
       <c r="X2" t="n">
         <v>21.8916976013072</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.26789018582519</v>
+        <v>22.26789018582522</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.31366175336123</v>
+        <v>28.31366175336127</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.7792067872159</v>
+        <v>21.77920678721595</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.57150861148232</v>
+        <v>22.5715086114823</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.53807092802807</v>
+        <v>24.53807092802812</v>
       </c>
       <c r="C3" t="n">
-        <v>11.33648860490307</v>
+        <v>11.33648860490306</v>
       </c>
       <c r="D3" t="n">
-        <v>22.06765862987742</v>
+        <v>22.06765862987748</v>
       </c>
       <c r="E3" t="n">
-        <v>20.88961691564188</v>
+        <v>20.88961691564185</v>
       </c>
       <c r="F3" t="n">
-        <v>23.26755793835071</v>
+        <v>23.26755793835073</v>
       </c>
       <c r="G3" t="n">
-        <v>29.07878250309486</v>
+        <v>29.07878250309482</v>
       </c>
       <c r="H3" t="n">
-        <v>20.78397023957728</v>
+        <v>20.78397023957723</v>
       </c>
       <c r="I3" t="n">
-        <v>22.95331874486712</v>
+        <v>22.95331874486711</v>
       </c>
       <c r="J3" t="n">
-        <v>25.47810376833857</v>
+        <v>25.47810376833858</v>
       </c>
       <c r="K3" t="n">
-        <v>23.54465419129922</v>
+        <v>23.54465419129917</v>
       </c>
       <c r="L3" t="n">
-        <v>22.51052438786214</v>
+        <v>22.51052438786213</v>
       </c>
       <c r="M3" t="n">
-        <v>29.16598006409603</v>
+        <v>29.165980064096</v>
       </c>
       <c r="N3" t="n">
-        <v>21.31723484402975</v>
+        <v>21.3172348440297</v>
       </c>
       <c r="O3" t="n">
         <v>33.9982630019223</v>
       </c>
       <c r="P3" t="n">
-        <v>23.8048952312748</v>
+        <v>23.80489523127482</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.98004018974436</v>
+        <v>21.98004018974435</v>
       </c>
       <c r="R3" t="n">
         <v>21.73877936656852</v>
       </c>
       <c r="S3" t="n">
-        <v>23.85005285598368</v>
+        <v>23.85005285598367</v>
       </c>
       <c r="T3" t="n">
-        <v>22.15100020370092</v>
+        <v>22.15100020370091</v>
       </c>
       <c r="U3" t="n">
-        <v>29.4384678630926</v>
+        <v>29.43846786309257</v>
       </c>
       <c r="V3" t="n">
-        <v>23.14292088678651</v>
+        <v>23.14292088678648</v>
       </c>
       <c r="W3" t="n">
-        <v>32.20661680831061</v>
+        <v>32.20661680831056</v>
       </c>
       <c r="X3" t="n">
-        <v>23.62584046053571</v>
+        <v>23.6258404605357</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.31429928659072</v>
+        <v>26.31429928659071</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.30551474895851</v>
+        <v>34.30551474895848</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.82256258630144</v>
+        <v>22.82256258630145</v>
       </c>
       <c r="AB3" t="n">
-        <v>28.49679944615954</v>
+        <v>28.49679944615952</v>
       </c>
     </row>
     <row r="4">
@@ -4202,31 +4202,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.22300070698345</v>
+        <v>20.22300070698343</v>
       </c>
       <c r="C4" t="n">
         <v>13.81665794729614</v>
       </c>
       <c r="D4" t="n">
-        <v>16.27491216899408</v>
+        <v>16.27491216899407</v>
       </c>
       <c r="E4" t="n">
         <v>14.4384792869398</v>
       </c>
       <c r="F4" t="n">
-        <v>18.16692155542735</v>
+        <v>18.16692155542733</v>
       </c>
       <c r="G4" t="n">
-        <v>27.4507251292361</v>
+        <v>27.45072512923609</v>
       </c>
       <c r="H4" t="n">
-        <v>14.24172608228116</v>
+        <v>14.24172608228115</v>
       </c>
       <c r="I4" t="n">
-        <v>17.66881633811849</v>
+        <v>17.66881633811848</v>
       </c>
       <c r="J4" t="n">
-        <v>21.67073326974903</v>
+        <v>21.67073326974902</v>
       </c>
       <c r="K4" t="n">
         <v>18.62732376463421</v>
@@ -4235,49 +4235,49 @@
         <v>16.98748277538724</v>
       </c>
       <c r="M4" t="n">
-        <v>27.70407030706276</v>
+        <v>27.70407030706274</v>
       </c>
       <c r="N4" t="n">
-        <v>15.089975495425</v>
+        <v>15.08997549542497</v>
       </c>
       <c r="O4" t="n">
-        <v>16.1903037837122</v>
+        <v>16.19030378371219</v>
       </c>
       <c r="P4" t="n">
-        <v>19.05953509824443</v>
+        <v>19.05953509824441</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.14167400462242</v>
+        <v>16.1416740046224</v>
       </c>
       <c r="R4" t="n">
         <v>15.74793536947058</v>
       </c>
       <c r="S4" t="n">
-        <v>19.12248911666432</v>
+        <v>19.12248911666431</v>
       </c>
       <c r="T4" t="n">
-        <v>16.4018360448841</v>
+        <v>16.40183604488408</v>
       </c>
       <c r="U4" t="n">
-        <v>18.70375101541945</v>
+        <v>18.70375101541944</v>
       </c>
       <c r="V4" t="n">
-        <v>17.80446035625249</v>
+        <v>17.80446035625248</v>
       </c>
       <c r="W4" t="n">
-        <v>17.68640493313329</v>
+        <v>17.68640493313328</v>
       </c>
       <c r="X4" t="n">
-        <v>18.7434408339434</v>
+        <v>18.74344083394339</v>
       </c>
       <c r="Y4" t="n">
-        <v>22.82768305694661</v>
+        <v>22.8276830569466</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.96527540644431</v>
+        <v>18.9652754064443</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.47280534045148</v>
+        <v>17.47280534045149</v>
       </c>
       <c r="AB4" t="n">
         <v>26.38124778882459</v>
@@ -4290,25 +4290,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>134.358943759233</v>
+        <v>134.3589437592331</v>
       </c>
       <c r="C5" t="n">
         <v>33.8786841032971</v>
       </c>
       <c r="D5" t="n">
-        <v>77.06744760946147</v>
+        <v>77.06744760946144</v>
       </c>
       <c r="E5" t="n">
-        <v>35.42001129504276</v>
+        <v>35.42001129504278</v>
       </c>
       <c r="F5" t="n">
-        <v>112.8269713895286</v>
+        <v>112.8269713895287</v>
       </c>
       <c r="G5" t="n">
-        <v>248.649530923073</v>
+        <v>248.6495309230735</v>
       </c>
       <c r="H5" t="n">
-        <v>41.61643384424067</v>
+        <v>41.61643384424086</v>
       </c>
       <c r="I5" t="n">
         <v>104.2706641404277</v>
@@ -4320,55 +4320,55 @@
         <v>113.8135564512455</v>
       </c>
       <c r="L5" t="n">
-        <v>85.84965356091425</v>
+        <v>85.84965356091428</v>
       </c>
       <c r="M5" t="n">
         <v>284.4146704161323</v>
       </c>
       <c r="N5" t="n">
-        <v>111.7975644674802</v>
+        <v>111.7975644674805</v>
       </c>
       <c r="O5" t="n">
-        <v>69.40766792172404</v>
+        <v>69.40766792172403</v>
       </c>
       <c r="P5" t="n">
-        <v>114.7975971361157</v>
+        <v>114.7975971361159</v>
       </c>
       <c r="Q5" t="n">
-        <v>72.93249457945115</v>
+        <v>72.93249457945117</v>
       </c>
       <c r="R5" t="n">
-        <v>69.8673895813008</v>
+        <v>69.8673895813009</v>
       </c>
       <c r="S5" t="n">
-        <v>118.6991192138537</v>
+        <v>118.6991192138539</v>
       </c>
       <c r="T5" t="n">
-        <v>80.94190053440046</v>
+        <v>80.94190053440052</v>
       </c>
       <c r="U5" t="n">
-        <v>115.5763660637416</v>
+        <v>115.5763660637407</v>
       </c>
       <c r="V5" t="n">
         <v>97.8995000279856</v>
       </c>
       <c r="W5" t="n">
-        <v>100.626811978755</v>
+        <v>100.6268119787549</v>
       </c>
       <c r="X5" t="n">
-        <v>119.9185313919324</v>
+        <v>119.9185313919325</v>
       </c>
       <c r="Y5" t="n">
-        <v>196.9154144690233</v>
+        <v>196.9154144690237</v>
       </c>
       <c r="Z5" t="n">
         <v>108.9682452730472</v>
       </c>
       <c r="AA5" t="n">
-        <v>97.22483145353603</v>
+        <v>97.2248314535362</v>
       </c>
       <c r="AB5" t="n">
-        <v>276.4469621679895</v>
+        <v>276.4469621679901</v>
       </c>
     </row>
     <row r="6">
@@ -4378,82 +4378,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.70176193064307</v>
+        <v>50.70567418643667</v>
       </c>
       <c r="C6" t="n">
-        <v>31.29541917095576</v>
+        <v>31.29541917095577</v>
       </c>
       <c r="D6" t="n">
-        <v>33.7536733926537</v>
+        <v>33.75367339265369</v>
       </c>
       <c r="E6" t="n">
-        <v>31.91724051059941</v>
+        <v>44.92115276639307</v>
       </c>
       <c r="F6" t="n">
         <v>35.64568277908702</v>
       </c>
       <c r="G6" t="n">
-        <v>44.92948635289571</v>
+        <v>57.93339860868929</v>
       </c>
       <c r="H6" t="n">
-        <v>44.7243995617344</v>
+        <v>31.72048730594075</v>
       </c>
       <c r="I6" t="n">
-        <v>35.14757756177812</v>
+        <v>35.14757756177811</v>
       </c>
       <c r="J6" t="n">
-        <v>39.14949449340868</v>
+        <v>52.15340674920227</v>
       </c>
       <c r="K6" t="n">
-        <v>49.1099972440874</v>
+        <v>49.10999724408738</v>
       </c>
       <c r="L6" t="n">
-        <v>34.46624399904688</v>
+        <v>47.47015625484046</v>
       </c>
       <c r="M6" t="n">
-        <v>45.1828315307224</v>
+        <v>45.18283153072235</v>
       </c>
       <c r="N6" t="n">
-        <v>32.58967739885804</v>
+        <v>32.58967739885802</v>
       </c>
       <c r="O6" t="n">
-        <v>33.6900056871452</v>
+        <v>46.37003138971642</v>
       </c>
       <c r="P6" t="n">
-        <v>49.23924729499504</v>
+        <v>35.50770162220731</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.62434748407559</v>
+        <v>46.62434748407557</v>
       </c>
       <c r="R6" t="n">
-        <v>46.23060884892382</v>
+        <v>46.23060884892379</v>
       </c>
       <c r="S6" t="n">
         <v>49.60516259611754</v>
       </c>
       <c r="T6" t="n">
-        <v>33.88059726854366</v>
+        <v>46.88450952433733</v>
       </c>
       <c r="U6" t="n">
-        <v>49.35145057113911</v>
+        <v>36.34753831534556</v>
       </c>
       <c r="V6" t="n">
-        <v>48.2871338357057</v>
+        <v>35.28322157991205</v>
       </c>
       <c r="W6" t="n">
-        <v>47.86610372743002</v>
+        <v>47.86610372743003</v>
       </c>
       <c r="X6" t="n">
-        <v>36.22220205760299</v>
+        <v>36.22220205760302</v>
       </c>
       <c r="Y6" t="n">
-        <v>41.27378318238537</v>
+        <v>41.2737831823854</v>
       </c>
       <c r="Z6" t="n">
-        <v>49.44794888589759</v>
+        <v>49.44794888589757</v>
       </c>
       <c r="AA6" t="n">
-        <v>47.95547881990468</v>
+        <v>47.9554788199047</v>
       </c>
       <c r="AB6" t="n">
         <v>43.92698788878964</v>
@@ -4469,82 +4469,82 @@
         <v>24.71472070718176</v>
       </c>
       <c r="C7" t="n">
-        <v>18.30837794749447</v>
+        <v>18.30837794749446</v>
       </c>
       <c r="D7" t="n">
-        <v>20.76663216919241</v>
+        <v>20.7666321691924</v>
       </c>
       <c r="E7" t="n">
-        <v>18.93019928713812</v>
+        <v>18.9301992871381</v>
       </c>
       <c r="F7" t="n">
         <v>22.65864155562569</v>
       </c>
       <c r="G7" t="n">
-        <v>31.9424451294344</v>
+        <v>31.94244512943441</v>
       </c>
       <c r="H7" t="n">
-        <v>18.7334460824795</v>
+        <v>18.73344608247948</v>
       </c>
       <c r="I7" t="n">
         <v>22.16053633831681</v>
       </c>
       <c r="J7" t="n">
-        <v>26.16245326994735</v>
+        <v>26.16245326994734</v>
       </c>
       <c r="K7" t="n">
-        <v>23.11904376483252</v>
+        <v>23.1190437648325</v>
       </c>
       <c r="L7" t="n">
         <v>21.47920277558555</v>
       </c>
       <c r="M7" t="n">
-        <v>32.19579030726111</v>
+        <v>32.1957903072611</v>
       </c>
       <c r="N7" t="n">
-        <v>19.58169549562331</v>
+        <v>19.58169549562329</v>
       </c>
       <c r="O7" t="n">
-        <v>20.68193614072422</v>
+        <v>20.68193614072421</v>
       </c>
       <c r="P7" t="n">
         <v>23.55116745525643</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.63339400482074</v>
+        <v>20.63339400482072</v>
       </c>
       <c r="R7" t="n">
-        <v>20.23965536966892</v>
+        <v>20.2396553696689</v>
       </c>
       <c r="S7" t="n">
         <v>23.61420911686264</v>
       </c>
       <c r="T7" t="n">
-        <v>20.89355604508241</v>
+        <v>20.8935560450824</v>
       </c>
       <c r="U7" t="n">
-        <v>23.35727564926273</v>
+        <v>23.35727564926274</v>
       </c>
       <c r="V7" t="n">
-        <v>22.29618035645082</v>
+        <v>22.2961803564508</v>
       </c>
       <c r="W7" t="n">
-        <v>22.17812493333164</v>
+        <v>22.17812493333162</v>
       </c>
       <c r="X7" t="n">
-        <v>23.2351608341417</v>
+        <v>23.23516083414168</v>
       </c>
       <c r="Y7" t="n">
-        <v>27.48442913341138</v>
+        <v>27.48442913341139</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.45699540664265</v>
+        <v>23.45699540664264</v>
       </c>
       <c r="AA7" t="n">
         <v>21.96452534064982</v>
       </c>
       <c r="AB7" t="n">
-        <v>30.87296778902289</v>
+        <v>30.87296778902291</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.02075152803981</v>
+        <v>37.02075152803978</v>
       </c>
       <c r="C8" t="n">
-        <v>41.77585864911255</v>
+        <v>41.7758586491125</v>
       </c>
       <c r="D8" t="n">
-        <v>44.23411287081048</v>
+        <v>44.23411287081043</v>
       </c>
       <c r="E8" t="n">
-        <v>42.3976799887562</v>
+        <v>36.45453716930127</v>
       </c>
       <c r="F8" t="n">
-        <v>36.70349582135898</v>
+        <v>36.70349582135895</v>
       </c>
       <c r="G8" t="n">
-        <v>55.40992583105252</v>
+        <v>57.72432517395766</v>
       </c>
       <c r="H8" t="n">
-        <v>42.20092678409758</v>
+        <v>42.20092678409749</v>
       </c>
       <c r="I8" t="n">
-        <v>45.6280170399349</v>
+        <v>45.62801703993484</v>
       </c>
       <c r="J8" t="n">
-        <v>49.62993397156546</v>
+        <v>49.62993397156538</v>
       </c>
       <c r="K8" t="n">
-        <v>46.58652446645065</v>
+        <v>46.58652446645058</v>
       </c>
       <c r="L8" t="n">
-        <v>44.94668347720365</v>
+        <v>44.94668347720359</v>
       </c>
       <c r="M8" t="n">
-        <v>55.66327100887918</v>
+        <v>55.66327100887911</v>
       </c>
       <c r="N8" t="n">
-        <v>34.3971852699244</v>
+        <v>34.39718526992435</v>
       </c>
       <c r="O8" t="n">
-        <v>37.8751557893547</v>
+        <v>37.87515578935463</v>
       </c>
       <c r="P8" t="n">
-        <v>40.16156954110544</v>
+        <v>40.16156954110538</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.74594517628564</v>
+        <v>30.74594517628561</v>
       </c>
       <c r="R8" t="n">
-        <v>43.70713607128699</v>
+        <v>43.70713607128694</v>
       </c>
       <c r="S8" t="n">
-        <v>47.08168981848073</v>
+        <v>47.08168981848068</v>
       </c>
       <c r="T8" t="n">
-        <v>44.36103674670048</v>
+        <v>44.36103674670044</v>
       </c>
       <c r="U8" t="n">
-        <v>39.95752225451095</v>
+        <v>41.37779445964721</v>
       </c>
       <c r="V8" t="n">
-        <v>45.76366105806889</v>
+        <v>42.71038981756086</v>
       </c>
       <c r="W8" t="n">
-        <v>45.64779918029134</v>
+        <v>45.64779918029129</v>
       </c>
       <c r="X8" t="n">
-        <v>34.3706810657005</v>
+        <v>34.37068106570042</v>
       </c>
       <c r="Y8" t="n">
         <v>62.04533074243984</v>
       </c>
       <c r="Z8" t="n">
-        <v>46.92447610826075</v>
+        <v>35.55569656561599</v>
       </c>
       <c r="AA8" t="n">
-        <v>45.43200604226789</v>
+        <v>45.43200604226784</v>
       </c>
       <c r="AB8" t="n">
-        <v>65.9995161969354</v>
+        <v>65.99951619693539</v>
       </c>
     </row>
     <row r="9">
@@ -4642,70 +4642,70 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.90123468924475</v>
+        <v>34.90123468924474</v>
       </c>
       <c r="C9" t="n">
-        <v>32.76678903804034</v>
+        <v>32.76678903804033</v>
       </c>
       <c r="D9" t="n">
-        <v>35.22504325973827</v>
+        <v>35.22504325973824</v>
       </c>
       <c r="E9" t="n">
-        <v>33.38861037768398</v>
+        <v>32.40267434560025</v>
       </c>
       <c r="F9" t="n">
-        <v>37.11705264617153</v>
+        <v>27.26916322813189</v>
       </c>
       <c r="G9" t="n">
-        <v>46.4008562199803</v>
+        <v>46.40085673454383</v>
       </c>
       <c r="H9" t="n">
-        <v>33.19185717302535</v>
+        <v>33.19185717302533</v>
       </c>
       <c r="I9" t="n">
-        <v>36.6189474288627</v>
+        <v>36.61894742886267</v>
       </c>
       <c r="J9" t="n">
-        <v>40.62086436049321</v>
+        <v>40.6208643604932</v>
       </c>
       <c r="K9" t="n">
         <v>37.57745485537836</v>
       </c>
       <c r="L9" t="n">
-        <v>35.93761386613144</v>
+        <v>35.9376138661314</v>
       </c>
       <c r="M9" t="n">
-        <v>46.65420139780696</v>
+        <v>46.65420139780691</v>
       </c>
       <c r="N9" t="n">
-        <v>34.04010658616917</v>
+        <v>34.04010658616913</v>
       </c>
       <c r="O9" t="n">
-        <v>36.55613666773034</v>
+        <v>36.55613666773031</v>
       </c>
       <c r="P9" t="n">
-        <v>39.7332587210341</v>
+        <v>39.73325872103406</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.09180560993018</v>
+        <v>35.09180560993015</v>
       </c>
       <c r="R9" t="n">
-        <v>34.69806646021479</v>
+        <v>34.69806646021475</v>
       </c>
       <c r="S9" t="n">
-        <v>38.07262020740851</v>
+        <v>38.07262020740852</v>
       </c>
       <c r="T9" t="n">
-        <v>35.35196713562823</v>
+        <v>35.35196713562824</v>
       </c>
       <c r="U9" t="n">
         <v>37.81890818243008</v>
       </c>
       <c r="V9" t="n">
-        <v>36.75459144699669</v>
+        <v>41.6842661195568</v>
       </c>
       <c r="W9" t="n">
-        <v>36.63653602387748</v>
+        <v>36.63653602387746</v>
       </c>
       <c r="X9" t="n">
         <v>37.69357192468757</v>
@@ -4714,10 +4714,10 @@
         <v>41.94284022395725</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.91540649718851</v>
+        <v>35.33983261701339</v>
       </c>
       <c r="AA9" t="n">
-        <v>36.42293643119567</v>
+        <v>36.42293643119568</v>
       </c>
       <c r="AB9" t="n">
         <v>45.33137887956877</v>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.61400852989945</v>
+        <v>20.61400852989958</v>
       </c>
       <c r="C2" t="n">
-        <v>14.89430063599209</v>
+        <v>14.89430063599207</v>
       </c>
       <c r="D2" t="n">
-        <v>20.49253495581512</v>
+        <v>20.49253495581511</v>
       </c>
       <c r="E2" t="n">
-        <v>20.48379986586477</v>
+        <v>20.48379986586482</v>
       </c>
       <c r="F2" t="n">
-        <v>20.48950182873286</v>
+        <v>20.48950182873284</v>
       </c>
       <c r="G2" t="n">
-        <v>20.83509127848032</v>
+        <v>20.83509127848031</v>
       </c>
       <c r="H2" t="n">
-        <v>20.57023197479116</v>
+        <v>20.57023197479119</v>
       </c>
       <c r="I2" t="n">
-        <v>20.53110697621932</v>
+        <v>20.53110697621933</v>
       </c>
       <c r="J2" t="n">
-        <v>20.69422904142775</v>
+        <v>20.69422904142772</v>
       </c>
       <c r="K2" t="n">
-        <v>20.57251443398583</v>
+        <v>20.57251443398582</v>
       </c>
       <c r="L2" t="n">
-        <v>20.6280604616401</v>
+        <v>20.62806046164009</v>
       </c>
       <c r="M2" t="n">
-        <v>20.84507742778385</v>
+        <v>20.84507742778383</v>
       </c>
       <c r="N2" t="n">
-        <v>20.55210486476421</v>
+        <v>20.55210486476419</v>
       </c>
       <c r="O2" t="n">
-        <v>27.48029743184424</v>
+        <v>27.48029743184427</v>
       </c>
       <c r="P2" t="n">
-        <v>20.63972502470748</v>
+        <v>20.63972502470745</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.57384532878837</v>
+        <v>20.57384532878839</v>
       </c>
       <c r="R2" t="n">
-        <v>20.51347717086399</v>
+        <v>20.51347717086394</v>
       </c>
       <c r="S2" t="n">
-        <v>20.60572692020297</v>
+        <v>20.60572692020291</v>
       </c>
       <c r="T2" t="n">
-        <v>20.51135397030392</v>
+        <v>20.51135397030391</v>
       </c>
       <c r="U2" t="n">
-        <v>23.97477726494252</v>
+        <v>23.9747772649426</v>
       </c>
       <c r="V2" t="n">
         <v>20.51669449754969</v>
       </c>
       <c r="W2" t="n">
-        <v>26.18424637773773</v>
+        <v>26.18424637773784</v>
       </c>
       <c r="X2" t="n">
-        <v>20.59223160628564</v>
+        <v>20.59223160628571</v>
       </c>
       <c r="Y2" t="n">
         <v>20.54508138409477</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.89304015231815</v>
+        <v>26.89304015231807</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.59358339857557</v>
+        <v>20.59358339857555</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.77652248237357</v>
+        <v>20.77652248237356</v>
       </c>
     </row>
     <row r="3">
@@ -4974,34 +4974,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.89663565890067</v>
+        <v>20.89663565890065</v>
       </c>
       <c r="C3" t="n">
         <v>10.502801528062</v>
       </c>
       <c r="D3" t="n">
-        <v>20.03830862596696</v>
+        <v>20.03830862596695</v>
       </c>
       <c r="E3" t="n">
-        <v>19.958603418382</v>
+        <v>19.95860341838198</v>
       </c>
       <c r="F3" t="n">
-        <v>20.01769820511583</v>
+        <v>20.01769820511582</v>
       </c>
       <c r="G3" t="n">
-        <v>22.46165062487628</v>
+        <v>22.46165062487636</v>
       </c>
       <c r="H3" t="n">
-        <v>20.5980483057907</v>
+        <v>20.5980483057906</v>
       </c>
       <c r="I3" t="n">
-        <v>20.31493274879815</v>
+        <v>20.31493274879809</v>
       </c>
       <c r="J3" t="n">
-        <v>21.46750703986072</v>
+        <v>21.46750703986081</v>
       </c>
       <c r="K3" t="n">
-        <v>20.60858575864413</v>
+        <v>20.60858575864422</v>
       </c>
       <c r="L3" t="n">
         <v>20.9984680435342</v>
@@ -5010,49 +5010,49 @@
         <v>23.38052008497102</v>
       </c>
       <c r="N3" t="n">
-        <v>20.46150820273857</v>
+        <v>20.46150820273856</v>
       </c>
       <c r="O3" t="n">
-        <v>31.88876110158803</v>
+        <v>31.88876110158804</v>
       </c>
       <c r="P3" t="n">
-        <v>21.07975352932432</v>
+        <v>21.07975352932434</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.61658650790672</v>
+        <v>20.61658650790668</v>
       </c>
       <c r="R3" t="n">
-        <v>20.18938408490849</v>
+        <v>20.18938408490852</v>
       </c>
       <c r="S3" t="n">
-        <v>20.83505564642519</v>
+        <v>20.8350556464252</v>
       </c>
       <c r="T3" t="n">
-        <v>20.17364782132345</v>
+        <v>20.17364782132346</v>
       </c>
       <c r="U3" t="n">
-        <v>26.82806656545964</v>
+        <v>26.82806656545963</v>
       </c>
       <c r="V3" t="n">
-        <v>20.20714677445131</v>
+        <v>20.20714677445143</v>
       </c>
       <c r="W3" t="n">
-        <v>30.78173152645657</v>
+        <v>30.78173152645674</v>
       </c>
       <c r="X3" t="n">
         <v>20.75021912556937</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.41153785601254</v>
+        <v>20.41153785601259</v>
       </c>
       <c r="Z3" t="n">
-        <v>31.37209965951664</v>
+        <v>31.37209965951671</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.75741253469018</v>
+        <v>20.75741253469017</v>
       </c>
       <c r="AB3" t="n">
-        <v>22.08161526476782</v>
+        <v>22.08161526476778</v>
       </c>
     </row>
     <row r="4">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.26402688343763</v>
+        <v>14.26402688343762</v>
       </c>
       <c r="C4" t="n">
         <v>12.28958314210003</v>
@@ -5074,7 +5074,7 @@
         <v>12.79326012422068</v>
       </c>
       <c r="F4" t="n">
-        <v>12.85766641784827</v>
+        <v>12.85766641784826</v>
       </c>
       <c r="G4" t="n">
         <v>16.76125823174729</v>
@@ -5089,10 +5089,10 @@
         <v>15.14073978247963</v>
       </c>
       <c r="K4" t="n">
-        <v>13.79533198186595</v>
+        <v>13.79533198186594</v>
       </c>
       <c r="L4" t="n">
-        <v>14.42274991665582</v>
+        <v>14.42274991665583</v>
       </c>
       <c r="M4" t="n">
         <v>18.40424503135301</v>
@@ -5107,22 +5107,22 @@
         <v>14.55450652246592</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.81036505090265</v>
+        <v>13.81036505090264</v>
       </c>
       <c r="R4" t="n">
-        <v>13.12847893642143</v>
+        <v>13.12847893642142</v>
       </c>
       <c r="S4" t="n">
-        <v>14.17048229218634</v>
+        <v>14.17048229218633</v>
       </c>
       <c r="T4" t="n">
-        <v>13.10449640937528</v>
+        <v>13.10449640937527</v>
       </c>
       <c r="U4" t="n">
         <v>14.78180072138945</v>
       </c>
       <c r="V4" t="n">
-        <v>12.97729173495497</v>
+        <v>12.97729173495495</v>
       </c>
       <c r="W4" t="n">
         <v>15.67202728015047</v>
@@ -5153,19 +5153,19 @@
         <v>63.70944368473182</v>
       </c>
       <c r="C5" t="n">
-        <v>31.19431507197439</v>
+        <v>31.19431507197434</v>
       </c>
       <c r="D5" t="n">
-        <v>42.56879671526212</v>
+        <v>42.56879671526213</v>
       </c>
       <c r="E5" t="n">
-        <v>31.04705575695834</v>
+        <v>31.04705575695835</v>
       </c>
       <c r="F5" t="n">
-        <v>42.49781915825385</v>
+        <v>42.4978191582542</v>
       </c>
       <c r="G5" t="n">
-        <v>103.7727176170919</v>
+        <v>103.7727176170921</v>
       </c>
       <c r="H5" t="n">
         <v>62.06158618238142</v>
@@ -5174,61 +5174,61 @@
         <v>51.54849219528403</v>
       </c>
       <c r="J5" t="n">
-        <v>79.88622567567057</v>
+        <v>79.88622567567053</v>
       </c>
       <c r="K5" t="n">
-        <v>59.34975294969711</v>
+        <v>59.34975294969699</v>
       </c>
       <c r="L5" t="n">
-        <v>67.5687328617221</v>
+        <v>67.56873286172211</v>
       </c>
       <c r="M5" t="n">
         <v>143.856524444545</v>
       </c>
       <c r="N5" t="n">
-        <v>75.9422096465338</v>
+        <v>75.94220964653375</v>
       </c>
       <c r="O5" t="n">
-        <v>51.50078310498841</v>
+        <v>51.50078310498839</v>
       </c>
       <c r="P5" t="n">
         <v>68.96708922361125</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.80092893367561</v>
+        <v>58.8009289336756</v>
       </c>
       <c r="R5" t="n">
-        <v>47.9368068769696</v>
+        <v>47.93680687696955</v>
       </c>
       <c r="S5" t="n">
-        <v>60.56492917666721</v>
+        <v>60.56492917666714</v>
       </c>
       <c r="T5" t="n">
-        <v>47.15918011156048</v>
+        <v>47.15918011156044</v>
       </c>
       <c r="U5" t="n">
-        <v>77.28809255424066</v>
+        <v>77.28809255424055</v>
       </c>
       <c r="V5" t="n">
-        <v>45.54468307468586</v>
+        <v>45.54468307468533</v>
       </c>
       <c r="W5" t="n">
-        <v>93.95377163105167</v>
+        <v>93.95377163105152</v>
       </c>
       <c r="X5" t="n">
-        <v>64.06743118983513</v>
+        <v>64.06743118983509</v>
       </c>
       <c r="Y5" t="n">
-        <v>52.79177664301565</v>
+        <v>52.79177664301566</v>
       </c>
       <c r="Z5" t="n">
-        <v>67.08110939129962</v>
+        <v>67.08110939129955</v>
       </c>
       <c r="AA5" t="n">
-        <v>62.99111817389056</v>
+        <v>62.99111817389055</v>
       </c>
       <c r="AB5" t="n">
-        <v>108.5476396739609</v>
+        <v>108.5476396739608</v>
       </c>
     </row>
     <row r="6">
@@ -5238,82 +5238,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.8333339506134</v>
+        <v>32.83333395061339</v>
       </c>
       <c r="C6" t="n">
-        <v>44.143014442325</v>
+        <v>44.14301444232499</v>
       </c>
       <c r="D6" t="n">
-        <v>44.74535828377505</v>
+        <v>31.46123405072572</v>
       </c>
       <c r="E6" t="n">
-        <v>44.64669142444569</v>
+        <v>31.36256719139632</v>
       </c>
       <c r="F6" t="n">
-        <v>44.71109771807325</v>
+        <v>44.71109771807326</v>
       </c>
       <c r="G6" t="n">
-        <v>35.33056529892298</v>
+        <v>48.6146895319723</v>
       </c>
       <c r="H6" t="n">
-        <v>32.33885762245514</v>
+        <v>32.33885762245512</v>
       </c>
       <c r="I6" t="n">
-        <v>45.18104699824703</v>
+        <v>31.89692276519773</v>
       </c>
       <c r="J6" t="n">
-        <v>33.71004684965536</v>
+        <v>33.71004684965534</v>
       </c>
       <c r="K6" t="n">
-        <v>45.64876328209102</v>
+        <v>32.36463904904158</v>
       </c>
       <c r="L6" t="n">
-        <v>46.27618121688085</v>
+        <v>32.99205698383147</v>
       </c>
       <c r="M6" t="n">
-        <v>36.97355209852875</v>
+        <v>50.25767633157808</v>
       </c>
       <c r="N6" t="n">
-        <v>32.14020390467146</v>
+        <v>32.14020390467143</v>
       </c>
       <c r="O6" t="n">
-        <v>45.07439745153987</v>
+        <v>45.07439745153992</v>
       </c>
       <c r="P6" t="n">
-        <v>46.07325225988225</v>
+        <v>32.02122705403884</v>
       </c>
       <c r="Q6" t="n">
-        <v>45.66379635112766</v>
+        <v>45.66379635112764</v>
       </c>
       <c r="R6" t="n">
-        <v>44.98191023664636</v>
+        <v>31.69778600359705</v>
       </c>
       <c r="S6" t="n">
-        <v>46.02391359241135</v>
+        <v>32.73978935936201</v>
       </c>
       <c r="T6" t="n">
-        <v>31.67380347655098</v>
+        <v>44.95792770960031</v>
       </c>
       <c r="U6" t="n">
-        <v>46.76411071657374</v>
+        <v>33.47998648352441</v>
       </c>
       <c r="V6" t="n">
-        <v>31.5465988021306</v>
+        <v>44.83072303517993</v>
       </c>
       <c r="W6" t="n">
         <v>35.23491699193158</v>
       </c>
       <c r="X6" t="n">
-        <v>32.58735358051501</v>
+        <v>32.58735358051499</v>
       </c>
       <c r="Y6" t="n">
-        <v>32.89351862114317</v>
+        <v>32.89351862114314</v>
       </c>
       <c r="Z6" t="n">
-        <v>33.06513927925185</v>
+        <v>46.34926351230118</v>
       </c>
       <c r="AA6" t="n">
-        <v>32.60262269628488</v>
+        <v>45.88674692933424</v>
       </c>
       <c r="AB6" t="n">
         <v>34.70327973887201</v>
@@ -5332,16 +5332,16 @@
         <v>16.71637209860818</v>
       </c>
       <c r="D7" t="n">
-        <v>17.31871594005821</v>
+        <v>17.31871594005822</v>
       </c>
       <c r="E7" t="n">
-        <v>17.22004908072885</v>
+        <v>17.22004908072883</v>
       </c>
       <c r="F7" t="n">
-        <v>17.28445537435642</v>
+        <v>17.28445537435641</v>
       </c>
       <c r="G7" t="n">
-        <v>21.18804718825545</v>
+        <v>21.18804718825544</v>
       </c>
       <c r="H7" t="n">
         <v>18.19633951178761</v>
@@ -5359,31 +5359,31 @@
         <v>18.84953887316397</v>
       </c>
       <c r="M7" t="n">
-        <v>22.83103398786118</v>
+        <v>22.83103398786117</v>
       </c>
       <c r="N7" t="n">
-        <v>17.99158546515002</v>
+        <v>17.99158546515001</v>
       </c>
       <c r="O7" t="n">
-        <v>17.98234365213203</v>
+        <v>17.98234365213202</v>
       </c>
       <c r="P7" t="n">
-        <v>18.98120854610913</v>
+        <v>18.98120854610914</v>
       </c>
       <c r="Q7" t="n">
         <v>18.23715400741079</v>
       </c>
       <c r="R7" t="n">
-        <v>17.55526789292957</v>
+        <v>17.55526789292956</v>
       </c>
       <c r="S7" t="n">
-        <v>18.59727124869449</v>
+        <v>18.59727124869448</v>
       </c>
       <c r="T7" t="n">
-        <v>17.53128536588343</v>
+        <v>17.53128536588344</v>
       </c>
       <c r="U7" t="n">
-        <v>19.33501101268263</v>
+        <v>19.33501101268261</v>
       </c>
       <c r="V7" t="n">
         <v>17.40408069146311</v>
@@ -5395,10 +5395,10 @@
         <v>18.44483546984752</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.9122520200279</v>
+        <v>17.91225202002791</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.92262116858437</v>
+        <v>18.92262116858436</v>
       </c>
       <c r="AA7" t="n">
         <v>18.4601045856174</v>
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.53837316338237</v>
+        <v>31.53837316338236</v>
       </c>
       <c r="C8" t="n">
-        <v>40.96418229198695</v>
+        <v>40.96418229198694</v>
       </c>
       <c r="D8" t="n">
-        <v>41.566526133437</v>
+        <v>41.56652613343698</v>
       </c>
       <c r="E8" t="n">
-        <v>41.46785927410761</v>
+        <v>35.39756090711028</v>
       </c>
       <c r="F8" t="n">
-        <v>31.90803885746169</v>
+        <v>31.90803885746172</v>
       </c>
       <c r="G8" t="n">
-        <v>45.43585738163421</v>
+        <v>47.79977408001915</v>
       </c>
       <c r="H8" t="n">
-        <v>42.4441497051664</v>
+        <v>42.44414970516634</v>
       </c>
       <c r="I8" t="n">
         <v>42.00221484790897</v>
       </c>
       <c r="J8" t="n">
-        <v>43.81533893236659</v>
+        <v>43.81533893236656</v>
       </c>
       <c r="K8" t="n">
-        <v>42.46993113175287</v>
+        <v>42.46993113175284</v>
       </c>
       <c r="L8" t="n">
-        <v>43.09734906654274</v>
+        <v>43.09734906654273</v>
       </c>
       <c r="M8" t="n">
-        <v>47.07884418123994</v>
+        <v>47.07884418123965</v>
       </c>
       <c r="N8" t="n">
-        <v>33.40229246378804</v>
+        <v>33.40229246378802</v>
       </c>
       <c r="O8" t="n">
-        <v>35.82165027329597</v>
+        <v>35.82165027329595</v>
       </c>
       <c r="P8" t="n">
-        <v>36.22522802589275</v>
+        <v>36.22522802589272</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.84430144360155</v>
+        <v>28.84430144360151</v>
       </c>
       <c r="R8" t="n">
-        <v>41.80307808630833</v>
+        <v>41.80307808630831</v>
       </c>
       <c r="S8" t="n">
-        <v>42.84508144207329</v>
+        <v>42.84508144207324</v>
       </c>
       <c r="T8" t="n">
-        <v>41.77909555926222</v>
+        <v>41.77909555926217</v>
       </c>
       <c r="U8" t="n">
-        <v>36.56843160055881</v>
+        <v>38.0191302754321</v>
       </c>
       <c r="V8" t="n">
-        <v>41.6518908848419</v>
+        <v>38.53400369841429</v>
       </c>
       <c r="W8" t="n">
         <v>44.34886690725232</v>
       </c>
       <c r="X8" t="n">
-        <v>30.0968387347497</v>
+        <v>30.09683873474964</v>
       </c>
       <c r="Y8" t="n">
-        <v>53.4919315438587</v>
+        <v>53.49193154385861</v>
       </c>
       <c r="Z8" t="n">
-        <v>43.17043136196314</v>
+        <v>31.55841294198932</v>
       </c>
       <c r="AA8" t="n">
-        <v>42.70791477899618</v>
+        <v>42.70791477899616</v>
       </c>
       <c r="AB8" t="n">
-        <v>56.6963525320335</v>
+        <v>56.69635253203346</v>
       </c>
     </row>
     <row r="9">
@@ -5502,67 +5502,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.00811526588056</v>
+        <v>29.00811526588058</v>
       </c>
       <c r="C9" t="n">
-        <v>31.29591587570408</v>
+        <v>31.29591587570411</v>
       </c>
       <c r="D9" t="n">
-        <v>31.89825971715412</v>
+        <v>31.89825971715415</v>
       </c>
       <c r="E9" t="n">
-        <v>31.79959285782476</v>
+        <v>30.81588470650347</v>
       </c>
       <c r="F9" t="n">
-        <v>31.86399915145233</v>
+        <v>22.03836186535598</v>
       </c>
       <c r="G9" t="n">
-        <v>35.76759096535134</v>
+        <v>35.76759156278712</v>
       </c>
       <c r="H9" t="n">
-        <v>32.77588328888353</v>
+        <v>32.77588328888355</v>
       </c>
       <c r="I9" t="n">
-        <v>32.33394843162613</v>
+        <v>32.33394843162614</v>
       </c>
       <c r="J9" t="n">
         <v>34.14707251608371</v>
       </c>
       <c r="K9" t="n">
-        <v>32.80166471547</v>
+        <v>32.80166471546998</v>
       </c>
       <c r="L9" t="n">
-        <v>33.42908265025989</v>
+        <v>33.42908265025992</v>
       </c>
       <c r="M9" t="n">
-        <v>37.41057776495706</v>
+        <v>37.41057776495708</v>
       </c>
       <c r="N9" t="n">
         <v>32.57112924224595</v>
       </c>
       <c r="O9" t="n">
-        <v>33.97447735456562</v>
+        <v>33.97447735456567</v>
       </c>
       <c r="P9" t="n">
-        <v>35.28053728499864</v>
+        <v>35.28053728499865</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.81669838194244</v>
+        <v>32.81669838194245</v>
       </c>
       <c r="R9" t="n">
-        <v>32.13481167002548</v>
+        <v>32.1348116700255</v>
       </c>
       <c r="S9" t="n">
-        <v>33.1768150257904</v>
+        <v>33.17681502579041</v>
       </c>
       <c r="T9" t="n">
-        <v>32.11082914297935</v>
+        <v>32.11082914297936</v>
       </c>
       <c r="U9" t="n">
-        <v>33.91701214995281</v>
+        <v>33.91701214995282</v>
       </c>
       <c r="V9" t="n">
-        <v>31.98362446855901</v>
+        <v>36.90216186896934</v>
       </c>
       <c r="W9" t="n">
         <v>34.67836001375456</v>
@@ -5571,16 +5571,16 @@
         <v>33.02437924694343</v>
       </c>
       <c r="Y9" t="n">
-        <v>32.49179579712381</v>
+        <v>32.49179579712383</v>
       </c>
       <c r="Z9" t="n">
-        <v>33.50216494568026</v>
+        <v>30.93241085272104</v>
       </c>
       <c r="AA9" t="n">
         <v>33.03964836271332</v>
       </c>
       <c r="AB9" t="n">
-        <v>35.11956871864685</v>
+        <v>35.11956871864689</v>
       </c>
     </row>
   </sheetData>
@@ -5749,82 +5749,82 @@
         <v>20.23383853120063</v>
       </c>
       <c r="C2" t="n">
-        <v>14.58580314489987</v>
+        <v>14.58580314489988</v>
       </c>
       <c r="D2" t="n">
-        <v>20.1289346505927</v>
+        <v>20.12893465059265</v>
       </c>
       <c r="E2" t="n">
-        <v>20.11989377759689</v>
+        <v>20.11989377759684</v>
       </c>
       <c r="F2" t="n">
-        <v>20.15728300486596</v>
+        <v>20.15728300486593</v>
       </c>
       <c r="G2" t="n">
-        <v>20.19996116114295</v>
+        <v>20.19996116114292</v>
       </c>
       <c r="H2" t="n">
-        <v>20.21550810593045</v>
+        <v>20.21550810593039</v>
       </c>
       <c r="I2" t="n">
         <v>20.19827587547955</v>
       </c>
       <c r="J2" t="n">
-        <v>20.20050926066774</v>
+        <v>20.2005092606678</v>
       </c>
       <c r="K2" t="n">
-        <v>20.18981543034257</v>
+        <v>20.18981543034256</v>
       </c>
       <c r="L2" t="n">
-        <v>20.16568644863063</v>
+        <v>20.16568644863053</v>
       </c>
       <c r="M2" t="n">
-        <v>20.017910136022</v>
+        <v>20.01791013602203</v>
       </c>
       <c r="N2" t="n">
-        <v>20.20533502837523</v>
+        <v>20.20533502837521</v>
       </c>
       <c r="O2" t="n">
-        <v>27.08511868742586</v>
+        <v>27.08511868742584</v>
       </c>
       <c r="P2" t="n">
-        <v>20.20357083615531</v>
+        <v>20.20357083615527</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.21027020454659</v>
+        <v>20.21027020454656</v>
       </c>
       <c r="R2" t="n">
-        <v>20.17757086592105</v>
+        <v>20.17757086592101</v>
       </c>
       <c r="S2" t="n">
-        <v>20.19632915703093</v>
+        <v>20.19632915703091</v>
       </c>
       <c r="T2" t="n">
-        <v>20.14050063817451</v>
+        <v>20.14050063817447</v>
       </c>
       <c r="U2" t="n">
-        <v>23.39838295086766</v>
+        <v>23.39838295086769</v>
       </c>
       <c r="V2" t="n">
-        <v>20.21026610891285</v>
+        <v>20.21026610891282</v>
       </c>
       <c r="W2" t="n">
-        <v>25.63733296461292</v>
+        <v>25.63733296461284</v>
       </c>
       <c r="X2" t="n">
-        <v>20.4022592516095</v>
+        <v>20.40225925160949</v>
       </c>
       <c r="Y2" t="n">
         <v>20.28000823464209</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.41858934232096</v>
+        <v>26.41858934232092</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.21647203771321</v>
+        <v>20.21647203771317</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.14933844126939</v>
+        <v>20.14933844126937</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.24038316766768</v>
+        <v>20.24038316766763</v>
       </c>
       <c r="C3" t="n">
-        <v>10.36132096797345</v>
+        <v>10.36132096797344</v>
       </c>
       <c r="D3" t="n">
-        <v>19.49955312285193</v>
+        <v>19.4995531228519</v>
       </c>
       <c r="E3" t="n">
-        <v>19.4166045700432</v>
+        <v>19.41660457004308</v>
       </c>
       <c r="F3" t="n">
-        <v>19.70123268420104</v>
+        <v>19.70123268420103</v>
       </c>
       <c r="G3" t="n">
-        <v>20.00111850409638</v>
+        <v>20.00111850409636</v>
       </c>
       <c r="H3" t="n">
         <v>20.11998401138089</v>
       </c>
       <c r="I3" t="n">
-        <v>19.99423532822455</v>
+        <v>19.99423532822448</v>
       </c>
       <c r="J3" t="n">
-        <v>20.00599331971682</v>
+        <v>20.00599331971681</v>
       </c>
       <c r="K3" t="n">
         <v>19.93333198761953</v>
       </c>
       <c r="L3" t="n">
-        <v>19.7612520436345</v>
+        <v>19.76125204363442</v>
       </c>
       <c r="M3" t="n">
-        <v>19.56500503591784</v>
+        <v>19.56500503591786</v>
       </c>
       <c r="N3" t="n">
-        <v>20.04105054698241</v>
+        <v>20.0410505469824</v>
       </c>
       <c r="O3" t="n">
-        <v>31.70981249882628</v>
+        <v>31.70981249882624</v>
       </c>
       <c r="P3" t="n">
-        <v>20.02478043419632</v>
+        <v>20.02478043419634</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.07508245439679</v>
+        <v>20.07508245439675</v>
       </c>
       <c r="R3" t="n">
-        <v>19.84685745283891</v>
+        <v>19.84685745283888</v>
       </c>
       <c r="S3" t="n">
-        <v>19.9737076114175</v>
+        <v>19.97370761141747</v>
       </c>
       <c r="T3" t="n">
-        <v>19.58228499597934</v>
+        <v>19.58228499597929</v>
       </c>
       <c r="U3" t="n">
-        <v>25.26928996433091</v>
+        <v>25.26928996433087</v>
       </c>
       <c r="V3" t="n">
-        <v>20.07415246009256</v>
+        <v>20.07415246009245</v>
       </c>
       <c r="W3" t="n">
-        <v>29.49566733759386</v>
+        <v>29.4956673375938</v>
       </c>
       <c r="X3" t="n">
-        <v>21.44501484497835</v>
+        <v>21.44501484497833</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.57460317679135</v>
+        <v>20.57460317679132</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.37058904948528</v>
+        <v>30.37058904948524</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.12075000769515</v>
+        <v>20.12075000769513</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.66706490701237</v>
+        <v>19.66706490701229</v>
       </c>
     </row>
     <row r="4">
@@ -5925,82 +5925,82 @@
         <v>13.08706935426641</v>
       </c>
       <c r="C4" t="n">
-        <v>11.93384492973943</v>
+        <v>11.93384492973941</v>
       </c>
       <c r="D4" t="n">
         <v>11.90213176463051</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8000109451359</v>
+        <v>11.80001094513588</v>
       </c>
       <c r="F4" t="n">
-        <v>12.22233946703446</v>
+        <v>12.22233946703448</v>
       </c>
       <c r="G4" t="n">
-        <v>12.70440887510479</v>
+        <v>12.70440887510477</v>
       </c>
       <c r="H4" t="n">
-        <v>12.8800187684275</v>
+        <v>12.88001876842749</v>
       </c>
       <c r="I4" t="n">
-        <v>12.68537279826725</v>
+        <v>12.68537279826724</v>
       </c>
       <c r="J4" t="n">
-        <v>12.68269192291977</v>
+        <v>12.68269192291976</v>
       </c>
       <c r="K4" t="n">
-        <v>12.58980817844818</v>
+        <v>12.58980817844815</v>
       </c>
       <c r="L4" t="n">
         <v>12.31726023013135</v>
       </c>
       <c r="M4" t="n">
-        <v>12.22175334897928</v>
+        <v>12.22175334897926</v>
       </c>
       <c r="N4" t="n">
-        <v>12.76510917759456</v>
+        <v>12.76510917759457</v>
       </c>
       <c r="O4" t="n">
-        <v>13.42087071993084</v>
+        <v>13.42087071993086</v>
       </c>
       <c r="P4" t="n">
-        <v>12.7451818149021</v>
+        <v>12.74518181490209</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.8208542627433</v>
+        <v>12.82085426274331</v>
       </c>
       <c r="R4" t="n">
-        <v>12.45150019052885</v>
+        <v>12.45150019052883</v>
       </c>
       <c r="S4" t="n">
-        <v>12.66338371785519</v>
+        <v>12.66338371785517</v>
       </c>
       <c r="T4" t="n">
-        <v>12.03277491498428</v>
+        <v>12.03277491498427</v>
       </c>
       <c r="U4" t="n">
-        <v>12.45196602091824</v>
+        <v>12.45196602091823</v>
       </c>
       <c r="V4" t="n">
-        <v>12.64348521409217</v>
+        <v>12.64348521409221</v>
       </c>
       <c r="W4" t="n">
-        <v>13.77398113609436</v>
+        <v>13.77398113609434</v>
       </c>
       <c r="X4" t="n">
-        <v>14.98945886864391</v>
+        <v>14.98945886864394</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.52272699293994</v>
+        <v>13.52272699293993</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.92533483381124</v>
+        <v>12.92533483381121</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.89090682134446</v>
+        <v>12.89090682134445</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.17171094560628</v>
+        <v>12.17171094560629</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.44888975728018</v>
+        <v>49.44888975728021</v>
       </c>
       <c r="C5" t="n">
         <v>32.88567874902607</v>
       </c>
       <c r="D5" t="n">
-        <v>32.57190796408788</v>
+        <v>32.57190796408787</v>
       </c>
       <c r="E5" t="n">
-        <v>21.21827661569969</v>
+        <v>21.21827661569972</v>
       </c>
       <c r="F5" t="n">
-        <v>37.90154368652869</v>
+        <v>37.90154368652868</v>
       </c>
       <c r="G5" t="n">
-        <v>43.98673825905001</v>
+        <v>43.98673825905</v>
       </c>
       <c r="H5" t="n">
-        <v>51.18987036384149</v>
+        <v>51.18987036384145</v>
       </c>
       <c r="I5" t="n">
-        <v>46.31621196510297</v>
+        <v>46.31621196510309</v>
       </c>
       <c r="J5" t="n">
-        <v>44.56738035815339</v>
+        <v>44.56738035815334</v>
       </c>
       <c r="K5" t="n">
-        <v>44.35614303436294</v>
+        <v>44.35614303436292</v>
       </c>
       <c r="L5" t="n">
-        <v>39.60294910198736</v>
+        <v>39.60294910198742</v>
       </c>
       <c r="M5" t="n">
         <v>39.68613662077924</v>
       </c>
       <c r="N5" t="n">
-        <v>42.38530294424561</v>
+        <v>42.3853029442456</v>
       </c>
       <c r="O5" t="n">
-        <v>54.31889222301832</v>
+        <v>54.31889222301828</v>
       </c>
       <c r="P5" t="n">
-        <v>43.61934383023043</v>
+        <v>43.61934383023044</v>
       </c>
       <c r="Q5" t="n">
-        <v>46.24723130430257</v>
+        <v>46.24723130430259</v>
       </c>
       <c r="R5" t="n">
-        <v>42.384389271688</v>
+        <v>42.38438927168805</v>
       </c>
       <c r="S5" t="n">
         <v>42.48945318542334</v>
       </c>
       <c r="T5" t="n">
-        <v>34.97833794800255</v>
+        <v>34.97833794800251</v>
       </c>
       <c r="U5" t="n">
-        <v>42.15801018837996</v>
+        <v>42.15801018837998</v>
       </c>
       <c r="V5" t="n">
-        <v>45.60229240891304</v>
+        <v>45.60229240891367</v>
       </c>
       <c r="W5" t="n">
-        <v>62.73011724854247</v>
+        <v>62.73011724854248</v>
       </c>
       <c r="X5" t="n">
-        <v>84.44555532491032</v>
+        <v>84.44555532491052</v>
       </c>
       <c r="Y5" t="n">
-        <v>61.11062561493644</v>
+        <v>61.11062561493659</v>
       </c>
       <c r="Z5" t="n">
-        <v>46.43246574374442</v>
+        <v>46.43246574374443</v>
       </c>
       <c r="AA5" t="n">
         <v>48.21420811978106</v>
       </c>
       <c r="AB5" t="n">
-        <v>37.67163875893401</v>
+        <v>37.67163875893397</v>
       </c>
     </row>
     <row r="6">
@@ -6101,82 +6101,82 @@
         <v>30.38383605476662</v>
       </c>
       <c r="C6" t="n">
-        <v>41.38390701368798</v>
+        <v>29.23061163023962</v>
       </c>
       <c r="D6" t="n">
-        <v>29.19889846513076</v>
+        <v>29.19889846513074</v>
       </c>
       <c r="E6" t="n">
-        <v>41.25007302908443</v>
+        <v>41.25007302908445</v>
       </c>
       <c r="F6" t="n">
-        <v>41.67240155098306</v>
+        <v>41.67240155098308</v>
       </c>
       <c r="G6" t="n">
-        <v>42.1544709590533</v>
+        <v>30.00117557560498</v>
       </c>
       <c r="H6" t="n">
-        <v>42.33008085237613</v>
+        <v>30.17678546892774</v>
       </c>
       <c r="I6" t="n">
-        <v>29.98213949876749</v>
+        <v>29.98213949876748</v>
       </c>
       <c r="J6" t="n">
-        <v>42.13275400686837</v>
+        <v>29.97945862341996</v>
       </c>
       <c r="K6" t="n">
         <v>29.88657487894838</v>
       </c>
       <c r="L6" t="n">
-        <v>41.76732231407991</v>
+        <v>41.76732231407989</v>
       </c>
       <c r="M6" t="n">
-        <v>29.51852004947949</v>
+        <v>41.67181543292787</v>
       </c>
       <c r="N6" t="n">
-        <v>30.06804001564689</v>
+        <v>30.06804001564694</v>
       </c>
       <c r="O6" t="n">
-        <v>30.72380155798313</v>
+        <v>30.72380155798312</v>
       </c>
       <c r="P6" t="n">
-        <v>41.87912427607575</v>
+        <v>29.01916513082336</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.27091634669188</v>
+        <v>30.11762096324351</v>
       </c>
       <c r="R6" t="n">
-        <v>41.90156227447741</v>
+        <v>41.90156227447742</v>
       </c>
       <c r="S6" t="n">
-        <v>42.11344580180376</v>
+        <v>29.96015041835541</v>
       </c>
       <c r="T6" t="n">
         <v>41.48283699893291</v>
       </c>
       <c r="U6" t="n">
-        <v>29.8345831222292</v>
+        <v>29.83458312222922</v>
       </c>
       <c r="V6" t="n">
-        <v>29.9402519145924</v>
+        <v>42.09354729804077</v>
       </c>
       <c r="W6" t="n">
-        <v>31.98796795464175</v>
+        <v>31.98796795464173</v>
       </c>
       <c r="X6" t="n">
-        <v>32.28622556914416</v>
+        <v>32.28622556914417</v>
       </c>
       <c r="Y6" t="n">
-        <v>31.69088436082926</v>
+        <v>31.69088436082928</v>
       </c>
       <c r="Z6" t="n">
-        <v>42.37539691775979</v>
+        <v>42.37539691775982</v>
       </c>
       <c r="AA6" t="n">
-        <v>30.18767352184467</v>
+        <v>42.34096890529301</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.47147908556864</v>
+        <v>29.47147908556863</v>
       </c>
     </row>
     <row r="7">
@@ -6186,79 +6186,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.04078768211648</v>
+        <v>17.04078768211645</v>
       </c>
       <c r="C7" t="n">
-        <v>15.88756325758947</v>
+        <v>15.88756325758946</v>
       </c>
       <c r="D7" t="n">
-        <v>15.85585009248058</v>
+        <v>15.85585009248055</v>
       </c>
       <c r="E7" t="n">
-        <v>15.75372927298594</v>
+        <v>15.75372927298592</v>
       </c>
       <c r="F7" t="n">
         <v>16.17605779488453</v>
       </c>
       <c r="G7" t="n">
-        <v>16.65812720295483</v>
+        <v>16.65812720295482</v>
       </c>
       <c r="H7" t="n">
-        <v>16.83373709627756</v>
+        <v>16.83373709627755</v>
       </c>
       <c r="I7" t="n">
-        <v>16.63909112611731</v>
+        <v>16.6390911261173</v>
       </c>
       <c r="J7" t="n">
-        <v>16.63641025076982</v>
+        <v>16.63641025076981</v>
       </c>
       <c r="K7" t="n">
-        <v>16.54352650629822</v>
+        <v>16.54352650629821</v>
       </c>
       <c r="L7" t="n">
-        <v>16.27097855798143</v>
+        <v>16.27097855798141</v>
       </c>
       <c r="M7" t="n">
-        <v>16.1754716768293</v>
+        <v>16.17547167682929</v>
       </c>
       <c r="N7" t="n">
-        <v>16.71882750544465</v>
+        <v>16.71882750544463</v>
       </c>
       <c r="O7" t="n">
-        <v>17.37450882877571</v>
+        <v>17.3745088287757</v>
       </c>
       <c r="P7" t="n">
-        <v>16.69881992374694</v>
+        <v>16.69881992374692</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.77457259059337</v>
+        <v>16.77457259059336</v>
       </c>
       <c r="R7" t="n">
-        <v>16.40521851837892</v>
+        <v>16.4052185183789</v>
       </c>
       <c r="S7" t="n">
-        <v>16.61710204570524</v>
+        <v>16.61710204570523</v>
       </c>
       <c r="T7" t="n">
-        <v>15.98649324283432</v>
+        <v>15.98649324283433</v>
       </c>
       <c r="U7" t="n">
-        <v>16.49006921863806</v>
+        <v>16.49006921863803</v>
       </c>
       <c r="V7" t="n">
-        <v>16.59720354194228</v>
+        <v>16.59720354194226</v>
       </c>
       <c r="W7" t="n">
-        <v>17.72769946394443</v>
+        <v>17.7276994639444</v>
       </c>
       <c r="X7" t="n">
-        <v>18.94317719649399</v>
+        <v>18.94317719649398</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.56229572160075</v>
+        <v>17.56229572160074</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.87905316166129</v>
+        <v>16.87905316166128</v>
       </c>
       <c r="AA7" t="n">
         <v>16.84462514919451</v>
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.85833408157534</v>
+        <v>28.85833408157537</v>
       </c>
       <c r="C8" t="n">
-        <v>38.07792221469526</v>
+        <v>38.07792221469528</v>
       </c>
       <c r="D8" t="n">
-        <v>38.04620904958637</v>
+        <v>38.04620904958635</v>
       </c>
       <c r="E8" t="n">
-        <v>37.94408823009173</v>
+        <v>32.42087152179678</v>
       </c>
       <c r="F8" t="n">
         <v>29.60956716130425</v>
       </c>
       <c r="G8" t="n">
-        <v>38.84848616006057</v>
+        <v>40.9993564165413</v>
       </c>
       <c r="H8" t="n">
-        <v>39.02409605338334</v>
+        <v>39.02409605338332</v>
       </c>
       <c r="I8" t="n">
-        <v>38.82945008322305</v>
+        <v>38.82945008322309</v>
       </c>
       <c r="J8" t="n">
-        <v>38.82676920787553</v>
+        <v>38.82676920787557</v>
       </c>
       <c r="K8" t="n">
-        <v>38.73388546340399</v>
+        <v>38.73388546340398</v>
       </c>
       <c r="L8" t="n">
-        <v>38.46133751508718</v>
+        <v>38.46133751508717</v>
       </c>
       <c r="M8" t="n">
-        <v>38.36583063393508</v>
+        <v>38.36583063393468</v>
       </c>
       <c r="N8" t="n">
-        <v>30.86852139685825</v>
+        <v>30.86852139685824</v>
       </c>
       <c r="O8" t="n">
-        <v>33.73392751563786</v>
+        <v>33.73392751563789</v>
       </c>
       <c r="P8" t="n">
         <v>32.51660133237337</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.5536245743497</v>
+        <v>26.55362457434971</v>
       </c>
       <c r="R8" t="n">
-        <v>38.59557747548466</v>
+        <v>38.5955774754847</v>
       </c>
       <c r="S8" t="n">
-        <v>38.80746100281101</v>
+        <v>38.807461002811</v>
       </c>
       <c r="T8" t="n">
-        <v>38.1768521999401</v>
+        <v>38.17685219994012</v>
       </c>
       <c r="U8" t="n">
-        <v>32.29799687175477</v>
+        <v>33.61798875945387</v>
       </c>
       <c r="V8" t="n">
-        <v>38.78756249904798</v>
+        <v>35.95133229413018</v>
       </c>
       <c r="W8" t="n">
-        <v>39.92009697680818</v>
+        <v>39.92009697680816</v>
       </c>
       <c r="X8" t="n">
         <v>29.67291806278769</v>
       </c>
       <c r="Y8" t="n">
-        <v>50.06426951681711</v>
+        <v>50.06426951681715</v>
       </c>
       <c r="Z8" t="n">
-        <v>39.06941211876706</v>
+        <v>28.50391924237589</v>
       </c>
       <c r="AA8" t="n">
         <v>39.03498410630026</v>
       </c>
       <c r="AB8" t="n">
-        <v>49.15105830831887</v>
+        <v>49.15105830831882</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.29814076180012</v>
+        <v>25.29814076180009</v>
       </c>
       <c r="C9" t="n">
-        <v>27.67512921436526</v>
+        <v>27.67512921436525</v>
       </c>
       <c r="D9" t="n">
-        <v>27.64341604925638</v>
+        <v>27.64341604925635</v>
       </c>
       <c r="E9" t="n">
-        <v>27.54129522976175</v>
+        <v>26.72653738253207</v>
       </c>
       <c r="F9" t="n">
-        <v>27.96362375166036</v>
+        <v>19.82551808112833</v>
       </c>
       <c r="G9" t="n">
-        <v>28.44569315973064</v>
+        <v>28.44569431069758</v>
       </c>
       <c r="H9" t="n">
-        <v>28.62130305305335</v>
+        <v>28.62130305305334</v>
       </c>
       <c r="I9" t="n">
-        <v>28.42665708289313</v>
+        <v>28.42665708289309</v>
       </c>
       <c r="J9" t="n">
         <v>28.42397620754559</v>
       </c>
       <c r="K9" t="n">
-        <v>28.33109246307402</v>
+        <v>28.33109246307396</v>
       </c>
       <c r="L9" t="n">
-        <v>28.05854451475723</v>
+        <v>28.05854451475721</v>
       </c>
       <c r="M9" t="n">
-        <v>27.9630376336051</v>
+        <v>27.96303763360508</v>
       </c>
       <c r="N9" t="n">
-        <v>28.50639346222044</v>
+        <v>28.50639346222042</v>
       </c>
       <c r="O9" t="n">
-        <v>30.33206446200685</v>
+        <v>30.33206446200683</v>
       </c>
       <c r="P9" t="n">
-        <v>29.91081054138744</v>
+        <v>29.91081054138741</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.56213969833616</v>
+        <v>28.56213969833611</v>
       </c>
       <c r="R9" t="n">
-        <v>28.1927844751547</v>
+        <v>28.19278447515469</v>
       </c>
       <c r="S9" t="n">
-        <v>28.40466800248104</v>
+        <v>28.404668002481</v>
       </c>
       <c r="T9" t="n">
-        <v>27.77405919961014</v>
+        <v>27.77405919961009</v>
       </c>
       <c r="U9" t="n">
-        <v>28.27910070635487</v>
+        <v>28.27910070635482</v>
       </c>
       <c r="V9" t="n">
-        <v>28.38476949871809</v>
+        <v>32.45856050038475</v>
       </c>
       <c r="W9" t="n">
-        <v>29.5152654207202</v>
+        <v>29.51526542072018</v>
       </c>
       <c r="X9" t="n">
-        <v>30.73074315326977</v>
+        <v>30.73074315326975</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.34986167837656</v>
+        <v>29.34986167837652</v>
       </c>
       <c r="Z9" t="n">
-        <v>28.66661911843709</v>
+        <v>26.53821512936406</v>
       </c>
       <c r="AA9" t="n">
-        <v>28.63219110597029</v>
+        <v>28.63219110597028</v>
       </c>
       <c r="AB9" t="n">
-        <v>27.91299523023216</v>
+        <v>27.91299523023211</v>
       </c>
     </row>
   </sheetData>
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.14039535648477</v>
+        <v>20.14039535648479</v>
       </c>
       <c r="C2" t="n">
         <v>14.51713482423661</v>
@@ -6615,73 +6615,73 @@
         <v>20.08834818424315</v>
       </c>
       <c r="E2" t="n">
-        <v>20.07302828343598</v>
+        <v>20.07302828343601</v>
       </c>
       <c r="F2" t="n">
-        <v>20.0964871303738</v>
+        <v>20.09648713037382</v>
       </c>
       <c r="G2" t="n">
-        <v>20.12297702082481</v>
+        <v>20.12297702082483</v>
       </c>
       <c r="H2" t="n">
-        <v>20.13872929653657</v>
+        <v>20.13872929653659</v>
       </c>
       <c r="I2" t="n">
-        <v>20.16881339422829</v>
+        <v>20.16881339422831</v>
       </c>
       <c r="J2" t="n">
-        <v>20.12753619346245</v>
+        <v>20.12753619346246</v>
       </c>
       <c r="K2" t="n">
-        <v>20.12407856012732</v>
+        <v>20.12407856012734</v>
       </c>
       <c r="L2" t="n">
-        <v>20.10184587463555</v>
+        <v>20.10184587463559</v>
       </c>
       <c r="M2" t="n">
-        <v>19.9674067124532</v>
+        <v>19.96740671245317</v>
       </c>
       <c r="N2" t="n">
-        <v>20.11311470559639</v>
+        <v>20.11311470559641</v>
       </c>
       <c r="O2" t="n">
-        <v>26.97311295903593</v>
+        <v>26.97311295903594</v>
       </c>
       <c r="P2" t="n">
-        <v>20.15077443244603</v>
+        <v>20.15077443244606</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.11121666580834</v>
+        <v>20.11121666580836</v>
       </c>
       <c r="R2" t="n">
         <v>20.17300413257821</v>
       </c>
       <c r="S2" t="n">
-        <v>20.12448393665919</v>
+        <v>20.12448393665922</v>
       </c>
       <c r="T2" t="n">
-        <v>20.08627400577496</v>
+        <v>20.08627400577497</v>
       </c>
       <c r="U2" t="n">
-        <v>23.30951305538372</v>
+        <v>23.30951305538368</v>
       </c>
       <c r="V2" t="n">
-        <v>20.14397987422212</v>
+        <v>20.14397987422213</v>
       </c>
       <c r="W2" t="n">
-        <v>25.5278149921654</v>
+        <v>25.52781499216538</v>
       </c>
       <c r="X2" t="n">
-        <v>20.4006933142787</v>
+        <v>20.40069331427868</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.20111684595414</v>
+        <v>20.20111684595416</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.27098667388916</v>
+        <v>26.27098667388918</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.17317846099924</v>
+        <v>20.17317846099926</v>
       </c>
       <c r="AB2" t="n">
         <v>20.103648446481</v>
@@ -6700,25 +6700,25 @@
         <v>10.23062097940476</v>
       </c>
       <c r="D3" t="n">
-        <v>19.55937845060993</v>
+        <v>19.55937845060992</v>
       </c>
       <c r="E3" t="n">
-        <v>19.43406444737419</v>
+        <v>19.43406444737418</v>
       </c>
       <c r="F3" t="n">
-        <v>19.61754365713844</v>
+        <v>19.61754365713843</v>
       </c>
       <c r="G3" t="n">
         <v>19.80254206518141</v>
       </c>
       <c r="H3" t="n">
-        <v>19.92166722540371</v>
+        <v>19.9216672254037</v>
       </c>
       <c r="I3" t="n">
-        <v>20.13452076764731</v>
+        <v>20.1345207676473</v>
       </c>
       <c r="J3" t="n">
-        <v>19.83628509231761</v>
+        <v>19.83628509231758</v>
       </c>
       <c r="K3" t="n">
         <v>19.81421545894507</v>
@@ -6727,16 +6727,16 @@
         <v>19.65515283623006</v>
       </c>
       <c r="M3" t="n">
-        <v>19.54899571780681</v>
+        <v>19.5489957178068</v>
       </c>
       <c r="N3" t="n">
-        <v>19.73372646490233</v>
+        <v>19.73372646490234</v>
       </c>
       <c r="O3" t="n">
-        <v>31.46403697826473</v>
+        <v>31.46403697826472</v>
       </c>
       <c r="P3" t="n">
-        <v>19.99813134810373</v>
+        <v>19.99813134810374</v>
       </c>
       <c r="Q3" t="n">
         <v>19.7204475199598</v>
@@ -6748,31 +6748,31 @@
         <v>19.81239212168318</v>
       </c>
       <c r="T3" t="n">
-        <v>19.54444427276686</v>
+        <v>19.54444427276684</v>
       </c>
       <c r="U3" t="n">
-        <v>25.13364597396175</v>
+        <v>25.13364597396172</v>
       </c>
       <c r="V3" t="n">
-        <v>19.95169855170034</v>
+        <v>19.95169855170038</v>
       </c>
       <c r="W3" t="n">
         <v>29.23428940796623</v>
       </c>
       <c r="X3" t="n">
-        <v>21.78172160324463</v>
+        <v>21.78172160324462</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.36205739459427</v>
+        <v>20.36205739459425</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.87863678640453</v>
+        <v>29.87863678640456</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.16208990733606</v>
+        <v>20.16208990733605</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.68685051866812</v>
+        <v>19.68685051866811</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.58429204077097</v>
+        <v>12.58429204077099</v>
       </c>
       <c r="C4" t="n">
-        <v>11.73097287500939</v>
+        <v>11.73097287500941</v>
       </c>
       <c r="D4" t="n">
-        <v>11.99639528741948</v>
+        <v>11.9963952874195</v>
       </c>
       <c r="E4" t="n">
-        <v>11.82334996030029</v>
+        <v>11.8233499603003</v>
       </c>
       <c r="F4" t="n">
-        <v>12.08832842806565</v>
+        <v>12.08832842806567</v>
       </c>
       <c r="G4" t="n">
-        <v>12.3875439266614</v>
+        <v>12.38754392666145</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5654731272307</v>
+        <v>12.56547312723072</v>
       </c>
       <c r="I4" t="n">
-        <v>12.90528685002733</v>
+        <v>12.90528685002735</v>
       </c>
       <c r="J4" t="n">
-        <v>12.41123402042516</v>
+        <v>12.41123402042518</v>
       </c>
       <c r="K4" t="n">
-        <v>12.3999863198164</v>
+        <v>12.39998631981642</v>
       </c>
       <c r="L4" t="n">
-        <v>12.14885790964642</v>
+        <v>12.14885790964645</v>
       </c>
       <c r="M4" t="n">
-        <v>12.19668580817513</v>
+        <v>12.19668580817516</v>
       </c>
       <c r="N4" t="n">
-        <v>12.27614453926731</v>
+        <v>12.27614453926735</v>
       </c>
       <c r="O4" t="n">
-        <v>13.12496625410105</v>
+        <v>13.12496625410107</v>
       </c>
       <c r="P4" t="n">
-        <v>12.70152847836428</v>
+        <v>12.7015284783643</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.25470530671995</v>
+        <v>12.25470530671996</v>
       </c>
       <c r="R4" t="n">
-        <v>12.95262316752423</v>
+        <v>12.95262316752425</v>
       </c>
       <c r="S4" t="n">
-        <v>12.40456523422652</v>
+        <v>12.40456523422655</v>
       </c>
       <c r="T4" t="n">
-        <v>11.97296648745213</v>
+        <v>11.97296648745215</v>
       </c>
       <c r="U4" t="n">
-        <v>12.31086370142801</v>
+        <v>12.31086370142803</v>
       </c>
       <c r="V4" t="n">
-        <v>12.44813760035643</v>
+        <v>12.44813760035646</v>
       </c>
       <c r="W4" t="n">
-        <v>13.43766426769299</v>
+        <v>13.437664267693</v>
       </c>
       <c r="X4" t="n">
-        <v>15.52447721702945</v>
+        <v>15.52447721702946</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.18863204260094</v>
+        <v>13.18863204260095</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.24009992529118</v>
+        <v>12.2400999252912</v>
       </c>
       <c r="AA4" t="n">
         <v>12.95459228723486</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.19990046625243</v>
+        <v>12.19990046625245</v>
       </c>
     </row>
     <row r="5">
@@ -6873,13 +6873,13 @@
         <v>42.1610403357338</v>
       </c>
       <c r="C5" t="n">
-        <v>30.15279359574158</v>
+        <v>30.15279359574157</v>
       </c>
       <c r="D5" t="n">
-        <v>34.86761216079086</v>
+        <v>34.86761216079081</v>
       </c>
       <c r="E5" t="n">
-        <v>23.52832509140452</v>
+        <v>23.52832509140451</v>
       </c>
       <c r="F5" t="n">
         <v>36.5335784732429</v>
@@ -6888,67 +6888,67 @@
         <v>39.72105280341343</v>
       </c>
       <c r="H5" t="n">
-        <v>46.34032824014366</v>
+        <v>46.34032824014361</v>
       </c>
       <c r="I5" t="n">
-        <v>51.3875488808512</v>
+        <v>51.38754888085104</v>
       </c>
       <c r="J5" t="n">
-        <v>41.22800581198242</v>
+        <v>41.22800581198246</v>
       </c>
       <c r="K5" t="n">
-        <v>41.91640962727019</v>
+        <v>41.91640962727016</v>
       </c>
       <c r="L5" t="n">
-        <v>37.27432029170355</v>
+        <v>37.27432029170352</v>
       </c>
       <c r="M5" t="n">
-        <v>39.31017676225328</v>
+        <v>39.3101767622533</v>
       </c>
       <c r="N5" t="n">
-        <v>40.43326969867123</v>
+        <v>40.4332696986712</v>
       </c>
       <c r="O5" t="n">
-        <v>50.64658486155327</v>
+        <v>50.64658486155324</v>
       </c>
       <c r="P5" t="n">
-        <v>43.82220319752915</v>
+        <v>43.82220319752911</v>
       </c>
       <c r="Q5" t="n">
-        <v>38.32495785776453</v>
+        <v>38.32495785776455</v>
       </c>
       <c r="R5" t="n">
-        <v>52.81427574536636</v>
+        <v>52.81427574536642</v>
       </c>
       <c r="S5" t="n">
-        <v>39.55317315894766</v>
+        <v>39.55317315894764</v>
       </c>
       <c r="T5" t="n">
-        <v>34.3855225300069</v>
+        <v>34.38552253000692</v>
       </c>
       <c r="U5" t="n">
-        <v>40.54952601582364</v>
+        <v>40.54952601582366</v>
       </c>
       <c r="V5" t="n">
-        <v>43.3558515389678</v>
+        <v>43.35585153896787</v>
       </c>
       <c r="W5" t="n">
-        <v>58.30158012516387</v>
+        <v>58.30158012516374</v>
       </c>
       <c r="X5" t="n">
-        <v>93.70237845680295</v>
+        <v>93.70237845680245</v>
       </c>
       <c r="Y5" t="n">
-        <v>56.2787938237222</v>
+        <v>56.27879382372222</v>
       </c>
       <c r="Z5" t="n">
         <v>36.74788118864883</v>
       </c>
       <c r="AA5" t="n">
-        <v>50.40198972538253</v>
+        <v>50.40198972538246</v>
       </c>
       <c r="AB5" t="n">
-        <v>39.29783924211418</v>
+        <v>39.29783924211419</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.00875529727436</v>
+        <v>42.00875529727437</v>
       </c>
       <c r="C6" t="n">
         <v>41.15543613151274</v>
       </c>
       <c r="D6" t="n">
-        <v>41.42085854392283</v>
+        <v>41.42085854392279</v>
       </c>
       <c r="E6" t="n">
-        <v>41.24781321680364</v>
+        <v>41.24781321680362</v>
       </c>
       <c r="F6" t="n">
-        <v>29.3750631753534</v>
+        <v>41.51279168456905</v>
       </c>
       <c r="G6" t="n">
-        <v>29.67427867394917</v>
+        <v>41.81200718316484</v>
       </c>
       <c r="H6" t="n">
         <v>29.85220787451843</v>
       </c>
       <c r="I6" t="n">
-        <v>42.32975010653072</v>
+        <v>30.19202159731513</v>
       </c>
       <c r="J6" t="n">
-        <v>41.83569727692858</v>
+        <v>29.69796876771293</v>
       </c>
       <c r="K6" t="n">
-        <v>29.68672106710418</v>
+        <v>41.82444957631974</v>
       </c>
       <c r="L6" t="n">
-        <v>41.57332116614983</v>
+        <v>41.5733211661498</v>
       </c>
       <c r="M6" t="n">
-        <v>41.62114906467855</v>
+        <v>41.62114906467854</v>
       </c>
       <c r="N6" t="n">
         <v>29.56772266083343</v>
       </c>
       <c r="O6" t="n">
-        <v>30.41654437566713</v>
+        <v>42.22529370043683</v>
       </c>
       <c r="P6" t="n">
-        <v>41.80182749935046</v>
+        <v>41.80182749935044</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.67916856322337</v>
+        <v>41.67916856322334</v>
       </c>
       <c r="R6" t="n">
-        <v>42.37708642402762</v>
+        <v>30.23935791481199</v>
       </c>
       <c r="S6" t="n">
-        <v>29.69129998151432</v>
+        <v>29.69129998151431</v>
       </c>
       <c r="T6" t="n">
-        <v>41.39742974395551</v>
+        <v>41.3974297439555</v>
       </c>
       <c r="U6" t="n">
-        <v>41.81686411292311</v>
+        <v>41.8168641129231</v>
       </c>
       <c r="V6" t="n">
-        <v>29.73487234764421</v>
+        <v>29.73487234764422</v>
       </c>
       <c r="W6" t="n">
-        <v>42.53798503417606</v>
+        <v>42.53798503417605</v>
       </c>
       <c r="X6" t="n">
-        <v>44.94894047353287</v>
+        <v>32.81121196431724</v>
       </c>
       <c r="Y6" t="n">
-        <v>31.34067556908411</v>
+        <v>31.34067556908413</v>
       </c>
       <c r="Z6" t="n">
-        <v>41.66456318179453</v>
+        <v>29.52683467257896</v>
       </c>
       <c r="AA6" t="n">
-        <v>42.37905554373824</v>
+        <v>30.24132703452261</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.48962499085951</v>
+        <v>29.48962499085953</v>
       </c>
     </row>
     <row r="7">
@@ -7046,43 +7046,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.51861545147709</v>
+        <v>16.51861545147707</v>
       </c>
       <c r="C7" t="n">
-        <v>15.66529628571551</v>
+        <v>15.66529628571549</v>
       </c>
       <c r="D7" t="n">
-        <v>15.93071869812561</v>
+        <v>15.9307186981256</v>
       </c>
       <c r="E7" t="n">
         <v>15.7576733710064</v>
       </c>
       <c r="F7" t="n">
-        <v>16.02265183877176</v>
+        <v>16.02265183877175</v>
       </c>
       <c r="G7" t="n">
-        <v>16.32186733736752</v>
+        <v>16.32186733736757</v>
       </c>
       <c r="H7" t="n">
-        <v>16.49979653793682</v>
+        <v>16.49979653793681</v>
       </c>
       <c r="I7" t="n">
-        <v>16.83961026073346</v>
+        <v>16.83961026073344</v>
       </c>
       <c r="J7" t="n">
-        <v>16.34555743113128</v>
+        <v>16.34555743113124</v>
       </c>
       <c r="K7" t="n">
-        <v>16.33430973052254</v>
+        <v>16.33430973052251</v>
       </c>
       <c r="L7" t="n">
-        <v>16.08318132035258</v>
+        <v>16.08318132035254</v>
       </c>
       <c r="M7" t="n">
-        <v>16.13100921888127</v>
+        <v>16.13100921888125</v>
       </c>
       <c r="N7" t="n">
-        <v>16.21046794997346</v>
+        <v>16.21046794997344</v>
       </c>
       <c r="O7" t="n">
         <v>17.0592095341325</v>
@@ -7091,40 +7091,40 @@
         <v>16.63577175839573</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.18902871742607</v>
+        <v>16.18902871742606</v>
       </c>
       <c r="R7" t="n">
         <v>16.88694657823036</v>
       </c>
       <c r="S7" t="n">
-        <v>16.33888864493266</v>
+        <v>16.33888864493265</v>
       </c>
       <c r="T7" t="n">
         <v>15.90728989815825</v>
       </c>
       <c r="U7" t="n">
-        <v>16.3254533575477</v>
+        <v>16.32545335754769</v>
       </c>
       <c r="V7" t="n">
-        <v>16.38246101106256</v>
+        <v>16.38246101106255</v>
       </c>
       <c r="W7" t="n">
-        <v>17.37198767839911</v>
+        <v>17.37198767839908</v>
       </c>
       <c r="X7" t="n">
-        <v>19.45880062773551</v>
+        <v>19.45880062773555</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.20449260829878</v>
+        <v>17.20449260829879</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.17442333599731</v>
+        <v>16.1744233359973</v>
       </c>
       <c r="AA7" t="n">
-        <v>16.88891569794098</v>
+        <v>16.88891569794095</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.13422387695854</v>
+        <v>16.13422387695853</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.31229030535088</v>
+        <v>28.31229030535089</v>
       </c>
       <c r="C8" t="n">
-        <v>37.79791354206713</v>
+        <v>37.79791354206709</v>
       </c>
       <c r="D8" t="n">
         <v>38.06333595447717</v>
       </c>
       <c r="E8" t="n">
-        <v>37.89029062735803</v>
+        <v>32.38510877757626</v>
       </c>
       <c r="F8" t="n">
-        <v>29.4270130852827</v>
+        <v>29.42701308528265</v>
       </c>
       <c r="G8" t="n">
-        <v>38.45448459371913</v>
+        <v>40.59833165288466</v>
       </c>
       <c r="H8" t="n">
-        <v>38.63241379428847</v>
+        <v>38.63241379428841</v>
       </c>
       <c r="I8" t="n">
-        <v>38.97222751708507</v>
+        <v>38.97222751708502</v>
       </c>
       <c r="J8" t="n">
-        <v>38.47817468748298</v>
+        <v>38.47817468748285</v>
       </c>
       <c r="K8" t="n">
-        <v>38.46692698687413</v>
+        <v>38.46692698687411</v>
       </c>
       <c r="L8" t="n">
-        <v>38.21579857670417</v>
+        <v>38.21579857670413</v>
       </c>
       <c r="M8" t="n">
-        <v>38.2636264752329</v>
+        <v>38.2636264752325</v>
       </c>
       <c r="N8" t="n">
-        <v>30.32867517724996</v>
+        <v>30.32867517724991</v>
       </c>
       <c r="O8" t="n">
-        <v>33.37992635651299</v>
+        <v>33.37992635651296</v>
       </c>
       <c r="P8" t="n">
-        <v>32.41661990083477</v>
+        <v>32.4166199008347</v>
       </c>
       <c r="Q8" t="n">
         <v>25.95086541412616</v>
       </c>
       <c r="R8" t="n">
-        <v>39.01956383458196</v>
+        <v>39.01956383458194</v>
       </c>
       <c r="S8" t="n">
-        <v>38.47150590128428</v>
+        <v>38.47150590128423</v>
       </c>
       <c r="T8" t="n">
-        <v>38.03990715450987</v>
+        <v>38.03990715450986</v>
       </c>
       <c r="U8" t="n">
-        <v>32.09642817837578</v>
+        <v>33.41211890526804</v>
       </c>
       <c r="V8" t="n">
-        <v>38.51507826741417</v>
+        <v>35.68827156864291</v>
       </c>
       <c r="W8" t="n">
-        <v>39.50663683408517</v>
+        <v>39.50663683408509</v>
       </c>
       <c r="X8" t="n">
-        <v>30.168221939971</v>
+        <v>30.16822193997105</v>
       </c>
       <c r="Y8" t="n">
-        <v>49.61530628205288</v>
+        <v>49.6153062820528</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.30704059234893</v>
+        <v>27.77604702664394</v>
       </c>
       <c r="AA8" t="n">
-        <v>39.02153295429257</v>
+        <v>39.02153295429255</v>
       </c>
       <c r="AB8" t="n">
-        <v>49.06673100184904</v>
+        <v>49.06673100184901</v>
       </c>
     </row>
     <row r="9">
@@ -7228,28 +7228,28 @@
         <v>26.67454945264188</v>
       </c>
       <c r="D9" t="n">
-        <v>26.93997186505199</v>
+        <v>26.93997186505197</v>
       </c>
       <c r="E9" t="n">
-        <v>26.76692653793276</v>
+        <v>25.99255588279293</v>
       </c>
       <c r="F9" t="n">
-        <v>27.03190500569811</v>
+        <v>19.29720307240748</v>
       </c>
       <c r="G9" t="n">
-        <v>27.33112050429391</v>
+        <v>27.33112144478655</v>
       </c>
       <c r="H9" t="n">
-        <v>27.50904970486319</v>
+        <v>27.50904970486317</v>
       </c>
       <c r="I9" t="n">
-        <v>27.84886342765981</v>
+        <v>27.84886342765983</v>
       </c>
       <c r="J9" t="n">
-        <v>27.35481059805765</v>
+        <v>27.35481059805763</v>
       </c>
       <c r="K9" t="n">
-        <v>27.34356289744889</v>
+        <v>27.34356289744888</v>
       </c>
       <c r="L9" t="n">
         <v>27.09243448727891</v>
@@ -7258,49 +7258,49 @@
         <v>27.14026238580763</v>
       </c>
       <c r="N9" t="n">
-        <v>27.21972111689983</v>
+        <v>27.21972111689981</v>
       </c>
       <c r="O9" t="n">
-        <v>29.18046001253851</v>
+        <v>29.1804600125385</v>
       </c>
       <c r="P9" t="n">
-        <v>28.9988449417952</v>
+        <v>28.99884494179519</v>
       </c>
       <c r="Q9" t="n">
         <v>27.19828282484519</v>
       </c>
       <c r="R9" t="n">
-        <v>27.89619974515675</v>
+        <v>27.89619974515671</v>
       </c>
       <c r="S9" t="n">
-        <v>27.34814181185902</v>
+        <v>27.34814181185898</v>
       </c>
       <c r="T9" t="n">
-        <v>26.91654306508463</v>
+        <v>26.91654306508461</v>
       </c>
       <c r="U9" t="n">
         <v>27.33597743405224</v>
       </c>
       <c r="V9" t="n">
-        <v>27.39171417798894</v>
+        <v>31.26356833085587</v>
       </c>
       <c r="W9" t="n">
-        <v>28.38124084532546</v>
+        <v>28.38124084532545</v>
       </c>
       <c r="X9" t="n">
-        <v>30.46805379466199</v>
+        <v>30.46805379466193</v>
       </c>
       <c r="Y9" t="n">
-        <v>28.21374577522516</v>
+        <v>28.21374577522518</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.18367650292367</v>
+        <v>25.16077682115472</v>
       </c>
       <c r="AA9" t="n">
-        <v>27.89816886486735</v>
+        <v>27.89816886486737</v>
       </c>
       <c r="AB9" t="n">
-        <v>27.14347704388489</v>
+        <v>27.14347704388491</v>
       </c>
     </row>
   </sheetData>
@@ -7466,79 +7466,79 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.86586605119863</v>
+        <v>21.8658660511986</v>
       </c>
       <c r="C2" t="n">
-        <v>15.87206723647718</v>
+        <v>15.8720672364772</v>
       </c>
       <c r="D2" t="n">
-        <v>21.54891142577355</v>
+        <v>21.54891142577356</v>
       </c>
       <c r="E2" t="n">
-        <v>21.5268009817005</v>
+        <v>21.52680098170051</v>
       </c>
       <c r="F2" t="n">
-        <v>21.55247104500331</v>
+        <v>21.55247104500332</v>
       </c>
       <c r="G2" t="n">
-        <v>22.83016934697827</v>
+        <v>22.83016934697828</v>
       </c>
       <c r="H2" t="n">
-        <v>21.46788369920587</v>
+        <v>21.46788369920588</v>
       </c>
       <c r="I2" t="n">
-        <v>21.5568501028431</v>
+        <v>21.55685010284311</v>
       </c>
       <c r="J2" t="n">
-        <v>22.16411379371773</v>
+        <v>22.16411379371768</v>
       </c>
       <c r="K2" t="n">
         <v>21.61038606160146</v>
       </c>
       <c r="L2" t="n">
-        <v>21.76950751646372</v>
+        <v>21.76950751646368</v>
       </c>
       <c r="M2" t="n">
-        <v>22.89902963442751</v>
+        <v>22.8990296344275</v>
       </c>
       <c r="N2" t="n">
         <v>21.60271505060779</v>
       </c>
       <c r="O2" t="n">
-        <v>28.88799144174504</v>
+        <v>28.88799144174506</v>
       </c>
       <c r="P2" t="n">
-        <v>21.83197914453167</v>
+        <v>21.83197914453168</v>
       </c>
       <c r="Q2" t="n">
         <v>21.61453804821398</v>
       </c>
       <c r="R2" t="n">
-        <v>21.52217305333398</v>
+        <v>21.52217305333399</v>
       </c>
       <c r="S2" t="n">
-        <v>21.77811322976773</v>
+        <v>21.77811322976772</v>
       </c>
       <c r="T2" t="n">
-        <v>21.54846449942715</v>
+        <v>21.54846449942716</v>
       </c>
       <c r="U2" t="n">
-        <v>25.29334275310731</v>
+        <v>25.29334275310734</v>
       </c>
       <c r="V2" t="n">
-        <v>21.55394467789287</v>
+        <v>21.55394467789288</v>
       </c>
       <c r="W2" t="n">
-        <v>27.30204507738478</v>
+        <v>27.30204507738477</v>
       </c>
       <c r="X2" t="n">
         <v>21.75779700640535</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.72789167326929</v>
+        <v>21.72789167326932</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.17367928365541</v>
+        <v>28.17367928365539</v>
       </c>
       <c r="AA2" t="n">
         <v>21.68186346790735</v>
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.61253208833655</v>
+        <v>23.61253208833651</v>
       </c>
       <c r="C3" t="n">
-        <v>11.29262173488421</v>
+        <v>11.29262173488422</v>
       </c>
       <c r="D3" t="n">
-        <v>21.36945873624387</v>
+        <v>21.36945873624386</v>
       </c>
       <c r="E3" t="n">
-        <v>21.19250978935564</v>
+        <v>21.19250978935565</v>
       </c>
       <c r="F3" t="n">
         <v>21.39612133410284</v>
       </c>
       <c r="G3" t="n">
-        <v>30.45762347430238</v>
+        <v>30.4576234743024</v>
       </c>
       <c r="H3" t="n">
-        <v>20.79225729190674</v>
+        <v>20.79225729190679</v>
       </c>
       <c r="I3" t="n">
-        <v>21.42717937798029</v>
+        <v>21.42717937798028</v>
       </c>
       <c r="J3" t="n">
         <v>25.73634773271088</v>
       </c>
       <c r="K3" t="n">
-        <v>21.80525446756697</v>
+        <v>21.80525446756696</v>
       </c>
       <c r="L3" t="n">
-        <v>22.93552838828019</v>
+        <v>22.93552838828025</v>
       </c>
       <c r="M3" t="n">
-        <v>31.78116836098241</v>
+        <v>31.78116836098243</v>
       </c>
       <c r="N3" t="n">
-        <v>21.75161463835135</v>
+        <v>21.75161463835134</v>
       </c>
       <c r="O3" t="n">
-        <v>33.87939028572723</v>
+        <v>33.87939028572717</v>
       </c>
       <c r="P3" t="n">
-        <v>23.37446350433029</v>
+        <v>23.37446350433027</v>
       </c>
       <c r="Q3" t="n">
         <v>21.83533410291756</v>
       </c>
       <c r="R3" t="n">
-        <v>21.17990484275163</v>
+        <v>21.17990484275162</v>
       </c>
       <c r="S3" t="n">
-        <v>22.98675367694977</v>
+        <v>22.98675367694979</v>
       </c>
       <c r="T3" t="n">
-        <v>21.36654351724483</v>
+        <v>21.36654351724481</v>
       </c>
       <c r="U3" t="n">
-        <v>29.40374579419308</v>
+        <v>29.4037457941931</v>
       </c>
       <c r="V3" t="n">
-        <v>21.39815004924732</v>
+        <v>21.39815004924734</v>
       </c>
       <c r="W3" t="n">
-        <v>31.83428484002877</v>
+        <v>31.83428484002878</v>
       </c>
       <c r="X3" t="n">
         <v>22.86220103032507</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.64293627970798</v>
+        <v>22.64293627970807</v>
       </c>
       <c r="Z3" t="n">
-        <v>33.80064853857763</v>
+        <v>33.80064853857765</v>
       </c>
       <c r="AA3" t="n">
         <v>22.31492189696565</v>
       </c>
       <c r="AB3" t="n">
-        <v>28.50435380095215</v>
+        <v>28.50435380095216</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.8869190727224</v>
+        <v>18.88691907272324</v>
       </c>
       <c r="C4" t="n">
-        <v>13.85376560701065</v>
+        <v>13.85376560701113</v>
       </c>
       <c r="D4" t="n">
-        <v>15.30677077221576</v>
+        <v>15.30677077221619</v>
       </c>
       <c r="E4" t="n">
-        <v>15.05702313510329</v>
+        <v>15.05702313510416</v>
       </c>
       <c r="F4" t="n">
-        <v>15.34697830892159</v>
+        <v>15.34697830892202</v>
       </c>
       <c r="G4" t="n">
-        <v>29.77916839998637</v>
+        <v>29.77916839998707</v>
       </c>
       <c r="H4" t="n">
-        <v>14.39152532603804</v>
+        <v>14.39152532603843</v>
       </c>
       <c r="I4" t="n">
-        <v>15.39644178168815</v>
+        <v>15.39644178168849</v>
       </c>
       <c r="J4" t="n">
-        <v>22.22221792029765</v>
+        <v>22.22221792029828</v>
       </c>
       <c r="K4" t="n">
-        <v>16.00115506362145</v>
+        <v>16.00115506362209</v>
       </c>
       <c r="L4" t="n">
-        <v>17.79850509577555</v>
+        <v>17.79850509577642</v>
       </c>
       <c r="M4" t="n">
-        <v>32.00736436986568</v>
+        <v>32.00736436986598</v>
       </c>
       <c r="N4" t="n">
-        <v>15.91450746560873</v>
+        <v>15.91450746560898</v>
       </c>
       <c r="O4" t="n">
-        <v>16.14533397825875</v>
+        <v>16.14533397825919</v>
       </c>
       <c r="P4" t="n">
-        <v>18.50415087317333</v>
+        <v>18.50415087317319</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.04805366241805</v>
+        <v>16.04805366241862</v>
       </c>
       <c r="R4" t="n">
-        <v>15.00474855525124</v>
+        <v>15.00474855525212</v>
       </c>
       <c r="S4" t="n">
-        <v>17.89571058636844</v>
+        <v>17.89571058636916</v>
       </c>
       <c r="T4" t="n">
-        <v>15.30172253353651</v>
+        <v>15.30172253353721</v>
       </c>
       <c r="U4" t="n">
-        <v>18.77813533073378</v>
+        <v>18.77813533073433</v>
       </c>
       <c r="V4" t="n">
-        <v>15.14811498848563</v>
+        <v>15.14811498848564</v>
       </c>
       <c r="W4" t="n">
-        <v>17.30748899221738</v>
+        <v>17.30748899221759</v>
       </c>
       <c r="X4" t="n">
-        <v>17.66622949756637</v>
+        <v>17.6662294975667</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.10307226435376</v>
+        <v>17.10307226435421</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.42017275798051</v>
+        <v>18.42017275798127</v>
       </c>
       <c r="AA4" t="n">
-        <v>16.80852524907777</v>
+        <v>16.80852524907854</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.52453878901775</v>
+        <v>26.52453878901838</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>119.6390773268086</v>
+        <v>119.6390773268091</v>
       </c>
       <c r="C5" t="n">
-        <v>34.35334397914739</v>
+        <v>34.35334397914799</v>
       </c>
       <c r="D5" t="n">
-        <v>62.53934654154926</v>
+        <v>62.53934654154975</v>
       </c>
       <c r="E5" t="n">
-        <v>47.16927057427053</v>
+        <v>47.16927057427115</v>
       </c>
       <c r="F5" t="n">
-        <v>63.99890263717738</v>
+        <v>63.99890263717784</v>
       </c>
       <c r="G5" t="n">
-        <v>304.9057698503571</v>
+        <v>304.9057698503576</v>
       </c>
       <c r="H5" t="n">
-        <v>45.84433877753997</v>
+        <v>45.84433877754061</v>
       </c>
       <c r="I5" t="n">
-        <v>64.82541980234433</v>
+        <v>64.82541980234468</v>
       </c>
       <c r="J5" t="n">
-        <v>180.637499644585</v>
+        <v>180.6374996445858</v>
       </c>
       <c r="K5" t="n">
-        <v>74.02704307456526</v>
+        <v>74.02704307456618</v>
       </c>
       <c r="L5" t="n">
-        <v>105.0169338035138</v>
+        <v>105.0169338035143</v>
       </c>
       <c r="M5" t="n">
-        <v>371.5409463179412</v>
+        <v>371.5409463179417</v>
       </c>
       <c r="N5" t="n">
-        <v>124.0776748683526</v>
+        <v>124.0776748683537</v>
       </c>
       <c r="O5" t="n">
-        <v>71.7956576569967</v>
+        <v>71.7956576569982</v>
       </c>
       <c r="P5" t="n">
-        <v>114.5061896374075</v>
+        <v>114.5061896374077</v>
       </c>
       <c r="Q5" t="n">
-        <v>75.16223046430267</v>
+        <v>75.16223046430352</v>
       </c>
       <c r="R5" t="n">
-        <v>57.54017124980102</v>
+        <v>57.54017124980134</v>
       </c>
       <c r="S5" t="n">
-        <v>101.1854052613741</v>
+        <v>101.185405261374</v>
       </c>
       <c r="T5" t="n">
-        <v>62.59656796050218</v>
+        <v>62.59656796050272</v>
       </c>
       <c r="U5" t="n">
-        <v>127.1666654717853</v>
+        <v>127.1666654717868</v>
       </c>
       <c r="V5" t="n">
-        <v>59.37712649426031</v>
+        <v>59.37712649426039</v>
       </c>
       <c r="W5" t="n">
-        <v>98.39343767440732</v>
+        <v>98.39343767440806</v>
       </c>
       <c r="X5" t="n">
-        <v>108.2170718622766</v>
+        <v>108.2170718622774</v>
       </c>
       <c r="Y5" t="n">
-        <v>98.58833151434015</v>
+        <v>98.58833151433967</v>
       </c>
       <c r="Z5" t="n">
-        <v>112.2717309121895</v>
+        <v>112.2717309121904</v>
       </c>
       <c r="AA5" t="n">
-        <v>89.03111704777028</v>
+        <v>89.03111704777098</v>
       </c>
       <c r="AB5" t="n">
-        <v>298.4285759248975</v>
+        <v>298.428575924898</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.5394012948499</v>
+        <v>51.53940129485029</v>
       </c>
       <c r="C6" t="n">
-        <v>32.46292690724272</v>
+        <v>32.46292690724358</v>
       </c>
       <c r="D6" t="n">
-        <v>47.95925299434292</v>
+        <v>47.95925299434329</v>
       </c>
       <c r="E6" t="n">
-        <v>47.70950535723075</v>
+        <v>47.70950535723122</v>
       </c>
       <c r="F6" t="n">
-        <v>47.99946053104909</v>
+        <v>47.99946053104915</v>
       </c>
       <c r="G6" t="n">
-        <v>48.38832970021876</v>
+        <v>48.38832970021945</v>
       </c>
       <c r="H6" t="n">
-        <v>47.0440075481651</v>
+        <v>47.04400754816548</v>
       </c>
       <c r="I6" t="n">
-        <v>34.00560308192052</v>
+        <v>34.0056030819209</v>
       </c>
       <c r="J6" t="n">
-        <v>54.87470014242481</v>
+        <v>40.83137922053069</v>
       </c>
       <c r="K6" t="n">
-        <v>34.61031636385387</v>
+        <v>34.61031636385452</v>
       </c>
       <c r="L6" t="n">
-        <v>36.40766639600795</v>
+        <v>50.45098731790346</v>
       </c>
       <c r="M6" t="n">
-        <v>64.65984659199242</v>
+        <v>64.65984659199293</v>
       </c>
       <c r="N6" t="n">
-        <v>34.53257646443762</v>
+        <v>34.53257646443893</v>
       </c>
       <c r="O6" t="n">
-        <v>34.76340297708761</v>
+        <v>34.76340297708949</v>
       </c>
       <c r="P6" t="n">
-        <v>50.83967133212317</v>
+        <v>50.83967133212351</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.65721496265048</v>
+        <v>48.70053588454562</v>
       </c>
       <c r="R6" t="n">
-        <v>47.65723077737837</v>
+        <v>47.6572307773792</v>
       </c>
       <c r="S6" t="n">
-        <v>50.54819280849553</v>
+        <v>50.54819280849618</v>
       </c>
       <c r="T6" t="n">
-        <v>47.95420475566367</v>
+        <v>33.91088383376962</v>
       </c>
       <c r="U6" t="n">
-        <v>51.65598029116853</v>
+        <v>51.65598029116927</v>
       </c>
       <c r="V6" t="n">
-        <v>33.75727628871803</v>
+        <v>47.80059721061274</v>
       </c>
       <c r="W6" t="n">
-        <v>36.91742797084058</v>
+        <v>36.91742797084141</v>
       </c>
       <c r="X6" t="n">
-        <v>50.31871171969352</v>
+        <v>36.2753907977992</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.76939503902427</v>
+        <v>36.76939503902776</v>
       </c>
       <c r="Z6" t="n">
-        <v>37.0293340582129</v>
+        <v>37.02933405821369</v>
       </c>
       <c r="AA6" t="n">
-        <v>49.46100747120522</v>
+        <v>49.46100747120556</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.20282607638741</v>
+        <v>45.20282607638777</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.73542898784568</v>
+        <v>23.73542898784595</v>
       </c>
       <c r="C7" t="n">
-        <v>18.70227552213356</v>
+        <v>18.70227552213386</v>
       </c>
       <c r="D7" t="n">
-        <v>20.15528068733905</v>
+        <v>20.15528068733892</v>
       </c>
       <c r="E7" t="n">
-        <v>19.90553305022656</v>
+        <v>19.90553305022689</v>
       </c>
       <c r="F7" t="n">
-        <v>20.19548822404454</v>
+        <v>20.19548822404474</v>
       </c>
       <c r="G7" t="n">
-        <v>34.62767831510966</v>
+        <v>34.6276783151098</v>
       </c>
       <c r="H7" t="n">
-        <v>19.24003524116062</v>
+        <v>19.24003524116116</v>
       </c>
       <c r="I7" t="n">
-        <v>20.24495169681143</v>
+        <v>20.24495169681122</v>
       </c>
       <c r="J7" t="n">
-        <v>27.07072783542128</v>
+        <v>27.07072783542104</v>
       </c>
       <c r="K7" t="n">
-        <v>20.84966497874474</v>
+        <v>20.84966497874482</v>
       </c>
       <c r="L7" t="n">
-        <v>22.64701501089849</v>
+        <v>22.64701501089914</v>
       </c>
       <c r="M7" t="n">
-        <v>36.85587428498894</v>
+        <v>36.8558742849887</v>
       </c>
       <c r="N7" t="n">
-        <v>20.76301738073167</v>
+        <v>20.76301738073174</v>
       </c>
       <c r="O7" t="n">
-        <v>20.99375303637341</v>
+        <v>20.99375303637382</v>
       </c>
       <c r="P7" t="n">
-        <v>23.35256993128693</v>
+        <v>23.3525699312878</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.89656357754132</v>
+        <v>20.89656357754133</v>
       </c>
       <c r="R7" t="n">
-        <v>19.85325847037452</v>
+        <v>19.85325847037482</v>
       </c>
       <c r="S7" t="n">
-        <v>22.74422050149175</v>
+        <v>22.74422050149192</v>
       </c>
       <c r="T7" t="n">
-        <v>20.15023244866015</v>
+        <v>20.15023244865996</v>
       </c>
       <c r="U7" t="n">
-        <v>23.8470573627958</v>
+        <v>23.84705736279603</v>
       </c>
       <c r="V7" t="n">
-        <v>19.9966249036084</v>
+        <v>19.99662490360841</v>
       </c>
       <c r="W7" t="n">
-        <v>22.15599890733996</v>
+        <v>22.15599890734032</v>
       </c>
       <c r="X7" t="n">
-        <v>22.51473941268965</v>
+        <v>22.51473941268945</v>
       </c>
       <c r="Y7" t="n">
-        <v>22.1769449177847</v>
+        <v>22.17694491778501</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.26868267310381</v>
+        <v>23.26868267310402</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.65703516420107</v>
+        <v>21.65703516420123</v>
       </c>
       <c r="AB7" t="n">
-        <v>31.37304870414105</v>
+        <v>31.37304870414111</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36.95658637460224</v>
+        <v>36.95658637460298</v>
       </c>
       <c r="C8" t="n">
-        <v>43.94283565120796</v>
+        <v>43.94283565120848</v>
       </c>
       <c r="D8" t="n">
-        <v>45.39584081641343</v>
+        <v>45.39584081641352</v>
       </c>
       <c r="E8" t="n">
-        <v>45.14609317930098</v>
+        <v>38.74611576908713</v>
       </c>
       <c r="F8" t="n">
-        <v>35.28912808440687</v>
+        <v>35.2891280844077</v>
       </c>
       <c r="G8" t="n">
-        <v>59.86823844418404</v>
+        <v>62.36053990197773</v>
       </c>
       <c r="H8" t="n">
-        <v>44.48059537023536</v>
+        <v>44.48059537023573</v>
       </c>
       <c r="I8" t="n">
-        <v>45.4855118258851</v>
+        <v>45.48551182588582</v>
       </c>
       <c r="J8" t="n">
-        <v>52.31128796449498</v>
+        <v>52.31128796449562</v>
       </c>
       <c r="K8" t="n">
-        <v>46.09022510781879</v>
+        <v>46.09022510781942</v>
       </c>
       <c r="L8" t="n">
-        <v>47.88757513997285</v>
+        <v>47.88757513997372</v>
       </c>
       <c r="M8" t="n">
-        <v>62.09643441406264</v>
+        <v>62.09643441406308</v>
       </c>
       <c r="N8" t="n">
-        <v>36.6865295824067</v>
+        <v>36.68652958240705</v>
       </c>
       <c r="O8" t="n">
-        <v>39.47776176443531</v>
+        <v>39.47776176443575</v>
       </c>
       <c r="P8" t="n">
-        <v>41.20896136167021</v>
+        <v>41.20896136167094</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.75563399578445</v>
+        <v>31.75563399578515</v>
       </c>
       <c r="R8" t="n">
-        <v>45.09381859944889</v>
+        <v>45.09381859944943</v>
       </c>
       <c r="S8" t="n">
-        <v>47.98478063056613</v>
+        <v>47.98478063056646</v>
       </c>
       <c r="T8" t="n">
-        <v>45.39079257773383</v>
+        <v>45.39079257773452</v>
       </c>
       <c r="U8" t="n">
-        <v>41.69291708648772</v>
+        <v>43.22229185820256</v>
       </c>
       <c r="V8" t="n">
-        <v>45.23718503268296</v>
+        <v>41.94794702668231</v>
       </c>
       <c r="W8" t="n">
-        <v>47.39892119411387</v>
+        <v>47.39892119411459</v>
       </c>
       <c r="X8" t="n">
-        <v>34.47541197558896</v>
+        <v>34.47541197558913</v>
       </c>
       <c r="Y8" t="n">
-        <v>59.36168074526904</v>
+        <v>59.3616807452695</v>
       </c>
       <c r="Z8" t="n">
-        <v>48.50924280217818</v>
+        <v>36.26657348309945</v>
       </c>
       <c r="AA8" t="n">
-        <v>46.89759529327546</v>
+        <v>46.89759529327583</v>
       </c>
       <c r="AB8" t="n">
-        <v>69.16888004428725</v>
+        <v>69.16888004428759</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.62437044412435</v>
+        <v>36.62437044412467</v>
       </c>
       <c r="C9" t="n">
-        <v>36.73082908222241</v>
+        <v>36.73082908222297</v>
       </c>
       <c r="D9" t="n">
-        <v>38.18383424742791</v>
+        <v>38.18383424742802</v>
       </c>
       <c r="E9" t="n">
-        <v>37.9340866103154</v>
+        <v>36.74788486549659</v>
       </c>
       <c r="F9" t="n">
-        <v>38.22404178413339</v>
+        <v>26.37583355099578</v>
       </c>
       <c r="G9" t="n">
-        <v>52.65623187519849</v>
+        <v>52.65623156922734</v>
       </c>
       <c r="H9" t="n">
-        <v>37.26858880124983</v>
+        <v>37.26858880125025</v>
       </c>
       <c r="I9" t="n">
-        <v>38.27350525689958</v>
+        <v>38.27350525690031</v>
       </c>
       <c r="J9" t="n">
-        <v>45.09928139550976</v>
+        <v>45.09928139551015</v>
       </c>
       <c r="K9" t="n">
-        <v>38.87821853883322</v>
+        <v>38.87821853883392</v>
       </c>
       <c r="L9" t="n">
-        <v>40.67556857098733</v>
+        <v>40.67556857098822</v>
       </c>
       <c r="M9" t="n">
-        <v>54.88442784507711</v>
+        <v>54.88442784507781</v>
       </c>
       <c r="N9" t="n">
-        <v>38.79157094082051</v>
+        <v>38.7915709408208</v>
       </c>
       <c r="O9" t="n">
-        <v>40.72565776756069</v>
+        <v>40.72565776756151</v>
       </c>
       <c r="P9" t="n">
-        <v>43.45490462430315</v>
+        <v>43.45490462430325</v>
       </c>
       <c r="Q9" t="n">
-        <v>38.92511683165812</v>
+        <v>38.92511683165882</v>
       </c>
       <c r="R9" t="n">
-        <v>37.88181203046337</v>
+        <v>37.88181203046396</v>
       </c>
       <c r="S9" t="n">
-        <v>40.7727740615806</v>
+        <v>40.77277406158101</v>
       </c>
       <c r="T9" t="n">
-        <v>38.1787860087483</v>
+        <v>38.17878600874909</v>
       </c>
       <c r="U9" t="n">
-        <v>41.88056154425355</v>
+        <v>41.88056154425405</v>
       </c>
       <c r="V9" t="n">
-        <v>38.02517846369746</v>
+        <v>43.95617513703877</v>
       </c>
       <c r="W9" t="n">
-        <v>40.18455246742914</v>
+        <v>40.18455246742941</v>
       </c>
       <c r="X9" t="n">
-        <v>40.54329297277781</v>
+        <v>40.54329297277856</v>
       </c>
       <c r="Y9" t="n">
-        <v>40.20549847787353</v>
+        <v>40.20549847787408</v>
       </c>
       <c r="Z9" t="n">
-        <v>41.29723623319266</v>
+        <v>38.19850704523802</v>
       </c>
       <c r="AA9" t="n">
-        <v>39.68558872428992</v>
+        <v>39.68558872429035</v>
       </c>
       <c r="AB9" t="n">
-        <v>49.40160226422989</v>
+        <v>49.40160226423025</v>
       </c>
     </row>
   </sheetData>
@@ -8329,67 +8329,67 @@
         <v>20.96553262575681</v>
       </c>
       <c r="C2" t="n">
-        <v>15.3339133819738</v>
+        <v>15.33391338197379</v>
       </c>
       <c r="D2" t="n">
-        <v>20.87639829539785</v>
+        <v>20.87639829539784</v>
       </c>
       <c r="E2" t="n">
-        <v>20.86278265514303</v>
+        <v>20.86278265514302</v>
       </c>
       <c r="F2" t="n">
         <v>20.86098806517368</v>
       </c>
       <c r="G2" t="n">
-        <v>21.94551191208977</v>
+        <v>21.94551191208976</v>
       </c>
       <c r="H2" t="n">
-        <v>20.89547913583231</v>
+        <v>20.8954791358323</v>
       </c>
       <c r="I2" t="n">
-        <v>20.91180741697982</v>
+        <v>20.9118074169798</v>
       </c>
       <c r="J2" t="n">
-        <v>21.24942202380112</v>
+        <v>21.24942202380111</v>
       </c>
       <c r="K2" t="n">
-        <v>20.95244717056438</v>
+        <v>20.95244717056439</v>
       </c>
       <c r="L2" t="n">
-        <v>20.98825223266122</v>
+        <v>20.98825223266123</v>
       </c>
       <c r="M2" t="n">
-        <v>20.88582966245728</v>
+        <v>20.88582966245729</v>
       </c>
       <c r="N2" t="n">
-        <v>20.93795189686085</v>
+        <v>20.93795189686084</v>
       </c>
       <c r="O2" t="n">
-        <v>27.94832277072405</v>
+        <v>27.94832277072403</v>
       </c>
       <c r="P2" t="n">
-        <v>21.07701890323521</v>
+        <v>21.07701890323517</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.97293783232717</v>
+        <v>20.97293783232718</v>
       </c>
       <c r="R2" t="n">
         <v>20.90359964266711</v>
       </c>
       <c r="S2" t="n">
-        <v>20.92987548608454</v>
+        <v>20.92987548608455</v>
       </c>
       <c r="T2" t="n">
-        <v>20.87461593621385</v>
+        <v>20.87461593621381</v>
       </c>
       <c r="U2" t="n">
-        <v>24.23415387859044</v>
+        <v>24.23415387859041</v>
       </c>
       <c r="V2" t="n">
         <v>20.92789392076021</v>
       </c>
       <c r="W2" t="n">
-        <v>26.48071450536202</v>
+        <v>26.48071450536201</v>
       </c>
       <c r="X2" t="n">
         <v>21.12521771238208</v>
@@ -8404,7 +8404,7 @@
         <v>20.93506617923351</v>
       </c>
       <c r="AB2" t="n">
-        <v>21.53974546365549</v>
+        <v>21.53974546365518</v>
       </c>
     </row>
     <row r="3">
@@ -8414,13 +8414,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.84160817669284</v>
+        <v>20.84160817669282</v>
       </c>
       <c r="C3" t="n">
-        <v>11.00481446985116</v>
+        <v>11.00481446985114</v>
       </c>
       <c r="D3" t="n">
-        <v>20.21233256789329</v>
+        <v>20.2123325678933</v>
       </c>
       <c r="E3" t="n">
         <v>20.09748367311798</v>
@@ -8429,70 +8429,70 @@
         <v>20.10285887585774</v>
       </c>
       <c r="G3" t="n">
-        <v>27.78467881630232</v>
+        <v>27.78467881630226</v>
       </c>
       <c r="H3" t="n">
-        <v>20.35053064674156</v>
+        <v>20.35053064674155</v>
       </c>
       <c r="I3" t="n">
-        <v>20.46560986784602</v>
+        <v>20.46560986784603</v>
       </c>
       <c r="J3" t="n">
-        <v>22.85562330233474</v>
+        <v>22.85562330233471</v>
       </c>
       <c r="K3" t="n">
-        <v>20.75470455998502</v>
+        <v>20.75470455998501</v>
       </c>
       <c r="L3" t="n">
-        <v>21.00564276119712</v>
+        <v>21.00564276119713</v>
       </c>
       <c r="M3" t="n">
-        <v>21.14233674970643</v>
+        <v>21.14233674970639</v>
       </c>
       <c r="N3" t="n">
-        <v>20.65018603491587</v>
+        <v>20.65018603491586</v>
       </c>
       <c r="O3" t="n">
-        <v>32.26789356795456</v>
+        <v>32.26789356795454</v>
       </c>
       <c r="P3" t="n">
-        <v>21.63299826024182</v>
+        <v>21.63299826024179</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.89745270947101</v>
+        <v>20.897452709471</v>
       </c>
       <c r="R3" t="n">
-        <v>20.40750090062374</v>
+        <v>20.40750090062373</v>
       </c>
       <c r="S3" t="n">
-        <v>20.58847429262892</v>
+        <v>20.5884742926289</v>
       </c>
       <c r="T3" t="n">
-        <v>20.19929848282213</v>
+        <v>20.19929848282209</v>
       </c>
       <c r="U3" t="n">
         <v>26.27917928822697</v>
       </c>
       <c r="V3" t="n">
-        <v>20.57572736137039</v>
+        <v>20.57572736137037</v>
       </c>
       <c r="W3" t="n">
-        <v>30.46182400336551</v>
+        <v>30.46182400336556</v>
       </c>
       <c r="X3" t="n">
         <v>21.98741089947929</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.62074405401855</v>
+        <v>23.62074405401856</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.92501410688944</v>
+        <v>30.9250141068894</v>
       </c>
       <c r="AA3" t="n">
         <v>20.62860835292756</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.95184567577621</v>
+        <v>24.95184567577583</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.17360921039757</v>
+        <v>14.17360921039976</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04819953244791</v>
+        <v>13.04819953244588</v>
       </c>
       <c r="D4" t="n">
-        <v>13.16679594517775</v>
+        <v>13.16679594517741</v>
       </c>
       <c r="E4" t="n">
-        <v>13.01300102499631</v>
+        <v>13.0130010249952</v>
       </c>
       <c r="F4" t="n">
-        <v>12.99273030574207</v>
+        <v>12.99273030573943</v>
       </c>
       <c r="G4" t="n">
-        <v>25.24292606227611</v>
+        <v>25.24292606227479</v>
       </c>
       <c r="H4" t="n">
-        <v>13.38232281550444</v>
+        <v>13.38232281550495</v>
       </c>
       <c r="I4" t="n">
-        <v>13.56675826244346</v>
+        <v>13.5667582624463</v>
       </c>
       <c r="J4" t="n">
-        <v>17.34828621438416</v>
+        <v>17.34828621438638</v>
       </c>
       <c r="K4" t="n">
-        <v>14.02580297439696</v>
+        <v>14.02580297439447</v>
       </c>
       <c r="L4" t="n">
-        <v>14.43023762192465</v>
+        <v>14.43023762192045</v>
       </c>
       <c r="M4" t="n">
-        <v>14.86000651920487</v>
+        <v>14.860006519203</v>
       </c>
       <c r="N4" t="n">
-        <v>13.86207218975575</v>
+        <v>13.86207218975752</v>
       </c>
       <c r="O4" t="n">
-        <v>13.96677758316643</v>
+        <v>13.96677758316264</v>
       </c>
       <c r="P4" t="n">
-        <v>15.43289800073426</v>
+        <v>15.43289800073961</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.25725442517761</v>
+        <v>14.25725442517522</v>
       </c>
       <c r="R4" t="n">
-        <v>13.47404767582304</v>
+        <v>13.47404767582158</v>
       </c>
       <c r="S4" t="n">
-        <v>13.77084541470506</v>
+        <v>13.77084541470682</v>
       </c>
       <c r="T4" t="n">
-        <v>13.14666337826703</v>
+        <v>13.14666337826835</v>
       </c>
       <c r="U4" t="n">
-        <v>13.93953060076969</v>
+        <v>13.93953060077106</v>
       </c>
       <c r="V4" t="n">
-        <v>13.54350490495393</v>
+        <v>13.54350490495392</v>
       </c>
       <c r="W4" t="n">
-        <v>15.22783641299148</v>
+        <v>15.22783641299286</v>
       </c>
       <c r="X4" t="n">
-        <v>15.97732572260269</v>
+        <v>15.97732572260136</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.38932635847687</v>
+        <v>18.38932635847669</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.00141911956635</v>
+        <v>14.00141911956585</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.82947668165817</v>
+        <v>13.82947668166115</v>
       </c>
       <c r="AB4" t="n">
-        <v>20.63106579567165</v>
+        <v>20.63106579567434</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.89353042374759</v>
+        <v>51.89353042374765</v>
       </c>
       <c r="C5" t="n">
-        <v>35.96349435296958</v>
+        <v>35.96349435296941</v>
       </c>
       <c r="D5" t="n">
-        <v>37.65204751809782</v>
+        <v>37.65204751809797</v>
       </c>
       <c r="E5" t="n">
-        <v>25.77314294996634</v>
+        <v>25.77314294996473</v>
       </c>
       <c r="F5" t="n">
-        <v>34.83764667412054</v>
+        <v>34.83764667412247</v>
       </c>
       <c r="G5" t="n">
-        <v>221.1963686157756</v>
+        <v>221.1963686157744</v>
       </c>
       <c r="H5" t="n">
-        <v>42.50934285597533</v>
+        <v>42.50934285597623</v>
       </c>
       <c r="I5" t="n">
-        <v>45.0165754674363</v>
+        <v>45.01657546743557</v>
       </c>
       <c r="J5" t="n">
-        <v>102.2969726204869</v>
+        <v>102.2969726204854</v>
       </c>
       <c r="K5" t="n">
-        <v>52.64153833089612</v>
+        <v>52.64153833089509</v>
       </c>
       <c r="L5" t="n">
-        <v>57.40856437787113</v>
+        <v>57.40856437786884</v>
       </c>
       <c r="M5" t="n">
-        <v>67.91930996351971</v>
+        <v>67.9193099635189</v>
       </c>
       <c r="N5" t="n">
-        <v>51.94281208577757</v>
+        <v>51.94281208577719</v>
       </c>
       <c r="O5" t="n">
-        <v>48.42867090363904</v>
+        <v>48.42867090363636</v>
       </c>
       <c r="P5" t="n">
-        <v>71.94137315049704</v>
+        <v>71.94137315049866</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.92408641800677</v>
+        <v>54.92408641800679</v>
       </c>
       <c r="R5" t="n">
-        <v>43.62057093106206</v>
+        <v>43.62057093106039</v>
       </c>
       <c r="S5" t="n">
-        <v>45.47109391665922</v>
+        <v>45.47109391665848</v>
       </c>
       <c r="T5" t="n">
-        <v>37.13361072225395</v>
+        <v>37.13361072224911</v>
       </c>
       <c r="U5" t="n">
-        <v>52.19717981367745</v>
+        <v>52.19717981367644</v>
       </c>
       <c r="V5" t="n">
-        <v>45.59349526398937</v>
+        <v>45.59349526398938</v>
       </c>
       <c r="W5" t="n">
-        <v>72.79107421251558</v>
+        <v>72.79107421252144</v>
       </c>
       <c r="X5" t="n">
-        <v>86.96795969978643</v>
+        <v>86.96795969979028</v>
       </c>
       <c r="Y5" t="n">
-        <v>131.475701095043</v>
+        <v>131.4757010950416</v>
       </c>
       <c r="Z5" t="n">
-        <v>48.74415332019856</v>
+        <v>48.74415332019771</v>
       </c>
       <c r="AA5" t="n">
-        <v>48.10827149362321</v>
+        <v>48.10827149362561</v>
       </c>
       <c r="AB5" t="n">
-        <v>180.3860888745756</v>
+        <v>180.3860888745767</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.21202551174078</v>
+        <v>31.44638295153297</v>
       </c>
       <c r="C6" t="n">
-        <v>43.08661583378844</v>
+        <v>43.08661583378739</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43956968631587</v>
+        <v>30.43956968631063</v>
       </c>
       <c r="E6" t="n">
-        <v>30.28577476613306</v>
+        <v>43.05141732633666</v>
       </c>
       <c r="F6" t="n">
-        <v>30.26550404687081</v>
+        <v>43.0311466070809</v>
       </c>
       <c r="G6" t="n">
-        <v>55.28134236361657</v>
+        <v>42.51569980340804</v>
       </c>
       <c r="H6" t="n">
-        <v>30.65509655663853</v>
+        <v>43.42073911684642</v>
       </c>
       <c r="I6" t="n">
-        <v>30.83953200358021</v>
+        <v>43.6051745637878</v>
       </c>
       <c r="J6" t="n">
-        <v>47.38670251572811</v>
+        <v>34.62105995551962</v>
       </c>
       <c r="K6" t="n">
-        <v>31.29857671552162</v>
+        <v>44.06421927573591</v>
       </c>
       <c r="L6" t="n">
-        <v>44.46865392326787</v>
+        <v>31.70301136305366</v>
       </c>
       <c r="M6" t="n">
-        <v>32.13278026034034</v>
+        <v>44.89842282054448</v>
       </c>
       <c r="N6" t="n">
-        <v>31.14162171021236</v>
+        <v>31.14162171021339</v>
       </c>
       <c r="O6" t="n">
-        <v>43.70572460404163</v>
+        <v>31.24632710361852</v>
       </c>
       <c r="P6" t="n">
-        <v>31.67686057869413</v>
+        <v>31.67686057868757</v>
       </c>
       <c r="Q6" t="n">
-        <v>31.53002816631438</v>
+        <v>44.29567072651672</v>
       </c>
       <c r="R6" t="n">
-        <v>43.5124639771663</v>
+        <v>43.51246397716307</v>
       </c>
       <c r="S6" t="n">
-        <v>31.04361915584189</v>
+        <v>31.04361915584006</v>
       </c>
       <c r="T6" t="n">
-        <v>30.41943711940518</v>
+        <v>30.41943711940156</v>
       </c>
       <c r="U6" t="n">
-        <v>44.15485621899893</v>
+        <v>31.3892136587901</v>
       </c>
       <c r="V6" t="n">
-        <v>43.58192120629563</v>
+        <v>43.58192120629541</v>
       </c>
       <c r="W6" t="n">
-        <v>33.42503939298343</v>
+        <v>33.4250393929869</v>
       </c>
       <c r="X6" t="n">
-        <v>46.01574202394863</v>
+        <v>33.25009946373459</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.6123467820242</v>
+        <v>36.61234678202102</v>
       </c>
       <c r="Z6" t="n">
-        <v>31.27419286070309</v>
+        <v>31.27419286069906</v>
       </c>
       <c r="AA6" t="n">
-        <v>43.86789298300284</v>
+        <v>43.86789298300269</v>
       </c>
       <c r="AB6" t="n">
-        <v>37.94691898817996</v>
+        <v>37.9469189881869</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.39197373020165</v>
+        <v>18.39197373020184</v>
       </c>
       <c r="C7" t="n">
-        <v>17.26656405224929</v>
+        <v>17.26656405224798</v>
       </c>
       <c r="D7" t="n">
-        <v>17.38516046498047</v>
+        <v>17.3851604649795</v>
       </c>
       <c r="E7" t="n">
-        <v>17.23136554479771</v>
+        <v>17.23136554479729</v>
       </c>
       <c r="F7" t="n">
-        <v>17.21109482554355</v>
+        <v>17.21109482554153</v>
       </c>
       <c r="G7" t="n">
-        <v>29.46129058207883</v>
+        <v>29.4612905820768</v>
       </c>
       <c r="H7" t="n">
-        <v>17.60068733530451</v>
+        <v>17.60068733530705</v>
       </c>
       <c r="I7" t="n">
-        <v>17.78512278224621</v>
+        <v>17.7851227822484</v>
       </c>
       <c r="J7" t="n">
-        <v>21.56665073418965</v>
+        <v>21.56665073418846</v>
       </c>
       <c r="K7" t="n">
-        <v>18.24416749419705</v>
+        <v>18.24416749419657</v>
       </c>
       <c r="L7" t="n">
-        <v>18.64860214172342</v>
+        <v>18.64860214172255</v>
       </c>
       <c r="M7" t="n">
-        <v>19.07837103900624</v>
+        <v>19.07837103900508</v>
       </c>
       <c r="N7" t="n">
-        <v>18.08043670956116</v>
+        <v>18.0804367095596</v>
       </c>
       <c r="O7" t="n">
-        <v>18.18505915082938</v>
+        <v>18.1850591508278</v>
       </c>
       <c r="P7" t="n">
-        <v>19.6511795684053</v>
+        <v>19.65117956840475</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.47561894498439</v>
+        <v>18.47561894497733</v>
       </c>
       <c r="R7" t="n">
-        <v>17.69241219562315</v>
+        <v>17.69241219562368</v>
       </c>
       <c r="S7" t="n">
-        <v>17.98920993450786</v>
+        <v>17.98920993450894</v>
       </c>
       <c r="T7" t="n">
-        <v>17.36502789806842</v>
+        <v>17.36502789807045</v>
       </c>
       <c r="U7" t="n">
-        <v>18.3306260457397</v>
+        <v>18.33062604574125</v>
       </c>
       <c r="V7" t="n">
-        <v>17.76186942475601</v>
+        <v>17.76186942475604</v>
       </c>
       <c r="W7" t="n">
-        <v>19.44620093279564</v>
+        <v>19.44620093279494</v>
       </c>
       <c r="X7" t="n">
-        <v>20.19569024241087</v>
+        <v>20.19569024240347</v>
       </c>
       <c r="Y7" t="n">
-        <v>22.78460019516833</v>
+        <v>22.78460019516461</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.21978363936772</v>
+        <v>18.21978363936794</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.04784120145822</v>
+        <v>18.04784120146324</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.84943031547706</v>
+        <v>24.84943031547644</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.47622903593469</v>
+        <v>30.47622903593566</v>
       </c>
       <c r="C8" t="n">
-        <v>40.15093734696052</v>
+        <v>40.15093734695827</v>
       </c>
       <c r="D8" t="n">
-        <v>40.26953375969299</v>
+        <v>40.26953375968983</v>
       </c>
       <c r="E8" t="n">
-        <v>40.11573883951156</v>
+        <v>34.36499459379238</v>
       </c>
       <c r="F8" t="n">
-        <v>30.97788229039615</v>
+        <v>30.97788229039325</v>
       </c>
       <c r="G8" t="n">
-        <v>52.34566387678593</v>
+        <v>54.58513869807555</v>
       </c>
       <c r="H8" t="n">
-        <v>40.48506063001962</v>
+        <v>40.48506063001736</v>
       </c>
       <c r="I8" t="n">
-        <v>40.66949607696539</v>
+        <v>40.6694960769587</v>
       </c>
       <c r="J8" t="n">
-        <v>44.45102402889812</v>
+        <v>44.45102402889876</v>
       </c>
       <c r="K8" t="n">
-        <v>41.12854078890685</v>
+        <v>41.12854078890687</v>
       </c>
       <c r="L8" t="n">
-        <v>41.53297543643588</v>
+        <v>41.53297543643284</v>
       </c>
       <c r="M8" t="n">
-        <v>41.96274433371879</v>
+        <v>41.96274433371506</v>
       </c>
       <c r="N8" t="n">
-        <v>32.59291174260808</v>
+        <v>32.59291174260866</v>
       </c>
       <c r="O8" t="n">
-        <v>34.99828747066001</v>
+        <v>34.99828747065906</v>
       </c>
       <c r="P8" t="n">
-        <v>35.90045799719329</v>
+        <v>35.90045799718485</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.43740456503658</v>
+        <v>28.43740456503767</v>
       </c>
       <c r="R8" t="n">
-        <v>40.57678549033832</v>
+        <v>40.57678549033401</v>
       </c>
       <c r="S8" t="n">
-        <v>40.87358322922177</v>
+        <v>40.87358322921921</v>
       </c>
       <c r="T8" t="n">
-        <v>40.24940119278359</v>
+        <v>40.24940119278075</v>
       </c>
       <c r="U8" t="n">
-        <v>34.57036724897127</v>
+        <v>35.94461042457848</v>
       </c>
       <c r="V8" t="n">
-        <v>40.64624271946636</v>
+        <v>37.69090694705208</v>
       </c>
       <c r="W8" t="n">
-        <v>42.33269676083152</v>
+        <v>42.33269676083239</v>
       </c>
       <c r="X8" t="n">
-        <v>31.14732813673326</v>
+        <v>31.14732813673216</v>
       </c>
       <c r="Y8" t="n">
-        <v>56.40185542008204</v>
+        <v>56.40185542008776</v>
       </c>
       <c r="Z8" t="n">
-        <v>41.10415693408159</v>
+        <v>30.10342120861144</v>
       </c>
       <c r="AA8" t="n">
-        <v>40.93221449617476</v>
+        <v>40.93221449617358</v>
       </c>
       <c r="AB8" t="n">
-        <v>59.0154299414843</v>
+        <v>59.01542994148168</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.52038377629106</v>
+        <v>28.52038377629307</v>
       </c>
       <c r="C9" t="n">
-        <v>31.55486289331626</v>
+        <v>31.55486289331364</v>
       </c>
       <c r="D9" t="n">
-        <v>31.67345930604877</v>
+        <v>31.67345930604519</v>
       </c>
       <c r="E9" t="n">
-        <v>31.51966438586732</v>
+        <v>30.5595805913048</v>
       </c>
       <c r="F9" t="n">
-        <v>31.49939366660772</v>
+        <v>21.90971198621169</v>
       </c>
       <c r="G9" t="n">
-        <v>43.7495894231417</v>
+        <v>43.74959146609301</v>
       </c>
       <c r="H9" t="n">
-        <v>31.88898617637277</v>
+        <v>31.88898617637273</v>
       </c>
       <c r="I9" t="n">
-        <v>32.07342162331848</v>
+        <v>32.07342162331403</v>
       </c>
       <c r="J9" t="n">
-        <v>35.85494957525585</v>
+        <v>35.85494957525414</v>
       </c>
       <c r="K9" t="n">
-        <v>32.53246633526128</v>
+        <v>32.53246633526223</v>
       </c>
       <c r="L9" t="n">
-        <v>32.93690098279168</v>
+        <v>32.9369009827882</v>
       </c>
       <c r="M9" t="n">
-        <v>33.36666988007455</v>
+        <v>33.36666988007078</v>
       </c>
       <c r="N9" t="n">
-        <v>32.36873555062812</v>
+        <v>32.36873555062525</v>
       </c>
       <c r="O9" t="n">
-        <v>33.85202536375964</v>
+        <v>33.85202536376219</v>
       </c>
       <c r="P9" t="n">
-        <v>35.61796379579587</v>
+        <v>35.6179637957943</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.76391982899297</v>
+        <v>32.76391982899352</v>
       </c>
       <c r="R9" t="n">
-        <v>31.98071103669544</v>
+        <v>31.98071103668937</v>
       </c>
       <c r="S9" t="n">
-        <v>32.27750877557879</v>
+        <v>32.2775087755746</v>
       </c>
       <c r="T9" t="n">
-        <v>31.65332673913803</v>
+        <v>31.65332673913615</v>
       </c>
       <c r="U9" t="n">
-        <v>32.62310327852676</v>
+        <v>32.62310327852465</v>
       </c>
       <c r="V9" t="n">
-        <v>32.05016826582173</v>
+        <v>36.85059226979084</v>
       </c>
       <c r="W9" t="n">
-        <v>33.73449977386252</v>
+        <v>33.73449977386062</v>
       </c>
       <c r="X9" t="n">
-        <v>34.48398908346838</v>
+        <v>34.48398908346911</v>
       </c>
       <c r="Y9" t="n">
-        <v>37.07289903622856</v>
+        <v>37.07289903623029</v>
       </c>
       <c r="Z9" t="n">
-        <v>32.50808248043598</v>
+        <v>30.00004026004167</v>
       </c>
       <c r="AA9" t="n">
-        <v>32.33614004253321</v>
+        <v>32.33614004252892</v>
       </c>
       <c r="AB9" t="n">
-        <v>39.13772915654669</v>
+        <v>39.13772915654212</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.6147731589231</v>
+        <v>21.49427387479611</v>
       </c>
       <c r="C2" t="n">
-        <v>16.23337825937018</v>
+        <v>15.76453677347148</v>
       </c>
       <c r="D2" t="n">
-        <v>21.92729669313035</v>
+        <v>21.43226328160575</v>
       </c>
       <c r="E2" t="n">
-        <v>21.92665257161309</v>
+        <v>21.31732393755548</v>
       </c>
       <c r="F2" t="n">
-        <v>22.02082685606884</v>
+        <v>21.49031215024842</v>
       </c>
       <c r="G2" t="n">
-        <v>23.27655556849001</v>
+        <v>22.38231373995819</v>
       </c>
       <c r="H2" t="n">
-        <v>21.89999850345947</v>
+        <v>21.33738723680796</v>
       </c>
       <c r="I2" t="n">
-        <v>22.02419281090002</v>
+        <v>21.46990824765629</v>
       </c>
       <c r="J2" t="n">
-        <v>22.57822349481856</v>
+        <v>21.87948163404551</v>
       </c>
       <c r="K2" t="n">
-        <v>22.00433042658867</v>
+        <v>21.45591547663293</v>
       </c>
       <c r="L2" t="n">
-        <v>22.15981429290735</v>
+        <v>21.41731995975388</v>
       </c>
       <c r="M2" t="n">
-        <v>23.39668971328538</v>
+        <v>22.73855529438004</v>
       </c>
       <c r="N2" t="n">
-        <v>21.956233763044</v>
+        <v>21.43437383303733</v>
       </c>
       <c r="O2" t="n">
-        <v>29.66886044214729</v>
+        <v>28.89384478428557</v>
       </c>
       <c r="P2" t="n">
-        <v>22.19423053043051</v>
+        <v>21.70617251506718</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.94790900823231</v>
+        <v>21.36807231876991</v>
       </c>
       <c r="R2" t="n">
-        <v>21.8911073334746</v>
+        <v>21.34181164367454</v>
       </c>
       <c r="S2" t="n">
-        <v>22.3084395400904</v>
+        <v>21.61817821173706</v>
       </c>
       <c r="T2" t="n">
-        <v>21.96691785713237</v>
+        <v>21.38138220633868</v>
       </c>
       <c r="U2" t="n">
-        <v>26.01165911328462</v>
+        <v>25.2412364370762</v>
       </c>
       <c r="V2" t="n">
-        <v>22.0348529322723</v>
+        <v>21.46857710411926</v>
       </c>
       <c r="W2" t="n">
-        <v>27.91110240491925</v>
+        <v>27.23057379125946</v>
       </c>
       <c r="X2" t="n">
-        <v>22.09839910382856</v>
+        <v>21.49552618038708</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.1014770770169</v>
+        <v>21.64243821774006</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.8888102554288</v>
+        <v>27.96831273648419</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.20679830386469</v>
+        <v>21.67164353990161</v>
       </c>
       <c r="AB2" t="n">
-        <v>23.09174124460817</v>
+        <v>22.87338174561294</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.71177048427282</v>
+        <v>21.98656652168485</v>
       </c>
       <c r="C3" t="n">
-        <v>11.62216093548261</v>
+        <v>11.5730224471232</v>
       </c>
       <c r="D3" t="n">
-        <v>21.83451298643324</v>
+        <v>21.55607773405834</v>
       </c>
       <c r="E3" t="n">
-        <v>21.81004043917533</v>
+        <v>20.7157453947673</v>
       </c>
       <c r="F3" t="n">
-        <v>22.50770937486349</v>
+        <v>21.97505242685843</v>
       </c>
       <c r="G3" t="n">
-        <v>31.43155124971207</v>
+        <v>28.31054854378133</v>
       </c>
       <c r="H3" t="n">
-        <v>21.64327368202101</v>
+        <v>20.88011033539232</v>
       </c>
       <c r="I3" t="n">
-        <v>22.52977925484184</v>
+        <v>21.82695888418551</v>
       </c>
       <c r="J3" t="n">
-        <v>26.46783852432716</v>
+        <v>24.73819906868664</v>
       </c>
       <c r="K3" t="n">
-        <v>22.38492243794064</v>
+        <v>21.72448331150946</v>
       </c>
       <c r="L3" t="n">
-        <v>23.48832928080673</v>
+        <v>21.44378752874241</v>
       </c>
       <c r="M3" t="n">
-        <v>33.15985594668322</v>
+        <v>31.70001337429634</v>
       </c>
       <c r="N3" t="n">
-        <v>22.03868393429902</v>
+        <v>21.56836897560769</v>
       </c>
       <c r="O3" t="n">
-        <v>35.72306562219285</v>
+        <v>34.70796329750474</v>
       </c>
       <c r="P3" t="n">
-        <v>23.72390220807924</v>
+        <v>23.49451157462831</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.98011842111961</v>
+        <v>21.09524535996798</v>
       </c>
       <c r="R3" t="n">
-        <v>21.57751330739046</v>
+        <v>20.91020233461428</v>
       </c>
       <c r="S3" t="n">
-        <v>24.54054995668109</v>
+        <v>22.87152297481995</v>
       </c>
       <c r="T3" t="n">
-        <v>22.11860275220802</v>
+        <v>21.1921625904426</v>
       </c>
       <c r="U3" t="n">
-        <v>31.25636540436967</v>
+        <v>29.86626164761305</v>
       </c>
       <c r="V3" t="n">
-        <v>22.59123944629648</v>
+        <v>21.80548155796395</v>
       </c>
       <c r="W3" t="n">
-        <v>32.81455243936725</v>
+        <v>32.13212079855701</v>
       </c>
       <c r="X3" t="n">
-        <v>23.05751999970946</v>
+        <v>22.00763225903866</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.07429139293061</v>
+        <v>23.05253695334803</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.7228276427156</v>
+        <v>33.27441209796649</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.82668102121088</v>
+        <v>23.26148492218728</v>
       </c>
       <c r="AB3" t="n">
-        <v>30.17014824359538</v>
+        <v>31.82646629409132</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.88524247260246</v>
+        <v>14.24029911125382</v>
       </c>
       <c r="C4" t="n">
-        <v>14.44660498580765</v>
+        <v>12.25413840473276</v>
       </c>
       <c r="D4" t="n">
-        <v>16.11987953667442</v>
+        <v>13.53986093488619</v>
       </c>
       <c r="E4" t="n">
-        <v>16.11260388782603</v>
+        <v>12.24156816912782</v>
       </c>
       <c r="F4" t="n">
-        <v>17.17634575306527</v>
+        <v>14.1955496100043</v>
       </c>
       <c r="G4" t="n">
-        <v>31.36037922360951</v>
+        <v>24.27111790678019</v>
       </c>
       <c r="H4" t="n">
-        <v>15.81153392655414</v>
+        <v>12.46819236375814</v>
       </c>
       <c r="I4" t="n">
-        <v>17.21436576129871</v>
+        <v>13.96507814396694</v>
       </c>
       <c r="J4" t="n">
-        <v>23.43886390952029</v>
+        <v>18.55946950438403</v>
       </c>
       <c r="K4" t="n">
-        <v>16.99001099335418</v>
+        <v>13.80702335826547</v>
       </c>
       <c r="L4" t="n">
-        <v>18.74627278953602</v>
+        <v>13.37106924030157</v>
       </c>
       <c r="M4" t="n">
-        <v>34.17817882618359</v>
+        <v>29.73190512023366</v>
       </c>
       <c r="N4" t="n">
-        <v>16.44673705305869</v>
+        <v>72.74358057785906</v>
       </c>
       <c r="O4" t="n">
-        <v>18.44119112747803</v>
+        <v>15.29391679713817</v>
       </c>
       <c r="P4" t="n">
-        <v>19.13502002461162</v>
+        <v>16.63379173130573</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.35270511788411</v>
+        <v>12.81479448035322</v>
       </c>
       <c r="R4" t="n">
-        <v>15.71110407143465</v>
+        <v>12.51816807464395</v>
       </c>
       <c r="S4" t="n">
-        <v>20.42506332745985</v>
+        <v>15.6398555958127</v>
       </c>
       <c r="T4" t="n">
-        <v>16.56741881071277</v>
+        <v>12.96513578329369</v>
       </c>
       <c r="U4" t="n">
-        <v>21.28592765514766</v>
+        <v>17.42290061528121</v>
       </c>
       <c r="V4" t="n">
-        <v>17.11938812198757</v>
+        <v>13.74551665879871</v>
       </c>
       <c r="W4" t="n">
-        <v>18.39844638386723</v>
+        <v>15.61768573392326</v>
       </c>
       <c r="X4" t="n">
-        <v>18.05255997650791</v>
+        <v>14.25444447899257</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.85304539766675</v>
+        <v>15.75080861618461</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.08880950389305</v>
+        <v>15.47831740717692</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.27697880701184</v>
+        <v>16.24377107269715</v>
       </c>
       <c r="AB4" t="n">
-        <v>29.22406090092803</v>
+        <v>29.6757422026279</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212.2826639206133</v>
+        <v>80.83421244859886</v>
       </c>
       <c r="C5" t="n">
-        <v>37.78545271724875</v>
+        <v>46.43740104499177</v>
       </c>
       <c r="D5" t="n">
-        <v>73.31721097296864</v>
+        <v>73.9109609922002</v>
       </c>
       <c r="E5" t="n">
-        <v>61.35774502076619</v>
+        <v>35.87646203413695</v>
       </c>
       <c r="F5" t="n">
-        <v>97.96031996290229</v>
+        <v>89.89490808415709</v>
       </c>
       <c r="G5" t="n">
-        <v>360.7990428075389</v>
+        <v>274.5107872497488</v>
       </c>
       <c r="H5" t="n">
-        <v>69.24105507676735</v>
+        <v>53.02386112773907</v>
       </c>
       <c r="I5" t="n">
-        <v>97.5651323032117</v>
+        <v>83.7857403695111</v>
       </c>
       <c r="J5" t="n">
-        <v>213.99457369058</v>
+        <v>169.8419161308594</v>
       </c>
       <c r="K5" t="n">
-        <v>91.20582045932483</v>
+        <v>79.05251456739906</v>
       </c>
       <c r="L5" t="n">
-        <v>122.835134227093</v>
+        <v>67.16033777320823</v>
       </c>
       <c r="M5" t="n">
-        <v>463.4293699861497</v>
+        <v>423.8657334709086</v>
       </c>
       <c r="N5" t="n">
-        <v>170.7592119567201</v>
+        <v>72.74358057785906</v>
       </c>
       <c r="O5" t="n">
-        <v>109.4781357312708</v>
+        <v>99.2542874061364</v>
       </c>
       <c r="P5" t="n">
-        <v>124.6860096352355</v>
+        <v>126.4271245696352</v>
       </c>
       <c r="Q5" t="n">
-        <v>77.11091348807646</v>
+        <v>57.7059648293685</v>
       </c>
       <c r="R5" t="n">
-        <v>65.84943938861259</v>
+        <v>53.1475284451575</v>
       </c>
       <c r="S5" t="n">
-        <v>151.5754605672234</v>
+        <v>109.4016392111159</v>
       </c>
       <c r="T5" t="n">
-        <v>83.10920457861906</v>
+        <v>61.8769843273186</v>
       </c>
       <c r="U5" t="n">
-        <v>175.8326842607502</v>
+        <v>149.5541684812713</v>
       </c>
       <c r="V5" t="n">
-        <v>91.08420248491848</v>
+        <v>76.15996438588667</v>
       </c>
       <c r="W5" t="n">
-        <v>116.7896480374106</v>
+        <v>113.1629904501172</v>
       </c>
       <c r="X5" t="n">
-        <v>113.3311851320153</v>
+        <v>88.32732513037396</v>
       </c>
       <c r="Y5" t="n">
-        <v>110.9429276373035</v>
+        <v>119.5969732904747</v>
       </c>
       <c r="Z5" t="n">
-        <v>163.6224978350546</v>
+        <v>105.7272039303549</v>
       </c>
       <c r="AA5" t="n">
-        <v>135.3200297008274</v>
+        <v>126.5422050581317</v>
       </c>
       <c r="AB5" t="n">
-        <v>367.7724391777456</v>
+        <v>435.8941750601039</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.06110183717151</v>
+        <v>34.22280182286057</v>
       </c>
       <c r="C6" t="n">
-        <v>49.6224643503767</v>
+        <v>47.08503157586952</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10407196336482</v>
+        <v>48.37075410602298</v>
       </c>
       <c r="E6" t="n">
-        <v>36.09679631451638</v>
+        <v>47.07246134026461</v>
       </c>
       <c r="F6" t="n">
-        <v>52.35220511763428</v>
+        <v>34.178052321611</v>
       </c>
       <c r="G6" t="n">
-        <v>66.53623858817859</v>
+        <v>59.102011077917</v>
       </c>
       <c r="H6" t="n">
-        <v>50.98739329112315</v>
+        <v>47.299085534895</v>
       </c>
       <c r="I6" t="n">
-        <v>37.19855818798908</v>
+        <v>33.9475808555737</v>
       </c>
       <c r="J6" t="n">
-        <v>58.61472327408934</v>
+        <v>38.54197221599075</v>
       </c>
       <c r="K6" t="n">
-        <v>36.97420342004461</v>
+        <v>48.63791652940228</v>
       </c>
       <c r="L6" t="n">
-        <v>38.73046521622641</v>
+        <v>48.20196241143842</v>
       </c>
       <c r="M6" t="n">
-        <v>54.162371252874</v>
+        <v>64.5627982913705</v>
       </c>
       <c r="N6" t="n">
-        <v>36.44736787333219</v>
+        <v>72.74358057785906</v>
       </c>
       <c r="O6" t="n">
-        <v>53.26927127824355</v>
+        <v>35.29190300955802</v>
       </c>
       <c r="P6" t="n">
-        <v>53.96308812198394</v>
+        <v>51.09565332470645</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.33689754457455</v>
+        <v>47.64568765149008</v>
       </c>
       <c r="R6" t="n">
-        <v>35.69529649812505</v>
+        <v>47.34906124578075</v>
       </c>
       <c r="S6" t="n">
-        <v>55.60092269202892</v>
+        <v>35.62235830741938</v>
       </c>
       <c r="T6" t="n">
-        <v>36.55161123740316</v>
+        <v>32.9476384949004</v>
       </c>
       <c r="U6" t="n">
-        <v>41.50440178377946</v>
+        <v>37.56847823447384</v>
       </c>
       <c r="V6" t="n">
-        <v>52.2952474865566</v>
+        <v>48.57640982993553</v>
       </c>
       <c r="W6" t="n">
-        <v>53.22651936474031</v>
+        <v>50.07955208986171</v>
       </c>
       <c r="X6" t="n">
-        <v>53.22841934107699</v>
+        <v>49.08533765012943</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.97462804207835</v>
+        <v>36.80047453711332</v>
       </c>
       <c r="Z6" t="n">
-        <v>41.07300193058347</v>
+        <v>35.46082011878364</v>
       </c>
       <c r="AA6" t="n">
-        <v>39.2611712337022</v>
+        <v>51.074664243834</v>
       </c>
       <c r="AB6" t="n">
-        <v>49.29256513660556</v>
+        <v>49.76992658177956</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.31002914318184</v>
+        <v>19.38286753229233</v>
       </c>
       <c r="C7" t="n">
-        <v>19.87139165638716</v>
+        <v>17.39670682577128</v>
       </c>
       <c r="D7" t="n">
-        <v>21.54466620725393</v>
+        <v>18.6824293559247</v>
       </c>
       <c r="E7" t="n">
-        <v>21.53739055840554</v>
+        <v>17.38413659016634</v>
       </c>
       <c r="F7" t="n">
-        <v>22.60113242364477</v>
+        <v>19.33811803104279</v>
       </c>
       <c r="G7" t="n">
-        <v>36.78516589418902</v>
+        <v>29.41368632781873</v>
       </c>
       <c r="H7" t="n">
-        <v>21.23632059713365</v>
+        <v>17.61076078479666</v>
       </c>
       <c r="I7" t="n">
-        <v>22.63915243187822</v>
+        <v>19.10764656500545</v>
       </c>
       <c r="J7" t="n">
-        <v>28.86365058009979</v>
+        <v>23.70203792542255</v>
       </c>
       <c r="K7" t="n">
-        <v>22.41479766393369</v>
+        <v>18.949591779304</v>
       </c>
       <c r="L7" t="n">
-        <v>24.17105946011554</v>
+        <v>18.5136376613401</v>
       </c>
       <c r="M7" t="n">
-        <v>39.60296549676309</v>
+        <v>34.87447354127217</v>
       </c>
       <c r="N7" t="n">
-        <v>21.87152372363821</v>
+        <v>72.74358057785906</v>
       </c>
       <c r="O7" t="n">
-        <v>23.86587678587839</v>
+        <v>20.43638439411393</v>
       </c>
       <c r="P7" t="n">
-        <v>24.55970568301199</v>
+        <v>21.77625932828149</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.77749178846362</v>
+        <v>17.95736290139171</v>
       </c>
       <c r="R7" t="n">
-        <v>21.13589074201418</v>
+        <v>17.66073649568247</v>
       </c>
       <c r="S7" t="n">
-        <v>25.84984999803935</v>
+        <v>20.7824240168512</v>
       </c>
       <c r="T7" t="n">
-        <v>21.99220548129226</v>
+        <v>18.10770420433222</v>
       </c>
       <c r="U7" t="n">
-        <v>26.94002247478684</v>
+        <v>22.72503963249836</v>
       </c>
       <c r="V7" t="n">
-        <v>22.54417479256707</v>
+        <v>18.88808507983721</v>
       </c>
       <c r="W7" t="n">
-        <v>23.82323305444675</v>
+        <v>20.76025415496173</v>
       </c>
       <c r="X7" t="n">
-        <v>23.47734664708741</v>
+        <v>19.39701290003109</v>
       </c>
       <c r="Y7" t="n">
-        <v>23.51211377018766</v>
+        <v>21.05645194480906</v>
       </c>
       <c r="Z7" t="n">
-        <v>26.51359617447257</v>
+        <v>20.62088582821544</v>
       </c>
       <c r="AA7" t="n">
-        <v>24.70176547759134</v>
+        <v>21.38633949373566</v>
       </c>
       <c r="AB7" t="n">
-        <v>34.6488475715075</v>
+        <v>34.81831062366643</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.58721287853874</v>
+        <v>33.49483799447192</v>
       </c>
       <c r="C8" t="n">
-        <v>47.28428631267651</v>
+        <v>44.2641442296689</v>
       </c>
       <c r="D8" t="n">
-        <v>48.95756086354328</v>
+        <v>45.54986675982229</v>
       </c>
       <c r="E8" t="n">
-        <v>41.95590662839572</v>
+        <v>37.45966411017863</v>
       </c>
       <c r="F8" t="n">
-        <v>38.92470640027043</v>
+        <v>35.43724116654578</v>
       </c>
       <c r="G8" t="n">
-        <v>66.92183578118077</v>
+        <v>58.92605289627778</v>
       </c>
       <c r="H8" t="n">
-        <v>48.64921525342301</v>
+        <v>44.47819818869428</v>
       </c>
       <c r="I8" t="n">
-        <v>50.05204708816755</v>
+        <v>45.97508396890308</v>
       </c>
       <c r="J8" t="n">
-        <v>56.27654523638913</v>
+        <v>50.56947532932017</v>
       </c>
       <c r="K8" t="n">
-        <v>49.82769232022304</v>
+        <v>45.8170291832016</v>
       </c>
       <c r="L8" t="n">
-        <v>51.58395411640488</v>
+        <v>45.38107506523768</v>
       </c>
       <c r="M8" t="n">
-        <v>67.01586015305259</v>
+        <v>61.74191094517046</v>
       </c>
       <c r="N8" t="n">
-        <v>39.10204485981949</v>
+        <v>72.74358057785906</v>
       </c>
       <c r="O8" t="n">
-        <v>43.89470359000318</v>
+        <v>40.13350585460747</v>
       </c>
       <c r="P8" t="n">
-        <v>43.9026249118636</v>
+        <v>40.80732841792073</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.47320851971391</v>
+        <v>29.56259297999511</v>
       </c>
       <c r="R8" t="n">
-        <v>48.54878539830351</v>
+        <v>44.52817389958005</v>
       </c>
       <c r="S8" t="n">
-        <v>53.26274465432871</v>
+        <v>47.64986142074882</v>
       </c>
       <c r="T8" t="n">
-        <v>49.40510013758163</v>
+        <v>44.97514160822984</v>
       </c>
       <c r="U8" t="n">
-        <v>47.94274940480065</v>
+        <v>43.36757056019276</v>
       </c>
       <c r="V8" t="n">
-        <v>46.36271666486422</v>
+        <v>42.26635182314928</v>
       </c>
       <c r="W8" t="n">
-        <v>51.23870925500425</v>
+        <v>47.63019837439488</v>
       </c>
       <c r="X8" t="n">
-        <v>36.37697738571631</v>
+        <v>32.17130686982671</v>
       </c>
       <c r="Y8" t="n">
-        <v>63.97908699974066</v>
+        <v>60.60184759692144</v>
       </c>
       <c r="Z8" t="n">
-        <v>40.54677733553581</v>
+        <v>34.49591694322211</v>
       </c>
       <c r="AA8" t="n">
-        <v>52.11466013388069</v>
+        <v>48.2537768976333</v>
       </c>
       <c r="AB8" t="n">
-        <v>75.78309067562478</v>
+        <v>75.00989984371908</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45.36419901995767</v>
+        <v>33.99020295776748</v>
       </c>
       <c r="C9" t="n">
-        <v>42.13436087162808</v>
+        <v>37.6929015442002</v>
       </c>
       <c r="D9" t="n">
-        <v>43.80763542249485</v>
+        <v>38.97862407435362</v>
       </c>
       <c r="E9" t="n">
-        <v>42.36739429305322</v>
+        <v>36.36736483720203</v>
       </c>
       <c r="F9" t="n">
-        <v>30.55112448332007</v>
+        <v>26.51994105598753</v>
       </c>
       <c r="G9" t="n">
-        <v>59.04813521537672</v>
+        <v>49.70987980988851</v>
       </c>
       <c r="H9" t="n">
-        <v>43.49928981237454</v>
+        <v>37.90695550322561</v>
       </c>
       <c r="I9" t="n">
-        <v>44.90212164711912</v>
+        <v>39.40384128343436</v>
       </c>
       <c r="J9" t="n">
-        <v>51.12661979534067</v>
+        <v>43.99823264385148</v>
       </c>
       <c r="K9" t="n">
-        <v>44.67776687917461</v>
+        <v>39.24578649773294</v>
       </c>
       <c r="L9" t="n">
-        <v>46.43402867535642</v>
+        <v>38.80983237976906</v>
       </c>
       <c r="M9" t="n">
-        <v>61.86593471200401</v>
+        <v>55.17066825970108</v>
       </c>
       <c r="N9" t="n">
-        <v>44.13449293887913</v>
+        <v>72.74358057785906</v>
       </c>
       <c r="O9" t="n">
-        <v>48.18653512540016</v>
+        <v>42.61795881128376</v>
       </c>
       <c r="P9" t="n">
-        <v>49.32785411160245</v>
+        <v>44.3678498236375</v>
       </c>
       <c r="Q9" t="n">
-        <v>44.04046110965136</v>
+        <v>38.25355638346152</v>
       </c>
       <c r="R9" t="n">
-        <v>43.39885995725508</v>
+        <v>37.95693121411139</v>
       </c>
       <c r="S9" t="n">
-        <v>48.11281921328029</v>
+        <v>41.07861873528013</v>
       </c>
       <c r="T9" t="n">
-        <v>44.25517469653315</v>
+        <v>38.40389892276117</v>
       </c>
       <c r="U9" t="n">
-        <v>49.20796524290949</v>
+        <v>43.02473866233461</v>
       </c>
       <c r="V9" t="n">
-        <v>51.97195962461829</v>
+        <v>45.74909456287626</v>
       </c>
       <c r="W9" t="n">
-        <v>46.08620226968767</v>
+        <v>41.05644887339069</v>
       </c>
       <c r="X9" t="n">
-        <v>45.74031586232834</v>
+        <v>39.69320761846004</v>
       </c>
       <c r="Y9" t="n">
-        <v>45.77508298542857</v>
+        <v>41.35264666323796</v>
       </c>
       <c r="Z9" t="n">
-        <v>45.03321153866818</v>
+        <v>37.48720377515487</v>
       </c>
       <c r="AA9" t="n">
-        <v>46.96473469283222</v>
+        <v>41.68253421216462</v>
       </c>
       <c r="AB9" t="n">
-        <v>56.9118167867484</v>
+        <v>55.11450534209533</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.10365442421887</v>
+        <v>20.19137928957402</v>
       </c>
       <c r="C2" t="n">
-        <v>14.44776792041822</v>
+        <v>14.53624947580798</v>
       </c>
       <c r="D2" t="n">
-        <v>20.01765429086684</v>
+        <v>20.10478654650179</v>
       </c>
       <c r="E2" t="n">
-        <v>19.98427164334042</v>
+        <v>20.07135631875591</v>
       </c>
       <c r="F2" t="n">
-        <v>20.03192603936754</v>
+        <v>20.11888445956161</v>
       </c>
       <c r="G2" t="n">
-        <v>20.09519499973437</v>
+        <v>20.17333585895253</v>
       </c>
       <c r="H2" t="n">
-        <v>20.0746674779864</v>
+        <v>20.1620060997065</v>
       </c>
       <c r="I2" t="n">
-        <v>20.11849011388137</v>
+        <v>20.19943372885131</v>
       </c>
       <c r="J2" t="n">
-        <v>20.07858439440225</v>
+        <v>20.16228729554945</v>
       </c>
       <c r="K2" t="n">
-        <v>20.10046986276369</v>
+        <v>20.17856747378477</v>
       </c>
       <c r="L2" t="n">
-        <v>20.06313781352827</v>
+        <v>20.14749188057354</v>
       </c>
       <c r="M2" t="n">
-        <v>19.92226634415952</v>
+        <v>20.00916939639456</v>
       </c>
       <c r="N2" t="n">
-        <v>20.05394106591794</v>
+        <v>20.14156090510413</v>
       </c>
       <c r="O2" t="n">
-        <v>26.80124736790884</v>
+        <v>26.90299114729642</v>
       </c>
       <c r="P2" t="n">
-        <v>20.08180943582521</v>
+        <v>20.16865328853671</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.0806345049116</v>
+        <v>20.16808114888288</v>
       </c>
       <c r="R2" t="n">
-        <v>20.09840674134291</v>
+        <v>20.18323151285802</v>
       </c>
       <c r="S2" t="n">
-        <v>20.0724461278893</v>
+        <v>20.15767394278448</v>
       </c>
       <c r="T2" t="n">
-        <v>20.03123022188858</v>
+        <v>20.11040936408481</v>
       </c>
       <c r="U2" t="n">
-        <v>23.33169710427291</v>
+        <v>23.39832796023908</v>
       </c>
       <c r="V2" t="n">
-        <v>20.07332743674587</v>
+        <v>20.16040428566181</v>
       </c>
       <c r="W2" t="n">
-        <v>25.53927450371254</v>
+        <v>25.6245834108532</v>
       </c>
       <c r="X2" t="n">
-        <v>20.29810715758065</v>
+        <v>20.38480134841038</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.26926682687691</v>
+        <v>20.3566091347899</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.22018571330784</v>
+        <v>26.30586283482008</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.12986716815421</v>
+        <v>20.2148519028519</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.03278547027455</v>
+        <v>20.11991376212034</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.08083389370513</v>
+        <v>20.17729243564109</v>
       </c>
       <c r="C3" t="n">
-        <v>10.18427035860091</v>
+        <v>10.27759461831922</v>
       </c>
       <c r="D3" t="n">
-        <v>19.47434986210089</v>
+        <v>19.56666454192426</v>
       </c>
       <c r="E3" t="n">
-        <v>19.22045624224205</v>
+        <v>19.3126864681297</v>
       </c>
       <c r="F3" t="n">
-        <v>19.57621415320087</v>
+        <v>19.66725672395556</v>
       </c>
       <c r="G3" t="n">
-        <v>20.02153701921722</v>
+        <v>20.0501205291306</v>
       </c>
       <c r="H3" t="n">
-        <v>19.88400294750157</v>
+        <v>19.97775811685509</v>
       </c>
       <c r="I3" t="n">
-        <v>20.195001026603</v>
+        <v>20.24302437056768</v>
       </c>
       <c r="J3" t="n">
-        <v>19.90560746028057</v>
+        <v>19.97357631133306</v>
       </c>
       <c r="K3" t="n">
-        <v>20.06387039924552</v>
+        <v>20.09212791585122</v>
       </c>
       <c r="L3" t="n">
-        <v>19.79591441408052</v>
+        <v>19.86853216803725</v>
       </c>
       <c r="M3" t="n">
-        <v>19.64546354886047</v>
+        <v>19.73594695084488</v>
       </c>
       <c r="N3" t="n">
-        <v>19.73122115607154</v>
+        <v>19.82691071544164</v>
       </c>
       <c r="O3" t="n">
-        <v>30.93758395818487</v>
+        <v>31.05374293192118</v>
       </c>
       <c r="P3" t="n">
-        <v>19.92528173857638</v>
+        <v>20.01549927418568</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.92096652609811</v>
+        <v>20.0154858026433</v>
       </c>
       <c r="R3" t="n">
-        <v>20.05253435956117</v>
+        <v>20.12825141291233</v>
       </c>
       <c r="S3" t="n">
-        <v>19.85965408703403</v>
+        <v>19.93842343892666</v>
       </c>
       <c r="T3" t="n">
-        <v>19.57042601262631</v>
+        <v>19.6057634945133</v>
       </c>
       <c r="U3" t="n">
-        <v>25.51027960713052</v>
+        <v>25.46972373601304</v>
       </c>
       <c r="V3" t="n">
-        <v>19.86685942069395</v>
+        <v>19.95878943308934</v>
       </c>
       <c r="W3" t="n">
-        <v>29.50793293609661</v>
+        <v>29.5975300819228</v>
       </c>
       <c r="X3" t="n">
-        <v>21.47201688571535</v>
+        <v>21.56118627914537</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.26883236969733</v>
+        <v>21.3625329652938</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.87226463968932</v>
+        <v>29.95213913714498</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.27262447005728</v>
+        <v>20.34948612940098</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.60214602975991</v>
+        <v>19.69411945520847</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.86425445933666</v>
+        <v>11.87258848828511</v>
       </c>
       <c r="C4" t="n">
-        <v>11.70190921405299</v>
+        <v>10.70107309328989</v>
       </c>
       <c r="D4" t="n">
-        <v>11.89284339110963</v>
+        <v>10.89448362065437</v>
       </c>
       <c r="E4" t="n">
-        <v>11.51577103052226</v>
+        <v>10.51687381960019</v>
       </c>
       <c r="F4" t="n">
-        <v>12.05404935575377</v>
+        <v>11.05372603402556</v>
       </c>
       <c r="G4" t="n">
-        <v>12.76870136825688</v>
+        <v>11.66877963902715</v>
       </c>
       <c r="H4" t="n">
-        <v>12.53683356698684</v>
+        <v>11.54080479639646</v>
       </c>
       <c r="I4" t="n">
-        <v>13.03183039882912</v>
+        <v>11.96356708514715</v>
       </c>
       <c r="J4" t="n">
-        <v>12.55309244563925</v>
+        <v>11.51603531012891</v>
       </c>
       <c r="K4" t="n">
-        <v>12.82828337272978</v>
+        <v>11.72787313521847</v>
       </c>
       <c r="L4" t="n">
-        <v>12.40660070302481</v>
+        <v>11.37686001441907</v>
       </c>
       <c r="M4" t="n">
-        <v>12.38118195130363</v>
+        <v>11.37983543372416</v>
       </c>
       <c r="N4" t="n">
-        <v>40.77114717237048</v>
+        <v>40.02814120245156</v>
       </c>
       <c r="O4" t="n">
-        <v>12.45191807146758</v>
+        <v>11.45298895905783</v>
       </c>
       <c r="P4" t="n">
-        <v>12.61750526623919</v>
+        <v>11.61588785209176</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.60423388107527</v>
+        <v>11.6094252715045</v>
       </c>
       <c r="R4" t="n">
-        <v>12.80497946719954</v>
+        <v>11.78055560211542</v>
       </c>
       <c r="S4" t="n">
-        <v>12.5117423957684</v>
+        <v>11.49187109107167</v>
       </c>
       <c r="T4" t="n">
-        <v>12.04618977723706</v>
+        <v>10.95799593187838</v>
       </c>
       <c r="U4" t="n">
-        <v>12.85829330732556</v>
+        <v>11.6569894502576</v>
       </c>
       <c r="V4" t="n">
-        <v>12.34385727782685</v>
+        <v>11.34513246654943</v>
       </c>
       <c r="W4" t="n">
-        <v>13.79184962436073</v>
+        <v>12.79430179900362</v>
       </c>
       <c r="X4" t="n">
-        <v>15.06068753533449</v>
+        <v>14.05737962138519</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.66362193873909</v>
+        <v>13.67034828335369</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.23213239929782</v>
+        <v>11.21289781763244</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.16033946054463</v>
+        <v>12.13772245319447</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.09733958031458</v>
+        <v>11.09843925877467</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.01117667170563</v>
+        <v>47.29920915022181</v>
       </c>
       <c r="C5" t="n">
-        <v>31.32728141296068</v>
+        <v>30.50608771152003</v>
       </c>
       <c r="D5" t="n">
-        <v>34.61487127967557</v>
+        <v>33.82888482341158</v>
       </c>
       <c r="E5" t="n">
-        <v>19.84069026029011</v>
+        <v>19.17741214784023</v>
       </c>
       <c r="F5" t="n">
-        <v>37.46923142650299</v>
+        <v>36.6322249686247</v>
       </c>
       <c r="G5" t="n">
-        <v>46.88004705132833</v>
+        <v>44.52624183810126</v>
       </c>
       <c r="H5" t="n">
-        <v>47.42852906216176</v>
+        <v>46.66700276259004</v>
       </c>
       <c r="I5" t="n">
-        <v>55.26804639832531</v>
+        <v>53.18211482358475</v>
       </c>
       <c r="J5" t="n">
-        <v>44.89196441525623</v>
+        <v>43.48808956194219</v>
       </c>
       <c r="K5" t="n">
-        <v>50.36247141968825</v>
+        <v>47.99104593575507</v>
       </c>
       <c r="L5" t="n">
-        <v>42.11905757791187</v>
+        <v>40.84601016763983</v>
       </c>
       <c r="M5" t="n">
-        <v>43.86215657924338</v>
+        <v>43.0340641236287</v>
       </c>
       <c r="N5" t="n">
-        <v>40.77114717237048</v>
+        <v>40.02814120245156</v>
       </c>
       <c r="O5" t="n">
-        <v>41.45652499996928</v>
+        <v>40.66142054900279</v>
       </c>
       <c r="P5" t="n">
-        <v>43.8318172621605</v>
+        <v>42.96810783145703</v>
       </c>
       <c r="Q5" t="n">
-        <v>45.70643534556238</v>
+        <v>44.96293821331807</v>
       </c>
       <c r="R5" t="n">
-        <v>51.70633919719791</v>
+        <v>50.39251664632429</v>
       </c>
       <c r="S5" t="n">
-        <v>42.58244508598287</v>
+        <v>41.44022413058418</v>
       </c>
       <c r="T5" t="n">
-        <v>36.90421182576389</v>
+        <v>34.41771993614323</v>
       </c>
       <c r="U5" t="n">
-        <v>50.14302167850035</v>
+        <v>46.16629457797177</v>
       </c>
       <c r="V5" t="n">
-        <v>43.05504893421226</v>
+        <v>42.26383707065441</v>
       </c>
       <c r="W5" t="n">
-        <v>66.52471249046508</v>
+        <v>65.70015677383869</v>
       </c>
       <c r="X5" t="n">
-        <v>88.60210047204959</v>
+        <v>87.71885736095145</v>
       </c>
       <c r="Y5" t="n">
-        <v>84.21389535898848</v>
+        <v>83.41119027918924</v>
       </c>
       <c r="Z5" t="n">
-        <v>37.8710499716893</v>
+        <v>36.76818722414653</v>
       </c>
       <c r="AA5" t="n">
-        <v>55.68820504116391</v>
+        <v>54.40786373771957</v>
       </c>
       <c r="AB5" t="n">
-        <v>39.03917460198872</v>
+        <v>38.22103386901189</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.1734988888291</v>
+        <v>29.18984895641055</v>
       </c>
       <c r="C6" t="n">
-        <v>29.01115364354546</v>
+        <v>40.14769590473188</v>
       </c>
       <c r="D6" t="n">
-        <v>41.31737703823377</v>
+        <v>28.21174408877989</v>
       </c>
       <c r="E6" t="n">
-        <v>28.82501546001468</v>
+        <v>39.96349663104212</v>
       </c>
       <c r="F6" t="n">
-        <v>29.36329378524621</v>
+        <v>40.50034884546758</v>
       </c>
       <c r="G6" t="n">
-        <v>42.19323501538088</v>
+        <v>28.98604010715269</v>
       </c>
       <c r="H6" t="n">
-        <v>41.96136721411096</v>
+        <v>28.85806526452197</v>
       </c>
       <c r="I6" t="n">
-        <v>42.45636404595325</v>
+        <v>29.28082755327266</v>
       </c>
       <c r="J6" t="n">
-        <v>41.97762609276339</v>
+        <v>40.96265812157091</v>
       </c>
       <c r="K6" t="n">
-        <v>30.13752780222216</v>
+        <v>29.04513360334395</v>
       </c>
       <c r="L6" t="n">
-        <v>41.83113435014897</v>
+        <v>40.82348282586103</v>
       </c>
       <c r="M6" t="n">
-        <v>41.80571559842778</v>
+        <v>28.69709590184966</v>
       </c>
       <c r="N6" t="n">
-        <v>40.77114717237048</v>
+        <v>40.02814120245156</v>
       </c>
       <c r="O6" t="n">
-        <v>41.55833288693233</v>
+        <v>40.58150530047708</v>
       </c>
       <c r="P6" t="n">
-        <v>41.72382723499217</v>
+        <v>27.91228956734955</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.02876752819939</v>
+        <v>28.92668573963</v>
       </c>
       <c r="R6" t="n">
-        <v>42.22951311432369</v>
+        <v>29.09781607024094</v>
       </c>
       <c r="S6" t="n">
-        <v>41.93627604289251</v>
+        <v>40.93849390251368</v>
       </c>
       <c r="T6" t="n">
-        <v>29.35543420672952</v>
+        <v>28.27525640000393</v>
       </c>
       <c r="U6" t="n">
-        <v>42.35412774853906</v>
+        <v>41.17219957782854</v>
       </c>
       <c r="V6" t="n">
-        <v>41.76839092495104</v>
+        <v>28.66239293467494</v>
       </c>
       <c r="W6" t="n">
-        <v>32.01896970341326</v>
+        <v>31.02990791931773</v>
       </c>
       <c r="X6" t="n">
-        <v>32.36993196482697</v>
+        <v>43.50400243282716</v>
       </c>
       <c r="Y6" t="n">
-        <v>32.82994199896462</v>
+        <v>31.8423516004476</v>
       </c>
       <c r="Z6" t="n">
-        <v>29.54137682879026</v>
+        <v>28.53015828575789</v>
       </c>
       <c r="AA6" t="n">
-        <v>30.46958389003706</v>
+        <v>41.58434526463644</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.41076195267397</v>
+        <v>28.42003596662344</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.78808433016163</v>
+        <v>15.81180075061221</v>
       </c>
       <c r="C7" t="n">
-        <v>15.62573908487796</v>
+        <v>14.64028535561698</v>
       </c>
       <c r="D7" t="n">
-        <v>15.8166732619346</v>
+        <v>14.83369588298145</v>
       </c>
       <c r="E7" t="n">
-        <v>15.4396009013472</v>
+        <v>14.45608608192728</v>
       </c>
       <c r="F7" t="n">
-        <v>15.97787922657874</v>
+        <v>14.99293829635265</v>
       </c>
       <c r="G7" t="n">
-        <v>16.69253123908183</v>
+        <v>15.60799190135424</v>
       </c>
       <c r="H7" t="n">
-        <v>16.4606634378118</v>
+        <v>15.48001705872355</v>
       </c>
       <c r="I7" t="n">
-        <v>16.95566026965408</v>
+        <v>15.90277934747422</v>
       </c>
       <c r="J7" t="n">
-        <v>16.47692231646419</v>
+        <v>15.45524757245599</v>
       </c>
       <c r="K7" t="n">
-        <v>16.75211324355474</v>
+        <v>15.66708539754556</v>
       </c>
       <c r="L7" t="n">
-        <v>16.33043057384977</v>
+        <v>15.31607227674615</v>
       </c>
       <c r="M7" t="n">
-        <v>16.30501182212858</v>
+        <v>15.31904769605126</v>
       </c>
       <c r="N7" t="n">
-        <v>40.77114717237048</v>
+        <v>40.02814120245156</v>
       </c>
       <c r="O7" t="n">
-        <v>16.37566711006179</v>
+        <v>15.39211971486075</v>
       </c>
       <c r="P7" t="n">
-        <v>16.54125430483344</v>
+        <v>15.55501860789467</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.52806375190023</v>
+        <v>15.54863753383158</v>
       </c>
       <c r="R7" t="n">
-        <v>16.72880933802449</v>
+        <v>15.7197678644425</v>
       </c>
       <c r="S7" t="n">
-        <v>16.43557226659335</v>
+        <v>15.43108335339876</v>
       </c>
       <c r="T7" t="n">
-        <v>15.97001964806202</v>
+        <v>14.89720819420547</v>
       </c>
       <c r="U7" t="n">
-        <v>16.8513680272207</v>
+        <v>15.66336512752602</v>
       </c>
       <c r="V7" t="n">
-        <v>16.2676871486518</v>
+        <v>15.28434472887654</v>
       </c>
       <c r="W7" t="n">
-        <v>17.71567949518568</v>
+        <v>16.7335140613307</v>
       </c>
       <c r="X7" t="n">
-        <v>18.98451740615945</v>
+        <v>17.99659188371228</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.65875260365346</v>
+        <v>17.67814786180969</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.15596227012277</v>
+        <v>15.15211007995951</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.08416933136958</v>
+        <v>16.07693471552156</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.02116945113956</v>
+        <v>15.03765152110174</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.61815641593129</v>
+        <v>27.64530043570153</v>
       </c>
       <c r="C8" t="n">
-        <v>37.79616441570202</v>
+        <v>36.8246894807062</v>
       </c>
       <c r="D8" t="n">
-        <v>37.98709859275861</v>
+        <v>37.01810000807069</v>
       </c>
       <c r="E8" t="n">
-        <v>32.10409315034363</v>
+        <v>31.12893892510811</v>
       </c>
       <c r="F8" t="n">
-        <v>29.41885749776663</v>
+        <v>28.43898791972392</v>
       </c>
       <c r="G8" t="n">
-        <v>41.00709617646689</v>
+        <v>39.93872349201634</v>
       </c>
       <c r="H8" t="n">
-        <v>38.63108876863579</v>
+        <v>37.66442118381275</v>
       </c>
       <c r="I8" t="n">
-        <v>39.12608560047808</v>
+        <v>38.08718347256346</v>
       </c>
       <c r="J8" t="n">
-        <v>38.64734764728821</v>
+        <v>37.63965169754523</v>
       </c>
       <c r="K8" t="n">
-        <v>38.92253857437876</v>
+        <v>37.85148952263474</v>
       </c>
       <c r="L8" t="n">
-        <v>38.50085590467374</v>
+        <v>37.50047640183536</v>
       </c>
       <c r="M8" t="n">
-        <v>38.47543715295249</v>
+        <v>37.50345182114064</v>
       </c>
       <c r="N8" t="n">
-        <v>40.77114717237048</v>
+        <v>40.02814120245156</v>
       </c>
       <c r="O8" t="n">
-        <v>32.73339961091703</v>
+        <v>31.75790038713172</v>
       </c>
       <c r="P8" t="n">
-        <v>32.35904445577016</v>
+        <v>31.38030597836362</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.3260204177419</v>
+        <v>25.34794824834845</v>
       </c>
       <c r="R8" t="n">
-        <v>38.89923466884853</v>
+        <v>37.90417198953169</v>
       </c>
       <c r="S8" t="n">
-        <v>38.60599759741736</v>
+        <v>37.61548747848796</v>
       </c>
       <c r="T8" t="n">
-        <v>38.14044497888604</v>
+        <v>37.08161231929468</v>
       </c>
       <c r="U8" t="n">
-        <v>33.97533023189278</v>
+        <v>32.79601452625397</v>
       </c>
       <c r="V8" t="n">
-        <v>35.61024974694475</v>
+        <v>34.63854315258745</v>
       </c>
       <c r="W8" t="n">
-        <v>39.88813700257481</v>
+        <v>38.91995243665688</v>
       </c>
       <c r="X8" t="n">
-        <v>29.73018799403687</v>
+        <v>28.74458355828461</v>
       </c>
       <c r="Y8" t="n">
-        <v>51.1077372839804</v>
+        <v>50.15244098020864</v>
       </c>
       <c r="Z8" t="n">
-        <v>27.79395698554524</v>
+        <v>26.79333640083156</v>
       </c>
       <c r="AA8" t="n">
-        <v>39.2545946621936</v>
+        <v>38.26133884061075</v>
       </c>
       <c r="AB8" t="n">
-        <v>48.99295839350556</v>
+        <v>48.0344408631896</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.21252517263299</v>
+        <v>23.47942391297359</v>
       </c>
       <c r="C9" t="n">
-        <v>25.05589973587912</v>
+        <v>25.66108125047079</v>
       </c>
       <c r="D9" t="n">
-        <v>25.24683391293573</v>
+        <v>25.85449177783524</v>
       </c>
       <c r="E9" t="n">
-        <v>24.17605442041413</v>
+        <v>24.70298411418589</v>
       </c>
       <c r="F9" t="n">
-        <v>18.47903412482736</v>
+        <v>18.28375464195658</v>
       </c>
       <c r="G9" t="n">
-        <v>26.12269285181463</v>
+        <v>26.62878874098057</v>
       </c>
       <c r="H9" t="n">
-        <v>25.89082408881293</v>
+        <v>26.50081295357735</v>
       </c>
       <c r="I9" t="n">
-        <v>26.38582092065518</v>
+        <v>26.92357524232803</v>
       </c>
       <c r="J9" t="n">
-        <v>25.90708296746535</v>
+        <v>26.4760434673098</v>
       </c>
       <c r="K9" t="n">
-        <v>26.18227389455587</v>
+        <v>26.68788129239935</v>
       </c>
       <c r="L9" t="n">
-        <v>25.76059122485091</v>
+        <v>26.33686817159997</v>
       </c>
       <c r="M9" t="n">
-        <v>25.73517247312974</v>
+        <v>26.33984359090505</v>
       </c>
       <c r="N9" t="n">
-        <v>40.77114717237048</v>
+        <v>40.02814120245156</v>
       </c>
       <c r="O9" t="n">
-        <v>26.80200148263988</v>
+        <v>27.52423542705581</v>
       </c>
       <c r="P9" t="n">
-        <v>27.18422158160364</v>
+        <v>27.92880938157748</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.95822536463308</v>
+        <v>26.56943437345793</v>
       </c>
       <c r="R9" t="n">
-        <v>26.15896998902564</v>
+        <v>26.7405637592963</v>
       </c>
       <c r="S9" t="n">
-        <v>25.86573291759451</v>
+        <v>26.45187924825256</v>
       </c>
       <c r="T9" t="n">
-        <v>25.40018029906317</v>
+        <v>25.91800408905927</v>
       </c>
       <c r="U9" t="n">
-        <v>26.28358462324106</v>
+        <v>26.68558492356743</v>
       </c>
       <c r="V9" t="n">
-        <v>29.1663846265564</v>
+        <v>30.17463073724196</v>
       </c>
       <c r="W9" t="n">
-        <v>27.14584014618684</v>
+        <v>27.75430995618451</v>
       </c>
       <c r="X9" t="n">
-        <v>28.41467805716056</v>
+        <v>29.01738777856609</v>
       </c>
       <c r="Y9" t="n">
-        <v>28.08891325465461</v>
+        <v>28.6989437566635</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.77394153750739</v>
+        <v>24.15124136803253</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.51432998237073</v>
+        <v>27.09773061037536</v>
       </c>
       <c r="AB9" t="n">
-        <v>25.45133010214067</v>
+        <v>26.05844741595555</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.39446511724639</v>
+        <v>21.39297878595206</v>
       </c>
       <c r="C2" t="n">
-        <v>16.09308793579301</v>
+        <v>15.61080934411243</v>
       </c>
       <c r="D2" t="n">
-        <v>21.88839539820625</v>
+        <v>21.42636615328227</v>
       </c>
       <c r="E2" t="n">
-        <v>21.77745485788709</v>
+        <v>21.20462375306081</v>
       </c>
       <c r="F2" t="n">
-        <v>21.87593666865846</v>
+        <v>21.36193938223521</v>
       </c>
       <c r="G2" t="n">
-        <v>23.12598691323161</v>
+        <v>22.24874908605559</v>
       </c>
       <c r="H2" t="n">
-        <v>21.68246563292092</v>
+        <v>21.18606598425893</v>
       </c>
       <c r="I2" t="n">
-        <v>21.78864063717815</v>
+        <v>21.26269672873059</v>
       </c>
       <c r="J2" t="n">
-        <v>22.47832265689217</v>
+        <v>21.79542959961925</v>
       </c>
       <c r="K2" t="n">
-        <v>21.89154616760286</v>
+        <v>21.3571418516112</v>
       </c>
       <c r="L2" t="n">
-        <v>22.01442195297522</v>
+        <v>21.28708519290849</v>
       </c>
       <c r="M2" t="n">
-        <v>23.17502193099648</v>
+        <v>22.52873691233603</v>
       </c>
       <c r="N2" t="n">
-        <v>21.82089059981837</v>
+        <v>21.31212810209554</v>
       </c>
       <c r="O2" t="n">
-        <v>29.4653024840987</v>
+        <v>28.70519110472672</v>
       </c>
       <c r="P2" t="n">
-        <v>22.16528679081736</v>
+        <v>21.69990422600758</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.83275390741482</v>
+        <v>21.27964244680674</v>
       </c>
       <c r="R2" t="n">
-        <v>21.74118239734821</v>
+        <v>21.20633668237934</v>
       </c>
       <c r="S2" t="n">
-        <v>22.19101654244786</v>
+        <v>21.51372978247361</v>
       </c>
       <c r="T2" t="n">
-        <v>21.84998198809051</v>
+        <v>21.26377712935965</v>
       </c>
       <c r="U2" t="n">
-        <v>25.75588674705895</v>
+        <v>24.98984996198465</v>
       </c>
       <c r="V2" t="n">
-        <v>21.82246973775669</v>
+        <v>21.30150396745816</v>
       </c>
       <c r="W2" t="n">
-        <v>27.68478654071352</v>
+        <v>27.03892919321734</v>
       </c>
       <c r="X2" t="n">
-        <v>22.00026880027274</v>
+        <v>21.41207112347618</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.96349682758798</v>
+        <v>21.51318299639348</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.58525878450701</v>
+        <v>27.75177809148661</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.95465714284027</v>
+        <v>21.38098762997768</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.94955509472935</v>
+        <v>22.72817957619731</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.91993649739</v>
+        <v>21.90082333597245</v>
       </c>
       <c r="C3" t="n">
-        <v>11.42018916857961</v>
+        <v>11.15406247304747</v>
       </c>
       <c r="D3" t="n">
-        <v>22.33796695715382</v>
+        <v>22.15358636785578</v>
       </c>
       <c r="E3" t="n">
-        <v>21.52451781644578</v>
+        <v>20.54904615913479</v>
       </c>
       <c r="F3" t="n">
-        <v>22.25047521417834</v>
+        <v>21.69403982441565</v>
       </c>
       <c r="G3" t="n">
-        <v>31.13183961100776</v>
+        <v>27.99194901657789</v>
       </c>
       <c r="H3" t="n">
-        <v>20.86640490718017</v>
+        <v>20.43581103441748</v>
       </c>
       <c r="I3" t="n">
-        <v>21.6249135560047</v>
+        <v>20.98279567373222</v>
       </c>
       <c r="J3" t="n">
-        <v>26.53303921478389</v>
+        <v>24.77518308696312</v>
       </c>
       <c r="K3" t="n">
-        <v>22.35578815890602</v>
+        <v>21.65471786326329</v>
       </c>
       <c r="L3" t="n">
-        <v>23.22999901780201</v>
+        <v>21.15190531835617</v>
       </c>
       <c r="M3" t="n">
-        <v>32.35165376049455</v>
+        <v>30.83797377213795</v>
       </c>
       <c r="N3" t="n">
-        <v>21.85189300847085</v>
+        <v>21.3332359940166</v>
       </c>
       <c r="O3" t="n">
-        <v>35.36962769954649</v>
+        <v>34.34070430910479</v>
       </c>
       <c r="P3" t="n">
-        <v>24.29417637223016</v>
+        <v>24.08483577796165</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.93732147123759</v>
+        <v>21.10165574168797</v>
       </c>
       <c r="R3" t="n">
-        <v>21.28588623577918</v>
+        <v>20.57973000117148</v>
       </c>
       <c r="S3" t="n">
-        <v>24.47997172220412</v>
+        <v>22.76264349499526</v>
       </c>
       <c r="T3" t="n">
-        <v>22.06322536170023</v>
+        <v>20.98997639282362</v>
       </c>
       <c r="U3" t="n">
-        <v>30.62968104127162</v>
+        <v>29.05515223363288</v>
       </c>
       <c r="V3" t="n">
-        <v>21.85628975551521</v>
+        <v>21.25199330264295</v>
       </c>
       <c r="W3" t="n">
-        <v>32.43209634926644</v>
+        <v>31.76494017137207</v>
       </c>
       <c r="X3" t="n">
-        <v>23.13623307781236</v>
+        <v>22.04943541394958</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.86789358847402</v>
+        <v>22.76647314872271</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.80710487426599</v>
+        <v>32.69443844201624</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.80518409843285</v>
+        <v>21.82337380192557</v>
       </c>
       <c r="AB3" t="n">
-        <v>29.92972792471181</v>
+        <v>31.42661203872743</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.64449632835854</v>
+        <v>14.06243202165174</v>
       </c>
       <c r="C4" t="n">
-        <v>14.14973849853232</v>
+        <v>11.56705249230071</v>
       </c>
       <c r="D4" t="n">
-        <v>16.9282060482277</v>
+        <v>14.43955769459424</v>
       </c>
       <c r="E4" t="n">
-        <v>15.67508161015317</v>
+        <v>11.93487527754887</v>
       </c>
       <c r="F4" t="n">
-        <v>16.78747896668655</v>
+        <v>13.71182767783873</v>
       </c>
       <c r="G4" t="n">
-        <v>30.90737153066349</v>
+        <v>23.72875123510869</v>
       </c>
       <c r="H4" t="n">
-        <v>14.60213461695758</v>
+        <v>11.72525674193626</v>
       </c>
       <c r="I4" t="n">
-        <v>15.80143013295788</v>
+        <v>12.59083625262781</v>
       </c>
       <c r="J4" t="n">
-        <v>23.5578634091551</v>
+        <v>18.5761405504051</v>
       </c>
       <c r="K4" t="n">
-        <v>16.96379543798858</v>
+        <v>13.65763736246726</v>
       </c>
       <c r="L4" t="n">
-        <v>18.35173395942274</v>
+        <v>12.86631517476489</v>
       </c>
       <c r="M4" t="n">
-        <v>32.9234102812203</v>
+        <v>28.33548558678973</v>
       </c>
       <c r="N4" t="n">
-        <v>16.16570829669514</v>
+        <v>63.85448785955532</v>
       </c>
       <c r="O4" t="n">
-        <v>18.0485364428669</v>
+        <v>14.83205631368906</v>
       </c>
       <c r="P4" t="n">
-        <v>20.05582170410384</v>
+        <v>17.5292960597568</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.29970981338814</v>
+        <v>12.78224593371329</v>
       </c>
       <c r="R4" t="n">
-        <v>15.26536748220986</v>
+        <v>11.95422360218807</v>
       </c>
       <c r="S4" t="n">
-        <v>20.3464510850408</v>
+        <v>15.42637007556536</v>
       </c>
       <c r="T4" t="n">
-        <v>16.49430890992873</v>
+        <v>12.60303987474184</v>
       </c>
       <c r="U4" t="n">
-        <v>20.51285734616016</v>
+        <v>16.26396828507982</v>
       </c>
       <c r="V4" t="n">
-        <v>15.9660530289252</v>
+        <v>12.82309446192706</v>
       </c>
       <c r="W4" t="n">
-        <v>18.02351865322559</v>
+        <v>15.16678512448522</v>
       </c>
       <c r="X4" t="n">
-        <v>18.19186758887614</v>
+        <v>14.27808875689568</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.54706702167972</v>
+        <v>15.2611354376346</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.8774273197238</v>
+        <v>14.67302246010592</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.6766629357772</v>
+        <v>13.92698639871672</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.85743100855262</v>
+        <v>29.00225208419326</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>179.6202175490478</v>
+        <v>75.86751252353439</v>
       </c>
       <c r="C5" t="n">
-        <v>33.48141907231208</v>
+        <v>34.32002911253267</v>
       </c>
       <c r="D5" t="n">
-        <v>88.15234721742446</v>
+        <v>91.04887680303129</v>
       </c>
       <c r="E5" t="n">
-        <v>52.41159062588102</v>
+        <v>31.48101226945077</v>
       </c>
       <c r="F5" t="n">
-        <v>86.28502821564338</v>
+        <v>77.43948485646797</v>
       </c>
       <c r="G5" t="n">
-        <v>330.8460487481331</v>
+        <v>249.4332485754639</v>
       </c>
       <c r="H5" t="n">
-        <v>43.15286862193832</v>
+        <v>38.20269374522474</v>
       </c>
       <c r="I5" t="n">
-        <v>66.23633204299203</v>
+        <v>54.6063595873996</v>
       </c>
       <c r="J5" t="n">
-        <v>205.6199913717037</v>
+        <v>162.9273027860839</v>
       </c>
       <c r="K5" t="n">
-        <v>86.23026353798241</v>
+        <v>73.5886351104306</v>
       </c>
       <c r="L5" t="n">
-        <v>110.9384331072377</v>
+        <v>57.0610005291497</v>
       </c>
       <c r="M5" t="n">
-        <v>410.9128261673363</v>
+        <v>371.6333814216433</v>
       </c>
       <c r="N5" t="n">
-        <v>148.9140949209065</v>
+        <v>63.85448785955532</v>
       </c>
       <c r="O5" t="n">
-        <v>98.45041720006189</v>
+        <v>88.14947513042242</v>
       </c>
       <c r="P5" t="n">
-        <v>136.1780524398766</v>
+        <v>137.7871256982372</v>
       </c>
       <c r="Q5" t="n">
-        <v>74.30592095074829</v>
+        <v>57.06740261259991</v>
       </c>
       <c r="R5" t="n">
-        <v>55.9250464477706</v>
+        <v>42.1126294302547</v>
       </c>
       <c r="S5" t="n">
-        <v>142.8749954409563</v>
+        <v>101.6646632831861</v>
       </c>
       <c r="T5" t="n">
-        <v>79.62392887615768</v>
+        <v>54.54225813566679</v>
       </c>
       <c r="U5" t="n">
-        <v>153.4906881901505</v>
+        <v>122.2364071118484</v>
       </c>
       <c r="V5" t="n">
-        <v>67.64684578794176</v>
+        <v>58.36629390326753</v>
       </c>
       <c r="W5" t="n">
-        <v>105.5898129644405</v>
+        <v>101.2210686187663</v>
       </c>
       <c r="X5" t="n">
-        <v>111.945472151845</v>
+        <v>86.81311663655421</v>
       </c>
       <c r="Y5" t="n">
-        <v>100.8128318630909</v>
+        <v>105.8481053438998</v>
       </c>
       <c r="Z5" t="n">
-        <v>134.0497299231778</v>
+        <v>87.79080517341438</v>
       </c>
       <c r="AA5" t="n">
-        <v>99.1361255138853</v>
+        <v>77.82911854454474</v>
       </c>
       <c r="AB5" t="n">
-        <v>341.0795953457664</v>
+        <v>399.2166060250481</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.29102193827808</v>
+        <v>32.7238540208416</v>
       </c>
       <c r="C6" t="n">
-        <v>46.95490470735396</v>
+        <v>44.07337616583381</v>
       </c>
       <c r="D6" t="n">
-        <v>49.73337225704934</v>
+        <v>33.10097969378415</v>
       </c>
       <c r="E6" t="n">
-        <v>34.32160722007279</v>
+        <v>44.4411989510819</v>
       </c>
       <c r="F6" t="n">
-        <v>35.43400457660616</v>
+        <v>32.37324967702865</v>
       </c>
       <c r="G6" t="n">
-        <v>49.55389714058309</v>
+        <v>56.23507490864173</v>
       </c>
       <c r="H6" t="n">
-        <v>47.40730082577915</v>
+        <v>44.23158041546935</v>
       </c>
       <c r="I6" t="n">
-        <v>34.44795574287754</v>
+        <v>45.09715992616086</v>
       </c>
       <c r="J6" t="n">
-        <v>56.36302961797673</v>
+        <v>51.08246422393815</v>
       </c>
       <c r="K6" t="n">
-        <v>49.76896164681021</v>
+        <v>32.31905936165721</v>
       </c>
       <c r="L6" t="n">
-        <v>36.99825956934238</v>
+        <v>45.37263884829796</v>
       </c>
       <c r="M6" t="n">
-        <v>51.56993589113989</v>
+        <v>60.84180926032272</v>
       </c>
       <c r="N6" t="n">
-        <v>34.82452376048676</v>
+        <v>63.85448785955532</v>
       </c>
       <c r="O6" t="n">
-        <v>50.52904353405521</v>
+        <v>33.50512565122019</v>
       </c>
       <c r="P6" t="n">
-        <v>52.53632568553816</v>
+        <v>49.69268411121386</v>
       </c>
       <c r="Q6" t="n">
-        <v>49.10487602220975</v>
+        <v>31.44366793290325</v>
       </c>
       <c r="R6" t="n">
-        <v>48.07053369103154</v>
+        <v>44.4605472757211</v>
       </c>
       <c r="S6" t="n">
-        <v>53.1516172938624</v>
+        <v>34.08779207475529</v>
       </c>
       <c r="T6" t="n">
-        <v>35.14083451984837</v>
+        <v>31.26446187393169</v>
       </c>
       <c r="U6" t="n">
-        <v>39.38882717585868</v>
+        <v>35.0844487218913</v>
       </c>
       <c r="V6" t="n">
-        <v>48.77121923774686</v>
+        <v>31.484516461117</v>
       </c>
       <c r="W6" t="n">
-        <v>50.50395382257634</v>
+        <v>34.83273220114899</v>
       </c>
       <c r="X6" t="n">
-        <v>50.99703379769773</v>
+        <v>46.78441243042877</v>
       </c>
       <c r="Y6" t="n">
-        <v>37.26050063654436</v>
+        <v>34.92139949828697</v>
       </c>
       <c r="Z6" t="n">
-        <v>52.68259352854544</v>
+        <v>33.33444445929587</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.32318854569684</v>
+        <v>46.43331007224975</v>
       </c>
       <c r="AB6" t="n">
-        <v>47.5832519978597</v>
+        <v>47.76599179391334</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.65072851681856</v>
+        <v>18.81311916740626</v>
       </c>
       <c r="C7" t="n">
-        <v>19.15597068699233</v>
+        <v>16.31773963805526</v>
       </c>
       <c r="D7" t="n">
-        <v>21.9344382366877</v>
+        <v>19.19024484034878</v>
       </c>
       <c r="E7" t="n">
-        <v>20.68131379861318</v>
+        <v>16.68556242330342</v>
       </c>
       <c r="F7" t="n">
-        <v>21.79371115514655</v>
+        <v>18.46251482359329</v>
       </c>
       <c r="G7" t="n">
-        <v>35.91360371912353</v>
+        <v>28.47943838086323</v>
       </c>
       <c r="H7" t="n">
-        <v>19.60836680541762</v>
+        <v>16.4759438876908</v>
       </c>
       <c r="I7" t="n">
-        <v>20.80766232141792</v>
+        <v>17.34152339838236</v>
       </c>
       <c r="J7" t="n">
-        <v>28.56409559761511</v>
+        <v>23.32682769615965</v>
       </c>
       <c r="K7" t="n">
-        <v>21.9700276264486</v>
+        <v>18.4083245082218</v>
       </c>
       <c r="L7" t="n">
-        <v>23.35796614788276</v>
+        <v>17.61700232051955</v>
       </c>
       <c r="M7" t="n">
-        <v>37.92964246968033</v>
+        <v>33.08617273254426</v>
       </c>
       <c r="N7" t="n">
-        <v>21.17194048515517</v>
+        <v>63.85448785955532</v>
       </c>
       <c r="O7" t="n">
-        <v>23.05467538210288</v>
+        <v>19.58265024435001</v>
       </c>
       <c r="P7" t="n">
-        <v>25.06196064333986</v>
+        <v>22.27988999041773</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.30594200184815</v>
+        <v>17.53293307946783</v>
       </c>
       <c r="R7" t="n">
-        <v>20.27159967066991</v>
+        <v>16.70491074794263</v>
       </c>
       <c r="S7" t="n">
-        <v>25.35268327350082</v>
+        <v>20.17705722131993</v>
       </c>
       <c r="T7" t="n">
-        <v>21.50054109838874</v>
+        <v>17.35372702049641</v>
       </c>
       <c r="U7" t="n">
-        <v>25.7435874635312</v>
+        <v>21.17008298456216</v>
       </c>
       <c r="V7" t="n">
-        <v>20.97228521738522</v>
+        <v>17.57378160768159</v>
       </c>
       <c r="W7" t="n">
-        <v>23.0297508416856</v>
+        <v>19.91747227023975</v>
       </c>
       <c r="X7" t="n">
-        <v>23.19809977733616</v>
+        <v>19.02877590265024</v>
       </c>
       <c r="Y7" t="n">
-        <v>22.78274342991867</v>
+        <v>20.17088102101071</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.8836595081838</v>
+        <v>19.42370960586048</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.68289512423719</v>
+        <v>18.67767354447125</v>
       </c>
       <c r="AB7" t="n">
-        <v>33.86366319701264</v>
+        <v>33.7529392299478</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40.99041147122054</v>
+        <v>31.99802704953751</v>
       </c>
       <c r="C8" t="n">
-        <v>44.71971193882129</v>
+        <v>41.37609734831383</v>
       </c>
       <c r="D8" t="n">
-        <v>47.49817948851664</v>
+        <v>44.24860255060739</v>
       </c>
       <c r="E8" t="n">
-        <v>39.73610459409497</v>
+        <v>35.42165834479484</v>
       </c>
       <c r="F8" t="n">
-        <v>37.03775952678001</v>
+        <v>33.49716742109601</v>
       </c>
       <c r="G8" t="n">
-        <v>64.01208309130436</v>
+        <v>55.99983326137459</v>
       </c>
       <c r="H8" t="n">
-        <v>45.17210805724652</v>
+        <v>41.53430159794938</v>
       </c>
       <c r="I8" t="n">
-        <v>46.37140357324682</v>
+        <v>42.39988110864097</v>
       </c>
       <c r="J8" t="n">
-        <v>54.12783684944401</v>
+        <v>48.38518540641823</v>
       </c>
       <c r="K8" t="n">
-        <v>47.53376887827753</v>
+        <v>43.4666822184804</v>
       </c>
       <c r="L8" t="n">
-        <v>48.92170739971168</v>
+        <v>42.67536003077808</v>
       </c>
       <c r="M8" t="n">
-        <v>63.49338372150905</v>
+        <v>58.1445304428037</v>
       </c>
       <c r="N8" t="n">
-        <v>37.25999151624517</v>
+        <v>63.85448785955532</v>
       </c>
       <c r="O8" t="n">
-        <v>41.74682161147022</v>
+        <v>37.96650555323327</v>
       </c>
       <c r="P8" t="n">
-        <v>43.11580307344649</v>
+        <v>40.04374922668478</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.24331850012496</v>
+        <v>28.38443707191305</v>
       </c>
       <c r="R8" t="n">
-        <v>45.83534092249882</v>
+        <v>41.76326845820122</v>
       </c>
       <c r="S8" t="n">
-        <v>50.9164245253297</v>
+        <v>45.23541493157849</v>
       </c>
       <c r="T8" t="n">
-        <v>47.06428235021761</v>
+        <v>42.41208473075498</v>
       </c>
       <c r="U8" t="n">
-        <v>45.34211431618625</v>
+        <v>40.43405758473557</v>
       </c>
       <c r="V8" t="n">
-        <v>43.19085876057834</v>
+        <v>39.3839225386934</v>
       </c>
       <c r="W8" t="n">
-        <v>48.5958944718888</v>
+        <v>44.97816345435081</v>
       </c>
       <c r="X8" t="n">
-        <v>35.25583550854762</v>
+        <v>30.96850516520416</v>
       </c>
       <c r="Y8" t="n">
-        <v>60.49415365303155</v>
+        <v>57.03004954736249</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.99627430381861</v>
+        <v>32.38806206153522</v>
       </c>
       <c r="AA8" t="n">
-        <v>48.24663637606608</v>
+        <v>43.73603125472987</v>
       </c>
       <c r="AB8" t="n">
-        <v>72.19645550023812</v>
+        <v>71.21410812810443</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40.87817701585088</v>
+        <v>30.89847684809519</v>
       </c>
       <c r="C9" t="n">
-        <v>37.67294492833415</v>
+        <v>33.26697337396175</v>
       </c>
       <c r="D9" t="n">
-        <v>40.45141247802957</v>
+        <v>36.13947857625526</v>
       </c>
       <c r="E9" t="n">
-        <v>37.97748715700209</v>
+        <v>32.51223265843094</v>
       </c>
       <c r="F9" t="n">
-        <v>28.11688477143053</v>
+        <v>24.19918804145333</v>
       </c>
       <c r="G9" t="n">
-        <v>54.43057806809725</v>
+        <v>45.42867114612677</v>
       </c>
       <c r="H9" t="n">
-        <v>38.12534104675945</v>
+        <v>33.42517762359729</v>
       </c>
       <c r="I9" t="n">
-        <v>39.32463656275975</v>
+        <v>34.29075713428884</v>
       </c>
       <c r="J9" t="n">
-        <v>47.08106983895694</v>
+        <v>40.27606143206614</v>
       </c>
       <c r="K9" t="n">
-        <v>40.48700186779045</v>
+        <v>35.35755824412828</v>
       </c>
       <c r="L9" t="n">
-        <v>41.87494038922461</v>
+        <v>34.56623605642599</v>
       </c>
       <c r="M9" t="n">
-        <v>56.44661671102213</v>
+        <v>50.03540646845077</v>
       </c>
       <c r="N9" t="n">
-        <v>39.68891472649702</v>
+        <v>63.85448785955532</v>
       </c>
       <c r="O9" t="n">
-        <v>43.32468492093378</v>
+        <v>38.1438580590398</v>
       </c>
       <c r="P9" t="n">
-        <v>45.71320497883491</v>
+        <v>41.19165444883517</v>
       </c>
       <c r="Q9" t="n">
-        <v>39.82291635082185</v>
+        <v>34.48216584473138</v>
       </c>
       <c r="R9" t="n">
-        <v>38.7885739120117</v>
+        <v>33.65414448384909</v>
       </c>
       <c r="S9" t="n">
-        <v>43.86965751484264</v>
+        <v>37.12629095722637</v>
       </c>
       <c r="T9" t="n">
-        <v>40.01751533973056</v>
+        <v>34.30296075640288</v>
       </c>
       <c r="U9" t="n">
-        <v>44.26550799574097</v>
+        <v>38.12294760436242</v>
       </c>
       <c r="V9" t="n">
-        <v>45.59325352574176</v>
+        <v>40.13581796537215</v>
       </c>
       <c r="W9" t="n">
-        <v>41.54672508302742</v>
+        <v>36.8667060061462</v>
       </c>
       <c r="X9" t="n">
-        <v>41.71507401867802</v>
+        <v>35.97800963855673</v>
       </c>
       <c r="Y9" t="n">
-        <v>41.29971767126054</v>
+        <v>37.1201147569172</v>
       </c>
       <c r="Z9" t="n">
-        <v>40.21152013263379</v>
+        <v>33.4404582077736</v>
       </c>
       <c r="AA9" t="n">
-        <v>41.19986936557905</v>
+        <v>35.62690728037774</v>
       </c>
       <c r="AB9" t="n">
-        <v>52.38063743835452</v>
+        <v>50.70217296585429</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.22731956354762</v>
+        <v>21.3360950709973</v>
       </c>
       <c r="C2" t="n">
-        <v>16.02634909711896</v>
+        <v>15.55223279818342</v>
       </c>
       <c r="D2" t="n">
-        <v>21.87379396157974</v>
+        <v>21.42175058188124</v>
       </c>
       <c r="E2" t="n">
-        <v>21.68255061804164</v>
+        <v>21.14101675082064</v>
       </c>
       <c r="F2" t="n">
-        <v>21.90861466389747</v>
+        <v>21.39682412409619</v>
       </c>
       <c r="G2" t="n">
-        <v>22.98094866793745</v>
+        <v>22.12621821145224</v>
       </c>
       <c r="H2" t="n">
-        <v>21.60959230106946</v>
+        <v>21.13345837525369</v>
       </c>
       <c r="I2" t="n">
-        <v>21.89050491770537</v>
+        <v>21.31021303450622</v>
       </c>
       <c r="J2" t="n">
-        <v>22.37694245800728</v>
+        <v>21.70744169158717</v>
       </c>
       <c r="K2" t="n">
-        <v>21.95207422295143</v>
+        <v>21.33340980969796</v>
       </c>
       <c r="L2" t="n">
-        <v>21.90051200673835</v>
+        <v>21.21454925439262</v>
       </c>
       <c r="M2" t="n">
-        <v>22.91331009691455</v>
+        <v>22.28641842928135</v>
       </c>
       <c r="N2" t="n">
-        <v>21.72689741053535</v>
+        <v>21.21884014275861</v>
       </c>
       <c r="O2" t="n">
-        <v>29.27709524608085</v>
+        <v>28.5603809835827</v>
       </c>
       <c r="P2" t="n">
-        <v>22.0958544760794</v>
+        <v>21.6366766520728</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.78782012967632</v>
+        <v>21.24788701599093</v>
       </c>
       <c r="R2" t="n">
-        <v>21.65112937484129</v>
+        <v>21.13964843235922</v>
       </c>
       <c r="S2" t="n">
-        <v>22.08611280507033</v>
+        <v>21.43239223172093</v>
       </c>
       <c r="T2" t="n">
-        <v>21.78181820959704</v>
+        <v>21.21038909680097</v>
       </c>
       <c r="U2" t="n">
-        <v>25.49757417356391</v>
+        <v>24.6449424605214</v>
       </c>
       <c r="V2" t="n">
-        <v>21.8282906895301</v>
+        <v>21.29778444850789</v>
       </c>
       <c r="W2" t="n">
-        <v>27.54626420566812</v>
+        <v>26.890481728739</v>
       </c>
       <c r="X2" t="n">
-        <v>21.99865268453366</v>
+        <v>21.41797695775215</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.13993369053797</v>
+        <v>21.72067012070698</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.50648724665728</v>
+        <v>27.68810117945237</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.87744329968901</v>
+        <v>21.26733066110872</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.80876396035079</v>
+        <v>22.56380468586739</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.16439979209642</v>
+        <v>21.8447580548202</v>
       </c>
       <c r="C3" t="n">
-        <v>11.41292410527209</v>
+        <v>11.09560653823011</v>
       </c>
       <c r="D3" t="n">
-        <v>22.66485966749205</v>
+        <v>22.46980118154184</v>
       </c>
       <c r="E3" t="n">
-        <v>21.27801181370205</v>
+        <v>20.44397394798668</v>
       </c>
       <c r="F3" t="n">
-        <v>22.91480519930439</v>
+        <v>22.29232706736931</v>
       </c>
       <c r="G3" t="n">
-        <v>30.52135060548566</v>
+        <v>27.46236938210271</v>
       </c>
       <c r="H3" t="n">
-        <v>20.7765499050671</v>
+        <v>20.40910130031831</v>
       </c>
       <c r="I3" t="n">
-        <v>22.78676798094313</v>
+        <v>21.67338814101014</v>
       </c>
       <c r="J3" t="n">
-        <v>26.23832606727692</v>
+        <v>24.49520937466491</v>
       </c>
       <c r="K3" t="n">
-        <v>23.21243538349032</v>
+        <v>21.83167303274645</v>
       </c>
       <c r="L3" t="n">
-        <v>22.84741257123522</v>
+        <v>20.98319426346161</v>
       </c>
       <c r="M3" t="n">
-        <v>30.924041750161</v>
+        <v>29.46667963863117</v>
       </c>
       <c r="N3" t="n">
-        <v>21.6116270988832</v>
+        <v>21.0160766440052</v>
       </c>
       <c r="O3" t="n">
-        <v>34.94724692118086</v>
+        <v>33.9778944988623</v>
       </c>
       <c r="P3" t="n">
-        <v>24.22753054796636</v>
+        <v>23.98073496660665</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.04619513363546</v>
+        <v>21.22334512879061</v>
       </c>
       <c r="R3" t="n">
-        <v>21.07315611378358</v>
+        <v>20.45231722605226</v>
       </c>
       <c r="S3" t="n">
-        <v>24.16132329725099</v>
+        <v>22.53074146626113</v>
       </c>
       <c r="T3" t="n">
-        <v>22.00752408648701</v>
+        <v>20.95789421160695</v>
       </c>
       <c r="U3" t="n">
-        <v>29.58203139532204</v>
+        <v>27.21585425092029</v>
       </c>
       <c r="V3" t="n">
-        <v>22.32490956737723</v>
+        <v>21.57187302043591</v>
       </c>
       <c r="W3" t="n">
-        <v>32.2553718630624</v>
+        <v>31.3247375778726</v>
       </c>
       <c r="X3" t="n">
-        <v>23.55561268006642</v>
+        <v>22.44084540194358</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.55772974026853</v>
+        <v>24.59614278008321</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.75862720966525</v>
+        <v>32.63632761214298</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6850277628864</v>
+        <v>21.36111727583307</v>
       </c>
       <c r="AB3" t="n">
-        <v>29.36065951176951</v>
+        <v>30.60966652241988</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.32929635066695</v>
+        <v>13.96864294414201</v>
       </c>
       <c r="C4" t="n">
-        <v>14.04493786712146</v>
+        <v>11.47367002566163</v>
       </c>
       <c r="D4" t="n">
-        <v>17.33606204662806</v>
+        <v>14.93616134305689</v>
       </c>
       <c r="E4" t="n">
-        <v>15.17588050508071</v>
+        <v>11.76514357728577</v>
       </c>
       <c r="F4" t="n">
-        <v>17.72937789762127</v>
+        <v>14.65460553563854</v>
       </c>
       <c r="G4" t="n">
-        <v>29.84188377126638</v>
+        <v>22.8934472901829</v>
       </c>
       <c r="H4" t="n">
-        <v>14.35178275239582</v>
+        <v>11.67976824823218</v>
       </c>
       <c r="I4" t="n">
-        <v>17.52481998348672</v>
+        <v>13.67629343565026</v>
       </c>
       <c r="J4" t="n">
-        <v>22.9862217584018</v>
+        <v>18.13155349727787</v>
       </c>
       <c r="K4" t="n">
-        <v>18.22027360952058</v>
+        <v>13.93831168248426</v>
       </c>
       <c r="L4" t="n">
-        <v>17.63785465760234</v>
+        <v>12.59572703175403</v>
       </c>
       <c r="M4" t="n">
-        <v>30.56434675942559</v>
+        <v>26.17077179612263</v>
       </c>
       <c r="N4" t="n">
-        <v>15.67679792682967</v>
+        <v>52.33776005304261</v>
       </c>
       <c r="O4" t="n">
-        <v>17.50344033569898</v>
+        <v>14.40624999660991</v>
       </c>
       <c r="P4" t="n">
-        <v>19.84433771078518</v>
+        <v>17.36385017674809</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.36494806536227</v>
+        <v>12.97229238513493</v>
       </c>
       <c r="R4" t="n">
-        <v>14.82096310864664</v>
+        <v>11.74968779080617</v>
       </c>
       <c r="S4" t="n">
-        <v>19.73430105534774</v>
+        <v>15.05636367339801</v>
       </c>
       <c r="T4" t="n">
-        <v>16.29715361704718</v>
+        <v>12.54873613798877</v>
       </c>
       <c r="U4" t="n">
-        <v>18.95231332519639</v>
+        <v>13.49596531714742</v>
       </c>
       <c r="V4" t="n">
-        <v>16.60938792360473</v>
+        <v>13.3334669197036</v>
       </c>
       <c r="W4" t="n">
-        <v>17.81633942994447</v>
+        <v>14.59541629448628</v>
       </c>
       <c r="X4" t="n">
-        <v>18.74639876024268</v>
+        <v>14.89353652256732</v>
       </c>
       <c r="Y4" t="n">
-        <v>20.14459745967999</v>
+        <v>18.17390922031513</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.75202267502952</v>
+        <v>14.61044024826204</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.37728299935056</v>
+        <v>13.1919173012591</v>
       </c>
       <c r="AB4" t="n">
-        <v>27.85118127584715</v>
+        <v>27.71163124104373</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>152.0412169342697</v>
+        <v>71.52743831288481</v>
       </c>
       <c r="C5" t="n">
-        <v>33.9214857145947</v>
+        <v>32.73255227166933</v>
       </c>
       <c r="D5" t="n">
-        <v>93.6390542605038</v>
+        <v>95.74729557622459</v>
       </c>
       <c r="E5" t="n">
-        <v>44.06563996191903</v>
+        <v>28.14979335285626</v>
       </c>
       <c r="F5" t="n">
-        <v>101.3357487756486</v>
+        <v>90.98893198737133</v>
       </c>
       <c r="G5" t="n">
-        <v>291.3353729685878</v>
+        <v>218.21636925584</v>
       </c>
       <c r="H5" t="n">
-        <v>39.46346793232073</v>
+        <v>36.52329597917397</v>
       </c>
       <c r="I5" t="n">
-        <v>98.34638152172636</v>
+        <v>73.27581654550892</v>
       </c>
       <c r="J5" t="n">
-        <v>185.0401273739148</v>
+        <v>145.7514119764388</v>
       </c>
       <c r="K5" t="n">
-        <v>103.5180323211417</v>
+        <v>74.14169353460855</v>
       </c>
       <c r="L5" t="n">
-        <v>94.76093645456658</v>
+        <v>50.31033004962366</v>
       </c>
       <c r="M5" t="n">
-        <v>344.4317690176389</v>
+        <v>309.0750229888308</v>
       </c>
       <c r="N5" t="n">
-        <v>115.5569834851782</v>
+        <v>52.33776005304261</v>
       </c>
       <c r="O5" t="n">
-        <v>86.53814964762869</v>
+        <v>76.97564100837621</v>
       </c>
       <c r="P5" t="n">
-        <v>126.5046733407932</v>
+        <v>126.7635865956607</v>
       </c>
       <c r="Q5" t="n">
-        <v>73.83848806932508</v>
+        <v>58.11972415555019</v>
       </c>
       <c r="R5" t="n">
-        <v>47.84152536773579</v>
+        <v>37.2609811666741</v>
       </c>
       <c r="S5" t="n">
-        <v>126.2787615374059</v>
+        <v>90.09487483002141</v>
       </c>
       <c r="T5" t="n">
-        <v>74.79781418908865</v>
+        <v>51.7548468974518</v>
       </c>
       <c r="U5" t="n">
-        <v>119.0301341394002</v>
+        <v>67.75570303477566</v>
       </c>
       <c r="V5" t="n">
-        <v>76.46342899736064</v>
+        <v>63.95107790098589</v>
       </c>
       <c r="W5" t="n">
-        <v>98.91226341268771</v>
+        <v>86.24815289759127</v>
       </c>
       <c r="X5" t="n">
-        <v>118.3914858518269</v>
+        <v>93.94491443004907</v>
       </c>
       <c r="Y5" t="n">
-        <v>143.3969600661715</v>
+        <v>151.8053676215576</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.7690152321436</v>
+        <v>80.12715154918479</v>
       </c>
       <c r="AA5" t="n">
-        <v>91.32229456843775</v>
+        <v>61.48690410415687</v>
       </c>
       <c r="AB5" t="n">
-        <v>304.3639992343212</v>
+        <v>351.0560267289542</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.75206016963478</v>
+        <v>44.23303261436206</v>
       </c>
       <c r="C6" t="n">
-        <v>31.46770168608924</v>
+        <v>28.88799468993229</v>
       </c>
       <c r="D6" t="n">
-        <v>47.88484528894177</v>
+        <v>45.20055101327683</v>
       </c>
       <c r="E6" t="n">
-        <v>32.59864432404848</v>
+        <v>42.02953324750575</v>
       </c>
       <c r="F6" t="n">
-        <v>48.27816113993494</v>
+        <v>32.06893019990923</v>
       </c>
       <c r="G6" t="n">
-        <v>47.26464759023417</v>
+        <v>40.30777195445356</v>
       </c>
       <c r="H6" t="n">
-        <v>31.77454657136363</v>
+        <v>29.09409291250282</v>
       </c>
       <c r="I6" t="n">
-        <v>34.94758380245447</v>
+        <v>31.09061809992097</v>
       </c>
       <c r="J6" t="n">
-        <v>53.5350050007155</v>
+        <v>48.39594316749783</v>
       </c>
       <c r="K6" t="n">
-        <v>48.76905685183424</v>
+        <v>44.20270135270425</v>
       </c>
       <c r="L6" t="n">
-        <v>35.06061847657009</v>
+        <v>42.86011670197406</v>
       </c>
       <c r="M6" t="n">
-        <v>61.1131300017393</v>
+        <v>43.58509646039332</v>
       </c>
       <c r="N6" t="n">
-        <v>33.11369695891425</v>
+        <v>52.33776005304261</v>
       </c>
       <c r="O6" t="n">
-        <v>34.94033936778357</v>
+        <v>44.3514804038119</v>
       </c>
       <c r="P6" t="n">
-        <v>50.08874728996172</v>
+        <v>47.30917494593844</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.913731307676</v>
+        <v>43.23668205535493</v>
       </c>
       <c r="R6" t="n">
-        <v>45.36974635096028</v>
+        <v>29.16401245507686</v>
       </c>
       <c r="S6" t="n">
-        <v>37.15706487431552</v>
+        <v>45.32075334361812</v>
       </c>
       <c r="T6" t="n">
-        <v>33.719917436015</v>
+        <v>29.96306080225943</v>
       </c>
       <c r="U6" t="n">
-        <v>36.57271240001938</v>
+        <v>31.04897580497879</v>
       </c>
       <c r="V6" t="n">
-        <v>47.15817116591835</v>
+        <v>43.59785658992364</v>
       </c>
       <c r="W6" t="n">
-        <v>36.17842140236897</v>
+        <v>44.540606653</v>
       </c>
       <c r="X6" t="n">
-        <v>36.16916257921046</v>
+        <v>32.30786118683805</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.55193459322763</v>
+        <v>36.51230668195686</v>
       </c>
       <c r="Z6" t="n">
-        <v>37.17478649399726</v>
+        <v>44.87482991848205</v>
       </c>
       <c r="AA6" t="n">
-        <v>47.92606624166424</v>
+        <v>43.45630697147916</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.34500524614689</v>
+        <v>45.21512480229501</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.89246617489259</v>
+        <v>18.32856253262682</v>
       </c>
       <c r="C7" t="n">
-        <v>18.6081076913471</v>
+        <v>15.83358961414644</v>
       </c>
       <c r="D7" t="n">
-        <v>21.89923187085369</v>
+        <v>19.29608093154172</v>
       </c>
       <c r="E7" t="n">
-        <v>19.73905032930633</v>
+        <v>16.12506316577059</v>
       </c>
       <c r="F7" t="n">
-        <v>22.29254772184689</v>
+        <v>19.01452512412335</v>
       </c>
       <c r="G7" t="n">
-        <v>34.40505359549199</v>
+        <v>27.25336687866775</v>
       </c>
       <c r="H7" t="n">
-        <v>18.91495257662147</v>
+        <v>16.03968783671701</v>
       </c>
       <c r="I7" t="n">
-        <v>22.08798980771234</v>
+        <v>18.03621302413509</v>
       </c>
       <c r="J7" t="n">
-        <v>27.54939158262741</v>
+        <v>22.4914730857627</v>
       </c>
       <c r="K7" t="n">
-        <v>22.78344343374623</v>
+        <v>18.2982312709691</v>
       </c>
       <c r="L7" t="n">
-        <v>22.20102448182798</v>
+        <v>16.95564662023884</v>
       </c>
       <c r="M7" t="n">
-        <v>35.12751658365117</v>
+        <v>30.53069138460747</v>
       </c>
       <c r="N7" t="n">
-        <v>20.23996775105533</v>
+        <v>52.33776005304261</v>
       </c>
       <c r="O7" t="n">
-        <v>22.06652318243711</v>
+        <v>18.76608278765158</v>
       </c>
       <c r="P7" t="n">
-        <v>24.40742055752329</v>
+        <v>21.72368296778978</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.92811788958791</v>
+        <v>17.33221197361976</v>
       </c>
       <c r="R7" t="n">
-        <v>19.38413293287228</v>
+        <v>16.10960737929099</v>
       </c>
       <c r="S7" t="n">
-        <v>24.29747087957338</v>
+        <v>19.41628326188296</v>
       </c>
       <c r="T7" t="n">
-        <v>20.86032344127284</v>
+        <v>16.90865572647359</v>
       </c>
       <c r="U7" t="n">
-        <v>23.7086375502498</v>
+        <v>17.99097362492504</v>
       </c>
       <c r="V7" t="n">
-        <v>21.17255774783034</v>
+        <v>17.69338650818845</v>
       </c>
       <c r="W7" t="n">
-        <v>22.37950925417012</v>
+        <v>18.95533588297111</v>
       </c>
       <c r="X7" t="n">
-        <v>23.30956858446828</v>
+        <v>19.25345611105214</v>
       </c>
       <c r="Y7" t="n">
-        <v>24.90540253976091</v>
+        <v>22.67251463236067</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.31519249925513</v>
+        <v>18.97035983674688</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.9404528235762</v>
+        <v>17.55183688974393</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.41435110007281</v>
+        <v>32.07155082952855</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.27385580434171</v>
+        <v>30.57085374690755</v>
       </c>
       <c r="C8" t="n">
-        <v>42.26334077878353</v>
+        <v>39.05628883503585</v>
       </c>
       <c r="D8" t="n">
-        <v>45.55446495829013</v>
+        <v>42.51878015243113</v>
       </c>
       <c r="E8" t="n">
-        <v>37.39129433282316</v>
+        <v>33.50101902477384</v>
       </c>
       <c r="F8" t="n">
-        <v>36.4302704019309</v>
+        <v>32.96743557517704</v>
       </c>
       <c r="G8" t="n">
-        <v>60.39799156624537</v>
+        <v>52.75292523048873</v>
       </c>
       <c r="H8" t="n">
-        <v>42.57018566405792</v>
+        <v>39.2623870576064</v>
       </c>
       <c r="I8" t="n">
-        <v>45.74322289514879</v>
+        <v>41.2589122450245</v>
       </c>
       <c r="J8" t="n">
-        <v>51.20462467006382</v>
+        <v>45.7141723066521</v>
       </c>
       <c r="K8" t="n">
-        <v>46.43867652118269</v>
+        <v>41.52093049185849</v>
       </c>
       <c r="L8" t="n">
-        <v>45.8562575692644</v>
+        <v>40.17834584112827</v>
       </c>
       <c r="M8" t="n">
-        <v>58.78274967108747</v>
+        <v>53.75339060549847</v>
       </c>
       <c r="N8" t="n">
-        <v>35.15608608578346</v>
+        <v>52.33776005304261</v>
       </c>
       <c r="O8" t="n">
-        <v>39.38431310948506</v>
+        <v>35.81629182046147</v>
       </c>
       <c r="P8" t="n">
-        <v>41.1365240650197</v>
+        <v>38.20052790352678</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.09393996646934</v>
+        <v>27.41660239883745</v>
       </c>
       <c r="R8" t="n">
-        <v>43.03936602030873</v>
+        <v>39.33230660018042</v>
       </c>
       <c r="S8" t="n">
-        <v>47.95270396700981</v>
+        <v>42.63898248277229</v>
       </c>
       <c r="T8" t="n">
-        <v>44.51555652870928</v>
+        <v>40.13135494736305</v>
       </c>
       <c r="U8" t="n">
-        <v>41.86233382430346</v>
+        <v>35.85515895472302</v>
       </c>
       <c r="V8" t="n">
-        <v>41.74272365183204</v>
+        <v>37.91197413340575</v>
       </c>
       <c r="W8" t="n">
-        <v>46.0369579754846</v>
+        <v>42.18019306936233</v>
       </c>
       <c r="X8" t="n">
-        <v>34.50866081611159</v>
+        <v>30.34422274890862</v>
       </c>
       <c r="Y8" t="n">
-        <v>59.76413635216654</v>
+        <v>56.80812978848885</v>
       </c>
       <c r="Z8" t="n">
-        <v>36.48716469842383</v>
+        <v>31.00868433489646</v>
       </c>
       <c r="AA8" t="n">
-        <v>45.59568591101263</v>
+        <v>40.77453611063338</v>
       </c>
       <c r="AB8" t="n">
-        <v>67.84605638339121</v>
+        <v>66.76420438076096</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.1426272750495</v>
+        <v>28.59555782567092</v>
       </c>
       <c r="C9" t="n">
-        <v>34.45240180190228</v>
+        <v>30.33356893450381</v>
       </c>
       <c r="D9" t="n">
-        <v>37.74352598140887</v>
+        <v>33.79606025189911</v>
       </c>
       <c r="E9" t="n">
-        <v>34.52303763879429</v>
+        <v>29.64808665629445</v>
       </c>
       <c r="F9" t="n">
-        <v>27.54611077704723</v>
+        <v>23.75632161939517</v>
       </c>
       <c r="G9" t="n">
-        <v>50.24934817225198</v>
+        <v>41.75334570194538</v>
       </c>
       <c r="H9" t="n">
-        <v>34.75924668717666</v>
+        <v>30.53966715707441</v>
       </c>
       <c r="I9" t="n">
-        <v>37.93228391826752</v>
+        <v>32.53619234449249</v>
       </c>
       <c r="J9" t="n">
-        <v>43.39368569318263</v>
+        <v>36.99145240612006</v>
       </c>
       <c r="K9" t="n">
-        <v>38.62773754430143</v>
+        <v>32.79821059132649</v>
       </c>
       <c r="L9" t="n">
-        <v>38.04531859238317</v>
+        <v>31.45562594059625</v>
       </c>
       <c r="M9" t="n">
-        <v>50.97181069420642</v>
+        <v>45.03067070496488</v>
       </c>
       <c r="N9" t="n">
-        <v>36.08426186161051</v>
+        <v>52.33776005304261</v>
       </c>
       <c r="O9" t="n">
-        <v>39.43339455533179</v>
+        <v>34.66895360767809</v>
       </c>
       <c r="P9" t="n">
-        <v>42.10540734444301</v>
+        <v>37.93163985057682</v>
       </c>
       <c r="Q9" t="n">
-        <v>36.77241246634789</v>
+        <v>31.83219079689741</v>
       </c>
       <c r="R9" t="n">
-        <v>35.22842704342747</v>
+        <v>30.60958669964837</v>
       </c>
       <c r="S9" t="n">
-        <v>40.14176499012859</v>
+        <v>33.91626258224032</v>
       </c>
       <c r="T9" t="n">
-        <v>36.70461755182801</v>
+        <v>31.40863504683095</v>
       </c>
       <c r="U9" t="n">
-        <v>39.55741251583245</v>
+        <v>32.49455004955033</v>
       </c>
       <c r="V9" t="n">
-        <v>42.31837896706988</v>
+        <v>37.0781339967843</v>
       </c>
       <c r="W9" t="n">
-        <v>38.22380336472531</v>
+        <v>33.45531520332852</v>
       </c>
       <c r="X9" t="n">
-        <v>39.15386269502349</v>
+        <v>33.75343543140953</v>
       </c>
       <c r="Y9" t="n">
-        <v>40.74969665031608</v>
+        <v>37.17249395271803</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.3896331159119</v>
+        <v>30.91822600287583</v>
       </c>
       <c r="AA9" t="n">
-        <v>37.78474693413138</v>
+        <v>32.05181621010129</v>
       </c>
       <c r="AB9" t="n">
-        <v>48.25864521062802</v>
+        <v>46.57153014988594</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.02268472976972</v>
+        <v>21.23829510997019</v>
       </c>
       <c r="C2" t="n">
-        <v>15.89437438478413</v>
+        <v>15.47808159778802</v>
       </c>
       <c r="D2" t="n">
-        <v>21.67315593412568</v>
+        <v>21.25313015755231</v>
       </c>
       <c r="E2" t="n">
-        <v>21.51057442984349</v>
+        <v>21.02502466050255</v>
       </c>
       <c r="F2" t="n">
-        <v>21.84065768993079</v>
+        <v>21.35932724260797</v>
       </c>
       <c r="G2" t="n">
-        <v>22.66256344278447</v>
+        <v>21.90269744997049</v>
       </c>
       <c r="H2" t="n">
-        <v>21.49315564351139</v>
+        <v>21.05376993795934</v>
       </c>
       <c r="I2" t="n">
-        <v>21.79655986511385</v>
+        <v>21.25149617590348</v>
       </c>
       <c r="J2" t="n">
-        <v>22.15364110547526</v>
+        <v>21.54944000266875</v>
       </c>
       <c r="K2" t="n">
-        <v>21.88141762430092</v>
+        <v>21.26817692425584</v>
       </c>
       <c r="L2" t="n">
-        <v>21.73624062522806</v>
+        <v>21.12787856039612</v>
       </c>
       <c r="M2" t="n">
-        <v>22.55174524981182</v>
+        <v>21.98772064489631</v>
       </c>
       <c r="N2" t="n">
-        <v>21.56825213461818</v>
+        <v>21.10383974669217</v>
       </c>
       <c r="O2" t="n">
-        <v>28.93293419049865</v>
+        <v>28.30224690253777</v>
       </c>
       <c r="P2" t="n">
-        <v>21.91968178819866</v>
+        <v>21.49518165177023</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.66136020698365</v>
+        <v>21.13965394921093</v>
       </c>
       <c r="R2" t="n">
-        <v>21.62650207510062</v>
+        <v>21.14056468594357</v>
       </c>
       <c r="S2" t="n">
-        <v>21.92525517948095</v>
+        <v>21.32555071233411</v>
       </c>
       <c r="T2" t="n">
-        <v>21.68439265008365</v>
+        <v>21.1497448916943</v>
       </c>
       <c r="U2" t="n">
-        <v>25.34303654521349</v>
+        <v>24.48485797527076</v>
       </c>
       <c r="V2" t="n">
-        <v>21.82640601188903</v>
+        <v>21.29130253094257</v>
       </c>
       <c r="W2" t="n">
-        <v>27.40174652955777</v>
+        <v>26.78390378063456</v>
       </c>
       <c r="X2" t="n">
-        <v>21.8916976013072</v>
+        <v>21.34896114092979</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.26789018582522</v>
+        <v>21.93352070877837</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.31366175336127</v>
+        <v>27.54459291073911</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.77920678721595</v>
+        <v>21.19761790545708</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.5715086114823</v>
+        <v>22.33666321198844</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.53807092802812</v>
+        <v>21.73946656269293</v>
       </c>
       <c r="C3" t="n">
-        <v>11.33648860490306</v>
+        <v>11.15912448155789</v>
       </c>
       <c r="D3" t="n">
-        <v>22.06765862987748</v>
+        <v>21.85688122982894</v>
       </c>
       <c r="E3" t="n">
-        <v>20.88961691564185</v>
+        <v>20.21241692373562</v>
       </c>
       <c r="F3" t="n">
-        <v>23.26755793835073</v>
+        <v>22.61872317509645</v>
       </c>
       <c r="G3" t="n">
-        <v>29.07878250309482</v>
+        <v>26.45541433474635</v>
       </c>
       <c r="H3" t="n">
-        <v>20.78397023957723</v>
+        <v>20.43499659533942</v>
       </c>
       <c r="I3" t="n">
-        <v>22.95331874486711</v>
+        <v>21.84833607746113</v>
       </c>
       <c r="J3" t="n">
-        <v>25.47810376833858</v>
+        <v>23.95839581579283</v>
       </c>
       <c r="K3" t="n">
-        <v>23.54465419129917</v>
+        <v>21.95955099207384</v>
       </c>
       <c r="L3" t="n">
-        <v>22.51052438786213</v>
+        <v>20.95877741578019</v>
       </c>
       <c r="M3" t="n">
-        <v>29.165980064096</v>
+        <v>27.91631022850988</v>
       </c>
       <c r="N3" t="n">
-        <v>21.3172348440297</v>
+        <v>20.78942559004687</v>
       </c>
       <c r="O3" t="n">
-        <v>33.9982630019223</v>
+        <v>33.22406351158173</v>
       </c>
       <c r="P3" t="n">
-        <v>23.80489523127482</v>
+        <v>23.56166992331954</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.98004018974435</v>
+        <v>21.04427312816806</v>
       </c>
       <c r="R3" t="n">
-        <v>21.73877936656852</v>
+        <v>21.05608828963251</v>
       </c>
       <c r="S3" t="n">
-        <v>23.85005285598367</v>
+        <v>22.36158970796643</v>
       </c>
       <c r="T3" t="n">
-        <v>22.15100020370091</v>
+        <v>21.12003501820378</v>
       </c>
       <c r="U3" t="n">
-        <v>29.43846786309257</v>
+        <v>26.71884437947478</v>
       </c>
       <c r="V3" t="n">
-        <v>23.14292088678648</v>
+        <v>22.11544569487337</v>
       </c>
       <c r="W3" t="n">
-        <v>32.20661680831056</v>
+        <v>31.22516759439238</v>
       </c>
       <c r="X3" t="n">
-        <v>23.6258404605357</v>
+        <v>22.53934946990528</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.31429928659071</v>
+        <v>26.71559231988147</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.30551474895848</v>
+        <v>32.2892302008452</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.82256258630145</v>
+        <v>21.45809062201337</v>
       </c>
       <c r="AB3" t="n">
-        <v>28.49679944615952</v>
+        <v>29.57626529515477</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.22300070698343</v>
+        <v>13.89151974900022</v>
       </c>
       <c r="C4" t="n">
-        <v>13.81665794729614</v>
+        <v>11.66166068185268</v>
       </c>
       <c r="D4" t="n">
-        <v>16.27491216899407</v>
+        <v>14.05908843589933</v>
       </c>
       <c r="E4" t="n">
-        <v>14.4384792869398</v>
+        <v>11.48253191300952</v>
       </c>
       <c r="F4" t="n">
-        <v>18.16692155542733</v>
+        <v>15.25863336467593</v>
       </c>
       <c r="G4" t="n">
-        <v>27.45072512923609</v>
+        <v>21.39624981948045</v>
       </c>
       <c r="H4" t="n">
-        <v>14.24172608228115</v>
+        <v>11.8072230453648</v>
       </c>
       <c r="I4" t="n">
-        <v>17.66881633811848</v>
+        <v>14.04063186150722</v>
       </c>
       <c r="J4" t="n">
-        <v>21.67073326974902</v>
+        <v>17.37558864743366</v>
       </c>
       <c r="K4" t="n">
-        <v>18.62732376463421</v>
+        <v>14.22904858767048</v>
       </c>
       <c r="L4" t="n">
-        <v>16.98748277538724</v>
+        <v>12.64431402743895</v>
       </c>
       <c r="M4" t="n">
-        <v>27.70407030706274</v>
+        <v>23.8429373268967</v>
       </c>
       <c r="N4" t="n">
-        <v>15.08997549542497</v>
+        <v>47.34142200342082</v>
       </c>
       <c r="O4" t="n">
-        <v>16.19030378371219</v>
+        <v>13.5285021462519</v>
       </c>
       <c r="P4" t="n">
-        <v>19.05953509824441</v>
+        <v>16.79317141227942</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.1416740046224</v>
+        <v>12.77732246104866</v>
       </c>
       <c r="R4" t="n">
-        <v>15.74793536947058</v>
+        <v>12.78760965140342</v>
       </c>
       <c r="S4" t="n">
-        <v>19.12248911666431</v>
+        <v>14.87711191726103</v>
       </c>
       <c r="T4" t="n">
-        <v>16.40183604488408</v>
+        <v>12.89130429846113</v>
       </c>
       <c r="U4" t="n">
-        <v>18.70375101541944</v>
+        <v>12.84213417031816</v>
       </c>
       <c r="V4" t="n">
-        <v>17.80446035625248</v>
+        <v>14.29571410235012</v>
       </c>
       <c r="W4" t="n">
-        <v>17.68640493313328</v>
+        <v>14.55641013206945</v>
       </c>
       <c r="X4" t="n">
-        <v>18.74344083394339</v>
+        <v>15.14154347757842</v>
       </c>
       <c r="Y4" t="n">
-        <v>22.8276830569466</v>
+        <v>21.62776669521114</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.9652754064443</v>
+        <v>14.19170641746297</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.47280534045149</v>
+        <v>13.4320520115862</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.38124778882459</v>
+        <v>26.18644000072867</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>134.3589437592331</v>
+        <v>69.24145398805237</v>
       </c>
       <c r="C5" t="n">
-        <v>33.8786841032971</v>
+        <v>35.92278751806452</v>
       </c>
       <c r="D5" t="n">
-        <v>77.06744760946144</v>
+        <v>78.1835226206901</v>
       </c>
       <c r="E5" t="n">
-        <v>35.42001129504278</v>
+        <v>24.08081665046787</v>
       </c>
       <c r="F5" t="n">
-        <v>112.8269713895287</v>
+        <v>101.4247046835429</v>
       </c>
       <c r="G5" t="n">
-        <v>248.6495309230735</v>
+        <v>188.540091880209</v>
       </c>
       <c r="H5" t="n">
-        <v>41.61643384424086</v>
+        <v>38.85264388979208</v>
       </c>
       <c r="I5" t="n">
-        <v>104.2706641404277</v>
+        <v>79.47221575919822</v>
       </c>
       <c r="J5" t="n">
-        <v>163.2833501353511</v>
+        <v>130.4760077109177</v>
       </c>
       <c r="K5" t="n">
-        <v>113.8135564512455</v>
+        <v>78.74365130755565</v>
       </c>
       <c r="L5" t="n">
-        <v>85.84965356091428</v>
+        <v>50.99631904871281</v>
       </c>
       <c r="M5" t="n">
-        <v>284.4146704161323</v>
+        <v>255.931109559756</v>
       </c>
       <c r="N5" t="n">
-        <v>111.7975644674805</v>
+        <v>47.34142200342082</v>
       </c>
       <c r="O5" t="n">
-        <v>69.40766792172403</v>
+        <v>63.1184370747827</v>
       </c>
       <c r="P5" t="n">
-        <v>114.7975971361159</v>
+        <v>114.753329661809</v>
       </c>
       <c r="Q5" t="n">
-        <v>72.93249457945117</v>
+        <v>54.10238225171535</v>
       </c>
       <c r="R5" t="n">
-        <v>69.8673895813009</v>
+        <v>57.03878977850526</v>
       </c>
       <c r="S5" t="n">
-        <v>118.6991192138539</v>
+        <v>86.34967831589513</v>
       </c>
       <c r="T5" t="n">
-        <v>80.94190053440052</v>
+        <v>58.0577071382409</v>
       </c>
       <c r="U5" t="n">
-        <v>115.5763660637407</v>
+        <v>55.87092410769711</v>
       </c>
       <c r="V5" t="n">
-        <v>97.8995000279856</v>
+        <v>78.42533012353385</v>
       </c>
       <c r="W5" t="n">
-        <v>100.6268119787549</v>
+        <v>85.51585918656947</v>
       </c>
       <c r="X5" t="n">
-        <v>119.9185313919325</v>
+        <v>96.56037958550316</v>
       </c>
       <c r="Y5" t="n">
-        <v>196.9154144690237</v>
+        <v>215.5258175779015</v>
       </c>
       <c r="Z5" t="n">
-        <v>108.9682452730472</v>
+        <v>71.5759636013802</v>
       </c>
       <c r="AA5" t="n">
-        <v>97.2248314535362</v>
+        <v>65.74757254057691</v>
       </c>
       <c r="AB5" t="n">
-        <v>276.4469621679901</v>
+        <v>316.9378905098605</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.70567418643667</v>
+        <v>31.34142491130263</v>
       </c>
       <c r="C6" t="n">
-        <v>31.29541917095577</v>
+        <v>29.11156584415504</v>
       </c>
       <c r="D6" t="n">
-        <v>33.75367339265369</v>
+        <v>44.27160211848631</v>
       </c>
       <c r="E6" t="n">
-        <v>44.92115276639307</v>
+        <v>41.69504559559649</v>
       </c>
       <c r="F6" t="n">
-        <v>35.64568277908702</v>
+        <v>32.70853852697834</v>
       </c>
       <c r="G6" t="n">
-        <v>57.93339860868929</v>
+        <v>38.84615498178286</v>
       </c>
       <c r="H6" t="n">
-        <v>31.72048730594075</v>
+        <v>42.01973672795168</v>
       </c>
       <c r="I6" t="n">
-        <v>35.14757756177811</v>
+        <v>31.49053702380965</v>
       </c>
       <c r="J6" t="n">
-        <v>52.15340674920227</v>
+        <v>47.58810233002056</v>
       </c>
       <c r="K6" t="n">
-        <v>49.10999724408738</v>
+        <v>44.44156227025741</v>
       </c>
       <c r="L6" t="n">
-        <v>47.47015625484046</v>
+        <v>30.0942191897414</v>
       </c>
       <c r="M6" t="n">
-        <v>45.18283153072235</v>
+        <v>41.29284248919907</v>
       </c>
       <c r="N6" t="n">
-        <v>32.58967739885802</v>
+        <v>47.34142200342082</v>
       </c>
       <c r="O6" t="n">
-        <v>46.37003138971642</v>
+        <v>30.99401210025023</v>
       </c>
       <c r="P6" t="n">
-        <v>35.50770162220731</v>
+        <v>46.68824301191672</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.62434748407557</v>
+        <v>42.9898361436356</v>
       </c>
       <c r="R6" t="n">
-        <v>46.23060884892379</v>
+        <v>43.00012333399035</v>
       </c>
       <c r="S6" t="n">
-        <v>49.60516259611754</v>
+        <v>32.3270170795634</v>
       </c>
       <c r="T6" t="n">
-        <v>46.88450952433733</v>
+        <v>43.10381798104808</v>
       </c>
       <c r="U6" t="n">
-        <v>36.34753831534556</v>
+        <v>43.171293864809</v>
       </c>
       <c r="V6" t="n">
-        <v>35.28322157991205</v>
+        <v>31.74561926465254</v>
       </c>
       <c r="W6" t="n">
-        <v>47.86610372743003</v>
+        <v>32.94265027313767</v>
       </c>
       <c r="X6" t="n">
-        <v>36.22220205760302</v>
+        <v>32.5914486398808</v>
       </c>
       <c r="Y6" t="n">
-        <v>41.2737831823854</v>
+        <v>39.98994988757526</v>
       </c>
       <c r="Z6" t="n">
-        <v>49.44794888589757</v>
+        <v>31.64161157976534</v>
       </c>
       <c r="AA6" t="n">
-        <v>47.9554788199047</v>
+        <v>43.64456569417309</v>
       </c>
       <c r="AB6" t="n">
-        <v>43.92698788878964</v>
+        <v>43.71864229025135</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.71472070718176</v>
+        <v>18.20390418830233</v>
       </c>
       <c r="C7" t="n">
-        <v>18.30837794749446</v>
+        <v>15.97404512115478</v>
       </c>
       <c r="D7" t="n">
-        <v>20.7666321691924</v>
+        <v>18.37147287520144</v>
       </c>
       <c r="E7" t="n">
-        <v>18.9301992871381</v>
+        <v>15.79491635231162</v>
       </c>
       <c r="F7" t="n">
-        <v>22.65864155562569</v>
+        <v>19.57101780397805</v>
       </c>
       <c r="G7" t="n">
-        <v>31.94244512943441</v>
+        <v>25.70863425878257</v>
       </c>
       <c r="H7" t="n">
-        <v>18.73344608247948</v>
+        <v>16.11960748466691</v>
       </c>
       <c r="I7" t="n">
-        <v>22.16053633831681</v>
+        <v>18.35301630080931</v>
       </c>
       <c r="J7" t="n">
-        <v>26.16245326994734</v>
+        <v>21.68797308673576</v>
       </c>
       <c r="K7" t="n">
-        <v>23.1190437648325</v>
+        <v>18.54143302697261</v>
       </c>
       <c r="L7" t="n">
-        <v>21.47920277558555</v>
+        <v>16.95669846674106</v>
       </c>
       <c r="M7" t="n">
-        <v>32.1957903072611</v>
+        <v>28.15532176619881</v>
       </c>
       <c r="N7" t="n">
-        <v>19.58169549562329</v>
+        <v>47.34142200342082</v>
       </c>
       <c r="O7" t="n">
-        <v>20.68193614072421</v>
+        <v>17.84079935614364</v>
       </c>
       <c r="P7" t="n">
-        <v>23.55116745525643</v>
+        <v>21.10546862217114</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.63339400482072</v>
+        <v>17.08970690035079</v>
       </c>
       <c r="R7" t="n">
-        <v>20.2396553696689</v>
+        <v>17.09999409070554</v>
       </c>
       <c r="S7" t="n">
-        <v>23.61420911686264</v>
+        <v>19.18949635656313</v>
       </c>
       <c r="T7" t="n">
-        <v>20.8935560450824</v>
+        <v>17.20368873776323</v>
       </c>
       <c r="U7" t="n">
-        <v>23.35727564926274</v>
+        <v>17.26828718585448</v>
       </c>
       <c r="V7" t="n">
-        <v>22.2961803564508</v>
+        <v>18.60809854165223</v>
       </c>
       <c r="W7" t="n">
-        <v>22.17812493333162</v>
+        <v>18.86879457137156</v>
       </c>
       <c r="X7" t="n">
-        <v>23.23516083414168</v>
+        <v>19.45392791688052</v>
       </c>
       <c r="Y7" t="n">
-        <v>27.48442913341139</v>
+        <v>26.0567971464171</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.45699540664264</v>
+        <v>18.50409085676507</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.96452534064982</v>
+        <v>17.74443645088829</v>
       </c>
       <c r="AB7" t="n">
-        <v>30.87296778902291</v>
+        <v>30.49882444003077</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.02075152803978</v>
+        <v>30.389089522585</v>
       </c>
       <c r="C8" t="n">
-        <v>41.7758586491125</v>
+        <v>39.06032707199242</v>
       </c>
       <c r="D8" t="n">
-        <v>44.23411287081043</v>
+        <v>41.45775482603908</v>
       </c>
       <c r="E8" t="n">
-        <v>36.45453716930127</v>
+        <v>33.07668591692151</v>
       </c>
       <c r="F8" t="n">
-        <v>36.70349582135895</v>
+        <v>33.45446658739661</v>
       </c>
       <c r="G8" t="n">
-        <v>57.72432517395766</v>
+        <v>51.05532960715961</v>
       </c>
       <c r="H8" t="n">
-        <v>42.20092678409749</v>
+        <v>39.20588943550455</v>
       </c>
       <c r="I8" t="n">
-        <v>45.62801703993484</v>
+        <v>41.43929825164695</v>
       </c>
       <c r="J8" t="n">
-        <v>49.62993397156538</v>
+        <v>44.77425503757343</v>
       </c>
       <c r="K8" t="n">
-        <v>46.58652446645058</v>
+        <v>41.62771497781025</v>
       </c>
       <c r="L8" t="n">
-        <v>44.94668347720359</v>
+        <v>40.04298041757872</v>
       </c>
       <c r="M8" t="n">
-        <v>55.66327100887911</v>
+        <v>51.24160371703873</v>
       </c>
       <c r="N8" t="n">
-        <v>34.39718526992435</v>
+        <v>47.34142200342082</v>
       </c>
       <c r="O8" t="n">
-        <v>37.87515578935463</v>
+        <v>34.79917601993784</v>
       </c>
       <c r="P8" t="n">
-        <v>40.16156954110538</v>
+        <v>37.49462259269697</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.74594517628561</v>
+        <v>27.13257794390224</v>
       </c>
       <c r="R8" t="n">
-        <v>43.70713607128694</v>
+        <v>40.18627604154317</v>
       </c>
       <c r="S8" t="n">
-        <v>47.08168981848068</v>
+        <v>42.27577830740077</v>
       </c>
       <c r="T8" t="n">
-        <v>44.36103674670044</v>
+        <v>40.2899706886009</v>
       </c>
       <c r="U8" t="n">
-        <v>41.37779445964721</v>
+        <v>35.03460446820321</v>
       </c>
       <c r="V8" t="n">
-        <v>42.71038981756086</v>
+        <v>38.71256141973845</v>
       </c>
       <c r="W8" t="n">
-        <v>45.64779918029129</v>
+        <v>41.95721890077151</v>
       </c>
       <c r="X8" t="n">
-        <v>34.37068106570042</v>
+        <v>30.49590612659198</v>
       </c>
       <c r="Y8" t="n">
-        <v>62.04533074243984</v>
+        <v>59.97809220135849</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.55569656561599</v>
+        <v>30.48678272470203</v>
       </c>
       <c r="AA8" t="n">
-        <v>45.43200604226784</v>
+        <v>40.83071840172595</v>
       </c>
       <c r="AB8" t="n">
-        <v>65.99951619693539</v>
+        <v>64.97221334241296</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.90123468924474</v>
+        <v>27.56883123072692</v>
       </c>
       <c r="C9" t="n">
-        <v>32.76678903804033</v>
+        <v>29.30375683452161</v>
       </c>
       <c r="D9" t="n">
-        <v>35.22504325973824</v>
+        <v>31.70118458856827</v>
       </c>
       <c r="E9" t="n">
-        <v>32.40267434560025</v>
+        <v>28.20957167523908</v>
       </c>
       <c r="F9" t="n">
-        <v>27.26916322813189</v>
+        <v>23.76081920037481</v>
       </c>
       <c r="G9" t="n">
-        <v>46.40085673454383</v>
+        <v>39.03834563355666</v>
       </c>
       <c r="H9" t="n">
-        <v>33.19185717302533</v>
+        <v>29.44931919803373</v>
       </c>
       <c r="I9" t="n">
-        <v>36.61894742886267</v>
+        <v>31.68272801417615</v>
       </c>
       <c r="J9" t="n">
-        <v>40.6208643604932</v>
+        <v>35.0176848001026</v>
       </c>
       <c r="K9" t="n">
-        <v>37.57745485537836</v>
+        <v>31.87114474033944</v>
       </c>
       <c r="L9" t="n">
-        <v>35.9376138661314</v>
+        <v>30.28641018010791</v>
       </c>
       <c r="M9" t="n">
-        <v>46.65420139780691</v>
+        <v>41.48503347956566</v>
       </c>
       <c r="N9" t="n">
-        <v>34.04010658616913</v>
+        <v>47.34142200342082</v>
       </c>
       <c r="O9" t="n">
-        <v>36.55613666773031</v>
+        <v>32.48452229663211</v>
       </c>
       <c r="P9" t="n">
-        <v>39.73325872103406</v>
+        <v>36.03494756265599</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.09180560993015</v>
+        <v>30.41941827512496</v>
       </c>
       <c r="R9" t="n">
-        <v>34.69806646021475</v>
+        <v>30.4297058040723</v>
       </c>
       <c r="S9" t="n">
-        <v>38.07262020740852</v>
+        <v>32.51920806992995</v>
       </c>
       <c r="T9" t="n">
-        <v>35.35196713562824</v>
+        <v>30.53340045113006</v>
       </c>
       <c r="U9" t="n">
-        <v>37.81890818243008</v>
+        <v>30.60087633489096</v>
       </c>
       <c r="V9" t="n">
-        <v>41.6842661195568</v>
+        <v>36.51308299253662</v>
       </c>
       <c r="W9" t="n">
-        <v>36.63653602387746</v>
+        <v>32.19850628473839</v>
       </c>
       <c r="X9" t="n">
-        <v>37.69357192468757</v>
+        <v>32.78363963024736</v>
       </c>
       <c r="Y9" t="n">
-        <v>41.94284022395725</v>
+        <v>39.3865088597839</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.33983261701339</v>
+        <v>29.44338984151141</v>
       </c>
       <c r="AA9" t="n">
-        <v>36.42293643119568</v>
+        <v>31.07414816425509</v>
       </c>
       <c r="AB9" t="n">
-        <v>45.33137887956877</v>
+        <v>43.8285361533976</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.61400852989958</v>
+        <v>20.43487486043432</v>
       </c>
       <c r="C2" t="n">
-        <v>14.89430063599207</v>
+        <v>14.75248353895647</v>
       </c>
       <c r="D2" t="n">
-        <v>20.49253495581511</v>
+        <v>20.36171535472032</v>
       </c>
       <c r="E2" t="n">
-        <v>20.48379986586482</v>
+        <v>20.34300431728504</v>
       </c>
       <c r="F2" t="n">
-        <v>20.48950182873284</v>
+        <v>20.35368168964199</v>
       </c>
       <c r="G2" t="n">
-        <v>20.83509127848031</v>
+        <v>20.60731615127637</v>
       </c>
       <c r="H2" t="n">
-        <v>20.57023197479119</v>
+        <v>20.43471381859563</v>
       </c>
       <c r="I2" t="n">
-        <v>20.53110697621933</v>
+        <v>20.3797693692289</v>
       </c>
       <c r="J2" t="n">
-        <v>20.69422904142772</v>
+        <v>20.51890859144792</v>
       </c>
       <c r="K2" t="n">
-        <v>20.57251443398582</v>
+        <v>20.43799524567663</v>
       </c>
       <c r="L2" t="n">
-        <v>20.62806046164009</v>
+        <v>20.44411380652109</v>
       </c>
       <c r="M2" t="n">
-        <v>20.84507742778383</v>
+        <v>20.6644699860364</v>
       </c>
       <c r="N2" t="n">
-        <v>20.55210486476419</v>
+        <v>20.41949145371041</v>
       </c>
       <c r="O2" t="n">
-        <v>27.48029743184427</v>
+        <v>27.25377677175635</v>
       </c>
       <c r="P2" t="n">
-        <v>20.63972502470745</v>
+        <v>20.51255971189085</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.57384532878839</v>
+        <v>20.43423887734557</v>
       </c>
       <c r="R2" t="n">
-        <v>20.51347717086394</v>
+        <v>20.36621270237733</v>
       </c>
       <c r="S2" t="n">
-        <v>20.60572692020291</v>
+        <v>20.45554251411863</v>
       </c>
       <c r="T2" t="n">
-        <v>20.51135397030391</v>
+        <v>20.36560996401567</v>
       </c>
       <c r="U2" t="n">
-        <v>23.9747772649426</v>
+        <v>23.69801528395832</v>
       </c>
       <c r="V2" t="n">
-        <v>20.51669449754969</v>
+        <v>20.38050285442896</v>
       </c>
       <c r="W2" t="n">
-        <v>26.18424637773784</v>
+        <v>25.98541818851819</v>
       </c>
       <c r="X2" t="n">
-        <v>20.59223160628571</v>
+        <v>20.45188879627555</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.54508138409477</v>
+        <v>20.41531026933828</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.89304015231807</v>
+        <v>26.70690121604713</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.59358339857555</v>
+        <v>20.4112188802528</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.77652248237356</v>
+        <v>20.69895736756448</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.89663565890065</v>
+        <v>20.45487517902098</v>
       </c>
       <c r="C3" t="n">
-        <v>10.502801528062</v>
+        <v>10.37737339727349</v>
       </c>
       <c r="D3" t="n">
-        <v>20.03830862596695</v>
+        <v>19.93972642610523</v>
       </c>
       <c r="E3" t="n">
-        <v>19.95860341838198</v>
+        <v>19.78883913650234</v>
       </c>
       <c r="F3" t="n">
-        <v>20.01769820511582</v>
+        <v>19.8833518521631</v>
       </c>
       <c r="G3" t="n">
-        <v>22.46165062487636</v>
+        <v>21.67647301326888</v>
       </c>
       <c r="H3" t="n">
-        <v>20.5980483057906</v>
+        <v>20.4657865109453</v>
       </c>
       <c r="I3" t="n">
-        <v>20.31493274879809</v>
+        <v>20.0694872011973</v>
       </c>
       <c r="J3" t="n">
-        <v>21.46750703986081</v>
+        <v>21.05336226424135</v>
       </c>
       <c r="K3" t="n">
-        <v>20.60858575864422</v>
+        <v>20.48360456461726</v>
       </c>
       <c r="L3" t="n">
-        <v>20.9984680435342</v>
+        <v>20.52314410803268</v>
       </c>
       <c r="M3" t="n">
-        <v>23.38052008497102</v>
+        <v>22.92723399575918</v>
       </c>
       <c r="N3" t="n">
-        <v>20.46150820273856</v>
+        <v>20.35010873062203</v>
       </c>
       <c r="O3" t="n">
-        <v>31.88876110158804</v>
+        <v>31.6112300578121</v>
       </c>
       <c r="P3" t="n">
-        <v>21.07975352932434</v>
+        <v>21.00711321385306</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.61658650790668</v>
+        <v>20.45533804799057</v>
       </c>
       <c r="R3" t="n">
-        <v>20.18938408490852</v>
+        <v>19.97293116151326</v>
       </c>
       <c r="S3" t="n">
-        <v>20.8350556464252</v>
+        <v>20.59946848024609</v>
       </c>
       <c r="T3" t="n">
-        <v>20.17364782132346</v>
+        <v>19.96853024249597</v>
       </c>
       <c r="U3" t="n">
-        <v>26.82806656545963</v>
+        <v>25.97377539362355</v>
       </c>
       <c r="V3" t="n">
-        <v>20.20714677445143</v>
+        <v>20.07035434427715</v>
       </c>
       <c r="W3" t="n">
-        <v>30.78173152645674</v>
+        <v>30.47678655805059</v>
       </c>
       <c r="X3" t="n">
-        <v>20.75021912556937</v>
+        <v>20.58357354331491</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.41153785601259</v>
+        <v>20.32041237102514</v>
       </c>
       <c r="Z3" t="n">
-        <v>31.37209965951671</v>
+        <v>31.02097129975424</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.75741253469017</v>
+        <v>20.29090546780717</v>
       </c>
       <c r="AB3" t="n">
-        <v>22.08161526476778</v>
+        <v>22.35566137967767</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.26402688343762</v>
+        <v>12.20975818050861</v>
       </c>
       <c r="C4" t="n">
-        <v>12.28958314210003</v>
+        <v>10.76385508707472</v>
       </c>
       <c r="D4" t="n">
-        <v>12.89192698355005</v>
+        <v>11.38338790843359</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79326012422068</v>
+        <v>11.17203813309971</v>
       </c>
       <c r="F4" t="n">
-        <v>12.85766641784826</v>
+        <v>11.29264396570529</v>
       </c>
       <c r="G4" t="n">
-        <v>16.76125823174729</v>
+        <v>14.15756188748254</v>
       </c>
       <c r="H4" t="n">
-        <v>13.76955055527944</v>
+        <v>12.20793913885758</v>
       </c>
       <c r="I4" t="n">
-        <v>13.32761569802206</v>
+        <v>11.58731630756489</v>
       </c>
       <c r="J4" t="n">
-        <v>15.14073978247963</v>
+        <v>13.12990734115937</v>
       </c>
       <c r="K4" t="n">
-        <v>13.79533198186594</v>
+        <v>12.24500436726854</v>
       </c>
       <c r="L4" t="n">
-        <v>14.42274991665583</v>
+        <v>12.3141163266838</v>
       </c>
       <c r="M4" t="n">
-        <v>18.40424503135301</v>
+        <v>16.33306501019788</v>
       </c>
       <c r="N4" t="n">
-        <v>13.56479650864187</v>
+        <v>52.57648196418342</v>
       </c>
       <c r="O4" t="n">
-        <v>13.55564162848883</v>
+        <v>12.00373411763503</v>
       </c>
       <c r="P4" t="n">
-        <v>14.55450652246592</v>
+        <v>13.08724431450743</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.81036505090264</v>
+        <v>12.20257445895446</v>
       </c>
       <c r="R4" t="n">
-        <v>13.12847893642142</v>
+        <v>11.43418751910154</v>
       </c>
       <c r="S4" t="n">
-        <v>14.17048229218633</v>
+        <v>12.44320883646329</v>
       </c>
       <c r="T4" t="n">
-        <v>13.10449640937527</v>
+        <v>11.42737931203336</v>
       </c>
       <c r="U4" t="n">
-        <v>14.78180072138945</v>
+        <v>12.24362231947276</v>
       </c>
       <c r="V4" t="n">
-        <v>12.97729173495495</v>
+        <v>11.41054396903212</v>
       </c>
       <c r="W4" t="n">
-        <v>15.67202728015047</v>
+        <v>13.96982083887608</v>
       </c>
       <c r="X4" t="n">
-        <v>14.01804651333936</v>
+        <v>12.40193841263244</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.35658436856044</v>
+        <v>11.89406586348827</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.49583221207621</v>
+        <v>12.6528048925528</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.03331562910925</v>
+        <v>11.94255300206989</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.1132359850428</v>
+        <v>15.19033641725974</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.70944368473182</v>
+        <v>53.06691958457606</v>
       </c>
       <c r="C5" t="n">
-        <v>31.19431507197434</v>
+        <v>29.61683716600238</v>
       </c>
       <c r="D5" t="n">
-        <v>42.56879671526213</v>
+        <v>41.33187758495062</v>
       </c>
       <c r="E5" t="n">
-        <v>31.04705575695835</v>
+        <v>27.68885575316493</v>
       </c>
       <c r="F5" t="n">
-        <v>42.4978191582542</v>
+        <v>40.15117064585947</v>
       </c>
       <c r="G5" t="n">
-        <v>103.7727176170921</v>
+        <v>84.82133109443699</v>
       </c>
       <c r="H5" t="n">
-        <v>62.06158618238142</v>
+        <v>59.7401083100837</v>
       </c>
       <c r="I5" t="n">
-        <v>51.54849219528403</v>
+        <v>45.692930258592</v>
       </c>
       <c r="J5" t="n">
-        <v>79.88622567567053</v>
+        <v>70.28124439276743</v>
       </c>
       <c r="K5" t="n">
-        <v>59.34975294969699</v>
+        <v>57.32556107252724</v>
       </c>
       <c r="L5" t="n">
-        <v>67.56873286172211</v>
+        <v>56.33600948767935</v>
       </c>
       <c r="M5" t="n">
-        <v>143.856524444545</v>
+        <v>132.4139614244141</v>
       </c>
       <c r="N5" t="n">
-        <v>75.94220964653375</v>
+        <v>52.57648196418342</v>
       </c>
       <c r="O5" t="n">
-        <v>51.50078310498839</v>
+        <v>49.49276831880218</v>
       </c>
       <c r="P5" t="n">
-        <v>68.96708922361125</v>
+        <v>68.43335000716641</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.8009289336756</v>
+        <v>55.71291507383991</v>
       </c>
       <c r="R5" t="n">
-        <v>47.93680687696955</v>
+        <v>42.90801949020118</v>
       </c>
       <c r="S5" t="n">
-        <v>60.56492917666714</v>
+        <v>55.86103678524316</v>
       </c>
       <c r="T5" t="n">
-        <v>47.15918011156044</v>
+        <v>42.72415068896642</v>
       </c>
       <c r="U5" t="n">
-        <v>77.28809255424055</v>
+        <v>56.99704112750878</v>
       </c>
       <c r="V5" t="n">
-        <v>45.54468307468533</v>
+        <v>43.23537666533319</v>
       </c>
       <c r="W5" t="n">
-        <v>93.95377163105152</v>
+        <v>89.03547148920055</v>
       </c>
       <c r="X5" t="n">
-        <v>64.06743118983509</v>
+        <v>60.74334693399254</v>
       </c>
       <c r="Y5" t="n">
-        <v>52.79177664301566</v>
+        <v>51.76411264943005</v>
       </c>
       <c r="Z5" t="n">
-        <v>67.08110939129955</v>
+        <v>60.20615673422505</v>
       </c>
       <c r="AA5" t="n">
-        <v>62.99111817389055</v>
+        <v>50.71986461294602</v>
       </c>
       <c r="AB5" t="n">
-        <v>108.5476396739608</v>
+        <v>119.042501217608</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.83333395061339</v>
+        <v>30.81549756007174</v>
       </c>
       <c r="C6" t="n">
-        <v>44.14301444232499</v>
+        <v>29.36959446663791</v>
       </c>
       <c r="D6" t="n">
-        <v>31.46123405072572</v>
+        <v>43.18772376122234</v>
       </c>
       <c r="E6" t="n">
-        <v>31.36256719139632</v>
+        <v>42.97637398588841</v>
       </c>
       <c r="F6" t="n">
-        <v>44.71109771807326</v>
+        <v>29.89838334526832</v>
       </c>
       <c r="G6" t="n">
-        <v>48.6146895319723</v>
+        <v>32.76330126704569</v>
       </c>
       <c r="H6" t="n">
-        <v>32.33885762245512</v>
+        <v>44.01227499164633</v>
       </c>
       <c r="I6" t="n">
-        <v>31.89692276519773</v>
+        <v>43.39165216035359</v>
       </c>
       <c r="J6" t="n">
-        <v>33.71004684965534</v>
+        <v>31.7356467207225</v>
       </c>
       <c r="K6" t="n">
-        <v>32.36463904904158</v>
+        <v>44.04934022005722</v>
       </c>
       <c r="L6" t="n">
-        <v>32.99205698383147</v>
+        <v>30.91985570624698</v>
       </c>
       <c r="M6" t="n">
-        <v>50.25767633157808</v>
+        <v>48.13740086298652</v>
       </c>
       <c r="N6" t="n">
-        <v>32.14020390467143</v>
+        <v>52.57648196418342</v>
       </c>
       <c r="O6" t="n">
-        <v>45.07439745153992</v>
+        <v>43.46214359572603</v>
       </c>
       <c r="P6" t="n">
-        <v>32.02122705403884</v>
+        <v>44.54565239389294</v>
       </c>
       <c r="Q6" t="n">
-        <v>45.66379635112764</v>
+        <v>44.00691031174314</v>
       </c>
       <c r="R6" t="n">
-        <v>31.69778600359705</v>
+        <v>43.23852337189026</v>
       </c>
       <c r="S6" t="n">
-        <v>32.73978935936201</v>
+        <v>31.0489482160264</v>
       </c>
       <c r="T6" t="n">
-        <v>44.95792770960031</v>
+        <v>30.03311869159648</v>
       </c>
       <c r="U6" t="n">
-        <v>33.47998648352441</v>
+        <v>30.94406295946985</v>
       </c>
       <c r="V6" t="n">
-        <v>44.83072303517993</v>
+        <v>43.21487982182082</v>
       </c>
       <c r="W6" t="n">
-        <v>35.23491699193158</v>
+        <v>45.42819731473337</v>
       </c>
       <c r="X6" t="n">
-        <v>32.58735358051499</v>
+        <v>31.00767779219554</v>
       </c>
       <c r="Y6" t="n">
-        <v>32.89351862114314</v>
+        <v>31.43250216328182</v>
       </c>
       <c r="Z6" t="n">
-        <v>46.34926351230118</v>
+        <v>31.25854427211592</v>
       </c>
       <c r="AA6" t="n">
-        <v>45.88674692933424</v>
+        <v>43.74688885485856</v>
       </c>
       <c r="AB6" t="n">
-        <v>34.70327973887201</v>
+        <v>33.82103756782119</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.69081583994578</v>
+        <v>16.53994546896019</v>
       </c>
       <c r="C7" t="n">
-        <v>16.71637209860818</v>
+        <v>15.09404237552632</v>
       </c>
       <c r="D7" t="n">
-        <v>17.31871594005822</v>
+        <v>15.71357519688518</v>
       </c>
       <c r="E7" t="n">
-        <v>17.22004908072883</v>
+        <v>15.50222542155128</v>
       </c>
       <c r="F7" t="n">
-        <v>17.28445537435641</v>
+        <v>15.62283125415689</v>
       </c>
       <c r="G7" t="n">
-        <v>21.18804718825544</v>
+        <v>18.48774917593412</v>
       </c>
       <c r="H7" t="n">
-        <v>18.19633951178761</v>
+        <v>16.53812642730916</v>
       </c>
       <c r="I7" t="n">
-        <v>17.75440465453021</v>
+        <v>15.91750359601649</v>
       </c>
       <c r="J7" t="n">
-        <v>19.5675287389878</v>
+        <v>17.46009462961097</v>
       </c>
       <c r="K7" t="n">
-        <v>18.2221209383741</v>
+        <v>16.57519165572013</v>
       </c>
       <c r="L7" t="n">
-        <v>18.84953887316397</v>
+        <v>16.64430361513542</v>
       </c>
       <c r="M7" t="n">
-        <v>22.83103398786117</v>
+        <v>20.66325229864948</v>
       </c>
       <c r="N7" t="n">
-        <v>17.99158546515001</v>
+        <v>52.57648196418342</v>
       </c>
       <c r="O7" t="n">
-        <v>17.98234365213202</v>
+        <v>16.33383335519777</v>
       </c>
       <c r="P7" t="n">
-        <v>18.98120854610914</v>
+        <v>17.41734355207017</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.23715400741079</v>
+        <v>16.53276174740603</v>
       </c>
       <c r="R7" t="n">
-        <v>17.55526789292956</v>
+        <v>15.76437480755311</v>
       </c>
       <c r="S7" t="n">
-        <v>18.59727124869448</v>
+        <v>16.77339612491489</v>
       </c>
       <c r="T7" t="n">
-        <v>17.53128536588344</v>
+        <v>15.75756660048496</v>
       </c>
       <c r="U7" t="n">
-        <v>19.33501101268261</v>
+        <v>16.66636093358034</v>
       </c>
       <c r="V7" t="n">
-        <v>17.40408069146311</v>
+        <v>15.74073125748376</v>
       </c>
       <c r="W7" t="n">
-        <v>20.09881623665866</v>
+        <v>18.30000812732768</v>
       </c>
       <c r="X7" t="n">
-        <v>18.44483546984752</v>
+        <v>16.73212570108401</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.91225202002791</v>
+        <v>16.31895441237388</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.92262116858436</v>
+        <v>16.98299218100439</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.4601045856174</v>
+        <v>16.27274029052148</v>
       </c>
       <c r="AB7" t="n">
-        <v>20.54002494155095</v>
+        <v>19.5205237057113</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.53837316338236</v>
+        <v>29.35207802555249</v>
       </c>
       <c r="C8" t="n">
-        <v>40.96418229198694</v>
+        <v>39.17532407765749</v>
       </c>
       <c r="D8" t="n">
-        <v>41.56652613343698</v>
+        <v>39.79485689901634</v>
       </c>
       <c r="E8" t="n">
-        <v>35.39756090711028</v>
+        <v>33.58301762260299</v>
       </c>
       <c r="F8" t="n">
-        <v>31.90803885746172</v>
+        <v>30.19056554240183</v>
       </c>
       <c r="G8" t="n">
-        <v>47.79977408001915</v>
+        <v>44.90576236513866</v>
       </c>
       <c r="H8" t="n">
-        <v>42.44414970516634</v>
+        <v>40.61940812944034</v>
       </c>
       <c r="I8" t="n">
-        <v>42.00221484790897</v>
+        <v>39.99878529814766</v>
       </c>
       <c r="J8" t="n">
-        <v>43.81533893236656</v>
+        <v>41.54137633174211</v>
       </c>
       <c r="K8" t="n">
-        <v>42.46993113175284</v>
+        <v>40.65647335785133</v>
       </c>
       <c r="L8" t="n">
-        <v>43.09734906654273</v>
+        <v>40.7255853172666</v>
       </c>
       <c r="M8" t="n">
-        <v>47.07884418123965</v>
+        <v>44.74453400078101</v>
       </c>
       <c r="N8" t="n">
-        <v>33.40229246378802</v>
+        <v>52.57648196418342</v>
       </c>
       <c r="O8" t="n">
-        <v>35.82165027329595</v>
+        <v>34.08031185291769</v>
       </c>
       <c r="P8" t="n">
-        <v>36.22522802589272</v>
+        <v>34.57538075315691</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.84430144360151</v>
+        <v>27.13024929088168</v>
       </c>
       <c r="R8" t="n">
-        <v>41.80307808630831</v>
+        <v>39.84565650968431</v>
       </c>
       <c r="S8" t="n">
-        <v>42.84508144207324</v>
+        <v>40.85467782704603</v>
       </c>
       <c r="T8" t="n">
-        <v>41.77909555926217</v>
+        <v>39.83884830261614</v>
       </c>
       <c r="U8" t="n">
-        <v>38.0191302754321</v>
+        <v>35.24787337134723</v>
       </c>
       <c r="V8" t="n">
-        <v>38.53400369841429</v>
+        <v>36.74022213317345</v>
       </c>
       <c r="W8" t="n">
-        <v>44.34886690725232</v>
+        <v>42.38350454107818</v>
       </c>
       <c r="X8" t="n">
-        <v>30.09683873474964</v>
+        <v>28.3624531564489</v>
       </c>
       <c r="Y8" t="n">
-        <v>53.49193154385861</v>
+        <v>51.60216104967012</v>
       </c>
       <c r="Z8" t="n">
-        <v>31.55841294198932</v>
+        <v>29.58579450655018</v>
       </c>
       <c r="AA8" t="n">
-        <v>42.70791477899616</v>
+        <v>40.35402199265267</v>
       </c>
       <c r="AB8" t="n">
-        <v>56.69635253203346</v>
+        <v>55.37337400213404</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.00811526588058</v>
+        <v>26.60232478347196</v>
       </c>
       <c r="C9" t="n">
-        <v>31.29591587570411</v>
+        <v>29.30090026982867</v>
       </c>
       <c r="D9" t="n">
-        <v>31.89825971715415</v>
+        <v>29.9204330911875</v>
       </c>
       <c r="E9" t="n">
-        <v>30.81588470650347</v>
+        <v>28.75255491428519</v>
       </c>
       <c r="F9" t="n">
-        <v>22.03836186535598</v>
+        <v>20.27553429322805</v>
       </c>
       <c r="G9" t="n">
-        <v>35.76759156278712</v>
+        <v>32.69460752476914</v>
       </c>
       <c r="H9" t="n">
-        <v>32.77588328888355</v>
+        <v>30.74498432161147</v>
       </c>
       <c r="I9" t="n">
-        <v>32.33394843162614</v>
+        <v>30.12436149031881</v>
       </c>
       <c r="J9" t="n">
-        <v>34.14707251608371</v>
+        <v>31.6669525239133</v>
       </c>
       <c r="K9" t="n">
-        <v>32.80166471546998</v>
+        <v>30.78204955002246</v>
       </c>
       <c r="L9" t="n">
-        <v>33.42908265025992</v>
+        <v>30.85116150943773</v>
       </c>
       <c r="M9" t="n">
-        <v>37.41057776495708</v>
+        <v>34.87011019295182</v>
       </c>
       <c r="N9" t="n">
-        <v>32.57112924224595</v>
+        <v>52.57648196418342</v>
       </c>
       <c r="O9" t="n">
-        <v>33.97447735456567</v>
+        <v>31.91425468016959</v>
       </c>
       <c r="P9" t="n">
-        <v>35.28053728499865</v>
+        <v>33.29647210841744</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.81669838194245</v>
+        <v>30.73962009624103</v>
       </c>
       <c r="R9" t="n">
-        <v>32.1348116700255</v>
+        <v>29.97123270185546</v>
       </c>
       <c r="S9" t="n">
-        <v>33.17681502579041</v>
+        <v>30.98025401921721</v>
       </c>
       <c r="T9" t="n">
-        <v>32.11082914297936</v>
+        <v>29.9644244947873</v>
       </c>
       <c r="U9" t="n">
-        <v>33.91701214995282</v>
+        <v>30.87536876266072</v>
       </c>
       <c r="V9" t="n">
-        <v>36.90216186896934</v>
+        <v>34.73022733349805</v>
       </c>
       <c r="W9" t="n">
-        <v>34.67836001375456</v>
+        <v>32.50686602162997</v>
       </c>
       <c r="X9" t="n">
-        <v>33.02437924694343</v>
+        <v>30.93898359538633</v>
       </c>
       <c r="Y9" t="n">
-        <v>32.49179579712383</v>
+        <v>30.52581230667622</v>
       </c>
       <c r="Z9" t="n">
-        <v>30.93241085272104</v>
+        <v>28.69109821359777</v>
       </c>
       <c r="AA9" t="n">
-        <v>33.03964836271332</v>
+        <v>30.47959818482381</v>
       </c>
       <c r="AB9" t="n">
-        <v>35.11956871864689</v>
+        <v>33.72738160001363</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.23383853120063</v>
+        <v>20.1924282892076</v>
       </c>
       <c r="C2" t="n">
-        <v>14.58580314489988</v>
+        <v>14.53687980812045</v>
       </c>
       <c r="D2" t="n">
-        <v>20.12893465059265</v>
+        <v>20.08619038763584</v>
       </c>
       <c r="E2" t="n">
-        <v>20.11989377759684</v>
+        <v>20.07789543281517</v>
       </c>
       <c r="F2" t="n">
-        <v>20.15728300486593</v>
+        <v>20.1156150850619</v>
       </c>
       <c r="G2" t="n">
-        <v>20.19996116114292</v>
+        <v>20.1569890847421</v>
       </c>
       <c r="H2" t="n">
-        <v>20.21550810593039</v>
+        <v>20.17433451081387</v>
       </c>
       <c r="I2" t="n">
-        <v>20.19827587547955</v>
+        <v>20.14922568238471</v>
       </c>
       <c r="J2" t="n">
-        <v>20.2005092606678</v>
+        <v>20.15813670084522</v>
       </c>
       <c r="K2" t="n">
-        <v>20.18981543034256</v>
+        <v>20.1462634751167</v>
       </c>
       <c r="L2" t="n">
-        <v>20.16568644863053</v>
+        <v>20.12399811447396</v>
       </c>
       <c r="M2" t="n">
-        <v>20.01791013602203</v>
+        <v>19.97663005348209</v>
       </c>
       <c r="N2" t="n">
-        <v>20.20533502837521</v>
+        <v>20.16383453184213</v>
       </c>
       <c r="O2" t="n">
-        <v>27.08511868742584</v>
+        <v>26.99023339447682</v>
       </c>
       <c r="P2" t="n">
-        <v>20.20357083615527</v>
+        <v>20.16222684502708</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.21027020454656</v>
+        <v>20.16855171683517</v>
       </c>
       <c r="R2" t="n">
-        <v>20.17757086592101</v>
+        <v>20.13518347206595</v>
       </c>
       <c r="S2" t="n">
-        <v>20.19632915703091</v>
+        <v>20.15321168816736</v>
       </c>
       <c r="T2" t="n">
-        <v>20.14050063817447</v>
+        <v>20.09487044352164</v>
       </c>
       <c r="U2" t="n">
-        <v>23.39838295086769</v>
+        <v>23.32529336825326</v>
       </c>
       <c r="V2" t="n">
-        <v>20.21026610891282</v>
+        <v>20.1683500855308</v>
       </c>
       <c r="W2" t="n">
-        <v>25.63733296461284</v>
+        <v>25.56087528795707</v>
       </c>
       <c r="X2" t="n">
-        <v>20.40225925160949</v>
+        <v>20.36143045035245</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.28000823464209</v>
+        <v>20.23873129661511</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.41858934232092</v>
+        <v>26.36590098837531</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.21647203771317</v>
+        <v>20.17430264709003</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.14933844126937</v>
+        <v>20.10800260415373</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.24038316766763</v>
+        <v>20.20020823605289</v>
       </c>
       <c r="C3" t="n">
-        <v>10.36132096797344</v>
+        <v>10.30874245633753</v>
       </c>
       <c r="D3" t="n">
-        <v>19.4995531228519</v>
+        <v>19.44985716347558</v>
       </c>
       <c r="E3" t="n">
-        <v>19.41660457004308</v>
+        <v>19.37220726682498</v>
       </c>
       <c r="F3" t="n">
-        <v>19.70123268420103</v>
+        <v>19.65920168730005</v>
       </c>
       <c r="G3" t="n">
-        <v>20.00111850409636</v>
+        <v>19.94990113316234</v>
       </c>
       <c r="H3" t="n">
-        <v>20.11998401138089</v>
+        <v>20.08148047975818</v>
       </c>
       <c r="I3" t="n">
-        <v>19.99423532822448</v>
+        <v>19.899450128799</v>
       </c>
       <c r="J3" t="n">
-        <v>20.00599331971681</v>
+        <v>19.95898836242792</v>
       </c>
       <c r="K3" t="n">
-        <v>19.93333198761953</v>
+        <v>19.87793019752578</v>
       </c>
       <c r="L3" t="n">
-        <v>19.76125204363442</v>
+        <v>19.71911270735462</v>
       </c>
       <c r="M3" t="n">
-        <v>19.56500503591786</v>
+        <v>19.52547739513038</v>
       </c>
       <c r="N3" t="n">
-        <v>20.0410505469824</v>
+        <v>20.00022419062811</v>
       </c>
       <c r="O3" t="n">
-        <v>31.70981249882624</v>
+        <v>31.58197804414088</v>
       </c>
       <c r="P3" t="n">
-        <v>20.02478043419634</v>
+        <v>19.98507761697139</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.07508245439675</v>
+        <v>20.03271654957474</v>
       </c>
       <c r="R3" t="n">
-        <v>19.84685745283888</v>
+        <v>19.7996701878229</v>
       </c>
       <c r="S3" t="n">
-        <v>19.97370761141747</v>
+        <v>19.92146205488975</v>
       </c>
       <c r="T3" t="n">
-        <v>19.58228499597929</v>
+        <v>19.51202653252107</v>
       </c>
       <c r="U3" t="n">
-        <v>25.26928996433087</v>
+        <v>25.17623494394837</v>
       </c>
       <c r="V3" t="n">
-        <v>20.07415246009245</v>
+        <v>20.03039216933784</v>
       </c>
       <c r="W3" t="n">
-        <v>29.4956673375938</v>
+        <v>29.39107266493372</v>
       </c>
       <c r="X3" t="n">
-        <v>21.44501484497833</v>
+        <v>21.40897050837243</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.57460317679132</v>
+        <v>20.53536936140487</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.37058904948524</v>
+        <v>30.30583632852227</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.12075000769513</v>
+        <v>20.07514693260751</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.66706490701229</v>
+        <v>19.62726621825501</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.08706935426641</v>
+        <v>11.91578687930597</v>
       </c>
       <c r="C4" t="n">
-        <v>11.93384492973941</v>
+        <v>10.76259396358697</v>
       </c>
       <c r="D4" t="n">
-        <v>11.90213176463051</v>
+        <v>10.71578090920367</v>
       </c>
       <c r="E4" t="n">
-        <v>11.80001094513588</v>
+        <v>10.6220855786366</v>
       </c>
       <c r="F4" t="n">
-        <v>12.22233946703448</v>
+        <v>11.04814640266063</v>
       </c>
       <c r="G4" t="n">
-        <v>12.70440887510477</v>
+        <v>11.51548476202868</v>
       </c>
       <c r="H4" t="n">
-        <v>12.88001876842749</v>
+        <v>11.71140932879963</v>
       </c>
       <c r="I4" t="n">
-        <v>12.68537279826724</v>
+        <v>11.42779356106051</v>
       </c>
       <c r="J4" t="n">
-        <v>12.68269192291976</v>
+        <v>11.5005320726507</v>
       </c>
       <c r="K4" t="n">
-        <v>12.58980817844815</v>
+        <v>11.39433406728566</v>
       </c>
       <c r="L4" t="n">
-        <v>12.31726023013135</v>
+        <v>11.14283657625385</v>
       </c>
       <c r="M4" t="n">
-        <v>12.22175334897926</v>
+        <v>11.05145782951666</v>
       </c>
       <c r="N4" t="n">
-        <v>12.76510917759457</v>
+        <v>44.65551266421883</v>
       </c>
       <c r="O4" t="n">
-        <v>13.42087071993086</v>
+        <v>12.25085854656114</v>
       </c>
       <c r="P4" t="n">
-        <v>12.74518181490209</v>
+        <v>11.57464767393633</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.82085426274331</v>
+        <v>11.6460900105934</v>
       </c>
       <c r="R4" t="n">
-        <v>12.45150019052883</v>
+        <v>11.26918033577414</v>
       </c>
       <c r="S4" t="n">
-        <v>12.66338371785517</v>
+        <v>11.47281733002873</v>
       </c>
       <c r="T4" t="n">
-        <v>12.03277491498427</v>
+        <v>10.81382613345679</v>
       </c>
       <c r="U4" t="n">
-        <v>12.45196602091823</v>
+        <v>11.30019693292595</v>
       </c>
       <c r="V4" t="n">
-        <v>12.64348521409221</v>
+        <v>11.46643697024836</v>
       </c>
       <c r="W4" t="n">
-        <v>13.77398113609434</v>
+        <v>12.58913793808071</v>
       </c>
       <c r="X4" t="n">
-        <v>14.98945886864394</v>
+        <v>13.82474403427233</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.52272699293993</v>
+        <v>12.37367824827751</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.92533483381121</v>
+        <v>11.74166350661655</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.89090682134445</v>
+        <v>11.71104941338072</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.17171094560629</v>
+        <v>11.00101972491135</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.44888975728021</v>
+        <v>48.24786980204052</v>
       </c>
       <c r="C5" t="n">
-        <v>32.88567874902607</v>
+        <v>31.67812887189249</v>
       </c>
       <c r="D5" t="n">
-        <v>32.57190796408787</v>
+        <v>31.10435103837502</v>
       </c>
       <c r="E5" t="n">
-        <v>21.21827661569972</v>
+        <v>19.88678324364253</v>
       </c>
       <c r="F5" t="n">
-        <v>37.90154368652868</v>
+        <v>36.64023227604471</v>
       </c>
       <c r="G5" t="n">
-        <v>43.98673825905</v>
+        <v>42.52782575821749</v>
       </c>
       <c r="H5" t="n">
-        <v>51.18987036384145</v>
+        <v>50.02702713246441</v>
       </c>
       <c r="I5" t="n">
-        <v>46.31621196510309</v>
+        <v>43.54559062343949</v>
       </c>
       <c r="J5" t="n">
-        <v>44.56738035815334</v>
+        <v>43.19383850607126</v>
       </c>
       <c r="K5" t="n">
-        <v>44.35614303436292</v>
+        <v>42.75765086986286</v>
       </c>
       <c r="L5" t="n">
-        <v>39.60294910198742</v>
+        <v>38.35691962570931</v>
       </c>
       <c r="M5" t="n">
-        <v>39.68613662077924</v>
+        <v>38.49267382069242</v>
       </c>
       <c r="N5" t="n">
-        <v>42.3853029442456</v>
+        <v>44.65551266421883</v>
       </c>
       <c r="O5" t="n">
-        <v>54.31889222301828</v>
+        <v>53.13714454682483</v>
       </c>
       <c r="P5" t="n">
-        <v>43.61934383023044</v>
+        <v>42.43118558297957</v>
       </c>
       <c r="Q5" t="n">
-        <v>46.24723130430259</v>
+        <v>44.98929017352919</v>
       </c>
       <c r="R5" t="n">
-        <v>42.38438927168805</v>
+        <v>40.96828016728203</v>
       </c>
       <c r="S5" t="n">
-        <v>42.48945318542334</v>
+        <v>41.00641108566079</v>
       </c>
       <c r="T5" t="n">
-        <v>34.97833794800251</v>
+        <v>32.95212943583633</v>
       </c>
       <c r="U5" t="n">
-        <v>42.15801018837998</v>
+        <v>40.93693951893597</v>
       </c>
       <c r="V5" t="n">
-        <v>45.60229240891367</v>
+        <v>44.31283440738962</v>
       </c>
       <c r="W5" t="n">
-        <v>62.73011724854248</v>
+        <v>61.29915343106503</v>
       </c>
       <c r="X5" t="n">
-        <v>84.44555532491052</v>
+        <v>83.35075719035508</v>
       </c>
       <c r="Y5" t="n">
-        <v>61.11062561493659</v>
+        <v>59.93090919657969</v>
       </c>
       <c r="Z5" t="n">
-        <v>46.43246574374443</v>
+        <v>45.04147456857592</v>
       </c>
       <c r="AA5" t="n">
-        <v>48.21420811978106</v>
+        <v>46.85631202339903</v>
       </c>
       <c r="AB5" t="n">
-        <v>37.67163875893397</v>
+        <v>36.47102135299252</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.38383605476662</v>
+        <v>41.37601195787492</v>
       </c>
       <c r="C6" t="n">
-        <v>29.23061163023962</v>
+        <v>28.09063876465111</v>
       </c>
       <c r="D6" t="n">
-        <v>29.19889846513074</v>
+        <v>28.04382571026784</v>
       </c>
       <c r="E6" t="n">
-        <v>41.25007302908445</v>
+        <v>27.95013037970073</v>
       </c>
       <c r="F6" t="n">
-        <v>41.67240155098308</v>
+        <v>40.50837148122965</v>
       </c>
       <c r="G6" t="n">
-        <v>30.00117557560498</v>
+        <v>40.97570984059769</v>
       </c>
       <c r="H6" t="n">
-        <v>30.17678546892774</v>
+        <v>41.17163440736857</v>
       </c>
       <c r="I6" t="n">
-        <v>29.98213949876748</v>
+        <v>40.88801863962946</v>
       </c>
       <c r="J6" t="n">
-        <v>29.97945862341996</v>
+        <v>40.96075715121966</v>
       </c>
       <c r="K6" t="n">
-        <v>29.88657487894838</v>
+        <v>40.85455914585464</v>
       </c>
       <c r="L6" t="n">
-        <v>41.76732231407989</v>
+        <v>28.47088137731805</v>
       </c>
       <c r="M6" t="n">
-        <v>41.67181543292787</v>
+        <v>40.51168290808562</v>
       </c>
       <c r="N6" t="n">
-        <v>30.06804001564694</v>
+        <v>44.65551266421883</v>
       </c>
       <c r="O6" t="n">
-        <v>30.72380155798312</v>
+        <v>41.38733583713773</v>
       </c>
       <c r="P6" t="n">
-        <v>29.01916513082336</v>
+        <v>27.88075193022629</v>
       </c>
       <c r="Q6" t="n">
-        <v>30.11762096324351</v>
+        <v>41.10631508916241</v>
       </c>
       <c r="R6" t="n">
-        <v>41.90156227447742</v>
+        <v>28.59722513683833</v>
       </c>
       <c r="S6" t="n">
-        <v>29.96015041835541</v>
+        <v>40.9330424085977</v>
       </c>
       <c r="T6" t="n">
-        <v>41.48283699893291</v>
+        <v>28.14187093452095</v>
       </c>
       <c r="U6" t="n">
-        <v>29.83458312222922</v>
+        <v>28.69336413412218</v>
       </c>
       <c r="V6" t="n">
-        <v>42.09354729804077</v>
+        <v>28.79448177131254</v>
       </c>
       <c r="W6" t="n">
-        <v>31.98796795464173</v>
+        <v>30.83379264087365</v>
       </c>
       <c r="X6" t="n">
-        <v>32.28622556914417</v>
+        <v>43.28496911284122</v>
       </c>
       <c r="Y6" t="n">
-        <v>31.69088436082928</v>
+        <v>30.55199737982576</v>
       </c>
       <c r="Z6" t="n">
-        <v>42.37539691775982</v>
+        <v>29.06970830768071</v>
       </c>
       <c r="AA6" t="n">
-        <v>42.34096890529301</v>
+        <v>41.17127449194971</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.47147908556863</v>
+        <v>28.33226372506881</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.04078768211645</v>
+        <v>15.82707144210441</v>
       </c>
       <c r="C7" t="n">
-        <v>15.88756325758946</v>
+        <v>14.67387852638538</v>
       </c>
       <c r="D7" t="n">
-        <v>15.85585009248055</v>
+        <v>14.62706547200208</v>
       </c>
       <c r="E7" t="n">
-        <v>15.75372927298592</v>
+        <v>14.53337014143501</v>
       </c>
       <c r="F7" t="n">
-        <v>16.17605779488453</v>
+        <v>14.95943096545906</v>
       </c>
       <c r="G7" t="n">
-        <v>16.65812720295482</v>
+        <v>15.42676932482708</v>
       </c>
       <c r="H7" t="n">
-        <v>16.83373709627755</v>
+        <v>15.62269389159806</v>
       </c>
       <c r="I7" t="n">
-        <v>16.6390911261173</v>
+        <v>15.33907812385892</v>
       </c>
       <c r="J7" t="n">
-        <v>16.63641025076981</v>
+        <v>15.41181663544913</v>
       </c>
       <c r="K7" t="n">
-        <v>16.54352650629821</v>
+        <v>15.30561863008407</v>
       </c>
       <c r="L7" t="n">
-        <v>16.27097855798141</v>
+        <v>15.05412113905227</v>
       </c>
       <c r="M7" t="n">
-        <v>16.17547167682929</v>
+        <v>14.9627423923151</v>
       </c>
       <c r="N7" t="n">
-        <v>16.71882750544463</v>
+        <v>44.65551266421883</v>
       </c>
       <c r="O7" t="n">
-        <v>17.3745088287757</v>
+        <v>16.16206143741476</v>
       </c>
       <c r="P7" t="n">
-        <v>16.69881992374692</v>
+        <v>15.48585056478996</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.77457259059336</v>
+        <v>15.55737457339183</v>
       </c>
       <c r="R7" t="n">
-        <v>16.4052185183789</v>
+        <v>15.18046489857255</v>
       </c>
       <c r="S7" t="n">
-        <v>16.61710204570523</v>
+        <v>15.38410189282716</v>
       </c>
       <c r="T7" t="n">
-        <v>15.98649324283433</v>
+        <v>14.72511069625519</v>
       </c>
       <c r="U7" t="n">
-        <v>16.49006921863803</v>
+        <v>15.27553302235864</v>
       </c>
       <c r="V7" t="n">
-        <v>16.59720354194226</v>
+        <v>15.37772153304678</v>
       </c>
       <c r="W7" t="n">
-        <v>17.7276994639444</v>
+        <v>16.50042250087913</v>
       </c>
       <c r="X7" t="n">
-        <v>18.94317719649398</v>
+        <v>17.73602859707075</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.56229572160074</v>
+        <v>16.350085211208</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.87905316166128</v>
+        <v>15.65294806941499</v>
       </c>
       <c r="AA7" t="n">
-        <v>16.84462514919451</v>
+        <v>15.62233397617914</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.12542927345635</v>
+        <v>14.91230428770977</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.85833408157537</v>
+        <v>27.63704984724175</v>
       </c>
       <c r="C8" t="n">
-        <v>38.07792221469528</v>
+        <v>36.79537275909948</v>
       </c>
       <c r="D8" t="n">
-        <v>38.04620904958635</v>
+        <v>36.74855970471617</v>
       </c>
       <c r="E8" t="n">
-        <v>32.42087152179678</v>
+        <v>31.16428636646737</v>
       </c>
       <c r="F8" t="n">
-        <v>29.60956716130425</v>
+        <v>28.37582302340662</v>
       </c>
       <c r="G8" t="n">
-        <v>40.9993564165413</v>
+        <v>39.68642353773436</v>
       </c>
       <c r="H8" t="n">
-        <v>39.02409605338332</v>
+        <v>37.74418812431215</v>
       </c>
       <c r="I8" t="n">
-        <v>38.82945008322309</v>
+        <v>37.46057235657304</v>
       </c>
       <c r="J8" t="n">
-        <v>38.82676920787557</v>
+        <v>37.53331086816321</v>
       </c>
       <c r="K8" t="n">
-        <v>38.73388546340398</v>
+        <v>37.42711286279816</v>
       </c>
       <c r="L8" t="n">
-        <v>38.46133751508717</v>
+        <v>37.17561537176638</v>
       </c>
       <c r="M8" t="n">
-        <v>38.36583063393468</v>
+        <v>37.08423662502895</v>
       </c>
       <c r="N8" t="n">
-        <v>30.86852139685824</v>
+        <v>44.65551266421883</v>
       </c>
       <c r="O8" t="n">
-        <v>33.73392751563789</v>
+        <v>32.48707447820999</v>
       </c>
       <c r="P8" t="n">
-        <v>32.51660133237337</v>
+        <v>31.2724270594338</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.55362457434971</v>
+        <v>25.34090476930306</v>
       </c>
       <c r="R8" t="n">
-        <v>38.5955774754847</v>
+        <v>37.30195913128664</v>
       </c>
       <c r="S8" t="n">
-        <v>38.807461002811</v>
+        <v>37.50559612554123</v>
       </c>
       <c r="T8" t="n">
-        <v>38.17685219994012</v>
+        <v>36.84660492896932</v>
       </c>
       <c r="U8" t="n">
-        <v>33.61798875945387</v>
+        <v>32.36441827301583</v>
       </c>
       <c r="V8" t="n">
-        <v>35.95133229413018</v>
+        <v>34.68007746678693</v>
       </c>
       <c r="W8" t="n">
-        <v>39.92009697680816</v>
+        <v>38.6239432428288</v>
       </c>
       <c r="X8" t="n">
-        <v>29.67291806278769</v>
+        <v>28.46462970843573</v>
       </c>
       <c r="Y8" t="n">
-        <v>50.06426951681715</v>
+        <v>48.72277348486035</v>
       </c>
       <c r="Z8" t="n">
-        <v>28.50391924237589</v>
+        <v>27.27138477403471</v>
       </c>
       <c r="AA8" t="n">
-        <v>39.03498410630026</v>
+        <v>37.74382820889323</v>
       </c>
       <c r="AB8" t="n">
-        <v>49.15105830831882</v>
+        <v>47.80503903811306</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.29814076180009</v>
+        <v>24.03400769467797</v>
       </c>
       <c r="C9" t="n">
-        <v>27.67512921436525</v>
+        <v>26.37249799636368</v>
       </c>
       <c r="D9" t="n">
-        <v>27.64341604925635</v>
+        <v>26.32568494198037</v>
       </c>
       <c r="E9" t="n">
-        <v>26.72653738253207</v>
+        <v>25.42612423528084</v>
       </c>
       <c r="F9" t="n">
-        <v>19.82551808112833</v>
+        <v>18.60876617541211</v>
       </c>
       <c r="G9" t="n">
-        <v>28.44569431069758</v>
+        <v>27.12538992341274</v>
       </c>
       <c r="H9" t="n">
-        <v>28.62130305305334</v>
+        <v>27.32131336157634</v>
       </c>
       <c r="I9" t="n">
-        <v>28.42665708289309</v>
+        <v>27.03769759383722</v>
       </c>
       <c r="J9" t="n">
-        <v>28.42397620754559</v>
+        <v>27.11043610542745</v>
       </c>
       <c r="K9" t="n">
-        <v>28.33109246307396</v>
+        <v>27.00423810006236</v>
       </c>
       <c r="L9" t="n">
-        <v>28.05854451475721</v>
+        <v>26.75274060903055</v>
       </c>
       <c r="M9" t="n">
-        <v>27.96303763360508</v>
+        <v>26.6613618622934</v>
       </c>
       <c r="N9" t="n">
-        <v>28.50639346222042</v>
+        <v>44.65551266421883</v>
       </c>
       <c r="O9" t="n">
-        <v>30.33206446200683</v>
+        <v>29.01790332824827</v>
       </c>
       <c r="P9" t="n">
-        <v>29.91081054138741</v>
+        <v>28.59335046986242</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.56213969833611</v>
+        <v>27.25599517197747</v>
       </c>
       <c r="R9" t="n">
-        <v>28.19278447515469</v>
+        <v>26.87908436855086</v>
       </c>
       <c r="S9" t="n">
-        <v>28.404668002481</v>
+        <v>27.08272136280545</v>
       </c>
       <c r="T9" t="n">
-        <v>27.77405919961009</v>
+        <v>26.42373016623348</v>
       </c>
       <c r="U9" t="n">
-        <v>28.27910070635482</v>
+        <v>26.97522336583474</v>
       </c>
       <c r="V9" t="n">
-        <v>32.45856050038475</v>
+        <v>31.10566957314456</v>
       </c>
       <c r="W9" t="n">
-        <v>29.51526542072018</v>
+        <v>28.19904197085743</v>
       </c>
       <c r="X9" t="n">
-        <v>30.73074315326975</v>
+        <v>29.43464806704904</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.34986167837652</v>
+        <v>28.04870468118629</v>
       </c>
       <c r="Z9" t="n">
-        <v>26.53821512936406</v>
+        <v>25.246393500042</v>
       </c>
       <c r="AA9" t="n">
-        <v>28.63219110597028</v>
+        <v>27.32095344615744</v>
       </c>
       <c r="AB9" t="n">
-        <v>27.91299523023211</v>
+        <v>26.61092375768806</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.14039535648479</v>
+        <v>20.10150990799991</v>
       </c>
       <c r="C2" t="n">
-        <v>14.51713482423661</v>
+        <v>14.47177498398529</v>
       </c>
       <c r="D2" t="n">
-        <v>20.08834818424315</v>
+        <v>20.04941261149206</v>
       </c>
       <c r="E2" t="n">
-        <v>20.07302828343601</v>
+        <v>20.03360733265956</v>
       </c>
       <c r="F2" t="n">
-        <v>20.09648713037382</v>
+        <v>20.05714942683666</v>
       </c>
       <c r="G2" t="n">
-        <v>20.12297702082483</v>
+        <v>20.083982429033</v>
       </c>
       <c r="H2" t="n">
-        <v>20.13872929653659</v>
+        <v>20.0998468227674</v>
       </c>
       <c r="I2" t="n">
-        <v>20.16881339422831</v>
+        <v>20.12760915550493</v>
       </c>
       <c r="J2" t="n">
-        <v>20.12753619346246</v>
+        <v>20.08844695743183</v>
       </c>
       <c r="K2" t="n">
-        <v>20.12407856012734</v>
+        <v>20.08448158991218</v>
       </c>
       <c r="L2" t="n">
-        <v>20.10184587463559</v>
+        <v>20.06271956768493</v>
       </c>
       <c r="M2" t="n">
-        <v>19.96740671245317</v>
+        <v>19.9286210590144</v>
       </c>
       <c r="N2" t="n">
-        <v>20.11311470559641</v>
+        <v>20.07417696042669</v>
       </c>
       <c r="O2" t="n">
-        <v>26.97311295903594</v>
+        <v>26.88439380623476</v>
       </c>
       <c r="P2" t="n">
-        <v>20.15077443244606</v>
+        <v>20.1120441424736</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.11121666580836</v>
+        <v>20.07228778208139</v>
       </c>
       <c r="R2" t="n">
-        <v>20.17300413257821</v>
+        <v>20.13423571905924</v>
       </c>
       <c r="S2" t="n">
-        <v>20.12448393665922</v>
+        <v>20.0852891531048</v>
       </c>
       <c r="T2" t="n">
-        <v>20.08627400577497</v>
+        <v>20.0459127409124</v>
       </c>
       <c r="U2" t="n">
-        <v>23.30951305538368</v>
+        <v>23.24895247627721</v>
       </c>
       <c r="V2" t="n">
-        <v>20.14397987422213</v>
+        <v>20.10502951172289</v>
       </c>
       <c r="W2" t="n">
-        <v>25.52781499216538</v>
+        <v>25.46461762964459</v>
       </c>
       <c r="X2" t="n">
-        <v>20.40069331427868</v>
+        <v>20.36277843422481</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.20111684595416</v>
+        <v>20.16178353415967</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.27098667388918</v>
+        <v>26.22326161812148</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.17317846099926</v>
+        <v>20.13416401037581</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.103648446481</v>
+        <v>20.06335830870971</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.92485107638846</v>
+        <v>19.88625686099381</v>
       </c>
       <c r="C3" t="n">
-        <v>10.23062097940476</v>
+        <v>10.18114553622518</v>
       </c>
       <c r="D3" t="n">
-        <v>19.55937845060992</v>
+        <v>19.5204085730237</v>
       </c>
       <c r="E3" t="n">
-        <v>19.43406444737418</v>
+        <v>19.39163833237121</v>
       </c>
       <c r="F3" t="n">
-        <v>19.61754365713843</v>
+        <v>19.57569482340647</v>
       </c>
       <c r="G3" t="n">
-        <v>19.80254206518141</v>
+        <v>19.76317161813717</v>
       </c>
       <c r="H3" t="n">
-        <v>19.9216672254037</v>
+        <v>19.88306667616139</v>
       </c>
       <c r="I3" t="n">
-        <v>20.1345207676473</v>
+        <v>20.07932453717982</v>
       </c>
       <c r="J3" t="n">
-        <v>19.83628509231758</v>
+        <v>19.79622943611928</v>
       </c>
       <c r="K3" t="n">
-        <v>19.81421545894507</v>
+        <v>19.77053878044764</v>
       </c>
       <c r="L3" t="n">
-        <v>19.65515283623006</v>
+        <v>19.61484693102237</v>
       </c>
       <c r="M3" t="n">
-        <v>19.5489957178068</v>
+        <v>19.51080507143106</v>
       </c>
       <c r="N3" t="n">
-        <v>19.73372646490234</v>
+        <v>19.69474766164626</v>
       </c>
       <c r="O3" t="n">
-        <v>31.46403697826472</v>
+        <v>31.3442876559348</v>
       </c>
       <c r="P3" t="n">
-        <v>19.99813134810374</v>
+        <v>19.96063948251193</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.7204475199598</v>
+        <v>19.68153445313519</v>
       </c>
       <c r="R3" t="n">
-        <v>20.16556782519468</v>
+        <v>20.12778813325059</v>
       </c>
       <c r="S3" t="n">
-        <v>19.81239212168318</v>
+        <v>19.77160299861103</v>
       </c>
       <c r="T3" t="n">
-        <v>19.54444427276684</v>
+        <v>19.49529240961365</v>
       </c>
       <c r="U3" t="n">
-        <v>25.13364597396172</v>
+        <v>25.05903819974214</v>
       </c>
       <c r="V3" t="n">
-        <v>19.95169855170038</v>
+        <v>19.91264653130648</v>
       </c>
       <c r="W3" t="n">
-        <v>29.23428940796623</v>
+        <v>29.15136592933198</v>
       </c>
       <c r="X3" t="n">
-        <v>21.78172160324462</v>
+        <v>21.75002297288738</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.36205739459425</v>
+        <v>20.32025184094968</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.87863678640456</v>
+        <v>29.82525043515111</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.16208990733605</v>
+        <v>20.12256374864246</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.68685051866811</v>
+        <v>19.63830809377089</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.58429204077099</v>
+        <v>11.44289712399332</v>
       </c>
       <c r="C4" t="n">
-        <v>11.73097287500941</v>
+        <v>10.58918319319856</v>
       </c>
       <c r="D4" t="n">
-        <v>11.9963952874195</v>
+        <v>10.85443419399721</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8233499603003</v>
+        <v>10.67590629879624</v>
       </c>
       <c r="F4" t="n">
-        <v>12.08832842806567</v>
+        <v>10.94182508242515</v>
       </c>
       <c r="G4" t="n">
-        <v>12.38754392666145</v>
+        <v>11.24491618602327</v>
       </c>
       <c r="H4" t="n">
-        <v>12.56547312723072</v>
+        <v>11.42411181123516</v>
       </c>
       <c r="I4" t="n">
-        <v>12.90528685002735</v>
+        <v>11.73770013080976</v>
       </c>
       <c r="J4" t="n">
-        <v>12.41123402042518</v>
+        <v>11.26753783161928</v>
       </c>
       <c r="K4" t="n">
-        <v>12.39998631981642</v>
+        <v>11.25055443777918</v>
       </c>
       <c r="L4" t="n">
-        <v>12.14885790964645</v>
+        <v>11.00474238569746</v>
       </c>
       <c r="M4" t="n">
-        <v>12.19668580817516</v>
+        <v>11.05589099775007</v>
       </c>
       <c r="N4" t="n">
-        <v>12.27614453926735</v>
+        <v>37.36408315653244</v>
       </c>
       <c r="O4" t="n">
-        <v>13.12496625410107</v>
+        <v>11.98586700452165</v>
       </c>
       <c r="P4" t="n">
-        <v>12.7015284783643</v>
+        <v>11.561886148361</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.25470530671996</v>
+        <v>11.11281976890162</v>
       </c>
       <c r="R4" t="n">
-        <v>12.95262316752425</v>
+        <v>11.8125502145257</v>
       </c>
       <c r="S4" t="n">
-        <v>12.40456523422655</v>
+        <v>11.25967623553753</v>
       </c>
       <c r="T4" t="n">
-        <v>11.97296648745215</v>
+        <v>10.81490154577959</v>
       </c>
       <c r="U4" t="n">
-        <v>12.31086370142803</v>
+        <v>11.18630445118015</v>
       </c>
       <c r="V4" t="n">
-        <v>12.44813760035646</v>
+        <v>11.3060110031223</v>
       </c>
       <c r="W4" t="n">
-        <v>13.437664267693</v>
+        <v>12.28762289654657</v>
       </c>
       <c r="X4" t="n">
-        <v>15.52447721702946</v>
+        <v>14.39404531716396</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.18863204260095</v>
+        <v>12.05948664119194</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.2400999252912</v>
+        <v>11.09828165848756</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.95459228723486</v>
+        <v>11.81174023195855</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.19990046625245</v>
+        <v>11.04288609324466</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.1610403357338</v>
+        <v>40.97590803429241</v>
       </c>
       <c r="C5" t="n">
-        <v>30.15279359574157</v>
+        <v>28.95218205400864</v>
       </c>
       <c r="D5" t="n">
-        <v>34.86761216079081</v>
+        <v>33.66317805119238</v>
       </c>
       <c r="E5" t="n">
-        <v>23.52832509140451</v>
+        <v>22.23103210918091</v>
       </c>
       <c r="F5" t="n">
-        <v>36.5335784732429</v>
+        <v>35.24418007635341</v>
       </c>
       <c r="G5" t="n">
-        <v>39.72105280341343</v>
+        <v>38.51553050986205</v>
       </c>
       <c r="H5" t="n">
-        <v>46.34032824014361</v>
+        <v>45.14150559818066</v>
       </c>
       <c r="I5" t="n">
-        <v>51.38754888085104</v>
+        <v>49.71186423820613</v>
       </c>
       <c r="J5" t="n">
-        <v>41.22800581198246</v>
+        <v>39.99853465259974</v>
       </c>
       <c r="K5" t="n">
-        <v>41.91640962727016</v>
+        <v>40.58690349938011</v>
       </c>
       <c r="L5" t="n">
-        <v>37.27432029170352</v>
+        <v>36.04486766517194</v>
       </c>
       <c r="M5" t="n">
-        <v>39.3101767622533</v>
+        <v>38.12411444298455</v>
       </c>
       <c r="N5" t="n">
-        <v>40.4332696986712</v>
+        <v>37.36408315653243</v>
       </c>
       <c r="O5" t="n">
-        <v>50.64658486155324</v>
+        <v>49.49661730634397</v>
       </c>
       <c r="P5" t="n">
-        <v>43.82220319752911</v>
+        <v>42.66546460243371</v>
       </c>
       <c r="Q5" t="n">
-        <v>38.32495785776455</v>
+        <v>37.12656081894842</v>
       </c>
       <c r="R5" t="n">
-        <v>52.81427574536642</v>
+        <v>51.64176572550528</v>
       </c>
       <c r="S5" t="n">
-        <v>39.55317315894764</v>
+        <v>38.31289218200111</v>
       </c>
       <c r="T5" t="n">
-        <v>34.38552253000692</v>
+        <v>32.89276732920383</v>
       </c>
       <c r="U5" t="n">
-        <v>40.54952601582366</v>
+        <v>39.3535209441478</v>
       </c>
       <c r="V5" t="n">
-        <v>43.35585153896787</v>
+        <v>42.16059716729511</v>
       </c>
       <c r="W5" t="n">
-        <v>58.30158012516374</v>
+        <v>56.96440636525377</v>
       </c>
       <c r="X5" t="n">
-        <v>93.70237845680245</v>
+        <v>92.69486763853506</v>
       </c>
       <c r="Y5" t="n">
-        <v>56.27879382372222</v>
+        <v>54.99645833452848</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.74788118864883</v>
+        <v>35.55779090642612</v>
       </c>
       <c r="AA5" t="n">
-        <v>50.40198972538246</v>
+        <v>49.18525622030166</v>
       </c>
       <c r="AB5" t="n">
-        <v>39.29783924211419</v>
+        <v>37.80683114908685</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.00875529727437</v>
+        <v>40.87757251836763</v>
       </c>
       <c r="C6" t="n">
-        <v>41.15543613151274</v>
+        <v>40.02385858757287</v>
       </c>
       <c r="D6" t="n">
-        <v>41.42085854392279</v>
+        <v>40.28910958837147</v>
       </c>
       <c r="E6" t="n">
-        <v>41.24781321680362</v>
+        <v>27.99117142138103</v>
       </c>
       <c r="F6" t="n">
-        <v>41.51279168456905</v>
+        <v>40.37650047679946</v>
       </c>
       <c r="G6" t="n">
-        <v>41.81200718316484</v>
+        <v>40.67959158039756</v>
       </c>
       <c r="H6" t="n">
-        <v>29.85220787451843</v>
+        <v>40.85878720560941</v>
       </c>
       <c r="I6" t="n">
-        <v>30.19202159731513</v>
+        <v>41.17237552518407</v>
       </c>
       <c r="J6" t="n">
-        <v>29.69796876771293</v>
+        <v>28.58280295420415</v>
       </c>
       <c r="K6" t="n">
-        <v>41.82444957631974</v>
+        <v>28.565819560364</v>
       </c>
       <c r="L6" t="n">
-        <v>41.5733211661498</v>
+        <v>40.43941778007176</v>
       </c>
       <c r="M6" t="n">
-        <v>41.62114906467854</v>
+        <v>40.49056639212438</v>
       </c>
       <c r="N6" t="n">
-        <v>29.56772266083343</v>
+        <v>37.36408315653243</v>
       </c>
       <c r="O6" t="n">
-        <v>42.22529370043683</v>
+        <v>29.30611534237287</v>
       </c>
       <c r="P6" t="n">
-        <v>41.80182749935044</v>
+        <v>40.66430711336487</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.67916856322334</v>
+        <v>40.54749516327591</v>
       </c>
       <c r="R6" t="n">
-        <v>30.23935791481199</v>
+        <v>41.24722560889998</v>
       </c>
       <c r="S6" t="n">
-        <v>29.69129998151431</v>
+        <v>40.69435162991189</v>
       </c>
       <c r="T6" t="n">
-        <v>41.3974297439555</v>
+        <v>28.13016666836446</v>
       </c>
       <c r="U6" t="n">
-        <v>41.8168641129231</v>
+        <v>40.68520866306813</v>
       </c>
       <c r="V6" t="n">
-        <v>29.73487234764422</v>
+        <v>28.62127612570715</v>
       </c>
       <c r="W6" t="n">
-        <v>42.53798503417605</v>
+        <v>41.39012825789108</v>
       </c>
       <c r="X6" t="n">
-        <v>32.81121196431724</v>
+        <v>31.70931043974881</v>
       </c>
       <c r="Y6" t="n">
-        <v>31.34067556908413</v>
+        <v>30.22247877044764</v>
       </c>
       <c r="Z6" t="n">
-        <v>29.52683467257896</v>
+        <v>28.41354678107242</v>
       </c>
       <c r="AA6" t="n">
-        <v>30.24132703452261</v>
+        <v>41.24641562633276</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.48962499085953</v>
+        <v>28.36126214696945</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.51861545147707</v>
+        <v>15.33100365586942</v>
       </c>
       <c r="C7" t="n">
-        <v>15.66529628571549</v>
+        <v>14.47728972507467</v>
       </c>
       <c r="D7" t="n">
-        <v>15.9307186981256</v>
+        <v>14.74254072587332</v>
       </c>
       <c r="E7" t="n">
-        <v>15.7576733710064</v>
+        <v>14.56401283067235</v>
       </c>
       <c r="F7" t="n">
-        <v>16.02265183877175</v>
+        <v>14.82993161430125</v>
       </c>
       <c r="G7" t="n">
-        <v>16.32186733736757</v>
+        <v>15.13302271789937</v>
       </c>
       <c r="H7" t="n">
-        <v>16.49979653793681</v>
+        <v>15.31221834311127</v>
       </c>
       <c r="I7" t="n">
-        <v>16.83961026073344</v>
+        <v>15.62580666268585</v>
       </c>
       <c r="J7" t="n">
-        <v>16.34555743113124</v>
+        <v>15.15564436349537</v>
       </c>
       <c r="K7" t="n">
-        <v>16.33430973052251</v>
+        <v>15.13866096965528</v>
       </c>
       <c r="L7" t="n">
-        <v>16.08318132035254</v>
+        <v>14.89284891757358</v>
       </c>
       <c r="M7" t="n">
-        <v>16.13100921888125</v>
+        <v>14.94399752962618</v>
       </c>
       <c r="N7" t="n">
-        <v>16.21046794997344</v>
+        <v>37.36408315653243</v>
       </c>
       <c r="O7" t="n">
-        <v>17.0592095341325</v>
+        <v>15.87389245816804</v>
       </c>
       <c r="P7" t="n">
-        <v>16.63577175839573</v>
+        <v>15.4499116020074</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.18902871742606</v>
+        <v>15.00092630077771</v>
       </c>
       <c r="R7" t="n">
-        <v>16.88694657823036</v>
+        <v>15.70065674640182</v>
       </c>
       <c r="S7" t="n">
-        <v>16.33888864493265</v>
+        <v>15.14778276741363</v>
       </c>
       <c r="T7" t="n">
-        <v>15.90728989815825</v>
+        <v>14.7030080776557</v>
       </c>
       <c r="U7" t="n">
-        <v>16.32545335754769</v>
+        <v>15.13769683205872</v>
       </c>
       <c r="V7" t="n">
-        <v>16.38246101106255</v>
+        <v>15.19411753499841</v>
       </c>
       <c r="W7" t="n">
-        <v>17.37198767839908</v>
+        <v>16.17572942842267</v>
       </c>
       <c r="X7" t="n">
-        <v>19.45880062773555</v>
+        <v>18.28215184904006</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.20449260829879</v>
+        <v>16.01182199058172</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.1744233359973</v>
+        <v>14.98638819036365</v>
       </c>
       <c r="AA7" t="n">
-        <v>16.88891569794095</v>
+        <v>15.69984676383466</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.13422387695853</v>
+        <v>14.93099262512077</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.31229030535089</v>
+        <v>27.11491860841153</v>
       </c>
       <c r="C8" t="n">
-        <v>37.79791354206709</v>
+        <v>36.53796982042312</v>
       </c>
       <c r="D8" t="n">
-        <v>38.06333595447717</v>
+        <v>36.80322082122179</v>
       </c>
       <c r="E8" t="n">
-        <v>32.38510877757626</v>
+        <v>31.15261863289415</v>
       </c>
       <c r="F8" t="n">
-        <v>29.42701308528265</v>
+        <v>28.21484646910748</v>
       </c>
       <c r="G8" t="n">
-        <v>40.59833165288466</v>
+        <v>39.32465701257566</v>
       </c>
       <c r="H8" t="n">
-        <v>38.63241379428841</v>
+        <v>37.37289843845974</v>
       </c>
       <c r="I8" t="n">
-        <v>38.97222751708502</v>
+        <v>37.68648675803431</v>
       </c>
       <c r="J8" t="n">
-        <v>38.47817468748285</v>
+        <v>37.21632445884386</v>
       </c>
       <c r="K8" t="n">
-        <v>38.46692698687411</v>
+        <v>37.19934106500374</v>
       </c>
       <c r="L8" t="n">
-        <v>38.21579857670413</v>
+        <v>36.95352901292205</v>
       </c>
       <c r="M8" t="n">
-        <v>38.2636264752325</v>
+        <v>37.00467762497443</v>
       </c>
       <c r="N8" t="n">
-        <v>30.32867517724991</v>
+        <v>37.36408315653243</v>
       </c>
       <c r="O8" t="n">
-        <v>33.37992635651296</v>
+        <v>32.15762567742929</v>
       </c>
       <c r="P8" t="n">
-        <v>32.4166199008347</v>
+        <v>31.19702285203886</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.95086541412616</v>
+        <v>24.76522234679071</v>
       </c>
       <c r="R8" t="n">
-        <v>39.01956383458194</v>
+        <v>37.76133684175029</v>
       </c>
       <c r="S8" t="n">
-        <v>38.47150590128423</v>
+        <v>37.20846286276211</v>
       </c>
       <c r="T8" t="n">
-        <v>38.03990715450986</v>
+        <v>36.76368817300418</v>
       </c>
       <c r="U8" t="n">
-        <v>33.41211890526804</v>
+        <v>32.18270004890822</v>
       </c>
       <c r="V8" t="n">
-        <v>35.68827156864291</v>
+        <v>34.44526604003086</v>
       </c>
       <c r="W8" t="n">
-        <v>39.50663683408509</v>
+        <v>38.23842920351902</v>
       </c>
       <c r="X8" t="n">
-        <v>30.16822193997105</v>
+        <v>28.9883338412082</v>
       </c>
       <c r="Y8" t="n">
-        <v>49.6153062820528</v>
+        <v>48.28931309586028</v>
       </c>
       <c r="Z8" t="n">
-        <v>27.77604702664394</v>
+        <v>26.57940695419627</v>
       </c>
       <c r="AA8" t="n">
-        <v>39.02153295429255</v>
+        <v>37.76052685918312</v>
       </c>
       <c r="AB8" t="n">
-        <v>49.06673100184901</v>
+        <v>47.726613242129</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.17264736941044</v>
+        <v>22.93789134715303</v>
       </c>
       <c r="C9" t="n">
-        <v>26.67454945264188</v>
+        <v>25.40199698639183</v>
       </c>
       <c r="D9" t="n">
-        <v>26.93997186505197</v>
+        <v>25.66724798719054</v>
       </c>
       <c r="E9" t="n">
-        <v>25.99255588279293</v>
+        <v>24.72298157683553</v>
       </c>
       <c r="F9" t="n">
-        <v>19.29720307240748</v>
+        <v>18.1061580456007</v>
       </c>
       <c r="G9" t="n">
-        <v>27.33112144478655</v>
+        <v>26.05773090026145</v>
       </c>
       <c r="H9" t="n">
-        <v>27.50904970486317</v>
+        <v>26.23692560442847</v>
       </c>
       <c r="I9" t="n">
-        <v>27.84886342765983</v>
+        <v>26.55051392400306</v>
       </c>
       <c r="J9" t="n">
-        <v>27.35481059805763</v>
+        <v>26.08035162481257</v>
       </c>
       <c r="K9" t="n">
-        <v>27.34356289744888</v>
+        <v>26.06336823097248</v>
       </c>
       <c r="L9" t="n">
-        <v>27.09243448727891</v>
+        <v>25.81755617889077</v>
       </c>
       <c r="M9" t="n">
-        <v>27.14026238580763</v>
+        <v>25.86870479094338</v>
       </c>
       <c r="N9" t="n">
-        <v>27.21972111689981</v>
+        <v>37.36408315653243</v>
       </c>
       <c r="O9" t="n">
-        <v>29.1804600125385</v>
+        <v>27.89820308519322</v>
       </c>
       <c r="P9" t="n">
-        <v>28.99884494179519</v>
+        <v>27.71334926161767</v>
       </c>
       <c r="Q9" t="n">
-        <v>27.19828282484519</v>
+        <v>25.92563448313982</v>
       </c>
       <c r="R9" t="n">
-        <v>27.89619974515671</v>
+        <v>26.625364007719</v>
       </c>
       <c r="S9" t="n">
-        <v>27.34814181185898</v>
+        <v>26.07249002873084</v>
       </c>
       <c r="T9" t="n">
-        <v>26.91654306508461</v>
+        <v>25.62771533897287</v>
       </c>
       <c r="U9" t="n">
-        <v>27.33597743405224</v>
+        <v>26.06334706188713</v>
       </c>
       <c r="V9" t="n">
-        <v>31.26356833085587</v>
+        <v>29.9475182033738</v>
       </c>
       <c r="W9" t="n">
-        <v>28.38124084532545</v>
+        <v>27.10043668973989</v>
       </c>
       <c r="X9" t="n">
-        <v>30.46805379466193</v>
+        <v>29.20685911035727</v>
       </c>
       <c r="Y9" t="n">
-        <v>28.21374577522518</v>
+        <v>26.93652925189892</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.16077682115472</v>
+        <v>23.91074564871487</v>
       </c>
       <c r="AA9" t="n">
-        <v>27.89816886486737</v>
+        <v>26.62455402515183</v>
       </c>
       <c r="AB9" t="n">
-        <v>27.14347704388491</v>
+        <v>25.85569988643796</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.8658660511986</v>
+        <v>21.17986406220293</v>
       </c>
       <c r="C2" t="n">
-        <v>15.8720672364772</v>
+        <v>15.45966271010025</v>
       </c>
       <c r="D2" t="n">
-        <v>21.54891142577356</v>
+        <v>21.14641137118383</v>
       </c>
       <c r="E2" t="n">
-        <v>21.52680098170051</v>
+        <v>21.05611701670566</v>
       </c>
       <c r="F2" t="n">
-        <v>21.55247104500332</v>
+        <v>21.12808187686736</v>
       </c>
       <c r="G2" t="n">
-        <v>22.83016934697828</v>
+        <v>22.04861579238794</v>
       </c>
       <c r="H2" t="n">
-        <v>21.46788369920588</v>
+        <v>21.04937509899803</v>
       </c>
       <c r="I2" t="n">
-        <v>21.55685010284311</v>
+        <v>21.11835751671493</v>
       </c>
       <c r="J2" t="n">
-        <v>22.16411379371768</v>
+        <v>21.58538298137212</v>
       </c>
       <c r="K2" t="n">
-        <v>21.61038606160146</v>
+        <v>21.18155692257758</v>
       </c>
       <c r="L2" t="n">
-        <v>21.76950751646368</v>
+        <v>21.14938432452638</v>
       </c>
       <c r="M2" t="n">
-        <v>22.8990296344275</v>
+        <v>22.33541402252422</v>
       </c>
       <c r="N2" t="n">
-        <v>21.60271505060779</v>
+        <v>21.18156281425597</v>
       </c>
       <c r="O2" t="n">
-        <v>28.88799144174506</v>
+        <v>28.27200599493827</v>
       </c>
       <c r="P2" t="n">
-        <v>21.83197914453168</v>
+        <v>21.43635466805076</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.61453804821398</v>
+        <v>21.17443826242437</v>
       </c>
       <c r="R2" t="n">
-        <v>21.52217305333399</v>
+        <v>21.07461840934283</v>
       </c>
       <c r="S2" t="n">
-        <v>21.77811322976772</v>
+        <v>21.26700009299384</v>
       </c>
       <c r="T2" t="n">
-        <v>21.54846449942716</v>
+        <v>21.09439080981455</v>
       </c>
       <c r="U2" t="n">
-        <v>25.29334275310734</v>
+        <v>24.60004480753317</v>
       </c>
       <c r="V2" t="n">
-        <v>21.55394467789288</v>
+        <v>21.12015481473067</v>
       </c>
       <c r="W2" t="n">
-        <v>27.30204507738477</v>
+        <v>26.7551905397697</v>
       </c>
       <c r="X2" t="n">
-        <v>21.75779700640535</v>
+        <v>21.26826216256243</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.72789167326932</v>
+        <v>21.34703538245024</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.17367928365539</v>
+        <v>27.53821687262025</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.68186346790735</v>
+        <v>21.19203583421028</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.54620165902156</v>
+        <v>22.36394522420247</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.61253208833651</v>
+        <v>21.34713390325739</v>
       </c>
       <c r="C3" t="n">
-        <v>11.29262173488422</v>
+        <v>11.04339164051727</v>
       </c>
       <c r="D3" t="n">
-        <v>21.36945873624386</v>
+        <v>21.11840465257362</v>
       </c>
       <c r="E3" t="n">
-        <v>21.19250978935565</v>
+        <v>20.45483127966252</v>
       </c>
       <c r="F3" t="n">
-        <v>21.39612133410284</v>
+        <v>20.98842006657905</v>
       </c>
       <c r="G3" t="n">
-        <v>30.4576234743024</v>
+        <v>27.51514813189534</v>
       </c>
       <c r="H3" t="n">
-        <v>20.79225729190679</v>
+        <v>20.42647739856483</v>
       </c>
       <c r="I3" t="n">
-        <v>21.42717937798028</v>
+        <v>20.91846631713499</v>
       </c>
       <c r="J3" t="n">
-        <v>25.73634773271088</v>
+        <v>24.2329425155995</v>
       </c>
       <c r="K3" t="n">
-        <v>21.80525446756696</v>
+        <v>21.36648361044672</v>
       </c>
       <c r="L3" t="n">
-        <v>22.93552838828025</v>
+        <v>21.13437720447408</v>
       </c>
       <c r="M3" t="n">
-        <v>31.78116836098243</v>
+        <v>30.37661926796127</v>
       </c>
       <c r="N3" t="n">
-        <v>21.75161463835134</v>
+        <v>21.36716818325452</v>
       </c>
       <c r="O3" t="n">
-        <v>33.87939028572717</v>
+        <v>33.14304211447074</v>
       </c>
       <c r="P3" t="n">
-        <v>23.37446350433027</v>
+        <v>23.17194843607973</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.83533410291756</v>
+        <v>21.3157296875086</v>
       </c>
       <c r="R3" t="n">
-        <v>21.17990484275162</v>
+        <v>20.6059322294137</v>
       </c>
       <c r="S3" t="n">
-        <v>22.98675367694979</v>
+        <v>21.9647664905942</v>
       </c>
       <c r="T3" t="n">
-        <v>21.36654351724481</v>
+        <v>20.7463370442813</v>
       </c>
       <c r="U3" t="n">
-        <v>29.4037457941931</v>
+        <v>27.7128780622788</v>
       </c>
       <c r="V3" t="n">
-        <v>21.39815004924734</v>
+        <v>20.92449164292898</v>
       </c>
       <c r="W3" t="n">
-        <v>31.83428484002878</v>
+        <v>31.2168555935874</v>
       </c>
       <c r="X3" t="n">
-        <v>22.86220103032507</v>
+        <v>21.98873333487736</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.64293627970807</v>
+        <v>22.54604645974194</v>
       </c>
       <c r="Z3" t="n">
-        <v>33.80064853857765</v>
+        <v>32.34688501247712</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.31492189696565</v>
+        <v>21.44037253053506</v>
       </c>
       <c r="AB3" t="n">
-        <v>28.50435380095216</v>
+        <v>29.79645454106085</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.88691907272324</v>
+        <v>13.24802113999765</v>
       </c>
       <c r="C4" t="n">
-        <v>13.85376560701113</v>
+        <v>11.45809034888348</v>
       </c>
       <c r="D4" t="n">
-        <v>15.30677077221619</v>
+        <v>12.87015760593855</v>
       </c>
       <c r="E4" t="n">
-        <v>15.05702313510416</v>
+        <v>11.85024133465236</v>
       </c>
       <c r="F4" t="n">
-        <v>15.34697830892202</v>
+        <v>12.66311753564996</v>
       </c>
       <c r="G4" t="n">
-        <v>29.77916839998707</v>
+        <v>23.0609715779778</v>
       </c>
       <c r="H4" t="n">
-        <v>14.39152532603843</v>
+        <v>11.77408827270942</v>
       </c>
       <c r="I4" t="n">
-        <v>15.39644178168849</v>
+        <v>12.55327641430158</v>
       </c>
       <c r="J4" t="n">
-        <v>22.22221792029828</v>
+        <v>17.79651701309741</v>
       </c>
       <c r="K4" t="n">
-        <v>16.00115506362209</v>
+        <v>13.26714277668339</v>
       </c>
       <c r="L4" t="n">
-        <v>17.79850509577642</v>
+        <v>12.90373848156873</v>
       </c>
       <c r="M4" t="n">
-        <v>32.00736436986598</v>
+        <v>27.74213057504567</v>
       </c>
       <c r="N4" t="n">
-        <v>15.91450746560898</v>
+        <v>68.29022042389396</v>
       </c>
       <c r="O4" t="n">
-        <v>16.14533397825919</v>
+        <v>13.43414315039703</v>
       </c>
       <c r="P4" t="n">
-        <v>18.50415087317319</v>
+        <v>16.14520052455688</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.04805366241862</v>
+        <v>13.18673423550756</v>
       </c>
       <c r="R4" t="n">
-        <v>15.00474855525212</v>
+        <v>12.05922307555038</v>
       </c>
       <c r="S4" t="n">
-        <v>17.89571058636916</v>
+        <v>14.23226269233542</v>
       </c>
       <c r="T4" t="n">
-        <v>15.30172253353721</v>
+        <v>12.28256143463208</v>
       </c>
       <c r="U4" t="n">
-        <v>18.77813533073433</v>
+        <v>14.42961528973319</v>
       </c>
       <c r="V4" t="n">
-        <v>15.14811498848564</v>
+        <v>12.36837088999778</v>
       </c>
       <c r="W4" t="n">
-        <v>17.30748899221759</v>
+        <v>14.60757789062221</v>
       </c>
       <c r="X4" t="n">
-        <v>17.6662294975667</v>
+        <v>14.24651834869341</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.10307226435421</v>
+        <v>14.97908218006846</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.42017275798127</v>
+        <v>14.29070965849937</v>
       </c>
       <c r="AA4" t="n">
-        <v>16.80852524907854</v>
+        <v>13.3855069041124</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.52453878901838</v>
+        <v>26.50740867627194</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>119.6390773268091</v>
+        <v>63.52813543357529</v>
       </c>
       <c r="C5" t="n">
-        <v>34.35334397914799</v>
+        <v>34.45380598558654</v>
       </c>
       <c r="D5" t="n">
-        <v>62.53934654154975</v>
+        <v>61.95854970630481</v>
       </c>
       <c r="E5" t="n">
-        <v>47.16927057427115</v>
+        <v>32.03039304989451</v>
       </c>
       <c r="F5" t="n">
-        <v>63.99890263717784</v>
+        <v>58.50764715438903</v>
       </c>
       <c r="G5" t="n">
-        <v>304.9057698503576</v>
+        <v>231.1010866236477</v>
       </c>
       <c r="H5" t="n">
-        <v>45.84433877754061</v>
+        <v>41.58202531216655</v>
       </c>
       <c r="I5" t="n">
-        <v>64.82541980234468</v>
+        <v>56.12461642612186</v>
       </c>
       <c r="J5" t="n">
-        <v>180.6374996445858</v>
+        <v>145.4324440877792</v>
       </c>
       <c r="K5" t="n">
-        <v>74.02704307456618</v>
+        <v>67.93162116767482</v>
       </c>
       <c r="L5" t="n">
-        <v>105.0169338035143</v>
+        <v>59.67616129145496</v>
       </c>
       <c r="M5" t="n">
-        <v>371.5409463179417</v>
+        <v>337.0225555538108</v>
       </c>
       <c r="N5" t="n">
-        <v>124.0776748683537</v>
+        <v>68.29022042389396</v>
       </c>
       <c r="O5" t="n">
-        <v>71.7956576569982</v>
+        <v>66.28397443391557</v>
       </c>
       <c r="P5" t="n">
-        <v>114.5061896374077</v>
+        <v>115.0977783572858</v>
       </c>
       <c r="Q5" t="n">
-        <v>75.16223046430352</v>
+        <v>66.44035617044078</v>
       </c>
       <c r="R5" t="n">
-        <v>57.54017124980134</v>
+        <v>46.57960811994215</v>
       </c>
       <c r="S5" t="n">
-        <v>101.185405261374</v>
+        <v>79.7679776536329</v>
       </c>
       <c r="T5" t="n">
-        <v>62.59656796050272</v>
+        <v>50.40660321088639</v>
       </c>
       <c r="U5" t="n">
-        <v>127.1666654717868</v>
+        <v>90.22627082477831</v>
       </c>
       <c r="V5" t="n">
-        <v>59.37712649426039</v>
+        <v>52.52027285752465</v>
       </c>
       <c r="W5" t="n">
-        <v>98.39343767440806</v>
+        <v>92.72072814182897</v>
       </c>
       <c r="X5" t="n">
-        <v>108.2170718622774</v>
+        <v>88.35722115248717</v>
       </c>
       <c r="Y5" t="n">
-        <v>98.58833151433967</v>
+        <v>102.4585750034777</v>
       </c>
       <c r="Z5" t="n">
-        <v>112.2717309121904</v>
+        <v>81.95125878331251</v>
       </c>
       <c r="AA5" t="n">
-        <v>89.03111704777098</v>
+        <v>69.6693272077445</v>
       </c>
       <c r="AB5" t="n">
-        <v>298.428575924898</v>
+        <v>348.2432103283355</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.53940129485029</v>
+        <v>31.88532745629383</v>
       </c>
       <c r="C6" t="n">
-        <v>32.46292690724358</v>
+        <v>30.09539666517957</v>
       </c>
       <c r="D6" t="n">
-        <v>47.95925299434329</v>
+        <v>31.50746392223466</v>
       </c>
       <c r="E6" t="n">
-        <v>47.70950535723122</v>
+        <v>44.25113857382328</v>
       </c>
       <c r="F6" t="n">
-        <v>47.99946053104915</v>
+        <v>31.30042385194601</v>
       </c>
       <c r="G6" t="n">
-        <v>48.38832970021945</v>
+        <v>55.46186881714863</v>
       </c>
       <c r="H6" t="n">
-        <v>47.04400754816548</v>
+        <v>30.41139458900556</v>
       </c>
       <c r="I6" t="n">
-        <v>34.0056030819209</v>
+        <v>31.19058273059772</v>
       </c>
       <c r="J6" t="n">
-        <v>40.83137922053069</v>
+        <v>36.43382332939354</v>
       </c>
       <c r="K6" t="n">
-        <v>34.61031636385452</v>
+        <v>45.66804001585426</v>
       </c>
       <c r="L6" t="n">
-        <v>50.45098731790346</v>
+        <v>45.30463572073962</v>
       </c>
       <c r="M6" t="n">
-        <v>64.65984659199293</v>
+        <v>46.37943689134181</v>
       </c>
       <c r="N6" t="n">
-        <v>34.53257646443893</v>
+        <v>68.29022042389396</v>
       </c>
       <c r="O6" t="n">
-        <v>34.76340297708949</v>
+        <v>45.49910838183719</v>
       </c>
       <c r="P6" t="n">
-        <v>50.83967133212351</v>
+        <v>48.21022065299724</v>
       </c>
       <c r="Q6" t="n">
-        <v>48.70053588454562</v>
+        <v>31.82404055180364</v>
       </c>
       <c r="R6" t="n">
-        <v>47.6572307773792</v>
+        <v>44.46012031472122</v>
       </c>
       <c r="S6" t="n">
-        <v>50.54819280849618</v>
+        <v>32.86956900863157</v>
       </c>
       <c r="T6" t="n">
-        <v>33.91088383376962</v>
+        <v>30.91986775092823</v>
       </c>
       <c r="U6" t="n">
-        <v>51.65598029116927</v>
+        <v>46.98772845363323</v>
       </c>
       <c r="V6" t="n">
-        <v>47.80059721061274</v>
+        <v>31.00567720629394</v>
       </c>
       <c r="W6" t="n">
-        <v>36.91742797084141</v>
+        <v>34.24362777582053</v>
       </c>
       <c r="X6" t="n">
-        <v>36.2753907977992</v>
+        <v>46.64741558786424</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.76939503902776</v>
+        <v>34.60777472778176</v>
       </c>
       <c r="Z6" t="n">
-        <v>37.02933405821369</v>
+        <v>46.69160689767028</v>
       </c>
       <c r="AA6" t="n">
-        <v>49.46100747120556</v>
+        <v>45.78640414328326</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.20282607638777</v>
+        <v>45.23277550547756</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.73542898784595</v>
+        <v>17.87779950861958</v>
       </c>
       <c r="C7" t="n">
-        <v>18.70227552213386</v>
+        <v>16.08786871750542</v>
       </c>
       <c r="D7" t="n">
-        <v>20.15528068733892</v>
+        <v>17.49993597456047</v>
       </c>
       <c r="E7" t="n">
-        <v>19.90553305022689</v>
+        <v>16.48001970327431</v>
       </c>
       <c r="F7" t="n">
-        <v>20.19548822404474</v>
+        <v>17.29289590427189</v>
       </c>
       <c r="G7" t="n">
-        <v>34.6276783151098</v>
+        <v>27.69074994659973</v>
       </c>
       <c r="H7" t="n">
-        <v>19.24003524116116</v>
+        <v>16.40386664133135</v>
       </c>
       <c r="I7" t="n">
-        <v>20.24495169681122</v>
+        <v>17.18305478292353</v>
       </c>
       <c r="J7" t="n">
-        <v>27.07072783542104</v>
+        <v>22.42629538171935</v>
       </c>
       <c r="K7" t="n">
-        <v>20.84966497874482</v>
+        <v>17.89692114530533</v>
       </c>
       <c r="L7" t="n">
-        <v>22.64701501089914</v>
+        <v>17.53351685019066</v>
       </c>
       <c r="M7" t="n">
-        <v>36.8558742849887</v>
+        <v>32.3719089436676</v>
       </c>
       <c r="N7" t="n">
-        <v>20.76301738073174</v>
+        <v>68.29022042389396</v>
       </c>
       <c r="O7" t="n">
-        <v>20.99375303637382</v>
+        <v>18.0638301904253</v>
       </c>
       <c r="P7" t="n">
-        <v>23.3525699312878</v>
+        <v>20.77488756458519</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.89656357754133</v>
+        <v>17.81651260412948</v>
       </c>
       <c r="R7" t="n">
-        <v>19.85325847037482</v>
+        <v>16.68900144417232</v>
       </c>
       <c r="S7" t="n">
-        <v>22.74422050149192</v>
+        <v>18.86204106095736</v>
       </c>
       <c r="T7" t="n">
-        <v>20.15023244865996</v>
+        <v>16.91233980325403</v>
       </c>
       <c r="U7" t="n">
-        <v>23.84705736279603</v>
+        <v>19.21277630991055</v>
       </c>
       <c r="V7" t="n">
-        <v>19.99662490360841</v>
+        <v>16.9981492586197</v>
       </c>
       <c r="W7" t="n">
-        <v>22.15599890734032</v>
+        <v>19.23735625924413</v>
       </c>
       <c r="X7" t="n">
-        <v>22.51473941268945</v>
+        <v>18.87629671731534</v>
       </c>
       <c r="Y7" t="n">
-        <v>22.17694491778501</v>
+        <v>19.76607647341963</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.26868267310402</v>
+        <v>18.92048802712133</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.65703516420123</v>
+        <v>18.01528527273436</v>
       </c>
       <c r="AB7" t="n">
-        <v>31.37304870414111</v>
+        <v>31.13718704489389</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36.95658637460298</v>
+        <v>30.96809808667582</v>
       </c>
       <c r="C8" t="n">
-        <v>43.94283565120848</v>
+        <v>40.89184867590747</v>
       </c>
       <c r="D8" t="n">
-        <v>45.39584081641352</v>
+        <v>42.30391593296248</v>
       </c>
       <c r="E8" t="n">
-        <v>38.74611576908713</v>
+        <v>35.04680985847732</v>
       </c>
       <c r="F8" t="n">
-        <v>35.2891280844077</v>
+        <v>32.20804914078884</v>
       </c>
       <c r="G8" t="n">
-        <v>62.36053990197773</v>
+        <v>54.92363804681196</v>
       </c>
       <c r="H8" t="n">
-        <v>44.48059537023573</v>
+        <v>41.20784659973337</v>
       </c>
       <c r="I8" t="n">
-        <v>45.48551182588582</v>
+        <v>41.98703474132559</v>
       </c>
       <c r="J8" t="n">
-        <v>52.31128796449562</v>
+        <v>47.23027534012135</v>
       </c>
       <c r="K8" t="n">
-        <v>46.09022510781942</v>
+        <v>42.70090110370734</v>
       </c>
       <c r="L8" t="n">
-        <v>47.88757513997372</v>
+        <v>42.3374968085927</v>
       </c>
       <c r="M8" t="n">
-        <v>62.09643441406308</v>
+        <v>57.17588890207073</v>
       </c>
       <c r="N8" t="n">
-        <v>36.68652958240705</v>
+        <v>68.29022042389396</v>
       </c>
       <c r="O8" t="n">
-        <v>39.47776176443575</v>
+        <v>36.28311882995141</v>
       </c>
       <c r="P8" t="n">
-        <v>41.20896136167094</v>
+        <v>38.38252276245375</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.75563399578515</v>
+        <v>28.60480543902406</v>
       </c>
       <c r="R8" t="n">
-        <v>45.09381859944943</v>
+        <v>41.49298140257436</v>
       </c>
       <c r="S8" t="n">
-        <v>47.98478063056646</v>
+        <v>43.6660210193594</v>
       </c>
       <c r="T8" t="n">
-        <v>45.39079257773452</v>
+        <v>41.71631976165605</v>
       </c>
       <c r="U8" t="n">
-        <v>43.22229185820256</v>
+        <v>38.3003980857514</v>
       </c>
       <c r="V8" t="n">
-        <v>41.94794702668231</v>
+        <v>38.59740495369309</v>
       </c>
       <c r="W8" t="n">
-        <v>47.39892119411459</v>
+        <v>44.04363829242482</v>
       </c>
       <c r="X8" t="n">
-        <v>34.47541197558913</v>
+        <v>30.73817172661736</v>
       </c>
       <c r="Y8" t="n">
-        <v>59.3616807452695</v>
+        <v>56.2117422967004</v>
       </c>
       <c r="Z8" t="n">
-        <v>36.26657348309945</v>
+        <v>31.79319895966314</v>
       </c>
       <c r="AA8" t="n">
-        <v>46.89759529327583</v>
+        <v>42.81926523113634</v>
       </c>
       <c r="AB8" t="n">
-        <v>69.16888004428759</v>
+        <v>68.17708668786992</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.62437044412467</v>
+        <v>29.77012705378517</v>
       </c>
       <c r="C9" t="n">
-        <v>36.73082908222297</v>
+        <v>32.74731383641242</v>
       </c>
       <c r="D9" t="n">
-        <v>38.18383424742802</v>
+        <v>34.15938109346747</v>
       </c>
       <c r="E9" t="n">
-        <v>36.74788486549659</v>
+        <v>32.03923271937193</v>
       </c>
       <c r="F9" t="n">
-        <v>26.37583355099578</v>
+        <v>22.96283532293332</v>
       </c>
       <c r="G9" t="n">
-        <v>52.65623156922734</v>
+        <v>44.3501940105111</v>
       </c>
       <c r="H9" t="n">
-        <v>37.26858880125025</v>
+        <v>33.06331176023832</v>
       </c>
       <c r="I9" t="n">
-        <v>38.27350525690031</v>
+        <v>33.84249990183052</v>
       </c>
       <c r="J9" t="n">
-        <v>45.09928139551015</v>
+        <v>39.08574050062632</v>
       </c>
       <c r="K9" t="n">
-        <v>38.87821853883392</v>
+        <v>34.55636626421231</v>
       </c>
       <c r="L9" t="n">
-        <v>40.67556857098822</v>
+        <v>34.19296196909765</v>
       </c>
       <c r="M9" t="n">
-        <v>54.88442784507781</v>
+        <v>49.0313540625746</v>
       </c>
       <c r="N9" t="n">
-        <v>38.7915709408208</v>
+        <v>68.29022042389396</v>
       </c>
       <c r="O9" t="n">
-        <v>40.72565776756151</v>
+        <v>36.3031817552418</v>
       </c>
       <c r="P9" t="n">
-        <v>43.45490462430325</v>
+        <v>39.35782204179382</v>
       </c>
       <c r="Q9" t="n">
-        <v>38.92511683165882</v>
+        <v>34.47595666804085</v>
       </c>
       <c r="R9" t="n">
-        <v>37.88181203046396</v>
+        <v>33.34844656307934</v>
       </c>
       <c r="S9" t="n">
-        <v>40.77277406158101</v>
+        <v>35.52148617986434</v>
       </c>
       <c r="T9" t="n">
-        <v>38.17878600874909</v>
+        <v>33.571784922161</v>
       </c>
       <c r="U9" t="n">
-        <v>41.88056154425405</v>
+        <v>35.87605470199135</v>
       </c>
       <c r="V9" t="n">
-        <v>43.95617513703877</v>
+        <v>39.15873986269717</v>
       </c>
       <c r="W9" t="n">
-        <v>40.18455246742941</v>
+        <v>35.89680137815112</v>
       </c>
       <c r="X9" t="n">
-        <v>40.54329297277856</v>
+        <v>35.53574183622231</v>
       </c>
       <c r="Y9" t="n">
-        <v>40.20549847787408</v>
+        <v>36.42552159232662</v>
       </c>
       <c r="Z9" t="n">
-        <v>38.19850704523802</v>
+        <v>32.70578473876964</v>
       </c>
       <c r="AA9" t="n">
-        <v>39.68558872429035</v>
+        <v>34.67473039164132</v>
       </c>
       <c r="AB9" t="n">
-        <v>49.40160226423025</v>
+        <v>47.79663216380088</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.96553262575681</v>
+        <v>20.72859578663366</v>
       </c>
       <c r="C2" t="n">
-        <v>15.33391338197379</v>
+        <v>15.08482395763467</v>
       </c>
       <c r="D2" t="n">
-        <v>20.87639829539784</v>
+        <v>20.63968307941956</v>
       </c>
       <c r="E2" t="n">
-        <v>20.86278265514302</v>
+        <v>20.62304214377377</v>
       </c>
       <c r="F2" t="n">
-        <v>20.86098806517368</v>
+        <v>20.62343616725611</v>
       </c>
       <c r="G2" t="n">
-        <v>21.94551191208976</v>
+        <v>21.42146262875745</v>
       </c>
       <c r="H2" t="n">
-        <v>20.8954791358323</v>
+        <v>20.65808349271166</v>
       </c>
       <c r="I2" t="n">
-        <v>20.9118074169798</v>
+        <v>20.66656332298849</v>
       </c>
       <c r="J2" t="n">
-        <v>21.24942202380111</v>
+        <v>20.92453320952728</v>
       </c>
       <c r="K2" t="n">
-        <v>20.95244717056439</v>
+        <v>20.70314746233186</v>
       </c>
       <c r="L2" t="n">
-        <v>20.98825223266123</v>
+        <v>20.68733455507442</v>
       </c>
       <c r="M2" t="n">
-        <v>20.88582966245729</v>
+        <v>20.63732924805135</v>
       </c>
       <c r="N2" t="n">
-        <v>20.93795189686084</v>
+        <v>20.70100266654153</v>
       </c>
       <c r="O2" t="n">
-        <v>27.94832277072403</v>
+        <v>27.6060258830174</v>
       </c>
       <c r="P2" t="n">
-        <v>21.07701890323517</v>
+        <v>20.84538239617545</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.97293783232718</v>
+        <v>20.73412912642117</v>
       </c>
       <c r="R2" t="n">
-        <v>20.90359964266711</v>
+        <v>20.66094311075175</v>
       </c>
       <c r="S2" t="n">
-        <v>20.92987548608455</v>
+        <v>20.68848705361428</v>
       </c>
       <c r="T2" t="n">
-        <v>20.87461593621381</v>
+        <v>20.62853133915198</v>
       </c>
       <c r="U2" t="n">
-        <v>24.23415387859041</v>
+        <v>23.94819596188228</v>
       </c>
       <c r="V2" t="n">
-        <v>20.92789392076021</v>
+        <v>20.68877264393211</v>
       </c>
       <c r="W2" t="n">
-        <v>26.48071450536201</v>
+        <v>26.2034425746285</v>
       </c>
       <c r="X2" t="n">
-        <v>21.12521771238208</v>
+        <v>20.87340572629732</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.35441687271306</v>
+        <v>21.14251850106937</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.1249473693385</v>
+        <v>26.87288955639909</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.93506617923351</v>
+        <v>20.68061905002543</v>
       </c>
       <c r="AB2" t="n">
-        <v>21.53974546365518</v>
+        <v>21.41725000709135</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.84160817669282</v>
+        <v>20.6567005837838</v>
       </c>
       <c r="C3" t="n">
-        <v>11.00481446985114</v>
+        <v>10.79770191833003</v>
       </c>
       <c r="D3" t="n">
-        <v>20.2123325678933</v>
+        <v>20.02899912797738</v>
       </c>
       <c r="E3" t="n">
-        <v>20.09748367311798</v>
+        <v>19.89256151878033</v>
       </c>
       <c r="F3" t="n">
-        <v>20.10285887585774</v>
+        <v>19.9135480554632</v>
       </c>
       <c r="G3" t="n">
-        <v>27.78467881630226</v>
+        <v>25.56580858005064</v>
       </c>
       <c r="H3" t="n">
-        <v>20.35053064674155</v>
+        <v>20.1622942144976</v>
       </c>
       <c r="I3" t="n">
-        <v>20.46560986784603</v>
+        <v>20.22119990379702</v>
       </c>
       <c r="J3" t="n">
-        <v>22.85562330233471</v>
+        <v>22.04758125777718</v>
       </c>
       <c r="K3" t="n">
-        <v>20.75470455998501</v>
+        <v>20.4820393926986</v>
       </c>
       <c r="L3" t="n">
-        <v>21.00564276119713</v>
+        <v>20.36660120583467</v>
       </c>
       <c r="M3" t="n">
-        <v>21.14233674970639</v>
+        <v>20.8704711449425</v>
       </c>
       <c r="N3" t="n">
-        <v>20.65018603491586</v>
+        <v>20.46516528997672</v>
       </c>
       <c r="O3" t="n">
-        <v>32.26789356795454</v>
+        <v>31.89137378036203</v>
       </c>
       <c r="P3" t="n">
-        <v>21.63299826024179</v>
+        <v>21.48575305085273</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.897452709471</v>
+        <v>20.69925042439755</v>
       </c>
       <c r="R3" t="n">
-        <v>20.40750090062373</v>
+        <v>20.18156919654641</v>
       </c>
       <c r="S3" t="n">
-        <v>20.5884742926289</v>
+        <v>20.37203004605989</v>
       </c>
       <c r="T3" t="n">
-        <v>20.19929848282209</v>
+        <v>19.94894585697099</v>
       </c>
       <c r="U3" t="n">
-        <v>26.27917928822697</v>
+        <v>25.90270655560754</v>
       </c>
       <c r="V3" t="n">
-        <v>20.57572736137037</v>
+        <v>20.37536808988717</v>
       </c>
       <c r="W3" t="n">
-        <v>30.46182400336556</v>
+        <v>30.16702491059381</v>
       </c>
       <c r="X3" t="n">
-        <v>21.98741089947929</v>
+        <v>21.69632696226968</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.62074405401856</v>
+        <v>23.61445643772175</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.9250141068894</v>
+        <v>30.6423210208509</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.62860835292756</v>
+        <v>20.31867627228659</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.95184567577583</v>
+        <v>25.57019906869325</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.17360921039976</v>
+        <v>12.34142214580649</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04819953244588</v>
+        <v>11.21253300069726</v>
       </c>
       <c r="D4" t="n">
-        <v>13.16679594517741</v>
+        <v>11.33711221595712</v>
       </c>
       <c r="E4" t="n">
-        <v>13.0130010249952</v>
+        <v>11.14914519262941</v>
       </c>
       <c r="F4" t="n">
-        <v>12.99273030573943</v>
+        <v>11.15359586912205</v>
       </c>
       <c r="G4" t="n">
-        <v>25.24292606227479</v>
+        <v>20.16767186208941</v>
       </c>
       <c r="H4" t="n">
-        <v>13.38232281550495</v>
+        <v>11.54495334869976</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5667582624463</v>
+        <v>11.64073693259115</v>
       </c>
       <c r="J4" t="n">
-        <v>17.34828621438638</v>
+        <v>14.52375908941649</v>
       </c>
       <c r="K4" t="n">
-        <v>14.02580297439447</v>
+        <v>12.05397161601011</v>
       </c>
       <c r="L4" t="n">
-        <v>14.43023762192045</v>
+        <v>11.87535755424061</v>
       </c>
       <c r="M4" t="n">
-        <v>14.860006519203</v>
+        <v>12.88859681632973</v>
       </c>
       <c r="N4" t="n">
-        <v>13.86207218975752</v>
+        <v>47.35781243703483</v>
       </c>
       <c r="O4" t="n">
-        <v>13.96677758316264</v>
+        <v>12.09783302902968</v>
       </c>
       <c r="P4" t="n">
-        <v>15.43289800073961</v>
+        <v>13.66058062507572</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.25725442517522</v>
+        <v>12.40392376416841</v>
       </c>
       <c r="R4" t="n">
-        <v>13.47404767582158</v>
+        <v>11.57725404995186</v>
       </c>
       <c r="S4" t="n">
-        <v>13.77084541470682</v>
+        <v>11.88837555542388</v>
       </c>
       <c r="T4" t="n">
-        <v>13.14666337826835</v>
+        <v>11.21114817958084</v>
       </c>
       <c r="U4" t="n">
-        <v>13.93953060077106</v>
+        <v>11.92831894186974</v>
       </c>
       <c r="V4" t="n">
-        <v>13.54350490495392</v>
+        <v>11.69422636482382</v>
       </c>
       <c r="W4" t="n">
-        <v>15.22783641299286</v>
+        <v>13.30655568464189</v>
       </c>
       <c r="X4" t="n">
-        <v>15.97732572260136</v>
+        <v>13.97711703017112</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.38932635847669</v>
+        <v>16.89023059213736</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.00141911956585</v>
+        <v>12.01792081514584</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.82947668166115</v>
+        <v>11.79950283542731</v>
       </c>
       <c r="AB4" t="n">
-        <v>20.63106579567434</v>
+        <v>20.06086874625916</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.89353042374765</v>
+        <v>50.07286420278697</v>
       </c>
       <c r="C5" t="n">
-        <v>35.96349435296941</v>
+        <v>34.0894969990155</v>
       </c>
       <c r="D5" t="n">
-        <v>37.65204751809797</v>
+        <v>35.8717275064336</v>
       </c>
       <c r="E5" t="n">
-        <v>25.77314294996473</v>
+        <v>23.38997182596083</v>
       </c>
       <c r="F5" t="n">
-        <v>34.83764667412247</v>
+        <v>32.88709717307597</v>
       </c>
       <c r="G5" t="n">
-        <v>221.1963686157744</v>
+        <v>169.8798270581533</v>
       </c>
       <c r="H5" t="n">
-        <v>42.50934285597623</v>
+        <v>40.56886094471616</v>
       </c>
       <c r="I5" t="n">
-        <v>45.01657546743557</v>
+        <v>41.42587262363742</v>
       </c>
       <c r="J5" t="n">
-        <v>102.2969726204854</v>
+        <v>85.28159671443368</v>
       </c>
       <c r="K5" t="n">
-        <v>52.64153833089509</v>
+        <v>48.59814196061659</v>
       </c>
       <c r="L5" t="n">
-        <v>57.40856437786884</v>
+        <v>44.10168575807327</v>
       </c>
       <c r="M5" t="n">
-        <v>67.9193099635189</v>
+        <v>63.76478840347349</v>
       </c>
       <c r="N5" t="n">
-        <v>51.94281208577719</v>
+        <v>47.35781243703483</v>
       </c>
       <c r="O5" t="n">
-        <v>48.42867090363636</v>
+        <v>46.03950464890355</v>
       </c>
       <c r="P5" t="n">
-        <v>71.94137315049866</v>
+        <v>71.09339415980506</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.92408641800679</v>
+        <v>52.76310103896795</v>
       </c>
       <c r="R5" t="n">
-        <v>43.62057093106039</v>
+        <v>40.55235349408754</v>
       </c>
       <c r="S5" t="n">
-        <v>45.47109391665848</v>
+        <v>42.8826638147365</v>
       </c>
       <c r="T5" t="n">
-        <v>37.13361072224911</v>
+        <v>33.40403990112248</v>
       </c>
       <c r="U5" t="n">
-        <v>52.19717981367644</v>
+        <v>46.69613207460696</v>
       </c>
       <c r="V5" t="n">
-        <v>45.59349526398938</v>
+        <v>43.41591734836197</v>
       </c>
       <c r="W5" t="n">
-        <v>72.79107421252144</v>
+        <v>69.37547665418393</v>
       </c>
       <c r="X5" t="n">
-        <v>86.96795969979028</v>
+        <v>82.16950144885226</v>
       </c>
       <c r="Y5" t="n">
-        <v>131.4757010950416</v>
+        <v>134.6153112881333</v>
       </c>
       <c r="Z5" t="n">
-        <v>48.74415332019771</v>
+        <v>44.59372077721391</v>
       </c>
       <c r="AA5" t="n">
-        <v>48.10827149362561</v>
+        <v>42.76212245320508</v>
       </c>
       <c r="AB5" t="n">
-        <v>180.3860888745767</v>
+        <v>202.5208652518698</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.44638295153297</v>
+        <v>42.24688106882514</v>
       </c>
       <c r="C6" t="n">
-        <v>43.08661583378739</v>
+        <v>41.11799192371586</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43956968631063</v>
+        <v>41.24257113897573</v>
       </c>
       <c r="E6" t="n">
-        <v>43.05141732633666</v>
+        <v>28.46402459620511</v>
       </c>
       <c r="F6" t="n">
-        <v>43.0311466070809</v>
+        <v>28.46847527269779</v>
       </c>
       <c r="G6" t="n">
-        <v>42.51569980340804</v>
+        <v>37.48255126566512</v>
       </c>
       <c r="H6" t="n">
-        <v>43.42073911684642</v>
+        <v>28.85983275227541</v>
       </c>
       <c r="I6" t="n">
-        <v>43.6051745637878</v>
+        <v>41.54619585560985</v>
       </c>
       <c r="J6" t="n">
-        <v>34.62105995551962</v>
+        <v>44.42921801243514</v>
       </c>
       <c r="K6" t="n">
-        <v>44.06421927573591</v>
+        <v>29.36885101958578</v>
       </c>
       <c r="L6" t="n">
-        <v>31.70301136305366</v>
+        <v>41.78081647725926</v>
       </c>
       <c r="M6" t="n">
-        <v>44.89842282054448</v>
+        <v>30.20347621990543</v>
       </c>
       <c r="N6" t="n">
-        <v>31.14162171021339</v>
+        <v>47.35781243703483</v>
       </c>
       <c r="O6" t="n">
-        <v>31.24632710361852</v>
+        <v>41.68668246630814</v>
       </c>
       <c r="P6" t="n">
-        <v>31.67686057868757</v>
+        <v>29.94916056543974</v>
       </c>
       <c r="Q6" t="n">
-        <v>44.29567072651672</v>
+        <v>29.71880316774408</v>
       </c>
       <c r="R6" t="n">
-        <v>43.51246397716307</v>
+        <v>41.4827129729705</v>
       </c>
       <c r="S6" t="n">
-        <v>31.04361915584006</v>
+        <v>29.20325495899952</v>
       </c>
       <c r="T6" t="n">
-        <v>30.41943711940156</v>
+        <v>28.52602758315655</v>
       </c>
       <c r="U6" t="n">
-        <v>31.3892136587901</v>
+        <v>41.96041689196507</v>
       </c>
       <c r="V6" t="n">
-        <v>43.58192120629541</v>
+        <v>29.00910576839952</v>
       </c>
       <c r="W6" t="n">
-        <v>33.4250393929869</v>
+        <v>31.54334792322917</v>
       </c>
       <c r="X6" t="n">
-        <v>33.25009946373459</v>
+        <v>43.88257595318976</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.61234678202102</v>
+        <v>35.10819792844828</v>
       </c>
       <c r="Z6" t="n">
-        <v>31.27419286069906</v>
+        <v>41.92337973816449</v>
       </c>
       <c r="AA6" t="n">
-        <v>43.86789298300269</v>
+        <v>29.114382239003</v>
       </c>
       <c r="AB6" t="n">
-        <v>37.9469189881869</v>
+        <v>37.42609751112312</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.39197373020184</v>
+        <v>16.45139123804044</v>
       </c>
       <c r="C7" t="n">
-        <v>17.26656405224798</v>
+        <v>15.3225020929312</v>
       </c>
       <c r="D7" t="n">
-        <v>17.3851604649795</v>
+        <v>15.44708130819107</v>
       </c>
       <c r="E7" t="n">
-        <v>17.23136554479729</v>
+        <v>15.25911428486334</v>
       </c>
       <c r="F7" t="n">
-        <v>17.21109482554153</v>
+        <v>15.26356496135602</v>
       </c>
       <c r="G7" t="n">
-        <v>29.4612905820768</v>
+        <v>24.27764095432334</v>
       </c>
       <c r="H7" t="n">
-        <v>17.60068733530705</v>
+        <v>15.65492244093371</v>
       </c>
       <c r="I7" t="n">
-        <v>17.7851227822484</v>
+        <v>15.75070602482509</v>
       </c>
       <c r="J7" t="n">
-        <v>21.56665073418846</v>
+        <v>18.63372818165043</v>
       </c>
       <c r="K7" t="n">
-        <v>18.24416749419657</v>
+        <v>16.16394070824404</v>
       </c>
       <c r="L7" t="n">
-        <v>18.64860214172255</v>
+        <v>15.98532664647455</v>
       </c>
       <c r="M7" t="n">
-        <v>19.07837103900508</v>
+        <v>16.99856590856367</v>
       </c>
       <c r="N7" t="n">
-        <v>18.0804367095596</v>
+        <v>47.35781243703483</v>
       </c>
       <c r="O7" t="n">
-        <v>18.1850591508278</v>
+        <v>16.20771838210057</v>
       </c>
       <c r="P7" t="n">
-        <v>19.65117956840475</v>
+        <v>17.77046597814663</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.47561894497733</v>
+        <v>16.51389285640235</v>
       </c>
       <c r="R7" t="n">
-        <v>17.69241219562368</v>
+        <v>15.68722314218581</v>
       </c>
       <c r="S7" t="n">
-        <v>17.98920993450894</v>
+        <v>15.99834464765782</v>
       </c>
       <c r="T7" t="n">
-        <v>17.36502789807045</v>
+        <v>15.32111727181477</v>
       </c>
       <c r="U7" t="n">
-        <v>18.33062604574125</v>
+        <v>16.16166052112781</v>
       </c>
       <c r="V7" t="n">
-        <v>17.76186942475604</v>
+        <v>15.80419545705776</v>
       </c>
       <c r="W7" t="n">
-        <v>19.44620093279494</v>
+        <v>17.41652477687583</v>
       </c>
       <c r="X7" t="n">
-        <v>20.19569024240347</v>
+        <v>18.08708612240507</v>
       </c>
       <c r="Y7" t="n">
-        <v>22.78460019516461</v>
+        <v>21.12683871144795</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.21978363936794</v>
+        <v>16.1278899073798</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.04784120146324</v>
+        <v>15.90947192766127</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.84943031547644</v>
+        <v>24.17083783849309</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.47622903593566</v>
+        <v>28.46829207988821</v>
       </c>
       <c r="C8" t="n">
-        <v>40.15093734695827</v>
+        <v>37.97191600465803</v>
       </c>
       <c r="D8" t="n">
-        <v>40.26953375968983</v>
+        <v>38.09649521991788</v>
       </c>
       <c r="E8" t="n">
-        <v>34.36499459379238</v>
+        <v>32.24702862624033</v>
       </c>
       <c r="F8" t="n">
-        <v>30.97788229039325</v>
+        <v>28.93688707477521</v>
       </c>
       <c r="G8" t="n">
-        <v>54.58513869807555</v>
+        <v>49.13177571552963</v>
       </c>
       <c r="H8" t="n">
-        <v>40.48506063001736</v>
+        <v>38.30433635266054</v>
       </c>
       <c r="I8" t="n">
-        <v>40.6694960769587</v>
+        <v>38.40011993655192</v>
       </c>
       <c r="J8" t="n">
-        <v>44.45102402889876</v>
+        <v>41.28314209337724</v>
       </c>
       <c r="K8" t="n">
-        <v>41.12854078890687</v>
+        <v>38.81335461997087</v>
       </c>
       <c r="L8" t="n">
-        <v>41.53297543643284</v>
+        <v>38.63474055820139</v>
       </c>
       <c r="M8" t="n">
-        <v>41.96274433371506</v>
+        <v>39.6479798202906</v>
       </c>
       <c r="N8" t="n">
-        <v>32.59291174260866</v>
+        <v>47.35781243703483</v>
       </c>
       <c r="O8" t="n">
-        <v>34.99828747065906</v>
+        <v>32.88020630500652</v>
       </c>
       <c r="P8" t="n">
-        <v>35.90045799718485</v>
+        <v>33.88775583806403</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.43740456503767</v>
+        <v>26.44126220455012</v>
       </c>
       <c r="R8" t="n">
-        <v>40.57678549033401</v>
+        <v>38.33663705391265</v>
       </c>
       <c r="S8" t="n">
-        <v>40.87358322921921</v>
+        <v>38.64775855938466</v>
       </c>
       <c r="T8" t="n">
-        <v>40.24940119278075</v>
+        <v>37.97053118354161</v>
       </c>
       <c r="U8" t="n">
-        <v>35.94461042457848</v>
+        <v>33.62228666196253</v>
       </c>
       <c r="V8" t="n">
-        <v>37.69090694705208</v>
+        <v>35.54486264894473</v>
       </c>
       <c r="W8" t="n">
-        <v>42.33269676083239</v>
+        <v>40.06802828284595</v>
       </c>
       <c r="X8" t="n">
-        <v>31.14732813673216</v>
+        <v>28.98894642100283</v>
       </c>
       <c r="Y8" t="n">
-        <v>56.40185542008776</v>
+        <v>54.34369873490068</v>
       </c>
       <c r="Z8" t="n">
-        <v>30.10342120861144</v>
+        <v>27.94728636014917</v>
       </c>
       <c r="AA8" t="n">
-        <v>40.93221449617358</v>
+        <v>38.5588858393881</v>
       </c>
       <c r="AB8" t="n">
-        <v>59.01542994148168</v>
+        <v>57.92680072870734</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.52038377629307</v>
+        <v>26.00388024473326</v>
       </c>
       <c r="C9" t="n">
-        <v>31.55486289331364</v>
+        <v>28.8212830415116</v>
       </c>
       <c r="D9" t="n">
-        <v>31.67345930604519</v>
+        <v>28.94586225677143</v>
       </c>
       <c r="E9" t="n">
-        <v>30.5595805913048</v>
+        <v>27.84710837329335</v>
       </c>
       <c r="F9" t="n">
-        <v>21.90971198621169</v>
+        <v>19.66506386261034</v>
       </c>
       <c r="G9" t="n">
-        <v>43.74959146609301</v>
+        <v>37.77642349338797</v>
       </c>
       <c r="H9" t="n">
-        <v>31.88898617637273</v>
+        <v>29.15370338951411</v>
       </c>
       <c r="I9" t="n">
-        <v>32.07342162331403</v>
+        <v>29.24948697340553</v>
       </c>
       <c r="J9" t="n">
-        <v>35.85494957525414</v>
+        <v>32.13250913023079</v>
       </c>
       <c r="K9" t="n">
-        <v>32.53246633526223</v>
+        <v>29.66272165682444</v>
       </c>
       <c r="L9" t="n">
-        <v>32.9369009827882</v>
+        <v>29.4841075950549</v>
       </c>
       <c r="M9" t="n">
-        <v>33.36666988007078</v>
+        <v>30.49734685714408</v>
       </c>
       <c r="N9" t="n">
-        <v>32.36873555062525</v>
+        <v>47.35781243703483</v>
       </c>
       <c r="O9" t="n">
-        <v>33.85202536376219</v>
+        <v>31.01438116973086</v>
       </c>
       <c r="P9" t="n">
-        <v>35.6179637957943</v>
+        <v>32.86155206855815</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.76391982899352</v>
+        <v>30.01267539546689</v>
       </c>
       <c r="R9" t="n">
-        <v>31.98071103668937</v>
+        <v>29.18600409076622</v>
       </c>
       <c r="S9" t="n">
-        <v>32.2775087755746</v>
+        <v>29.49712559623822</v>
       </c>
       <c r="T9" t="n">
-        <v>31.65332673913615</v>
+        <v>28.81989822039516</v>
       </c>
       <c r="U9" t="n">
-        <v>32.62310327852465</v>
+        <v>29.66370800976073</v>
       </c>
       <c r="V9" t="n">
-        <v>36.85059226979084</v>
+        <v>33.85691367689995</v>
       </c>
       <c r="W9" t="n">
-        <v>33.73449977386062</v>
+        <v>30.9153057254562</v>
       </c>
       <c r="X9" t="n">
-        <v>34.48398908346911</v>
+        <v>31.58586707098547</v>
       </c>
       <c r="Y9" t="n">
-        <v>37.07289903623029</v>
+        <v>34.62561966002838</v>
       </c>
       <c r="Z9" t="n">
-        <v>30.00004026004167</v>
+        <v>27.247408364537</v>
       </c>
       <c r="AA9" t="n">
-        <v>32.33614004252892</v>
+        <v>29.40825287624168</v>
       </c>
       <c r="AB9" t="n">
-        <v>39.13772915654212</v>
+        <v>37.66961878707347</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -798,7 +798,7 @@
         <v>29.73190512023366</v>
       </c>
       <c r="N4" t="n">
-        <v>72.74358057785906</v>
+        <v>13.56370058420747</v>
       </c>
       <c r="O4" t="n">
         <v>15.29391679713817</v>
@@ -974,7 +974,7 @@
         <v>64.5627982913705</v>
       </c>
       <c r="N6" t="n">
-        <v>72.74358057785906</v>
+        <v>33.56168172892661</v>
       </c>
       <c r="O6" t="n">
         <v>35.29190300955802</v>
@@ -1062,7 +1062,7 @@
         <v>34.87447354127217</v>
       </c>
       <c r="N7" t="n">
-        <v>72.74358057785906</v>
+        <v>18.70626900524597</v>
       </c>
       <c r="O7" t="n">
         <v>20.43638439411393</v>
@@ -1150,7 +1150,7 @@
         <v>61.74191094517046</v>
       </c>
       <c r="N8" t="n">
-        <v>72.74358057785906</v>
+        <v>35.68608558638438</v>
       </c>
       <c r="O8" t="n">
         <v>40.13350585460747</v>
@@ -1238,7 +1238,7 @@
         <v>55.17066825970108</v>
       </c>
       <c r="N9" t="n">
-        <v>72.74358057785906</v>
+        <v>39.0024637236749</v>
       </c>
       <c r="O9" t="n">
         <v>42.61795881128376</v>
@@ -1658,7 +1658,7 @@
         <v>11.37983543372416</v>
       </c>
       <c r="N4" t="n">
-        <v>40.02814120245156</v>
+        <v>11.30986691810858</v>
       </c>
       <c r="O4" t="n">
         <v>11.45298895905783</v>
@@ -1834,7 +1834,7 @@
         <v>28.69709590184966</v>
       </c>
       <c r="N6" t="n">
-        <v>40.02814120245156</v>
+        <v>28.63430769899086</v>
       </c>
       <c r="O6" t="n">
         <v>40.58150530047708</v>
@@ -1922,7 +1922,7 @@
         <v>15.31904769605126</v>
       </c>
       <c r="N7" t="n">
-        <v>40.02814120245156</v>
+        <v>15.24907918043565</v>
       </c>
       <c r="O7" t="n">
         <v>15.39211971486075</v>
@@ -2010,7 +2010,7 @@
         <v>37.50345182114064</v>
       </c>
       <c r="N8" t="n">
-        <v>40.02814120245156</v>
+        <v>29.4098006961697</v>
       </c>
       <c r="O8" t="n">
         <v>31.75790038713172</v>
@@ -2098,7 +2098,7 @@
         <v>26.33984359090505</v>
       </c>
       <c r="N9" t="n">
-        <v>40.02814120245156</v>
+        <v>26.26987507528947</v>
       </c>
       <c r="O9" t="n">
         <v>27.52423542705581</v>
@@ -2518,7 +2518,7 @@
         <v>28.33548558678973</v>
       </c>
       <c r="N4" t="n">
-        <v>63.85448785955532</v>
+        <v>13.14918635434016</v>
       </c>
       <c r="O4" t="n">
         <v>14.83205631368906</v>
@@ -2694,7 +2694,7 @@
         <v>60.84180926032272</v>
       </c>
       <c r="N6" t="n">
-        <v>63.85448785955532</v>
+        <v>31.82204508302336</v>
       </c>
       <c r="O6" t="n">
         <v>33.50512565122019</v>
@@ -2782,7 +2782,7 @@
         <v>33.08617273254426</v>
       </c>
       <c r="N7" t="n">
-        <v>63.85448785955532</v>
+        <v>17.89987350009472</v>
       </c>
       <c r="O7" t="n">
         <v>19.58265024435001</v>
@@ -2870,7 +2870,7 @@
         <v>58.1445304428037</v>
       </c>
       <c r="N8" t="n">
-        <v>63.85448785955532</v>
+        <v>33.75432120886236</v>
       </c>
       <c r="O8" t="n">
         <v>37.96650555323327</v>
@@ -2958,7 +2958,7 @@
         <v>50.03540646845077</v>
       </c>
       <c r="N9" t="n">
-        <v>63.85448785955532</v>
+        <v>34.84910723600117</v>
       </c>
       <c r="O9" t="n">
         <v>38.1438580590398</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.3360950709973</v>
+        <v>21.33609507099736</v>
       </c>
       <c r="C2" t="n">
-        <v>15.55223279818342</v>
+        <v>15.55223279818347</v>
       </c>
       <c r="D2" t="n">
-        <v>21.42175058188124</v>
+        <v>21.42175058188122</v>
       </c>
       <c r="E2" t="n">
-        <v>21.14101675082064</v>
+        <v>21.14101675082071</v>
       </c>
       <c r="F2" t="n">
-        <v>21.39682412409619</v>
+        <v>21.39682412409626</v>
       </c>
       <c r="G2" t="n">
-        <v>22.12621821145224</v>
+        <v>22.12621821145231</v>
       </c>
       <c r="H2" t="n">
-        <v>21.13345837525369</v>
+        <v>21.13345837525373</v>
       </c>
       <c r="I2" t="n">
-        <v>21.31021303450622</v>
+        <v>21.31021303450628</v>
       </c>
       <c r="J2" t="n">
-        <v>21.70744169158717</v>
+        <v>21.70744169158724</v>
       </c>
       <c r="K2" t="n">
-        <v>21.33340980969796</v>
+        <v>21.33340980969799</v>
       </c>
       <c r="L2" t="n">
-        <v>21.21454925439262</v>
+        <v>21.21454925439267</v>
       </c>
       <c r="M2" t="n">
-        <v>22.28641842928135</v>
+        <v>22.28641842928136</v>
       </c>
       <c r="N2" t="n">
-        <v>21.21884014275861</v>
+        <v>21.21884014275859</v>
       </c>
       <c r="O2" t="n">
-        <v>28.5603809835827</v>
+        <v>28.56038098358269</v>
       </c>
       <c r="P2" t="n">
-        <v>21.6366766520728</v>
+        <v>21.63667665207281</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.24788701599093</v>
+        <v>21.24788701599098</v>
       </c>
       <c r="R2" t="n">
-        <v>21.13964843235922</v>
+        <v>21.13964843235928</v>
       </c>
       <c r="S2" t="n">
-        <v>21.43239223172093</v>
+        <v>21.43239223172102</v>
       </c>
       <c r="T2" t="n">
         <v>21.21038909680097</v>
       </c>
       <c r="U2" t="n">
-        <v>24.6449424605214</v>
+        <v>24.64494246052146</v>
       </c>
       <c r="V2" t="n">
-        <v>21.29778444850789</v>
+        <v>21.29778444850796</v>
       </c>
       <c r="W2" t="n">
         <v>26.890481728739</v>
       </c>
       <c r="X2" t="n">
-        <v>21.41797695775215</v>
+        <v>21.41797695775226</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.72067012070698</v>
+        <v>21.72067012070701</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.68810117945237</v>
+        <v>27.68810117945246</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.26733066110872</v>
+        <v>21.26733066110878</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.56380468586739</v>
+        <v>22.5638046858674</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.8447580548202</v>
+        <v>21.84475805482018</v>
       </c>
       <c r="C3" t="n">
         <v>11.09560653823011</v>
       </c>
       <c r="D3" t="n">
-        <v>22.46980118154184</v>
+        <v>22.46980118154181</v>
       </c>
       <c r="E3" t="n">
         <v>20.44397394798668</v>
       </c>
       <c r="F3" t="n">
-        <v>22.29232706736931</v>
+        <v>22.29232706736928</v>
       </c>
       <c r="G3" t="n">
         <v>27.46236938210271</v>
       </c>
       <c r="H3" t="n">
-        <v>20.40910130031831</v>
+        <v>20.40910130031829</v>
       </c>
       <c r="I3" t="n">
-        <v>21.67338814101014</v>
+        <v>21.67338814101012</v>
       </c>
       <c r="J3" t="n">
-        <v>24.49520937466491</v>
+        <v>24.49520937466487</v>
       </c>
       <c r="K3" t="n">
-        <v>21.83167303274645</v>
+        <v>21.83167303274642</v>
       </c>
       <c r="L3" t="n">
-        <v>20.98319426346161</v>
+        <v>20.98319426346157</v>
       </c>
       <c r="M3" t="n">
-        <v>29.46667963863117</v>
+        <v>29.46667963863116</v>
       </c>
       <c r="N3" t="n">
-        <v>21.0160766440052</v>
+        <v>21.01607664400517</v>
       </c>
       <c r="O3" t="n">
-        <v>33.9778944988623</v>
+        <v>33.97789449886231</v>
       </c>
       <c r="P3" t="n">
         <v>23.98073496660665</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.22334512879061</v>
+        <v>21.22334512879059</v>
       </c>
       <c r="R3" t="n">
-        <v>20.45231722605226</v>
+        <v>20.45231722605227</v>
       </c>
       <c r="S3" t="n">
-        <v>22.53074146626113</v>
+        <v>22.53074146626115</v>
       </c>
       <c r="T3" t="n">
-        <v>20.95789421160695</v>
+        <v>20.95789421160693</v>
       </c>
       <c r="U3" t="n">
-        <v>27.21585425092029</v>
+        <v>27.21585425092031</v>
       </c>
       <c r="V3" t="n">
-        <v>21.57187302043591</v>
+        <v>21.5718730204359</v>
       </c>
       <c r="W3" t="n">
-        <v>31.3247375778726</v>
+        <v>31.32473757787255</v>
       </c>
       <c r="X3" t="n">
-        <v>22.44084540194358</v>
+        <v>22.44084540194357</v>
       </c>
       <c r="Y3" t="n">
         <v>24.59614278008321</v>
       </c>
       <c r="Z3" t="n">
-        <v>32.63632761214298</v>
+        <v>32.63632761214301</v>
       </c>
       <c r="AA3" t="n">
         <v>21.36111727583307</v>
       </c>
       <c r="AB3" t="n">
-        <v>30.60966652241988</v>
+        <v>30.60966652241986</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.96864294414201</v>
+        <v>13.96864294414199</v>
       </c>
       <c r="C4" t="n">
-        <v>11.47367002566163</v>
+        <v>11.4736700256616</v>
       </c>
       <c r="D4" t="n">
-        <v>14.93616134305689</v>
+        <v>14.93616134305687</v>
       </c>
       <c r="E4" t="n">
-        <v>11.76514357728577</v>
+        <v>11.76514357728575</v>
       </c>
       <c r="F4" t="n">
-        <v>14.65460553563854</v>
+        <v>14.65460553563852</v>
       </c>
       <c r="G4" t="n">
-        <v>22.8934472901829</v>
+        <v>22.89344729018288</v>
       </c>
       <c r="H4" t="n">
-        <v>11.67976824823218</v>
+        <v>11.67976824823217</v>
       </c>
       <c r="I4" t="n">
-        <v>13.67629343565026</v>
+        <v>13.67629343565023</v>
       </c>
       <c r="J4" t="n">
-        <v>18.13155349727787</v>
+        <v>18.13155349727785</v>
       </c>
       <c r="K4" t="n">
-        <v>13.93831168248426</v>
+        <v>13.93831168248425</v>
       </c>
       <c r="L4" t="n">
-        <v>12.59572703175403</v>
+        <v>12.59572703175396</v>
       </c>
       <c r="M4" t="n">
-        <v>26.17077179612263</v>
+        <v>26.17077179612262</v>
       </c>
       <c r="N4" t="n">
-        <v>52.33776005304261</v>
+        <v>12.64419458975321</v>
       </c>
       <c r="O4" t="n">
-        <v>14.40624999660991</v>
+        <v>14.40624999660987</v>
       </c>
       <c r="P4" t="n">
         <v>17.36385017674809</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.97229238513493</v>
+        <v>12.97229238513491</v>
       </c>
       <c r="R4" t="n">
-        <v>11.74968779080617</v>
+        <v>11.74968779080615</v>
       </c>
       <c r="S4" t="n">
-        <v>15.05636367339801</v>
+        <v>15.05636367339809</v>
       </c>
       <c r="T4" t="n">
-        <v>12.54873613798877</v>
+        <v>12.54873613798875</v>
       </c>
       <c r="U4" t="n">
-        <v>13.49596531714742</v>
+        <v>13.49596531714747</v>
       </c>
       <c r="V4" t="n">
-        <v>13.3334669197036</v>
+        <v>13.33346691970359</v>
       </c>
       <c r="W4" t="n">
-        <v>14.59541629448628</v>
+        <v>14.59541629448627</v>
       </c>
       <c r="X4" t="n">
-        <v>14.89353652256732</v>
+        <v>14.89353652256728</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.17390922031513</v>
+        <v>18.17390922031512</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.61044024826204</v>
+        <v>14.61044024826201</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.1919173012591</v>
+        <v>13.19191730125906</v>
       </c>
       <c r="AB4" t="n">
-        <v>27.71163124104373</v>
+        <v>27.71163124104368</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.52743831288481</v>
+        <v>71.52743831288466</v>
       </c>
       <c r="C5" t="n">
         <v>32.73255227166933</v>
       </c>
       <c r="D5" t="n">
-        <v>95.74729557622459</v>
+        <v>95.74729557622445</v>
       </c>
       <c r="E5" t="n">
-        <v>28.14979335285626</v>
+        <v>28.14979335285621</v>
       </c>
       <c r="F5" t="n">
-        <v>90.98893198737133</v>
+        <v>90.98893198737119</v>
       </c>
       <c r="G5" t="n">
-        <v>218.21636925584</v>
+        <v>218.2163692558403</v>
       </c>
       <c r="H5" t="n">
-        <v>36.52329597917397</v>
+        <v>36.52329597917418</v>
       </c>
       <c r="I5" t="n">
-        <v>73.27581654550892</v>
+        <v>73.27581654550889</v>
       </c>
       <c r="J5" t="n">
-        <v>145.7514119764388</v>
+        <v>145.7514119764385</v>
       </c>
       <c r="K5" t="n">
-        <v>74.14169353460855</v>
+        <v>74.14169353460844</v>
       </c>
       <c r="L5" t="n">
-        <v>50.31033004962366</v>
+        <v>50.31033004962315</v>
       </c>
       <c r="M5" t="n">
-        <v>309.0750229888308</v>
+        <v>309.0750229888297</v>
       </c>
       <c r="N5" t="n">
-        <v>52.33776005304261</v>
+        <v>52.33776005304276</v>
       </c>
       <c r="O5" t="n">
-        <v>76.97564100837621</v>
+        <v>76.9756410083763</v>
       </c>
       <c r="P5" t="n">
-        <v>126.7635865956607</v>
+        <v>126.7635865956609</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.11972415555019</v>
+        <v>58.11972415555009</v>
       </c>
       <c r="R5" t="n">
-        <v>37.2609811666741</v>
+        <v>37.26098116667409</v>
       </c>
       <c r="S5" t="n">
-        <v>90.09487483002141</v>
+        <v>90.09487483002047</v>
       </c>
       <c r="T5" t="n">
-        <v>51.7548468974518</v>
+        <v>51.7548468974517</v>
       </c>
       <c r="U5" t="n">
-        <v>67.75570303477566</v>
+        <v>67.75570303477835</v>
       </c>
       <c r="V5" t="n">
-        <v>63.95107790098589</v>
+        <v>63.95107790098623</v>
       </c>
       <c r="W5" t="n">
-        <v>86.24815289759127</v>
+        <v>86.24815289759084</v>
       </c>
       <c r="X5" t="n">
-        <v>93.94491443004907</v>
+        <v>93.94491443004941</v>
       </c>
       <c r="Y5" t="n">
-        <v>151.8053676215576</v>
+        <v>151.8053676215575</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.12715154918479</v>
+        <v>80.12715154918456</v>
       </c>
       <c r="AA5" t="n">
-        <v>61.48690410415687</v>
+        <v>61.48690410415675</v>
       </c>
       <c r="AB5" t="n">
-        <v>351.0560267289542</v>
+        <v>351.0560267289533</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.23303261436206</v>
+        <v>44.23303261436202</v>
       </c>
       <c r="C6" t="n">
-        <v>28.88799468993229</v>
+        <v>28.88799468993228</v>
       </c>
       <c r="D6" t="n">
-        <v>45.20055101327683</v>
+        <v>45.2005510132768</v>
       </c>
       <c r="E6" t="n">
-        <v>42.02953324750575</v>
+        <v>42.02953324750572</v>
       </c>
       <c r="F6" t="n">
-        <v>32.06893019990923</v>
+        <v>32.0689301999092</v>
       </c>
       <c r="G6" t="n">
         <v>40.30777195445356</v>
       </c>
       <c r="H6" t="n">
-        <v>29.09409291250282</v>
+        <v>29.09409291250281</v>
       </c>
       <c r="I6" t="n">
         <v>31.09061809992097</v>
       </c>
       <c r="J6" t="n">
-        <v>48.39594316749783</v>
+        <v>48.39594316749779</v>
       </c>
       <c r="K6" t="n">
-        <v>44.20270135270425</v>
+        <v>44.20270135270421</v>
       </c>
       <c r="L6" t="n">
-        <v>42.86011670197406</v>
+        <v>42.86011670197402</v>
       </c>
       <c r="M6" t="n">
-        <v>43.58509646039332</v>
+        <v>43.5850964603933</v>
       </c>
       <c r="N6" t="n">
-        <v>52.33776005304261</v>
+        <v>30.06935819243503</v>
       </c>
       <c r="O6" t="n">
-        <v>44.3514804038119</v>
+        <v>44.35148040381185</v>
       </c>
       <c r="P6" t="n">
-        <v>47.30917494593844</v>
+        <v>47.30917494593841</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.23668205535493</v>
+        <v>43.23668205535489</v>
       </c>
       <c r="R6" t="n">
-        <v>29.16401245507686</v>
+        <v>29.16401245507685</v>
       </c>
       <c r="S6" t="n">
         <v>45.32075334361812</v>
       </c>
       <c r="T6" t="n">
-        <v>29.96306080225943</v>
+        <v>29.96306080225941</v>
       </c>
       <c r="U6" t="n">
-        <v>31.04897580497879</v>
+        <v>31.04897580497886</v>
       </c>
       <c r="V6" t="n">
         <v>43.59785658992364</v>
       </c>
       <c r="W6" t="n">
-        <v>44.540606653</v>
+        <v>44.54060665299995</v>
       </c>
       <c r="X6" t="n">
         <v>32.30786118683805</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.51230668195686</v>
+        <v>36.51230668195692</v>
       </c>
       <c r="Z6" t="n">
-        <v>44.87482991848205</v>
+        <v>44.874829918482</v>
       </c>
       <c r="AA6" t="n">
-        <v>43.45630697147916</v>
+        <v>43.45630697147912</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.21512480229501</v>
+        <v>45.21512480229499</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.32856253262682</v>
+        <v>18.3285625326268</v>
       </c>
       <c r="C7" t="n">
-        <v>15.83358961414644</v>
+        <v>15.83358961414643</v>
       </c>
       <c r="D7" t="n">
-        <v>19.29608093154172</v>
+        <v>19.2960809315417</v>
       </c>
       <c r="E7" t="n">
-        <v>16.12506316577059</v>
+        <v>16.12506316577057</v>
       </c>
       <c r="F7" t="n">
         <v>19.01452512412335</v>
       </c>
       <c r="G7" t="n">
-        <v>27.25336687866775</v>
+        <v>27.25336687866771</v>
       </c>
       <c r="H7" t="n">
         <v>16.03968783671701</v>
       </c>
       <c r="I7" t="n">
-        <v>18.03621302413509</v>
+        <v>18.03621302413506</v>
       </c>
       <c r="J7" t="n">
-        <v>22.4914730857627</v>
+        <v>22.49147308576267</v>
       </c>
       <c r="K7" t="n">
-        <v>18.2982312709691</v>
+        <v>18.29823127096908</v>
       </c>
       <c r="L7" t="n">
-        <v>16.95564662023884</v>
+        <v>16.95564662023881</v>
       </c>
       <c r="M7" t="n">
-        <v>30.53069138460747</v>
+        <v>30.53069138460746</v>
       </c>
       <c r="N7" t="n">
-        <v>52.33776005304261</v>
+        <v>17.00411417823802</v>
       </c>
       <c r="O7" t="n">
-        <v>18.76608278765158</v>
+        <v>18.76608278765156</v>
       </c>
       <c r="P7" t="n">
-        <v>21.72368296778978</v>
+        <v>21.72368296778976</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.33221197361976</v>
+        <v>17.33221197361974</v>
       </c>
       <c r="R7" t="n">
-        <v>16.10960737929099</v>
+        <v>16.10960737929098</v>
       </c>
       <c r="S7" t="n">
-        <v>19.41628326188296</v>
+        <v>19.41628326188295</v>
       </c>
       <c r="T7" t="n">
-        <v>16.90865572647359</v>
+        <v>16.90865572647357</v>
       </c>
       <c r="U7" t="n">
-        <v>17.99097362492504</v>
+        <v>17.99097362492522</v>
       </c>
       <c r="V7" t="n">
-        <v>17.69338650818845</v>
+        <v>17.69338650818844</v>
       </c>
       <c r="W7" t="n">
-        <v>18.95533588297111</v>
+        <v>18.95533588297108</v>
       </c>
       <c r="X7" t="n">
-        <v>19.25345611105214</v>
+        <v>19.25345611105211</v>
       </c>
       <c r="Y7" t="n">
         <v>22.67251463236067</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.97035983674688</v>
+        <v>18.97035983674683</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.55183688974393</v>
+        <v>17.55183688974391</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.07155082952855</v>
+        <v>32.07155082952852</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.57085374690755</v>
+        <v>30.57085374690757</v>
       </c>
       <c r="C8" t="n">
-        <v>39.05628883503585</v>
+        <v>39.05628883503586</v>
       </c>
       <c r="D8" t="n">
-        <v>42.51878015243113</v>
+        <v>42.51878015243115</v>
       </c>
       <c r="E8" t="n">
-        <v>33.50101902477384</v>
+        <v>33.50101902477381</v>
       </c>
       <c r="F8" t="n">
-        <v>32.96743557517704</v>
+        <v>32.96743557517703</v>
       </c>
       <c r="G8" t="n">
-        <v>52.75292523048873</v>
+        <v>52.75292523048871</v>
       </c>
       <c r="H8" t="n">
-        <v>39.2623870576064</v>
+        <v>39.26238705760643</v>
       </c>
       <c r="I8" t="n">
-        <v>41.2589122450245</v>
+        <v>41.25891224502448</v>
       </c>
       <c r="J8" t="n">
         <v>45.7141723066521</v>
       </c>
       <c r="K8" t="n">
-        <v>41.52093049185849</v>
+        <v>41.52093049185851</v>
       </c>
       <c r="L8" t="n">
-        <v>40.17834584112827</v>
+        <v>40.17834584112832</v>
       </c>
       <c r="M8" t="n">
-        <v>53.75339060549847</v>
+        <v>53.75339060549843</v>
       </c>
       <c r="N8" t="n">
-        <v>52.33776005304261</v>
+        <v>31.71516021194316</v>
       </c>
       <c r="O8" t="n">
-        <v>35.81629182046147</v>
+        <v>35.81629182046146</v>
       </c>
       <c r="P8" t="n">
-        <v>38.20052790352678</v>
+        <v>38.20052790352675</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.41660239883745</v>
+        <v>27.41660239883743</v>
       </c>
       <c r="R8" t="n">
-        <v>39.33230660018042</v>
+        <v>39.3323066001804</v>
       </c>
       <c r="S8" t="n">
-        <v>42.63898248277229</v>
+        <v>42.63898248277235</v>
       </c>
       <c r="T8" t="n">
-        <v>40.13135494736305</v>
+        <v>40.13135494736301</v>
       </c>
       <c r="U8" t="n">
-        <v>35.85515895472302</v>
+        <v>35.855158954723</v>
       </c>
       <c r="V8" t="n">
-        <v>37.91197413340575</v>
+        <v>37.91197413340582</v>
       </c>
       <c r="W8" t="n">
-        <v>42.18019306936233</v>
+        <v>42.18019306936232</v>
       </c>
       <c r="X8" t="n">
         <v>30.34422274890862</v>
       </c>
       <c r="Y8" t="n">
-        <v>56.80812978848885</v>
+        <v>56.80812978848879</v>
       </c>
       <c r="Z8" t="n">
-        <v>31.00868433489646</v>
+        <v>31.0086843348965</v>
       </c>
       <c r="AA8" t="n">
-        <v>40.77453611063338</v>
+        <v>40.77453611063336</v>
       </c>
       <c r="AB8" t="n">
-        <v>66.76420438076096</v>
+        <v>66.76420438076087</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.59555782567092</v>
+        <v>28.5955578256709</v>
       </c>
       <c r="C9" t="n">
-        <v>30.33356893450381</v>
+        <v>30.33356893450379</v>
       </c>
       <c r="D9" t="n">
         <v>33.79606025189911</v>
       </c>
       <c r="E9" t="n">
-        <v>29.64808665629445</v>
+        <v>29.64808665629443</v>
       </c>
       <c r="F9" t="n">
-        <v>23.75632161939517</v>
+        <v>23.75632161939516</v>
       </c>
       <c r="G9" t="n">
-        <v>41.75334570194538</v>
+        <v>41.75334570194534</v>
       </c>
       <c r="H9" t="n">
-        <v>30.53966715707441</v>
+        <v>30.53966715707439</v>
       </c>
       <c r="I9" t="n">
-        <v>32.53619234449249</v>
+        <v>32.53619234449246</v>
       </c>
       <c r="J9" t="n">
-        <v>36.99145240612006</v>
+        <v>36.99145240612005</v>
       </c>
       <c r="K9" t="n">
-        <v>32.79821059132649</v>
+        <v>32.79821059132646</v>
       </c>
       <c r="L9" t="n">
-        <v>31.45562594059625</v>
+        <v>31.45562594059618</v>
       </c>
       <c r="M9" t="n">
-        <v>45.03067070496488</v>
+        <v>45.03067070496481</v>
       </c>
       <c r="N9" t="n">
-        <v>52.33776005304261</v>
+        <v>31.50409349859544</v>
       </c>
       <c r="O9" t="n">
-        <v>34.66895360767809</v>
+        <v>34.66895360767813</v>
       </c>
       <c r="P9" t="n">
-        <v>37.93163985057682</v>
+        <v>37.9316398505768</v>
       </c>
       <c r="Q9" t="n">
-        <v>31.83219079689741</v>
+        <v>31.83219079689742</v>
       </c>
       <c r="R9" t="n">
-        <v>30.60958669964837</v>
+        <v>30.60958669964836</v>
       </c>
       <c r="S9" t="n">
-        <v>33.91626258224032</v>
+        <v>33.91626258224031</v>
       </c>
       <c r="T9" t="n">
-        <v>31.40863504683095</v>
+        <v>31.40863504683096</v>
       </c>
       <c r="U9" t="n">
-        <v>32.49455004955033</v>
+        <v>32.49455004955054</v>
       </c>
       <c r="V9" t="n">
         <v>37.0781339967843</v>
       </c>
       <c r="W9" t="n">
-        <v>33.45531520332852</v>
+        <v>33.45531520332851</v>
       </c>
       <c r="X9" t="n">
         <v>33.75343543140953</v>
       </c>
       <c r="Y9" t="n">
-        <v>37.17249395271803</v>
+        <v>37.17249395271802</v>
       </c>
       <c r="Z9" t="n">
-        <v>30.91822600287583</v>
+        <v>30.91822600287581</v>
       </c>
       <c r="AA9" t="n">
-        <v>32.05181621010129</v>
+        <v>32.0518162101013</v>
       </c>
       <c r="AB9" t="n">
-        <v>46.57153014988594</v>
+        <v>46.57153014988589</v>
       </c>
     </row>
   </sheetData>
@@ -4026,40 +4026,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.23829510997019</v>
+        <v>21.23829510997018</v>
       </c>
       <c r="C2" t="n">
         <v>15.47808159778802</v>
       </c>
       <c r="D2" t="n">
-        <v>21.25313015755231</v>
+        <v>21.25313015755233</v>
       </c>
       <c r="E2" t="n">
-        <v>21.02502466050255</v>
+        <v>21.02502466050257</v>
       </c>
       <c r="F2" t="n">
-        <v>21.35932724260797</v>
+        <v>21.35932724260799</v>
       </c>
       <c r="G2" t="n">
         <v>21.90269744997049</v>
       </c>
       <c r="H2" t="n">
-        <v>21.05376993795934</v>
+        <v>21.05376993795937</v>
       </c>
       <c r="I2" t="n">
-        <v>21.25149617590348</v>
+        <v>21.25149617590349</v>
       </c>
       <c r="J2" t="n">
         <v>21.54944000266875</v>
       </c>
       <c r="K2" t="n">
-        <v>21.26817692425584</v>
+        <v>21.26817692425586</v>
       </c>
       <c r="L2" t="n">
-        <v>21.12787856039612</v>
+        <v>21.12787856039614</v>
       </c>
       <c r="M2" t="n">
-        <v>21.98772064489631</v>
+        <v>21.9877206448963</v>
       </c>
       <c r="N2" t="n">
         <v>21.10383974669217</v>
@@ -4068,31 +4068,31 @@
         <v>28.30224690253777</v>
       </c>
       <c r="P2" t="n">
-        <v>21.49518165177023</v>
+        <v>21.49518165177025</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.13965394921093</v>
+        <v>21.13965394921095</v>
       </c>
       <c r="R2" t="n">
         <v>21.14056468594357</v>
       </c>
       <c r="S2" t="n">
-        <v>21.32555071233411</v>
+        <v>21.32555071233414</v>
       </c>
       <c r="T2" t="n">
         <v>21.1497448916943</v>
       </c>
       <c r="U2" t="n">
-        <v>24.48485797527076</v>
+        <v>24.48485797527074</v>
       </c>
       <c r="V2" t="n">
-        <v>21.29130253094257</v>
+        <v>21.29130253094259</v>
       </c>
       <c r="W2" t="n">
-        <v>26.78390378063456</v>
+        <v>26.78390378063457</v>
       </c>
       <c r="X2" t="n">
-        <v>21.34896114092979</v>
+        <v>21.34896114092981</v>
       </c>
       <c r="Y2" t="n">
         <v>21.93352070877837</v>
@@ -4101,7 +4101,7 @@
         <v>27.54459291073911</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.19761790545708</v>
+        <v>21.1976179054571</v>
       </c>
       <c r="AB2" t="n">
         <v>22.33666321198844</v>
@@ -4114,16 +4114,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.73946656269293</v>
+        <v>21.73946656269292</v>
       </c>
       <c r="C3" t="n">
-        <v>11.15912448155789</v>
+        <v>11.15912448155788</v>
       </c>
       <c r="D3" t="n">
-        <v>21.85688122982894</v>
+        <v>21.85688122982891</v>
       </c>
       <c r="E3" t="n">
-        <v>20.21241692373562</v>
+        <v>20.21241692373559</v>
       </c>
       <c r="F3" t="n">
         <v>22.61872317509645</v>
@@ -4132,31 +4132,31 @@
         <v>26.45541433474635</v>
       </c>
       <c r="H3" t="n">
-        <v>20.43499659533942</v>
+        <v>20.4349965953394</v>
       </c>
       <c r="I3" t="n">
-        <v>21.84833607746113</v>
+        <v>21.84833607746111</v>
       </c>
       <c r="J3" t="n">
-        <v>23.95839581579283</v>
+        <v>23.95839581579281</v>
       </c>
       <c r="K3" t="n">
-        <v>21.95955099207384</v>
+        <v>21.95955099207383</v>
       </c>
       <c r="L3" t="n">
-        <v>20.95877741578019</v>
+        <v>20.95877741578017</v>
       </c>
       <c r="M3" t="n">
-        <v>27.91631022850988</v>
+        <v>27.91631022850987</v>
       </c>
       <c r="N3" t="n">
-        <v>20.78942559004687</v>
+        <v>20.78942559004685</v>
       </c>
       <c r="O3" t="n">
-        <v>33.22406351158173</v>
+        <v>33.2240635115817</v>
       </c>
       <c r="P3" t="n">
-        <v>23.56166992331954</v>
+        <v>23.56166992331953</v>
       </c>
       <c r="Q3" t="n">
         <v>21.04427312816806</v>
@@ -4165,34 +4165,34 @@
         <v>21.05608828963251</v>
       </c>
       <c r="S3" t="n">
-        <v>22.36158970796643</v>
+        <v>22.36158970796644</v>
       </c>
       <c r="T3" t="n">
-        <v>21.12003501820378</v>
+        <v>21.12003501820381</v>
       </c>
       <c r="U3" t="n">
-        <v>26.71884437947478</v>
+        <v>26.7188443794748</v>
       </c>
       <c r="V3" t="n">
-        <v>22.11544569487337</v>
+        <v>22.11544569487341</v>
       </c>
       <c r="W3" t="n">
-        <v>31.22516759439238</v>
+        <v>31.22516759439241</v>
       </c>
       <c r="X3" t="n">
-        <v>22.53934946990528</v>
+        <v>22.53934946990527</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.71559231988147</v>
+        <v>26.71559231988141</v>
       </c>
       <c r="Z3" t="n">
-        <v>32.2892302008452</v>
+        <v>32.28923020084516</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.45809062201337</v>
+        <v>21.45809062201334</v>
       </c>
       <c r="AB3" t="n">
-        <v>29.57626529515477</v>
+        <v>29.57626529515476</v>
       </c>
     </row>
     <row r="4">
@@ -4202,64 +4202,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.89151974900022</v>
+        <v>13.89151974900026</v>
       </c>
       <c r="C4" t="n">
-        <v>11.66166068185268</v>
+        <v>11.66166068185271</v>
       </c>
       <c r="D4" t="n">
-        <v>14.05908843589933</v>
+        <v>14.05908843589934</v>
       </c>
       <c r="E4" t="n">
-        <v>11.48253191300952</v>
+        <v>11.48253191300954</v>
       </c>
       <c r="F4" t="n">
-        <v>15.25863336467593</v>
+        <v>15.25863336467599</v>
       </c>
       <c r="G4" t="n">
-        <v>21.39624981948045</v>
+        <v>21.39624981948041</v>
       </c>
       <c r="H4" t="n">
-        <v>11.8072230453648</v>
+        <v>11.80722304536481</v>
       </c>
       <c r="I4" t="n">
-        <v>14.04063186150722</v>
+        <v>14.04063186150724</v>
       </c>
       <c r="J4" t="n">
-        <v>17.37558864743366</v>
+        <v>17.37558864743364</v>
       </c>
       <c r="K4" t="n">
-        <v>14.22904858767048</v>
+        <v>14.2290485876705</v>
       </c>
       <c r="L4" t="n">
-        <v>12.64431402743895</v>
+        <v>12.64431402743898</v>
       </c>
       <c r="M4" t="n">
-        <v>23.8429373268967</v>
+        <v>23.84293732689669</v>
       </c>
       <c r="N4" t="n">
-        <v>47.34142200342082</v>
+        <v>12.37278456825199</v>
       </c>
       <c r="O4" t="n">
-        <v>13.5285021462519</v>
+        <v>13.52850214625191</v>
       </c>
       <c r="P4" t="n">
-        <v>16.79317141227942</v>
+        <v>16.79317141227944</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.77732246104866</v>
+        <v>12.77732246104867</v>
       </c>
       <c r="R4" t="n">
-        <v>12.78760965140342</v>
+        <v>12.78760965140343</v>
       </c>
       <c r="S4" t="n">
-        <v>14.87711191726103</v>
+        <v>14.87711191726104</v>
       </c>
       <c r="T4" t="n">
-        <v>12.89130429846113</v>
+        <v>12.89130429846115</v>
       </c>
       <c r="U4" t="n">
-        <v>12.84213417031816</v>
+        <v>12.84213417031819</v>
       </c>
       <c r="V4" t="n">
         <v>14.29571410235012</v>
@@ -4268,19 +4268,19 @@
         <v>14.55641013206945</v>
       </c>
       <c r="X4" t="n">
-        <v>15.14154347757842</v>
+        <v>15.14154347757841</v>
       </c>
       <c r="Y4" t="n">
-        <v>21.62776669521114</v>
+        <v>21.62776669521115</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.19170641746297</v>
+        <v>14.19170641746299</v>
       </c>
       <c r="AA4" t="n">
         <v>13.4320520115862</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.18644000072867</v>
+        <v>26.18644000072872</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69.24145398805237</v>
+        <v>69.24145398805246</v>
       </c>
       <c r="C5" t="n">
-        <v>35.92278751806452</v>
+        <v>35.92278751806449</v>
       </c>
       <c r="D5" t="n">
-        <v>78.1835226206901</v>
+        <v>78.18352262068947</v>
       </c>
       <c r="E5" t="n">
         <v>24.08081665046787</v>
       </c>
       <c r="F5" t="n">
-        <v>101.4247046835429</v>
+        <v>101.4247046835427</v>
       </c>
       <c r="G5" t="n">
-        <v>188.540091880209</v>
+        <v>188.5400918802081</v>
       </c>
       <c r="H5" t="n">
-        <v>38.85264388979208</v>
+        <v>38.85264388979205</v>
       </c>
       <c r="I5" t="n">
-        <v>79.47221575919822</v>
+        <v>79.47221575919818</v>
       </c>
       <c r="J5" t="n">
-        <v>130.4760077109177</v>
+        <v>130.4760077109172</v>
       </c>
       <c r="K5" t="n">
-        <v>78.74365130755565</v>
+        <v>78.74365130755562</v>
       </c>
       <c r="L5" t="n">
-        <v>50.99631904871281</v>
+        <v>50.99631904871275</v>
       </c>
       <c r="M5" t="n">
-        <v>255.931109559756</v>
+        <v>255.9311095597559</v>
       </c>
       <c r="N5" t="n">
-        <v>47.34142200342082</v>
+        <v>47.34142200342075</v>
       </c>
       <c r="O5" t="n">
-        <v>63.1184370747827</v>
+        <v>63.11843707478229</v>
       </c>
       <c r="P5" t="n">
-        <v>114.753329661809</v>
+        <v>114.7533296618081</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.10238225171535</v>
+        <v>54.10238225171527</v>
       </c>
       <c r="R5" t="n">
-        <v>57.03878977850526</v>
+        <v>57.03878977850512</v>
       </c>
       <c r="S5" t="n">
-        <v>86.34967831589513</v>
+        <v>86.34967831589506</v>
       </c>
       <c r="T5" t="n">
-        <v>58.0577071382409</v>
+        <v>58.05770713824083</v>
       </c>
       <c r="U5" t="n">
-        <v>55.87092410769711</v>
+        <v>55.87092410769705</v>
       </c>
       <c r="V5" t="n">
-        <v>78.42533012353385</v>
+        <v>78.42533012353401</v>
       </c>
       <c r="W5" t="n">
-        <v>85.51585918656947</v>
+        <v>85.51585918656956</v>
       </c>
       <c r="X5" t="n">
-        <v>96.56037958550316</v>
+        <v>96.56037958550255</v>
       </c>
       <c r="Y5" t="n">
-        <v>215.5258175779015</v>
+        <v>215.5258175779009</v>
       </c>
       <c r="Z5" t="n">
-        <v>71.5759636013802</v>
+        <v>71.57596360138017</v>
       </c>
       <c r="AA5" t="n">
-        <v>65.74757254057691</v>
+        <v>65.74757254057683</v>
       </c>
       <c r="AB5" t="n">
-        <v>316.9378905098605</v>
+        <v>316.9378905098603</v>
       </c>
     </row>
     <row r="6">
@@ -4384,79 +4384,79 @@
         <v>29.11156584415504</v>
       </c>
       <c r="D6" t="n">
-        <v>44.27160211848631</v>
+        <v>44.27160211848633</v>
       </c>
       <c r="E6" t="n">
-        <v>41.69504559559649</v>
+        <v>41.69504559559651</v>
       </c>
       <c r="F6" t="n">
-        <v>32.70853852697834</v>
+        <v>32.70853852697832</v>
       </c>
       <c r="G6" t="n">
-        <v>38.84615498178286</v>
+        <v>38.84615498178276</v>
       </c>
       <c r="H6" t="n">
-        <v>42.01973672795168</v>
+        <v>42.01973672795178</v>
       </c>
       <c r="I6" t="n">
-        <v>31.49053702380965</v>
+        <v>31.49053702380963</v>
       </c>
       <c r="J6" t="n">
-        <v>47.58810233002056</v>
+        <v>47.58810233002058</v>
       </c>
       <c r="K6" t="n">
-        <v>44.44156227025741</v>
+        <v>44.44156227025746</v>
       </c>
       <c r="L6" t="n">
-        <v>30.0942191897414</v>
+        <v>30.09421918974137</v>
       </c>
       <c r="M6" t="n">
-        <v>41.29284248919907</v>
+        <v>41.29284248919909</v>
       </c>
       <c r="N6" t="n">
-        <v>47.34142200342082</v>
+        <v>29.83805111455157</v>
       </c>
       <c r="O6" t="n">
-        <v>30.99401210025023</v>
+        <v>30.99401210025018</v>
       </c>
       <c r="P6" t="n">
-        <v>46.68824301191672</v>
+        <v>46.68824301191673</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.9898361436356</v>
+        <v>42.98983614363563</v>
       </c>
       <c r="R6" t="n">
-        <v>43.00012333399035</v>
+        <v>43.00012333399039</v>
       </c>
       <c r="S6" t="n">
-        <v>32.3270170795634</v>
+        <v>32.32701707956338</v>
       </c>
       <c r="T6" t="n">
-        <v>43.10381798104808</v>
+        <v>43.10381798104805</v>
       </c>
       <c r="U6" t="n">
-        <v>43.171293864809</v>
+        <v>43.17129386480907</v>
       </c>
       <c r="V6" t="n">
-        <v>31.74561926465254</v>
+        <v>31.74561926465248</v>
       </c>
       <c r="W6" t="n">
-        <v>32.94265027313767</v>
+        <v>32.94265027313766</v>
       </c>
       <c r="X6" t="n">
         <v>32.5914486398808</v>
       </c>
       <c r="Y6" t="n">
-        <v>39.98994988757526</v>
+        <v>39.98994988757519</v>
       </c>
       <c r="Z6" t="n">
-        <v>31.64161157976534</v>
+        <v>31.64161157976533</v>
       </c>
       <c r="AA6" t="n">
-        <v>43.64456569417309</v>
+        <v>43.64456569417308</v>
       </c>
       <c r="AB6" t="n">
-        <v>43.71864229025135</v>
+        <v>43.71864229025144</v>
       </c>
     </row>
     <row r="7">
@@ -4472,79 +4472,79 @@
         <v>15.97404512115478</v>
       </c>
       <c r="D7" t="n">
-        <v>18.37147287520144</v>
+        <v>18.37147287520142</v>
       </c>
       <c r="E7" t="n">
-        <v>15.79491635231162</v>
+        <v>15.79491635231163</v>
       </c>
       <c r="F7" t="n">
-        <v>19.57101780397805</v>
+        <v>19.57101780397807</v>
       </c>
       <c r="G7" t="n">
-        <v>25.70863425878257</v>
+        <v>25.70863425878251</v>
       </c>
       <c r="H7" t="n">
-        <v>16.11960748466691</v>
+        <v>16.11960748466689</v>
       </c>
       <c r="I7" t="n">
-        <v>18.35301630080931</v>
+        <v>18.35301630080932</v>
       </c>
       <c r="J7" t="n">
-        <v>21.68797308673576</v>
+        <v>21.68797308673572</v>
       </c>
       <c r="K7" t="n">
-        <v>18.54143302697261</v>
+        <v>18.5414330269726</v>
       </c>
       <c r="L7" t="n">
         <v>16.95669846674106</v>
       </c>
       <c r="M7" t="n">
-        <v>28.15532176619881</v>
+        <v>28.15532176619879</v>
       </c>
       <c r="N7" t="n">
-        <v>47.34142200342082</v>
+        <v>16.68516900755409</v>
       </c>
       <c r="O7" t="n">
-        <v>17.84079935614364</v>
+        <v>17.84079935614363</v>
       </c>
       <c r="P7" t="n">
-        <v>21.10546862217114</v>
+        <v>21.10546862217111</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.08970690035079</v>
+        <v>17.08970690035078</v>
       </c>
       <c r="R7" t="n">
-        <v>17.09999409070554</v>
+        <v>17.09999409070551</v>
       </c>
       <c r="S7" t="n">
-        <v>19.18949635656313</v>
+        <v>19.18949635656311</v>
       </c>
       <c r="T7" t="n">
-        <v>17.20368873776323</v>
+        <v>17.20368873776325</v>
       </c>
       <c r="U7" t="n">
         <v>17.26828718585448</v>
       </c>
       <c r="V7" t="n">
-        <v>18.60809854165223</v>
+        <v>18.6080985416522</v>
       </c>
       <c r="W7" t="n">
-        <v>18.86879457137156</v>
+        <v>18.86879457137157</v>
       </c>
       <c r="X7" t="n">
-        <v>19.45392791688052</v>
+        <v>19.45392791688048</v>
       </c>
       <c r="Y7" t="n">
-        <v>26.0567971464171</v>
+        <v>26.05679714641701</v>
       </c>
       <c r="Z7" t="n">
         <v>18.50409085676507</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.74443645088829</v>
+        <v>17.74443645088827</v>
       </c>
       <c r="AB7" t="n">
-        <v>30.49882444003077</v>
+        <v>30.49882444003081</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.389089522585</v>
+        <v>30.38908952258498</v>
       </c>
       <c r="C8" t="n">
-        <v>39.06032707199242</v>
+        <v>39.0603270719924</v>
       </c>
       <c r="D8" t="n">
-        <v>41.45775482603908</v>
+        <v>41.45775482603907</v>
       </c>
       <c r="E8" t="n">
-        <v>33.07668591692151</v>
+        <v>33.07668591692149</v>
       </c>
       <c r="F8" t="n">
-        <v>33.45446658739661</v>
+        <v>33.45446658739657</v>
       </c>
       <c r="G8" t="n">
-        <v>51.05532960715961</v>
+        <v>51.05532960715949</v>
       </c>
       <c r="H8" t="n">
-        <v>39.20588943550455</v>
+        <v>39.20588943550449</v>
       </c>
       <c r="I8" t="n">
-        <v>41.43929825164695</v>
+        <v>41.43929825164692</v>
       </c>
       <c r="J8" t="n">
-        <v>44.77425503757343</v>
+        <v>44.77425503757335</v>
       </c>
       <c r="K8" t="n">
-        <v>41.62771497781025</v>
+        <v>41.62771497781021</v>
       </c>
       <c r="L8" t="n">
-        <v>40.04298041757872</v>
+        <v>40.04298041757868</v>
       </c>
       <c r="M8" t="n">
-        <v>51.24160371703873</v>
+        <v>51.24160371703868</v>
       </c>
       <c r="N8" t="n">
-        <v>47.34142200342082</v>
+        <v>31.32127736701013</v>
       </c>
       <c r="O8" t="n">
-        <v>34.79917601993784</v>
+        <v>34.7991760199378</v>
       </c>
       <c r="P8" t="n">
-        <v>37.49462259269697</v>
+        <v>37.49462259269693</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.13257794390224</v>
+        <v>27.13257794390223</v>
       </c>
       <c r="R8" t="n">
-        <v>40.18627604154317</v>
+        <v>40.18627604154314</v>
       </c>
       <c r="S8" t="n">
-        <v>42.27577830740077</v>
+        <v>42.27577830740074</v>
       </c>
       <c r="T8" t="n">
-        <v>40.2899706886009</v>
+        <v>40.28997068860086</v>
       </c>
       <c r="U8" t="n">
-        <v>35.03460446820321</v>
+        <v>35.03460446820315</v>
       </c>
       <c r="V8" t="n">
-        <v>38.71256141973845</v>
+        <v>38.71256141973844</v>
       </c>
       <c r="W8" t="n">
-        <v>41.95721890077151</v>
+        <v>41.95721890077149</v>
       </c>
       <c r="X8" t="n">
-        <v>30.49590612659198</v>
+        <v>30.4959061265919</v>
       </c>
       <c r="Y8" t="n">
-        <v>59.97809220135849</v>
+        <v>59.97809220135834</v>
       </c>
       <c r="Z8" t="n">
-        <v>30.48678272470203</v>
+        <v>30.48678272470202</v>
       </c>
       <c r="AA8" t="n">
-        <v>40.83071840172595</v>
+        <v>40.8307184017259</v>
       </c>
       <c r="AB8" t="n">
-        <v>64.97221334241296</v>
+        <v>64.97221334241291</v>
       </c>
     </row>
     <row r="9">
@@ -4645,79 +4645,79 @@
         <v>27.56883123072692</v>
       </c>
       <c r="C9" t="n">
-        <v>29.30375683452161</v>
+        <v>29.30375683452157</v>
       </c>
       <c r="D9" t="n">
         <v>31.70118458856827</v>
       </c>
       <c r="E9" t="n">
-        <v>28.20957167523908</v>
+        <v>28.20957167523901</v>
       </c>
       <c r="F9" t="n">
         <v>23.76081920037481</v>
       </c>
       <c r="G9" t="n">
-        <v>39.03834563355666</v>
+        <v>39.03834563355664</v>
       </c>
       <c r="H9" t="n">
-        <v>29.44931919803373</v>
+        <v>29.4493191980337</v>
       </c>
       <c r="I9" t="n">
-        <v>31.68272801417615</v>
+        <v>31.68272801417611</v>
       </c>
       <c r="J9" t="n">
-        <v>35.0176848001026</v>
+        <v>35.01768480010253</v>
       </c>
       <c r="K9" t="n">
-        <v>31.87114474033944</v>
+        <v>31.87114474033939</v>
       </c>
       <c r="L9" t="n">
-        <v>30.28641018010791</v>
+        <v>30.28641018010786</v>
       </c>
       <c r="M9" t="n">
-        <v>41.48503347956566</v>
+        <v>41.48503347956557</v>
       </c>
       <c r="N9" t="n">
-        <v>47.34142200342082</v>
+        <v>30.01488072092089</v>
       </c>
       <c r="O9" t="n">
-        <v>32.48452229663211</v>
+        <v>32.48452229663206</v>
       </c>
       <c r="P9" t="n">
         <v>36.03494756265599</v>
       </c>
       <c r="Q9" t="n">
-        <v>30.41941827512496</v>
+        <v>30.41941827512494</v>
       </c>
       <c r="R9" t="n">
-        <v>30.4297058040723</v>
+        <v>30.42970580407227</v>
       </c>
       <c r="S9" t="n">
-        <v>32.51920806992995</v>
+        <v>32.51920806992993</v>
       </c>
       <c r="T9" t="n">
-        <v>30.53340045113006</v>
+        <v>30.53340045113009</v>
       </c>
       <c r="U9" t="n">
         <v>30.60087633489096</v>
       </c>
       <c r="V9" t="n">
-        <v>36.51308299253662</v>
+        <v>36.5130829925366</v>
       </c>
       <c r="W9" t="n">
-        <v>32.19850628473839</v>
+        <v>32.19850628473838</v>
       </c>
       <c r="X9" t="n">
-        <v>32.78363963024736</v>
+        <v>32.78363963024727</v>
       </c>
       <c r="Y9" t="n">
-        <v>39.3865088597839</v>
+        <v>39.38650885978396</v>
       </c>
       <c r="Z9" t="n">
-        <v>29.44338984151141</v>
+        <v>29.44338984151139</v>
       </c>
       <c r="AA9" t="n">
-        <v>31.07414816425509</v>
+        <v>31.07414816425506</v>
       </c>
       <c r="AB9" t="n">
         <v>43.8285361533976</v>
@@ -5098,7 +5098,7 @@
         <v>16.33306501019788</v>
       </c>
       <c r="N4" t="n">
-        <v>52.57648196418342</v>
+        <v>12.03599552484537</v>
       </c>
       <c r="O4" t="n">
         <v>12.00373411763503</v>
@@ -5274,7 +5274,7 @@
         <v>48.13740086298652</v>
       </c>
       <c r="N6" t="n">
-        <v>52.57648196418342</v>
+        <v>30.64646789144917</v>
       </c>
       <c r="O6" t="n">
         <v>43.46214359572603</v>
@@ -5362,7 +5362,7 @@
         <v>20.66325229864948</v>
       </c>
       <c r="N7" t="n">
-        <v>52.57648196418342</v>
+        <v>16.36618281329694</v>
       </c>
       <c r="O7" t="n">
         <v>16.33383335519777</v>
@@ -5450,7 +5450,7 @@
         <v>44.74453400078101</v>
       </c>
       <c r="N8" t="n">
-        <v>52.57648196418342</v>
+        <v>31.71198864028573</v>
       </c>
       <c r="O8" t="n">
         <v>34.08031185291769</v>
@@ -5538,7 +5538,7 @@
         <v>34.87011019295182</v>
       </c>
       <c r="N9" t="n">
-        <v>52.57648196418342</v>
+        <v>30.57304070759925</v>
       </c>
       <c r="O9" t="n">
         <v>31.91425468016959</v>
@@ -5958,7 +5958,7 @@
         <v>11.05145782951666</v>
       </c>
       <c r="N4" t="n">
-        <v>44.65551266421883</v>
+        <v>11.59280723608483</v>
       </c>
       <c r="O4" t="n">
         <v>12.25085854656114</v>
@@ -6073,7 +6073,7 @@
         <v>44.31283440738962</v>
       </c>
       <c r="W5" t="n">
-        <v>61.29915343106503</v>
+        <v>61.29915343106504</v>
       </c>
       <c r="X5" t="n">
         <v>83.35075719035508</v>
@@ -6134,7 +6134,7 @@
         <v>40.51168290808562</v>
       </c>
       <c r="N6" t="n">
-        <v>44.65551266421883</v>
+        <v>28.92684219865218</v>
       </c>
       <c r="O6" t="n">
         <v>41.38733583713773</v>
@@ -6222,7 +6222,7 @@
         <v>14.9627423923151</v>
       </c>
       <c r="N7" t="n">
-        <v>44.65551266421883</v>
+        <v>15.50409179888326</v>
       </c>
       <c r="O7" t="n">
         <v>16.16206143741476</v>
@@ -6310,7 +6310,7 @@
         <v>37.08423662502895</v>
       </c>
       <c r="N8" t="n">
-        <v>44.65551266421883</v>
+        <v>29.63243618643935</v>
       </c>
       <c r="O8" t="n">
         <v>32.48707447820999</v>
@@ -6377,7 +6377,7 @@
         <v>18.60876617541211</v>
       </c>
       <c r="G9" t="n">
-        <v>27.12538992341274</v>
+        <v>27.12538992341273</v>
       </c>
       <c r="H9" t="n">
         <v>27.32131336157634</v>
@@ -6398,7 +6398,7 @@
         <v>26.6613618622934</v>
       </c>
       <c r="N9" t="n">
-        <v>44.65551266421883</v>
+        <v>27.20271126886153</v>
       </c>
       <c r="O9" t="n">
         <v>29.01790332824827</v>
@@ -6818,7 +6818,7 @@
         <v>11.05589099775007</v>
       </c>
       <c r="N4" t="n">
-        <v>37.36408315653244</v>
+        <v>11.13415890737669</v>
       </c>
       <c r="O4" t="n">
         <v>11.98586700452165</v>
@@ -6906,7 +6906,7 @@
         <v>38.12411444298455</v>
       </c>
       <c r="N5" t="n">
-        <v>37.36408315653243</v>
+        <v>37.36408315653244</v>
       </c>
       <c r="O5" t="n">
         <v>49.49661730634397</v>
@@ -6994,7 +6994,7 @@
         <v>40.49056639212438</v>
       </c>
       <c r="N6" t="n">
-        <v>37.36408315653243</v>
+        <v>28.45408894046494</v>
       </c>
       <c r="O6" t="n">
         <v>29.30611534237287</v>
@@ -7082,7 +7082,7 @@
         <v>14.94399752962618</v>
       </c>
       <c r="N7" t="n">
-        <v>37.36408315653243</v>
+        <v>15.02226543925277</v>
       </c>
       <c r="O7" t="n">
         <v>15.87389245816804</v>
@@ -7170,7 +7170,7 @@
         <v>37.00467762497443</v>
       </c>
       <c r="N8" t="n">
-        <v>37.36408315653243</v>
+        <v>29.11673328380713</v>
       </c>
       <c r="O8" t="n">
         <v>32.15762567742929</v>
@@ -7258,7 +7258,7 @@
         <v>25.86870479094338</v>
       </c>
       <c r="N9" t="n">
-        <v>37.36408315653243</v>
+        <v>25.94697270056999</v>
       </c>
       <c r="O9" t="n">
         <v>27.89820308519322</v>
@@ -7678,7 +7678,7 @@
         <v>27.74213057504567</v>
       </c>
       <c r="N4" t="n">
-        <v>68.29022042389396</v>
+        <v>13.26720932590121</v>
       </c>
       <c r="O4" t="n">
         <v>13.43414315039703</v>
@@ -7854,7 +7854,7 @@
         <v>46.37943689134181</v>
       </c>
       <c r="N6" t="n">
-        <v>68.29022042389396</v>
+        <v>31.91243765511211</v>
       </c>
       <c r="O6" t="n">
         <v>45.49910838183719</v>
@@ -7942,7 +7942,7 @@
         <v>32.3719089436676</v>
       </c>
       <c r="N7" t="n">
-        <v>68.29022042389396</v>
+        <v>17.89698769452314</v>
       </c>
       <c r="O7" t="n">
         <v>18.0638301904253</v>
@@ -8030,7 +8030,7 @@
         <v>57.17588890207073</v>
       </c>
       <c r="N8" t="n">
-        <v>68.29022042389396</v>
+        <v>33.62090492714491</v>
       </c>
       <c r="O8" t="n">
         <v>36.28311882995141</v>
@@ -8118,7 +8118,7 @@
         <v>49.0313540625746</v>
       </c>
       <c r="N9" t="n">
-        <v>68.29022042389396</v>
+        <v>34.55643281343012</v>
       </c>
       <c r="O9" t="n">
         <v>36.3031817552418</v>
@@ -8538,7 +8538,7 @@
         <v>12.88859681632973</v>
       </c>
       <c r="N4" t="n">
-        <v>47.35781243703483</v>
+        <v>12.02974516090364</v>
       </c>
       <c r="O4" t="n">
         <v>12.09783302902968</v>
@@ -8714,7 +8714,7 @@
         <v>30.20347621990543</v>
       </c>
       <c r="N6" t="n">
-        <v>47.35781243703483</v>
+        <v>29.35110641725971</v>
       </c>
       <c r="O6" t="n">
         <v>41.68668246630814</v>
@@ -8802,7 +8802,7 @@
         <v>16.99856590856367</v>
       </c>
       <c r="N7" t="n">
-        <v>47.35781243703483</v>
+        <v>16.1397142531376</v>
       </c>
       <c r="O7" t="n">
         <v>16.20771838210057</v>
@@ -8890,7 +8890,7 @@
         <v>39.6479798202906</v>
       </c>
       <c r="N8" t="n">
-        <v>47.35781243703483</v>
+        <v>30.54715175521682</v>
       </c>
       <c r="O8" t="n">
         <v>32.88020630500652</v>
@@ -8978,7 +8978,7 @@
         <v>30.49734685714408</v>
       </c>
       <c r="N9" t="n">
-        <v>47.35781243703483</v>
+        <v>29.63849520171797</v>
       </c>
       <c r="O9" t="n">
         <v>31.01438116973086</v>

--- a/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -586,64 +586,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.49427387479611</v>
+        <v>21.49427387479615</v>
       </c>
       <c r="C2" t="n">
-        <v>15.76453677347148</v>
+        <v>15.76453677347149</v>
       </c>
       <c r="D2" t="n">
-        <v>21.43226328160575</v>
+        <v>21.43226328160576</v>
       </c>
       <c r="E2" t="n">
-        <v>21.31732393755548</v>
+        <v>21.31732393755549</v>
       </c>
       <c r="F2" t="n">
-        <v>21.49031215024842</v>
+        <v>21.49031215024845</v>
       </c>
       <c r="G2" t="n">
-        <v>22.38231373995819</v>
+        <v>22.3823137399582</v>
       </c>
       <c r="H2" t="n">
-        <v>21.33738723680796</v>
+        <v>21.33738723680797</v>
       </c>
       <c r="I2" t="n">
         <v>21.46990824765629</v>
       </c>
       <c r="J2" t="n">
-        <v>21.87948163404551</v>
+        <v>21.87948163404555</v>
       </c>
       <c r="K2" t="n">
-        <v>21.45591547663293</v>
+        <v>21.45591547663294</v>
       </c>
       <c r="L2" t="n">
-        <v>21.41731995975388</v>
+        <v>21.41731995975387</v>
       </c>
       <c r="M2" t="n">
-        <v>22.73855529438004</v>
+        <v>22.73855529438005</v>
       </c>
       <c r="N2" t="n">
-        <v>21.43437383303733</v>
+        <v>21.43437383303734</v>
       </c>
       <c r="O2" t="n">
-        <v>28.89384478428557</v>
+        <v>28.89384478428558</v>
       </c>
       <c r="P2" t="n">
         <v>21.70617251506718</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.36807231876991</v>
+        <v>21.36807231876988</v>
       </c>
       <c r="R2" t="n">
-        <v>21.34181164367454</v>
+        <v>21.34181164367455</v>
       </c>
       <c r="S2" t="n">
-        <v>21.61817821173706</v>
+        <v>21.61817821173707</v>
       </c>
       <c r="T2" t="n">
-        <v>21.38138220633868</v>
+        <v>21.3813822063387</v>
       </c>
       <c r="U2" t="n">
-        <v>25.2412364370762</v>
+        <v>25.24123643707624</v>
       </c>
       <c r="V2" t="n">
         <v>21.46857710411926</v>
@@ -652,7 +652,7 @@
         <v>27.23057379125946</v>
       </c>
       <c r="X2" t="n">
-        <v>21.49552618038708</v>
+        <v>21.49552618038709</v>
       </c>
       <c r="Y2" t="n">
         <v>21.64243821774006</v>
@@ -661,10 +661,10 @@
         <v>27.96831273648419</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.67164353990161</v>
+        <v>21.6716435399016</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.87338174561294</v>
+        <v>22.87338174561295</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.98656652168485</v>
+        <v>22.07923323308708</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5730224471232</v>
+        <v>11.62211807675921</v>
       </c>
       <c r="D3" t="n">
-        <v>21.55607773405834</v>
+        <v>21.63411015780082</v>
       </c>
       <c r="E3" t="n">
-        <v>20.7157453947673</v>
+        <v>20.76197008387948</v>
       </c>
       <c r="F3" t="n">
-        <v>21.97505242685843</v>
+        <v>22.06817506342993</v>
       </c>
       <c r="G3" t="n">
-        <v>28.31054854378133</v>
+        <v>28.6254122428934</v>
       </c>
       <c r="H3" t="n">
-        <v>20.88011033539232</v>
+        <v>20.9342703290879</v>
       </c>
       <c r="I3" t="n">
-        <v>21.82695888418551</v>
+        <v>21.91467466990651</v>
       </c>
       <c r="J3" t="n">
-        <v>24.73819906868664</v>
+        <v>24.92800481291167</v>
       </c>
       <c r="K3" t="n">
-        <v>21.72448331150946</v>
+        <v>21.80843354190752</v>
       </c>
       <c r="L3" t="n">
-        <v>21.44378752874241</v>
+        <v>21.51754126782492</v>
       </c>
       <c r="M3" t="n">
-        <v>31.70001337429634</v>
+        <v>32.14366869980996</v>
       </c>
       <c r="N3" t="n">
-        <v>21.56836897560769</v>
+        <v>21.64669720026424</v>
       </c>
       <c r="O3" t="n">
-        <v>34.70796329750474</v>
+        <v>34.82384924102001</v>
       </c>
       <c r="P3" t="n">
-        <v>23.49451157462831</v>
+        <v>23.63991365337958</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.09524535996798</v>
+        <v>21.15687469568895</v>
       </c>
       <c r="R3" t="n">
-        <v>20.91020233461428</v>
+        <v>20.96539819485939</v>
       </c>
       <c r="S3" t="n">
-        <v>22.87152297481995</v>
+        <v>22.9954852888012</v>
       </c>
       <c r="T3" t="n">
-        <v>21.1921625904426</v>
+        <v>21.25730204681534</v>
       </c>
       <c r="U3" t="n">
-        <v>29.86626164761305</v>
+        <v>30.03375656348383</v>
       </c>
       <c r="V3" t="n">
-        <v>21.80548155796395</v>
+        <v>21.8918369785955</v>
       </c>
       <c r="W3" t="n">
-        <v>32.13212079855701</v>
+        <v>32.25608864793718</v>
       </c>
       <c r="X3" t="n">
-        <v>22.00763225903866</v>
+        <v>22.10165973865432</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.05253695334803</v>
+        <v>23.18328996491086</v>
       </c>
       <c r="Z3" t="n">
-        <v>33.27441209796649</v>
+        <v>33.39459185945581</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.26148492218728</v>
+        <v>23.39951691620977</v>
       </c>
       <c r="AB3" t="n">
-        <v>31.82646629409132</v>
+        <v>32.26735247055734</v>
       </c>
     </row>
     <row r="4">
@@ -765,79 +765,79 @@
         <v>14.24029911125382</v>
       </c>
       <c r="C4" t="n">
-        <v>12.25413840473276</v>
+        <v>12.25413840473278</v>
       </c>
       <c r="D4" t="n">
         <v>13.53986093488619</v>
       </c>
       <c r="E4" t="n">
-        <v>12.24156816912782</v>
+        <v>12.24156816912783</v>
       </c>
       <c r="F4" t="n">
-        <v>14.1955496100043</v>
+        <v>14.19554961000431</v>
       </c>
       <c r="G4" t="n">
-        <v>24.27111790678019</v>
+        <v>24.27111790678024</v>
       </c>
       <c r="H4" t="n">
-        <v>12.46819236375814</v>
+        <v>12.46819236375815</v>
       </c>
       <c r="I4" t="n">
-        <v>13.96507814396694</v>
+        <v>13.96507814396695</v>
       </c>
       <c r="J4" t="n">
-        <v>18.55946950438403</v>
+        <v>18.55946950438405</v>
       </c>
       <c r="K4" t="n">
-        <v>13.80702335826547</v>
+        <v>13.80702335826549</v>
       </c>
       <c r="L4" t="n">
-        <v>13.37106924030157</v>
+        <v>13.37106924030162</v>
       </c>
       <c r="M4" t="n">
-        <v>29.73190512023366</v>
+        <v>29.73190512023365</v>
       </c>
       <c r="N4" t="n">
-        <v>13.56370058420747</v>
+        <v>13.56370058420748</v>
       </c>
       <c r="O4" t="n">
-        <v>15.29391679713817</v>
+        <v>15.29391679713815</v>
       </c>
       <c r="P4" t="n">
-        <v>16.63379173130573</v>
+        <v>16.63379173130572</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.81479448035322</v>
+        <v>12.81479448035321</v>
       </c>
       <c r="R4" t="n">
-        <v>12.51816807464395</v>
+        <v>12.51816807464397</v>
       </c>
       <c r="S4" t="n">
-        <v>15.6398555958127</v>
+        <v>15.63985559581271</v>
       </c>
       <c r="T4" t="n">
         <v>12.96513578329369</v>
       </c>
       <c r="U4" t="n">
-        <v>17.42290061528121</v>
+        <v>17.42290061528118</v>
       </c>
       <c r="V4" t="n">
-        <v>13.74551665879871</v>
+        <v>13.74551665879874</v>
       </c>
       <c r="W4" t="n">
-        <v>15.61768573392326</v>
+        <v>15.61768573392325</v>
       </c>
       <c r="X4" t="n">
-        <v>14.25444447899257</v>
+        <v>14.25444447899259</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.75080861618461</v>
+        <v>15.75080861618459</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.47831740717692</v>
+        <v>15.47831740717693</v>
       </c>
       <c r="AA4" t="n">
-        <v>16.24377107269715</v>
+        <v>16.24377107269718</v>
       </c>
       <c r="AB4" t="n">
         <v>29.6757422026279</v>
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.83421244859886</v>
+        <v>80.8342124485871</v>
       </c>
       <c r="C5" t="n">
         <v>46.43740104499177</v>
       </c>
       <c r="D5" t="n">
-        <v>73.9109609922002</v>
+        <v>73.91096099219956</v>
       </c>
       <c r="E5" t="n">
-        <v>35.87646203413695</v>
+        <v>35.87646203413696</v>
       </c>
       <c r="F5" t="n">
         <v>89.89490808415709</v>
       </c>
       <c r="G5" t="n">
-        <v>274.5107872497488</v>
+        <v>274.5107872497496</v>
       </c>
       <c r="H5" t="n">
-        <v>53.02386112773907</v>
+        <v>53.02386112773891</v>
       </c>
       <c r="I5" t="n">
-        <v>83.7857403695111</v>
+        <v>83.78574036951119</v>
       </c>
       <c r="J5" t="n">
-        <v>169.8419161308594</v>
+        <v>169.8419161308595</v>
       </c>
       <c r="K5" t="n">
-        <v>79.05251456739906</v>
+        <v>79.05251456739892</v>
       </c>
       <c r="L5" t="n">
-        <v>67.16033777320823</v>
+        <v>67.1603377732082</v>
       </c>
       <c r="M5" t="n">
-        <v>423.8657334709086</v>
+        <v>423.8657334709078</v>
       </c>
       <c r="N5" t="n">
-        <v>72.74358057785906</v>
+        <v>72.74358057785903</v>
       </c>
       <c r="O5" t="n">
-        <v>99.2542874061364</v>
+        <v>99.2542874061361</v>
       </c>
       <c r="P5" t="n">
-        <v>126.4271245696352</v>
+        <v>126.4271245696355</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.7059648293685</v>
+        <v>57.70596482936848</v>
       </c>
       <c r="R5" t="n">
-        <v>53.1475284451575</v>
+        <v>53.14752844515749</v>
       </c>
       <c r="S5" t="n">
-        <v>109.4016392111159</v>
+        <v>109.4016392111166</v>
       </c>
       <c r="T5" t="n">
-        <v>61.8769843273186</v>
+        <v>61.87698432731858</v>
       </c>
       <c r="U5" t="n">
-        <v>149.5541684812713</v>
+        <v>149.5541684812716</v>
       </c>
       <c r="V5" t="n">
-        <v>76.15996438588667</v>
+        <v>76.15996438588671</v>
       </c>
       <c r="W5" t="n">
-        <v>113.1629904501172</v>
+        <v>113.1629904501171</v>
       </c>
       <c r="X5" t="n">
-        <v>88.32732513037396</v>
+        <v>88.32732513037364</v>
       </c>
       <c r="Y5" t="n">
-        <v>119.5969732904747</v>
+        <v>119.5969732904748</v>
       </c>
       <c r="Z5" t="n">
         <v>105.7272039303549</v>
       </c>
       <c r="AA5" t="n">
-        <v>126.5422050581317</v>
+        <v>126.5422050581319</v>
       </c>
       <c r="AB5" t="n">
-        <v>435.8941750601039</v>
+        <v>435.8941750601041</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.22280182286057</v>
+        <v>34.22280182286058</v>
       </c>
       <c r="C6" t="n">
-        <v>47.08503157586952</v>
+        <v>47.08503157586957</v>
       </c>
       <c r="D6" t="n">
-        <v>48.37075410602298</v>
+        <v>48.37075410602301</v>
       </c>
       <c r="E6" t="n">
-        <v>47.07246134026461</v>
+        <v>47.07246134026467</v>
       </c>
       <c r="F6" t="n">
-        <v>34.178052321611</v>
+        <v>34.17805232161102</v>
       </c>
       <c r="G6" t="n">
-        <v>59.102011077917</v>
+        <v>59.10201107791707</v>
       </c>
       <c r="H6" t="n">
-        <v>47.299085534895</v>
+        <v>47.29908553489503</v>
       </c>
       <c r="I6" t="n">
-        <v>33.9475808555737</v>
+        <v>33.94758085557368</v>
       </c>
       <c r="J6" t="n">
-        <v>38.54197221599075</v>
+        <v>38.54197221599078</v>
       </c>
       <c r="K6" t="n">
-        <v>48.63791652940228</v>
+        <v>48.63791652940232</v>
       </c>
       <c r="L6" t="n">
-        <v>48.20196241143842</v>
+        <v>48.20196241143844</v>
       </c>
       <c r="M6" t="n">
-        <v>64.5627982913705</v>
+        <v>64.56279829137044</v>
       </c>
       <c r="N6" t="n">
-        <v>33.56168172892661</v>
+        <v>33.56168172892656</v>
       </c>
       <c r="O6" t="n">
-        <v>35.29190300955802</v>
+        <v>35.29190300955801</v>
       </c>
       <c r="P6" t="n">
-        <v>51.09565332470645</v>
+        <v>51.09565332470648</v>
       </c>
       <c r="Q6" t="n">
-        <v>47.64568765149008</v>
+        <v>47.64568765149007</v>
       </c>
       <c r="R6" t="n">
-        <v>47.34906124578075</v>
+        <v>47.3490612457808</v>
       </c>
       <c r="S6" t="n">
-        <v>35.62235830741938</v>
+        <v>35.62235830741937</v>
       </c>
       <c r="T6" t="n">
         <v>32.9476384949004</v>
       </c>
       <c r="U6" t="n">
-        <v>37.56847823447384</v>
+        <v>37.56847823447387</v>
       </c>
       <c r="V6" t="n">
-        <v>48.57640982993553</v>
+        <v>48.57640982993557</v>
       </c>
       <c r="W6" t="n">
         <v>50.07955208986171</v>
       </c>
       <c r="X6" t="n">
-        <v>49.08533765012943</v>
+        <v>49.08533765012945</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.80047453711332</v>
+        <v>36.80047453711331</v>
       </c>
       <c r="Z6" t="n">
-        <v>35.46082011878364</v>
+        <v>35.46082011878367</v>
       </c>
       <c r="AA6" t="n">
-        <v>51.074664243834</v>
+        <v>51.07466424383397</v>
       </c>
       <c r="AB6" t="n">
-        <v>49.76992658177956</v>
+        <v>49.76992658177953</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.38286753229233</v>
+        <v>19.38286753229231</v>
       </c>
       <c r="C7" t="n">
         <v>17.39670682577128</v>
       </c>
       <c r="D7" t="n">
-        <v>18.6824293559247</v>
+        <v>18.68242935592466</v>
       </c>
       <c r="E7" t="n">
-        <v>17.38413659016634</v>
+        <v>17.38413659016633</v>
       </c>
       <c r="F7" t="n">
-        <v>19.33811803104279</v>
+        <v>19.3381180310428</v>
       </c>
       <c r="G7" t="n">
-        <v>29.41368632781873</v>
+        <v>29.41368632781874</v>
       </c>
       <c r="H7" t="n">
-        <v>17.61076078479666</v>
+        <v>17.61076078479665</v>
       </c>
       <c r="I7" t="n">
-        <v>19.10764656500545</v>
+        <v>19.10764656500544</v>
       </c>
       <c r="J7" t="n">
-        <v>23.70203792542255</v>
+        <v>23.70203792542256</v>
       </c>
       <c r="K7" t="n">
         <v>18.949591779304</v>
       </c>
       <c r="L7" t="n">
-        <v>18.5136376613401</v>
+        <v>18.51363766134009</v>
       </c>
       <c r="M7" t="n">
-        <v>34.87447354127217</v>
+        <v>34.87447354127212</v>
       </c>
       <c r="N7" t="n">
-        <v>18.70626900524597</v>
+        <v>18.70626900524598</v>
       </c>
       <c r="O7" t="n">
-        <v>20.43638439411393</v>
+        <v>20.43638439411389</v>
       </c>
       <c r="P7" t="n">
-        <v>21.77625932828149</v>
+        <v>21.77625932828146</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.95736290139171</v>
+        <v>17.95736290139174</v>
       </c>
       <c r="R7" t="n">
-        <v>17.66073649568247</v>
+        <v>17.66073649568244</v>
       </c>
       <c r="S7" t="n">
-        <v>20.7824240168512</v>
+        <v>20.78242401685119</v>
       </c>
       <c r="T7" t="n">
-        <v>18.10770420433222</v>
+        <v>18.1077042043322</v>
       </c>
       <c r="U7" t="n">
-        <v>22.72503963249836</v>
+        <v>22.72503963249842</v>
       </c>
       <c r="V7" t="n">
-        <v>18.88808507983721</v>
+        <v>18.88808507983723</v>
       </c>
       <c r="W7" t="n">
-        <v>20.76025415496173</v>
+        <v>20.76025415496172</v>
       </c>
       <c r="X7" t="n">
         <v>19.39701290003109</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.05645194480906</v>
+        <v>21.05645194480904</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.62088582821544</v>
+        <v>20.62088582821541</v>
       </c>
       <c r="AA7" t="n">
         <v>21.38633949373566</v>
       </c>
       <c r="AB7" t="n">
-        <v>34.81831062366643</v>
+        <v>34.81831062366639</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.49483799447192</v>
+        <v>33.49483799447197</v>
       </c>
       <c r="C8" t="n">
-        <v>44.2641442296689</v>
+        <v>44.26414422966901</v>
       </c>
       <c r="D8" t="n">
-        <v>45.54986675982229</v>
+        <v>45.54986675982244</v>
       </c>
       <c r="E8" t="n">
-        <v>37.45966411017863</v>
+        <v>37.45966411017872</v>
       </c>
       <c r="F8" t="n">
-        <v>35.43724116654578</v>
+        <v>35.43724116654587</v>
       </c>
       <c r="G8" t="n">
-        <v>58.92605289627778</v>
+        <v>58.92605289627794</v>
       </c>
       <c r="H8" t="n">
-        <v>44.47819818869428</v>
+        <v>44.47819818869442</v>
       </c>
       <c r="I8" t="n">
-        <v>45.97508396890308</v>
+        <v>45.97508396890325</v>
       </c>
       <c r="J8" t="n">
-        <v>50.56947532932017</v>
+        <v>50.56947532932033</v>
       </c>
       <c r="K8" t="n">
-        <v>45.8170291832016</v>
+        <v>45.81702918320177</v>
       </c>
       <c r="L8" t="n">
-        <v>45.38107506523768</v>
+        <v>45.38107506523781</v>
       </c>
       <c r="M8" t="n">
-        <v>61.74191094517046</v>
+        <v>61.74191094517057</v>
       </c>
       <c r="N8" t="n">
-        <v>35.68608558638438</v>
+        <v>35.68608558638449</v>
       </c>
       <c r="O8" t="n">
-        <v>40.13350585460747</v>
+        <v>40.13350585460751</v>
       </c>
       <c r="P8" t="n">
-        <v>40.80732841792073</v>
+        <v>40.80732841792079</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.56259297999511</v>
+        <v>29.5625929799952</v>
       </c>
       <c r="R8" t="n">
-        <v>44.52817389958005</v>
+        <v>44.52817389958018</v>
       </c>
       <c r="S8" t="n">
-        <v>47.64986142074882</v>
+        <v>47.64986142074891</v>
       </c>
       <c r="T8" t="n">
-        <v>44.97514160822984</v>
+        <v>44.97514160822993</v>
       </c>
       <c r="U8" t="n">
-        <v>43.36757056019276</v>
+        <v>43.36757056019292</v>
       </c>
       <c r="V8" t="n">
-        <v>42.26635182314928</v>
+        <v>42.26635182314945</v>
       </c>
       <c r="W8" t="n">
-        <v>47.63019837439488</v>
+        <v>47.63019837439495</v>
       </c>
       <c r="X8" t="n">
-        <v>32.17130686982671</v>
+        <v>32.17130686982675</v>
       </c>
       <c r="Y8" t="n">
-        <v>60.60184759692144</v>
+        <v>60.6018475969216</v>
       </c>
       <c r="Z8" t="n">
-        <v>34.49591694322211</v>
+        <v>34.49591694322217</v>
       </c>
       <c r="AA8" t="n">
-        <v>48.2537768976333</v>
+        <v>48.25377689763341</v>
       </c>
       <c r="AB8" t="n">
-        <v>75.00989984371908</v>
+        <v>75.00989984371924</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.99020295776748</v>
+        <v>33.99020295776752</v>
       </c>
       <c r="C9" t="n">
-        <v>37.6929015442002</v>
+        <v>37.69290154420023</v>
       </c>
       <c r="D9" t="n">
-        <v>38.97862407435362</v>
+        <v>38.97862407435366</v>
       </c>
       <c r="E9" t="n">
-        <v>36.36736483720203</v>
+        <v>36.36736483720205</v>
       </c>
       <c r="F9" t="n">
-        <v>26.51994105598753</v>
+        <v>26.51994105598755</v>
       </c>
       <c r="G9" t="n">
-        <v>49.70987980988851</v>
+        <v>49.70987980988854</v>
       </c>
       <c r="H9" t="n">
-        <v>37.90695550322561</v>
+        <v>37.90695550322565</v>
       </c>
       <c r="I9" t="n">
-        <v>39.40384128343436</v>
+        <v>39.4038412834344</v>
       </c>
       <c r="J9" t="n">
-        <v>43.99823264385148</v>
+        <v>43.99823264385152</v>
       </c>
       <c r="K9" t="n">
-        <v>39.24578649773294</v>
+        <v>39.24578649773296</v>
       </c>
       <c r="L9" t="n">
-        <v>38.80983237976906</v>
+        <v>38.80983237976908</v>
       </c>
       <c r="M9" t="n">
-        <v>55.17066825970108</v>
+        <v>55.17066825970105</v>
       </c>
       <c r="N9" t="n">
-        <v>39.0024637236749</v>
+        <v>39.00246372367496</v>
       </c>
       <c r="O9" t="n">
-        <v>42.61795881128376</v>
+        <v>42.61795881128377</v>
       </c>
       <c r="P9" t="n">
-        <v>44.3678498236375</v>
+        <v>44.36784982363756</v>
       </c>
       <c r="Q9" t="n">
-        <v>38.25355638346152</v>
+        <v>38.25355638346154</v>
       </c>
       <c r="R9" t="n">
-        <v>37.95693121411139</v>
+        <v>37.95693121411144</v>
       </c>
       <c r="S9" t="n">
-        <v>41.07861873528013</v>
+        <v>41.07861873528022</v>
       </c>
       <c r="T9" t="n">
-        <v>38.40389892276117</v>
+        <v>38.40389892276118</v>
       </c>
       <c r="U9" t="n">
-        <v>43.02473866233461</v>
+        <v>43.02473866233462</v>
       </c>
       <c r="V9" t="n">
-        <v>45.74909456287626</v>
+        <v>45.74909456287631</v>
       </c>
       <c r="W9" t="n">
-        <v>41.05644887339069</v>
+        <v>41.0564488733907</v>
       </c>
       <c r="X9" t="n">
-        <v>39.69320761846004</v>
+        <v>39.69320761846008</v>
       </c>
       <c r="Y9" t="n">
-        <v>41.35264666323796</v>
+        <v>41.352646663238</v>
       </c>
       <c r="Z9" t="n">
         <v>37.48720377515487</v>
       </c>
       <c r="AA9" t="n">
-        <v>41.68253421216462</v>
+        <v>41.68253421216467</v>
       </c>
       <c r="AB9" t="n">
-        <v>55.11450534209533</v>
+        <v>55.1145053420954</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.19137928957402</v>
+        <v>20.1913792895741</v>
       </c>
       <c r="C2" t="n">
         <v>14.53624947580798</v>
       </c>
       <c r="D2" t="n">
-        <v>20.10478654650179</v>
+        <v>20.10478654650176</v>
       </c>
       <c r="E2" t="n">
-        <v>20.07135631875591</v>
+        <v>20.07135631875598</v>
       </c>
       <c r="F2" t="n">
-        <v>20.11888445956161</v>
+        <v>20.11888445956159</v>
       </c>
       <c r="G2" t="n">
-        <v>20.17333585895253</v>
+        <v>20.17333585895259</v>
       </c>
       <c r="H2" t="n">
-        <v>20.1620060997065</v>
+        <v>20.16200609970646</v>
       </c>
       <c r="I2" t="n">
-        <v>20.19943372885131</v>
+        <v>20.19943372885129</v>
       </c>
       <c r="J2" t="n">
-        <v>20.16228729554945</v>
+        <v>20.16228729554942</v>
       </c>
       <c r="K2" t="n">
-        <v>20.17856747378477</v>
+        <v>20.17856747378469</v>
       </c>
       <c r="L2" t="n">
-        <v>20.14749188057354</v>
+        <v>20.1474918805735</v>
       </c>
       <c r="M2" t="n">
-        <v>20.00916939639456</v>
+        <v>20.00916939639457</v>
       </c>
       <c r="N2" t="n">
-        <v>20.14156090510413</v>
+        <v>20.1415609051041</v>
       </c>
       <c r="O2" t="n">
-        <v>26.90299114729642</v>
+        <v>26.90299114729644</v>
       </c>
       <c r="P2" t="n">
-        <v>20.16865328853671</v>
+        <v>20.16865328853669</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.16808114888288</v>
+        <v>20.16808114888285</v>
       </c>
       <c r="R2" t="n">
-        <v>20.18323151285802</v>
+        <v>20.18323151285799</v>
       </c>
       <c r="S2" t="n">
-        <v>20.15767394278448</v>
+        <v>20.15767394278455</v>
       </c>
       <c r="T2" t="n">
-        <v>20.11040936408481</v>
+        <v>20.11040936408489</v>
       </c>
       <c r="U2" t="n">
-        <v>23.39832796023908</v>
+        <v>23.39832796023914</v>
       </c>
       <c r="V2" t="n">
-        <v>20.16040428566181</v>
+        <v>20.16040428566179</v>
       </c>
       <c r="W2" t="n">
-        <v>25.6245834108532</v>
+        <v>25.62458341085324</v>
       </c>
       <c r="X2" t="n">
-        <v>20.38480134841038</v>
+        <v>20.38480134841049</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.3566091347899</v>
+        <v>20.35660913478988</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.30586283482008</v>
+        <v>26.30586283482018</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.2148519028519</v>
+        <v>20.21485190285189</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.11991376212034</v>
+        <v>20.11991376212043</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.17729243564109</v>
+        <v>20.2373784913482</v>
       </c>
       <c r="C3" t="n">
-        <v>10.27759461831922</v>
+        <v>10.31193723077661</v>
       </c>
       <c r="D3" t="n">
-        <v>19.56666454192426</v>
+        <v>19.60537052069066</v>
       </c>
       <c r="E3" t="n">
-        <v>19.3126864681297</v>
+        <v>19.3404832668928</v>
       </c>
       <c r="F3" t="n">
-        <v>19.66725672395556</v>
+        <v>19.70964647072302</v>
       </c>
       <c r="G3" t="n">
-        <v>20.0501205291306</v>
+        <v>20.10571445764226</v>
       </c>
       <c r="H3" t="n">
-        <v>19.97775811685509</v>
+        <v>20.03121256153439</v>
       </c>
       <c r="I3" t="n">
-        <v>20.24302437056768</v>
+        <v>20.30584292318942</v>
       </c>
       <c r="J3" t="n">
-        <v>19.97357631133306</v>
+        <v>20.02658033705717</v>
       </c>
       <c r="K3" t="n">
-        <v>20.09212791585122</v>
+        <v>20.1495184057044</v>
       </c>
       <c r="L3" t="n">
-        <v>19.86853216803725</v>
+        <v>19.91782176799529</v>
       </c>
       <c r="M3" t="n">
-        <v>19.73594695084488</v>
+        <v>19.78567278998155</v>
       </c>
       <c r="N3" t="n">
-        <v>19.82691071544164</v>
+        <v>19.87484187133979</v>
       </c>
       <c r="O3" t="n">
-        <v>31.05374293192118</v>
+        <v>31.10450877985651</v>
       </c>
       <c r="P3" t="n">
-        <v>20.01549927418568</v>
+        <v>20.0698375717041</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.0154858026433</v>
+        <v>20.07017890914959</v>
       </c>
       <c r="R3" t="n">
-        <v>20.12825141291233</v>
+        <v>20.18702588432194</v>
       </c>
       <c r="S3" t="n">
-        <v>19.93842343892666</v>
+        <v>19.99017673562116</v>
       </c>
       <c r="T3" t="n">
-        <v>19.6057634945133</v>
+        <v>19.64590941263852</v>
       </c>
       <c r="U3" t="n">
-        <v>25.46972373601304</v>
+        <v>25.52674519759846</v>
       </c>
       <c r="V3" t="n">
-        <v>19.95878943308934</v>
+        <v>20.01119173969231</v>
       </c>
       <c r="W3" t="n">
-        <v>29.5975300819228</v>
+        <v>29.67849287996785</v>
       </c>
       <c r="X3" t="n">
-        <v>21.56118627914537</v>
+        <v>21.67091350174009</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.3625329652938</v>
+        <v>21.46470344313407</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.95213913714498</v>
+        <v>29.99764986565835</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.34948612940098</v>
+        <v>20.41583609004315</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.69411945520847</v>
+        <v>19.73741520081813</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.87258848828511</v>
+        <v>11.87258848828514</v>
       </c>
       <c r="C4" t="n">
-        <v>10.70107309328989</v>
+        <v>10.70107309328991</v>
       </c>
       <c r="D4" t="n">
-        <v>10.89448362065437</v>
+        <v>10.89448362065439</v>
       </c>
       <c r="E4" t="n">
-        <v>10.51687381960019</v>
+        <v>10.51687381960021</v>
       </c>
       <c r="F4" t="n">
-        <v>11.05372603402556</v>
+        <v>11.05372603402558</v>
       </c>
       <c r="G4" t="n">
         <v>11.66877963902715</v>
       </c>
       <c r="H4" t="n">
-        <v>11.54080479639646</v>
+        <v>11.54080479639648</v>
       </c>
       <c r="I4" t="n">
-        <v>11.96356708514715</v>
+        <v>11.96356708514717</v>
       </c>
       <c r="J4" t="n">
         <v>11.51603531012891</v>
       </c>
       <c r="K4" t="n">
-        <v>11.72787313521847</v>
+        <v>11.72787313521849</v>
       </c>
       <c r="L4" t="n">
-        <v>11.37686001441907</v>
+        <v>11.37686001441909</v>
       </c>
       <c r="M4" t="n">
-        <v>11.37983543372416</v>
+        <v>11.37983543372418</v>
       </c>
       <c r="N4" t="n">
-        <v>11.30986691810858</v>
+        <v>11.30986691810863</v>
       </c>
       <c r="O4" t="n">
-        <v>11.45298895905783</v>
+        <v>11.45298895905788</v>
       </c>
       <c r="P4" t="n">
-        <v>11.61588785209176</v>
+        <v>11.61588785209179</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.6094252715045</v>
+        <v>11.60942527150453</v>
       </c>
       <c r="R4" t="n">
-        <v>11.78055560211542</v>
+        <v>11.78055560211546</v>
       </c>
       <c r="S4" t="n">
-        <v>11.49187109107167</v>
+        <v>11.49187109107171</v>
       </c>
       <c r="T4" t="n">
-        <v>10.95799593187838</v>
+        <v>10.95799593187841</v>
       </c>
       <c r="U4" t="n">
-        <v>11.6569894502576</v>
+        <v>11.65698945025759</v>
       </c>
       <c r="V4" t="n">
-        <v>11.34513246654943</v>
+        <v>11.34513246654946</v>
       </c>
       <c r="W4" t="n">
-        <v>12.79430179900362</v>
+        <v>12.79430179900367</v>
       </c>
       <c r="X4" t="n">
-        <v>14.05737962138519</v>
+        <v>14.05737962138521</v>
       </c>
       <c r="Y4" t="n">
         <v>13.67034828335369</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.21289781763244</v>
+        <v>11.21289781763247</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.13772245319447</v>
+        <v>12.13772245319451</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.09843925877467</v>
+        <v>11.09843925877469</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.29920915022181</v>
+        <v>47.29920915022178</v>
       </c>
       <c r="C5" t="n">
-        <v>30.50608771152003</v>
+        <v>30.50608771152013</v>
       </c>
       <c r="D5" t="n">
-        <v>33.82888482341158</v>
+        <v>33.82888482341161</v>
       </c>
       <c r="E5" t="n">
-        <v>19.17741214784023</v>
+        <v>19.17741214784029</v>
       </c>
       <c r="F5" t="n">
-        <v>36.6322249686247</v>
+        <v>36.63222496862474</v>
       </c>
       <c r="G5" t="n">
-        <v>44.52624183810126</v>
+        <v>44.52624183810221</v>
       </c>
       <c r="H5" t="n">
         <v>46.66700276259004</v>
       </c>
       <c r="I5" t="n">
-        <v>53.18211482358475</v>
+        <v>53.18211482358473</v>
       </c>
       <c r="J5" t="n">
-        <v>43.48808956194219</v>
+        <v>43.48808956194249</v>
       </c>
       <c r="K5" t="n">
-        <v>47.99104593575507</v>
+        <v>47.99104593575505</v>
       </c>
       <c r="L5" t="n">
-        <v>40.84601016763983</v>
+        <v>40.84601016763985</v>
       </c>
       <c r="M5" t="n">
-        <v>43.0340641236287</v>
+        <v>43.03406412362867</v>
       </c>
       <c r="N5" t="n">
-        <v>40.02814120245156</v>
+        <v>40.02814120245154</v>
       </c>
       <c r="O5" t="n">
-        <v>40.66142054900279</v>
+        <v>40.66142054900281</v>
       </c>
       <c r="P5" t="n">
-        <v>42.96810783145703</v>
+        <v>42.96810783145701</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.96293821331807</v>
+        <v>44.96293821331808</v>
       </c>
       <c r="R5" t="n">
-        <v>50.39251664632429</v>
+        <v>50.39251664632432</v>
       </c>
       <c r="S5" t="n">
-        <v>41.44022413058418</v>
+        <v>41.4402241305842</v>
       </c>
       <c r="T5" t="n">
         <v>34.41771993614323</v>
       </c>
       <c r="U5" t="n">
-        <v>46.16629457797177</v>
+        <v>46.16629457797181</v>
       </c>
       <c r="V5" t="n">
-        <v>42.26383707065441</v>
+        <v>42.26383707065425</v>
       </c>
       <c r="W5" t="n">
-        <v>65.70015677383869</v>
+        <v>65.70015677383849</v>
       </c>
       <c r="X5" t="n">
         <v>87.71885736095145</v>
       </c>
       <c r="Y5" t="n">
-        <v>83.41119027918924</v>
+        <v>83.41119027918941</v>
       </c>
       <c r="Z5" t="n">
-        <v>36.76818722414653</v>
+        <v>36.76818722414656</v>
       </c>
       <c r="AA5" t="n">
-        <v>54.40786373771957</v>
+        <v>54.40786373771975</v>
       </c>
       <c r="AB5" t="n">
-        <v>38.22103386901189</v>
+        <v>38.22103386901198</v>
       </c>
     </row>
     <row r="6">
@@ -1801,82 +1801,82 @@
         <v>29.18984895641055</v>
       </c>
       <c r="C6" t="n">
-        <v>40.14769590473188</v>
+        <v>40.1476959047319</v>
       </c>
       <c r="D6" t="n">
-        <v>28.21174408877989</v>
+        <v>28.21174408877987</v>
       </c>
       <c r="E6" t="n">
-        <v>39.96349663104212</v>
+        <v>39.96349663104213</v>
       </c>
       <c r="F6" t="n">
-        <v>40.50034884546758</v>
+        <v>40.50034884546757</v>
       </c>
       <c r="G6" t="n">
-        <v>28.98604010715269</v>
+        <v>28.98604010715265</v>
       </c>
       <c r="H6" t="n">
-        <v>28.85806526452197</v>
+        <v>28.85806526452196</v>
       </c>
       <c r="I6" t="n">
-        <v>29.28082755327266</v>
+        <v>29.28082755327264</v>
       </c>
       <c r="J6" t="n">
-        <v>40.96265812157091</v>
+        <v>40.96265812157092</v>
       </c>
       <c r="K6" t="n">
         <v>29.04513360334395</v>
       </c>
       <c r="L6" t="n">
-        <v>40.82348282586103</v>
+        <v>40.82348282586106</v>
       </c>
       <c r="M6" t="n">
-        <v>28.69709590184966</v>
+        <v>28.69709590184964</v>
       </c>
       <c r="N6" t="n">
         <v>28.63430769899086</v>
       </c>
       <c r="O6" t="n">
-        <v>40.58150530047708</v>
+        <v>40.58150530047712</v>
       </c>
       <c r="P6" t="n">
-        <v>27.91228956734955</v>
+        <v>27.91228956734954</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.92668573963</v>
+        <v>28.92668573962999</v>
       </c>
       <c r="R6" t="n">
-        <v>29.09781607024094</v>
+        <v>29.09781607024091</v>
       </c>
       <c r="S6" t="n">
-        <v>40.93849390251368</v>
+        <v>40.93849390251364</v>
       </c>
       <c r="T6" t="n">
-        <v>28.27525640000393</v>
+        <v>28.27525640000394</v>
       </c>
       <c r="U6" t="n">
-        <v>41.17219957782854</v>
+        <v>41.17219957782855</v>
       </c>
       <c r="V6" t="n">
-        <v>28.66239293467494</v>
+        <v>28.66239293467491</v>
       </c>
       <c r="W6" t="n">
-        <v>31.02990791931773</v>
+        <v>31.0299079193176</v>
       </c>
       <c r="X6" t="n">
-        <v>43.50400243282716</v>
+        <v>43.50400243282713</v>
       </c>
       <c r="Y6" t="n">
-        <v>31.8423516004476</v>
+        <v>31.84235160044757</v>
       </c>
       <c r="Z6" t="n">
-        <v>28.53015828575789</v>
+        <v>28.53015828575788</v>
       </c>
       <c r="AA6" t="n">
-        <v>41.58434526463644</v>
+        <v>41.58434526463645</v>
       </c>
       <c r="AB6" t="n">
-        <v>28.42003596662344</v>
+        <v>28.42003596662343</v>
       </c>
     </row>
     <row r="7">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.81180075061221</v>
+        <v>15.81180075061222</v>
       </c>
       <c r="C7" t="n">
         <v>14.64028535561698</v>
       </c>
       <c r="D7" t="n">
-        <v>14.83369588298145</v>
+        <v>14.83369588298146</v>
       </c>
       <c r="E7" t="n">
-        <v>14.45608608192728</v>
+        <v>14.4560860819273</v>
       </c>
       <c r="F7" t="n">
         <v>14.99293829635265</v>
@@ -1904,43 +1904,43 @@
         <v>15.60799190135424</v>
       </c>
       <c r="H7" t="n">
-        <v>15.48001705872355</v>
+        <v>15.48001705872358</v>
       </c>
       <c r="I7" t="n">
-        <v>15.90277934747422</v>
+        <v>15.90277934747423</v>
       </c>
       <c r="J7" t="n">
-        <v>15.45524757245599</v>
+        <v>15.455247572456</v>
       </c>
       <c r="K7" t="n">
-        <v>15.66708539754556</v>
+        <v>15.66708539754555</v>
       </c>
       <c r="L7" t="n">
-        <v>15.31607227674615</v>
+        <v>15.31607227674614</v>
       </c>
       <c r="M7" t="n">
         <v>15.31904769605126</v>
       </c>
       <c r="N7" t="n">
-        <v>15.24907918043565</v>
+        <v>15.24907918043567</v>
       </c>
       <c r="O7" t="n">
         <v>15.39211971486075</v>
       </c>
       <c r="P7" t="n">
-        <v>15.55501860789467</v>
+        <v>15.5550186078947</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.54863753383158</v>
+        <v>15.54863753383159</v>
       </c>
       <c r="R7" t="n">
-        <v>15.7197678644425</v>
+        <v>15.71976786444251</v>
       </c>
       <c r="S7" t="n">
-        <v>15.43108335339876</v>
+        <v>15.43108335339875</v>
       </c>
       <c r="T7" t="n">
-        <v>14.89720819420547</v>
+        <v>14.89720819420548</v>
       </c>
       <c r="U7" t="n">
         <v>15.66336512752602</v>
@@ -1949,7 +1949,7 @@
         <v>15.28434472887654</v>
       </c>
       <c r="W7" t="n">
-        <v>16.7335140613307</v>
+        <v>16.73351406133067</v>
       </c>
       <c r="X7" t="n">
         <v>17.99659188371228</v>
@@ -1958,13 +1958,13 @@
         <v>17.67814786180969</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.15211007995951</v>
+        <v>15.15211007995953</v>
       </c>
       <c r="AA7" t="n">
-        <v>16.07693471552156</v>
+        <v>16.07693471552157</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.03765152110174</v>
+        <v>15.03765152110175</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.64530043570153</v>
+        <v>27.64530043570156</v>
       </c>
       <c r="C8" t="n">
-        <v>36.8246894807062</v>
+        <v>36.82468948070624</v>
       </c>
       <c r="D8" t="n">
-        <v>37.01810000807069</v>
+        <v>37.01810000807075</v>
       </c>
       <c r="E8" t="n">
-        <v>31.12893892510811</v>
+        <v>31.12893892510819</v>
       </c>
       <c r="F8" t="n">
-        <v>28.43898791972392</v>
+        <v>28.43898791972397</v>
       </c>
       <c r="G8" t="n">
-        <v>39.93872349201634</v>
+        <v>39.93872349201641</v>
       </c>
       <c r="H8" t="n">
-        <v>37.66442118381275</v>
+        <v>37.66442118381282</v>
       </c>
       <c r="I8" t="n">
-        <v>38.08718347256346</v>
+        <v>38.08718347256355</v>
       </c>
       <c r="J8" t="n">
-        <v>37.63965169754523</v>
+        <v>37.6396516975453</v>
       </c>
       <c r="K8" t="n">
-        <v>37.85148952263474</v>
+        <v>37.85148952263485</v>
       </c>
       <c r="L8" t="n">
-        <v>37.50047640183536</v>
+        <v>37.50047640183544</v>
       </c>
       <c r="M8" t="n">
-        <v>37.50345182114064</v>
+        <v>37.50345182114071</v>
       </c>
       <c r="N8" t="n">
-        <v>29.4098006961697</v>
+        <v>29.40980069616976</v>
       </c>
       <c r="O8" t="n">
-        <v>31.75790038713172</v>
+        <v>31.75790038713177</v>
       </c>
       <c r="P8" t="n">
-        <v>31.38030597836362</v>
+        <v>31.3803059783637</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.34794824834845</v>
+        <v>25.34794824834848</v>
       </c>
       <c r="R8" t="n">
-        <v>37.90417198953169</v>
+        <v>37.90417198953181</v>
       </c>
       <c r="S8" t="n">
-        <v>37.61548747848796</v>
+        <v>37.61548747848808</v>
       </c>
       <c r="T8" t="n">
-        <v>37.08161231929468</v>
+        <v>37.08161231929472</v>
       </c>
       <c r="U8" t="n">
-        <v>32.79601452625397</v>
+        <v>32.79601452625406</v>
       </c>
       <c r="V8" t="n">
-        <v>34.63854315258745</v>
+        <v>34.63854315258752</v>
       </c>
       <c r="W8" t="n">
-        <v>38.91995243665688</v>
+        <v>38.91995243665694</v>
       </c>
       <c r="X8" t="n">
-        <v>28.74458355828461</v>
+        <v>28.74458355828465</v>
       </c>
       <c r="Y8" t="n">
-        <v>50.15244098020864</v>
+        <v>50.15244098020878</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.79333640083156</v>
+        <v>26.79333640083162</v>
       </c>
       <c r="AA8" t="n">
-        <v>38.26133884061075</v>
+        <v>38.26133884061084</v>
       </c>
       <c r="AB8" t="n">
-        <v>48.0344408631896</v>
+        <v>48.03444086318974</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.47942391297359</v>
+        <v>23.47942391297362</v>
       </c>
       <c r="C9" t="n">
-        <v>25.66108125047079</v>
+        <v>25.6610812504708</v>
       </c>
       <c r="D9" t="n">
-        <v>25.85449177783524</v>
+        <v>25.85449177783527</v>
       </c>
       <c r="E9" t="n">
-        <v>24.70298411418589</v>
+        <v>24.7029841141859</v>
       </c>
       <c r="F9" t="n">
-        <v>18.28375464195658</v>
+        <v>18.28375464195662</v>
       </c>
       <c r="G9" t="n">
-        <v>26.62878874098057</v>
+        <v>26.62878874098059</v>
       </c>
       <c r="H9" t="n">
-        <v>26.50081295357735</v>
+        <v>26.50081295357737</v>
       </c>
       <c r="I9" t="n">
-        <v>26.92357524232803</v>
+        <v>26.92357524232807</v>
       </c>
       <c r="J9" t="n">
-        <v>26.4760434673098</v>
+        <v>26.47604346730981</v>
       </c>
       <c r="K9" t="n">
-        <v>26.68788129239935</v>
+        <v>26.68788129239939</v>
       </c>
       <c r="L9" t="n">
-        <v>26.33686817159997</v>
+        <v>26.33686817159999</v>
       </c>
       <c r="M9" t="n">
-        <v>26.33984359090505</v>
+        <v>26.3398435909051</v>
       </c>
       <c r="N9" t="n">
-        <v>26.26987507528947</v>
+        <v>26.26987507528949</v>
       </c>
       <c r="O9" t="n">
         <v>27.52423542705581</v>
       </c>
       <c r="P9" t="n">
-        <v>27.92880938157748</v>
+        <v>27.9288093815775</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.56943437345793</v>
+        <v>26.56943437345791</v>
       </c>
       <c r="R9" t="n">
-        <v>26.7405637592963</v>
+        <v>26.74056375929631</v>
       </c>
       <c r="S9" t="n">
-        <v>26.45187924825256</v>
+        <v>26.45187924825258</v>
       </c>
       <c r="T9" t="n">
-        <v>25.91800408905927</v>
+        <v>25.9180040890593</v>
       </c>
       <c r="U9" t="n">
-        <v>26.68558492356743</v>
+        <v>26.68558492356745</v>
       </c>
       <c r="V9" t="n">
-        <v>30.17463073724196</v>
+        <v>30.17463073724195</v>
       </c>
       <c r="W9" t="n">
-        <v>27.75430995618451</v>
+        <v>27.75430995618453</v>
       </c>
       <c r="X9" t="n">
-        <v>29.01738777856609</v>
+        <v>29.01738777856613</v>
       </c>
       <c r="Y9" t="n">
-        <v>28.6989437566635</v>
+        <v>28.69894375666352</v>
       </c>
       <c r="Z9" t="n">
         <v>24.15124136803253</v>
       </c>
       <c r="AA9" t="n">
-        <v>27.09773061037536</v>
+        <v>27.09773061037539</v>
       </c>
       <c r="AB9" t="n">
-        <v>26.05844741595555</v>
+        <v>26.05844741595558</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.39297878595206</v>
+        <v>21.3929787859521</v>
       </c>
       <c r="C2" t="n">
-        <v>15.61080934411243</v>
+        <v>15.61080934411241</v>
       </c>
       <c r="D2" t="n">
-        <v>21.42636615328227</v>
+        <v>21.42636615328224</v>
       </c>
       <c r="E2" t="n">
-        <v>21.20462375306081</v>
+        <v>21.20462375306077</v>
       </c>
       <c r="F2" t="n">
-        <v>21.36193938223521</v>
+        <v>21.36193938223519</v>
       </c>
       <c r="G2" t="n">
-        <v>22.24874908605559</v>
+        <v>22.24874908605555</v>
       </c>
       <c r="H2" t="n">
-        <v>21.18606598425893</v>
+        <v>21.1860659842589</v>
       </c>
       <c r="I2" t="n">
-        <v>21.26269672873059</v>
+        <v>21.26269672873056</v>
       </c>
       <c r="J2" t="n">
-        <v>21.79542959961925</v>
+        <v>21.79542959961921</v>
       </c>
       <c r="K2" t="n">
-        <v>21.3571418516112</v>
+        <v>21.35714185161125</v>
       </c>
       <c r="L2" t="n">
-        <v>21.28708519290849</v>
+        <v>21.28708519290857</v>
       </c>
       <c r="M2" t="n">
-        <v>22.52873691233603</v>
+        <v>22.52873691233606</v>
       </c>
       <c r="N2" t="n">
-        <v>21.31212810209554</v>
+        <v>21.31212810209551</v>
       </c>
       <c r="O2" t="n">
-        <v>28.70519110472672</v>
+        <v>28.70519110472678</v>
       </c>
       <c r="P2" t="n">
-        <v>21.69990422600758</v>
+        <v>21.69990422600759</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.27964244680674</v>
+        <v>21.27964244680678</v>
       </c>
       <c r="R2" t="n">
-        <v>21.20633668237934</v>
+        <v>21.20633668237929</v>
       </c>
       <c r="S2" t="n">
-        <v>21.51372978247361</v>
+        <v>21.51372978247363</v>
       </c>
       <c r="T2" t="n">
-        <v>21.26377712935965</v>
+        <v>21.2637771293596</v>
       </c>
       <c r="U2" t="n">
-        <v>24.98984996198465</v>
+        <v>24.9898499619847</v>
       </c>
       <c r="V2" t="n">
         <v>21.30150396745816</v>
       </c>
       <c r="W2" t="n">
-        <v>27.03892919321734</v>
+        <v>27.03892919321735</v>
       </c>
       <c r="X2" t="n">
-        <v>21.41207112347618</v>
+        <v>21.41207112347615</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.51318299639348</v>
+        <v>21.51318299639345</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.75177809148661</v>
+        <v>27.75177809148667</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.38098762997768</v>
+        <v>21.38098762997766</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.72817957619731</v>
+        <v>22.72817957619778</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.90082333597245</v>
+        <v>21.99287338079382</v>
       </c>
       <c r="C3" t="n">
-        <v>11.15406247304747</v>
+        <v>11.19110108610307</v>
       </c>
       <c r="D3" t="n">
-        <v>22.15358636785578</v>
+        <v>22.25522127406964</v>
       </c>
       <c r="E3" t="n">
-        <v>20.54904615913479</v>
+        <v>20.5917831234101</v>
       </c>
       <c r="F3" t="n">
-        <v>21.69403982441565</v>
+        <v>21.77962799637405</v>
       </c>
       <c r="G3" t="n">
-        <v>27.99194901657789</v>
+        <v>28.29812308560635</v>
       </c>
       <c r="H3" t="n">
-        <v>20.43581103441748</v>
+        <v>20.47655578198592</v>
       </c>
       <c r="I3" t="n">
-        <v>20.98279567373222</v>
+        <v>21.04294126199065</v>
       </c>
       <c r="J3" t="n">
-        <v>24.77518308696312</v>
+        <v>24.9688074036322</v>
       </c>
       <c r="K3" t="n">
-        <v>21.65471786326329</v>
+        <v>21.73868529891649</v>
       </c>
       <c r="L3" t="n">
-        <v>21.15190531835617</v>
+        <v>21.21775854472894</v>
       </c>
       <c r="M3" t="n">
-        <v>30.83797377213795</v>
+        <v>31.25350563543024</v>
       </c>
       <c r="N3" t="n">
-        <v>21.3332359940166</v>
+        <v>21.40564537299214</v>
       </c>
       <c r="O3" t="n">
-        <v>34.34070430910479</v>
+        <v>34.4496946045323</v>
       </c>
       <c r="P3" t="n">
-        <v>24.08483577796165</v>
+        <v>24.25333430587241</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.10165574168797</v>
+        <v>21.1659219829745</v>
       </c>
       <c r="R3" t="n">
-        <v>20.57973000117148</v>
+        <v>20.62558763218789</v>
       </c>
       <c r="S3" t="n">
-        <v>22.76264349499526</v>
+        <v>22.88519707768512</v>
       </c>
       <c r="T3" t="n">
-        <v>20.98997639282362</v>
+        <v>21.05034848760789</v>
       </c>
       <c r="U3" t="n">
-        <v>29.05515223363288</v>
+        <v>29.20010765200301</v>
       </c>
       <c r="V3" t="n">
-        <v>21.25199330264295</v>
+        <v>21.32125726770734</v>
       </c>
       <c r="W3" t="n">
-        <v>31.76494017137207</v>
+        <v>31.88219627367545</v>
       </c>
       <c r="X3" t="n">
-        <v>22.04943541394958</v>
+        <v>22.14736644764503</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.76647314872271</v>
+        <v>22.88954766533946</v>
       </c>
       <c r="Z3" t="n">
-        <v>32.69443844201624</v>
+        <v>32.80009748296708</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.82337380192557</v>
+        <v>21.91302296446057</v>
       </c>
       <c r="AB3" t="n">
-        <v>31.42661203872743</v>
+        <v>31.85573049698</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.06243202165174</v>
+        <v>14.06243202165171</v>
       </c>
       <c r="C4" t="n">
         <v>11.56705249230071</v>
       </c>
       <c r="D4" t="n">
-        <v>14.43955769459424</v>
+        <v>14.43955769459422</v>
       </c>
       <c r="E4" t="n">
-        <v>11.93487527754887</v>
+        <v>11.93487527754886</v>
       </c>
       <c r="F4" t="n">
         <v>13.71182767783873</v>
       </c>
       <c r="G4" t="n">
-        <v>23.72875123510869</v>
+        <v>23.72875123510867</v>
       </c>
       <c r="H4" t="n">
-        <v>11.72525674193626</v>
+        <v>11.72525674193625</v>
       </c>
       <c r="I4" t="n">
         <v>12.59083625262781</v>
       </c>
       <c r="J4" t="n">
-        <v>18.5761405504051</v>
+        <v>18.57614055040514</v>
       </c>
       <c r="K4" t="n">
-        <v>13.65763736246726</v>
+        <v>13.65763736246725</v>
       </c>
       <c r="L4" t="n">
-        <v>12.86631517476489</v>
+        <v>12.86631517476522</v>
       </c>
       <c r="M4" t="n">
         <v>28.33548558678973</v>
       </c>
       <c r="N4" t="n">
-        <v>13.14918635434016</v>
+        <v>13.14918635434014</v>
       </c>
       <c r="O4" t="n">
-        <v>14.83205631368906</v>
+        <v>14.83205631368905</v>
       </c>
       <c r="P4" t="n">
-        <v>17.5292960597568</v>
+        <v>17.52929605975678</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.78224593371329</v>
+        <v>12.78224593371332</v>
       </c>
       <c r="R4" t="n">
-        <v>11.95422360218807</v>
+        <v>11.95422360218808</v>
       </c>
       <c r="S4" t="n">
-        <v>15.42637007556536</v>
+        <v>15.42637007556534</v>
       </c>
       <c r="T4" t="n">
-        <v>12.60303987474184</v>
+        <v>12.60303987474185</v>
       </c>
       <c r="U4" t="n">
-        <v>16.26396828507982</v>
+        <v>16.26396828507981</v>
       </c>
       <c r="V4" t="n">
         <v>12.82309446192706</v>
       </c>
       <c r="W4" t="n">
-        <v>15.16678512448522</v>
+        <v>15.16678512448521</v>
       </c>
       <c r="X4" t="n">
-        <v>14.27808875689568</v>
+        <v>14.27808875689577</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.2611354376346</v>
+        <v>15.26113543763459</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.67302246010592</v>
+        <v>14.67302246010593</v>
       </c>
       <c r="AA4" t="n">
         <v>13.92698639871672</v>
       </c>
       <c r="AB4" t="n">
-        <v>29.00225208419326</v>
+        <v>29.00225208419323</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.86751252353439</v>
+        <v>75.86751252353926</v>
       </c>
       <c r="C5" t="n">
-        <v>34.32002911253267</v>
+        <v>34.32002911253264</v>
       </c>
       <c r="D5" t="n">
-        <v>91.04887680303129</v>
+        <v>91.04887680303108</v>
       </c>
       <c r="E5" t="n">
-        <v>31.48101226945077</v>
+        <v>31.48101226945184</v>
       </c>
       <c r="F5" t="n">
-        <v>77.43948485646797</v>
+        <v>77.43948485646803</v>
       </c>
       <c r="G5" t="n">
-        <v>249.4332485754639</v>
+        <v>249.4332485754636</v>
       </c>
       <c r="H5" t="n">
         <v>38.20269374522474</v>
       </c>
       <c r="I5" t="n">
-        <v>54.6063595873996</v>
+        <v>54.60635958740002</v>
       </c>
       <c r="J5" t="n">
-        <v>162.9273027860839</v>
+        <v>162.9273027860849</v>
       </c>
       <c r="K5" t="n">
-        <v>73.5886351104306</v>
+        <v>73.58863511043066</v>
       </c>
       <c r="L5" t="n">
-        <v>57.0610005291497</v>
+        <v>57.06100052915806</v>
       </c>
       <c r="M5" t="n">
-        <v>371.6333814216433</v>
+        <v>371.6333814216426</v>
       </c>
       <c r="N5" t="n">
-        <v>63.85448785955532</v>
+        <v>63.85448785955542</v>
       </c>
       <c r="O5" t="n">
-        <v>88.14947513042242</v>
+        <v>88.14947513042233</v>
       </c>
       <c r="P5" t="n">
-        <v>137.7871256982372</v>
+        <v>137.787125698237</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.06740261259991</v>
+        <v>57.0674026126002</v>
       </c>
       <c r="R5" t="n">
-        <v>42.1126294302547</v>
+        <v>42.11262943025467</v>
       </c>
       <c r="S5" t="n">
-        <v>101.6646632831861</v>
+        <v>101.664663283185</v>
       </c>
       <c r="T5" t="n">
-        <v>54.54225813566679</v>
+        <v>54.54225813566676</v>
       </c>
       <c r="U5" t="n">
-        <v>122.2364071118484</v>
+        <v>122.2364071118482</v>
       </c>
       <c r="V5" t="n">
-        <v>58.36629390326753</v>
+        <v>58.36629390326759</v>
       </c>
       <c r="W5" t="n">
-        <v>101.2210686187663</v>
+        <v>101.2210686187665</v>
       </c>
       <c r="X5" t="n">
-        <v>86.81311663655421</v>
+        <v>86.81311663655558</v>
       </c>
       <c r="Y5" t="n">
         <v>105.8481053438998</v>
       </c>
       <c r="Z5" t="n">
-        <v>87.79080517341438</v>
+        <v>87.79080517341637</v>
       </c>
       <c r="AA5" t="n">
-        <v>77.82911854454474</v>
+        <v>77.82911854454514</v>
       </c>
       <c r="AB5" t="n">
-        <v>399.2166060250481</v>
+        <v>399.2166060250463</v>
       </c>
     </row>
     <row r="6">
@@ -2658,64 +2658,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.7238540208416</v>
+        <v>32.7238540208417</v>
       </c>
       <c r="C6" t="n">
-        <v>44.07337616583381</v>
+        <v>44.0733761658338</v>
       </c>
       <c r="D6" t="n">
         <v>33.10097969378415</v>
       </c>
       <c r="E6" t="n">
-        <v>44.4411989510819</v>
+        <v>44.44119895108197</v>
       </c>
       <c r="F6" t="n">
-        <v>32.37324967702865</v>
+        <v>32.37324967702862</v>
       </c>
       <c r="G6" t="n">
-        <v>56.23507490864173</v>
+        <v>56.23507490864178</v>
       </c>
       <c r="H6" t="n">
-        <v>44.23158041546935</v>
+        <v>44.2315804154694</v>
       </c>
       <c r="I6" t="n">
-        <v>45.09715992616086</v>
+        <v>45.09715992616088</v>
       </c>
       <c r="J6" t="n">
-        <v>51.08246422393815</v>
+        <v>51.08246422393823</v>
       </c>
       <c r="K6" t="n">
         <v>32.31905936165721</v>
       </c>
       <c r="L6" t="n">
-        <v>45.37263884829796</v>
+        <v>45.37263884829805</v>
       </c>
       <c r="M6" t="n">
-        <v>60.84180926032272</v>
+        <v>60.84180926032278</v>
       </c>
       <c r="N6" t="n">
-        <v>31.82204508302336</v>
+        <v>31.82204508302335</v>
       </c>
       <c r="O6" t="n">
-        <v>33.50512565122019</v>
+        <v>33.50512565122009</v>
       </c>
       <c r="P6" t="n">
         <v>49.69268411121386</v>
       </c>
       <c r="Q6" t="n">
-        <v>31.44366793290325</v>
+        <v>31.44366793290328</v>
       </c>
       <c r="R6" t="n">
-        <v>44.4605472757211</v>
+        <v>44.46054727572117</v>
       </c>
       <c r="S6" t="n">
-        <v>34.08779207475529</v>
+        <v>34.08779207475528</v>
       </c>
       <c r="T6" t="n">
-        <v>31.26446187393169</v>
+        <v>31.26446187393173</v>
       </c>
       <c r="U6" t="n">
-        <v>35.0844487218913</v>
+        <v>35.08444872189129</v>
       </c>
       <c r="V6" t="n">
         <v>31.484516461117</v>
@@ -2724,19 +2724,19 @@
         <v>34.83273220114899</v>
       </c>
       <c r="X6" t="n">
-        <v>46.78441243042877</v>
+        <v>46.7844124304288</v>
       </c>
       <c r="Y6" t="n">
-        <v>34.92139949828697</v>
+        <v>34.92139949828687</v>
       </c>
       <c r="Z6" t="n">
-        <v>33.33444445929587</v>
+        <v>33.33444445929589</v>
       </c>
       <c r="AA6" t="n">
-        <v>46.43331007224975</v>
+        <v>46.43331007224979</v>
       </c>
       <c r="AB6" t="n">
-        <v>47.76599179391334</v>
+        <v>47.76599179391337</v>
       </c>
     </row>
     <row r="7">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.81311916740626</v>
+        <v>18.81311916740627</v>
       </c>
       <c r="C7" t="n">
-        <v>16.31773963805526</v>
+        <v>16.31773963805527</v>
       </c>
       <c r="D7" t="n">
         <v>19.19024484034878</v>
       </c>
       <c r="E7" t="n">
-        <v>16.68556242330342</v>
+        <v>16.68556242330347</v>
       </c>
       <c r="F7" t="n">
-        <v>18.46251482359329</v>
+        <v>18.4625148235933</v>
       </c>
       <c r="G7" t="n">
-        <v>28.47943838086323</v>
+        <v>28.47943838086321</v>
       </c>
       <c r="H7" t="n">
-        <v>16.4759438876908</v>
+        <v>16.47594388769081</v>
       </c>
       <c r="I7" t="n">
-        <v>17.34152339838236</v>
+        <v>17.34152339838235</v>
       </c>
       <c r="J7" t="n">
-        <v>23.32682769615965</v>
+        <v>23.32682769615968</v>
       </c>
       <c r="K7" t="n">
-        <v>18.4083245082218</v>
+        <v>18.40832450822179</v>
       </c>
       <c r="L7" t="n">
-        <v>17.61700232051955</v>
+        <v>17.6170023205194</v>
       </c>
       <c r="M7" t="n">
         <v>33.08617273254426</v>
       </c>
       <c r="N7" t="n">
-        <v>17.89987350009472</v>
+        <v>17.89987350009473</v>
       </c>
       <c r="O7" t="n">
-        <v>19.58265024435001</v>
+        <v>19.58265024434998</v>
       </c>
       <c r="P7" t="n">
-        <v>22.27988999041773</v>
+        <v>22.27988999041775</v>
       </c>
       <c r="Q7" t="n">
         <v>17.53293307946783</v>
@@ -2797,34 +2797,34 @@
         <v>16.70491074794263</v>
       </c>
       <c r="S7" t="n">
-        <v>20.17705722131993</v>
+        <v>20.17705722131994</v>
       </c>
       <c r="T7" t="n">
-        <v>17.35372702049641</v>
+        <v>17.3537270204964</v>
       </c>
       <c r="U7" t="n">
         <v>21.17008298456216</v>
       </c>
       <c r="V7" t="n">
-        <v>17.57378160768159</v>
+        <v>17.57378160768163</v>
       </c>
       <c r="W7" t="n">
-        <v>19.91747227023975</v>
+        <v>19.91747227023976</v>
       </c>
       <c r="X7" t="n">
-        <v>19.02877590265024</v>
+        <v>19.0287759026503</v>
       </c>
       <c r="Y7" t="n">
-        <v>20.17088102101071</v>
+        <v>20.1708810210107</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.42370960586048</v>
+        <v>19.42370960586052</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.67767354447125</v>
+        <v>18.67767354447126</v>
       </c>
       <c r="AB7" t="n">
-        <v>33.7529392299478</v>
+        <v>33.75293922994783</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.99802704953751</v>
+        <v>31.99802704953758</v>
       </c>
       <c r="C8" t="n">
-        <v>41.37609734831383</v>
+        <v>41.37609734831385</v>
       </c>
       <c r="D8" t="n">
-        <v>44.24860255060739</v>
+        <v>44.24860255060742</v>
       </c>
       <c r="E8" t="n">
-        <v>35.42165834479484</v>
+        <v>35.42165834479493</v>
       </c>
       <c r="F8" t="n">
-        <v>33.49716742109601</v>
+        <v>33.49716742109607</v>
       </c>
       <c r="G8" t="n">
-        <v>55.99983326137459</v>
+        <v>55.99983326137466</v>
       </c>
       <c r="H8" t="n">
-        <v>41.53430159794938</v>
+        <v>41.53430159794943</v>
       </c>
       <c r="I8" t="n">
-        <v>42.39988110864097</v>
+        <v>42.399881108641</v>
       </c>
       <c r="J8" t="n">
-        <v>48.38518540641823</v>
+        <v>48.38518540641837</v>
       </c>
       <c r="K8" t="n">
-        <v>43.4666822184804</v>
+        <v>43.4666822184805</v>
       </c>
       <c r="L8" t="n">
-        <v>42.67536003077808</v>
+        <v>42.67536003077829</v>
       </c>
       <c r="M8" t="n">
-        <v>58.1445304428037</v>
+        <v>58.14453044280378</v>
       </c>
       <c r="N8" t="n">
-        <v>33.75432120886236</v>
+        <v>33.75432120886241</v>
       </c>
       <c r="O8" t="n">
-        <v>37.96650555323327</v>
+        <v>37.96650555323332</v>
       </c>
       <c r="P8" t="n">
-        <v>40.04374922668478</v>
+        <v>40.04374922668484</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.38443707191305</v>
+        <v>28.3844370719131</v>
       </c>
       <c r="R8" t="n">
-        <v>41.76326845820122</v>
+        <v>41.7632684582013</v>
       </c>
       <c r="S8" t="n">
-        <v>45.23541493157849</v>
+        <v>45.23541493157857</v>
       </c>
       <c r="T8" t="n">
-        <v>42.41208473075498</v>
+        <v>42.41208473075504</v>
       </c>
       <c r="U8" t="n">
-        <v>40.43405758473557</v>
+        <v>40.43405758473566</v>
       </c>
       <c r="V8" t="n">
-        <v>39.3839225386934</v>
+        <v>39.3839225386935</v>
       </c>
       <c r="W8" t="n">
-        <v>44.97816345435081</v>
+        <v>44.97816345435089</v>
       </c>
       <c r="X8" t="n">
-        <v>30.96850516520416</v>
+        <v>30.96850516520431</v>
       </c>
       <c r="Y8" t="n">
-        <v>57.03004954736249</v>
+        <v>57.03004954736254</v>
       </c>
       <c r="Z8" t="n">
-        <v>32.38806206153522</v>
+        <v>32.38806206153525</v>
       </c>
       <c r="AA8" t="n">
-        <v>43.73603125472987</v>
+        <v>43.73603125472994</v>
       </c>
       <c r="AB8" t="n">
-        <v>71.21410812810443</v>
+        <v>71.2141081281045</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.89847684809519</v>
+        <v>30.89847684809526</v>
       </c>
       <c r="C9" t="n">
-        <v>33.26697337396175</v>
+        <v>33.26697337396178</v>
       </c>
       <c r="D9" t="n">
-        <v>36.13947857625526</v>
+        <v>36.1394785762553</v>
       </c>
       <c r="E9" t="n">
-        <v>32.51223265843094</v>
+        <v>32.512232658431</v>
       </c>
       <c r="F9" t="n">
-        <v>24.19918804145333</v>
+        <v>24.19918804145334</v>
       </c>
       <c r="G9" t="n">
-        <v>45.42867114612677</v>
+        <v>45.42867114612685</v>
       </c>
       <c r="H9" t="n">
-        <v>33.42517762359729</v>
+        <v>33.42517762359731</v>
       </c>
       <c r="I9" t="n">
-        <v>34.29075713428884</v>
+        <v>34.2907571342889</v>
       </c>
       <c r="J9" t="n">
-        <v>40.27606143206614</v>
+        <v>40.27606143206621</v>
       </c>
       <c r="K9" t="n">
-        <v>35.35755824412828</v>
+        <v>35.35755824412833</v>
       </c>
       <c r="L9" t="n">
-        <v>34.56623605642599</v>
+        <v>34.56623605642603</v>
       </c>
       <c r="M9" t="n">
-        <v>50.03540646845077</v>
+        <v>50.03540646845079</v>
       </c>
       <c r="N9" t="n">
-        <v>34.84910723600117</v>
+        <v>34.84910723600125</v>
       </c>
       <c r="O9" t="n">
-        <v>38.1438580590398</v>
+        <v>38.14385805903979</v>
       </c>
       <c r="P9" t="n">
-        <v>41.19165444883517</v>
+        <v>41.19165444883522</v>
       </c>
       <c r="Q9" t="n">
-        <v>34.48216584473138</v>
+        <v>34.48216584473145</v>
       </c>
       <c r="R9" t="n">
-        <v>33.65414448384909</v>
+        <v>33.65414448384914</v>
       </c>
       <c r="S9" t="n">
-        <v>37.12629095722637</v>
+        <v>37.12629095722649</v>
       </c>
       <c r="T9" t="n">
-        <v>34.30296075640288</v>
+        <v>34.30296075640294</v>
       </c>
       <c r="U9" t="n">
         <v>38.12294760436242</v>
       </c>
       <c r="V9" t="n">
-        <v>40.13581796537215</v>
+        <v>40.1358179653722</v>
       </c>
       <c r="W9" t="n">
-        <v>36.8667060061462</v>
+        <v>36.86670600614626</v>
       </c>
       <c r="X9" t="n">
-        <v>35.97800963855673</v>
+        <v>35.97800963855684</v>
       </c>
       <c r="Y9" t="n">
-        <v>37.1201147569172</v>
+        <v>37.12011475691722</v>
       </c>
       <c r="Z9" t="n">
-        <v>33.4404582077736</v>
+        <v>33.44045820777366</v>
       </c>
       <c r="AA9" t="n">
-        <v>35.62690728037774</v>
+        <v>35.62690728037781</v>
       </c>
       <c r="AB9" t="n">
-        <v>50.70217296585429</v>
+        <v>50.70217296585426</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.33609507099736</v>
+        <v>21.33609507099725</v>
       </c>
       <c r="C2" t="n">
-        <v>15.55223279818347</v>
+        <v>15.55223279818346</v>
       </c>
       <c r="D2" t="n">
-        <v>21.42175058188122</v>
+        <v>21.42175058188113</v>
       </c>
       <c r="E2" t="n">
-        <v>21.14101675082071</v>
+        <v>21.14101675082064</v>
       </c>
       <c r="F2" t="n">
-        <v>21.39682412409626</v>
+        <v>21.39682412409615</v>
       </c>
       <c r="G2" t="n">
-        <v>22.12621821145231</v>
+        <v>22.12621821145223</v>
       </c>
       <c r="H2" t="n">
-        <v>21.13345837525373</v>
+        <v>21.13345837525362</v>
       </c>
       <c r="I2" t="n">
-        <v>21.31021303450628</v>
+        <v>21.31021303450618</v>
       </c>
       <c r="J2" t="n">
-        <v>21.70744169158724</v>
+        <v>21.70744169158714</v>
       </c>
       <c r="K2" t="n">
-        <v>21.33340980969799</v>
+        <v>21.33340980969788</v>
       </c>
       <c r="L2" t="n">
-        <v>21.21454925439267</v>
+        <v>21.21454925439262</v>
       </c>
       <c r="M2" t="n">
-        <v>22.28641842928136</v>
+        <v>22.28641842928134</v>
       </c>
       <c r="N2" t="n">
-        <v>21.21884014275859</v>
+        <v>21.21884014275851</v>
       </c>
       <c r="O2" t="n">
-        <v>28.56038098358269</v>
+        <v>28.56038098358265</v>
       </c>
       <c r="P2" t="n">
-        <v>21.63667665207281</v>
+        <v>21.63667665207271</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.24788701599098</v>
+        <v>21.24788701599088</v>
       </c>
       <c r="R2" t="n">
-        <v>21.13964843235928</v>
+        <v>21.13964843235916</v>
       </c>
       <c r="S2" t="n">
-        <v>21.43239223172102</v>
+        <v>21.43239223172089</v>
       </c>
       <c r="T2" t="n">
-        <v>21.21038909680097</v>
+        <v>21.21038909680087</v>
       </c>
       <c r="U2" t="n">
-        <v>24.64494246052146</v>
+        <v>24.64494246052135</v>
       </c>
       <c r="V2" t="n">
-        <v>21.29778444850796</v>
+        <v>21.29778444850787</v>
       </c>
       <c r="W2" t="n">
-        <v>26.890481728739</v>
+        <v>26.89048172873896</v>
       </c>
       <c r="X2" t="n">
-        <v>21.41797695775226</v>
+        <v>21.41797695775216</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.72067012070701</v>
+        <v>21.72067012070691</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.68810117945246</v>
+        <v>27.6881011794524</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.26733066110878</v>
+        <v>21.26733066110871</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.5638046858674</v>
+        <v>22.56380468586737</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.84475805482018</v>
+        <v>21.93629323428736</v>
       </c>
       <c r="C3" t="n">
-        <v>11.09560653823011</v>
+        <v>11.1321290835478</v>
       </c>
       <c r="D3" t="n">
-        <v>22.46980118154181</v>
+        <v>22.58418294942351</v>
       </c>
       <c r="E3" t="n">
-        <v>20.44397394798668</v>
+        <v>20.48450212807392</v>
       </c>
       <c r="F3" t="n">
-        <v>22.29232706736928</v>
+        <v>22.40080347124237</v>
       </c>
       <c r="G3" t="n">
-        <v>27.46236938210271</v>
+        <v>27.7516055024068</v>
       </c>
       <c r="H3" t="n">
-        <v>20.40910130031829</v>
+        <v>20.4504083251663</v>
       </c>
       <c r="I3" t="n">
-        <v>21.67338814101012</v>
+        <v>21.75956724725999</v>
       </c>
       <c r="J3" t="n">
-        <v>24.49520937466487</v>
+        <v>24.68060920684244</v>
       </c>
       <c r="K3" t="n">
-        <v>21.83167303274642</v>
+        <v>21.92352202833473</v>
       </c>
       <c r="L3" t="n">
-        <v>20.98319426346157</v>
+        <v>21.04458992301743</v>
       </c>
       <c r="M3" t="n">
-        <v>29.46667963863116</v>
+        <v>29.83494790003905</v>
       </c>
       <c r="N3" t="n">
-        <v>21.01607664400517</v>
+        <v>21.07875754225517</v>
       </c>
       <c r="O3" t="n">
-        <v>33.97789449886231</v>
+        <v>34.07902944206467</v>
       </c>
       <c r="P3" t="n">
-        <v>23.98073496660665</v>
+        <v>24.14713703521081</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.22334512879059</v>
+        <v>21.29345194871204</v>
       </c>
       <c r="R3" t="n">
-        <v>20.45231722605227</v>
+        <v>20.49514635007634</v>
       </c>
       <c r="S3" t="n">
-        <v>22.53074146626115</v>
+        <v>22.64664491928571</v>
       </c>
       <c r="T3" t="n">
-        <v>20.95789421160693</v>
+        <v>21.01862805980176</v>
       </c>
       <c r="U3" t="n">
-        <v>27.21585425092031</v>
+        <v>27.3003290763269</v>
       </c>
       <c r="V3" t="n">
-        <v>21.5718730204359</v>
+        <v>21.65393665041959</v>
       </c>
       <c r="W3" t="n">
-        <v>31.32473757787255</v>
+        <v>31.43081725632182</v>
       </c>
       <c r="X3" t="n">
-        <v>22.44084540194357</v>
+        <v>22.55418045970159</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.59614278008321</v>
+        <v>24.78543175091301</v>
       </c>
       <c r="Z3" t="n">
-        <v>32.63632761214301</v>
+        <v>32.74216253096994</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.36111727583307</v>
+        <v>21.43592528043325</v>
       </c>
       <c r="AB3" t="n">
-        <v>30.60966652241986</v>
+        <v>31.01134608062745</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.96864294414199</v>
+        <v>13.968642944142</v>
       </c>
       <c r="C4" t="n">
-        <v>11.4736700256616</v>
+        <v>11.47367002566161</v>
       </c>
       <c r="D4" t="n">
-        <v>14.93616134305687</v>
+        <v>14.93616134305688</v>
       </c>
       <c r="E4" t="n">
         <v>11.76514357728575</v>
       </c>
       <c r="F4" t="n">
-        <v>14.65460553563852</v>
+        <v>14.6546055356385</v>
       </c>
       <c r="G4" t="n">
-        <v>22.89344729018288</v>
+        <v>22.89344729018292</v>
       </c>
       <c r="H4" t="n">
         <v>11.67976824823217</v>
       </c>
       <c r="I4" t="n">
-        <v>13.67629343565023</v>
+        <v>13.67629343565024</v>
       </c>
       <c r="J4" t="n">
-        <v>18.13155349727785</v>
+        <v>18.1315534972778</v>
       </c>
       <c r="K4" t="n">
-        <v>13.93831168248425</v>
+        <v>13.93831168248424</v>
       </c>
       <c r="L4" t="n">
-        <v>12.59572703175396</v>
+        <v>12.595727031754</v>
       </c>
       <c r="M4" t="n">
         <v>26.17077179612262</v>
       </c>
       <c r="N4" t="n">
-        <v>12.64419458975321</v>
+        <v>12.6441945897532</v>
       </c>
       <c r="O4" t="n">
         <v>14.40624999660987</v>
       </c>
       <c r="P4" t="n">
-        <v>17.36385017674809</v>
+        <v>17.36385017674805</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.97229238513491</v>
+        <v>12.97229238513492</v>
       </c>
       <c r="R4" t="n">
-        <v>11.74968779080615</v>
+        <v>11.74968779080616</v>
       </c>
       <c r="S4" t="n">
-        <v>15.05636367339809</v>
+        <v>15.05636367339811</v>
       </c>
       <c r="T4" t="n">
         <v>12.54873613798875</v>
       </c>
       <c r="U4" t="n">
-        <v>13.49596531714747</v>
+        <v>13.49596531714742</v>
       </c>
       <c r="V4" t="n">
-        <v>13.33346691970359</v>
+        <v>13.33346691970358</v>
       </c>
       <c r="W4" t="n">
-        <v>14.59541629448627</v>
+        <v>14.59541629448626</v>
       </c>
       <c r="X4" t="n">
-        <v>14.89353652256728</v>
+        <v>14.8935365225673</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.17390922031512</v>
+        <v>18.17390922031514</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.61044024826201</v>
+        <v>14.61044024826203</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.19191730125906</v>
+        <v>13.19191730125907</v>
       </c>
       <c r="AB4" t="n">
-        <v>27.71163124104368</v>
+        <v>27.71163124104369</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.52743831288466</v>
+        <v>71.5274383128847</v>
       </c>
       <c r="C5" t="n">
         <v>32.73255227166933</v>
       </c>
       <c r="D5" t="n">
-        <v>95.74729557622445</v>
+        <v>95.74729557622457</v>
       </c>
       <c r="E5" t="n">
         <v>28.14979335285621</v>
       </c>
       <c r="F5" t="n">
-        <v>90.98893198737119</v>
+        <v>90.98893198737109</v>
       </c>
       <c r="G5" t="n">
-        <v>218.2163692558403</v>
+        <v>218.2163692558389</v>
       </c>
       <c r="H5" t="n">
-        <v>36.52329597917418</v>
+        <v>36.52329597917411</v>
       </c>
       <c r="I5" t="n">
-        <v>73.27581654550889</v>
+        <v>73.27581654550885</v>
       </c>
       <c r="J5" t="n">
-        <v>145.7514119764385</v>
+        <v>145.7514119764384</v>
       </c>
       <c r="K5" t="n">
-        <v>74.14169353460844</v>
+        <v>74.14169353460836</v>
       </c>
       <c r="L5" t="n">
-        <v>50.31033004962315</v>
+        <v>50.31033004962347</v>
       </c>
       <c r="M5" t="n">
-        <v>309.0750229888297</v>
+        <v>309.0750229888303</v>
       </c>
       <c r="N5" t="n">
-        <v>52.33776005304276</v>
+        <v>52.33776005304274</v>
       </c>
       <c r="O5" t="n">
-        <v>76.9756410083763</v>
+        <v>76.97564100837613</v>
       </c>
       <c r="P5" t="n">
-        <v>126.7635865956609</v>
+        <v>126.7635865956607</v>
       </c>
       <c r="Q5" t="n">
         <v>58.11972415555009</v>
       </c>
       <c r="R5" t="n">
-        <v>37.26098116667409</v>
+        <v>37.26098116667407</v>
       </c>
       <c r="S5" t="n">
-        <v>90.09487483002047</v>
+        <v>90.09487483002036</v>
       </c>
       <c r="T5" t="n">
-        <v>51.7548468974517</v>
+        <v>51.75484689745183</v>
       </c>
       <c r="U5" t="n">
-        <v>67.75570303477835</v>
+        <v>67.75570303477572</v>
       </c>
       <c r="V5" t="n">
-        <v>63.95107790098623</v>
+        <v>63.95107790098567</v>
       </c>
       <c r="W5" t="n">
-        <v>86.24815289759084</v>
+        <v>86.24815289759121</v>
       </c>
       <c r="X5" t="n">
-        <v>93.94491443004941</v>
+        <v>93.94491443004898</v>
       </c>
       <c r="Y5" t="n">
-        <v>151.8053676215575</v>
+        <v>151.8053676215577</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.12715154918456</v>
+        <v>80.1271515491848</v>
       </c>
       <c r="AA5" t="n">
-        <v>61.48690410415675</v>
+        <v>61.48690410415644</v>
       </c>
       <c r="AB5" t="n">
-        <v>351.0560267289533</v>
+        <v>351.0560267289536</v>
       </c>
     </row>
     <row r="6">
@@ -3518,22 +3518,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.23303261436202</v>
+        <v>44.23303261436199</v>
       </c>
       <c r="C6" t="n">
         <v>28.88799468993228</v>
       </c>
       <c r="D6" t="n">
-        <v>45.2005510132768</v>
+        <v>45.20055101327681</v>
       </c>
       <c r="E6" t="n">
         <v>42.02953324750572</v>
       </c>
       <c r="F6" t="n">
-        <v>32.0689301999092</v>
+        <v>32.06893019990921</v>
       </c>
       <c r="G6" t="n">
-        <v>40.30777195445356</v>
+        <v>40.30777195445354</v>
       </c>
       <c r="H6" t="n">
         <v>29.09409291250281</v>
@@ -3542,25 +3542,25 @@
         <v>31.09061809992097</v>
       </c>
       <c r="J6" t="n">
-        <v>48.39594316749779</v>
+        <v>48.39594316749775</v>
       </c>
       <c r="K6" t="n">
-        <v>44.20270135270421</v>
+        <v>44.20270135270422</v>
       </c>
       <c r="L6" t="n">
-        <v>42.86011670197402</v>
+        <v>42.86011670197406</v>
       </c>
       <c r="M6" t="n">
-        <v>43.5850964603933</v>
+        <v>43.58509646039332</v>
       </c>
       <c r="N6" t="n">
-        <v>30.06935819243503</v>
+        <v>30.06935819243499</v>
       </c>
       <c r="O6" t="n">
-        <v>44.35148040381185</v>
+        <v>44.35148040381186</v>
       </c>
       <c r="P6" t="n">
-        <v>47.30917494593841</v>
+        <v>47.30917494593842</v>
       </c>
       <c r="Q6" t="n">
         <v>43.23668205535489</v>
@@ -3572,13 +3572,13 @@
         <v>45.32075334361812</v>
       </c>
       <c r="T6" t="n">
-        <v>29.96306080225941</v>
+        <v>29.96306080225943</v>
       </c>
       <c r="U6" t="n">
-        <v>31.04897580497886</v>
+        <v>31.04897580497882</v>
       </c>
       <c r="V6" t="n">
-        <v>43.59785658992364</v>
+        <v>43.59785658992363</v>
       </c>
       <c r="W6" t="n">
         <v>44.54060665299995</v>
@@ -3587,16 +3587,16 @@
         <v>32.30786118683805</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.51230668195692</v>
+        <v>36.51230668195686</v>
       </c>
       <c r="Z6" t="n">
-        <v>44.874829918482</v>
+        <v>44.87482991848201</v>
       </c>
       <c r="AA6" t="n">
-        <v>43.45630697147912</v>
+        <v>43.45630697147915</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.21512480229499</v>
+        <v>45.21512480229502</v>
       </c>
     </row>
     <row r="7">
@@ -3606,43 +3606,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.3285625326268</v>
+        <v>18.32856253262682</v>
       </c>
       <c r="C7" t="n">
-        <v>15.83358961414643</v>
+        <v>15.83358961414644</v>
       </c>
       <c r="D7" t="n">
         <v>19.2960809315417</v>
       </c>
       <c r="E7" t="n">
-        <v>16.12506316577057</v>
+        <v>16.12506316577059</v>
       </c>
       <c r="F7" t="n">
-        <v>19.01452512412335</v>
+        <v>19.01452512412336</v>
       </c>
       <c r="G7" t="n">
-        <v>27.25336687866771</v>
+        <v>27.25336687866776</v>
       </c>
       <c r="H7" t="n">
-        <v>16.03968783671701</v>
+        <v>16.03968783671702</v>
       </c>
       <c r="I7" t="n">
-        <v>18.03621302413506</v>
+        <v>18.03621302413507</v>
       </c>
       <c r="J7" t="n">
-        <v>22.49147308576267</v>
+        <v>22.49147308576273</v>
       </c>
       <c r="K7" t="n">
-        <v>18.29823127096908</v>
+        <v>18.29823127096907</v>
       </c>
       <c r="L7" t="n">
-        <v>16.95564662023881</v>
+        <v>16.95564662023882</v>
       </c>
       <c r="M7" t="n">
-        <v>30.53069138460746</v>
+        <v>30.53069138460747</v>
       </c>
       <c r="N7" t="n">
-        <v>17.00411417823802</v>
+        <v>17.00411417823804</v>
       </c>
       <c r="O7" t="n">
         <v>18.76608278765156</v>
@@ -3651,10 +3651,10 @@
         <v>21.72368296778976</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.33221197361974</v>
+        <v>17.33221197361976</v>
       </c>
       <c r="R7" t="n">
-        <v>16.10960737929098</v>
+        <v>16.109607379291</v>
       </c>
       <c r="S7" t="n">
         <v>19.41628326188295</v>
@@ -3663,28 +3663,28 @@
         <v>16.90865572647357</v>
       </c>
       <c r="U7" t="n">
-        <v>17.99097362492522</v>
+        <v>17.99097362492505</v>
       </c>
       <c r="V7" t="n">
-        <v>17.69338650818844</v>
+        <v>17.69338650818843</v>
       </c>
       <c r="W7" t="n">
-        <v>18.95533588297108</v>
+        <v>18.95533588297111</v>
       </c>
       <c r="X7" t="n">
-        <v>19.25345611105211</v>
+        <v>19.2534561110521</v>
       </c>
       <c r="Y7" t="n">
         <v>22.67251463236067</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.97035983674683</v>
+        <v>18.97035983674689</v>
       </c>
       <c r="AA7" t="n">
         <v>17.55183688974391</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.07155082952852</v>
+        <v>32.07155082952856</v>
       </c>
     </row>
     <row r="8">
@@ -3694,76 +3694,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.57085374690757</v>
+        <v>30.57085374690756</v>
       </c>
       <c r="C8" t="n">
-        <v>39.05628883503586</v>
+        <v>39.0562888350359</v>
       </c>
       <c r="D8" t="n">
         <v>42.51878015243115</v>
       </c>
       <c r="E8" t="n">
-        <v>33.50101902477381</v>
+        <v>33.50101902477383</v>
       </c>
       <c r="F8" t="n">
         <v>32.96743557517703</v>
       </c>
       <c r="G8" t="n">
-        <v>52.75292523048871</v>
+        <v>52.75292523048864</v>
       </c>
       <c r="H8" t="n">
-        <v>39.26238705760643</v>
+        <v>39.26238705760642</v>
       </c>
       <c r="I8" t="n">
-        <v>41.25891224502448</v>
+        <v>41.25891224502453</v>
       </c>
       <c r="J8" t="n">
         <v>45.7141723066521</v>
       </c>
       <c r="K8" t="n">
-        <v>41.52093049185851</v>
+        <v>41.52093049185854</v>
       </c>
       <c r="L8" t="n">
-        <v>40.17834584112832</v>
+        <v>40.17834584112828</v>
       </c>
       <c r="M8" t="n">
-        <v>53.75339060549843</v>
+        <v>53.75339060549847</v>
       </c>
       <c r="N8" t="n">
-        <v>31.71516021194316</v>
+        <v>31.71516021194317</v>
       </c>
       <c r="O8" t="n">
-        <v>35.81629182046146</v>
+        <v>35.81629182046149</v>
       </c>
       <c r="P8" t="n">
-        <v>38.20052790352675</v>
+        <v>38.20052790352683</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.41660239883743</v>
+        <v>27.41660239883745</v>
       </c>
       <c r="R8" t="n">
-        <v>39.3323066001804</v>
+        <v>39.33230660018042</v>
       </c>
       <c r="S8" t="n">
-        <v>42.63898248277235</v>
+        <v>42.63898248277239</v>
       </c>
       <c r="T8" t="n">
         <v>40.13135494736301</v>
       </c>
       <c r="U8" t="n">
-        <v>35.855158954723</v>
+        <v>35.85515895472302</v>
       </c>
       <c r="V8" t="n">
-        <v>37.91197413340582</v>
+        <v>37.91197413340576</v>
       </c>
       <c r="W8" t="n">
-        <v>42.18019306936232</v>
+        <v>42.18019306936229</v>
       </c>
       <c r="X8" t="n">
-        <v>30.34422274890862</v>
+        <v>30.34422274890861</v>
       </c>
       <c r="Y8" t="n">
-        <v>56.80812978848879</v>
+        <v>56.80812978848885</v>
       </c>
       <c r="Z8" t="n">
         <v>31.0086843348965</v>
@@ -3772,7 +3772,7 @@
         <v>40.77453611063336</v>
       </c>
       <c r="AB8" t="n">
-        <v>66.76420438076087</v>
+        <v>66.76420438076096</v>
       </c>
     </row>
     <row r="9">
@@ -3782,64 +3782,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.5955578256709</v>
+        <v>28.59555782567094</v>
       </c>
       <c r="C9" t="n">
-        <v>30.33356893450379</v>
+        <v>30.3335689345038</v>
       </c>
       <c r="D9" t="n">
-        <v>33.79606025189911</v>
+        <v>33.7960602518991</v>
       </c>
       <c r="E9" t="n">
-        <v>29.64808665629443</v>
+        <v>29.64808665629447</v>
       </c>
       <c r="F9" t="n">
-        <v>23.75632161939516</v>
+        <v>23.75632161939518</v>
       </c>
       <c r="G9" t="n">
-        <v>41.75334570194534</v>
+        <v>41.75334570194529</v>
       </c>
       <c r="H9" t="n">
-        <v>30.53966715707439</v>
+        <v>30.53966715707436</v>
       </c>
       <c r="I9" t="n">
         <v>32.53619234449246</v>
       </c>
       <c r="J9" t="n">
-        <v>36.99145240612005</v>
+        <v>36.99145240612006</v>
       </c>
       <c r="K9" t="n">
-        <v>32.79821059132646</v>
+        <v>32.79821059132645</v>
       </c>
       <c r="L9" t="n">
-        <v>31.45562594059618</v>
+        <v>31.45562594059625</v>
       </c>
       <c r="M9" t="n">
-        <v>45.03067070496481</v>
+        <v>45.03067070496485</v>
       </c>
       <c r="N9" t="n">
-        <v>31.50409349859544</v>
+        <v>31.5040934985954</v>
       </c>
       <c r="O9" t="n">
-        <v>34.66895360767813</v>
+        <v>34.66895360767816</v>
       </c>
       <c r="P9" t="n">
-        <v>37.9316398505768</v>
+        <v>37.93163985057684</v>
       </c>
       <c r="Q9" t="n">
         <v>31.83219079689742</v>
       </c>
       <c r="R9" t="n">
-        <v>30.60958669964836</v>
+        <v>30.60958669964839</v>
       </c>
       <c r="S9" t="n">
         <v>33.91626258224031</v>
       </c>
       <c r="T9" t="n">
-        <v>31.40863504683096</v>
+        <v>31.40863504683097</v>
       </c>
       <c r="U9" t="n">
-        <v>32.49455004955054</v>
+        <v>32.49455004955031</v>
       </c>
       <c r="V9" t="n">
         <v>37.0781339967843</v>
@@ -3848,19 +3848,19 @@
         <v>33.45531520332851</v>
       </c>
       <c r="X9" t="n">
-        <v>33.75343543140953</v>
+        <v>33.75343543140952</v>
       </c>
       <c r="Y9" t="n">
-        <v>37.17249395271802</v>
+        <v>37.17249395271801</v>
       </c>
       <c r="Z9" t="n">
-        <v>30.91822600287581</v>
+        <v>30.91822600287584</v>
       </c>
       <c r="AA9" t="n">
-        <v>32.0518162101013</v>
+        <v>32.05181621010129</v>
       </c>
       <c r="AB9" t="n">
-        <v>46.57153014988589</v>
+        <v>46.57153014988592</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.23829510997018</v>
+        <v>21.23829510997017</v>
       </c>
       <c r="C2" t="n">
-        <v>15.47808159778802</v>
+        <v>15.47808159778799</v>
       </c>
       <c r="D2" t="n">
-        <v>21.25313015755233</v>
+        <v>21.25313015755228</v>
       </c>
       <c r="E2" t="n">
-        <v>21.02502466050257</v>
+        <v>21.02502466050254</v>
       </c>
       <c r="F2" t="n">
-        <v>21.35932724260799</v>
+        <v>21.35932724260795</v>
       </c>
       <c r="G2" t="n">
-        <v>21.90269744997049</v>
+        <v>21.90269744997045</v>
       </c>
       <c r="H2" t="n">
-        <v>21.05376993795937</v>
+        <v>21.05376993795931</v>
       </c>
       <c r="I2" t="n">
-        <v>21.25149617590349</v>
+        <v>21.25149617590345</v>
       </c>
       <c r="J2" t="n">
-        <v>21.54944000266875</v>
+        <v>21.54944000266872</v>
       </c>
       <c r="K2" t="n">
-        <v>21.26817692425586</v>
+        <v>21.26817692425583</v>
       </c>
       <c r="L2" t="n">
-        <v>21.12787856039614</v>
+        <v>21.12787856039611</v>
       </c>
       <c r="M2" t="n">
-        <v>21.9877206448963</v>
+        <v>21.98772064489629</v>
       </c>
       <c r="N2" t="n">
-        <v>21.10383974669217</v>
+        <v>21.10383974669214</v>
       </c>
       <c r="O2" t="n">
-        <v>28.30224690253777</v>
+        <v>28.30224690253772</v>
       </c>
       <c r="P2" t="n">
-        <v>21.49518165177025</v>
+        <v>21.4951816517702</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.13965394921095</v>
+        <v>21.13965394921092</v>
       </c>
       <c r="R2" t="n">
-        <v>21.14056468594357</v>
+        <v>21.14056468594356</v>
       </c>
       <c r="S2" t="n">
-        <v>21.32555071233414</v>
+        <v>21.3255507123341</v>
       </c>
       <c r="T2" t="n">
-        <v>21.1497448916943</v>
+        <v>21.14974489169427</v>
       </c>
       <c r="U2" t="n">
-        <v>24.48485797527074</v>
+        <v>24.48485797527071</v>
       </c>
       <c r="V2" t="n">
-        <v>21.29130253094259</v>
+        <v>21.29130253094256</v>
       </c>
       <c r="W2" t="n">
-        <v>26.78390378063457</v>
+        <v>26.7839037806345</v>
       </c>
       <c r="X2" t="n">
-        <v>21.34896114092981</v>
+        <v>21.34896114092977</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.93352070877837</v>
+        <v>21.93352070877835</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.54459291073911</v>
+        <v>27.54459291073908</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.1976179054571</v>
+        <v>21.19761790545706</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.33666321198844</v>
+        <v>22.33666321198841</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.73946656269292</v>
+        <v>21.82924589319164</v>
       </c>
       <c r="C3" t="n">
-        <v>11.15912448155788</v>
+        <v>11.19981776235259</v>
       </c>
       <c r="D3" t="n">
-        <v>21.85688122982891</v>
+        <v>21.9514942681457</v>
       </c>
       <c r="E3" t="n">
-        <v>20.21241692373559</v>
+        <v>20.24660296998105</v>
       </c>
       <c r="F3" t="n">
-        <v>22.61872317509645</v>
+        <v>22.74079409367051</v>
       </c>
       <c r="G3" t="n">
-        <v>26.45541433474635</v>
+        <v>26.71144251370635</v>
       </c>
       <c r="H3" t="n">
-        <v>20.4349965953394</v>
+        <v>20.47913667464465</v>
       </c>
       <c r="I3" t="n">
-        <v>21.84833607746111</v>
+        <v>21.94267031676204</v>
       </c>
       <c r="J3" t="n">
-        <v>23.95839581579281</v>
+        <v>24.12702691667235</v>
       </c>
       <c r="K3" t="n">
-        <v>21.95955099207383</v>
+        <v>22.05787628811188</v>
       </c>
       <c r="L3" t="n">
-        <v>20.95877741578017</v>
+        <v>21.02120577811515</v>
       </c>
       <c r="M3" t="n">
-        <v>27.91631022850987</v>
+        <v>28.23199461662133</v>
       </c>
       <c r="N3" t="n">
-        <v>20.78942559004685</v>
+        <v>20.84598024037834</v>
       </c>
       <c r="O3" t="n">
-        <v>33.2240635115817</v>
+        <v>33.30574192484998</v>
       </c>
       <c r="P3" t="n">
-        <v>23.56166992331953</v>
+        <v>23.71541641475692</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.04427312816806</v>
+        <v>21.10995743123961</v>
       </c>
       <c r="R3" t="n">
-        <v>21.05608828963251</v>
+        <v>21.12229235487297</v>
       </c>
       <c r="S3" t="n">
-        <v>22.36158970796644</v>
+        <v>22.47346397089236</v>
       </c>
       <c r="T3" t="n">
-        <v>21.12003501820381</v>
+        <v>21.18842427399942</v>
       </c>
       <c r="U3" t="n">
-        <v>26.7188443794748</v>
+        <v>26.7882297894529</v>
       </c>
       <c r="V3" t="n">
-        <v>22.11544569487341</v>
+        <v>22.2186213074165</v>
       </c>
       <c r="W3" t="n">
-        <v>31.22516759439241</v>
+        <v>31.33032716174591</v>
       </c>
       <c r="X3" t="n">
-        <v>22.53934946990527</v>
+        <v>22.65820402774589</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.71559231988141</v>
+        <v>26.98152646935355</v>
       </c>
       <c r="Z3" t="n">
-        <v>32.28923020084516</v>
+        <v>32.38573723238891</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.45809062201334</v>
+        <v>21.53821100459263</v>
       </c>
       <c r="AB3" t="n">
-        <v>29.57626529515476</v>
+        <v>29.94359759712679</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.89151974900026</v>
+        <v>13.89151974900023</v>
       </c>
       <c r="C4" t="n">
-        <v>11.66166068185271</v>
+        <v>11.66166068185268</v>
       </c>
       <c r="D4" t="n">
-        <v>14.05908843589934</v>
+        <v>14.05908843589926</v>
       </c>
       <c r="E4" t="n">
-        <v>11.48253191300954</v>
+        <v>11.48253191300952</v>
       </c>
       <c r="F4" t="n">
-        <v>15.25863336467599</v>
+        <v>15.25863336467594</v>
       </c>
       <c r="G4" t="n">
-        <v>21.39624981948041</v>
+        <v>21.39624981948038</v>
       </c>
       <c r="H4" t="n">
-        <v>11.80722304536481</v>
+        <v>11.80722304536479</v>
       </c>
       <c r="I4" t="n">
-        <v>14.04063186150724</v>
+        <v>14.04063186150721</v>
       </c>
       <c r="J4" t="n">
-        <v>17.37558864743364</v>
+        <v>17.37558864743362</v>
       </c>
       <c r="K4" t="n">
-        <v>14.2290485876705</v>
+        <v>14.22904858767048</v>
       </c>
       <c r="L4" t="n">
-        <v>12.64431402743898</v>
+        <v>12.64431402743895</v>
       </c>
       <c r="M4" t="n">
         <v>23.84293732689669</v>
       </c>
       <c r="N4" t="n">
-        <v>12.37278456825199</v>
+        <v>12.37278456825198</v>
       </c>
       <c r="O4" t="n">
-        <v>13.52850214625191</v>
+        <v>13.52850214625185</v>
       </c>
       <c r="P4" t="n">
-        <v>16.79317141227944</v>
+        <v>16.79317141227938</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.77732246104867</v>
+        <v>12.77732246104866</v>
       </c>
       <c r="R4" t="n">
-        <v>12.78760965140343</v>
+        <v>12.78760965140341</v>
       </c>
       <c r="S4" t="n">
-        <v>14.87711191726104</v>
+        <v>14.87711191726099</v>
       </c>
       <c r="T4" t="n">
-        <v>12.89130429846115</v>
+        <v>12.89130429846113</v>
       </c>
       <c r="U4" t="n">
-        <v>12.84213417031819</v>
+        <v>12.84213417031814</v>
       </c>
       <c r="V4" t="n">
-        <v>14.29571410235012</v>
+        <v>14.29571410235007</v>
       </c>
       <c r="W4" t="n">
         <v>14.55641013206945</v>
       </c>
       <c r="X4" t="n">
-        <v>15.14154347757841</v>
+        <v>15.14154347757837</v>
       </c>
       <c r="Y4" t="n">
-        <v>21.62776669521115</v>
+        <v>21.62776669521109</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.19170641746299</v>
+        <v>14.19170641746297</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.4320520115862</v>
+        <v>13.43205201158618</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.18644000072872</v>
+        <v>26.18644000072867</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69.24145398805246</v>
+        <v>69.24145398805243</v>
       </c>
       <c r="C5" t="n">
         <v>35.92278751806449</v>
       </c>
       <c r="D5" t="n">
-        <v>78.18352262068947</v>
+        <v>78.18352262068882</v>
       </c>
       <c r="E5" t="n">
         <v>24.08081665046787</v>
       </c>
       <c r="F5" t="n">
-        <v>101.4247046835427</v>
+        <v>101.4247046835429</v>
       </c>
       <c r="G5" t="n">
-        <v>188.5400918802081</v>
+        <v>188.5400918802079</v>
       </c>
       <c r="H5" t="n">
-        <v>38.85264388979205</v>
+        <v>38.85264388979206</v>
       </c>
       <c r="I5" t="n">
-        <v>79.47221575919818</v>
+        <v>79.47221575919808</v>
       </c>
       <c r="J5" t="n">
-        <v>130.4760077109172</v>
+        <v>130.4760077109173</v>
       </c>
       <c r="K5" t="n">
-        <v>78.74365130755562</v>
+        <v>78.7436513075555</v>
       </c>
       <c r="L5" t="n">
-        <v>50.99631904871275</v>
+        <v>50.99631904871277</v>
       </c>
       <c r="M5" t="n">
-        <v>255.9311095597559</v>
+        <v>255.9311095597561</v>
       </c>
       <c r="N5" t="n">
-        <v>47.34142200342075</v>
+        <v>47.34142200342062</v>
       </c>
       <c r="O5" t="n">
-        <v>63.11843707478229</v>
+        <v>63.11843707478202</v>
       </c>
       <c r="P5" t="n">
-        <v>114.7533296618081</v>
+        <v>114.7533296618086</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.10238225171527</v>
+        <v>54.10238225171537</v>
       </c>
       <c r="R5" t="n">
-        <v>57.03878977850512</v>
+        <v>57.03878977850513</v>
       </c>
       <c r="S5" t="n">
-        <v>86.34967831589506</v>
+        <v>86.34967831589472</v>
       </c>
       <c r="T5" t="n">
-        <v>58.05770713824083</v>
+        <v>58.05770713824077</v>
       </c>
       <c r="U5" t="n">
-        <v>55.87092410769705</v>
+        <v>55.87092410769701</v>
       </c>
       <c r="V5" t="n">
-        <v>78.42533012353401</v>
+        <v>78.4253301235338</v>
       </c>
       <c r="W5" t="n">
-        <v>85.51585918656956</v>
+        <v>85.51585918656943</v>
       </c>
       <c r="X5" t="n">
-        <v>96.56037958550255</v>
+        <v>96.56037958550243</v>
       </c>
       <c r="Y5" t="n">
-        <v>215.5258175779009</v>
+        <v>215.5258175779008</v>
       </c>
       <c r="Z5" t="n">
-        <v>71.57596360138017</v>
+        <v>71.57596360138015</v>
       </c>
       <c r="AA5" t="n">
-        <v>65.74757254057683</v>
+        <v>65.7475725405769</v>
       </c>
       <c r="AB5" t="n">
-        <v>316.9378905098603</v>
+        <v>316.9378905098602</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.34142491130263</v>
+        <v>31.3414249113026</v>
       </c>
       <c r="C6" t="n">
-        <v>29.11156584415504</v>
+        <v>29.11156584415501</v>
       </c>
       <c r="D6" t="n">
-        <v>44.27160211848633</v>
+        <v>44.27160211848622</v>
       </c>
       <c r="E6" t="n">
-        <v>41.69504559559651</v>
+        <v>41.69504559559646</v>
       </c>
       <c r="F6" t="n">
         <v>32.70853852697832</v>
       </c>
       <c r="G6" t="n">
-        <v>38.84615498178276</v>
+        <v>38.84615498178272</v>
       </c>
       <c r="H6" t="n">
-        <v>42.01973672795178</v>
+        <v>42.01973672795173</v>
       </c>
       <c r="I6" t="n">
-        <v>31.49053702380963</v>
+        <v>31.49053702380961</v>
       </c>
       <c r="J6" t="n">
-        <v>47.58810233002058</v>
+        <v>47.58810233002056</v>
       </c>
       <c r="K6" t="n">
-        <v>44.44156227025746</v>
+        <v>44.44156227025741</v>
       </c>
       <c r="L6" t="n">
         <v>30.09421918974137</v>
       </c>
       <c r="M6" t="n">
-        <v>41.29284248919909</v>
+        <v>41.29284248919906</v>
       </c>
       <c r="N6" t="n">
-        <v>29.83805111455157</v>
+        <v>29.83805111455174</v>
       </c>
       <c r="O6" t="n">
-        <v>30.99401210025018</v>
+        <v>30.99401210025025</v>
       </c>
       <c r="P6" t="n">
-        <v>46.68824301191673</v>
+        <v>46.68824301191668</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.98983614363563</v>
+        <v>42.98983614363559</v>
       </c>
       <c r="R6" t="n">
-        <v>43.00012333399039</v>
+        <v>43.00012333399035</v>
       </c>
       <c r="S6" t="n">
-        <v>32.32701707956338</v>
+        <v>32.32701707956336</v>
       </c>
       <c r="T6" t="n">
-        <v>43.10381798104805</v>
+        <v>43.10381798104807</v>
       </c>
       <c r="U6" t="n">
-        <v>43.17129386480907</v>
+        <v>43.171293864809</v>
       </c>
       <c r="V6" t="n">
-        <v>31.74561926465248</v>
+        <v>31.7456192646525</v>
       </c>
       <c r="W6" t="n">
-        <v>32.94265027313766</v>
+        <v>32.94265027313763</v>
       </c>
       <c r="X6" t="n">
-        <v>32.5914486398808</v>
+        <v>32.59144863988077</v>
       </c>
       <c r="Y6" t="n">
-        <v>39.98994988757519</v>
+        <v>39.98994988757526</v>
       </c>
       <c r="Z6" t="n">
-        <v>31.64161157976533</v>
+        <v>31.64161157976532</v>
       </c>
       <c r="AA6" t="n">
-        <v>43.64456569417308</v>
+        <v>43.64456569417305</v>
       </c>
       <c r="AB6" t="n">
-        <v>43.71864229025144</v>
+        <v>43.71864229025134</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.20390418830233</v>
+        <v>18.20390418830229</v>
       </c>
       <c r="C7" t="n">
-        <v>15.97404512115478</v>
+        <v>15.97404512115475</v>
       </c>
       <c r="D7" t="n">
-        <v>18.37147287520142</v>
+        <v>18.37147287520134</v>
       </c>
       <c r="E7" t="n">
-        <v>15.79491635231163</v>
+        <v>15.79491635231162</v>
       </c>
       <c r="F7" t="n">
-        <v>19.57101780397807</v>
+        <v>19.57101780397804</v>
       </c>
       <c r="G7" t="n">
-        <v>25.70863425878251</v>
+        <v>25.70863425878248</v>
       </c>
       <c r="H7" t="n">
-        <v>16.11960748466689</v>
+        <v>16.11960748466687</v>
       </c>
       <c r="I7" t="n">
-        <v>18.35301630080932</v>
+        <v>18.35301630080929</v>
       </c>
       <c r="J7" t="n">
-        <v>21.68797308673572</v>
+        <v>21.6879730867357</v>
       </c>
       <c r="K7" t="n">
-        <v>18.5414330269726</v>
+        <v>18.54143302697259</v>
       </c>
       <c r="L7" t="n">
-        <v>16.95669846674106</v>
+        <v>16.95669846674104</v>
       </c>
       <c r="M7" t="n">
-        <v>28.15532176619879</v>
+        <v>28.15532176619881</v>
       </c>
       <c r="N7" t="n">
-        <v>16.68516900755409</v>
+        <v>16.68516900755406</v>
       </c>
       <c r="O7" t="n">
-        <v>17.84079935614363</v>
+        <v>17.84079935614354</v>
       </c>
       <c r="P7" t="n">
-        <v>21.10546862217111</v>
+        <v>21.10546862217107</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.08970690035078</v>
+        <v>17.08970690035077</v>
       </c>
       <c r="R7" t="n">
         <v>17.09999409070551</v>
       </c>
       <c r="S7" t="n">
-        <v>19.18949635656311</v>
+        <v>19.18949635656308</v>
       </c>
       <c r="T7" t="n">
-        <v>17.20368873776325</v>
+        <v>17.20368873776322</v>
       </c>
       <c r="U7" t="n">
-        <v>17.26828718585448</v>
+        <v>17.26828718585444</v>
       </c>
       <c r="V7" t="n">
-        <v>18.6080985416522</v>
+        <v>18.60809854165216</v>
       </c>
       <c r="W7" t="n">
-        <v>18.86879457137157</v>
+        <v>18.86879457137152</v>
       </c>
       <c r="X7" t="n">
         <v>19.45392791688048</v>
       </c>
       <c r="Y7" t="n">
-        <v>26.05679714641701</v>
+        <v>26.05679714641703</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.50409085676507</v>
+        <v>18.50409085676505</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.74443645088827</v>
+        <v>17.74443645088826</v>
       </c>
       <c r="AB7" t="n">
-        <v>30.49882444003081</v>
+        <v>30.49882444003077</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.38908952258498</v>
+        <v>30.38908952258496</v>
       </c>
       <c r="C8" t="n">
-        <v>39.0603270719924</v>
+        <v>39.06032707199236</v>
       </c>
       <c r="D8" t="n">
-        <v>41.45775482603907</v>
+        <v>41.45775482603896</v>
       </c>
       <c r="E8" t="n">
-        <v>33.07668591692149</v>
+        <v>33.07668591692145</v>
       </c>
       <c r="F8" t="n">
-        <v>33.45446658739657</v>
+        <v>33.45446658739653</v>
       </c>
       <c r="G8" t="n">
-        <v>51.05532960715949</v>
+        <v>51.05532960715946</v>
       </c>
       <c r="H8" t="n">
-        <v>39.20588943550449</v>
+        <v>39.20588943550451</v>
       </c>
       <c r="I8" t="n">
-        <v>41.43929825164692</v>
+        <v>41.43929825164691</v>
       </c>
       <c r="J8" t="n">
-        <v>44.77425503757335</v>
+        <v>44.77425503757333</v>
       </c>
       <c r="K8" t="n">
-        <v>41.62771497781021</v>
+        <v>41.62771497781019</v>
       </c>
       <c r="L8" t="n">
-        <v>40.04298041757868</v>
+        <v>40.04298041757865</v>
       </c>
       <c r="M8" t="n">
-        <v>51.24160371703868</v>
+        <v>51.24160371703866</v>
       </c>
       <c r="N8" t="n">
-        <v>31.32127736701013</v>
+        <v>31.32127736701008</v>
       </c>
       <c r="O8" t="n">
-        <v>34.7991760199378</v>
+        <v>34.79917601993775</v>
       </c>
       <c r="P8" t="n">
-        <v>37.49462259269693</v>
+        <v>37.49462259269691</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.13257794390223</v>
+        <v>27.1325779439022</v>
       </c>
       <c r="R8" t="n">
-        <v>40.18627604154314</v>
+        <v>40.1862760415431</v>
       </c>
       <c r="S8" t="n">
-        <v>42.27577830740074</v>
+        <v>42.27577830740067</v>
       </c>
       <c r="T8" t="n">
-        <v>40.28997068860086</v>
+        <v>40.28997068860087</v>
       </c>
       <c r="U8" t="n">
-        <v>35.03460446820315</v>
+        <v>35.03460446820312</v>
       </c>
       <c r="V8" t="n">
-        <v>38.71256141973844</v>
+        <v>38.7125614197384</v>
       </c>
       <c r="W8" t="n">
-        <v>41.95721890077149</v>
+        <v>41.95721890077145</v>
       </c>
       <c r="X8" t="n">
         <v>30.4959061265919</v>
       </c>
       <c r="Y8" t="n">
-        <v>59.97809220135834</v>
+        <v>59.97809220135829</v>
       </c>
       <c r="Z8" t="n">
-        <v>30.48678272470202</v>
+        <v>30.48678272470199</v>
       </c>
       <c r="AA8" t="n">
-        <v>40.8307184017259</v>
+        <v>40.83071840172587</v>
       </c>
       <c r="AB8" t="n">
-        <v>64.97221334241291</v>
+        <v>64.97221334241286</v>
       </c>
     </row>
     <row r="9">
@@ -4645,82 +4645,82 @@
         <v>27.56883123072692</v>
       </c>
       <c r="C9" t="n">
-        <v>29.30375683452157</v>
+        <v>29.30375683452154</v>
       </c>
       <c r="D9" t="n">
-        <v>31.70118458856827</v>
+        <v>31.70118458856812</v>
       </c>
       <c r="E9" t="n">
-        <v>28.20957167523901</v>
+        <v>28.20957167523897</v>
       </c>
       <c r="F9" t="n">
-        <v>23.76081920037481</v>
+        <v>23.76081920037479</v>
       </c>
       <c r="G9" t="n">
-        <v>39.03834563355664</v>
+        <v>39.03834563355658</v>
       </c>
       <c r="H9" t="n">
-        <v>29.4493191980337</v>
+        <v>29.44931919803366</v>
       </c>
       <c r="I9" t="n">
-        <v>31.68272801417611</v>
+        <v>31.68272801417609</v>
       </c>
       <c r="J9" t="n">
-        <v>35.01768480010253</v>
+        <v>35.01768480010248</v>
       </c>
       <c r="K9" t="n">
-        <v>31.87114474033939</v>
+        <v>31.87114474033935</v>
       </c>
       <c r="L9" t="n">
-        <v>30.28641018010786</v>
+        <v>30.28641018010782</v>
       </c>
       <c r="M9" t="n">
-        <v>41.48503347956557</v>
+        <v>41.48503347956555</v>
       </c>
       <c r="N9" t="n">
-        <v>30.01488072092089</v>
+        <v>30.01488072092085</v>
       </c>
       <c r="O9" t="n">
-        <v>32.48452229663206</v>
+        <v>32.48452229663198</v>
       </c>
       <c r="P9" t="n">
-        <v>36.03494756265599</v>
+        <v>36.03494756265589</v>
       </c>
       <c r="Q9" t="n">
-        <v>30.41941827512494</v>
+        <v>30.41941827512487</v>
       </c>
       <c r="R9" t="n">
-        <v>30.42970580407227</v>
+        <v>30.42970580407228</v>
       </c>
       <c r="S9" t="n">
-        <v>32.51920806992993</v>
+        <v>32.51920806992985</v>
       </c>
       <c r="T9" t="n">
-        <v>30.53340045113009</v>
+        <v>30.53340045113001</v>
       </c>
       <c r="U9" t="n">
-        <v>30.60087633489096</v>
+        <v>30.60087633489089</v>
       </c>
       <c r="V9" t="n">
-        <v>36.5130829925366</v>
+        <v>36.51308299253651</v>
       </c>
       <c r="W9" t="n">
-        <v>32.19850628473838</v>
+        <v>32.19850628473834</v>
       </c>
       <c r="X9" t="n">
-        <v>32.78363963024727</v>
+        <v>32.78363963024723</v>
       </c>
       <c r="Y9" t="n">
-        <v>39.38650885978396</v>
+        <v>39.3865088597838</v>
       </c>
       <c r="Z9" t="n">
-        <v>29.44338984151139</v>
+        <v>29.44338984151133</v>
       </c>
       <c r="AA9" t="n">
-        <v>31.07414816425506</v>
+        <v>31.07414816425502</v>
       </c>
       <c r="AB9" t="n">
-        <v>43.8285361533976</v>
+        <v>43.82853615339752</v>
       </c>
     </row>
   </sheetData>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.43487486043432</v>
+        <v>20.43487486043433</v>
       </c>
       <c r="C2" t="n">
         <v>14.75248353895647</v>
@@ -4895,7 +4895,7 @@
         <v>20.36171535472032</v>
       </c>
       <c r="E2" t="n">
-        <v>20.34300431728504</v>
+        <v>20.34300431728505</v>
       </c>
       <c r="F2" t="n">
         <v>20.35368168964199</v>
@@ -4904,49 +4904,49 @@
         <v>20.60731615127637</v>
       </c>
       <c r="H2" t="n">
-        <v>20.43471381859563</v>
+        <v>20.4347138185956</v>
       </c>
       <c r="I2" t="n">
-        <v>20.3797693692289</v>
+        <v>20.37976936922891</v>
       </c>
       <c r="J2" t="n">
         <v>20.51890859144792</v>
       </c>
       <c r="K2" t="n">
-        <v>20.43799524567663</v>
+        <v>20.43799524567662</v>
       </c>
       <c r="L2" t="n">
-        <v>20.44411380652109</v>
+        <v>20.4441138065211</v>
       </c>
       <c r="M2" t="n">
-        <v>20.6644699860364</v>
+        <v>20.66446998603642</v>
       </c>
       <c r="N2" t="n">
-        <v>20.41949145371041</v>
+        <v>20.41949145371044</v>
       </c>
       <c r="O2" t="n">
-        <v>27.25377677175635</v>
+        <v>27.25377677175632</v>
       </c>
       <c r="P2" t="n">
-        <v>20.51255971189085</v>
+        <v>20.51255971189086</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.43423887734557</v>
+        <v>20.43423887734556</v>
       </c>
       <c r="R2" t="n">
         <v>20.36621270237733</v>
       </c>
       <c r="S2" t="n">
-        <v>20.45554251411863</v>
+        <v>20.45554251411864</v>
       </c>
       <c r="T2" t="n">
-        <v>20.36560996401567</v>
+        <v>20.36560996401566</v>
       </c>
       <c r="U2" t="n">
-        <v>23.69801528395832</v>
+        <v>23.69801528395831</v>
       </c>
       <c r="V2" t="n">
-        <v>20.38050285442896</v>
+        <v>20.38050285442895</v>
       </c>
       <c r="W2" t="n">
         <v>25.98541818851819</v>
@@ -4955,16 +4955,16 @@
         <v>20.45188879627555</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.41531026933828</v>
+        <v>20.41531026933826</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.70690121604713</v>
+        <v>26.70690121604711</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.4112188802528</v>
+        <v>20.41121888025281</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.69895736756448</v>
+        <v>20.69895736756447</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.45487517902098</v>
+        <v>20.51845174333582</v>
       </c>
       <c r="C3" t="n">
-        <v>10.37737339727349</v>
+        <v>10.40909920594212</v>
       </c>
       <c r="D3" t="n">
-        <v>19.93972642610523</v>
+        <v>19.98539271915712</v>
       </c>
       <c r="E3" t="n">
-        <v>19.78883913650234</v>
+        <v>19.82722715541776</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8833518521631</v>
+        <v>19.92708967040248</v>
       </c>
       <c r="G3" t="n">
-        <v>21.67647301326888</v>
+        <v>21.78321233064246</v>
       </c>
       <c r="H3" t="n">
-        <v>20.4657865109453</v>
+        <v>20.53028433235697</v>
       </c>
       <c r="I3" t="n">
-        <v>20.0694872011973</v>
+        <v>20.11979315842811</v>
       </c>
       <c r="J3" t="n">
-        <v>21.05336226424135</v>
+        <v>21.13827953403196</v>
       </c>
       <c r="K3" t="n">
-        <v>20.48360456461726</v>
+        <v>20.54857883993516</v>
       </c>
       <c r="L3" t="n">
-        <v>20.52314410803268</v>
+        <v>20.58931476883951</v>
       </c>
       <c r="M3" t="n">
-        <v>22.92723399575918</v>
+        <v>23.08469458366366</v>
       </c>
       <c r="N3" t="n">
-        <v>20.35010873062203</v>
+        <v>20.41028049192074</v>
       </c>
       <c r="O3" t="n">
-        <v>31.6112300578121</v>
+        <v>31.67020472766953</v>
       </c>
       <c r="P3" t="n">
-        <v>21.00711321385306</v>
+        <v>21.08999047569061</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.45533804799057</v>
+        <v>20.51931066999289</v>
       </c>
       <c r="R3" t="n">
-        <v>19.97293116151326</v>
+        <v>20.01984204751592</v>
       </c>
       <c r="S3" t="n">
-        <v>20.59946848024609</v>
+        <v>20.66836069965413</v>
       </c>
       <c r="T3" t="n">
-        <v>19.96853024249597</v>
+        <v>20.01520192095204</v>
       </c>
       <c r="U3" t="n">
-        <v>25.97377539362355</v>
+        <v>26.04043960068695</v>
       </c>
       <c r="V3" t="n">
-        <v>20.07035434427715</v>
+        <v>20.12039194551379</v>
       </c>
       <c r="W3" t="n">
-        <v>30.47678655805059</v>
+        <v>30.5799752168762</v>
       </c>
       <c r="X3" t="n">
-        <v>20.58357354331491</v>
+        <v>20.65209243036329</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.32041237102514</v>
+        <v>20.3794610066607</v>
       </c>
       <c r="Z3" t="n">
-        <v>31.02097129975424</v>
+        <v>31.09441303718555</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.29090546780717</v>
+        <v>20.34889164501899</v>
       </c>
       <c r="AB3" t="n">
-        <v>22.35566137967767</v>
+        <v>22.48693820453488</v>
       </c>
     </row>
     <row r="4">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.20975818050861</v>
+        <v>12.2097581805086</v>
       </c>
       <c r="C4" t="n">
         <v>10.76385508707472</v>
@@ -5074,10 +5074,10 @@
         <v>11.17203813309971</v>
       </c>
       <c r="F4" t="n">
-        <v>11.29264396570529</v>
+        <v>11.2926439657053</v>
       </c>
       <c r="G4" t="n">
-        <v>14.15756188748254</v>
+        <v>14.15756188748255</v>
       </c>
       <c r="H4" t="n">
         <v>12.20793913885758</v>
@@ -5086,49 +5086,49 @@
         <v>11.58731630756489</v>
       </c>
       <c r="J4" t="n">
-        <v>13.12990734115937</v>
+        <v>13.12990734115938</v>
       </c>
       <c r="K4" t="n">
-        <v>12.24500436726854</v>
+        <v>12.24500436726853</v>
       </c>
       <c r="L4" t="n">
-        <v>12.3141163266838</v>
+        <v>12.31411632668381</v>
       </c>
       <c r="M4" t="n">
-        <v>16.33306501019788</v>
+        <v>16.33306501019786</v>
       </c>
       <c r="N4" t="n">
-        <v>12.03599552484537</v>
+        <v>12.03599552484536</v>
       </c>
       <c r="O4" t="n">
-        <v>12.00373411763503</v>
+        <v>12.00373411763501</v>
       </c>
       <c r="P4" t="n">
-        <v>13.08724431450743</v>
+        <v>13.08724431450742</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.20257445895446</v>
+        <v>12.20257445895445</v>
       </c>
       <c r="R4" t="n">
-        <v>11.43418751910154</v>
+        <v>11.43418751910155</v>
       </c>
       <c r="S4" t="n">
-        <v>12.44320883646329</v>
+        <v>12.4432088364633</v>
       </c>
       <c r="T4" t="n">
-        <v>11.42737931203336</v>
+        <v>11.42737931203338</v>
       </c>
       <c r="U4" t="n">
         <v>12.24362231947276</v>
       </c>
       <c r="V4" t="n">
-        <v>11.41054396903212</v>
+        <v>11.41054396903217</v>
       </c>
       <c r="W4" t="n">
-        <v>13.96982083887608</v>
+        <v>13.96982083887607</v>
       </c>
       <c r="X4" t="n">
-        <v>12.40193841263244</v>
+        <v>12.40193841263243</v>
       </c>
       <c r="Y4" t="n">
         <v>11.89406586348827</v>
@@ -5140,7 +5140,7 @@
         <v>11.94255300206989</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.19033641725974</v>
+        <v>15.19033641725973</v>
       </c>
     </row>
     <row r="5">
@@ -5150,79 +5150,79 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.06691958457606</v>
+        <v>53.06691958457615</v>
       </c>
       <c r="C5" t="n">
-        <v>29.61683716600238</v>
+        <v>29.6168371660024</v>
       </c>
       <c r="D5" t="n">
-        <v>41.33187758495062</v>
+        <v>41.33187758495056</v>
       </c>
       <c r="E5" t="n">
-        <v>27.68885575316493</v>
+        <v>27.68885575316492</v>
       </c>
       <c r="F5" t="n">
-        <v>40.15117064585947</v>
+        <v>40.1511706458594</v>
       </c>
       <c r="G5" t="n">
-        <v>84.82133109443699</v>
+        <v>84.82133109444159</v>
       </c>
       <c r="H5" t="n">
-        <v>59.7401083100837</v>
+        <v>59.74010831008356</v>
       </c>
       <c r="I5" t="n">
-        <v>45.692930258592</v>
+        <v>45.69293025859196</v>
       </c>
       <c r="J5" t="n">
-        <v>70.28124439276743</v>
+        <v>70.28124439276785</v>
       </c>
       <c r="K5" t="n">
-        <v>57.32556107252724</v>
+        <v>57.32556107252727</v>
       </c>
       <c r="L5" t="n">
-        <v>56.33600948767935</v>
+        <v>56.33600948767949</v>
       </c>
       <c r="M5" t="n">
         <v>132.4139614244141</v>
       </c>
       <c r="N5" t="n">
-        <v>52.57648196418342</v>
+        <v>52.57648196418351</v>
       </c>
       <c r="O5" t="n">
-        <v>49.49276831880218</v>
+        <v>49.4927683188021</v>
       </c>
       <c r="P5" t="n">
-        <v>68.43335000716641</v>
+        <v>68.43335000716645</v>
       </c>
       <c r="Q5" t="n">
-        <v>55.71291507383991</v>
+        <v>55.71291507383992</v>
       </c>
       <c r="R5" t="n">
-        <v>42.90801949020118</v>
+        <v>42.90801949020148</v>
       </c>
       <c r="S5" t="n">
-        <v>55.86103678524316</v>
+        <v>55.86103678524313</v>
       </c>
       <c r="T5" t="n">
-        <v>42.72415068896642</v>
+        <v>42.72415068896651</v>
       </c>
       <c r="U5" t="n">
-        <v>56.99704112750878</v>
+        <v>56.99704112750869</v>
       </c>
       <c r="V5" t="n">
-        <v>43.23537666533319</v>
+        <v>43.23537666533301</v>
       </c>
       <c r="W5" t="n">
-        <v>89.03547148920055</v>
+        <v>89.03547148920083</v>
       </c>
       <c r="X5" t="n">
-        <v>60.74334693399254</v>
+        <v>60.74334693399264</v>
       </c>
       <c r="Y5" t="n">
         <v>51.76411264943005</v>
       </c>
       <c r="Z5" t="n">
-        <v>60.20615673422505</v>
+        <v>60.20615673422506</v>
       </c>
       <c r="AA5" t="n">
         <v>50.71986461294602</v>
@@ -5238,82 +5238,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.81549756007174</v>
+        <v>30.81549756007175</v>
       </c>
       <c r="C6" t="n">
-        <v>29.36959446663791</v>
+        <v>29.36959446663792</v>
       </c>
       <c r="D6" t="n">
-        <v>43.18772376122234</v>
+        <v>43.18772376122229</v>
       </c>
       <c r="E6" t="n">
-        <v>42.97637398588841</v>
+        <v>42.97637398588844</v>
       </c>
       <c r="F6" t="n">
-        <v>29.89838334526832</v>
+        <v>29.89838334526833</v>
       </c>
       <c r="G6" t="n">
-        <v>32.76330126704569</v>
+        <v>32.76330126704572</v>
       </c>
       <c r="H6" t="n">
-        <v>44.01227499164633</v>
+        <v>44.01227499164631</v>
       </c>
       <c r="I6" t="n">
-        <v>43.39165216035359</v>
+        <v>43.39165216035362</v>
       </c>
       <c r="J6" t="n">
-        <v>31.7356467207225</v>
+        <v>31.73564672072252</v>
       </c>
       <c r="K6" t="n">
-        <v>44.04934022005722</v>
+        <v>44.04934022005715</v>
       </c>
       <c r="L6" t="n">
-        <v>30.91985570624698</v>
+        <v>30.91985570624699</v>
       </c>
       <c r="M6" t="n">
-        <v>48.13740086298652</v>
+        <v>48.13740086298655</v>
       </c>
       <c r="N6" t="n">
-        <v>30.64646789144917</v>
+        <v>30.64646789144923</v>
       </c>
       <c r="O6" t="n">
-        <v>43.46214359572603</v>
+        <v>43.46214359572609</v>
       </c>
       <c r="P6" t="n">
-        <v>44.54565239389294</v>
+        <v>44.54565239389297</v>
       </c>
       <c r="Q6" t="n">
-        <v>44.00691031174314</v>
+        <v>44.00691031174308</v>
       </c>
       <c r="R6" t="n">
-        <v>43.23852337189026</v>
+        <v>43.23852337189027</v>
       </c>
       <c r="S6" t="n">
-        <v>31.0489482160264</v>
+        <v>31.04894821602642</v>
       </c>
       <c r="T6" t="n">
-        <v>30.03311869159648</v>
+        <v>30.03311869159649</v>
       </c>
       <c r="U6" t="n">
-        <v>30.94406295946985</v>
+        <v>30.94406295946984</v>
       </c>
       <c r="V6" t="n">
-        <v>43.21487982182082</v>
+        <v>43.21487982182092</v>
       </c>
       <c r="W6" t="n">
         <v>45.42819731473337</v>
       </c>
       <c r="X6" t="n">
-        <v>31.00767779219554</v>
+        <v>31.00767779219555</v>
       </c>
       <c r="Y6" t="n">
         <v>31.43250216328182</v>
       </c>
       <c r="Z6" t="n">
-        <v>31.25854427211592</v>
+        <v>31.25854427211591</v>
       </c>
       <c r="AA6" t="n">
-        <v>43.74688885485856</v>
+        <v>43.74688885485855</v>
       </c>
       <c r="AB6" t="n">
         <v>33.82103756782119</v>
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.53994546896019</v>
+        <v>16.53994546896017</v>
       </c>
       <c r="C7" t="n">
-        <v>15.09404237552632</v>
+        <v>15.09404237552634</v>
       </c>
       <c r="D7" t="n">
-        <v>15.71357519688518</v>
+        <v>15.71357519688511</v>
       </c>
       <c r="E7" t="n">
-        <v>15.50222542155128</v>
+        <v>15.5022254215513</v>
       </c>
       <c r="F7" t="n">
-        <v>15.62283125415689</v>
+        <v>15.62283125415687</v>
       </c>
       <c r="G7" t="n">
-        <v>18.48774917593412</v>
+        <v>18.48774917593416</v>
       </c>
       <c r="H7" t="n">
-        <v>16.53812642730916</v>
+        <v>16.53812642730913</v>
       </c>
       <c r="I7" t="n">
         <v>15.91750359601649</v>
       </c>
       <c r="J7" t="n">
-        <v>17.46009462961097</v>
+        <v>17.46009462961103</v>
       </c>
       <c r="K7" t="n">
-        <v>16.57519165572013</v>
+        <v>16.57519165572011</v>
       </c>
       <c r="L7" t="n">
-        <v>16.64430361513542</v>
+        <v>16.64430361513541</v>
       </c>
       <c r="M7" t="n">
         <v>20.66325229864948</v>
       </c>
       <c r="N7" t="n">
-        <v>16.36618281329694</v>
+        <v>16.36618281329695</v>
       </c>
       <c r="O7" t="n">
-        <v>16.33383335519777</v>
+        <v>16.33383335519778</v>
       </c>
       <c r="P7" t="n">
-        <v>17.41734355207017</v>
+        <v>17.41734355207018</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.53276174740603</v>
+        <v>16.53276174740604</v>
       </c>
       <c r="R7" t="n">
-        <v>15.76437480755311</v>
+        <v>15.76437480755314</v>
       </c>
       <c r="S7" t="n">
-        <v>16.77339612491489</v>
+        <v>16.77339612491484</v>
       </c>
       <c r="T7" t="n">
-        <v>15.75756660048496</v>
+        <v>15.75756660048495</v>
       </c>
       <c r="U7" t="n">
-        <v>16.66636093358034</v>
+        <v>16.66636093358035</v>
       </c>
       <c r="V7" t="n">
-        <v>15.74073125748376</v>
+        <v>15.74073125748374</v>
       </c>
       <c r="W7" t="n">
-        <v>18.30000812732768</v>
+        <v>18.30000812732763</v>
       </c>
       <c r="X7" t="n">
         <v>16.73212570108401</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.31895441237388</v>
+        <v>16.31895441237391</v>
       </c>
       <c r="Z7" t="n">
         <v>16.98299218100439</v>
       </c>
       <c r="AA7" t="n">
-        <v>16.27274029052148</v>
+        <v>16.2727402905215</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.5205237057113</v>
+        <v>19.52052370571128</v>
       </c>
     </row>
     <row r="8">
@@ -5414,25 +5414,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.35207802555249</v>
+        <v>29.35207802555254</v>
       </c>
       <c r="C8" t="n">
         <v>39.17532407765749</v>
       </c>
       <c r="D8" t="n">
-        <v>39.79485689901634</v>
+        <v>39.79485689901639</v>
       </c>
       <c r="E8" t="n">
         <v>33.58301762260299</v>
       </c>
       <c r="F8" t="n">
-        <v>30.19056554240183</v>
+        <v>30.19056554240188</v>
       </c>
       <c r="G8" t="n">
-        <v>44.90576236513866</v>
+        <v>44.90576236513868</v>
       </c>
       <c r="H8" t="n">
-        <v>40.61940812944034</v>
+        <v>40.61940812944039</v>
       </c>
       <c r="I8" t="n">
         <v>39.99878529814766</v>
@@ -5441,58 +5441,58 @@
         <v>41.54137633174211</v>
       </c>
       <c r="K8" t="n">
-        <v>40.65647335785133</v>
+        <v>40.65647335785132</v>
       </c>
       <c r="L8" t="n">
-        <v>40.7255853172666</v>
+        <v>40.72558531726666</v>
       </c>
       <c r="M8" t="n">
         <v>44.74453400078101</v>
       </c>
       <c r="N8" t="n">
-        <v>31.71198864028573</v>
+        <v>31.71198864028574</v>
       </c>
       <c r="O8" t="n">
-        <v>34.08031185291769</v>
+        <v>34.08031185291766</v>
       </c>
       <c r="P8" t="n">
         <v>34.57538075315691</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.13024929088168</v>
+        <v>27.13024929088172</v>
       </c>
       <c r="R8" t="n">
-        <v>39.84565650968431</v>
+        <v>39.84565650968433</v>
       </c>
       <c r="S8" t="n">
-        <v>40.85467782704603</v>
+        <v>40.85467782704609</v>
       </c>
       <c r="T8" t="n">
-        <v>39.83884830261614</v>
+        <v>39.83884830261618</v>
       </c>
       <c r="U8" t="n">
-        <v>35.24787337134723</v>
+        <v>35.24787337134727</v>
       </c>
       <c r="V8" t="n">
-        <v>36.74022213317345</v>
+        <v>36.74022213317356</v>
       </c>
       <c r="W8" t="n">
         <v>42.38350454107818</v>
       </c>
       <c r="X8" t="n">
-        <v>28.3624531564489</v>
+        <v>28.36245315644894</v>
       </c>
       <c r="Y8" t="n">
-        <v>51.60216104967012</v>
+        <v>51.60216104967016</v>
       </c>
       <c r="Z8" t="n">
-        <v>29.58579450655018</v>
+        <v>29.5857945065502</v>
       </c>
       <c r="AA8" t="n">
-        <v>40.35402199265267</v>
+        <v>40.35402199265273</v>
       </c>
       <c r="AB8" t="n">
-        <v>55.37337400213404</v>
+        <v>55.37337400213406</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.60232478347196</v>
+        <v>26.60232478347202</v>
       </c>
       <c r="C9" t="n">
-        <v>29.30090026982867</v>
+        <v>29.30090026982869</v>
       </c>
       <c r="D9" t="n">
-        <v>29.9204330911875</v>
+        <v>29.92043309118748</v>
       </c>
       <c r="E9" t="n">
         <v>28.75255491428519</v>
       </c>
       <c r="F9" t="n">
-        <v>20.27553429322805</v>
+        <v>20.27553429322801</v>
       </c>
       <c r="G9" t="n">
         <v>32.69460752476914</v>
       </c>
       <c r="H9" t="n">
-        <v>30.74498432161147</v>
+        <v>30.74498432161142</v>
       </c>
       <c r="I9" t="n">
-        <v>30.12436149031881</v>
+        <v>30.1243614903189</v>
       </c>
       <c r="J9" t="n">
-        <v>31.6669525239133</v>
+        <v>31.66695252391333</v>
       </c>
       <c r="K9" t="n">
-        <v>30.78204955002246</v>
+        <v>30.78204955002247</v>
       </c>
       <c r="L9" t="n">
-        <v>30.85116150943773</v>
+        <v>30.85116150943769</v>
       </c>
       <c r="M9" t="n">
-        <v>34.87011019295182</v>
+        <v>34.87011019295186</v>
       </c>
       <c r="N9" t="n">
-        <v>30.57304070759925</v>
+        <v>30.57304070759938</v>
       </c>
       <c r="O9" t="n">
-        <v>31.91425468016959</v>
+        <v>31.91425468016954</v>
       </c>
       <c r="P9" t="n">
         <v>33.29647210841744</v>
       </c>
       <c r="Q9" t="n">
-        <v>30.73962009624103</v>
+        <v>30.73962009624115</v>
       </c>
       <c r="R9" t="n">
-        <v>29.97123270185546</v>
+        <v>29.97123270185556</v>
       </c>
       <c r="S9" t="n">
-        <v>30.98025401921721</v>
+        <v>30.9802540192172</v>
       </c>
       <c r="T9" t="n">
-        <v>29.9644244947873</v>
+        <v>29.96442449478731</v>
       </c>
       <c r="U9" t="n">
-        <v>30.87536876266072</v>
+        <v>30.87536876266075</v>
       </c>
       <c r="V9" t="n">
-        <v>34.73022733349805</v>
+        <v>34.73022733349802</v>
       </c>
       <c r="W9" t="n">
-        <v>32.50686602162997</v>
+        <v>32.50686602163004</v>
       </c>
       <c r="X9" t="n">
-        <v>30.93898359538633</v>
+        <v>30.93898359538631</v>
       </c>
       <c r="Y9" t="n">
-        <v>30.52581230667622</v>
+        <v>30.52581230667625</v>
       </c>
       <c r="Z9" t="n">
-        <v>28.69109821359777</v>
+        <v>28.69109821359772</v>
       </c>
       <c r="AA9" t="n">
-        <v>30.47959818482381</v>
+        <v>30.4795981848238</v>
       </c>
       <c r="AB9" t="n">
-        <v>33.72738160001363</v>
+        <v>33.7273816000137</v>
       </c>
     </row>
   </sheetData>
@@ -5752,10 +5752,10 @@
         <v>14.53687980812045</v>
       </c>
       <c r="D2" t="n">
-        <v>20.08619038763584</v>
+        <v>20.08619038763583</v>
       </c>
       <c r="E2" t="n">
-        <v>20.07789543281517</v>
+        <v>20.07789543281518</v>
       </c>
       <c r="F2" t="n">
         <v>20.1156150850619</v>
@@ -5776,43 +5776,43 @@
         <v>20.1462634751167</v>
       </c>
       <c r="L2" t="n">
-        <v>20.12399811447396</v>
+        <v>20.12399811447395</v>
       </c>
       <c r="M2" t="n">
-        <v>19.97663005348209</v>
+        <v>19.9766300534821</v>
       </c>
       <c r="N2" t="n">
         <v>20.16383453184213</v>
       </c>
       <c r="O2" t="n">
-        <v>26.99023339447682</v>
+        <v>26.99023339447681</v>
       </c>
       <c r="P2" t="n">
-        <v>20.16222684502708</v>
+        <v>20.16222684502709</v>
       </c>
       <c r="Q2" t="n">
         <v>20.16855171683517</v>
       </c>
       <c r="R2" t="n">
-        <v>20.13518347206595</v>
+        <v>20.13518347206594</v>
       </c>
       <c r="S2" t="n">
-        <v>20.15321168816736</v>
+        <v>20.15321168816737</v>
       </c>
       <c r="T2" t="n">
         <v>20.09487044352164</v>
       </c>
       <c r="U2" t="n">
-        <v>23.32529336825326</v>
+        <v>23.32529336825327</v>
       </c>
       <c r="V2" t="n">
-        <v>20.1683500855308</v>
+        <v>20.16835008553081</v>
       </c>
       <c r="W2" t="n">
         <v>25.56087528795707</v>
       </c>
       <c r="X2" t="n">
-        <v>20.36143045035245</v>
+        <v>20.36143045035247</v>
       </c>
       <c r="Y2" t="n">
         <v>20.23873129661511</v>
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.20020823605289</v>
+        <v>20.26116383500312</v>
       </c>
       <c r="C3" t="n">
-        <v>10.30874245633753</v>
+        <v>10.34438145627114</v>
       </c>
       <c r="D3" t="n">
-        <v>19.44985716347558</v>
+        <v>19.48446067875318</v>
       </c>
       <c r="E3" t="n">
-        <v>19.37220726682498</v>
+        <v>19.40226206245773</v>
       </c>
       <c r="F3" t="n">
-        <v>19.65920168730005</v>
+        <v>19.70138095834803</v>
       </c>
       <c r="G3" t="n">
-        <v>19.94990113316234</v>
+        <v>20.00201336629769</v>
       </c>
       <c r="H3" t="n">
-        <v>20.08148047975818</v>
+        <v>20.13871219180023</v>
       </c>
       <c r="I3" t="n">
-        <v>19.899450128799</v>
+        <v>19.95011635611417</v>
       </c>
       <c r="J3" t="n">
-        <v>19.95898836242792</v>
+        <v>20.01150775902606</v>
       </c>
       <c r="K3" t="n">
-        <v>19.87793019752578</v>
+        <v>19.92774773385412</v>
       </c>
       <c r="L3" t="n">
-        <v>19.71911270735462</v>
+        <v>19.76310347032529</v>
       </c>
       <c r="M3" t="n">
-        <v>19.52547739513038</v>
+        <v>19.56770815558192</v>
       </c>
       <c r="N3" t="n">
-        <v>20.00022419062811</v>
+        <v>20.05440403791791</v>
       </c>
       <c r="O3" t="n">
-        <v>31.58197804414088</v>
+        <v>31.6502988814967</v>
       </c>
       <c r="P3" t="n">
-        <v>19.98507761697139</v>
+        <v>20.03841798379332</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.03271654957474</v>
+        <v>20.08814658745848</v>
       </c>
       <c r="R3" t="n">
-        <v>19.7996701878229</v>
+        <v>19.84681818313043</v>
       </c>
       <c r="S3" t="n">
-        <v>19.92146205488975</v>
+        <v>19.97270596281848</v>
       </c>
       <c r="T3" t="n">
-        <v>19.51202653252107</v>
+        <v>19.54884434888208</v>
       </c>
       <c r="U3" t="n">
-        <v>25.17623494394837</v>
+        <v>25.22515360629359</v>
       </c>
       <c r="V3" t="n">
-        <v>20.03039216933784</v>
+        <v>20.08539192744485</v>
       </c>
       <c r="W3" t="n">
-        <v>29.39107266493372</v>
+        <v>29.46737201647031</v>
       </c>
       <c r="X3" t="n">
-        <v>21.40897050837243</v>
+        <v>21.513387697982</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.53536936140487</v>
+        <v>20.60839845265878</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.30583632852227</v>
+        <v>30.3629778144447</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.07514693260751</v>
+        <v>20.13188343889757</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.62726621825501</v>
+        <v>19.66828639072096</v>
       </c>
     </row>
     <row r="4">
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.91578687930597</v>
+        <v>11.91578687930598</v>
       </c>
       <c r="C4" t="n">
-        <v>10.76259396358697</v>
+        <v>10.76259396358698</v>
       </c>
       <c r="D4" t="n">
-        <v>10.71578090920367</v>
+        <v>10.71578090920366</v>
       </c>
       <c r="E4" t="n">
         <v>10.6220855786366</v>
       </c>
       <c r="F4" t="n">
-        <v>11.04814640266063</v>
+        <v>11.04814640266064</v>
       </c>
       <c r="G4" t="n">
         <v>11.51548476202868</v>
@@ -5952,13 +5952,13 @@
         <v>11.39433406728566</v>
       </c>
       <c r="L4" t="n">
-        <v>11.14283657625385</v>
+        <v>11.14283657625386</v>
       </c>
       <c r="M4" t="n">
         <v>11.05145782951666</v>
       </c>
       <c r="N4" t="n">
-        <v>11.59280723608483</v>
+        <v>11.59280723608482</v>
       </c>
       <c r="O4" t="n">
         <v>12.25085854656114</v>
@@ -5967,13 +5967,13 @@
         <v>11.57464767393633</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.6460900105934</v>
+        <v>11.64609001059342</v>
       </c>
       <c r="R4" t="n">
         <v>11.26918033577414</v>
       </c>
       <c r="S4" t="n">
-        <v>11.47281733002873</v>
+        <v>11.47281733002874</v>
       </c>
       <c r="T4" t="n">
         <v>10.81382613345679</v>
@@ -5985,16 +5985,16 @@
         <v>11.46643697024836</v>
       </c>
       <c r="W4" t="n">
-        <v>12.58913793808071</v>
+        <v>12.58913793808072</v>
       </c>
       <c r="X4" t="n">
-        <v>13.82474403427233</v>
+        <v>13.82474403427232</v>
       </c>
       <c r="Y4" t="n">
         <v>12.37367824827751</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.74166350661655</v>
+        <v>11.74166350661656</v>
       </c>
       <c r="AA4" t="n">
         <v>11.71104941338072</v>
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.24786980204052</v>
+        <v>48.24786980204061</v>
       </c>
       <c r="C5" t="n">
-        <v>31.67812887189249</v>
+        <v>31.67812887189255</v>
       </c>
       <c r="D5" t="n">
-        <v>31.10435103837502</v>
+        <v>31.104351038375</v>
       </c>
       <c r="E5" t="n">
         <v>19.88678324364253</v>
       </c>
       <c r="F5" t="n">
-        <v>36.64023227604471</v>
+        <v>36.64023227604479</v>
       </c>
       <c r="G5" t="n">
-        <v>42.52782575821749</v>
+        <v>42.52782575821784</v>
       </c>
       <c r="H5" t="n">
-        <v>50.02702713246441</v>
+        <v>50.0270271324645</v>
       </c>
       <c r="I5" t="n">
-        <v>43.54559062343949</v>
+        <v>43.54559062343955</v>
       </c>
       <c r="J5" t="n">
-        <v>43.19383850607126</v>
+        <v>43.19383850607138</v>
       </c>
       <c r="K5" t="n">
         <v>42.75765086986286</v>
       </c>
       <c r="L5" t="n">
-        <v>38.35691962570931</v>
+        <v>38.3569196257093</v>
       </c>
       <c r="M5" t="n">
-        <v>38.49267382069242</v>
+        <v>38.49267382069239</v>
       </c>
       <c r="N5" t="n">
-        <v>44.65551266421883</v>
+        <v>44.65551266421893</v>
       </c>
       <c r="O5" t="n">
-        <v>53.13714454682483</v>
+        <v>53.13714454682491</v>
       </c>
       <c r="P5" t="n">
-        <v>42.43118558297957</v>
+        <v>42.43118558297962</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.98929017352919</v>
+        <v>44.98929017352921</v>
       </c>
       <c r="R5" t="n">
-        <v>40.96828016728203</v>
+        <v>40.96828016728207</v>
       </c>
       <c r="S5" t="n">
-        <v>41.00641108566079</v>
+        <v>41.0064110856608</v>
       </c>
       <c r="T5" t="n">
-        <v>32.95212943583633</v>
+        <v>32.95212943583634</v>
       </c>
       <c r="U5" t="n">
         <v>40.93693951893597</v>
       </c>
       <c r="V5" t="n">
-        <v>44.31283440738962</v>
+        <v>44.31283440738972</v>
       </c>
       <c r="W5" t="n">
-        <v>61.29915343106504</v>
+        <v>61.29915343106502</v>
       </c>
       <c r="X5" t="n">
-        <v>83.35075719035508</v>
+        <v>83.3507571903553</v>
       </c>
       <c r="Y5" t="n">
-        <v>59.93090919657969</v>
+        <v>59.9309091965797</v>
       </c>
       <c r="Z5" t="n">
-        <v>45.04147456857592</v>
+        <v>45.04147456857594</v>
       </c>
       <c r="AA5" t="n">
-        <v>46.85631202339903</v>
+        <v>46.85631202339901</v>
       </c>
       <c r="AB5" t="n">
-        <v>36.47102135299252</v>
+        <v>36.47102135299251</v>
       </c>
     </row>
     <row r="6">
@@ -6098,40 +6098,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.37601195787492</v>
+        <v>41.37601195787494</v>
       </c>
       <c r="C6" t="n">
-        <v>28.09063876465111</v>
+        <v>28.09063876465115</v>
       </c>
       <c r="D6" t="n">
         <v>28.04382571026784</v>
       </c>
       <c r="E6" t="n">
-        <v>27.95013037970073</v>
+        <v>27.95013037970074</v>
       </c>
       <c r="F6" t="n">
-        <v>40.50837148122965</v>
+        <v>40.50837148122969</v>
       </c>
       <c r="G6" t="n">
-        <v>40.97570984059769</v>
+        <v>40.97570984059771</v>
       </c>
       <c r="H6" t="n">
-        <v>41.17163440736857</v>
+        <v>41.1716344073686</v>
       </c>
       <c r="I6" t="n">
-        <v>40.88801863962946</v>
+        <v>40.88801863962949</v>
       </c>
       <c r="J6" t="n">
-        <v>40.96075715121966</v>
+        <v>40.96075715121968</v>
       </c>
       <c r="K6" t="n">
-        <v>40.85455914585464</v>
+        <v>40.85455914585469</v>
       </c>
       <c r="L6" t="n">
-        <v>28.47088137731805</v>
+        <v>28.47088137731807</v>
       </c>
       <c r="M6" t="n">
-        <v>40.51168290808562</v>
+        <v>40.51168290808567</v>
       </c>
       <c r="N6" t="n">
         <v>28.92684219865218</v>
@@ -6140,22 +6140,22 @@
         <v>41.38733583713773</v>
       </c>
       <c r="P6" t="n">
-        <v>27.88075193022629</v>
+        <v>27.88075193022628</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.10631508916241</v>
+        <v>41.10631508916242</v>
       </c>
       <c r="R6" t="n">
-        <v>28.59722513683833</v>
+        <v>28.59722513683834</v>
       </c>
       <c r="S6" t="n">
-        <v>40.9330424085977</v>
+        <v>40.93304240859772</v>
       </c>
       <c r="T6" t="n">
-        <v>28.14187093452095</v>
+        <v>28.14187093452096</v>
       </c>
       <c r="U6" t="n">
-        <v>28.69336413412218</v>
+        <v>28.69336413412219</v>
       </c>
       <c r="V6" t="n">
         <v>28.79448177131254</v>
@@ -6164,7 +6164,7 @@
         <v>30.83379264087365</v>
       </c>
       <c r="X6" t="n">
-        <v>43.28496911284122</v>
+        <v>43.28496911284124</v>
       </c>
       <c r="Y6" t="n">
         <v>30.55199737982576</v>
@@ -6173,10 +6173,10 @@
         <v>29.06970830768071</v>
       </c>
       <c r="AA6" t="n">
-        <v>41.17127449194971</v>
+        <v>41.17127449194975</v>
       </c>
       <c r="AB6" t="n">
-        <v>28.33226372506881</v>
+        <v>28.3322637250688</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.82707144210441</v>
+        <v>15.82707144210442</v>
       </c>
       <c r="C7" t="n">
-        <v>14.67387852638538</v>
+        <v>14.6738785263854</v>
       </c>
       <c r="D7" t="n">
-        <v>14.62706547200208</v>
+        <v>14.6270654720021</v>
       </c>
       <c r="E7" t="n">
         <v>14.53337014143501</v>
       </c>
       <c r="F7" t="n">
-        <v>14.95943096545906</v>
+        <v>14.95943096545908</v>
       </c>
       <c r="G7" t="n">
-        <v>15.42676932482708</v>
+        <v>15.42676932482709</v>
       </c>
       <c r="H7" t="n">
-        <v>15.62269389159806</v>
+        <v>15.62269389159807</v>
       </c>
       <c r="I7" t="n">
-        <v>15.33907812385892</v>
+        <v>15.33907812385894</v>
       </c>
       <c r="J7" t="n">
-        <v>15.41181663544913</v>
+        <v>15.41181663544915</v>
       </c>
       <c r="K7" t="n">
-        <v>15.30561863008407</v>
+        <v>15.30561863008408</v>
       </c>
       <c r="L7" t="n">
-        <v>15.05412113905227</v>
+        <v>15.05412113905228</v>
       </c>
       <c r="M7" t="n">
-        <v>14.9627423923151</v>
+        <v>14.96274239231511</v>
       </c>
       <c r="N7" t="n">
-        <v>15.50409179888326</v>
+        <v>15.50409179888327</v>
       </c>
       <c r="O7" t="n">
-        <v>16.16206143741476</v>
+        <v>16.16206143741477</v>
       </c>
       <c r="P7" t="n">
-        <v>15.48585056478996</v>
+        <v>15.48585056478997</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.55737457339183</v>
+        <v>15.55737457339185</v>
       </c>
       <c r="R7" t="n">
-        <v>15.18046489857255</v>
+        <v>15.18046489857256</v>
       </c>
       <c r="S7" t="n">
-        <v>15.38410189282716</v>
+        <v>15.38410189282718</v>
       </c>
       <c r="T7" t="n">
-        <v>14.72511069625519</v>
+        <v>14.72511069625521</v>
       </c>
       <c r="U7" t="n">
-        <v>15.27553302235864</v>
+        <v>15.27553302235865</v>
       </c>
       <c r="V7" t="n">
-        <v>15.37772153304678</v>
+        <v>15.37772153304679</v>
       </c>
       <c r="W7" t="n">
-        <v>16.50042250087913</v>
+        <v>16.50042250087914</v>
       </c>
       <c r="X7" t="n">
-        <v>17.73602859707075</v>
+        <v>17.73602859707078</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.350085211208</v>
+        <v>16.35008521120802</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.65294806941499</v>
+        <v>15.65294806941501</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.62233397617914</v>
+        <v>15.62233397617915</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.91230428770977</v>
+        <v>14.91230428770979</v>
       </c>
     </row>
     <row r="8">
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.63704984724175</v>
+        <v>27.63704984724176</v>
       </c>
       <c r="C8" t="n">
-        <v>36.79537275909948</v>
+        <v>36.79537275909949</v>
       </c>
       <c r="D8" t="n">
         <v>36.74855970471617</v>
@@ -6286,64 +6286,64 @@
         <v>31.16428636646737</v>
       </c>
       <c r="F8" t="n">
-        <v>28.37582302340662</v>
+        <v>28.37582302340665</v>
       </c>
       <c r="G8" t="n">
-        <v>39.68642353773436</v>
+        <v>39.68642353773438</v>
       </c>
       <c r="H8" t="n">
-        <v>37.74418812431215</v>
+        <v>37.74418812431214</v>
       </c>
       <c r="I8" t="n">
-        <v>37.46057235657304</v>
+        <v>37.460572356573</v>
       </c>
       <c r="J8" t="n">
-        <v>37.53331086816321</v>
+        <v>37.53331086816323</v>
       </c>
       <c r="K8" t="n">
-        <v>37.42711286279816</v>
+        <v>37.42711286279815</v>
       </c>
       <c r="L8" t="n">
-        <v>37.17561537176638</v>
+        <v>37.17561537176633</v>
       </c>
       <c r="M8" t="n">
         <v>37.08423662502895</v>
       </c>
       <c r="N8" t="n">
-        <v>29.63243618643935</v>
+        <v>29.63243618643936</v>
       </c>
       <c r="O8" t="n">
-        <v>32.48707447820999</v>
+        <v>32.48707447820998</v>
       </c>
       <c r="P8" t="n">
         <v>31.2724270594338</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.34090476930306</v>
+        <v>25.34090476930308</v>
       </c>
       <c r="R8" t="n">
-        <v>37.30195913128664</v>
+        <v>37.30195913128663</v>
       </c>
       <c r="S8" t="n">
-        <v>37.50559612554123</v>
+        <v>37.50559612554125</v>
       </c>
       <c r="T8" t="n">
-        <v>36.84660492896932</v>
+        <v>36.84660492896927</v>
       </c>
       <c r="U8" t="n">
         <v>32.36441827301583</v>
       </c>
       <c r="V8" t="n">
-        <v>34.68007746678693</v>
+        <v>34.68007746678691</v>
       </c>
       <c r="W8" t="n">
-        <v>38.6239432428288</v>
+        <v>38.62394324282882</v>
       </c>
       <c r="X8" t="n">
         <v>28.46462970843573</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.72277348486035</v>
+        <v>48.72277348486037</v>
       </c>
       <c r="Z8" t="n">
         <v>27.27138477403471</v>
@@ -6352,7 +6352,7 @@
         <v>37.74382820889323</v>
       </c>
       <c r="AB8" t="n">
-        <v>47.80503903811306</v>
+        <v>47.80503903811304</v>
       </c>
     </row>
     <row r="9">
@@ -6362,52 +6362,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.03400769467797</v>
+        <v>24.03400769467798</v>
       </c>
       <c r="C9" t="n">
         <v>26.37249799636368</v>
       </c>
       <c r="D9" t="n">
-        <v>26.32568494198037</v>
+        <v>26.32568494198038</v>
       </c>
       <c r="E9" t="n">
         <v>25.42612423528084</v>
       </c>
       <c r="F9" t="n">
-        <v>18.60876617541211</v>
+        <v>18.60876617541212</v>
       </c>
       <c r="G9" t="n">
-        <v>27.12538992341273</v>
+        <v>27.12538992341275</v>
       </c>
       <c r="H9" t="n">
-        <v>27.32131336157634</v>
+        <v>27.32131336157636</v>
       </c>
       <c r="I9" t="n">
-        <v>27.03769759383722</v>
+        <v>27.03769759383723</v>
       </c>
       <c r="J9" t="n">
-        <v>27.11043610542745</v>
+        <v>27.11043610542743</v>
       </c>
       <c r="K9" t="n">
-        <v>27.00423810006236</v>
+        <v>27.00423810006238</v>
       </c>
       <c r="L9" t="n">
-        <v>26.75274060903055</v>
+        <v>26.75274060903058</v>
       </c>
       <c r="M9" t="n">
         <v>26.6613618622934</v>
       </c>
       <c r="N9" t="n">
-        <v>27.20271126886153</v>
+        <v>27.20271126886156</v>
       </c>
       <c r="O9" t="n">
-        <v>29.01790332824827</v>
+        <v>29.01790332824829</v>
       </c>
       <c r="P9" t="n">
-        <v>28.59335046986242</v>
+        <v>28.59335046986244</v>
       </c>
       <c r="Q9" t="n">
-        <v>27.25599517197747</v>
+        <v>27.2559951719775</v>
       </c>
       <c r="R9" t="n">
         <v>26.87908436855086</v>
@@ -6416,31 +6416,31 @@
         <v>27.08272136280545</v>
       </c>
       <c r="T9" t="n">
-        <v>26.42373016623348</v>
+        <v>26.42373016623351</v>
       </c>
       <c r="U9" t="n">
-        <v>26.97522336583474</v>
+        <v>26.97522336583475</v>
       </c>
       <c r="V9" t="n">
-        <v>31.10566957314456</v>
+        <v>31.10566957314455</v>
       </c>
       <c r="W9" t="n">
-        <v>28.19904197085743</v>
+        <v>28.19904197085746</v>
       </c>
       <c r="X9" t="n">
-        <v>29.43464806704904</v>
+        <v>29.43464806704902</v>
       </c>
       <c r="Y9" t="n">
         <v>28.04870468118629</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.246393500042</v>
+        <v>25.24639350004201</v>
       </c>
       <c r="AA9" t="n">
-        <v>27.32095344615744</v>
+        <v>27.32095344615746</v>
       </c>
       <c r="AB9" t="n">
-        <v>26.61092375768806</v>
+        <v>26.61092375768808</v>
       </c>
     </row>
   </sheetData>
@@ -6606,31 +6606,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.10150990799991</v>
+        <v>20.1015099079999</v>
       </c>
       <c r="C2" t="n">
         <v>14.47177498398529</v>
       </c>
       <c r="D2" t="n">
-        <v>20.04941261149206</v>
+        <v>20.04941261149209</v>
       </c>
       <c r="E2" t="n">
-        <v>20.03360733265956</v>
+        <v>20.03360733265955</v>
       </c>
       <c r="F2" t="n">
-        <v>20.05714942683666</v>
+        <v>20.05714942683667</v>
       </c>
       <c r="G2" t="n">
-        <v>20.083982429033</v>
+        <v>20.08398242903299</v>
       </c>
       <c r="H2" t="n">
         <v>20.0998468227674</v>
       </c>
       <c r="I2" t="n">
-        <v>20.12760915550493</v>
+        <v>20.12760915550495</v>
       </c>
       <c r="J2" t="n">
-        <v>20.08844695743183</v>
+        <v>20.08844695743186</v>
       </c>
       <c r="K2" t="n">
         <v>20.08448158991218</v>
@@ -6639,13 +6639,13 @@
         <v>20.06271956768493</v>
       </c>
       <c r="M2" t="n">
-        <v>19.9286210590144</v>
+        <v>19.92862105901441</v>
       </c>
       <c r="N2" t="n">
-        <v>20.07417696042669</v>
+        <v>20.07417696042668</v>
       </c>
       <c r="O2" t="n">
-        <v>26.88439380623476</v>
+        <v>26.88439380623475</v>
       </c>
       <c r="P2" t="n">
         <v>20.1120441424736</v>
@@ -6654,16 +6654,16 @@
         <v>20.07228778208139</v>
       </c>
       <c r="R2" t="n">
-        <v>20.13423571905924</v>
+        <v>20.13423571905927</v>
       </c>
       <c r="S2" t="n">
-        <v>20.0852891531048</v>
+        <v>20.08528915310482</v>
       </c>
       <c r="T2" t="n">
-        <v>20.0459127409124</v>
+        <v>20.04591274091241</v>
       </c>
       <c r="U2" t="n">
-        <v>23.24895247627721</v>
+        <v>23.2489524762772</v>
       </c>
       <c r="V2" t="n">
         <v>20.10502951172289</v>
@@ -6672,16 +6672,16 @@
         <v>25.46461762964459</v>
       </c>
       <c r="X2" t="n">
-        <v>20.36277843422481</v>
+        <v>20.36277843422483</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.16178353415967</v>
+        <v>20.16178353415966</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.22326161812148</v>
+        <v>26.22326161812149</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.13416401037581</v>
+        <v>20.13416401037583</v>
       </c>
       <c r="AB2" t="n">
         <v>20.06335830870971</v>
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.88625686099381</v>
+        <v>19.937497286861</v>
       </c>
       <c r="C3" t="n">
-        <v>10.18114553622518</v>
+        <v>10.21365320754225</v>
       </c>
       <c r="D3" t="n">
-        <v>19.5204085730237</v>
+        <v>19.55889274718257</v>
       </c>
       <c r="E3" t="n">
-        <v>19.39163833237121</v>
+        <v>19.42365083241763</v>
       </c>
       <c r="F3" t="n">
-        <v>19.57569482340647</v>
+        <v>19.61623920899432</v>
       </c>
       <c r="G3" t="n">
-        <v>19.76317161813717</v>
+        <v>19.81004415884821</v>
       </c>
       <c r="H3" t="n">
-        <v>19.88306667616139</v>
+        <v>19.93456413195342</v>
       </c>
       <c r="I3" t="n">
-        <v>20.07932453717982</v>
+        <v>20.13773588086601</v>
       </c>
       <c r="J3" t="n">
-        <v>19.79622943611928</v>
+        <v>19.84436799310265</v>
       </c>
       <c r="K3" t="n">
-        <v>19.77053878044764</v>
+        <v>19.81789101295337</v>
       </c>
       <c r="L3" t="n">
-        <v>19.61484693102237</v>
+        <v>19.65651849708139</v>
       </c>
       <c r="M3" t="n">
-        <v>19.51080507143106</v>
+        <v>19.55390217547007</v>
       </c>
       <c r="N3" t="n">
-        <v>19.69474766164626</v>
+        <v>19.73942031992381</v>
       </c>
       <c r="O3" t="n">
-        <v>31.3442876559348</v>
+        <v>31.40750078326742</v>
       </c>
       <c r="P3" t="n">
-        <v>19.96063948251193</v>
+        <v>20.01444883572724</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.68153445313519</v>
+        <v>19.72576803832628</v>
       </c>
       <c r="R3" t="n">
-        <v>20.12778813325059</v>
+        <v>20.1879666157499</v>
       </c>
       <c r="S3" t="n">
-        <v>19.77160299861103</v>
+        <v>19.81886892093179</v>
       </c>
       <c r="T3" t="n">
-        <v>19.49529240961365</v>
+        <v>19.53289840871508</v>
       </c>
       <c r="U3" t="n">
-        <v>25.05903819974214</v>
+        <v>25.10615868378123</v>
       </c>
       <c r="V3" t="n">
-        <v>19.91264653130648</v>
+        <v>19.96482696741695</v>
       </c>
       <c r="W3" t="n">
-        <v>29.15136592933198</v>
+        <v>29.2216958716126</v>
       </c>
       <c r="X3" t="n">
-        <v>21.75002297288738</v>
+        <v>21.8679894227113</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.32025184094968</v>
+        <v>20.38699854013991</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.82525043515111</v>
+        <v>29.86888787783201</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.12256374864246</v>
+        <v>20.18230735144523</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.63830809377089</v>
+        <v>19.6810333942243</v>
       </c>
     </row>
     <row r="4">
@@ -6785,19 +6785,19 @@
         <v>11.44289712399332</v>
       </c>
       <c r="C4" t="n">
-        <v>10.58918319319856</v>
+        <v>10.58918319319857</v>
       </c>
       <c r="D4" t="n">
-        <v>10.85443419399721</v>
+        <v>10.85443419399723</v>
       </c>
       <c r="E4" t="n">
         <v>10.67590629879624</v>
       </c>
       <c r="F4" t="n">
-        <v>10.94182508242515</v>
+        <v>10.94182508242516</v>
       </c>
       <c r="G4" t="n">
-        <v>11.24491618602327</v>
+        <v>11.24491618602328</v>
       </c>
       <c r="H4" t="n">
         <v>11.42411181123516</v>
@@ -6806,58 +6806,58 @@
         <v>11.73770013080976</v>
       </c>
       <c r="J4" t="n">
-        <v>11.26753783161928</v>
+        <v>11.26753783161929</v>
       </c>
       <c r="K4" t="n">
         <v>11.25055443777918</v>
       </c>
       <c r="L4" t="n">
-        <v>11.00474238569746</v>
+        <v>11.00474238569747</v>
       </c>
       <c r="M4" t="n">
-        <v>11.05589099775007</v>
+        <v>11.05589099775008</v>
       </c>
       <c r="N4" t="n">
-        <v>11.13415890737669</v>
+        <v>11.1341589073767</v>
       </c>
       <c r="O4" t="n">
         <v>11.98586700452165</v>
       </c>
       <c r="P4" t="n">
-        <v>11.561886148361</v>
+        <v>11.56188614836101</v>
       </c>
       <c r="Q4" t="n">
         <v>11.11281976890162</v>
       </c>
       <c r="R4" t="n">
-        <v>11.8125502145257</v>
+        <v>11.81255021452571</v>
       </c>
       <c r="S4" t="n">
         <v>11.25967623553753</v>
       </c>
       <c r="T4" t="n">
-        <v>10.81490154577959</v>
+        <v>10.8149015457796</v>
       </c>
       <c r="U4" t="n">
-        <v>11.18630445118015</v>
+        <v>11.18630445118016</v>
       </c>
       <c r="V4" t="n">
         <v>11.3060110031223</v>
       </c>
       <c r="W4" t="n">
-        <v>12.28762289654657</v>
+        <v>12.28762289654656</v>
       </c>
       <c r="X4" t="n">
-        <v>14.39404531716396</v>
+        <v>14.39404531716397</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.05948664119194</v>
+        <v>12.05948664119195</v>
       </c>
       <c r="Z4" t="n">
         <v>11.09828165848756</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.81174023195855</v>
+        <v>11.81174023195859</v>
       </c>
       <c r="AB4" t="n">
         <v>11.04288609324466</v>
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.97590803429241</v>
+        <v>40.97590803429243</v>
       </c>
       <c r="C5" t="n">
-        <v>28.95218205400864</v>
+        <v>28.95218205400865</v>
       </c>
       <c r="D5" t="n">
-        <v>33.66317805119238</v>
+        <v>33.66317805119237</v>
       </c>
       <c r="E5" t="n">
         <v>22.23103210918091</v>
       </c>
       <c r="F5" t="n">
-        <v>35.24418007635341</v>
+        <v>35.24418007635344</v>
       </c>
       <c r="G5" t="n">
-        <v>38.51553050986205</v>
+        <v>38.515530509862</v>
       </c>
       <c r="H5" t="n">
-        <v>45.14150559818066</v>
+        <v>45.1415055981807</v>
       </c>
       <c r="I5" t="n">
-        <v>49.71186423820613</v>
+        <v>49.71186423820615</v>
       </c>
       <c r="J5" t="n">
-        <v>39.99853465259974</v>
+        <v>39.99853465259977</v>
       </c>
       <c r="K5" t="n">
-        <v>40.58690349938011</v>
+        <v>40.58690349938018</v>
       </c>
       <c r="L5" t="n">
         <v>36.04486766517194</v>
       </c>
       <c r="M5" t="n">
-        <v>38.12411444298455</v>
+        <v>38.12411444298461</v>
       </c>
       <c r="N5" t="n">
-        <v>37.36408315653244</v>
+        <v>37.36408315653247</v>
       </c>
       <c r="O5" t="n">
-        <v>49.49661730634397</v>
+        <v>49.49661730634404</v>
       </c>
       <c r="P5" t="n">
-        <v>42.66546460243371</v>
+        <v>42.6654646024338</v>
       </c>
       <c r="Q5" t="n">
-        <v>37.12656081894842</v>
+        <v>37.12656081894841</v>
       </c>
       <c r="R5" t="n">
-        <v>51.64176572550528</v>
+        <v>51.64176572550535</v>
       </c>
       <c r="S5" t="n">
         <v>38.31289218200111</v>
       </c>
       <c r="T5" t="n">
-        <v>32.89276732920383</v>
+        <v>32.89276732920392</v>
       </c>
       <c r="U5" t="n">
-        <v>39.3535209441478</v>
+        <v>39.35352094414784</v>
       </c>
       <c r="V5" t="n">
-        <v>42.16059716729511</v>
+        <v>42.16059716729509</v>
       </c>
       <c r="W5" t="n">
-        <v>56.96440636525377</v>
+        <v>56.96440636525375</v>
       </c>
       <c r="X5" t="n">
-        <v>92.69486763853506</v>
+        <v>92.6948676385351</v>
       </c>
       <c r="Y5" t="n">
-        <v>54.99645833452848</v>
+        <v>54.99645833452839</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.55779090642612</v>
+        <v>35.55779090642621</v>
       </c>
       <c r="AA5" t="n">
-        <v>49.18525622030166</v>
+        <v>49.18525622030236</v>
       </c>
       <c r="AB5" t="n">
-        <v>37.80683114908685</v>
+        <v>37.80683114908684</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.87757251836763</v>
+        <v>40.87757251836769</v>
       </c>
       <c r="C6" t="n">
-        <v>40.02385858757287</v>
+        <v>40.02385858757293</v>
       </c>
       <c r="D6" t="n">
-        <v>40.28910958837147</v>
+        <v>40.2891095883715</v>
       </c>
       <c r="E6" t="n">
-        <v>27.99117142138103</v>
+        <v>27.99117142138104</v>
       </c>
       <c r="F6" t="n">
         <v>40.37650047679946</v>
       </c>
       <c r="G6" t="n">
-        <v>40.67959158039756</v>
+        <v>40.6795915803976</v>
       </c>
       <c r="H6" t="n">
-        <v>40.85878720560941</v>
+        <v>40.85878720560944</v>
       </c>
       <c r="I6" t="n">
-        <v>41.17237552518407</v>
+        <v>41.17237552518411</v>
       </c>
       <c r="J6" t="n">
-        <v>28.58280295420415</v>
+        <v>28.58280295420414</v>
       </c>
       <c r="K6" t="n">
-        <v>28.565819560364</v>
+        <v>28.56581956036401</v>
       </c>
       <c r="L6" t="n">
-        <v>40.43941778007176</v>
+        <v>40.43941778007181</v>
       </c>
       <c r="M6" t="n">
-        <v>40.49056639212438</v>
+        <v>40.49056639212441</v>
       </c>
       <c r="N6" t="n">
-        <v>28.45408894046494</v>
+        <v>28.45408894046496</v>
       </c>
       <c r="O6" t="n">
         <v>29.30611534237287</v>
       </c>
       <c r="P6" t="n">
-        <v>40.66430711336487</v>
+        <v>40.664307113365</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.54749516327591</v>
+        <v>40.54749516327595</v>
       </c>
       <c r="R6" t="n">
-        <v>41.24722560889998</v>
+        <v>41.24722560890004</v>
       </c>
       <c r="S6" t="n">
-        <v>40.69435162991189</v>
+        <v>40.69435162991192</v>
       </c>
       <c r="T6" t="n">
-        <v>28.13016666836446</v>
+        <v>28.1301666683645</v>
       </c>
       <c r="U6" t="n">
-        <v>40.68520866306813</v>
+        <v>40.68520866306815</v>
       </c>
       <c r="V6" t="n">
-        <v>28.62127612570715</v>
+        <v>28.62127612570714</v>
       </c>
       <c r="W6" t="n">
-        <v>41.39012825789108</v>
+        <v>41.3901282578911</v>
       </c>
       <c r="X6" t="n">
         <v>31.70931043974881</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.22247877044764</v>
+        <v>30.22247877044758</v>
       </c>
       <c r="Z6" t="n">
         <v>28.41354678107242</v>
       </c>
       <c r="AA6" t="n">
-        <v>41.24641562633276</v>
+        <v>41.24641562633287</v>
       </c>
       <c r="AB6" t="n">
-        <v>28.36126214696945</v>
+        <v>28.36126214696947</v>
       </c>
     </row>
     <row r="7">
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.33100365586942</v>
+        <v>15.33100365586943</v>
       </c>
       <c r="C7" t="n">
         <v>14.47728972507467</v>
@@ -7055,13 +7055,13 @@
         <v>14.74254072587332</v>
       </c>
       <c r="E7" t="n">
-        <v>14.56401283067235</v>
+        <v>14.56401283067237</v>
       </c>
       <c r="F7" t="n">
-        <v>14.82993161430125</v>
+        <v>14.82993161430126</v>
       </c>
       <c r="G7" t="n">
-        <v>15.13302271789937</v>
+        <v>15.13302271789939</v>
       </c>
       <c r="H7" t="n">
         <v>15.31221834311127</v>
@@ -7070,61 +7070,61 @@
         <v>15.62580666268585</v>
       </c>
       <c r="J7" t="n">
-        <v>15.15564436349537</v>
+        <v>15.15564436349538</v>
       </c>
       <c r="K7" t="n">
-        <v>15.13866096965528</v>
+        <v>15.13866096965529</v>
       </c>
       <c r="L7" t="n">
-        <v>14.89284891757358</v>
+        <v>14.89284891757357</v>
       </c>
       <c r="M7" t="n">
         <v>14.94399752962618</v>
       </c>
       <c r="N7" t="n">
-        <v>15.02226543925277</v>
+        <v>15.02226543925278</v>
       </c>
       <c r="O7" t="n">
         <v>15.87389245816804</v>
       </c>
       <c r="P7" t="n">
-        <v>15.4499116020074</v>
+        <v>15.44991160200741</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.00092630077771</v>
+        <v>15.00092630077772</v>
       </c>
       <c r="R7" t="n">
-        <v>15.70065674640182</v>
+        <v>15.70065674640181</v>
       </c>
       <c r="S7" t="n">
         <v>15.14778276741363</v>
       </c>
       <c r="T7" t="n">
-        <v>14.7030080776557</v>
+        <v>14.70300807765572</v>
       </c>
       <c r="U7" t="n">
-        <v>15.13769683205872</v>
+        <v>15.13769683205874</v>
       </c>
       <c r="V7" t="n">
-        <v>15.19411753499841</v>
+        <v>15.19411753499843</v>
       </c>
       <c r="W7" t="n">
         <v>16.17572942842267</v>
       </c>
       <c r="X7" t="n">
-        <v>18.28215184904006</v>
+        <v>18.28215184904005</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.01182199058172</v>
+        <v>16.01182199058173</v>
       </c>
       <c r="Z7" t="n">
         <v>14.98638819036365</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.69984676383466</v>
+        <v>15.6998467638347</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.93099262512077</v>
+        <v>14.93099262512078</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.11491860841153</v>
+        <v>27.11491860841155</v>
       </c>
       <c r="C8" t="n">
-        <v>36.53796982042312</v>
+        <v>36.53796982042318</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80322082122179</v>
+        <v>36.80322082122184</v>
       </c>
       <c r="E8" t="n">
         <v>31.15261863289415</v>
       </c>
       <c r="F8" t="n">
-        <v>28.21484646910748</v>
+        <v>28.21484646910749</v>
       </c>
       <c r="G8" t="n">
-        <v>39.32465701257566</v>
+        <v>39.32465701257571</v>
       </c>
       <c r="H8" t="n">
-        <v>37.37289843845974</v>
+        <v>37.37289843845979</v>
       </c>
       <c r="I8" t="n">
-        <v>37.68648675803431</v>
+        <v>37.68648675803438</v>
       </c>
       <c r="J8" t="n">
-        <v>37.21632445884386</v>
+        <v>37.21632445884391</v>
       </c>
       <c r="K8" t="n">
-        <v>37.19934106500374</v>
+        <v>37.19934106500376</v>
       </c>
       <c r="L8" t="n">
-        <v>36.95352901292205</v>
+        <v>36.95352901292208</v>
       </c>
       <c r="M8" t="n">
-        <v>37.00467762497443</v>
+        <v>37.00467762497447</v>
       </c>
       <c r="N8" t="n">
-        <v>29.11673328380713</v>
+        <v>29.11673328380715</v>
       </c>
       <c r="O8" t="n">
-        <v>32.15762567742929</v>
+        <v>32.15762567742934</v>
       </c>
       <c r="P8" t="n">
-        <v>31.19702285203886</v>
+        <v>31.19702285203887</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.76522234679071</v>
+        <v>24.76522234679074</v>
       </c>
       <c r="R8" t="n">
-        <v>37.76133684175029</v>
+        <v>37.76133684175032</v>
       </c>
       <c r="S8" t="n">
-        <v>37.20846286276211</v>
+        <v>37.20846286276214</v>
       </c>
       <c r="T8" t="n">
-        <v>36.76368817300418</v>
+        <v>36.76368817300422</v>
       </c>
       <c r="U8" t="n">
-        <v>32.18270004890822</v>
+        <v>32.18270004890824</v>
       </c>
       <c r="V8" t="n">
-        <v>34.44526604003086</v>
+        <v>34.44526604003089</v>
       </c>
       <c r="W8" t="n">
-        <v>38.23842920351902</v>
+        <v>38.23842920351908</v>
       </c>
       <c r="X8" t="n">
-        <v>28.9883338412082</v>
+        <v>28.98833384120823</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.28931309586028</v>
+        <v>48.28931309586036</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.57940695419627</v>
+        <v>26.57940695419629</v>
       </c>
       <c r="AA8" t="n">
-        <v>37.76052685918312</v>
+        <v>37.76052685918317</v>
       </c>
       <c r="AB8" t="n">
-        <v>47.726613242129</v>
+        <v>47.72661324212903</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.93789134715303</v>
+        <v>22.93789134715304</v>
       </c>
       <c r="C9" t="n">
-        <v>25.40199698639183</v>
+        <v>25.40199698639186</v>
       </c>
       <c r="D9" t="n">
         <v>25.66724798719054</v>
       </c>
       <c r="E9" t="n">
-        <v>24.72298157683553</v>
+        <v>24.72298157683555</v>
       </c>
       <c r="F9" t="n">
         <v>18.1061580456007</v>
       </c>
       <c r="G9" t="n">
-        <v>26.05773090026145</v>
+        <v>26.05773090026148</v>
       </c>
       <c r="H9" t="n">
-        <v>26.23692560442847</v>
+        <v>26.2369256044285</v>
       </c>
       <c r="I9" t="n">
         <v>26.55051392400306</v>
       </c>
       <c r="J9" t="n">
-        <v>26.08035162481257</v>
+        <v>26.08035162481259</v>
       </c>
       <c r="K9" t="n">
-        <v>26.06336823097248</v>
+        <v>26.0633682309725</v>
       </c>
       <c r="L9" t="n">
-        <v>25.81755617889077</v>
+        <v>25.81755617889078</v>
       </c>
       <c r="M9" t="n">
         <v>25.86870479094338</v>
       </c>
       <c r="N9" t="n">
-        <v>25.94697270056999</v>
+        <v>25.94697270057002</v>
       </c>
       <c r="O9" t="n">
-        <v>27.89820308519322</v>
+        <v>27.89820308519324</v>
       </c>
       <c r="P9" t="n">
-        <v>27.71334926161767</v>
+        <v>27.71334926161766</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.92563448313982</v>
+        <v>25.92563448313985</v>
       </c>
       <c r="R9" t="n">
-        <v>26.625364007719</v>
+        <v>26.62536400771901</v>
       </c>
       <c r="S9" t="n">
-        <v>26.07249002873084</v>
+        <v>26.07249002873085</v>
       </c>
       <c r="T9" t="n">
-        <v>25.62771533897287</v>
+        <v>25.62771533897291</v>
       </c>
       <c r="U9" t="n">
-        <v>26.06334706188713</v>
+        <v>26.06334706188715</v>
       </c>
       <c r="V9" t="n">
         <v>29.9475182033738</v>
       </c>
       <c r="W9" t="n">
-        <v>27.10043668973989</v>
+        <v>27.1004366897399</v>
       </c>
       <c r="X9" t="n">
         <v>29.20685911035727</v>
       </c>
       <c r="Y9" t="n">
-        <v>26.93652925189892</v>
+        <v>26.93652925189891</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.91074564871487</v>
+        <v>23.91074564871489</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.62455402515183</v>
+        <v>26.62455402515187</v>
       </c>
       <c r="AB9" t="n">
-        <v>25.85569988643796</v>
+        <v>25.85569988643797</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.17986406220293</v>
+        <v>21.1798640622029</v>
       </c>
       <c r="C2" t="n">
-        <v>15.45966271010025</v>
+        <v>15.45966271010024</v>
       </c>
       <c r="D2" t="n">
-        <v>21.14641137118383</v>
+        <v>21.1464113711838</v>
       </c>
       <c r="E2" t="n">
-        <v>21.05611701670566</v>
+        <v>21.05611701670561</v>
       </c>
       <c r="F2" t="n">
-        <v>21.12808187686736</v>
+        <v>21.12808187686733</v>
       </c>
       <c r="G2" t="n">
-        <v>22.04861579238794</v>
+        <v>22.04861579238792</v>
       </c>
       <c r="H2" t="n">
-        <v>21.04937509899803</v>
+        <v>21.04937509899799</v>
       </c>
       <c r="I2" t="n">
-        <v>21.11835751671493</v>
+        <v>21.11835751671491</v>
       </c>
       <c r="J2" t="n">
-        <v>21.58538298137212</v>
+        <v>21.58538298137206</v>
       </c>
       <c r="K2" t="n">
-        <v>21.18155692257758</v>
+        <v>21.18155692257756</v>
       </c>
       <c r="L2" t="n">
-        <v>21.14938432452638</v>
+        <v>21.14938432452625</v>
       </c>
       <c r="M2" t="n">
         <v>22.33541402252422</v>
       </c>
       <c r="N2" t="n">
-        <v>21.18156281425597</v>
+        <v>21.18156281425595</v>
       </c>
       <c r="O2" t="n">
-        <v>28.27200599493827</v>
+        <v>28.27200599493825</v>
       </c>
       <c r="P2" t="n">
-        <v>21.43635466805076</v>
+        <v>21.43635466805073</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.17443826242437</v>
+        <v>21.17443826242435</v>
       </c>
       <c r="R2" t="n">
-        <v>21.07461840934283</v>
+        <v>21.07461840934282</v>
       </c>
       <c r="S2" t="n">
-        <v>21.26700009299384</v>
+        <v>21.26700009299381</v>
       </c>
       <c r="T2" t="n">
-        <v>21.09439080981455</v>
+        <v>21.09439080981454</v>
       </c>
       <c r="U2" t="n">
-        <v>24.60004480753317</v>
+        <v>24.60004480753313</v>
       </c>
       <c r="V2" t="n">
-        <v>21.12015481473067</v>
+        <v>21.12015481473066</v>
       </c>
       <c r="W2" t="n">
-        <v>26.7551905397697</v>
+        <v>26.75519053976964</v>
       </c>
       <c r="X2" t="n">
-        <v>21.26826216256243</v>
+        <v>21.26826216256238</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.34703538245024</v>
+        <v>21.34703538245022</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.53821687262025</v>
+        <v>27.53821687262022</v>
       </c>
       <c r="AA2" t="n">
         <v>21.19203583421028</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.36394522420247</v>
+        <v>22.36394522420246</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.34713390325739</v>
+        <v>21.42362866688607</v>
       </c>
       <c r="C3" t="n">
-        <v>11.04339164051727</v>
+        <v>11.08049320404625</v>
       </c>
       <c r="D3" t="n">
-        <v>21.11840465257362</v>
+        <v>21.18726995263056</v>
       </c>
       <c r="E3" t="n">
-        <v>20.45483127966252</v>
+        <v>20.49817655279287</v>
       </c>
       <c r="F3" t="n">
-        <v>20.98842006657905</v>
+        <v>21.05284194641744</v>
       </c>
       <c r="G3" t="n">
-        <v>27.51514813189534</v>
+        <v>27.80900586200268</v>
       </c>
       <c r="H3" t="n">
-        <v>20.42647739856483</v>
+        <v>20.47085829191465</v>
       </c>
       <c r="I3" t="n">
-        <v>20.91846631713499</v>
+        <v>20.98028373573226</v>
       </c>
       <c r="J3" t="n">
-        <v>24.2329425155995</v>
+        <v>24.41166282469792</v>
       </c>
       <c r="K3" t="n">
-        <v>21.36648361044672</v>
+        <v>21.44419363800623</v>
       </c>
       <c r="L3" t="n">
-        <v>21.13437720447408</v>
+        <v>21.20355241766219</v>
       </c>
       <c r="M3" t="n">
-        <v>30.37661926796127</v>
+        <v>30.78128377928121</v>
       </c>
       <c r="N3" t="n">
-        <v>21.36716818325452</v>
+        <v>21.44472133090441</v>
       </c>
       <c r="O3" t="n">
-        <v>33.14304211447074</v>
+        <v>33.22359201516151</v>
       </c>
       <c r="P3" t="n">
-        <v>23.17194843607973</v>
+        <v>23.31233693286705</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.3157296875086</v>
+        <v>21.3915722695949</v>
       </c>
       <c r="R3" t="n">
-        <v>20.6059322294137</v>
+        <v>20.65668309120689</v>
       </c>
       <c r="S3" t="n">
-        <v>21.9647664905942</v>
+        <v>22.06328639945976</v>
       </c>
       <c r="T3" t="n">
-        <v>20.7463370442813</v>
+        <v>20.80201424833598</v>
       </c>
       <c r="U3" t="n">
-        <v>27.7128780622788</v>
+        <v>27.81945885356804</v>
       </c>
       <c r="V3" t="n">
-        <v>20.92449164292898</v>
+        <v>20.98613090667391</v>
       </c>
       <c r="W3" t="n">
-        <v>31.2168555935874</v>
+        <v>31.32412735119177</v>
       </c>
       <c r="X3" t="n">
-        <v>21.98873333487736</v>
+        <v>22.08846556913631</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.54604645974194</v>
+        <v>22.66527345724389</v>
       </c>
       <c r="Z3" t="n">
-        <v>32.34688501247712</v>
+        <v>32.44654685637101</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.44037253053506</v>
+        <v>21.52042521366909</v>
       </c>
       <c r="AB3" t="n">
-        <v>29.79645454106085</v>
+        <v>30.17198584757379</v>
       </c>
     </row>
     <row r="4">
@@ -7642,37 +7642,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.24802113999765</v>
+        <v>13.24802113999736</v>
       </c>
       <c r="C4" t="n">
-        <v>11.45809034888348</v>
+        <v>11.4580903488835</v>
       </c>
       <c r="D4" t="n">
         <v>12.87015760593855</v>
       </c>
       <c r="E4" t="n">
-        <v>11.85024133465236</v>
+        <v>11.85024133465231</v>
       </c>
       <c r="F4" t="n">
         <v>12.66311753564996</v>
       </c>
       <c r="G4" t="n">
-        <v>23.0609715779778</v>
+        <v>23.06097157797784</v>
       </c>
       <c r="H4" t="n">
-        <v>11.77408827270942</v>
+        <v>11.7740882727094</v>
       </c>
       <c r="I4" t="n">
         <v>12.55327641430158</v>
       </c>
       <c r="J4" t="n">
-        <v>17.79651701309741</v>
+        <v>17.79651701309737</v>
       </c>
       <c r="K4" t="n">
         <v>13.26714277668339</v>
       </c>
       <c r="L4" t="n">
-        <v>12.90373848156873</v>
+        <v>12.90373848156804</v>
       </c>
       <c r="M4" t="n">
         <v>27.74213057504567</v>
@@ -7684,19 +7684,19 @@
         <v>13.43414315039703</v>
       </c>
       <c r="P4" t="n">
-        <v>16.14520052455688</v>
+        <v>16.14520052455687</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.18673423550756</v>
+        <v>13.18673423550754</v>
       </c>
       <c r="R4" t="n">
-        <v>12.05922307555038</v>
+        <v>12.0592230755504</v>
       </c>
       <c r="S4" t="n">
-        <v>14.23226269233542</v>
+        <v>14.23226269233537</v>
       </c>
       <c r="T4" t="n">
-        <v>12.28256143463208</v>
+        <v>12.28256143463206</v>
       </c>
       <c r="U4" t="n">
         <v>14.42961528973319</v>
@@ -7705,19 +7705,19 @@
         <v>12.36837088999778</v>
       </c>
       <c r="W4" t="n">
-        <v>14.60757789062221</v>
+        <v>14.60757789062218</v>
       </c>
       <c r="X4" t="n">
-        <v>14.24651834869341</v>
+        <v>14.2465183486932</v>
       </c>
       <c r="Y4" t="n">
         <v>14.97908218006846</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.29070965849937</v>
+        <v>14.29070965849928</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.3855069041124</v>
+        <v>13.38550690411238</v>
       </c>
       <c r="AB4" t="n">
         <v>26.50740867627194</v>
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.52813543357529</v>
+        <v>63.52813543357218</v>
       </c>
       <c r="C5" t="n">
-        <v>34.45380598558654</v>
+        <v>34.45380598558658</v>
       </c>
       <c r="D5" t="n">
-        <v>61.95854970630481</v>
+        <v>61.95854970630469</v>
       </c>
       <c r="E5" t="n">
-        <v>32.03039304989451</v>
+        <v>32.03039304989365</v>
       </c>
       <c r="F5" t="n">
-        <v>58.50764715438903</v>
+        <v>58.50764715438902</v>
       </c>
       <c r="G5" t="n">
-        <v>231.1010866236477</v>
+        <v>231.1010866236418</v>
       </c>
       <c r="H5" t="n">
-        <v>41.58202531216655</v>
+        <v>41.58202531216679</v>
       </c>
       <c r="I5" t="n">
-        <v>56.12461642612186</v>
+        <v>56.12461642612176</v>
       </c>
       <c r="J5" t="n">
-        <v>145.4324440877792</v>
+        <v>145.4324440877781</v>
       </c>
       <c r="K5" t="n">
-        <v>67.93162116767482</v>
+        <v>67.93162116767479</v>
       </c>
       <c r="L5" t="n">
-        <v>59.67616129145496</v>
+        <v>59.67616129144488</v>
       </c>
       <c r="M5" t="n">
-        <v>337.0225555538108</v>
+        <v>337.0225555538105</v>
       </c>
       <c r="N5" t="n">
-        <v>68.29022042389396</v>
+        <v>68.2902204238939</v>
       </c>
       <c r="O5" t="n">
-        <v>66.28397443391557</v>
+        <v>66.28397443391562</v>
       </c>
       <c r="P5" t="n">
-        <v>115.0977783572858</v>
+        <v>115.0977783572856</v>
       </c>
       <c r="Q5" t="n">
-        <v>66.44035617044078</v>
+        <v>66.44035617043978</v>
       </c>
       <c r="R5" t="n">
-        <v>46.57960811994215</v>
+        <v>46.57960811994248</v>
       </c>
       <c r="S5" t="n">
-        <v>79.7679776536329</v>
+        <v>79.76797765363165</v>
       </c>
       <c r="T5" t="n">
-        <v>50.40660321088639</v>
+        <v>50.40660321088613</v>
       </c>
       <c r="U5" t="n">
-        <v>90.22627082477831</v>
+        <v>90.22627082477821</v>
       </c>
       <c r="V5" t="n">
-        <v>52.52027285752465</v>
+        <v>52.52027285752496</v>
       </c>
       <c r="W5" t="n">
-        <v>92.72072814182897</v>
+        <v>92.7207281418282</v>
       </c>
       <c r="X5" t="n">
-        <v>88.35722115248717</v>
+        <v>88.35722115248632</v>
       </c>
       <c r="Y5" t="n">
-        <v>102.4585750034777</v>
+        <v>102.4585750034775</v>
       </c>
       <c r="Z5" t="n">
-        <v>81.95125878331251</v>
+        <v>81.95125878330998</v>
       </c>
       <c r="AA5" t="n">
-        <v>69.6693272077445</v>
+        <v>69.66932720774386</v>
       </c>
       <c r="AB5" t="n">
-        <v>348.2432103283355</v>
+        <v>348.2432103283351</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.88532745629383</v>
+        <v>31.88532745629368</v>
       </c>
       <c r="C6" t="n">
-        <v>30.09539666517957</v>
+        <v>30.0953966651796</v>
       </c>
       <c r="D6" t="n">
-        <v>31.50746392223466</v>
+        <v>31.50746392223467</v>
       </c>
       <c r="E6" t="n">
-        <v>44.25113857382328</v>
+        <v>44.25113857382318</v>
       </c>
       <c r="F6" t="n">
-        <v>31.30042385194601</v>
+        <v>31.30042385194603</v>
       </c>
       <c r="G6" t="n">
-        <v>55.46186881714863</v>
+        <v>55.46186881714868</v>
       </c>
       <c r="H6" t="n">
-        <v>30.41139458900556</v>
+        <v>30.41139458900559</v>
       </c>
       <c r="I6" t="n">
-        <v>31.19058273059772</v>
+        <v>31.19058273059773</v>
       </c>
       <c r="J6" t="n">
         <v>36.43382332939354</v>
       </c>
       <c r="K6" t="n">
-        <v>45.66804001585426</v>
+        <v>45.66804001585427</v>
       </c>
       <c r="L6" t="n">
-        <v>45.30463572073962</v>
+        <v>45.30463572073849</v>
       </c>
       <c r="M6" t="n">
         <v>46.37943689134181</v>
       </c>
       <c r="N6" t="n">
-        <v>31.91243765511211</v>
+        <v>31.91243765511204</v>
       </c>
       <c r="O6" t="n">
-        <v>45.49910838183719</v>
+        <v>45.4991083818372</v>
       </c>
       <c r="P6" t="n">
-        <v>48.21022065299724</v>
+        <v>48.21022065299719</v>
       </c>
       <c r="Q6" t="n">
-        <v>31.82404055180364</v>
+        <v>31.82404055180356</v>
       </c>
       <c r="R6" t="n">
-        <v>44.46012031472122</v>
+        <v>44.46012031472127</v>
       </c>
       <c r="S6" t="n">
-        <v>32.86956900863157</v>
+        <v>32.86956900863152</v>
       </c>
       <c r="T6" t="n">
-        <v>30.91986775092823</v>
+        <v>30.91986775092825</v>
       </c>
       <c r="U6" t="n">
-        <v>46.98772845363323</v>
+        <v>46.98772845363322</v>
       </c>
       <c r="V6" t="n">
-        <v>31.00567720629394</v>
+        <v>31.00567720629397</v>
       </c>
       <c r="W6" t="n">
-        <v>34.24362777582053</v>
+        <v>34.24362777582049</v>
       </c>
       <c r="X6" t="n">
-        <v>46.64741558786424</v>
+        <v>46.64741558786398</v>
       </c>
       <c r="Y6" t="n">
-        <v>34.60777472778176</v>
+        <v>34.60777472778177</v>
       </c>
       <c r="Z6" t="n">
-        <v>46.69160689767028</v>
+        <v>46.69160689767018</v>
       </c>
       <c r="AA6" t="n">
-        <v>45.78640414328326</v>
+        <v>45.78640414328322</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.23277550547756</v>
+        <v>45.23277550547758</v>
       </c>
     </row>
     <row r="7">
@@ -7906,82 +7906,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.87779950861958</v>
+        <v>17.87779950861931</v>
       </c>
       <c r="C7" t="n">
         <v>16.08786871750542</v>
       </c>
       <c r="D7" t="n">
-        <v>17.49993597456047</v>
+        <v>17.49993597456049</v>
       </c>
       <c r="E7" t="n">
-        <v>16.48001970327431</v>
+        <v>16.48001970327424</v>
       </c>
       <c r="F7" t="n">
-        <v>17.29289590427189</v>
+        <v>17.2928959042719</v>
       </c>
       <c r="G7" t="n">
         <v>27.69074994659973</v>
       </c>
       <c r="H7" t="n">
-        <v>16.40386664133135</v>
+        <v>16.40386664133134</v>
       </c>
       <c r="I7" t="n">
-        <v>17.18305478292353</v>
+        <v>17.18305478292352</v>
       </c>
       <c r="J7" t="n">
-        <v>22.42629538171935</v>
+        <v>22.4262953817193</v>
       </c>
       <c r="K7" t="n">
-        <v>17.89692114530533</v>
+        <v>17.89692114530531</v>
       </c>
       <c r="L7" t="n">
-        <v>17.53351685019066</v>
+        <v>17.53351685018959</v>
       </c>
       <c r="M7" t="n">
-        <v>32.3719089436676</v>
+        <v>32.37190894366759</v>
       </c>
       <c r="N7" t="n">
-        <v>17.89698769452314</v>
+        <v>17.89698769452313</v>
       </c>
       <c r="O7" t="n">
-        <v>18.0638301904253</v>
+        <v>18.06383019042529</v>
       </c>
       <c r="P7" t="n">
-        <v>20.77488756458519</v>
+        <v>20.77488756458513</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.81651260412948</v>
+        <v>17.81651260412942</v>
       </c>
       <c r="R7" t="n">
-        <v>16.68900144417232</v>
+        <v>16.68900144417233</v>
       </c>
       <c r="S7" t="n">
-        <v>18.86204106095736</v>
+        <v>18.86204106095732</v>
       </c>
       <c r="T7" t="n">
         <v>16.91233980325403</v>
       </c>
       <c r="U7" t="n">
-        <v>19.21277630991055</v>
+        <v>19.21277630991054</v>
       </c>
       <c r="V7" t="n">
-        <v>16.9981492586197</v>
+        <v>16.99814925861971</v>
       </c>
       <c r="W7" t="n">
-        <v>19.23735625924413</v>
+        <v>19.23735625924409</v>
       </c>
       <c r="X7" t="n">
-        <v>18.87629671731534</v>
+        <v>18.87629671731513</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.76607647341963</v>
+        <v>19.76607647341962</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.92048802712133</v>
+        <v>18.92048802712129</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.01528527273436</v>
+        <v>18.01528527273435</v>
       </c>
       <c r="AB7" t="n">
         <v>31.13718704489389</v>
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.96809808667582</v>
+        <v>30.96809808667561</v>
       </c>
       <c r="C8" t="n">
-        <v>40.89184867590747</v>
+        <v>40.89184867590748</v>
       </c>
       <c r="D8" t="n">
-        <v>42.30391593296248</v>
+        <v>42.30391593296251</v>
       </c>
       <c r="E8" t="n">
-        <v>35.04680985847732</v>
+        <v>35.04680985847729</v>
       </c>
       <c r="F8" t="n">
         <v>32.20804914078884</v>
       </c>
       <c r="G8" t="n">
-        <v>54.92363804681196</v>
+        <v>54.92363804681203</v>
       </c>
       <c r="H8" t="n">
-        <v>41.20784659973337</v>
+        <v>41.20784659973334</v>
       </c>
       <c r="I8" t="n">
-        <v>41.98703474132559</v>
+        <v>41.98703474132557</v>
       </c>
       <c r="J8" t="n">
-        <v>47.23027534012135</v>
+        <v>47.23027534012137</v>
       </c>
       <c r="K8" t="n">
         <v>42.70090110370734</v>
       </c>
       <c r="L8" t="n">
-        <v>42.3374968085927</v>
+        <v>42.33749680859216</v>
       </c>
       <c r="M8" t="n">
-        <v>57.17588890207073</v>
+        <v>57.17588890207072</v>
       </c>
       <c r="N8" t="n">
         <v>33.62090492714491</v>
       </c>
       <c r="O8" t="n">
-        <v>36.28311882995141</v>
+        <v>36.28311882995142</v>
       </c>
       <c r="P8" t="n">
-        <v>38.38252276245375</v>
+        <v>38.38252276245373</v>
       </c>
       <c r="Q8" t="n">
         <v>28.60480543902406</v>
       </c>
       <c r="R8" t="n">
-        <v>41.49298140257436</v>
+        <v>41.49298140257437</v>
       </c>
       <c r="S8" t="n">
-        <v>43.6660210193594</v>
+        <v>43.66602101935939</v>
       </c>
       <c r="T8" t="n">
-        <v>41.71631976165605</v>
+        <v>41.71631976165607</v>
       </c>
       <c r="U8" t="n">
-        <v>38.3003980857514</v>
+        <v>38.30039808575141</v>
       </c>
       <c r="V8" t="n">
-        <v>38.59740495369309</v>
+        <v>38.59740495369311</v>
       </c>
       <c r="W8" t="n">
-        <v>44.04363829242482</v>
+        <v>44.04363829242485</v>
       </c>
       <c r="X8" t="n">
-        <v>30.73817172661736</v>
+        <v>30.7381717266172</v>
       </c>
       <c r="Y8" t="n">
-        <v>56.2117422967004</v>
+        <v>56.21174229670045</v>
       </c>
       <c r="Z8" t="n">
-        <v>31.79319895966314</v>
+        <v>31.79319895966304</v>
       </c>
       <c r="AA8" t="n">
-        <v>42.81926523113634</v>
+        <v>42.81926523113633</v>
       </c>
       <c r="AB8" t="n">
-        <v>68.17708668786992</v>
+        <v>68.17708668786987</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.77012705378517</v>
+        <v>29.77012705378484</v>
       </c>
       <c r="C9" t="n">
-        <v>32.74731383641242</v>
+        <v>32.74731383641236</v>
       </c>
       <c r="D9" t="n">
-        <v>34.15938109346747</v>
+        <v>34.15938109346745</v>
       </c>
       <c r="E9" t="n">
-        <v>32.03923271937193</v>
+        <v>32.03923271937185</v>
       </c>
       <c r="F9" t="n">
-        <v>22.96283532293332</v>
+        <v>22.96283532293328</v>
       </c>
       <c r="G9" t="n">
         <v>44.3501940105111</v>
       </c>
       <c r="H9" t="n">
-        <v>33.06331176023832</v>
+        <v>33.06331176023836</v>
       </c>
       <c r="I9" t="n">
-        <v>33.84249990183052</v>
+        <v>33.84249990183051</v>
       </c>
       <c r="J9" t="n">
-        <v>39.08574050062632</v>
+        <v>39.08574050062631</v>
       </c>
       <c r="K9" t="n">
         <v>34.55636626421231</v>
       </c>
       <c r="L9" t="n">
-        <v>34.19296196909765</v>
+        <v>34.19296196909666</v>
       </c>
       <c r="M9" t="n">
-        <v>49.0313540625746</v>
+        <v>49.03135406257458</v>
       </c>
       <c r="N9" t="n">
-        <v>34.55643281343012</v>
+        <v>34.55643281343009</v>
       </c>
       <c r="O9" t="n">
-        <v>36.3031817552418</v>
+        <v>36.30318175524181</v>
       </c>
       <c r="P9" t="n">
-        <v>39.35782204179382</v>
+        <v>39.35782204179379</v>
       </c>
       <c r="Q9" t="n">
-        <v>34.47595666804085</v>
+        <v>34.47595666804077</v>
       </c>
       <c r="R9" t="n">
-        <v>33.34844656307934</v>
+        <v>33.34844656307926</v>
       </c>
       <c r="S9" t="n">
-        <v>35.52148617986434</v>
+        <v>35.52148617986416</v>
       </c>
       <c r="T9" t="n">
         <v>33.571784922161</v>
       </c>
       <c r="U9" t="n">
-        <v>35.87605470199135</v>
+        <v>35.87605470199138</v>
       </c>
       <c r="V9" t="n">
-        <v>39.15873986269717</v>
+        <v>39.1587398626972</v>
       </c>
       <c r="W9" t="n">
-        <v>35.89680137815112</v>
+        <v>35.8968013781511</v>
       </c>
       <c r="X9" t="n">
-        <v>35.53574183622231</v>
+        <v>35.53574183622207</v>
       </c>
       <c r="Y9" t="n">
-        <v>36.42552159232662</v>
+        <v>36.42552159232667</v>
       </c>
       <c r="Z9" t="n">
-        <v>32.70578473876964</v>
+        <v>32.70578473876951</v>
       </c>
       <c r="AA9" t="n">
-        <v>34.67473039164132</v>
+        <v>34.67473039164125</v>
       </c>
       <c r="AB9" t="n">
-        <v>47.79663216380088</v>
+        <v>47.79663216380087</v>
       </c>
     </row>
   </sheetData>
@@ -8326,82 +8326,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.72859578663366</v>
+        <v>20.7285957866336</v>
       </c>
       <c r="C2" t="n">
-        <v>15.08482395763467</v>
+        <v>15.08482395763463</v>
       </c>
       <c r="D2" t="n">
-        <v>20.63968307941956</v>
+        <v>20.63968307941951</v>
       </c>
       <c r="E2" t="n">
-        <v>20.62304214377377</v>
+        <v>20.62304214377371</v>
       </c>
       <c r="F2" t="n">
-        <v>20.62343616725611</v>
+        <v>20.62343616725608</v>
       </c>
       <c r="G2" t="n">
-        <v>21.42146262875745</v>
+        <v>21.42146262875736</v>
       </c>
       <c r="H2" t="n">
-        <v>20.65808349271166</v>
+        <v>20.65808349271161</v>
       </c>
       <c r="I2" t="n">
-        <v>20.66656332298849</v>
+        <v>20.6665633229884</v>
       </c>
       <c r="J2" t="n">
-        <v>20.92453320952728</v>
+        <v>20.92453320952727</v>
       </c>
       <c r="K2" t="n">
-        <v>20.70314746233186</v>
+        <v>20.7031474623318</v>
       </c>
       <c r="L2" t="n">
-        <v>20.68733455507442</v>
+        <v>20.68733455507432</v>
       </c>
       <c r="M2" t="n">
-        <v>20.63732924805135</v>
+        <v>20.63732924805137</v>
       </c>
       <c r="N2" t="n">
-        <v>20.70100266654153</v>
+        <v>20.70100266654151</v>
       </c>
       <c r="O2" t="n">
-        <v>27.6060258830174</v>
+        <v>27.60602588301744</v>
       </c>
       <c r="P2" t="n">
-        <v>20.84538239617545</v>
+        <v>20.84538239617539</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.73412912642117</v>
+        <v>20.73412912642108</v>
       </c>
       <c r="R2" t="n">
-        <v>20.66094311075175</v>
+        <v>20.66094311075178</v>
       </c>
       <c r="S2" t="n">
-        <v>20.68848705361428</v>
+        <v>20.68848705361423</v>
       </c>
       <c r="T2" t="n">
-        <v>20.62853133915198</v>
+        <v>20.62853133915191</v>
       </c>
       <c r="U2" t="n">
-        <v>23.94819596188228</v>
+        <v>23.94819596188234</v>
       </c>
       <c r="V2" t="n">
-        <v>20.68877264393211</v>
+        <v>20.68877264393204</v>
       </c>
       <c r="W2" t="n">
-        <v>26.2034425746285</v>
+        <v>26.20344257462853</v>
       </c>
       <c r="X2" t="n">
-        <v>20.87340572629732</v>
+        <v>20.87340572629727</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.14251850106937</v>
+        <v>21.14251850106928</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.87288955639909</v>
+        <v>26.87288955639907</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.68061905002543</v>
+        <v>20.68061905002548</v>
       </c>
       <c r="AB2" t="n">
         <v>21.41725000709135</v>
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.6567005837838</v>
+        <v>20.7199039880983</v>
       </c>
       <c r="C3" t="n">
-        <v>10.79770191833003</v>
+        <v>10.83616296869116</v>
       </c>
       <c r="D3" t="n">
-        <v>20.02899912797738</v>
+        <v>20.07028079414422</v>
       </c>
       <c r="E3" t="n">
-        <v>19.89256151878033</v>
+        <v>19.92712181724325</v>
       </c>
       <c r="F3" t="n">
-        <v>19.9135480554632</v>
+        <v>19.95078220289382</v>
       </c>
       <c r="G3" t="n">
-        <v>25.56580858005064</v>
+        <v>25.80236711055435</v>
       </c>
       <c r="H3" t="n">
-        <v>20.1622942144976</v>
+        <v>20.20841666464443</v>
       </c>
       <c r="I3" t="n">
-        <v>20.22119990379702</v>
+        <v>20.26935790169954</v>
       </c>
       <c r="J3" t="n">
-        <v>22.04758125777718</v>
+        <v>22.16004059140972</v>
       </c>
       <c r="K3" t="n">
-        <v>20.4820393926986</v>
+        <v>20.53938598178632</v>
       </c>
       <c r="L3" t="n">
-        <v>20.36660120583467</v>
+        <v>20.41968807619805</v>
       </c>
       <c r="M3" t="n">
-        <v>20.8704711449425</v>
+        <v>20.94684170907485</v>
       </c>
       <c r="N3" t="n">
-        <v>20.46516528997672</v>
+        <v>20.5218683564559</v>
       </c>
       <c r="O3" t="n">
-        <v>31.89137378036203</v>
+        <v>31.9491454588587</v>
       </c>
       <c r="P3" t="n">
-        <v>21.48575305085273</v>
+        <v>21.57801574595238</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.69925042439755</v>
+        <v>20.76440324053435</v>
       </c>
       <c r="R3" t="n">
-        <v>20.18156919654641</v>
+        <v>20.22835030671121</v>
       </c>
       <c r="S3" t="n">
-        <v>20.37203004605989</v>
+        <v>20.42530411039216</v>
       </c>
       <c r="T3" t="n">
-        <v>19.94894585697099</v>
+        <v>19.98740663180769</v>
       </c>
       <c r="U3" t="n">
-        <v>25.90270655560754</v>
+        <v>25.95975828174149</v>
       </c>
       <c r="V3" t="n">
-        <v>20.37536808988717</v>
+        <v>20.42867553020951</v>
       </c>
       <c r="W3" t="n">
-        <v>30.16702491059381</v>
+        <v>30.2520981198575</v>
       </c>
       <c r="X3" t="n">
-        <v>21.69632696226968</v>
+        <v>21.79688340939261</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.61445643772175</v>
+        <v>23.78255201511372</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.6423210208509</v>
+        <v>30.69840232323162</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.31867627228659</v>
+        <v>20.37014856481386</v>
       </c>
       <c r="AB3" t="n">
-        <v>25.57019906869325</v>
+        <v>25.80765256006185</v>
       </c>
     </row>
     <row r="4">
@@ -8505,7 +8505,7 @@
         <v>12.34142214580649</v>
       </c>
       <c r="C4" t="n">
-        <v>11.21253300069726</v>
+        <v>11.21253300069727</v>
       </c>
       <c r="D4" t="n">
         <v>11.33711221595712</v>
@@ -8517,16 +8517,16 @@
         <v>11.15359586912205</v>
       </c>
       <c r="G4" t="n">
-        <v>20.16767186208941</v>
+        <v>20.16767186208934</v>
       </c>
       <c r="H4" t="n">
-        <v>11.54495334869976</v>
+        <v>11.54495334869977</v>
       </c>
       <c r="I4" t="n">
-        <v>11.64073693259115</v>
+        <v>11.64073693259114</v>
       </c>
       <c r="J4" t="n">
-        <v>14.52375908941649</v>
+        <v>14.52375908941646</v>
       </c>
       <c r="K4" t="n">
         <v>12.05397161601011</v>
@@ -8544,10 +8544,10 @@
         <v>12.09783302902968</v>
       </c>
       <c r="P4" t="n">
-        <v>13.66058062507572</v>
+        <v>13.66058062507573</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.40392376416841</v>
+        <v>12.40392376416842</v>
       </c>
       <c r="R4" t="n">
         <v>11.57725404995186</v>
@@ -8556,19 +8556,19 @@
         <v>11.88837555542388</v>
       </c>
       <c r="T4" t="n">
-        <v>11.21114817958084</v>
+        <v>11.21114817958086</v>
       </c>
       <c r="U4" t="n">
-        <v>11.92831894186974</v>
+        <v>11.92831894186975</v>
       </c>
       <c r="V4" t="n">
-        <v>11.69422636482382</v>
+        <v>11.69422636482381</v>
       </c>
       <c r="W4" t="n">
         <v>13.30655568464189</v>
       </c>
       <c r="X4" t="n">
-        <v>13.97711703017112</v>
+        <v>13.97711703017113</v>
       </c>
       <c r="Y4" t="n">
         <v>16.89023059213736</v>
@@ -8577,10 +8577,10 @@
         <v>12.01792081514584</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.79950283542731</v>
+        <v>11.7995028354273</v>
       </c>
       <c r="AB4" t="n">
-        <v>20.06086874625916</v>
+        <v>20.06086874625917</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.07286420278697</v>
+        <v>50.07286420278689</v>
       </c>
       <c r="C5" t="n">
-        <v>34.0894969990155</v>
+        <v>34.08949699901549</v>
       </c>
       <c r="D5" t="n">
-        <v>35.8717275064336</v>
+        <v>35.87172750643359</v>
       </c>
       <c r="E5" t="n">
         <v>23.38997182596083</v>
       </c>
       <c r="F5" t="n">
-        <v>32.88709717307597</v>
+        <v>32.88709717307596</v>
       </c>
       <c r="G5" t="n">
-        <v>169.8798270581533</v>
+        <v>169.879827058152</v>
       </c>
       <c r="H5" t="n">
-        <v>40.56886094471616</v>
+        <v>40.56886094471612</v>
       </c>
       <c r="I5" t="n">
-        <v>41.42587262363742</v>
+        <v>41.42587262363736</v>
       </c>
       <c r="J5" t="n">
-        <v>85.28159671443368</v>
+        <v>85.28159671443308</v>
       </c>
       <c r="K5" t="n">
-        <v>48.59814196061659</v>
+        <v>48.59814196061658</v>
       </c>
       <c r="L5" t="n">
         <v>44.10168575807327</v>
       </c>
       <c r="M5" t="n">
-        <v>63.76478840347349</v>
+        <v>63.76478840347353</v>
       </c>
       <c r="N5" t="n">
-        <v>47.35781243703483</v>
+        <v>47.35781243703472</v>
       </c>
       <c r="O5" t="n">
-        <v>46.03950464890355</v>
+        <v>46.03950464890356</v>
       </c>
       <c r="P5" t="n">
-        <v>71.09339415980506</v>
+        <v>71.093394159805</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.76310103896795</v>
+        <v>52.76310103896797</v>
       </c>
       <c r="R5" t="n">
-        <v>40.55235349408754</v>
+        <v>40.55235349408756</v>
       </c>
       <c r="S5" t="n">
-        <v>42.8826638147365</v>
+        <v>42.88266381473645</v>
       </c>
       <c r="T5" t="n">
-        <v>33.40403990112248</v>
+        <v>33.40403990112278</v>
       </c>
       <c r="U5" t="n">
-        <v>46.69613207460696</v>
+        <v>46.69613207460701</v>
       </c>
       <c r="V5" t="n">
-        <v>43.41591734836197</v>
+        <v>43.4159173483619</v>
       </c>
       <c r="W5" t="n">
-        <v>69.37547665418393</v>
+        <v>69.3754766541838</v>
       </c>
       <c r="X5" t="n">
-        <v>82.16950144885226</v>
+        <v>82.1695014488523</v>
       </c>
       <c r="Y5" t="n">
-        <v>134.6153112881333</v>
+        <v>134.6153112881332</v>
       </c>
       <c r="Z5" t="n">
-        <v>44.59372077721391</v>
+        <v>44.5937207772139</v>
       </c>
       <c r="AA5" t="n">
-        <v>42.76212245320508</v>
+        <v>42.76212245320487</v>
       </c>
       <c r="AB5" t="n">
-        <v>202.5208652518698</v>
+        <v>202.5208652518702</v>
       </c>
     </row>
     <row r="6">
@@ -8678,31 +8678,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.24688106882514</v>
+        <v>42.24688106882518</v>
       </c>
       <c r="C6" t="n">
         <v>41.11799192371586</v>
       </c>
       <c r="D6" t="n">
-        <v>41.24257113897573</v>
+        <v>41.24257113897574</v>
       </c>
       <c r="E6" t="n">
-        <v>28.46402459620511</v>
+        <v>28.46402459620508</v>
       </c>
       <c r="F6" t="n">
-        <v>28.46847527269779</v>
+        <v>28.46847527269778</v>
       </c>
       <c r="G6" t="n">
-        <v>37.48255126566512</v>
+        <v>37.48255126566505</v>
       </c>
       <c r="H6" t="n">
-        <v>28.85983275227541</v>
+        <v>28.85983275227542</v>
       </c>
       <c r="I6" t="n">
-        <v>41.54619585560985</v>
+        <v>41.54619585560982</v>
       </c>
       <c r="J6" t="n">
-        <v>44.42921801243514</v>
+        <v>44.42921801243513</v>
       </c>
       <c r="K6" t="n">
         <v>29.36885101958578</v>
@@ -8714,49 +8714,49 @@
         <v>30.20347621990543</v>
       </c>
       <c r="N6" t="n">
-        <v>29.35110641725971</v>
+        <v>29.35110641725969</v>
       </c>
       <c r="O6" t="n">
-        <v>41.68668246630814</v>
+        <v>41.68668246630815</v>
       </c>
       <c r="P6" t="n">
-        <v>29.94916056543974</v>
+        <v>29.94916056543975</v>
       </c>
       <c r="Q6" t="n">
         <v>29.71880316774408</v>
       </c>
       <c r="R6" t="n">
-        <v>41.4827129729705</v>
+        <v>41.48271297297049</v>
       </c>
       <c r="S6" t="n">
-        <v>29.20325495899952</v>
+        <v>29.20325495899953</v>
       </c>
       <c r="T6" t="n">
         <v>28.52602758315655</v>
       </c>
       <c r="U6" t="n">
-        <v>41.96041689196507</v>
+        <v>41.96041689196508</v>
       </c>
       <c r="V6" t="n">
-        <v>29.00910576839952</v>
+        <v>29.00910576839951</v>
       </c>
       <c r="W6" t="n">
-        <v>31.54334792322917</v>
+        <v>31.54334792322905</v>
       </c>
       <c r="X6" t="n">
-        <v>43.88257595318976</v>
+        <v>43.88257595318977</v>
       </c>
       <c r="Y6" t="n">
         <v>35.10819792844828</v>
       </c>
       <c r="Z6" t="n">
-        <v>41.92337973816449</v>
+        <v>41.92337973816451</v>
       </c>
       <c r="AA6" t="n">
-        <v>29.114382239003</v>
+        <v>29.11438223900299</v>
       </c>
       <c r="AB6" t="n">
-        <v>37.42609751112312</v>
+        <v>37.42609751112313</v>
       </c>
     </row>
     <row r="7">
@@ -8769,7 +8769,7 @@
         <v>16.45139123804044</v>
       </c>
       <c r="C7" t="n">
-        <v>15.3225020929312</v>
+        <v>15.32250209293121</v>
       </c>
       <c r="D7" t="n">
         <v>15.44708130819107</v>
@@ -8781,7 +8781,7 @@
         <v>15.26356496135602</v>
       </c>
       <c r="G7" t="n">
-        <v>24.27764095432334</v>
+        <v>24.27764095432329</v>
       </c>
       <c r="H7" t="n">
         <v>15.65492244093371</v>
@@ -8790,37 +8790,37 @@
         <v>15.75070602482509</v>
       </c>
       <c r="J7" t="n">
-        <v>18.63372818165043</v>
+        <v>18.6337281816504</v>
       </c>
       <c r="K7" t="n">
         <v>16.16394070824404</v>
       </c>
       <c r="L7" t="n">
-        <v>15.98532664647455</v>
+        <v>15.98532664647456</v>
       </c>
       <c r="M7" t="n">
-        <v>16.99856590856367</v>
+        <v>16.99856590856368</v>
       </c>
       <c r="N7" t="n">
-        <v>16.1397142531376</v>
+        <v>16.13971425313761</v>
       </c>
       <c r="O7" t="n">
-        <v>16.20771838210057</v>
+        <v>16.20771838210058</v>
       </c>
       <c r="P7" t="n">
-        <v>17.77046597814663</v>
+        <v>17.77046597814665</v>
       </c>
       <c r="Q7" t="n">
         <v>16.51389285640235</v>
       </c>
       <c r="R7" t="n">
-        <v>15.68722314218581</v>
+        <v>15.68722314218582</v>
       </c>
       <c r="S7" t="n">
-        <v>15.99834464765782</v>
+        <v>15.99834464765781</v>
       </c>
       <c r="T7" t="n">
-        <v>15.32111727181477</v>
+        <v>15.32111727181478</v>
       </c>
       <c r="U7" t="n">
         <v>16.16166052112781</v>
@@ -8829,10 +8829,10 @@
         <v>15.80419545705776</v>
       </c>
       <c r="W7" t="n">
-        <v>17.41652477687583</v>
+        <v>17.41652477687584</v>
       </c>
       <c r="X7" t="n">
-        <v>18.08708612240507</v>
+        <v>18.08708612240508</v>
       </c>
       <c r="Y7" t="n">
         <v>21.12683871144795</v>
@@ -8841,10 +8841,10 @@
         <v>16.1278899073798</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.90947192766127</v>
+        <v>15.90947192766125</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.17083783849309</v>
+        <v>24.17083783849311</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.46829207988821</v>
+        <v>28.46829207988818</v>
       </c>
       <c r="C8" t="n">
-        <v>37.97191600465803</v>
+        <v>37.97191600465795</v>
       </c>
       <c r="D8" t="n">
-        <v>38.09649521991788</v>
+        <v>38.09649521991783</v>
       </c>
       <c r="E8" t="n">
-        <v>32.24702862624033</v>
+        <v>32.24702862624029</v>
       </c>
       <c r="F8" t="n">
-        <v>28.93688707477521</v>
+        <v>28.93688707477517</v>
       </c>
       <c r="G8" t="n">
-        <v>49.13177571552963</v>
+        <v>49.13177571552941</v>
       </c>
       <c r="H8" t="n">
-        <v>38.30433635266054</v>
+        <v>38.30433635266048</v>
       </c>
       <c r="I8" t="n">
-        <v>38.40011993655192</v>
+        <v>38.40011993655182</v>
       </c>
       <c r="J8" t="n">
-        <v>41.28314209337724</v>
+        <v>41.28314209337718</v>
       </c>
       <c r="K8" t="n">
-        <v>38.81335461997087</v>
+        <v>38.8133546199708</v>
       </c>
       <c r="L8" t="n">
-        <v>38.63474055820139</v>
+        <v>38.63474055820132</v>
       </c>
       <c r="M8" t="n">
-        <v>39.6479798202906</v>
+        <v>39.64797982029054</v>
       </c>
       <c r="N8" t="n">
-        <v>30.54715175521682</v>
+        <v>30.5471517552168</v>
       </c>
       <c r="O8" t="n">
-        <v>32.88020630500652</v>
+        <v>32.8802063050065</v>
       </c>
       <c r="P8" t="n">
-        <v>33.88775583806403</v>
+        <v>33.88775583806402</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.44126220455012</v>
+        <v>26.44126220455009</v>
       </c>
       <c r="R8" t="n">
-        <v>38.33663705391265</v>
+        <v>38.33663705391257</v>
       </c>
       <c r="S8" t="n">
-        <v>38.64775855938466</v>
+        <v>38.64775855938458</v>
       </c>
       <c r="T8" t="n">
-        <v>37.97053118354161</v>
+        <v>37.97053118354156</v>
       </c>
       <c r="U8" t="n">
-        <v>33.62228666196253</v>
+        <v>33.62228666196247</v>
       </c>
       <c r="V8" t="n">
-        <v>35.54486264894473</v>
+        <v>35.5448626489447</v>
       </c>
       <c r="W8" t="n">
-        <v>40.06802828284595</v>
+        <v>40.06802828284589</v>
       </c>
       <c r="X8" t="n">
-        <v>28.98894642100283</v>
+        <v>28.98894642100284</v>
       </c>
       <c r="Y8" t="n">
-        <v>54.34369873490068</v>
+        <v>54.34369873490066</v>
       </c>
       <c r="Z8" t="n">
-        <v>27.94728636014917</v>
+        <v>27.94728636014912</v>
       </c>
       <c r="AA8" t="n">
-        <v>38.5588858393881</v>
+        <v>38.55888583938803</v>
       </c>
       <c r="AB8" t="n">
-        <v>57.92680072870734</v>
+        <v>57.92680072870732</v>
       </c>
     </row>
     <row r="9">
@@ -8948,79 +8948,79 @@
         <v>28.8212830415116</v>
       </c>
       <c r="D9" t="n">
-        <v>28.94586225677143</v>
+        <v>28.94586225677144</v>
       </c>
       <c r="E9" t="n">
-        <v>27.84710837329335</v>
+        <v>27.84710837329336</v>
       </c>
       <c r="F9" t="n">
-        <v>19.66506386261034</v>
+        <v>19.66506386261035</v>
       </c>
       <c r="G9" t="n">
-        <v>37.77642349338797</v>
+        <v>37.77642349338781</v>
       </c>
       <c r="H9" t="n">
-        <v>29.15370338951411</v>
+        <v>29.1537033895141</v>
       </c>
       <c r="I9" t="n">
-        <v>29.24948697340553</v>
+        <v>29.24948697340549</v>
       </c>
       <c r="J9" t="n">
         <v>32.13250913023079</v>
       </c>
       <c r="K9" t="n">
-        <v>29.66272165682444</v>
+        <v>29.66272165682441</v>
       </c>
       <c r="L9" t="n">
-        <v>29.4841075950549</v>
+        <v>29.48410759505497</v>
       </c>
       <c r="M9" t="n">
-        <v>30.49734685714408</v>
+        <v>30.49734685714406</v>
       </c>
       <c r="N9" t="n">
-        <v>29.63849520171797</v>
+        <v>29.63849520171798</v>
       </c>
       <c r="O9" t="n">
-        <v>31.01438116973086</v>
+        <v>31.01438116973092</v>
       </c>
       <c r="P9" t="n">
-        <v>32.86155206855815</v>
+        <v>32.86155206855818</v>
       </c>
       <c r="Q9" t="n">
         <v>30.01267539546689</v>
       </c>
       <c r="R9" t="n">
-        <v>29.18600409076622</v>
+        <v>29.18600409076619</v>
       </c>
       <c r="S9" t="n">
-        <v>29.49712559623822</v>
+        <v>29.4971255962382</v>
       </c>
       <c r="T9" t="n">
-        <v>28.81989822039516</v>
+        <v>28.81989822039517</v>
       </c>
       <c r="U9" t="n">
         <v>29.66370800976073</v>
       </c>
       <c r="V9" t="n">
-        <v>33.85691367689995</v>
+        <v>33.85691367689998</v>
       </c>
       <c r="W9" t="n">
-        <v>30.9153057254562</v>
+        <v>30.91530572545618</v>
       </c>
       <c r="X9" t="n">
-        <v>31.58586707098547</v>
+        <v>31.58586707098546</v>
       </c>
       <c r="Y9" t="n">
-        <v>34.62561966002838</v>
+        <v>34.62561966002834</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.247408364537</v>
+        <v>27.24740836453698</v>
       </c>
       <c r="AA9" t="n">
-        <v>29.40825287624168</v>
+        <v>29.40825287624163</v>
       </c>
       <c r="AB9" t="n">
-        <v>37.66961878707347</v>
+        <v>37.6696187870735</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.49427387479615</v>
+        <v>21.49427387479618</v>
       </c>
       <c r="C2" t="n">
-        <v>15.76453677347148</v>
+        <v>15.76453677347146</v>
       </c>
       <c r="D2" t="n">
-        <v>21.43226328160576</v>
+        <v>21.43226328160573</v>
       </c>
       <c r="E2" t="n">
-        <v>21.31732393755549</v>
+        <v>21.31732393755548</v>
       </c>
       <c r="F2" t="n">
-        <v>21.49031215024845</v>
+        <v>21.49031215024847</v>
       </c>
       <c r="G2" t="n">
-        <v>22.38231373995821</v>
+        <v>22.38231373995825</v>
       </c>
       <c r="H2" t="n">
-        <v>21.33738723680797</v>
+        <v>21.33738723680795</v>
       </c>
       <c r="I2" t="n">
-        <v>21.4699082476563</v>
+        <v>21.46990824765629</v>
       </c>
       <c r="J2" t="n">
         <v>21.87948163404555</v>
       </c>
       <c r="K2" t="n">
-        <v>21.45591547663294</v>
+        <v>21.45591547663291</v>
       </c>
       <c r="L2" t="n">
         <v>21.41731995975389</v>
       </c>
       <c r="M2" t="n">
-        <v>22.73855529438004</v>
+        <v>22.73855529438003</v>
       </c>
       <c r="N2" t="n">
-        <v>21.43437383303734</v>
+        <v>21.43437383303731</v>
       </c>
       <c r="O2" t="n">
-        <v>28.89384478428556</v>
+        <v>28.89384478428557</v>
       </c>
       <c r="P2" t="n">
-        <v>21.70617251506719</v>
+        <v>21.70617251506722</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.36807231876989</v>
+        <v>21.36807231876984</v>
       </c>
       <c r="R2" t="n">
-        <v>21.34181164367455</v>
+        <v>21.34181164367464</v>
       </c>
       <c r="S2" t="n">
-        <v>21.61817821173708</v>
+        <v>21.61817821173698</v>
       </c>
       <c r="T2" t="n">
-        <v>21.3813822063387</v>
+        <v>21.38138220633866</v>
       </c>
       <c r="U2" t="n">
-        <v>25.24123643707623</v>
+        <v>25.24123643707621</v>
       </c>
       <c r="V2" t="n">
-        <v>21.46857710411926</v>
+        <v>21.46857710411931</v>
       </c>
       <c r="W2" t="n">
-        <v>27.23057379125947</v>
+        <v>27.23057379125941</v>
       </c>
       <c r="X2" t="n">
-        <v>21.4955261803871</v>
+        <v>21.49552618038712</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.64243821774007</v>
+        <v>21.64243821774011</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.96831273648418</v>
+        <v>27.96831273648409</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.67164353990161</v>
+        <v>21.67164353990167</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.87338174561296</v>
+        <v>22.87338174561293</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.59836707736653</v>
+        <v>23.14224171820514</v>
       </c>
       <c r="C3" t="n">
-        <v>18.02771630773206</v>
+        <v>16.25553831415238</v>
       </c>
       <c r="D3" t="n">
-        <v>26.24166535410428</v>
+        <v>22.74020697306093</v>
       </c>
       <c r="E3" t="n">
-        <v>18.33502002479857</v>
+        <v>16.64150953691766</v>
       </c>
       <c r="F3" t="n">
-        <v>27.62478105751323</v>
+        <v>23.24072848851326</v>
       </c>
       <c r="G3" t="n">
-        <v>48.06766893805099</v>
+        <v>30.13296949566783</v>
       </c>
       <c r="H3" t="n">
-        <v>24.04513068161843</v>
+        <v>21.99061920566681</v>
       </c>
       <c r="I3" t="n">
-        <v>27.13062581547932</v>
+        <v>23.05833473725859</v>
       </c>
       <c r="J3" t="n">
-        <v>36.53863297020791</v>
+        <v>26.24036083173975</v>
       </c>
       <c r="K3" t="n">
-        <v>26.7868039331381</v>
+        <v>22.92618237125767</v>
       </c>
       <c r="L3" t="n">
-        <v>25.85366879743496</v>
+        <v>22.57690379492382</v>
       </c>
       <c r="M3" t="n">
-        <v>59.70435538345907</v>
+        <v>34.38757245763765</v>
       </c>
       <c r="N3" t="n">
-        <v>26.2713585884272</v>
+        <v>22.73556255758706</v>
       </c>
       <c r="O3" t="n">
-        <v>37.04310806132315</v>
+        <v>31.15795010260706</v>
       </c>
       <c r="P3" t="n">
-        <v>32.46175952904553</v>
+        <v>24.80190802327237</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.73449055255051</v>
+        <v>22.20604428208497</v>
       </c>
       <c r="R3" t="n">
-        <v>24.14072930551634</v>
+        <v>22.01453779880177</v>
       </c>
       <c r="S3" t="n">
-        <v>30.47744276273276</v>
+        <v>24.13791595730353</v>
       </c>
       <c r="T3" t="n">
-        <v>25.05597253937936</v>
+        <v>22.32738293677017</v>
       </c>
       <c r="U3" t="n">
-        <v>37.93342475081449</v>
+        <v>28.97872086479471</v>
       </c>
       <c r="V3" t="n">
-        <v>27.01599740159164</v>
+        <v>22.95470466321627</v>
       </c>
       <c r="W3" t="n">
-        <v>36.08828042637098</v>
+        <v>29.7913813350798</v>
       </c>
       <c r="X3" t="n">
-        <v>27.71250483317134</v>
+        <v>23.24642600841173</v>
       </c>
       <c r="Y3" t="n">
-        <v>31.09519352530368</v>
+        <v>24.39298050644614</v>
       </c>
       <c r="Z3" t="n">
-        <v>36.49704640545576</v>
+        <v>30.38232044630526</v>
       </c>
       <c r="AA3" t="n">
-        <v>31.76735455696258</v>
+        <v>24.6302324143913</v>
       </c>
       <c r="AB3" t="n">
-        <v>59.64512246122719</v>
+        <v>34.65414647799553</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80.83421244859878</v>
+        <v>80.8342124485952</v>
       </c>
       <c r="C4" t="n">
-        <v>46.43740104499172</v>
+        <v>46.43740104499579</v>
       </c>
       <c r="D4" t="n">
-        <v>73.91096099219976</v>
+        <v>73.91096099219951</v>
       </c>
       <c r="E4" t="n">
-        <v>35.87646203413696</v>
+        <v>35.87646203413546</v>
       </c>
       <c r="F4" t="n">
-        <v>89.89490808415711</v>
+        <v>89.89490808415698</v>
       </c>
       <c r="G4" t="n">
-        <v>274.5107872497494</v>
+        <v>274.5107872497505</v>
       </c>
       <c r="H4" t="n">
-        <v>53.02386112773883</v>
+        <v>53.02386112773621</v>
       </c>
       <c r="I4" t="n">
-        <v>83.78574036951116</v>
+        <v>83.78574036951323</v>
       </c>
       <c r="J4" t="n">
-        <v>169.8419161308595</v>
+        <v>169.8419161308585</v>
       </c>
       <c r="K4" t="n">
-        <v>79.05251456739914</v>
+        <v>79.05251456739548</v>
       </c>
       <c r="L4" t="n">
-        <v>67.16033777320871</v>
+        <v>67.16033777320411</v>
       </c>
       <c r="M4" t="n">
-        <v>423.8657334709084</v>
+        <v>423.8657334709088</v>
       </c>
       <c r="N4" t="n">
-        <v>72.74358057785916</v>
+        <v>72.74358057785979</v>
       </c>
       <c r="O4" t="n">
-        <v>99.25428740613555</v>
+        <v>99.25428740612952</v>
       </c>
       <c r="P4" t="n">
         <v>126.4271245696351</v>
       </c>
       <c r="Q4" t="n">
-        <v>57.70596482936852</v>
+        <v>57.70596482937054</v>
       </c>
       <c r="R4" t="n">
-        <v>53.14752844515753</v>
+        <v>53.1475284451582</v>
       </c>
       <c r="S4" t="n">
-        <v>109.4016392111163</v>
+        <v>109.4016392111089</v>
       </c>
       <c r="T4" t="n">
-        <v>61.87698432731872</v>
+        <v>61.87698432731243</v>
       </c>
       <c r="U4" t="n">
-        <v>149.5541684812711</v>
+        <v>149.5541684812719</v>
       </c>
       <c r="V4" t="n">
-        <v>76.15996438588664</v>
+        <v>76.15996438588661</v>
       </c>
       <c r="W4" t="n">
-        <v>113.1629904501171</v>
+        <v>113.162990450122</v>
       </c>
       <c r="X4" t="n">
-        <v>88.32732513037391</v>
+        <v>88.32732513037206</v>
       </c>
       <c r="Y4" t="n">
-        <v>119.5969732904741</v>
+        <v>119.5969732904744</v>
       </c>
       <c r="Z4" t="n">
-        <v>105.7272039303547</v>
+        <v>105.7272039303526</v>
       </c>
       <c r="AA4" t="n">
-        <v>126.542205058132</v>
+        <v>126.5422050581356</v>
       </c>
       <c r="AB4" t="n">
-        <v>435.894175060104</v>
+        <v>435.8941750601055</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.49483799447191</v>
+        <v>33.49483799446367</v>
       </c>
       <c r="C5" t="n">
-        <v>44.2641442296689</v>
+        <v>44.26414422966419</v>
       </c>
       <c r="D5" t="n">
-        <v>45.54986675982229</v>
+        <v>45.54986675982094</v>
       </c>
       <c r="E5" t="n">
-        <v>37.45966411017863</v>
+        <v>37.45966411017596</v>
       </c>
       <c r="F5" t="n">
-        <v>35.43724116654577</v>
+        <v>35.43724116654082</v>
       </c>
       <c r="G5" t="n">
-        <v>58.92605289627774</v>
+        <v>58.92605289627481</v>
       </c>
       <c r="H5" t="n">
-        <v>44.47819818869428</v>
+        <v>44.47819818869091</v>
       </c>
       <c r="I5" t="n">
-        <v>45.97508396890309</v>
+        <v>45.97508396889928</v>
       </c>
       <c r="J5" t="n">
-        <v>50.56947532932018</v>
+        <v>50.56947532932037</v>
       </c>
       <c r="K5" t="n">
-        <v>45.81702918320161</v>
+        <v>45.81702918320782</v>
       </c>
       <c r="L5" t="n">
-        <v>45.38107506523771</v>
+        <v>45.38107506523505</v>
       </c>
       <c r="M5" t="n">
-        <v>61.74191094517042</v>
+        <v>61.74191094517305</v>
       </c>
       <c r="N5" t="n">
-        <v>72.74358057785916</v>
+        <v>35.68608558638265</v>
       </c>
       <c r="O5" t="n">
-        <v>40.13350585460748</v>
+        <v>40.13350585460369</v>
       </c>
       <c r="P5" t="n">
-        <v>40.80732841792069</v>
+        <v>40.80732841791193</v>
       </c>
       <c r="Q5" t="n">
-        <v>29.56259297999514</v>
+        <v>29.56259297999187</v>
       </c>
       <c r="R5" t="n">
-        <v>44.52817389958006</v>
+        <v>44.5281738995792</v>
       </c>
       <c r="S5" t="n">
-        <v>47.64986142074881</v>
+        <v>47.64986142074744</v>
       </c>
       <c r="T5" t="n">
-        <v>44.97514160822984</v>
+        <v>44.97514160823412</v>
       </c>
       <c r="U5" t="n">
-        <v>43.36757056019279</v>
+        <v>43.36757056018921</v>
       </c>
       <c r="V5" t="n">
-        <v>42.26635182314929</v>
+        <v>42.26635182314932</v>
       </c>
       <c r="W5" t="n">
-        <v>47.63019837439487</v>
+        <v>47.63019837438988</v>
       </c>
       <c r="X5" t="n">
-        <v>32.17130686982669</v>
+        <v>32.17130686982237</v>
       </c>
       <c r="Y5" t="n">
-        <v>60.60184759692141</v>
+        <v>60.60184759692257</v>
       </c>
       <c r="Z5" t="n">
-        <v>34.4959169432221</v>
+        <v>34.49591694321806</v>
       </c>
       <c r="AA5" t="n">
-        <v>48.2537768976333</v>
+        <v>48.25377689763589</v>
       </c>
       <c r="AB5" t="n">
-        <v>75.00989984371907</v>
+        <v>75.00989984371735</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.99020295776751</v>
+        <v>33.99020295776957</v>
       </c>
       <c r="C6" t="n">
-        <v>37.69290154420023</v>
+        <v>37.69290154419636</v>
       </c>
       <c r="D6" t="n">
-        <v>38.97862407435366</v>
+        <v>38.97862407434776</v>
       </c>
       <c r="E6" t="n">
-        <v>36.36736483720206</v>
+        <v>36.36736483720503</v>
       </c>
       <c r="F6" t="n">
-        <v>26.51994105598756</v>
+        <v>26.51994105598803</v>
       </c>
       <c r="G6" t="n">
-        <v>49.70987980988856</v>
+        <v>49.70987980988377</v>
       </c>
       <c r="H6" t="n">
-        <v>37.90695550322563</v>
+        <v>37.90695550322579</v>
       </c>
       <c r="I6" t="n">
-        <v>39.40384128343442</v>
+        <v>39.40384128343679</v>
       </c>
       <c r="J6" t="n">
-        <v>43.99823264385151</v>
+        <v>43.99823264384784</v>
       </c>
       <c r="K6" t="n">
-        <v>39.24578649773296</v>
+        <v>39.24578649773463</v>
       </c>
       <c r="L6" t="n">
-        <v>38.80983237976908</v>
+        <v>38.8098323797659</v>
       </c>
       <c r="M6" t="n">
-        <v>55.17066825970112</v>
+        <v>55.17066825969917</v>
       </c>
       <c r="N6" t="n">
-        <v>72.74358057785916</v>
+        <v>39.00246372367262</v>
       </c>
       <c r="O6" t="n">
-        <v>42.61795881128377</v>
+        <v>42.61795881128471</v>
       </c>
       <c r="P6" t="n">
-        <v>44.36784982363753</v>
+        <v>44.36784982363667</v>
       </c>
       <c r="Q6" t="n">
-        <v>38.25355638346156</v>
+        <v>38.25355638345483</v>
       </c>
       <c r="R6" t="n">
-        <v>37.95693121411144</v>
+        <v>37.95693121410601</v>
       </c>
       <c r="S6" t="n">
-        <v>41.07861873528017</v>
+        <v>41.07861873527962</v>
       </c>
       <c r="T6" t="n">
-        <v>38.40389892276118</v>
+        <v>38.40389892275686</v>
       </c>
       <c r="U6" t="n">
-        <v>43.0247386623346</v>
+        <v>43.02473866233623</v>
       </c>
       <c r="V6" t="n">
-        <v>45.74909456287628</v>
+        <v>45.74909456287625</v>
       </c>
       <c r="W6" t="n">
-        <v>41.05644887339071</v>
+        <v>41.05644887339079</v>
       </c>
       <c r="X6" t="n">
-        <v>39.69320761846007</v>
+        <v>39.69320761845765</v>
       </c>
       <c r="Y6" t="n">
-        <v>41.35264666323798</v>
+        <v>41.35264666322833</v>
       </c>
       <c r="Z6" t="n">
-        <v>37.48720377515488</v>
+        <v>37.48720377514672</v>
       </c>
       <c r="AA6" t="n">
-        <v>41.68253421216465</v>
+        <v>41.68253421216266</v>
       </c>
       <c r="AB6" t="n">
-        <v>55.11450534209536</v>
+        <v>55.11450534209258</v>
       </c>
     </row>
   </sheetData>
@@ -1182,82 +1182,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.19137928957403</v>
+        <v>20.191379289574</v>
       </c>
       <c r="C2" t="n">
-        <v>14.53624947580797</v>
+        <v>14.53624947580798</v>
       </c>
       <c r="D2" t="n">
-        <v>20.10478654650179</v>
+        <v>20.10478654650177</v>
       </c>
       <c r="E2" t="n">
-        <v>20.07135631875592</v>
+        <v>20.0713563187559</v>
       </c>
       <c r="F2" t="n">
-        <v>20.11888445956162</v>
+        <v>20.11888445956161</v>
       </c>
       <c r="G2" t="n">
-        <v>20.17333585895254</v>
+        <v>20.17333585895252</v>
       </c>
       <c r="H2" t="n">
-        <v>20.1620060997065</v>
+        <v>20.16200609970648</v>
       </c>
       <c r="I2" t="n">
-        <v>20.19943372885132</v>
+        <v>20.19943372885133</v>
       </c>
       <c r="J2" t="n">
-        <v>20.16228729554952</v>
+        <v>20.16228729554944</v>
       </c>
       <c r="K2" t="n">
-        <v>20.17856747378471</v>
+        <v>20.17856747378472</v>
       </c>
       <c r="L2" t="n">
-        <v>20.14749188057355</v>
+        <v>20.14749188057353</v>
       </c>
       <c r="M2" t="n">
-        <v>20.00916939639455</v>
+        <v>20.00916939639458</v>
       </c>
       <c r="N2" t="n">
-        <v>20.14156090510414</v>
+        <v>20.14156090510411</v>
       </c>
       <c r="O2" t="n">
-        <v>26.90299114729644</v>
+        <v>26.90299114729643</v>
       </c>
       <c r="P2" t="n">
-        <v>20.16865328853685</v>
+        <v>20.16865328853673</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.16808114888289</v>
+        <v>20.16808114888287</v>
       </c>
       <c r="R2" t="n">
-        <v>20.18323151285804</v>
+        <v>20.18323151285802</v>
       </c>
       <c r="S2" t="n">
-        <v>20.1576739427845</v>
+        <v>20.15767394278448</v>
       </c>
       <c r="T2" t="n">
-        <v>20.11040936408481</v>
+        <v>20.11040936408479</v>
       </c>
       <c r="U2" t="n">
-        <v>23.39832796023913</v>
+        <v>23.39832796023907</v>
       </c>
       <c r="V2" t="n">
-        <v>20.16040428566183</v>
+        <v>20.1604042856618</v>
       </c>
       <c r="W2" t="n">
-        <v>25.62458341085321</v>
+        <v>25.62458341085317</v>
       </c>
       <c r="X2" t="n">
-        <v>20.38480134841041</v>
+        <v>20.3848013484104</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.35660913478991</v>
+        <v>20.35660913478988</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.30586283482009</v>
+        <v>26.3058628348201</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.21485190285192</v>
+        <v>20.2148519028519</v>
       </c>
       <c r="AB2" t="n">
         <v>20.11991376212043</v>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.65980945543129</v>
+        <v>21.18798823156275</v>
       </c>
       <c r="C3" t="n">
-        <v>15.73815174111164</v>
+        <v>14.86577840821052</v>
       </c>
       <c r="D3" t="n">
-        <v>21.68986292721894</v>
+        <v>20.55272701372235</v>
       </c>
       <c r="E3" t="n">
-        <v>15.82862067451841</v>
+        <v>15.26704098198984</v>
       </c>
       <c r="F3" t="n">
-        <v>22.02592972594183</v>
+        <v>20.6654558973676</v>
       </c>
       <c r="G3" t="n">
-        <v>23.24680161490949</v>
+        <v>21.05605811237451</v>
       </c>
       <c r="H3" t="n">
-        <v>23.04251562372049</v>
+        <v>21.03143862488368</v>
       </c>
       <c r="I3" t="n">
-        <v>23.90390756112546</v>
+        <v>21.31640930573857</v>
       </c>
       <c r="J3" t="n">
-        <v>23.00645572321778</v>
+        <v>20.98565140598658</v>
       </c>
       <c r="K3" t="n">
-        <v>23.40618024889213</v>
+        <v>21.13426009617802</v>
       </c>
       <c r="L3" t="n">
-        <v>22.66487033336002</v>
+        <v>20.87158838581789</v>
       </c>
       <c r="M3" t="n">
-        <v>22.56235111996374</v>
+        <v>20.76712808617194</v>
       </c>
       <c r="N3" t="n">
-        <v>22.53754116745649</v>
+        <v>20.8297865122313</v>
       </c>
       <c r="O3" t="n">
-        <v>29.55146452605309</v>
+        <v>27.65134421448422</v>
       </c>
       <c r="P3" t="n">
-        <v>23.13172921498542</v>
+        <v>21.00933438568123</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.15736685024843</v>
+        <v>21.03659573468335</v>
       </c>
       <c r="R3" t="n">
-        <v>23.5317445582236</v>
+        <v>21.19351496984895</v>
       </c>
       <c r="S3" t="n">
-        <v>22.89108681573299</v>
+        <v>20.93163667865544</v>
       </c>
       <c r="T3" t="n">
-        <v>21.82083340874721</v>
+        <v>20.58985025525544</v>
       </c>
       <c r="U3" t="n">
-        <v>26.59580014796752</v>
+        <v>24.32583252879328</v>
       </c>
       <c r="V3" t="n">
-        <v>22.95252129220143</v>
+        <v>20.96011393746966</v>
       </c>
       <c r="W3" t="n">
-        <v>30.92971329634046</v>
+        <v>27.22339661322875</v>
       </c>
       <c r="X3" t="n">
-        <v>28.21157598963839</v>
+        <v>22.76202752037205</v>
       </c>
       <c r="Y3" t="n">
-        <v>27.52875859152915</v>
+        <v>22.55541232905469</v>
       </c>
       <c r="Z3" t="n">
-        <v>28.4904126651375</v>
+        <v>26.91088786307446</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.23317485536723</v>
+        <v>21.4118223264736</v>
       </c>
       <c r="AB3" t="n">
-        <v>22.10992403209529</v>
+        <v>20.7057792993554</v>
       </c>
     </row>
     <row r="4">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.29920915022185</v>
+        <v>47.29920915022174</v>
       </c>
       <c r="C4" t="n">
         <v>30.50608771152005</v>
       </c>
       <c r="D4" t="n">
-        <v>33.82888482341158</v>
+        <v>33.82888482341159</v>
       </c>
       <c r="E4" t="n">
-        <v>19.17741214784026</v>
+        <v>19.17741214784024</v>
       </c>
       <c r="F4" t="n">
-        <v>36.63222496862473</v>
+        <v>36.6322249686247</v>
       </c>
       <c r="G4" t="n">
-        <v>44.52624183810126</v>
+        <v>44.52624183810118</v>
       </c>
       <c r="H4" t="n">
-        <v>46.66700276259002</v>
+        <v>46.66700276259007</v>
       </c>
       <c r="I4" t="n">
-        <v>53.18211482358482</v>
+        <v>53.18211482358467</v>
       </c>
       <c r="J4" t="n">
-        <v>43.48808956194222</v>
+        <v>43.48808956194219</v>
       </c>
       <c r="K4" t="n">
-        <v>47.99104593575512</v>
+        <v>47.9910459357551</v>
       </c>
       <c r="L4" t="n">
         <v>40.84601016763985</v>
       </c>
       <c r="M4" t="n">
-        <v>43.03406412362875</v>
+        <v>43.0340641236287</v>
       </c>
       <c r="N4" t="n">
-        <v>40.02814120245154</v>
+        <v>40.02814120245152</v>
       </c>
       <c r="O4" t="n">
-        <v>40.66142054900283</v>
+        <v>40.66142054900282</v>
       </c>
       <c r="P4" t="n">
-        <v>42.96810783145703</v>
+        <v>42.96810783145705</v>
       </c>
       <c r="Q4" t="n">
-        <v>44.9629382133181</v>
+        <v>44.96293821331806</v>
       </c>
       <c r="R4" t="n">
-        <v>50.39251664632431</v>
+        <v>50.39251664632425</v>
       </c>
       <c r="S4" t="n">
-        <v>41.44022413058423</v>
+        <v>41.44022413058417</v>
       </c>
       <c r="T4" t="n">
-        <v>34.41771993614329</v>
+        <v>34.41771993614326</v>
       </c>
       <c r="U4" t="n">
-        <v>46.16629457797187</v>
+        <v>46.16629457797178</v>
       </c>
       <c r="V4" t="n">
-        <v>42.26383707065428</v>
+        <v>42.26383707065422</v>
       </c>
       <c r="W4" t="n">
-        <v>65.70015677383857</v>
+        <v>65.70015677383856</v>
       </c>
       <c r="X4" t="n">
-        <v>87.7188573609514</v>
+        <v>87.71885736095155</v>
       </c>
       <c r="Y4" t="n">
-        <v>83.41119027918931</v>
+        <v>83.41119027918928</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.76818722414653</v>
+        <v>36.76818722414655</v>
       </c>
       <c r="AA4" t="n">
-        <v>54.40786373771967</v>
+        <v>54.40786373771959</v>
       </c>
       <c r="AB4" t="n">
-        <v>38.22103386901194</v>
+        <v>38.22103386901193</v>
       </c>
     </row>
     <row r="5">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.64530043570155</v>
+        <v>27.64530043570151</v>
       </c>
       <c r="C5" t="n">
-        <v>36.82468948070616</v>
+        <v>36.82468948070618</v>
       </c>
       <c r="D5" t="n">
-        <v>37.01810000807065</v>
+        <v>37.01810000807066</v>
       </c>
       <c r="E5" t="n">
-        <v>31.12893892510815</v>
+        <v>31.12893892510812</v>
       </c>
       <c r="F5" t="n">
-        <v>28.4389879197239</v>
+        <v>28.43898791972392</v>
       </c>
       <c r="G5" t="n">
-        <v>39.93872349201631</v>
+        <v>39.93872349201632</v>
       </c>
       <c r="H5" t="n">
-        <v>37.66442118381279</v>
+        <v>37.66442118381277</v>
       </c>
       <c r="I5" t="n">
-        <v>38.0871834725635</v>
+        <v>38.08718347256345</v>
       </c>
       <c r="J5" t="n">
-        <v>37.6396516975452</v>
+        <v>37.63965169754518</v>
       </c>
       <c r="K5" t="n">
-        <v>37.85148952263475</v>
+        <v>37.85148952263476</v>
       </c>
       <c r="L5" t="n">
-        <v>37.50047640183531</v>
+        <v>37.50047640183536</v>
       </c>
       <c r="M5" t="n">
-        <v>37.50345182114062</v>
+        <v>37.50345182114064</v>
       </c>
       <c r="N5" t="n">
-        <v>40.02814120245154</v>
+        <v>29.4098006961697</v>
       </c>
       <c r="O5" t="n">
-        <v>31.75790038713173</v>
+        <v>31.75790038713171</v>
       </c>
       <c r="P5" t="n">
-        <v>31.38030597836363</v>
+        <v>31.38030597836361</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.34794824834844</v>
+        <v>25.34794824834843</v>
       </c>
       <c r="R5" t="n">
-        <v>37.90417198953173</v>
+        <v>37.9041719895317</v>
       </c>
       <c r="S5" t="n">
-        <v>37.61548747848796</v>
+        <v>37.61548747848799</v>
       </c>
       <c r="T5" t="n">
-        <v>37.08161231929463</v>
+        <v>37.08161231929466</v>
       </c>
       <c r="U5" t="n">
-        <v>32.79601452625398</v>
+        <v>32.79601452625397</v>
       </c>
       <c r="V5" t="n">
-        <v>34.63854315258745</v>
+        <v>34.63854315258738</v>
       </c>
       <c r="W5" t="n">
-        <v>38.9199524366569</v>
+        <v>38.91995243665691</v>
       </c>
       <c r="X5" t="n">
-        <v>28.7445835582846</v>
+        <v>28.74458355828461</v>
       </c>
       <c r="Y5" t="n">
         <v>50.15244098020864</v>
       </c>
       <c r="Z5" t="n">
-        <v>26.79333640083157</v>
+        <v>26.79333640083155</v>
       </c>
       <c r="AA5" t="n">
-        <v>38.26133884061075</v>
+        <v>38.26133884061077</v>
       </c>
       <c r="AB5" t="n">
-        <v>48.03444086318967</v>
+        <v>48.03444086318962</v>
       </c>
     </row>
     <row r="6">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.47942391297363</v>
+        <v>23.47942391297359</v>
       </c>
       <c r="C6" t="n">
-        <v>25.66108125047083</v>
+        <v>25.66108125047079</v>
       </c>
       <c r="D6" t="n">
-        <v>25.8544917778353</v>
+        <v>25.85449177783527</v>
       </c>
       <c r="E6" t="n">
         <v>24.7029841141859</v>
       </c>
       <c r="F6" t="n">
-        <v>18.28375464195661</v>
+        <v>18.28375464195659</v>
       </c>
       <c r="G6" t="n">
-        <v>26.62878874098063</v>
+        <v>26.62878874098061</v>
       </c>
       <c r="H6" t="n">
-        <v>26.50081295357738</v>
+        <v>26.50081295357736</v>
       </c>
       <c r="I6" t="n">
-        <v>26.92357524232806</v>
+        <v>26.92357524232805</v>
       </c>
       <c r="J6" t="n">
         <v>26.4760434673098</v>
       </c>
       <c r="K6" t="n">
-        <v>26.68788129239939</v>
+        <v>26.68788129239937</v>
       </c>
       <c r="L6" t="n">
-        <v>26.33686817159999</v>
+        <v>26.33686817159997</v>
       </c>
       <c r="M6" t="n">
-        <v>26.3398435909051</v>
+        <v>26.33984359090506</v>
       </c>
       <c r="N6" t="n">
-        <v>40.02814120245154</v>
+        <v>26.2698750752895</v>
       </c>
       <c r="O6" t="n">
-        <v>27.52423542705585</v>
+        <v>27.52423542705584</v>
       </c>
       <c r="P6" t="n">
-        <v>27.92880938157752</v>
+        <v>27.92880938157751</v>
       </c>
       <c r="Q6" t="n">
-        <v>26.56943437345795</v>
+        <v>26.56943437345794</v>
       </c>
       <c r="R6" t="n">
-        <v>26.74056375929634</v>
+        <v>26.74056375929633</v>
       </c>
       <c r="S6" t="n">
         <v>26.45187924825257</v>
       </c>
       <c r="T6" t="n">
-        <v>25.91800408905932</v>
+        <v>25.91800408905929</v>
       </c>
       <c r="U6" t="n">
-        <v>26.68558492356748</v>
+        <v>26.68558492356745</v>
       </c>
       <c r="V6" t="n">
-        <v>30.17463073724195</v>
+        <v>30.17463073724192</v>
       </c>
       <c r="W6" t="n">
-        <v>27.75430995618455</v>
+        <v>27.75430995618452</v>
       </c>
       <c r="X6" t="n">
-        <v>29.01738777856612</v>
+        <v>29.0173877785661</v>
       </c>
       <c r="Y6" t="n">
-        <v>28.69894375666353</v>
+        <v>28.69894375666352</v>
       </c>
       <c r="Z6" t="n">
-        <v>24.15124136803258</v>
+        <v>24.15124136803255</v>
       </c>
       <c r="AA6" t="n">
-        <v>27.0977306103754</v>
+        <v>27.09773061037536</v>
       </c>
       <c r="AB6" t="n">
-        <v>26.05844741595559</v>
+        <v>26.05844741595556</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.39297878595209</v>
+        <v>21.39297878595205</v>
       </c>
       <c r="C2" t="n">
-        <v>15.61080934411246</v>
+        <v>15.61080934411245</v>
       </c>
       <c r="D2" t="n">
-        <v>21.42636615328231</v>
+        <v>21.42636615328228</v>
       </c>
       <c r="E2" t="n">
-        <v>21.20462375306084</v>
+        <v>21.20462375306081</v>
       </c>
       <c r="F2" t="n">
-        <v>21.36193938223525</v>
+        <v>21.3619393822352</v>
       </c>
       <c r="G2" t="n">
-        <v>22.24874908605562</v>
+        <v>22.24874908605555</v>
       </c>
       <c r="H2" t="n">
-        <v>21.18606598425896</v>
+        <v>21.18606598425895</v>
       </c>
       <c r="I2" t="n">
-        <v>21.26269672873062</v>
+        <v>21.2626967287306</v>
       </c>
       <c r="J2" t="n">
-        <v>21.79542959961927</v>
+        <v>21.79542959961923</v>
       </c>
       <c r="K2" t="n">
-        <v>21.35714185161123</v>
+        <v>21.3571418516112</v>
       </c>
       <c r="L2" t="n">
-        <v>21.28708519290852</v>
+        <v>21.28708519290856</v>
       </c>
       <c r="M2" t="n">
-        <v>22.52873691233606</v>
+        <v>22.52873691233603</v>
       </c>
       <c r="N2" t="n">
-        <v>21.31212810209558</v>
+        <v>21.31212810209554</v>
       </c>
       <c r="O2" t="n">
         <v>28.70519110472675</v>
       </c>
       <c r="P2" t="n">
-        <v>21.6999042260076</v>
+        <v>21.69990422600752</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.27964244680677</v>
+        <v>21.27964244680673</v>
       </c>
       <c r="R2" t="n">
-        <v>21.20633668237936</v>
+        <v>21.20633668237933</v>
       </c>
       <c r="S2" t="n">
-        <v>21.51372978247364</v>
+        <v>21.51372978247365</v>
       </c>
       <c r="T2" t="n">
-        <v>21.26377712935967</v>
+        <v>21.26377712935964</v>
       </c>
       <c r="U2" t="n">
         <v>24.98984996198467</v>
       </c>
       <c r="V2" t="n">
-        <v>21.3015039674582</v>
+        <v>21.30150396745817</v>
       </c>
       <c r="W2" t="n">
-        <v>27.03892919321737</v>
+        <v>27.03892919321731</v>
       </c>
       <c r="X2" t="n">
         <v>21.4120711234762</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.5131829963935</v>
+        <v>21.51318299639346</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.75177809148663</v>
+        <v>27.7517780914866</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.38098762997771</v>
+        <v>21.38098762997769</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.72817957619779</v>
+        <v>22.72817957619778</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.46739411021623</v>
+        <v>23.03388262849475</v>
       </c>
       <c r="C3" t="n">
-        <v>16.83905812135275</v>
+        <v>15.78467893988396</v>
       </c>
       <c r="D3" t="n">
-        <v>28.33791367901052</v>
+        <v>23.41310314350937</v>
       </c>
       <c r="E3" t="n">
-        <v>17.95869772372915</v>
+        <v>16.46383499954863</v>
       </c>
       <c r="F3" t="n">
-        <v>26.85726593366309</v>
+        <v>22.90035926716999</v>
       </c>
       <c r="G3" t="n">
-        <v>47.1899145102227</v>
+        <v>29.74727125513714</v>
       </c>
       <c r="H3" t="n">
-        <v>22.73909745809401</v>
+        <v>21.47041588327418</v>
       </c>
       <c r="I3" t="n">
-        <v>24.5225585603876</v>
+        <v>22.08374844626802</v>
       </c>
       <c r="J3" t="n">
-        <v>36.81348307466624</v>
+        <v>26.26743158497754</v>
       </c>
       <c r="K3" t="n">
-        <v>26.71218001509467</v>
+        <v>22.82258427913983</v>
       </c>
       <c r="L3" t="n">
-        <v>25.05259527812024</v>
+        <v>22.24026923950319</v>
       </c>
       <c r="M3" t="n">
-        <v>57.04280709424864</v>
+        <v>33.37198710911608</v>
       </c>
       <c r="N3" t="n">
-        <v>25.65308322399665</v>
+        <v>22.46070063557785</v>
       </c>
       <c r="O3" t="n">
-        <v>36.27144830151128</v>
+        <v>30.79121652998711</v>
       </c>
       <c r="P3" t="n">
-        <v>34.51606690238665</v>
+        <v>25.4365856292063</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.90300990576784</v>
+        <v>22.20311055006176</v>
       </c>
       <c r="R3" t="n">
-        <v>23.20876033219118</v>
+        <v>21.62673908014364</v>
       </c>
       <c r="S3" t="n">
-        <v>30.27289089187328</v>
+        <v>23.99953727089731</v>
       </c>
       <c r="T3" t="n">
-        <v>24.54388935031917</v>
+        <v>22.08826979904298</v>
       </c>
       <c r="U3" t="n">
-        <v>35.72174274568825</v>
+        <v>28.11683384904522</v>
       </c>
       <c r="V3" t="n">
-        <v>25.36835549926178</v>
+        <v>22.33368885742324</v>
       </c>
       <c r="W3" t="n">
-        <v>35.33062165489407</v>
+        <v>29.42599939802803</v>
       </c>
       <c r="X3" t="n">
-        <v>27.99718797447314</v>
+        <v>23.28242736298611</v>
       </c>
       <c r="Y3" t="n">
-        <v>30.31393035723407</v>
+        <v>24.05519213039003</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.02550082545871</v>
+        <v>29.77598527883753</v>
       </c>
       <c r="AA3" t="n">
-        <v>27.24078945404765</v>
+        <v>23.00102837038901</v>
       </c>
       <c r="AB3" t="n">
-        <v>58.48908859714238</v>
+        <v>34.1877620527432</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.86751252353433</v>
+        <v>75.8675125235399</v>
       </c>
       <c r="C4" t="n">
-        <v>34.32002911253266</v>
+        <v>34.32002911253269</v>
       </c>
       <c r="D4" t="n">
-        <v>91.04887680303142</v>
+        <v>91.04887680303119</v>
       </c>
       <c r="E4" t="n">
-        <v>31.48101226945125</v>
+        <v>31.48101226945572</v>
       </c>
       <c r="F4" t="n">
-        <v>77.43948485646784</v>
+        <v>77.439484856468</v>
       </c>
       <c r="G4" t="n">
-        <v>249.4332485754635</v>
+        <v>249.4332485754612</v>
       </c>
       <c r="H4" t="n">
-        <v>38.20269374522478</v>
+        <v>38.20269374522483</v>
       </c>
       <c r="I4" t="n">
-        <v>54.60635958739964</v>
+        <v>54.60635958739972</v>
       </c>
       <c r="J4" t="n">
-        <v>162.9273027860844</v>
+        <v>162.927302786084</v>
       </c>
       <c r="K4" t="n">
-        <v>73.58863511043059</v>
+        <v>73.58863511043128</v>
       </c>
       <c r="L4" t="n">
-        <v>57.06100052915029</v>
+        <v>57.06100052918689</v>
       </c>
       <c r="M4" t="n">
-        <v>371.6333814216426</v>
+        <v>371.6333814216429</v>
       </c>
       <c r="N4" t="n">
-        <v>63.85448785955532</v>
+        <v>63.85448785955563</v>
       </c>
       <c r="O4" t="n">
-        <v>88.14947513042253</v>
+        <v>88.14947513042263</v>
       </c>
       <c r="P4" t="n">
-        <v>137.7871256982373</v>
+        <v>137.7871256982371</v>
       </c>
       <c r="Q4" t="n">
-        <v>57.06740261259976</v>
+        <v>57.06740261260091</v>
       </c>
       <c r="R4" t="n">
-        <v>42.11262943025477</v>
+        <v>42.11262943025487</v>
       </c>
       <c r="S4" t="n">
-        <v>101.6646632831862</v>
+        <v>101.6646632831865</v>
       </c>
       <c r="T4" t="n">
-        <v>54.5422581356667</v>
+        <v>54.54225813566739</v>
       </c>
       <c r="U4" t="n">
         <v>122.2364071118484</v>
       </c>
       <c r="V4" t="n">
-        <v>58.36629390326767</v>
+        <v>58.36629390326753</v>
       </c>
       <c r="W4" t="n">
-        <v>101.2210686187662</v>
+        <v>101.221068618766</v>
       </c>
       <c r="X4" t="n">
-        <v>86.81311663655401</v>
+        <v>86.81311663655529</v>
       </c>
       <c r="Y4" t="n">
-        <v>105.8481053438998</v>
+        <v>105.8481053438999</v>
       </c>
       <c r="Z4" t="n">
-        <v>87.79080517341427</v>
+        <v>87.79080517341943</v>
       </c>
       <c r="AA4" t="n">
-        <v>77.82911854454497</v>
+        <v>77.82911854454588</v>
       </c>
       <c r="AB4" t="n">
-        <v>399.2166060250463</v>
+        <v>399.216606025048</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.99802704953748</v>
+        <v>31.99802704953751</v>
       </c>
       <c r="C5" t="n">
-        <v>41.37609734831391</v>
+        <v>41.37609734831389</v>
       </c>
       <c r="D5" t="n">
-        <v>44.24860255060747</v>
+        <v>44.24860255060745</v>
       </c>
       <c r="E5" t="n">
-        <v>35.42165834479491</v>
+        <v>35.42165834479514</v>
       </c>
       <c r="F5" t="n">
         <v>33.49716742109609</v>
       </c>
       <c r="G5" t="n">
-        <v>55.99983326137469</v>
+        <v>55.9998332613746</v>
       </c>
       <c r="H5" t="n">
-        <v>41.53430159794949</v>
+        <v>41.53430159794944</v>
       </c>
       <c r="I5" t="n">
-        <v>42.39988110864108</v>
+        <v>42.39988110864098</v>
       </c>
       <c r="J5" t="n">
-        <v>48.38518540641836</v>
+        <v>48.38518540641829</v>
       </c>
       <c r="K5" t="n">
-        <v>43.46668221848049</v>
+        <v>43.46668221848047</v>
       </c>
       <c r="L5" t="n">
-        <v>42.67536003077821</v>
+        <v>42.67536003077939</v>
       </c>
       <c r="M5" t="n">
-        <v>58.14453044280381</v>
+        <v>58.1445304428037</v>
       </c>
       <c r="N5" t="n">
-        <v>63.85448785955532</v>
+        <v>33.7543212088624</v>
       </c>
       <c r="O5" t="n">
-        <v>37.96650555323336</v>
+        <v>37.96650555323327</v>
       </c>
       <c r="P5" t="n">
-        <v>40.04374922668478</v>
+        <v>40.04374922668484</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.38443707191309</v>
+        <v>28.38443707191317</v>
       </c>
       <c r="R5" t="n">
-        <v>41.76326845820132</v>
+        <v>41.7632684582013</v>
       </c>
       <c r="S5" t="n">
-        <v>45.23541493157855</v>
+        <v>45.23541493157859</v>
       </c>
       <c r="T5" t="n">
-        <v>42.41208473075497</v>
+        <v>42.41208473075505</v>
       </c>
       <c r="U5" t="n">
-        <v>40.43405758473561</v>
+        <v>40.43405758473563</v>
       </c>
       <c r="V5" t="n">
-        <v>39.38392253869351</v>
+        <v>39.38392253869348</v>
       </c>
       <c r="W5" t="n">
-        <v>44.97816345435093</v>
+        <v>44.97816345435091</v>
       </c>
       <c r="X5" t="n">
-        <v>30.96850516520422</v>
+        <v>30.96850516520431</v>
       </c>
       <c r="Y5" t="n">
-        <v>57.03004954736257</v>
+        <v>57.03004954736252</v>
       </c>
       <c r="Z5" t="n">
-        <v>32.38806206153524</v>
+        <v>32.38806206153533</v>
       </c>
       <c r="AA5" t="n">
-        <v>43.73603125472996</v>
+        <v>43.73603125472995</v>
       </c>
       <c r="AB5" t="n">
-        <v>71.21410812810458</v>
+        <v>71.21410812810448</v>
       </c>
     </row>
     <row r="6">
@@ -2130,82 +2130,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.89847684809521</v>
+        <v>30.89847684809556</v>
       </c>
       <c r="C6" t="n">
-        <v>33.26697337396177</v>
+        <v>33.26697337396173</v>
       </c>
       <c r="D6" t="n">
-        <v>36.13947857625529</v>
+        <v>36.13947857625527</v>
       </c>
       <c r="E6" t="n">
-        <v>32.51223265843097</v>
+        <v>32.51223265843119</v>
       </c>
       <c r="F6" t="n">
-        <v>24.19918804145336</v>
+        <v>24.19918804145332</v>
       </c>
       <c r="G6" t="n">
-        <v>45.4286711461268</v>
+        <v>45.42867114612683</v>
       </c>
       <c r="H6" t="n">
-        <v>33.4251776235973</v>
+        <v>33.42517762359725</v>
       </c>
       <c r="I6" t="n">
-        <v>34.29075713428889</v>
+        <v>34.29075713428878</v>
       </c>
       <c r="J6" t="n">
-        <v>40.27606143206619</v>
+        <v>40.27606143206611</v>
       </c>
       <c r="K6" t="n">
-        <v>35.35755824412834</v>
+        <v>35.35755824412841</v>
       </c>
       <c r="L6" t="n">
-        <v>34.56623605642604</v>
+        <v>34.56623605642589</v>
       </c>
       <c r="M6" t="n">
-        <v>50.03540646845077</v>
+        <v>50.03540646845079</v>
       </c>
       <c r="N6" t="n">
-        <v>63.85448785955532</v>
+        <v>34.84910723600129</v>
       </c>
       <c r="O6" t="n">
-        <v>38.14385805903983</v>
+        <v>38.14385805903972</v>
       </c>
       <c r="P6" t="n">
-        <v>41.19165444883521</v>
+        <v>41.19165444883515</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.48216584473141</v>
+        <v>34.48216584473135</v>
       </c>
       <c r="R6" t="n">
-        <v>33.65414448384914</v>
+        <v>33.65414448384917</v>
       </c>
       <c r="S6" t="n">
-        <v>37.12629095722641</v>
+        <v>37.12629095722635</v>
       </c>
       <c r="T6" t="n">
-        <v>34.30296075640291</v>
+        <v>34.30296075640298</v>
       </c>
       <c r="U6" t="n">
-        <v>38.12294760436247</v>
+        <v>38.12294760436242</v>
       </c>
       <c r="V6" t="n">
-        <v>40.1358179653722</v>
+        <v>40.13581796537215</v>
       </c>
       <c r="W6" t="n">
-        <v>36.86670600614625</v>
+        <v>36.86670600614622</v>
       </c>
       <c r="X6" t="n">
-        <v>35.97800963855677</v>
+        <v>35.97800963855725</v>
       </c>
       <c r="Y6" t="n">
         <v>37.12011475691723</v>
       </c>
       <c r="Z6" t="n">
-        <v>33.44045820777364</v>
+        <v>33.44045820777367</v>
       </c>
       <c r="AA6" t="n">
-        <v>35.62690728037778</v>
+        <v>35.62690728037782</v>
       </c>
       <c r="AB6" t="n">
         <v>50.70217296585432</v>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.33609507099732</v>
+        <v>21.33609507099738</v>
       </c>
       <c r="C2" t="n">
-        <v>15.55223279818343</v>
+        <v>15.55223279818347</v>
       </c>
       <c r="D2" t="n">
-        <v>21.42175058188119</v>
+        <v>21.42175058188124</v>
       </c>
       <c r="E2" t="n">
-        <v>21.14101675082067</v>
+        <v>21.14101675082072</v>
       </c>
       <c r="F2" t="n">
-        <v>21.39682412409624</v>
+        <v>21.39682412409628</v>
       </c>
       <c r="G2" t="n">
-        <v>22.12621821145225</v>
+        <v>22.12621821145233</v>
       </c>
       <c r="H2" t="n">
-        <v>21.13345837525366</v>
+        <v>21.13345837525374</v>
       </c>
       <c r="I2" t="n">
-        <v>21.31021303450628</v>
+        <v>21.3102130345063</v>
       </c>
       <c r="J2" t="n">
         <v>21.70744169158723</v>
       </c>
       <c r="K2" t="n">
-        <v>21.33340980969792</v>
+        <v>21.33340980969801</v>
       </c>
       <c r="L2" t="n">
-        <v>21.21454925439265</v>
+        <v>21.2145492543927</v>
       </c>
       <c r="M2" t="n">
-        <v>22.28641842928138</v>
+        <v>22.28641842928136</v>
       </c>
       <c r="N2" t="n">
-        <v>21.21884014275859</v>
+        <v>21.21884014275862</v>
       </c>
       <c r="O2" t="n">
-        <v>28.56038098358269</v>
+        <v>28.56038098358271</v>
       </c>
       <c r="P2" t="n">
-        <v>21.63667665207277</v>
+        <v>21.63667665207282</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.24788701599094</v>
+        <v>21.247887015991</v>
       </c>
       <c r="R2" t="n">
-        <v>21.13964843235926</v>
+        <v>21.13964843235928</v>
       </c>
       <c r="S2" t="n">
-        <v>21.43239223172097</v>
+        <v>21.43239223172102</v>
       </c>
       <c r="T2" t="n">
-        <v>21.21038909680097</v>
+        <v>21.21038909680099</v>
       </c>
       <c r="U2" t="n">
-        <v>24.6449424605214</v>
+        <v>24.64494246052144</v>
       </c>
       <c r="V2" t="n">
-        <v>21.29778444850794</v>
+        <v>21.29778444850798</v>
       </c>
       <c r="W2" t="n">
-        <v>26.89048172873894</v>
+        <v>26.89048172873903</v>
       </c>
       <c r="X2" t="n">
-        <v>21.41797695775219</v>
+        <v>21.41797695775227</v>
       </c>
       <c r="Y2" t="n">
         <v>21.72067012070703</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.68810117945243</v>
+        <v>27.68810117945247</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.26733066110875</v>
+        <v>21.2673306611088</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.56380468586736</v>
+        <v>22.56380468586737</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.35834159938061</v>
+        <v>22.97560952763384</v>
       </c>
       <c r="C3" t="n">
-        <v>16.72856624228087</v>
+        <v>15.72615866897508</v>
       </c>
       <c r="D3" t="n">
-        <v>29.44652810234673</v>
+        <v>23.76706635704</v>
       </c>
       <c r="E3" t="n">
-        <v>17.69733810236421</v>
+        <v>16.34861615094141</v>
       </c>
       <c r="F3" t="n">
-        <v>28.89515116845068</v>
+        <v>23.57162609492394</v>
       </c>
       <c r="G3" t="n">
-        <v>45.56185050280291</v>
+        <v>29.12627586408509</v>
       </c>
       <c r="H3" t="n">
-        <v>22.72801702425582</v>
+        <v>21.43745594460213</v>
       </c>
       <c r="I3" t="n">
-        <v>26.85288763365326</v>
+        <v>22.87237406022711</v>
       </c>
       <c r="J3" t="n">
-        <v>35.99016789802126</v>
+        <v>25.9460573067763</v>
       </c>
       <c r="K3" t="n">
-        <v>27.37129864196269</v>
+        <v>23.00208384221284</v>
       </c>
       <c r="L3" t="n">
-        <v>24.57973798102431</v>
+        <v>22.04972222634861</v>
       </c>
       <c r="M3" t="n">
-        <v>52.63706301904227</v>
+        <v>31.8096681140074</v>
       </c>
       <c r="N3" t="n">
-        <v>24.69574201198257</v>
+        <v>22.10157722216281</v>
       </c>
       <c r="O3" t="n">
-        <v>35.42652073749271</v>
+        <v>30.43690937087486</v>
       </c>
       <c r="P3" t="n">
-        <v>34.25832788129705</v>
+        <v>25.30656942248542</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.37672577915011</v>
+        <v>22.33367099479674</v>
       </c>
       <c r="R3" t="n">
-        <v>22.86796715542034</v>
+        <v>21.479541695793</v>
       </c>
       <c r="S3" t="n">
-        <v>29.59732118736929</v>
+        <v>23.73581070202393</v>
       </c>
       <c r="T3" t="n">
-        <v>24.51463856817712</v>
+        <v>22.05057070571133</v>
       </c>
       <c r="U3" t="n">
-        <v>30.04245470608662</v>
+        <v>26.10967123437838</v>
       </c>
       <c r="V3" t="n">
-        <v>26.48297402428491</v>
+        <v>22.67371416897405</v>
       </c>
       <c r="W3" t="n">
-        <v>34.19026496500594</v>
+        <v>28.97255277899711</v>
       </c>
       <c r="X3" t="n">
-        <v>29.35030689847691</v>
+        <v>23.72130911698338</v>
       </c>
       <c r="Y3" t="n">
-        <v>36.34225195441184</v>
+        <v>26.10244919171468</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.96459244488155</v>
+        <v>29.68453983005663</v>
       </c>
       <c r="AA3" t="n">
-        <v>25.81277289117914</v>
+        <v>22.48119935997435</v>
       </c>
       <c r="AB3" t="n">
-        <v>55.90260104798936</v>
+        <v>33.25660531101775</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.52743831288456</v>
+        <v>71.52743831288504</v>
       </c>
       <c r="C4" t="n">
-        <v>32.73255227166922</v>
+        <v>32.73255227166931</v>
       </c>
       <c r="D4" t="n">
-        <v>95.74729557622446</v>
+        <v>95.74729557622464</v>
       </c>
       <c r="E4" t="n">
-        <v>28.14979335285619</v>
+        <v>28.14979335285621</v>
       </c>
       <c r="F4" t="n">
-        <v>90.98893198737106</v>
+        <v>90.98893198737119</v>
       </c>
       <c r="G4" t="n">
-        <v>218.2163692558402</v>
+        <v>218.2163692558406</v>
       </c>
       <c r="H4" t="n">
-        <v>36.52329597917411</v>
+        <v>36.52329597917414</v>
       </c>
       <c r="I4" t="n">
-        <v>73.27581654550868</v>
+        <v>73.27581654550889</v>
       </c>
       <c r="J4" t="n">
-        <v>145.7514119764386</v>
+        <v>145.7514119764388</v>
       </c>
       <c r="K4" t="n">
-        <v>74.14169353460848</v>
+        <v>74.14169353460855</v>
       </c>
       <c r="L4" t="n">
-        <v>50.31033004962346</v>
+        <v>50.31033004962359</v>
       </c>
       <c r="M4" t="n">
-        <v>309.0750229888307</v>
+        <v>309.0750229888303</v>
       </c>
       <c r="N4" t="n">
-        <v>52.33776005304266</v>
+        <v>52.33776005304275</v>
       </c>
       <c r="O4" t="n">
-        <v>76.97564100837609</v>
+        <v>76.97564100837627</v>
       </c>
       <c r="P4" t="n">
-        <v>126.7635865956607</v>
+        <v>126.7635865956609</v>
       </c>
       <c r="Q4" t="n">
-        <v>58.11972415555004</v>
+        <v>58.11972415555</v>
       </c>
       <c r="R4" t="n">
-        <v>37.26098116667404</v>
+        <v>37.26098116667408</v>
       </c>
       <c r="S4" t="n">
-        <v>90.0948748300199</v>
+        <v>90.09487483002036</v>
       </c>
       <c r="T4" t="n">
-        <v>51.75484689745171</v>
+        <v>51.75484689745187</v>
       </c>
       <c r="U4" t="n">
-        <v>67.75570303477555</v>
+        <v>67.75570303477568</v>
       </c>
       <c r="V4" t="n">
         <v>63.95107790098575</v>
       </c>
       <c r="W4" t="n">
-        <v>86.24815289759115</v>
+        <v>86.24815289759076</v>
       </c>
       <c r="X4" t="n">
-        <v>93.94491443004898</v>
+        <v>93.94491443004912</v>
       </c>
       <c r="Y4" t="n">
-        <v>151.8053676215573</v>
+        <v>151.8053676215574</v>
       </c>
       <c r="Z4" t="n">
         <v>80.1271515491847</v>
       </c>
       <c r="AA4" t="n">
-        <v>61.48690410415676</v>
+        <v>61.48690410415695</v>
       </c>
       <c r="AB4" t="n">
-        <v>351.0560267289546</v>
+        <v>351.0560267289549</v>
       </c>
     </row>
     <row r="5">
@@ -2638,82 +2638,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.57085374690749</v>
+        <v>30.57085374690757</v>
       </c>
       <c r="C5" t="n">
-        <v>39.05628883503577</v>
+        <v>39.05628883503586</v>
       </c>
       <c r="D5" t="n">
-        <v>42.51878015243086</v>
+        <v>42.51878015243113</v>
       </c>
       <c r="E5" t="n">
-        <v>33.50101902477375</v>
+        <v>33.50101902477384</v>
       </c>
       <c r="F5" t="n">
-        <v>32.96743557517689</v>
+        <v>32.96743557517703</v>
       </c>
       <c r="G5" t="n">
-        <v>52.75292523048869</v>
+        <v>52.75292523048873</v>
       </c>
       <c r="H5" t="n">
-        <v>39.26238705760643</v>
+        <v>39.26238705760641</v>
       </c>
       <c r="I5" t="n">
-        <v>41.25891224502438</v>
+        <v>41.25891224502452</v>
       </c>
       <c r="J5" t="n">
-        <v>45.71417230665203</v>
+        <v>45.71417230665211</v>
       </c>
       <c r="K5" t="n">
-        <v>41.52093049185846</v>
+        <v>41.52093049185852</v>
       </c>
       <c r="L5" t="n">
-        <v>40.17834584112823</v>
+        <v>40.17834584112827</v>
       </c>
       <c r="M5" t="n">
-        <v>53.75339060549825</v>
+        <v>53.75339060549842</v>
       </c>
       <c r="N5" t="n">
-        <v>52.33776005304264</v>
+        <v>31.71516021194314</v>
       </c>
       <c r="O5" t="n">
-        <v>35.81629182046137</v>
+        <v>35.81629182046147</v>
       </c>
       <c r="P5" t="n">
-        <v>38.20052790352663</v>
+        <v>38.20052790352678</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.41660239883743</v>
+        <v>27.41660239883744</v>
       </c>
       <c r="R5" t="n">
-        <v>39.33230660018031</v>
+        <v>39.33230660018042</v>
       </c>
       <c r="S5" t="n">
-        <v>42.63898248277231</v>
+        <v>42.63898248277238</v>
       </c>
       <c r="T5" t="n">
-        <v>40.13135494736296</v>
+        <v>40.131354947363</v>
       </c>
       <c r="U5" t="n">
-        <v>35.85515895472301</v>
+        <v>35.85515895472302</v>
       </c>
       <c r="V5" t="n">
         <v>37.91197413340576</v>
       </c>
       <c r="W5" t="n">
-        <v>42.18019306936228</v>
+        <v>42.18019306936226</v>
       </c>
       <c r="X5" t="n">
-        <v>30.34422274890862</v>
+        <v>30.3442227489086</v>
       </c>
       <c r="Y5" t="n">
-        <v>56.80812978848854</v>
+        <v>56.80812978848877</v>
       </c>
       <c r="Z5" t="n">
-        <v>31.00868433489636</v>
+        <v>31.00868433489651</v>
       </c>
       <c r="AA5" t="n">
-        <v>40.7745361106333</v>
+        <v>40.77453611063336</v>
       </c>
       <c r="AB5" t="n">
         <v>66.76420438076092</v>
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.59555782567091</v>
+        <v>28.59555782567096</v>
       </c>
       <c r="C6" t="n">
-        <v>30.33356893450367</v>
+        <v>30.33356893450381</v>
       </c>
       <c r="D6" t="n">
-        <v>33.79606025189901</v>
+        <v>33.79606025189911</v>
       </c>
       <c r="E6" t="n">
-        <v>29.6480866562945</v>
+        <v>29.64808665629445</v>
       </c>
       <c r="F6" t="n">
-        <v>23.75632161939514</v>
+        <v>23.75632161939517</v>
       </c>
       <c r="G6" t="n">
-        <v>41.75334570194531</v>
+        <v>41.75334570194538</v>
       </c>
       <c r="H6" t="n">
-        <v>30.53966715707436</v>
+        <v>30.5396671570744</v>
       </c>
       <c r="I6" t="n">
-        <v>32.53619234449241</v>
+        <v>32.53619234449247</v>
       </c>
       <c r="J6" t="n">
-        <v>36.99145240611989</v>
+        <v>36.99145240612007</v>
       </c>
       <c r="K6" t="n">
-        <v>32.79821059132649</v>
+        <v>32.79821059132647</v>
       </c>
       <c r="L6" t="n">
-        <v>31.45562594059613</v>
+        <v>31.45562594059623</v>
       </c>
       <c r="M6" t="n">
-        <v>45.03067070496481</v>
+        <v>45.03067070496485</v>
       </c>
       <c r="N6" t="n">
-        <v>52.33776005304266</v>
+        <v>31.50409349859543</v>
       </c>
       <c r="O6" t="n">
-        <v>34.66895360767812</v>
+        <v>34.66895360767815</v>
       </c>
       <c r="P6" t="n">
-        <v>37.93163985057673</v>
+        <v>37.93163985057685</v>
       </c>
       <c r="Q6" t="n">
-        <v>31.83219079689735</v>
+        <v>31.83219079689744</v>
       </c>
       <c r="R6" t="n">
-        <v>30.60958669964808</v>
+        <v>30.60958669964838</v>
       </c>
       <c r="S6" t="n">
-        <v>33.91626258224051</v>
+        <v>33.91626258224032</v>
       </c>
       <c r="T6" t="n">
-        <v>31.40863504683096</v>
+        <v>31.40863504683097</v>
       </c>
       <c r="U6" t="n">
-        <v>32.49455004955003</v>
+        <v>32.49455004955033</v>
       </c>
       <c r="V6" t="n">
-        <v>37.07813399678418</v>
+        <v>37.07813399678439</v>
       </c>
       <c r="W6" t="n">
-        <v>33.45531520332851</v>
+        <v>33.4553152033285</v>
       </c>
       <c r="X6" t="n">
-        <v>33.7534354314096</v>
+        <v>33.75343543140954</v>
       </c>
       <c r="Y6" t="n">
-        <v>37.17249395271796</v>
+        <v>37.17249395271804</v>
       </c>
       <c r="Z6" t="n">
-        <v>30.91822600287578</v>
+        <v>30.91822600287584</v>
       </c>
       <c r="AA6" t="n">
-        <v>32.0518162101013</v>
+        <v>32.05181621010131</v>
       </c>
       <c r="AB6" t="n">
-        <v>46.57153014988559</v>
+        <v>46.57153014988592</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.2382951099702</v>
+        <v>21.23829510997017</v>
       </c>
       <c r="C2" t="n">
-        <v>15.47808159778801</v>
+        <v>15.478081597788</v>
       </c>
       <c r="D2" t="n">
-        <v>21.25313015755231</v>
+        <v>21.25313015755228</v>
       </c>
       <c r="E2" t="n">
-        <v>21.02502466050258</v>
+        <v>21.02502466050254</v>
       </c>
       <c r="F2" t="n">
-        <v>21.359327242608</v>
+        <v>21.35932724260795</v>
       </c>
       <c r="G2" t="n">
-        <v>21.90269744997049</v>
+        <v>21.90269744997047</v>
       </c>
       <c r="H2" t="n">
-        <v>21.05376993795934</v>
+        <v>21.05376993795932</v>
       </c>
       <c r="I2" t="n">
-        <v>21.25149617590349</v>
+        <v>21.25149617590345</v>
       </c>
       <c r="J2" t="n">
-        <v>21.54944000266876</v>
+        <v>21.54944000266873</v>
       </c>
       <c r="K2" t="n">
-        <v>21.26817692425585</v>
+        <v>21.26817692425583</v>
       </c>
       <c r="L2" t="n">
-        <v>21.12787856039614</v>
+        <v>21.12787856039611</v>
       </c>
       <c r="M2" t="n">
-        <v>21.98772064489632</v>
+        <v>21.98772064489631</v>
       </c>
       <c r="N2" t="n">
-        <v>21.10383974669219</v>
+        <v>21.10383974669214</v>
       </c>
       <c r="O2" t="n">
-        <v>28.30224690253777</v>
+        <v>28.30224690253774</v>
       </c>
       <c r="P2" t="n">
-        <v>21.49518165177025</v>
+        <v>21.49518165177022</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.13965394921095</v>
+        <v>21.13965394921092</v>
       </c>
       <c r="R2" t="n">
-        <v>21.1405646859436</v>
+        <v>21.14056468594357</v>
       </c>
       <c r="S2" t="n">
-        <v>21.32555071233411</v>
+        <v>21.32555071233409</v>
       </c>
       <c r="T2" t="n">
-        <v>21.1497448916943</v>
+        <v>21.14974489169428</v>
       </c>
       <c r="U2" t="n">
-        <v>24.48485797527078</v>
+        <v>24.48485797527074</v>
       </c>
       <c r="V2" t="n">
-        <v>21.29130253094258</v>
+        <v>21.29130253094257</v>
       </c>
       <c r="W2" t="n">
-        <v>26.78390378063456</v>
+        <v>26.78390378063453</v>
       </c>
       <c r="X2" t="n">
-        <v>21.3489611409298</v>
+        <v>21.34896114092977</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.93352070877838</v>
+        <v>21.93352070877835</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.54459291073915</v>
+        <v>27.54459291073908</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.19761790545708</v>
+        <v>21.19761790545706</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.33666321198845</v>
+        <v>22.33666321198843</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.13240780799728</v>
+        <v>22.85239349642213</v>
       </c>
       <c r="C3" t="n">
-        <v>17.04947805810849</v>
+        <v>15.8023829975829</v>
       </c>
       <c r="D3" t="n">
-        <v>27.56444350299688</v>
+        <v>23.06073868447785</v>
       </c>
       <c r="E3" t="n">
-        <v>17.0537989935375</v>
+        <v>16.10804346351736</v>
       </c>
       <c r="F3" t="n">
-        <v>30.0797379902281</v>
+        <v>23.94071735697687</v>
       </c>
       <c r="G3" t="n">
-        <v>42.43200407303853</v>
+        <v>27.96478174033834</v>
       </c>
       <c r="H3" t="n">
-        <v>22.92575684198831</v>
+        <v>21.47376229332998</v>
       </c>
       <c r="I3" t="n">
-        <v>27.53894971535195</v>
+        <v>23.07166146924427</v>
       </c>
       <c r="J3" t="n">
-        <v>34.37728370298594</v>
+        <v>25.32757981566959</v>
       </c>
       <c r="K3" t="n">
-        <v>27.90311623846776</v>
+        <v>23.14490765228086</v>
       </c>
       <c r="L3" t="n">
-        <v>24.61222518327801</v>
+        <v>22.02648210229212</v>
       </c>
       <c r="M3" t="n">
-        <v>47.7243008338548</v>
+        <v>29.92805490284038</v>
       </c>
       <c r="N3" t="n">
-        <v>24.0698138860704</v>
+        <v>21.85147062170815</v>
       </c>
       <c r="O3" t="n">
-        <v>33.48361891451622</v>
+        <v>29.69590809742503</v>
       </c>
       <c r="P3" t="n">
-        <v>33.02493577059244</v>
+        <v>24.81953109198625</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.90690262007684</v>
+        <v>22.132177192407</v>
       </c>
       <c r="R3" t="n">
-        <v>24.95360217050519</v>
+        <v>22.18046611856409</v>
       </c>
       <c r="S3" t="n">
-        <v>29.16273565459119</v>
+        <v>23.54542355652281</v>
       </c>
       <c r="T3" t="n">
-        <v>25.15597286552567</v>
+        <v>22.24166226542915</v>
       </c>
       <c r="U3" t="n">
-        <v>28.58157354793763</v>
+        <v>25.56799851289754</v>
       </c>
       <c r="V3" t="n">
-        <v>28.36187536695747</v>
+        <v>23.25842614504882</v>
       </c>
       <c r="W3" t="n">
-        <v>34.03111119903118</v>
+        <v>28.87708946856099</v>
       </c>
       <c r="X3" t="n">
-        <v>29.79177640439287</v>
+        <v>23.81576347986672</v>
       </c>
       <c r="Y3" t="n">
-        <v>43.33629895160128</v>
+        <v>28.52120925185949</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.02484183610511</v>
+        <v>29.30084913418109</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.23932461840978</v>
+        <v>22.59630191040002</v>
       </c>
       <c r="AB3" t="n">
-        <v>52.67058242231676</v>
+        <v>32.01524077597279</v>
       </c>
     </row>
     <row r="4">
@@ -3146,85 +3146,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.24145398805081</v>
+        <v>69.24145398805251</v>
       </c>
       <c r="C4" t="n">
-        <v>35.92278751806084</v>
+        <v>35.9227875180645</v>
       </c>
       <c r="D4" t="n">
-        <v>78.18352262068694</v>
+        <v>78.18352262069004</v>
       </c>
       <c r="E4" t="n">
-        <v>24.08081665046561</v>
+        <v>24.08081665046787</v>
       </c>
       <c r="F4" t="n">
-        <v>101.4247046835405</v>
+        <v>101.424704683543</v>
       </c>
       <c r="G4" t="n">
-        <v>188.54009188021</v>
+        <v>188.5400918802075</v>
       </c>
       <c r="H4" t="n">
-        <v>38.85264388979604</v>
+        <v>38.85264388979209</v>
       </c>
       <c r="I4" t="n">
-        <v>79.4722157591932</v>
+        <v>79.47221575919824</v>
       </c>
       <c r="J4" t="n">
         <v>130.4760077109174</v>
       </c>
       <c r="K4" t="n">
-        <v>78.74365130755405</v>
+        <v>78.74365130755578</v>
       </c>
       <c r="L4" t="n">
-        <v>50.99631904871657</v>
+        <v>50.99631904871284</v>
       </c>
       <c r="M4" t="n">
-        <v>255.9311095597509</v>
+        <v>255.9311095597562</v>
       </c>
       <c r="N4" t="n">
-        <v>47.3414220034178</v>
+        <v>47.34142200342086</v>
       </c>
       <c r="O4" t="n">
-        <v>63.11843707478415</v>
+        <v>63.11843707478268</v>
       </c>
       <c r="P4" t="n">
-        <v>114.7533296618059</v>
+        <v>114.7533296618089</v>
       </c>
       <c r="Q4" t="n">
-        <v>54.10238225171555</v>
+        <v>54.10238225171533</v>
       </c>
       <c r="R4" t="n">
-        <v>57.03878977850809</v>
+        <v>57.03878977850524</v>
       </c>
       <c r="S4" t="n">
-        <v>86.34967831589248</v>
+        <v>86.3496783158952</v>
       </c>
       <c r="T4" t="n">
-        <v>58.05770713823527</v>
+        <v>58.05770713824094</v>
       </c>
       <c r="U4" t="n">
-        <v>55.87092410770025</v>
+        <v>55.87092410769709</v>
       </c>
       <c r="V4" t="n">
-        <v>78.42533012353408</v>
+        <v>78.42533012353414</v>
       </c>
       <c r="W4" t="n">
-        <v>85.51585918656463</v>
+        <v>85.51585918656954</v>
       </c>
       <c r="X4" t="n">
-        <v>96.56037958550627</v>
+        <v>96.56037958550307</v>
       </c>
       <c r="Y4" t="n">
-        <v>215.5258175778993</v>
+        <v>215.5258175779015</v>
       </c>
       <c r="Z4" t="n">
-        <v>71.57596360137684</v>
+        <v>71.57596360138012</v>
       </c>
       <c r="AA4" t="n">
-        <v>65.74757254057245</v>
+        <v>65.74757254057687</v>
       </c>
       <c r="AB4" t="n">
-        <v>316.937890509856</v>
+        <v>316.9378905098602</v>
       </c>
     </row>
     <row r="5">
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.38908952257817</v>
+        <v>30.38908952258501</v>
       </c>
       <c r="C5" t="n">
-        <v>39.06032707199279</v>
+        <v>39.0603270719925</v>
       </c>
       <c r="D5" t="n">
-        <v>41.45775482603454</v>
+        <v>41.45775482603914</v>
       </c>
       <c r="E5" t="n">
-        <v>33.07668591692214</v>
+        <v>33.07668591692155</v>
       </c>
       <c r="F5" t="n">
-        <v>33.45446658739142</v>
+        <v>33.45446658739663</v>
       </c>
       <c r="G5" t="n">
-        <v>51.05532960715578</v>
+        <v>51.05532960715958</v>
       </c>
       <c r="H5" t="n">
-        <v>39.20588943550523</v>
+        <v>39.20588943550458</v>
       </c>
       <c r="I5" t="n">
-        <v>41.43929825164865</v>
+        <v>41.43929825164699</v>
       </c>
       <c r="J5" t="n">
-        <v>44.77425503757067</v>
+        <v>44.77425503757343</v>
       </c>
       <c r="K5" t="n">
-        <v>41.62771497781024</v>
+        <v>41.62771497781029</v>
       </c>
       <c r="L5" t="n">
-        <v>40.04298041757983</v>
+        <v>40.04298041757875</v>
       </c>
       <c r="M5" t="n">
-        <v>51.24160371703846</v>
+        <v>51.24160371703876</v>
       </c>
       <c r="N5" t="n">
-        <v>47.3414220034178</v>
+        <v>31.32127736701015</v>
       </c>
       <c r="O5" t="n">
-        <v>34.79917601994185</v>
+        <v>34.79917601993788</v>
       </c>
       <c r="P5" t="n">
-        <v>37.4946225926987</v>
+        <v>37.49462259269698</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.13257794390546</v>
+        <v>27.13257794390226</v>
       </c>
       <c r="R5" t="n">
-        <v>40.1862760415402</v>
+        <v>40.18627604154322</v>
       </c>
       <c r="S5" t="n">
-        <v>42.27577830740069</v>
+        <v>42.27577830740083</v>
       </c>
       <c r="T5" t="n">
-        <v>40.28997068859995</v>
+        <v>40.28997068860094</v>
       </c>
       <c r="U5" t="n">
-        <v>35.03460446819689</v>
+        <v>35.03460446820323</v>
       </c>
       <c r="V5" t="n">
         <v>38.71256141973849</v>
       </c>
       <c r="W5" t="n">
-        <v>41.95721890077229</v>
+        <v>41.95721890077154</v>
       </c>
       <c r="X5" t="n">
-        <v>30.49590612658911</v>
+        <v>30.49590612659201</v>
       </c>
       <c r="Y5" t="n">
-        <v>59.97809220135039</v>
+        <v>59.97809220135855</v>
       </c>
       <c r="Z5" t="n">
-        <v>30.48678272470223</v>
+        <v>30.48678272470205</v>
       </c>
       <c r="AA5" t="n">
-        <v>40.83071840172172</v>
+        <v>40.83071840172597</v>
       </c>
       <c r="AB5" t="n">
-        <v>64.97221334241112</v>
+        <v>64.97221334241299</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.56883123073051</v>
+        <v>27.56883123072695</v>
       </c>
       <c r="C6" t="n">
-        <v>29.30375683452123</v>
+        <v>29.30375683452159</v>
       </c>
       <c r="D6" t="n">
-        <v>31.70118458856827</v>
+        <v>31.70118458856823</v>
       </c>
       <c r="E6" t="n">
-        <v>28.20957167523735</v>
+        <v>28.20957167523903</v>
       </c>
       <c r="F6" t="n">
-        <v>23.76081920037727</v>
+        <v>23.76081920037481</v>
       </c>
       <c r="G6" t="n">
-        <v>39.03834563355737</v>
+        <v>39.03834563355664</v>
       </c>
       <c r="H6" t="n">
-        <v>29.44931919803233</v>
+        <v>29.4493191980337</v>
       </c>
       <c r="I6" t="n">
-        <v>31.68272801417447</v>
+        <v>31.68272801417614</v>
       </c>
       <c r="J6" t="n">
-        <v>35.01768480010173</v>
+        <v>35.01768480010254</v>
       </c>
       <c r="K6" t="n">
-        <v>31.87114474033473</v>
+        <v>31.8711447403394</v>
       </c>
       <c r="L6" t="n">
-        <v>30.28641018010299</v>
+        <v>30.28641018010789</v>
       </c>
       <c r="M6" t="n">
-        <v>41.48503347956301</v>
+        <v>41.48503347956562</v>
       </c>
       <c r="N6" t="n">
-        <v>47.3414220034178</v>
+        <v>30.01488072092091</v>
       </c>
       <c r="O6" t="n">
-        <v>32.48452229663395</v>
+        <v>32.48452229663208</v>
       </c>
       <c r="P6" t="n">
-        <v>36.03494756266</v>
+        <v>36.03494756265599</v>
       </c>
       <c r="Q6" t="n">
-        <v>30.41941827512298</v>
+        <v>30.41941827512495</v>
       </c>
       <c r="R6" t="n">
-        <v>30.42970580406865</v>
+        <v>30.42970580407233</v>
       </c>
       <c r="S6" t="n">
-        <v>32.51920806992121</v>
+        <v>32.51920806992992</v>
       </c>
       <c r="T6" t="n">
-        <v>30.53340045112707</v>
+        <v>30.53340045113006</v>
       </c>
       <c r="U6" t="n">
-        <v>30.60087633488884</v>
+        <v>30.60087633489094</v>
       </c>
       <c r="V6" t="n">
         <v>36.51308299253659</v>
       </c>
       <c r="W6" t="n">
-        <v>32.19850628473598</v>
+        <v>32.19850628473838</v>
       </c>
       <c r="X6" t="n">
-        <v>32.78363963024499</v>
+        <v>32.78363963024733</v>
       </c>
       <c r="Y6" t="n">
-        <v>39.38650885977896</v>
+        <v>39.3865088597839</v>
       </c>
       <c r="Z6" t="n">
-        <v>29.44338984151374</v>
+        <v>29.44338984151139</v>
       </c>
       <c r="AA6" t="n">
-        <v>31.07414816425278</v>
+        <v>31.07414816425509</v>
       </c>
       <c r="AB6" t="n">
-        <v>43.82853615340211</v>
+        <v>43.82853615339756</v>
       </c>
     </row>
   </sheetData>
@@ -3566,31 +3566,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.43487486043433</v>
+        <v>20.43487486043432</v>
       </c>
       <c r="C2" t="n">
-        <v>14.75248353895649</v>
+        <v>14.75248353895647</v>
       </c>
       <c r="D2" t="n">
         <v>20.36171535472033</v>
       </c>
       <c r="E2" t="n">
-        <v>20.34300431728506</v>
+        <v>20.34300431728505</v>
       </c>
       <c r="F2" t="n">
-        <v>20.35368168964199</v>
+        <v>20.35368168964201</v>
       </c>
       <c r="G2" t="n">
-        <v>20.60731615127639</v>
+        <v>20.60731615127638</v>
       </c>
       <c r="H2" t="n">
-        <v>20.43471381859564</v>
+        <v>20.43471381859562</v>
       </c>
       <c r="I2" t="n">
-        <v>20.37976936922891</v>
+        <v>20.37976936922892</v>
       </c>
       <c r="J2" t="n">
-        <v>20.51890859144794</v>
+        <v>20.51890859144793</v>
       </c>
       <c r="K2" t="n">
         <v>20.43799524567664</v>
@@ -3599,52 +3599,52 @@
         <v>20.4441138065211</v>
       </c>
       <c r="M2" t="n">
-        <v>20.66446998603642</v>
+        <v>20.6644699860364</v>
       </c>
       <c r="N2" t="n">
-        <v>20.41949145371044</v>
+        <v>20.41949145371042</v>
       </c>
       <c r="O2" t="n">
-        <v>27.25377677175637</v>
+        <v>27.25377677175635</v>
       </c>
       <c r="P2" t="n">
-        <v>20.51255971189087</v>
+        <v>20.51255971189086</v>
       </c>
       <c r="Q2" t="n">
         <v>20.43423887734559</v>
       </c>
       <c r="R2" t="n">
-        <v>20.36621270237734</v>
+        <v>20.36621270237733</v>
       </c>
       <c r="S2" t="n">
-        <v>20.45554251411864</v>
+        <v>20.45554251411862</v>
       </c>
       <c r="T2" t="n">
-        <v>20.36560996401568</v>
+        <v>20.36560996401565</v>
       </c>
       <c r="U2" t="n">
-        <v>23.69801528395833</v>
+        <v>23.69801528395834</v>
       </c>
       <c r="V2" t="n">
-        <v>20.38050285442899</v>
+        <v>20.38050285442897</v>
       </c>
       <c r="W2" t="n">
-        <v>25.9854181885182</v>
+        <v>25.98541818851817</v>
       </c>
       <c r="X2" t="n">
-        <v>20.45188879627557</v>
+        <v>20.45188879627554</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.41531026933829</v>
+        <v>20.4153102693383</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.70690121604715</v>
+        <v>26.70690121604714</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.41121888025282</v>
+        <v>20.41121888025281</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.69895736756451</v>
+        <v>20.69895736756449</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.19185195617437</v>
+        <v>21.48652770777196</v>
       </c>
       <c r="C3" t="n">
-        <v>15.70428912970463</v>
+        <v>14.96268639901478</v>
       </c>
       <c r="D3" t="n">
-        <v>22.53894492632485</v>
+        <v>20.95579117724213</v>
       </c>
       <c r="E3" t="n">
-        <v>16.9917516570936</v>
+        <v>15.75283582358187</v>
       </c>
       <c r="F3" t="n">
-        <v>22.3603036505149</v>
+        <v>20.89905152968327</v>
       </c>
       <c r="G3" t="n">
-        <v>28.16133967379142</v>
+        <v>22.79516006184298</v>
       </c>
       <c r="H3" t="n">
-        <v>24.26732719658759</v>
+        <v>21.57876751144688</v>
       </c>
       <c r="I3" t="n">
-        <v>22.96482482584479</v>
+        <v>21.10720860538045</v>
       </c>
       <c r="J3" t="n">
-        <v>26.15084820464272</v>
+        <v>22.14899571993423</v>
       </c>
       <c r="K3" t="n">
-        <v>24.31335685521258</v>
+        <v>21.5617154808942</v>
       </c>
       <c r="L3" t="n">
-        <v>24.42700150899808</v>
+        <v>21.57859037778982</v>
       </c>
       <c r="M3" t="n">
-        <v>32.65667614191553</v>
+        <v>24.29162575372451</v>
       </c>
       <c r="N3" t="n">
-        <v>23.87306516872423</v>
+        <v>21.40261892731752</v>
       </c>
       <c r="O3" t="n">
-        <v>30.60619794187808</v>
+        <v>28.18223953097599</v>
       </c>
       <c r="P3" t="n">
-        <v>25.97195250203948</v>
+        <v>22.09039532659412</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.22094391691195</v>
+        <v>21.52047922251416</v>
       </c>
       <c r="R3" t="n">
-        <v>22.65211588774023</v>
+        <v>21.00036859643179</v>
       </c>
       <c r="S3" t="n">
-        <v>24.67573427698906</v>
+        <v>21.62971694074219</v>
       </c>
       <c r="T3" t="n">
-        <v>22.6319429144724</v>
+        <v>20.99465569501384</v>
       </c>
       <c r="U3" t="n">
-        <v>27.72557801512458</v>
+        <v>24.85019913780761</v>
       </c>
       <c r="V3" t="n">
-        <v>22.94572128865277</v>
+        <v>21.0790369394796</v>
       </c>
       <c r="W3" t="n">
-        <v>33.22910001968987</v>
+        <v>28.1645031600235</v>
       </c>
       <c r="X3" t="n">
-        <v>24.63940007284189</v>
+        <v>21.6790453649692</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.77139593525009</v>
+        <v>21.3701860589358</v>
       </c>
       <c r="Z3" t="n">
-        <v>31.33071984552632</v>
+        <v>28.01591934933561</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.67401331400123</v>
+        <v>21.33508709104577</v>
       </c>
       <c r="AB3" t="n">
-        <v>30.41281700619789</v>
+        <v>23.73031047238522</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.06691958457612</v>
+        <v>53.06691958457607</v>
       </c>
       <c r="C4" t="n">
-        <v>29.61683716600237</v>
+        <v>29.61683716600239</v>
       </c>
       <c r="D4" t="n">
-        <v>41.3318775849506</v>
+        <v>41.33187758495063</v>
       </c>
       <c r="E4" t="n">
-        <v>27.68885575316492</v>
+        <v>27.68885575316487</v>
       </c>
       <c r="F4" t="n">
-        <v>40.15117064585945</v>
+        <v>40.15117064585942</v>
       </c>
       <c r="G4" t="n">
-        <v>84.82133109443711</v>
+        <v>84.82133109443694</v>
       </c>
       <c r="H4" t="n">
-        <v>59.74010831008364</v>
+        <v>59.74010831008355</v>
       </c>
       <c r="I4" t="n">
-        <v>45.69293025859197</v>
+        <v>45.69293025859201</v>
       </c>
       <c r="J4" t="n">
-        <v>70.28124439276746</v>
+        <v>70.28124439276735</v>
       </c>
       <c r="K4" t="n">
-        <v>57.32556107252718</v>
+        <v>57.32556107252717</v>
       </c>
       <c r="L4" t="n">
-        <v>56.33600948767949</v>
+        <v>56.33600948767942</v>
       </c>
       <c r="M4" t="n">
         <v>132.4139614244141</v>
       </c>
       <c r="N4" t="n">
-        <v>52.5764819641835</v>
+        <v>52.5764819641833</v>
       </c>
       <c r="O4" t="n">
-        <v>49.49276831880215</v>
+        <v>49.49276831880205</v>
       </c>
       <c r="P4" t="n">
-        <v>68.43335000716638</v>
+        <v>68.43335000716648</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.71291507383989</v>
+        <v>55.7129150738398</v>
       </c>
       <c r="R4" t="n">
-        <v>42.90801949020121</v>
+        <v>42.90801949020117</v>
       </c>
       <c r="S4" t="n">
-        <v>55.86103678524316</v>
+        <v>55.86103678524321</v>
       </c>
       <c r="T4" t="n">
         <v>42.72415068896645</v>
       </c>
       <c r="U4" t="n">
-        <v>56.99704112750872</v>
+        <v>56.99704112750891</v>
       </c>
       <c r="V4" t="n">
-        <v>43.23537666533302</v>
+        <v>43.23537666533206</v>
       </c>
       <c r="W4" t="n">
-        <v>89.03547148920055</v>
+        <v>89.03547148920066</v>
       </c>
       <c r="X4" t="n">
-        <v>60.74334693399251</v>
+        <v>60.74334693399258</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.76411264943019</v>
+        <v>51.76411264943009</v>
       </c>
       <c r="Z4" t="n">
-        <v>60.20615673422506</v>
+        <v>60.20615673422496</v>
       </c>
       <c r="AA4" t="n">
-        <v>50.71986461294607</v>
+        <v>50.71986461294595</v>
       </c>
       <c r="AB4" t="n">
-        <v>119.0425012176082</v>
+        <v>119.0425012176081</v>
       </c>
     </row>
     <row r="5">
@@ -3830,85 +3830,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.35207802555254</v>
+        <v>29.3520780255525</v>
       </c>
       <c r="C5" t="n">
-        <v>39.1753240776575</v>
+        <v>39.17532407765741</v>
       </c>
       <c r="D5" t="n">
-        <v>39.79485689901637</v>
+        <v>39.79485689901624</v>
       </c>
       <c r="E5" t="n">
-        <v>33.58301762260302</v>
+        <v>33.58301762260301</v>
       </c>
       <c r="F5" t="n">
         <v>30.19056554240185</v>
       </c>
       <c r="G5" t="n">
-        <v>44.90576236513872</v>
+        <v>44.90576236513856</v>
       </c>
       <c r="H5" t="n">
-        <v>40.61940812944039</v>
+        <v>40.61940812944021</v>
       </c>
       <c r="I5" t="n">
-        <v>39.99878529814769</v>
+        <v>39.99878529814754</v>
       </c>
       <c r="J5" t="n">
-        <v>41.54137633174214</v>
+        <v>41.54137633174211</v>
       </c>
       <c r="K5" t="n">
-        <v>40.65647335785133</v>
+        <v>40.65647335785135</v>
       </c>
       <c r="L5" t="n">
-        <v>40.72558531726661</v>
+        <v>40.72558531726651</v>
       </c>
       <c r="M5" t="n">
-        <v>44.74453400078105</v>
+        <v>44.7445340007809</v>
       </c>
       <c r="N5" t="n">
-        <v>52.5764819641835</v>
+        <v>31.71198864028571</v>
       </c>
       <c r="O5" t="n">
-        <v>34.08031185291769</v>
+        <v>34.08031185291761</v>
       </c>
       <c r="P5" t="n">
         <v>34.57538075315689</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.13024929088171</v>
+        <v>27.13024929088166</v>
       </c>
       <c r="R5" t="n">
-        <v>39.8456565096843</v>
+        <v>39.8456565096842</v>
       </c>
       <c r="S5" t="n">
-        <v>40.85467782704605</v>
+        <v>40.85467782704597</v>
       </c>
       <c r="T5" t="n">
-        <v>39.83884830261614</v>
+        <v>39.83884830261606</v>
       </c>
       <c r="U5" t="n">
-        <v>35.2478733713473</v>
+        <v>35.24787337134718</v>
       </c>
       <c r="V5" t="n">
-        <v>36.7402221331735</v>
+        <v>36.74022213317346</v>
       </c>
       <c r="W5" t="n">
-        <v>42.38350454107814</v>
+        <v>42.38350454107808</v>
       </c>
       <c r="X5" t="n">
-        <v>28.36245315644891</v>
+        <v>28.36245315644886</v>
       </c>
       <c r="Y5" t="n">
-        <v>51.60216104967012</v>
+        <v>51.60216104967007</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.58579450655021</v>
+        <v>29.58579450655016</v>
       </c>
       <c r="AA5" t="n">
-        <v>40.35402199265272</v>
+        <v>40.35402199265263</v>
       </c>
       <c r="AB5" t="n">
-        <v>55.37337400213414</v>
+        <v>55.37337400213401</v>
       </c>
     </row>
     <row r="6">
@@ -3918,25 +3918,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.60232478347201</v>
+        <v>26.60232478347199</v>
       </c>
       <c r="C6" t="n">
-        <v>29.30090026982866</v>
+        <v>29.30090026982867</v>
       </c>
       <c r="D6" t="n">
-        <v>29.9204330911875</v>
+        <v>29.92043309118752</v>
       </c>
       <c r="E6" t="n">
-        <v>28.75255491428518</v>
+        <v>28.7525549142852</v>
       </c>
       <c r="F6" t="n">
-        <v>20.27553429322807</v>
+        <v>20.27553429322805</v>
       </c>
       <c r="G6" t="n">
         <v>32.69460752476913</v>
       </c>
       <c r="H6" t="n">
-        <v>30.74498432161148</v>
+        <v>30.74498432161149</v>
       </c>
       <c r="I6" t="n">
         <v>30.1243614903188</v>
@@ -3945,43 +3945,43 @@
         <v>31.66695252391331</v>
       </c>
       <c r="K6" t="n">
-        <v>30.7820495500225</v>
+        <v>30.78204955002251</v>
       </c>
       <c r="L6" t="n">
-        <v>30.85116150943775</v>
+        <v>30.85116150943777</v>
       </c>
       <c r="M6" t="n">
-        <v>34.87011019295182</v>
+        <v>34.87011019295181</v>
       </c>
       <c r="N6" t="n">
-        <v>52.5764819641835</v>
+        <v>30.5730407075993</v>
       </c>
       <c r="O6" t="n">
-        <v>31.9142546801696</v>
+        <v>31.91425468016961</v>
       </c>
       <c r="P6" t="n">
         <v>33.29647210841743</v>
       </c>
       <c r="Q6" t="n">
-        <v>30.73962009624102</v>
+        <v>30.73962009624104</v>
       </c>
       <c r="R6" t="n">
-        <v>29.97123270185547</v>
+        <v>29.97123270185546</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9802540192172</v>
+        <v>30.98025401921721</v>
       </c>
       <c r="T6" t="n">
-        <v>29.9644244947873</v>
+        <v>29.96442449478731</v>
       </c>
       <c r="U6" t="n">
-        <v>30.87536876266071</v>
+        <v>30.8753687626607</v>
       </c>
       <c r="V6" t="n">
-        <v>34.73022733349812</v>
+        <v>34.73022733349815</v>
       </c>
       <c r="W6" t="n">
-        <v>32.50686602162997</v>
+        <v>32.50686602162999</v>
       </c>
       <c r="X6" t="n">
         <v>30.93898359538633</v>
@@ -3990,13 +3990,13 @@
         <v>30.52581230667622</v>
       </c>
       <c r="Z6" t="n">
-        <v>28.69109821359773</v>
+        <v>28.69109821359778</v>
       </c>
       <c r="AA6" t="n">
         <v>30.47959818482383</v>
       </c>
       <c r="AB6" t="n">
-        <v>33.72738160001365</v>
+        <v>33.72738160001364</v>
       </c>
     </row>
   </sheetData>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.19242828920761</v>
+        <v>20.19242828920756</v>
       </c>
       <c r="C2" t="n">
-        <v>14.53687980812047</v>
+        <v>14.53687980812044</v>
       </c>
       <c r="D2" t="n">
-        <v>20.08619038763585</v>
+        <v>20.08619038763582</v>
       </c>
       <c r="E2" t="n">
-        <v>20.07789543281518</v>
+        <v>20.07789543281515</v>
       </c>
       <c r="F2" t="n">
         <v>20.11561508506191</v>
       </c>
       <c r="G2" t="n">
-        <v>20.15698908474211</v>
+        <v>20.15698908474208</v>
       </c>
       <c r="H2" t="n">
-        <v>20.17433451081388</v>
+        <v>20.17433451081386</v>
       </c>
       <c r="I2" t="n">
-        <v>20.14922568238474</v>
+        <v>20.14922568238472</v>
       </c>
       <c r="J2" t="n">
-        <v>20.15813670084524</v>
+        <v>20.15813670084523</v>
       </c>
       <c r="K2" t="n">
-        <v>20.14626347511671</v>
+        <v>20.14626347511668</v>
       </c>
       <c r="L2" t="n">
-        <v>20.12399811447396</v>
+        <v>20.12399811447392</v>
       </c>
       <c r="M2" t="n">
-        <v>19.9766300534821</v>
+        <v>19.97663005348209</v>
       </c>
       <c r="N2" t="n">
-        <v>20.16383453184215</v>
+        <v>20.1638345318421</v>
       </c>
       <c r="O2" t="n">
-        <v>26.99023339447682</v>
+        <v>26.9902333944768</v>
       </c>
       <c r="P2" t="n">
         <v>20.1622268450271</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.16855171683518</v>
+        <v>20.16855171683515</v>
       </c>
       <c r="R2" t="n">
-        <v>20.13518347206596</v>
+        <v>20.13518347206593</v>
       </c>
       <c r="S2" t="n">
-        <v>20.15321168816737</v>
+        <v>20.15321168816732</v>
       </c>
       <c r="T2" t="n">
-        <v>20.09487044352165</v>
+        <v>20.09487044352162</v>
       </c>
       <c r="U2" t="n">
-        <v>23.32529336825328</v>
+        <v>23.32529336825323</v>
       </c>
       <c r="V2" t="n">
-        <v>20.16835008553083</v>
+        <v>20.16835008553079</v>
       </c>
       <c r="W2" t="n">
-        <v>25.56087528795709</v>
+        <v>25.56087528795704</v>
       </c>
       <c r="X2" t="n">
-        <v>20.36143045035248</v>
+        <v>20.36143045035244</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.23873129661511</v>
+        <v>20.23873129661509</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.36590098837534</v>
+        <v>26.36590098837529</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.17430264709004</v>
+        <v>20.17430264709001</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.10800260415375</v>
+        <v>20.10800260415373</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.74775963656285</v>
+        <v>21.21272566014108</v>
       </c>
       <c r="C3" t="n">
-        <v>15.86275769735512</v>
+        <v>14.89999039452142</v>
       </c>
       <c r="D3" t="n">
-        <v>21.32121817644263</v>
+        <v>20.42406607089493</v>
       </c>
       <c r="E3" t="n">
-        <v>16.04441563483803</v>
+        <v>15.31876950493675</v>
       </c>
       <c r="F3" t="n">
-        <v>22.01415679898123</v>
+        <v>20.65453266317322</v>
       </c>
       <c r="G3" t="n">
-        <v>22.93461993663676</v>
+        <v>20.94954042244082</v>
       </c>
       <c r="H3" t="n">
-        <v>23.39690741190296</v>
+        <v>21.1487857550457</v>
       </c>
       <c r="I3" t="n">
-        <v>22.79516975613506</v>
+        <v>20.92609013422718</v>
       </c>
       <c r="J3" t="n">
-        <v>22.97036682079594</v>
+        <v>20.96574216341116</v>
       </c>
       <c r="K3" t="n">
-        <v>22.71895972898165</v>
+        <v>20.89935802469216</v>
       </c>
       <c r="L3" t="n">
-        <v>22.18762976835606</v>
+        <v>20.72170003659455</v>
       </c>
       <c r="M3" t="n">
-        <v>21.88360054292958</v>
+        <v>20.5439719913873</v>
       </c>
       <c r="N3" t="n">
-        <v>23.11875333392578</v>
+        <v>21.01600069775793</v>
       </c>
       <c r="O3" t="n">
-        <v>31.19414318150557</v>
+        <v>28.20259825076113</v>
       </c>
       <c r="P3" t="n">
-        <v>23.04747461819094</v>
+        <v>20.97444545606482</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.2312643052185</v>
+        <v>21.04485245960105</v>
       </c>
       <c r="R3" t="n">
-        <v>22.47138606945889</v>
+        <v>20.8172088731294</v>
       </c>
       <c r="S3" t="n">
-        <v>22.85137567521219</v>
+        <v>20.90818280527684</v>
       </c>
       <c r="T3" t="n">
-        <v>21.52461371342767</v>
+        <v>20.49518094397783</v>
       </c>
       <c r="U3" t="n">
-        <v>25.8209029597392</v>
+        <v>24.04077399482342</v>
       </c>
       <c r="V3" t="n">
-        <v>23.19916279681857</v>
+        <v>21.03588856292963</v>
       </c>
       <c r="W3" t="n">
-        <v>30.46368980649339</v>
+        <v>27.01549213283397</v>
       </c>
       <c r="X3" t="n">
-        <v>27.73056834954743</v>
+        <v>22.58503156047711</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.85453535091755</v>
+        <v>21.6193786963868</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.58384648920815</v>
+        <v>27.27661023842126</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.35605095914907</v>
+        <v>21.10117927832104</v>
       </c>
       <c r="AB3" t="n">
-        <v>21.90770645355548</v>
+        <v>20.62734500018378</v>
       </c>
     </row>
     <row r="4">
@@ -4338,37 +4338,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.2478698020405</v>
+        <v>48.24786980204059</v>
       </c>
       <c r="C4" t="n">
-        <v>31.67812887189258</v>
+        <v>31.67812887189252</v>
       </c>
       <c r="D4" t="n">
-        <v>31.10435103837504</v>
+        <v>31.104351038375</v>
       </c>
       <c r="E4" t="n">
-        <v>19.88678324364253</v>
+        <v>19.88678324364252</v>
       </c>
       <c r="F4" t="n">
-        <v>36.64023227604475</v>
+        <v>36.64023227604471</v>
       </c>
       <c r="G4" t="n">
-        <v>42.52782575821782</v>
+        <v>42.52782575821784</v>
       </c>
       <c r="H4" t="n">
-        <v>50.02702713246444</v>
+        <v>50.02702713246445</v>
       </c>
       <c r="I4" t="n">
-        <v>43.54559062343954</v>
+        <v>43.54559062343942</v>
       </c>
       <c r="J4" t="n">
-        <v>43.19383850607134</v>
+        <v>43.1938385060713</v>
       </c>
       <c r="K4" t="n">
-        <v>42.75765086986289</v>
+        <v>42.75765086986286</v>
       </c>
       <c r="L4" t="n">
-        <v>38.35691962570931</v>
+        <v>38.35691962570928</v>
       </c>
       <c r="M4" t="n">
         <v>38.4926738206924</v>
@@ -4377,46 +4377,46 @@
         <v>44.6555126642189</v>
       </c>
       <c r="O4" t="n">
-        <v>53.13714454682489</v>
+        <v>53.13714454682484</v>
       </c>
       <c r="P4" t="n">
-        <v>42.43118558297967</v>
+        <v>42.43118558297964</v>
       </c>
       <c r="Q4" t="n">
-        <v>44.98929017352921</v>
+        <v>44.98929017352922</v>
       </c>
       <c r="R4" t="n">
-        <v>40.96828016728206</v>
+        <v>40.96828016728205</v>
       </c>
       <c r="S4" t="n">
-        <v>41.00641108566084</v>
+        <v>41.00641108566082</v>
       </c>
       <c r="T4" t="n">
-        <v>32.95212943583634</v>
+        <v>32.95212943583632</v>
       </c>
       <c r="U4" t="n">
-        <v>40.93693951893599</v>
+        <v>40.93693951893596</v>
       </c>
       <c r="V4" t="n">
-        <v>44.3128344073896</v>
+        <v>44.31283440738951</v>
       </c>
       <c r="W4" t="n">
-        <v>61.29915343106506</v>
+        <v>61.29915343106497</v>
       </c>
       <c r="X4" t="n">
-        <v>83.35075719035504</v>
+        <v>83.35075719035518</v>
       </c>
       <c r="Y4" t="n">
-        <v>59.93090919657975</v>
+        <v>59.93090919657959</v>
       </c>
       <c r="Z4" t="n">
-        <v>45.04147456857592</v>
+        <v>45.04147456857585</v>
       </c>
       <c r="AA4" t="n">
-        <v>46.856312023399</v>
+        <v>46.85631202339901</v>
       </c>
       <c r="AB4" t="n">
-        <v>36.47102135299253</v>
+        <v>36.47102135299254</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.63704984724184</v>
+        <v>27.63704984724177</v>
       </c>
       <c r="C5" t="n">
-        <v>36.79537275909959</v>
+        <v>36.79537275909949</v>
       </c>
       <c r="D5" t="n">
-        <v>36.7485597047163</v>
+        <v>36.74855970471618</v>
       </c>
       <c r="E5" t="n">
-        <v>31.16428636646746</v>
+        <v>31.16428636646736</v>
       </c>
       <c r="F5" t="n">
-        <v>28.37582302340671</v>
+        <v>28.37582302340662</v>
       </c>
       <c r="G5" t="n">
-        <v>39.68642353773454</v>
+        <v>39.68642353773436</v>
       </c>
       <c r="H5" t="n">
-        <v>37.74418812431229</v>
+        <v>37.74418812431212</v>
       </c>
       <c r="I5" t="n">
-        <v>37.46057235657313</v>
+        <v>37.46057235657302</v>
       </c>
       <c r="J5" t="n">
-        <v>37.53331086816334</v>
+        <v>37.53331086816321</v>
       </c>
       <c r="K5" t="n">
-        <v>37.42711286279831</v>
+        <v>37.42711286279814</v>
       </c>
       <c r="L5" t="n">
-        <v>37.17561537176648</v>
+        <v>37.17561537176636</v>
       </c>
       <c r="M5" t="n">
-        <v>37.08423662502906</v>
+        <v>37.08423662502893</v>
       </c>
       <c r="N5" t="n">
-        <v>44.6555126642189</v>
+        <v>29.63243618643936</v>
       </c>
       <c r="O5" t="n">
-        <v>32.48707447821009</v>
+        <v>32.48707447820999</v>
       </c>
       <c r="P5" t="n">
-        <v>31.27242705943388</v>
+        <v>31.27242705943382</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.34090476930315</v>
+        <v>25.34090476930307</v>
       </c>
       <c r="R5" t="n">
-        <v>37.30195913128679</v>
+        <v>37.30195913128663</v>
       </c>
       <c r="S5" t="n">
-        <v>37.50559612554135</v>
+        <v>37.50559612554125</v>
       </c>
       <c r="T5" t="n">
-        <v>36.84660492896942</v>
+        <v>36.84660492896928</v>
       </c>
       <c r="U5" t="n">
-        <v>32.36441827301591</v>
+        <v>32.36441827301581</v>
       </c>
       <c r="V5" t="n">
-        <v>34.68007746678702</v>
+        <v>34.68007746678692</v>
       </c>
       <c r="W5" t="n">
-        <v>38.62394324282893</v>
+        <v>38.6239432428288</v>
       </c>
       <c r="X5" t="n">
-        <v>28.46462970843581</v>
+        <v>28.46462970843573</v>
       </c>
       <c r="Y5" t="n">
-        <v>48.72277348486054</v>
+        <v>48.72277348486037</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.27138477403481</v>
+        <v>27.27138477403469</v>
       </c>
       <c r="AA5" t="n">
-        <v>37.74382820889335</v>
+        <v>37.74382820889323</v>
       </c>
       <c r="AB5" t="n">
-        <v>47.80503903811323</v>
+        <v>47.80503903811305</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.03400769467797</v>
+        <v>24.03400769467796</v>
       </c>
       <c r="C6" t="n">
-        <v>26.37249799636369</v>
+        <v>26.37249799636367</v>
       </c>
       <c r="D6" t="n">
-        <v>26.32568494198041</v>
+        <v>26.32568494198034</v>
       </c>
       <c r="E6" t="n">
-        <v>25.42612423528085</v>
+        <v>25.42612423528081</v>
       </c>
       <c r="F6" t="n">
-        <v>18.60876617541212</v>
+        <v>18.6087661754121</v>
       </c>
       <c r="G6" t="n">
-        <v>27.12538992341285</v>
+        <v>27.12538992341273</v>
       </c>
       <c r="H6" t="n">
-        <v>27.32131336157638</v>
+        <v>27.32131336157634</v>
       </c>
       <c r="I6" t="n">
-        <v>27.03769759383723</v>
+        <v>27.03769759383721</v>
       </c>
       <c r="J6" t="n">
-        <v>27.11043610542742</v>
+        <v>27.1104361054274</v>
       </c>
       <c r="K6" t="n">
-        <v>27.00423810006242</v>
+        <v>27.00423810006236</v>
       </c>
       <c r="L6" t="n">
-        <v>26.75274060903061</v>
+        <v>26.75274060903052</v>
       </c>
       <c r="M6" t="n">
-        <v>26.6613618622934</v>
+        <v>26.66136186229337</v>
       </c>
       <c r="N6" t="n">
-        <v>44.6555126642189</v>
+        <v>27.20271126886152</v>
       </c>
       <c r="O6" t="n">
-        <v>29.0179033282483</v>
+        <v>29.01790332824825</v>
       </c>
       <c r="P6" t="n">
-        <v>28.59335046986244</v>
+        <v>28.5933504698624</v>
       </c>
       <c r="Q6" t="n">
-        <v>27.25599517197749</v>
+        <v>27.25599517197747</v>
       </c>
       <c r="R6" t="n">
-        <v>26.87908436855088</v>
+        <v>26.87908436855083</v>
       </c>
       <c r="S6" t="n">
-        <v>27.08272136280548</v>
+        <v>27.08272136280543</v>
       </c>
       <c r="T6" t="n">
-        <v>26.42373016623349</v>
+        <v>26.42373016623348</v>
       </c>
       <c r="U6" t="n">
-        <v>26.97522336583474</v>
+        <v>26.97522336583472</v>
       </c>
       <c r="V6" t="n">
-        <v>31.10566957314457</v>
+        <v>31.10566957314452</v>
       </c>
       <c r="W6" t="n">
-        <v>28.19904197085744</v>
+        <v>28.19904197085742</v>
       </c>
       <c r="X6" t="n">
-        <v>29.43464806704906</v>
+        <v>29.43464806704905</v>
       </c>
       <c r="Y6" t="n">
-        <v>28.04870468118634</v>
+        <v>28.04870468118628</v>
       </c>
       <c r="Z6" t="n">
-        <v>25.24639350004204</v>
+        <v>25.246393500042</v>
       </c>
       <c r="AA6" t="n">
-        <v>27.32095344615745</v>
+        <v>27.32095344615743</v>
       </c>
       <c r="AB6" t="n">
-        <v>26.61092375768809</v>
+        <v>26.61092375768806</v>
       </c>
     </row>
   </sheetData>
@@ -4758,61 +4758,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.10150990799994</v>
+        <v>20.10150990799989</v>
       </c>
       <c r="C2" t="n">
-        <v>14.47177498398529</v>
+        <v>14.47177498398528</v>
       </c>
       <c r="D2" t="n">
-        <v>20.04941261149214</v>
+        <v>20.04941261149209</v>
       </c>
       <c r="E2" t="n">
-        <v>20.0336073326596</v>
+        <v>20.03360733265955</v>
       </c>
       <c r="F2" t="n">
-        <v>20.05714942683672</v>
+        <v>20.05714942683667</v>
       </c>
       <c r="G2" t="n">
-        <v>20.08398242903302</v>
+        <v>20.08398242903298</v>
       </c>
       <c r="H2" t="n">
-        <v>20.09984682276743</v>
+        <v>20.0998468227674</v>
       </c>
       <c r="I2" t="n">
-        <v>20.12760915550497</v>
+        <v>20.12760915550493</v>
       </c>
       <c r="J2" t="n">
-        <v>20.08844695743187</v>
+        <v>20.08844695743184</v>
       </c>
       <c r="K2" t="n">
-        <v>20.08448158991223</v>
+        <v>20.08448158991218</v>
       </c>
       <c r="L2" t="n">
-        <v>20.06271956768496</v>
+        <v>20.06271956768493</v>
       </c>
       <c r="M2" t="n">
-        <v>19.92862105901442</v>
+        <v>19.92862105901441</v>
       </c>
       <c r="N2" t="n">
-        <v>20.07417696042668</v>
+        <v>20.07417696042667</v>
       </c>
       <c r="O2" t="n">
-        <v>26.88439380623481</v>
+        <v>26.88439380623474</v>
       </c>
       <c r="P2" t="n">
         <v>20.11204414247359</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.07228778208144</v>
+        <v>20.07228778208137</v>
       </c>
       <c r="R2" t="n">
-        <v>20.13423571905931</v>
+        <v>20.13423571905928</v>
       </c>
       <c r="S2" t="n">
-        <v>20.08528915310486</v>
+        <v>20.08528915310482</v>
       </c>
       <c r="T2" t="n">
-        <v>20.04591274091247</v>
+        <v>20.04591274091241</v>
       </c>
       <c r="U2" t="n">
         <v>23.24895247627719</v>
@@ -4821,22 +4821,22 @@
         <v>20.10502951172288</v>
       </c>
       <c r="W2" t="n">
-        <v>25.46461762964459</v>
+        <v>25.46461762964456</v>
       </c>
       <c r="X2" t="n">
-        <v>20.36277843422488</v>
+        <v>20.36277843422481</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.1617835341597</v>
+        <v>20.16178353415967</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.22326161812152</v>
+        <v>26.22326161812149</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.13416401037586</v>
+        <v>20.13416401037581</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.06335830870973</v>
+        <v>20.06335830870958</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.80461105374363</v>
+        <v>20.86514613685304</v>
       </c>
       <c r="C3" t="n">
-        <v>15.5255174353876</v>
+        <v>14.75248372640726</v>
       </c>
       <c r="D3" t="n">
-        <v>21.62840184204149</v>
+        <v>20.49477057060223</v>
       </c>
       <c r="E3" t="n">
-        <v>16.18989726982366</v>
+        <v>15.36041440531578</v>
       </c>
       <c r="F3" t="n">
-        <v>21.81560871574433</v>
+        <v>20.55732244120972</v>
       </c>
       <c r="G3" t="n">
-        <v>22.40356938945099</v>
+        <v>20.7404164539715</v>
       </c>
       <c r="H3" t="n">
-        <v>22.82192502787636</v>
+        <v>20.91913002761023</v>
       </c>
       <c r="I3" t="n">
-        <v>23.4581287368005</v>
+        <v>21.12659814038221</v>
       </c>
       <c r="J3" t="n">
-        <v>22.51814016214543</v>
+        <v>20.78544437392586</v>
       </c>
       <c r="K3" t="n">
-        <v>22.44365762467767</v>
+        <v>20.7739906670776</v>
       </c>
       <c r="L3" t="n">
-        <v>21.92487870513224</v>
+        <v>20.59682670333889</v>
       </c>
       <c r="M3" t="n">
-        <v>21.91341291786586</v>
+        <v>20.51214413948752</v>
       </c>
       <c r="N3" t="n">
-        <v>22.19665884360633</v>
+        <v>20.67433406011036</v>
       </c>
       <c r="O3" t="n">
-        <v>30.64227074225916</v>
+        <v>27.96812799590841</v>
       </c>
       <c r="P3" t="n">
-        <v>23.042123272772</v>
+        <v>20.94312561034597</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.15570056946711</v>
+        <v>20.66134745630809</v>
       </c>
       <c r="R3" t="n">
-        <v>23.61976163699644</v>
+        <v>21.18865413444775</v>
       </c>
       <c r="S3" t="n">
-        <v>22.4374531311415</v>
+        <v>20.74413852476877</v>
       </c>
       <c r="T3" t="n">
-        <v>21.54736484695128</v>
+        <v>20.46574602466128</v>
       </c>
       <c r="U3" t="n">
-        <v>25.58956147331083</v>
+        <v>23.91993229558071</v>
       </c>
       <c r="V3" t="n">
-        <v>22.89117069777791</v>
+        <v>20.90305930126304</v>
       </c>
       <c r="W3" t="n">
-        <v>29.84628157363495</v>
+        <v>26.76720105629384</v>
       </c>
       <c r="X3" t="n">
-        <v>28.92456178798624</v>
+        <v>22.94841499926999</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.22836895525822</v>
+        <v>21.37668219993478</v>
       </c>
       <c r="Z3" t="n">
-        <v>28.25661588847741</v>
+        <v>26.78358039437642</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.58428724344018</v>
+        <v>21.15147139849058</v>
       </c>
       <c r="AB3" t="n">
-        <v>22.01669073269727</v>
+        <v>20.63741418124295</v>
       </c>
     </row>
     <row r="4">
@@ -4934,85 +4934,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.97590803429247</v>
+        <v>40.97590803429246</v>
       </c>
       <c r="C4" t="n">
-        <v>28.95218205400866</v>
+        <v>28.95218205400865</v>
       </c>
       <c r="D4" t="n">
-        <v>33.6631780511924</v>
+        <v>33.66317805119239</v>
       </c>
       <c r="E4" t="n">
-        <v>22.23103210918093</v>
+        <v>22.23103210918091</v>
       </c>
       <c r="F4" t="n">
-        <v>35.24418007635342</v>
+        <v>35.24418007635343</v>
       </c>
       <c r="G4" t="n">
-        <v>38.51553050986114</v>
+        <v>38.51553050985807</v>
       </c>
       <c r="H4" t="n">
-        <v>45.14150559818068</v>
+        <v>45.14150559818073</v>
       </c>
       <c r="I4" t="n">
-        <v>49.71186423820616</v>
+        <v>49.71186423820618</v>
       </c>
       <c r="J4" t="n">
-        <v>39.99853465259984</v>
+        <v>39.99853465259884</v>
       </c>
       <c r="K4" t="n">
-        <v>40.58690349938017</v>
+        <v>40.58690349938022</v>
       </c>
       <c r="L4" t="n">
-        <v>36.04486766517197</v>
+        <v>36.044867665172</v>
       </c>
       <c r="M4" t="n">
-        <v>38.12411444298459</v>
+        <v>38.12411444298462</v>
       </c>
       <c r="N4" t="n">
-        <v>37.36408315653243</v>
+        <v>37.36408315653246</v>
       </c>
       <c r="O4" t="n">
-        <v>49.49661730634399</v>
+        <v>49.49661730634398</v>
       </c>
       <c r="P4" t="n">
-        <v>42.66546460243374</v>
+        <v>42.66546460243373</v>
       </c>
       <c r="Q4" t="n">
-        <v>37.12656081894841</v>
+        <v>37.12656081894842</v>
       </c>
       <c r="R4" t="n">
-        <v>51.64176572550555</v>
+        <v>51.64176572550532</v>
       </c>
       <c r="S4" t="n">
-        <v>38.31289218200112</v>
+        <v>38.31289218200119</v>
       </c>
       <c r="T4" t="n">
-        <v>32.89276732920389</v>
+        <v>32.89276732920388</v>
       </c>
       <c r="U4" t="n">
-        <v>39.35352094414784</v>
+        <v>39.35352094414783</v>
       </c>
       <c r="V4" t="n">
-        <v>42.16059716729508</v>
+        <v>42.16059716729519</v>
       </c>
       <c r="W4" t="n">
-        <v>56.96440636525371</v>
+        <v>56.96440636525378</v>
       </c>
       <c r="X4" t="n">
-        <v>92.6948676385353</v>
+        <v>92.69486763853575</v>
       </c>
       <c r="Y4" t="n">
-        <v>54.99645833452841</v>
+        <v>54.99645833452864</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.55779090642616</v>
+        <v>35.55779090642615</v>
       </c>
       <c r="AA4" t="n">
-        <v>49.18525622030164</v>
+        <v>49.18525622030167</v>
       </c>
       <c r="AB4" t="n">
-        <v>37.80683114908688</v>
+        <v>37.80683114908687</v>
       </c>
     </row>
     <row r="5">
@@ -5022,73 +5022,73 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.11491860841155</v>
+        <v>27.11491860841156</v>
       </c>
       <c r="C5" t="n">
-        <v>36.53796982042317</v>
+        <v>36.53796982042318</v>
       </c>
       <c r="D5" t="n">
-        <v>36.80322082122183</v>
+        <v>36.80322082122185</v>
       </c>
       <c r="E5" t="n">
-        <v>31.15261863289418</v>
+        <v>31.15261863289417</v>
       </c>
       <c r="F5" t="n">
-        <v>28.21484646910749</v>
+        <v>28.2148464691075</v>
       </c>
       <c r="G5" t="n">
         <v>39.32465701257568</v>
       </c>
       <c r="H5" t="n">
-        <v>37.37289843845981</v>
+        <v>37.37289843845979</v>
       </c>
       <c r="I5" t="n">
-        <v>37.68648675803438</v>
+        <v>37.68648675803437</v>
       </c>
       <c r="J5" t="n">
-        <v>37.21632445884389</v>
+        <v>37.2163244588439</v>
       </c>
       <c r="K5" t="n">
-        <v>37.19934106500379</v>
+        <v>37.19934106500376</v>
       </c>
       <c r="L5" t="n">
         <v>36.95352901292209</v>
       </c>
       <c r="M5" t="n">
-        <v>37.00467762497451</v>
+        <v>37.0046776249745</v>
       </c>
       <c r="N5" t="n">
-        <v>37.36408315653244</v>
+        <v>29.11673328380716</v>
       </c>
       <c r="O5" t="n">
-        <v>32.15762567742933</v>
+        <v>32.15762567742932</v>
       </c>
       <c r="P5" t="n">
-        <v>31.19702285203887</v>
+        <v>31.19702285203888</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.76522234679073</v>
+        <v>24.76522234679075</v>
       </c>
       <c r="R5" t="n">
         <v>37.76133684175033</v>
       </c>
       <c r="S5" t="n">
-        <v>37.20846286276214</v>
+        <v>37.20846286276215</v>
       </c>
       <c r="T5" t="n">
-        <v>36.7636881730042</v>
+        <v>36.76368817300418</v>
       </c>
       <c r="U5" t="n">
-        <v>32.18270004890825</v>
+        <v>32.18270004890822</v>
       </c>
       <c r="V5" t="n">
-        <v>34.44526604003091</v>
+        <v>34.44526604003092</v>
       </c>
       <c r="W5" t="n">
-        <v>38.23842920351906</v>
+        <v>38.23842920351904</v>
       </c>
       <c r="X5" t="n">
-        <v>28.98833384120825</v>
+        <v>28.98833384120826</v>
       </c>
       <c r="Y5" t="n">
         <v>48.28931309586036</v>
@@ -5097,10 +5097,10 @@
         <v>26.57940695419629</v>
       </c>
       <c r="AA5" t="n">
-        <v>37.76052685918317</v>
+        <v>37.76052685918313</v>
       </c>
       <c r="AB5" t="n">
-        <v>47.72661324212904</v>
+        <v>47.72661324212902</v>
       </c>
     </row>
     <row r="6">
@@ -5110,34 +5110,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.93789134715304</v>
+        <v>22.93789134715301</v>
       </c>
       <c r="C6" t="n">
-        <v>25.40199698639189</v>
+        <v>25.40199698639186</v>
       </c>
       <c r="D6" t="n">
-        <v>25.66724798719056</v>
+        <v>25.66724798719055</v>
       </c>
       <c r="E6" t="n">
-        <v>24.72298157683556</v>
+        <v>24.72298157683551</v>
       </c>
       <c r="F6" t="n">
-        <v>18.10615804560071</v>
+        <v>18.10615804560069</v>
       </c>
       <c r="G6" t="n">
-        <v>26.05773090026144</v>
+        <v>26.05773090026148</v>
       </c>
       <c r="H6" t="n">
-        <v>26.23692560442854</v>
+        <v>26.23692560442849</v>
       </c>
       <c r="I6" t="n">
-        <v>26.55051392400308</v>
+        <v>26.55051392400307</v>
       </c>
       <c r="J6" t="n">
-        <v>26.0803516248126</v>
+        <v>26.08035162481259</v>
       </c>
       <c r="K6" t="n">
-        <v>26.06336823097249</v>
+        <v>26.06336823097247</v>
       </c>
       <c r="L6" t="n">
         <v>25.8175561788908</v>
@@ -5146,49 +5146,49 @@
         <v>25.86870479094341</v>
       </c>
       <c r="N6" t="n">
-        <v>37.36408315653243</v>
+        <v>25.94697270057</v>
       </c>
       <c r="O6" t="n">
-        <v>27.89820308519324</v>
+        <v>27.89820308519321</v>
       </c>
       <c r="P6" t="n">
-        <v>27.71334926161768</v>
+        <v>27.71334926161766</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.92563448313984</v>
+        <v>25.92563448313981</v>
       </c>
       <c r="R6" t="n">
-        <v>26.62536400771903</v>
+        <v>26.62536400771901</v>
       </c>
       <c r="S6" t="n">
-        <v>26.07249002873086</v>
+        <v>26.07249002873085</v>
       </c>
       <c r="T6" t="n">
-        <v>25.6277153389729</v>
+        <v>25.62771533897286</v>
       </c>
       <c r="U6" t="n">
         <v>26.06334706188716</v>
       </c>
       <c r="V6" t="n">
-        <v>29.94751820337378</v>
+        <v>29.94751820337379</v>
       </c>
       <c r="W6" t="n">
-        <v>27.10043668973991</v>
+        <v>27.10043668973989</v>
       </c>
       <c r="X6" t="n">
-        <v>29.20685911035731</v>
+        <v>29.20685911035729</v>
       </c>
       <c r="Y6" t="n">
-        <v>26.93652925189893</v>
+        <v>26.93652925189894</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.91074564871491</v>
+        <v>23.9107456487149</v>
       </c>
       <c r="AA6" t="n">
-        <v>26.62455402515187</v>
+        <v>26.62455402515184</v>
       </c>
       <c r="AB6" t="n">
-        <v>25.85569988643799</v>
+        <v>25.85569988643796</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.17986406220312</v>
+        <v>21.17986406220285</v>
       </c>
       <c r="C2" t="n">
-        <v>15.45966271009962</v>
+        <v>15.45966271010037</v>
       </c>
       <c r="D2" t="n">
-        <v>21.14641137118054</v>
+        <v>21.14641137118382</v>
       </c>
       <c r="E2" t="n">
-        <v>21.05611701670584</v>
+        <v>21.05611701670559</v>
       </c>
       <c r="F2" t="n">
-        <v>21.12808187686752</v>
+        <v>21.12808187686728</v>
       </c>
       <c r="G2" t="n">
-        <v>22.04861579238636</v>
+        <v>22.04861579238803</v>
       </c>
       <c r="H2" t="n">
-        <v>21.04937509899554</v>
+        <v>21.04937509899818</v>
       </c>
       <c r="I2" t="n">
-        <v>21.11835751671511</v>
+        <v>21.11835751671499</v>
       </c>
       <c r="J2" t="n">
-        <v>21.58538298137229</v>
+        <v>21.58538298137211</v>
       </c>
       <c r="K2" t="n">
-        <v>21.18155692257887</v>
+        <v>21.1815569225777</v>
       </c>
       <c r="L2" t="n">
-        <v>21.14938432452636</v>
+        <v>21.14938432452654</v>
       </c>
       <c r="M2" t="n">
-        <v>22.33541402252684</v>
+        <v>22.33541402252424</v>
       </c>
       <c r="N2" t="n">
-        <v>21.18156281425233</v>
+        <v>21.18156281425615</v>
       </c>
       <c r="O2" t="n">
-        <v>28.27200599493878</v>
+        <v>28.27200599493845</v>
       </c>
       <c r="P2" t="n">
-        <v>21.43635466805038</v>
+        <v>21.43635466805073</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.1744382624214</v>
+        <v>21.17443826242434</v>
       </c>
       <c r="R2" t="n">
-        <v>21.07461840934632</v>
+        <v>21.07461840934291</v>
       </c>
       <c r="S2" t="n">
-        <v>21.26700009299747</v>
+        <v>21.26700009299381</v>
       </c>
       <c r="T2" t="n">
-        <v>21.09439080981518</v>
+        <v>21.09439080981477</v>
       </c>
       <c r="U2" t="n">
-        <v>24.60004480753464</v>
+        <v>24.60004480753341</v>
       </c>
       <c r="V2" t="n">
-        <v>21.12015481473084</v>
+        <v>21.12015481473059</v>
       </c>
       <c r="W2" t="n">
-        <v>26.75519053977327</v>
+        <v>26.75519053976968</v>
       </c>
       <c r="X2" t="n">
-        <v>21.2682621625612</v>
+        <v>21.26826216256256</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.34703538245046</v>
+        <v>21.34703538245024</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.53821687261981</v>
+        <v>27.53821687262036</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.19203583420925</v>
+        <v>21.19203583421025</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.36394522420354</v>
+        <v>22.36394522420251</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.91160173417283</v>
+        <v>22.41964292634579</v>
       </c>
       <c r="C3" t="n">
-        <v>16.72118486096574</v>
+        <v>15.65722635298462</v>
       </c>
       <c r="D3" t="n">
-        <v>25.20172930356931</v>
+        <v>22.22991919274362</v>
       </c>
       <c r="E3" t="n">
-        <v>17.91734064969959</v>
+        <v>16.37946415723687</v>
       </c>
       <c r="F3" t="n">
-        <v>24.78975009052487</v>
+        <v>22.09000985046519</v>
       </c>
       <c r="G3" t="n">
-        <v>45.91714884792916</v>
+        <v>29.11653004737438</v>
       </c>
       <c r="H3" t="n">
-        <v>22.94983597437566</v>
+        <v>21.45881696464059</v>
       </c>
       <c r="I3" t="n">
-        <v>24.55293933547921</v>
+        <v>22.00781935257255</v>
       </c>
       <c r="J3" t="n">
-        <v>35.30988428235503</v>
+        <v>25.59781798826339</v>
       </c>
       <c r="K3" t="n">
-        <v>26.01318716150217</v>
+        <v>22.48986572825321</v>
       </c>
       <c r="L3" t="n">
-        <v>25.23476154198808</v>
+        <v>22.21297768598931</v>
       </c>
       <c r="M3" t="n">
-        <v>55.8765043544079</v>
+        <v>32.55120393325728</v>
       </c>
       <c r="N3" t="n">
-        <v>26.00291035865993</v>
+        <v>22.49456537748593</v>
       </c>
       <c r="O3" t="n">
-        <v>33.3612329419207</v>
+        <v>29.6164246308951</v>
       </c>
       <c r="P3" t="n">
-        <v>31.80222411104716</v>
+        <v>24.42513600073502</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.84301869645015</v>
+        <v>22.4332338684962</v>
       </c>
       <c r="R3" t="n">
-        <v>23.53514145741548</v>
+        <v>21.65525505610413</v>
       </c>
       <c r="S3" t="n">
-        <v>27.93275100870701</v>
+        <v>23.08390603882036</v>
       </c>
       <c r="T3" t="n">
-        <v>23.98903416908644</v>
+        <v>21.80782038489946</v>
       </c>
       <c r="U3" t="n">
-        <v>31.97962670659786</v>
+        <v>26.68826804267884</v>
       </c>
       <c r="V3" t="n">
-        <v>24.54352528384851</v>
+        <v>21.96930133979404</v>
       </c>
       <c r="W3" t="n">
-        <v>34.19523569714106</v>
+        <v>28.88545840179649</v>
       </c>
       <c r="X3" t="n">
-        <v>28.03941155621821</v>
+        <v>23.20953210915918</v>
       </c>
       <c r="Y3" t="n">
-        <v>29.83646019767077</v>
+        <v>23.80143254122618</v>
       </c>
       <c r="Z3" t="n">
-        <v>34.30942197420345</v>
+        <v>29.40585360344376</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.23449405722928</v>
+        <v>22.56631433079794</v>
       </c>
       <c r="AB3" t="n">
-        <v>53.43069416622536</v>
+        <v>32.28675777640419</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63.52813543357482</v>
+        <v>63.52813543357557</v>
       </c>
       <c r="C4" t="n">
-        <v>34.45380598558659</v>
+        <v>34.45380598558663</v>
       </c>
       <c r="D4" t="n">
-        <v>61.95854970630471</v>
+        <v>61.95854970630481</v>
       </c>
       <c r="E4" t="n">
-        <v>32.03039304989404</v>
+        <v>32.03039304989448</v>
       </c>
       <c r="F4" t="n">
-        <v>58.50764715438902</v>
+        <v>58.50764715438909</v>
       </c>
       <c r="G4" t="n">
-        <v>231.1010866236474</v>
+        <v>231.1010866236476</v>
       </c>
       <c r="H4" t="n">
-        <v>41.58202531216657</v>
+        <v>41.58202531216661</v>
       </c>
       <c r="I4" t="n">
-        <v>56.12461642612178</v>
+        <v>56.1246164261219</v>
       </c>
       <c r="J4" t="n">
-        <v>145.4324440877788</v>
+        <v>145.4324440877792</v>
       </c>
       <c r="K4" t="n">
-        <v>67.9316211676749</v>
+        <v>67.93162116767508</v>
       </c>
       <c r="L4" t="n">
-        <v>59.67616129145256</v>
+        <v>59.67616129145485</v>
       </c>
       <c r="M4" t="n">
-        <v>337.0225555538104</v>
+        <v>337.02255555381</v>
       </c>
       <c r="N4" t="n">
-        <v>68.2902204238941</v>
+        <v>68.29022042389407</v>
       </c>
       <c r="O4" t="n">
-        <v>66.28397443391549</v>
+        <v>66.28397443391557</v>
       </c>
       <c r="P4" t="n">
-        <v>115.0977783572857</v>
+        <v>115.0977783572859</v>
       </c>
       <c r="Q4" t="n">
-        <v>66.44035617044096</v>
+        <v>66.44035617044088</v>
       </c>
       <c r="R4" t="n">
-        <v>46.57960811994221</v>
+        <v>46.57960811994245</v>
       </c>
       <c r="S4" t="n">
-        <v>79.76797765363278</v>
+        <v>79.76797765363311</v>
       </c>
       <c r="T4" t="n">
-        <v>50.40660321088635</v>
+        <v>50.4066032108866</v>
       </c>
       <c r="U4" t="n">
-        <v>90.22627082477828</v>
+        <v>90.22627082477854</v>
       </c>
       <c r="V4" t="n">
-        <v>52.52027285752499</v>
+        <v>52.52027285752501</v>
       </c>
       <c r="W4" t="n">
-        <v>92.72072814182887</v>
+        <v>92.72072814182931</v>
       </c>
       <c r="X4" t="n">
-        <v>88.35722115248737</v>
+        <v>88.35722115248716</v>
       </c>
       <c r="Y4" t="n">
         <v>102.4585750034776</v>
       </c>
       <c r="Z4" t="n">
-        <v>81.95125878331257</v>
+        <v>81.95125878331245</v>
       </c>
       <c r="AA4" t="n">
-        <v>69.66932720774443</v>
+        <v>69.66932720774477</v>
       </c>
       <c r="AB4" t="n">
-        <v>348.2432103283363</v>
+        <v>348.243210328336</v>
       </c>
     </row>
     <row r="5">
@@ -5618,85 +5618,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.96809808667584</v>
+        <v>30.96809808667591</v>
       </c>
       <c r="C5" t="n">
-        <v>40.89184867590748</v>
+        <v>40.89184867590752</v>
       </c>
       <c r="D5" t="n">
-        <v>42.30391593296251</v>
+        <v>42.30391593296248</v>
       </c>
       <c r="E5" t="n">
-        <v>35.04680985847729</v>
+        <v>35.04680985847759</v>
       </c>
       <c r="F5" t="n">
-        <v>32.20804914078884</v>
+        <v>32.20804914078911</v>
       </c>
       <c r="G5" t="n">
-        <v>54.92363804681197</v>
+        <v>54.92363804681204</v>
       </c>
       <c r="H5" t="n">
-        <v>41.20784659973335</v>
+        <v>41.20784659973329</v>
       </c>
       <c r="I5" t="n">
-        <v>41.98703474132559</v>
+        <v>41.98703474132574</v>
       </c>
       <c r="J5" t="n">
-        <v>47.23027534012135</v>
+        <v>47.23027534012142</v>
       </c>
       <c r="K5" t="n">
-        <v>42.70090110370732</v>
+        <v>42.70090110370771</v>
       </c>
       <c r="L5" t="n">
-        <v>42.3374968085927</v>
+        <v>42.33749680859279</v>
       </c>
       <c r="M5" t="n">
-        <v>57.17588890207065</v>
+        <v>57.1758889020706</v>
       </c>
       <c r="N5" t="n">
-        <v>68.2902204238941</v>
+        <v>33.62090492714499</v>
       </c>
       <c r="O5" t="n">
-        <v>36.28311882995136</v>
+        <v>36.28311882995152</v>
       </c>
       <c r="P5" t="n">
-        <v>38.38252276245376</v>
+        <v>38.38252276245391</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.60480543902406</v>
+        <v>28.60480543902413</v>
       </c>
       <c r="R5" t="n">
-        <v>41.49298140257436</v>
+        <v>41.49298140257446</v>
       </c>
       <c r="S5" t="n">
-        <v>43.66602101935936</v>
+        <v>43.66602101935937</v>
       </c>
       <c r="T5" t="n">
-        <v>41.71631976165608</v>
+        <v>41.71631976165606</v>
       </c>
       <c r="U5" t="n">
-        <v>38.30039808575141</v>
+        <v>38.30039808575133</v>
       </c>
       <c r="V5" t="n">
-        <v>38.59740495369309</v>
+        <v>38.59740495369314</v>
       </c>
       <c r="W5" t="n">
-        <v>44.04363829242483</v>
+        <v>44.04363829242479</v>
       </c>
       <c r="X5" t="n">
-        <v>30.73817172661732</v>
+        <v>30.73817172661735</v>
       </c>
       <c r="Y5" t="n">
-        <v>56.2117422967004</v>
+        <v>56.21174229670044</v>
       </c>
       <c r="Z5" t="n">
-        <v>31.79319895966312</v>
+        <v>31.79319895966329</v>
       </c>
       <c r="AA5" t="n">
-        <v>42.81926523113635</v>
+        <v>42.81926523113644</v>
       </c>
       <c r="AB5" t="n">
-        <v>68.17708668786985</v>
+        <v>68.17708668786992</v>
       </c>
     </row>
     <row r="6">
@@ -5706,85 +5706,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.77012705378515</v>
+        <v>29.77012705378547</v>
       </c>
       <c r="C6" t="n">
-        <v>32.74731383641239</v>
+        <v>32.74731383641224</v>
       </c>
       <c r="D6" t="n">
-        <v>34.1593810934675</v>
+        <v>34.1593810934672</v>
       </c>
       <c r="E6" t="n">
-        <v>32.03923271937193</v>
+        <v>32.03923271937161</v>
       </c>
       <c r="F6" t="n">
-        <v>22.96283532293331</v>
+        <v>22.96283532293353</v>
       </c>
       <c r="G6" t="n">
-        <v>44.35019401051107</v>
+        <v>44.3501940105112</v>
       </c>
       <c r="H6" t="n">
-        <v>33.06331176023829</v>
+        <v>33.06331176023858</v>
       </c>
       <c r="I6" t="n">
-        <v>33.84249990183049</v>
+        <v>33.84249990183023</v>
       </c>
       <c r="J6" t="n">
-        <v>39.08574050062632</v>
+        <v>39.08574050062668</v>
       </c>
       <c r="K6" t="n">
-        <v>34.55636626421229</v>
+        <v>34.55636626421234</v>
       </c>
       <c r="L6" t="n">
-        <v>34.19296196909768</v>
+        <v>34.19296196909762</v>
       </c>
       <c r="M6" t="n">
-        <v>49.03135406257461</v>
+        <v>49.03135406257471</v>
       </c>
       <c r="N6" t="n">
-        <v>68.2902204238941</v>
+        <v>34.55643281343002</v>
       </c>
       <c r="O6" t="n">
-        <v>36.30318175524181</v>
+        <v>36.3031817552419</v>
       </c>
       <c r="P6" t="n">
-        <v>39.35782204179378</v>
+        <v>39.35782204179353</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.47595666804082</v>
+        <v>34.47595666804087</v>
       </c>
       <c r="R6" t="n">
-        <v>33.34844656307929</v>
+        <v>33.34844656307907</v>
       </c>
       <c r="S6" t="n">
-        <v>35.52148617986438</v>
+        <v>35.52148617986461</v>
       </c>
       <c r="T6" t="n">
-        <v>33.57178492216104</v>
+        <v>33.57178492216091</v>
       </c>
       <c r="U6" t="n">
-        <v>35.87605470199131</v>
+        <v>35.87605470199161</v>
       </c>
       <c r="V6" t="n">
-        <v>39.1587398626972</v>
+        <v>39.15873986269717</v>
       </c>
       <c r="W6" t="n">
-        <v>35.89680137815108</v>
+        <v>35.89680137815093</v>
       </c>
       <c r="X6" t="n">
-        <v>35.53574183622236</v>
+        <v>35.53574183622192</v>
       </c>
       <c r="Y6" t="n">
-        <v>36.42552159232663</v>
+        <v>36.4255215923265</v>
       </c>
       <c r="Z6" t="n">
-        <v>32.70578473876964</v>
+        <v>32.70578473876949</v>
       </c>
       <c r="AA6" t="n">
-        <v>34.67473039164134</v>
+        <v>34.6747303916414</v>
       </c>
       <c r="AB6" t="n">
-        <v>47.79663216380087</v>
+        <v>47.79663216380105</v>
       </c>
     </row>
   </sheetData>
@@ -5956,43 +5956,43 @@
         <v>15.08482395763466</v>
       </c>
       <c r="D2" t="n">
-        <v>20.63968307941956</v>
+        <v>20.63968307941955</v>
       </c>
       <c r="E2" t="n">
         <v>20.62304214377377</v>
       </c>
       <c r="F2" t="n">
-        <v>20.6234361672561</v>
+        <v>20.62343616725608</v>
       </c>
       <c r="G2" t="n">
         <v>21.42146262875744</v>
       </c>
       <c r="H2" t="n">
-        <v>20.65808349271165</v>
+        <v>20.65808349271166</v>
       </c>
       <c r="I2" t="n">
-        <v>20.66656332298848</v>
+        <v>20.66656332298847</v>
       </c>
       <c r="J2" t="n">
         <v>20.92453320952727</v>
       </c>
       <c r="K2" t="n">
-        <v>20.70314746233185</v>
+        <v>20.70314746233184</v>
       </c>
       <c r="L2" t="n">
-        <v>20.68733455507442</v>
+        <v>20.68733455507441</v>
       </c>
       <c r="M2" t="n">
-        <v>20.63732924805134</v>
+        <v>20.63732924805133</v>
       </c>
       <c r="N2" t="n">
         <v>20.70100266654153</v>
       </c>
       <c r="O2" t="n">
-        <v>27.60602588301738</v>
+        <v>27.60602588301739</v>
       </c>
       <c r="P2" t="n">
-        <v>20.84538239617545</v>
+        <v>20.84538239617542</v>
       </c>
       <c r="Q2" t="n">
         <v>20.73412912642115</v>
@@ -6001,22 +6001,22 @@
         <v>20.66094311075175</v>
       </c>
       <c r="S2" t="n">
-        <v>20.68848705361428</v>
+        <v>20.68848705361426</v>
       </c>
       <c r="T2" t="n">
         <v>20.62853133915197</v>
       </c>
       <c r="U2" t="n">
-        <v>23.94819596188229</v>
+        <v>23.94819596188228</v>
       </c>
       <c r="V2" t="n">
-        <v>20.6887726439321</v>
+        <v>20.68877264393209</v>
       </c>
       <c r="W2" t="n">
-        <v>26.20344257462848</v>
+        <v>26.20344257462847</v>
       </c>
       <c r="X2" t="n">
-        <v>20.87340572629733</v>
+        <v>20.87340572629732</v>
       </c>
       <c r="Y2" t="n">
         <v>21.14251850106936</v>
@@ -6025,10 +6025,10 @@
         <v>26.87288955639907</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.68061905002543</v>
+        <v>20.68061905002541</v>
       </c>
       <c r="AB2" t="n">
-        <v>21.41725000709134</v>
+        <v>21.41725000709132</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.3457821408597</v>
+        <v>21.67764878421558</v>
       </c>
       <c r="C3" t="n">
-        <v>16.52282746387743</v>
+        <v>15.39409603318979</v>
       </c>
       <c r="D3" t="n">
-        <v>22.32451809265599</v>
+        <v>21.01997105232929</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81027978254268</v>
+        <v>15.81395696855713</v>
       </c>
       <c r="F3" t="n">
-        <v>21.95150579240332</v>
+        <v>20.89399193457771</v>
       </c>
       <c r="G3" t="n">
-        <v>40.29083529683399</v>
+        <v>26.94127826349714</v>
       </c>
       <c r="H3" t="n">
-        <v>22.76743991904468</v>
+        <v>21.1824397504773</v>
       </c>
       <c r="I3" t="n">
-        <v>22.95540062873697</v>
+        <v>21.23775487096115</v>
       </c>
       <c r="J3" t="n">
-        <v>28.87376880196618</v>
+        <v>23.18653718053771</v>
       </c>
       <c r="K3" t="n">
-        <v>23.8014108096774</v>
+        <v>21.52819525461542</v>
       </c>
       <c r="L3" t="n">
-        <v>23.41292893101104</v>
+        <v>21.38164665321432</v>
       </c>
       <c r="M3" t="n">
-        <v>25.40424702101026</v>
+        <v>21.98585155167933</v>
       </c>
       <c r="N3" t="n">
-        <v>23.74291182397521</v>
+        <v>21.49893320313393</v>
       </c>
       <c r="O3" t="n">
-        <v>30.74538524311089</v>
+        <v>28.40827726122826</v>
       </c>
       <c r="P3" t="n">
-        <v>27.02378608199318</v>
+        <v>22.57677604363011</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.51590920787922</v>
+        <v>21.74609373034597</v>
       </c>
       <c r="R3" t="n">
-        <v>22.82829622465854</v>
+        <v>21.19655201284246</v>
       </c>
       <c r="S3" t="n">
-        <v>23.42965231923781</v>
+        <v>21.36936288540928</v>
       </c>
       <c r="T3" t="n">
-        <v>22.06469533291036</v>
+        <v>20.92726350089194</v>
       </c>
       <c r="U3" t="n">
-        <v>27.02257152980873</v>
+        <v>24.74509800577231</v>
       </c>
       <c r="V3" t="n">
-        <v>23.4347048991238</v>
+        <v>21.38150161909925</v>
       </c>
       <c r="W3" t="n">
-        <v>31.74458945353686</v>
+        <v>27.78359644064076</v>
       </c>
       <c r="X3" t="n">
-        <v>27.7702369660307</v>
+        <v>22.88340814402431</v>
       </c>
       <c r="Y3" t="n">
-        <v>33.98924177031368</v>
+        <v>25.01519094608269</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.86165175604724</v>
+        <v>27.62532036215615</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.26262239161849</v>
+        <v>21.32810743764967</v>
       </c>
       <c r="AB3" t="n">
-        <v>40.37226209438843</v>
+        <v>27.38442505851065</v>
       </c>
     </row>
     <row r="4">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.0728642027869</v>
+        <v>50.07286420278692</v>
       </c>
       <c r="C4" t="n">
         <v>34.08949699901547</v>
@@ -6135,76 +6135,76 @@
         <v>35.87172750643356</v>
       </c>
       <c r="E4" t="n">
-        <v>23.38997182596078</v>
+        <v>23.38997182596082</v>
       </c>
       <c r="F4" t="n">
-        <v>32.88709717307596</v>
+        <v>32.88709717307594</v>
       </c>
       <c r="G4" t="n">
-        <v>169.879827058152</v>
+        <v>169.8798270581511</v>
       </c>
       <c r="H4" t="n">
         <v>40.56886094471614</v>
       </c>
       <c r="I4" t="n">
-        <v>41.42587262363737</v>
+        <v>41.42587262363736</v>
       </c>
       <c r="J4" t="n">
-        <v>85.28159671443316</v>
+        <v>85.28159671443328</v>
       </c>
       <c r="K4" t="n">
-        <v>48.59814196061656</v>
+        <v>48.59814196061657</v>
       </c>
       <c r="L4" t="n">
-        <v>44.10168575807327</v>
+        <v>44.10168575807329</v>
       </c>
       <c r="M4" t="n">
-        <v>63.76478840347347</v>
+        <v>63.7647884034734</v>
       </c>
       <c r="N4" t="n">
-        <v>47.35781243703475</v>
+        <v>47.35781243703477</v>
       </c>
       <c r="O4" t="n">
-        <v>46.0395046489035</v>
+        <v>46.03950464890376</v>
       </c>
       <c r="P4" t="n">
-        <v>71.093394159805</v>
+        <v>71.09339415980503</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.76310103896791</v>
+        <v>52.7631010389679</v>
       </c>
       <c r="R4" t="n">
-        <v>40.55235349408754</v>
+        <v>40.55235349408758</v>
       </c>
       <c r="S4" t="n">
-        <v>42.88266381473652</v>
+        <v>42.88266381473649</v>
       </c>
       <c r="T4" t="n">
         <v>33.40403990112276</v>
       </c>
       <c r="U4" t="n">
-        <v>46.69613207460697</v>
+        <v>46.69613207460696</v>
       </c>
       <c r="V4" t="n">
-        <v>43.41591734836194</v>
+        <v>43.41591734836192</v>
       </c>
       <c r="W4" t="n">
-        <v>69.37547665418379</v>
+        <v>69.3754766541838</v>
       </c>
       <c r="X4" t="n">
-        <v>82.16950144885244</v>
+        <v>82.16950144885243</v>
       </c>
       <c r="Y4" t="n">
-        <v>134.6153112881334</v>
+        <v>134.6153112881332</v>
       </c>
       <c r="Z4" t="n">
         <v>44.59372077721386</v>
       </c>
       <c r="AA4" t="n">
-        <v>42.76212245320488</v>
+        <v>42.76212245320481</v>
       </c>
       <c r="AB4" t="n">
-        <v>202.5208652518699</v>
+        <v>202.5208652518697</v>
       </c>
     </row>
     <row r="5">
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.46829207988817</v>
+        <v>28.46829207988819</v>
       </c>
       <c r="C5" t="n">
-        <v>37.97191600465793</v>
+        <v>37.971916004658</v>
       </c>
       <c r="D5" t="n">
-        <v>38.0964952199178</v>
+        <v>38.09649521991784</v>
       </c>
       <c r="E5" t="n">
-        <v>32.24702862624027</v>
+        <v>32.2470286262403</v>
       </c>
       <c r="F5" t="n">
-        <v>28.93688707477514</v>
+        <v>28.93688707477519</v>
       </c>
       <c r="G5" t="n">
         <v>49.13177571552941</v>
       </c>
       <c r="H5" t="n">
-        <v>38.30433635266046</v>
+        <v>38.30433635266053</v>
       </c>
       <c r="I5" t="n">
-        <v>38.40011993655182</v>
+        <v>38.40011993655188</v>
       </c>
       <c r="J5" t="n">
-        <v>41.28314209337711</v>
+        <v>41.28314209337722</v>
       </c>
       <c r="K5" t="n">
-        <v>38.81335461997081</v>
+        <v>38.81335461997082</v>
       </c>
       <c r="L5" t="n">
-        <v>38.63474055820132</v>
+        <v>38.63474055820136</v>
       </c>
       <c r="M5" t="n">
-        <v>39.64797982029052</v>
+        <v>39.64797982029053</v>
       </c>
       <c r="N5" t="n">
-        <v>47.35781243703475</v>
+        <v>30.54715175521679</v>
       </c>
       <c r="O5" t="n">
-        <v>32.88020630500647</v>
+        <v>32.8802063050065</v>
       </c>
       <c r="P5" t="n">
-        <v>33.88775583806401</v>
+        <v>33.887755838064</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.44126220455008</v>
+        <v>26.4412622045501</v>
       </c>
       <c r="R5" t="n">
-        <v>38.33663705391258</v>
+        <v>38.33663705391257</v>
       </c>
       <c r="S5" t="n">
-        <v>38.64775855938457</v>
+        <v>38.64775855938463</v>
       </c>
       <c r="T5" t="n">
-        <v>37.97053118354151</v>
+        <v>37.97053118354157</v>
       </c>
       <c r="U5" t="n">
-        <v>33.62228666196248</v>
+        <v>33.62228666196251</v>
       </c>
       <c r="V5" t="n">
-        <v>35.54486264894467</v>
+        <v>35.54486264894472</v>
       </c>
       <c r="W5" t="n">
-        <v>40.0680282828459</v>
+        <v>40.06802828284588</v>
       </c>
       <c r="X5" t="n">
-        <v>28.9889464210028</v>
+        <v>28.98894642100281</v>
       </c>
       <c r="Y5" t="n">
-        <v>54.34369873490057</v>
+        <v>54.34369873490068</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.9472863601491</v>
+        <v>27.94728636014911</v>
       </c>
       <c r="AA5" t="n">
-        <v>38.55888583938803</v>
+        <v>38.55888583938805</v>
       </c>
       <c r="AB5" t="n">
-        <v>57.92680072870731</v>
+        <v>57.92680072870738</v>
       </c>
     </row>
     <row r="6">
@@ -6302,16 +6302,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.00388024473322</v>
+        <v>26.00388024473323</v>
       </c>
       <c r="C6" t="n">
         <v>28.82128304151153</v>
       </c>
       <c r="D6" t="n">
-        <v>28.9458622567714</v>
+        <v>28.94586225677138</v>
       </c>
       <c r="E6" t="n">
-        <v>27.8471083732933</v>
+        <v>27.84710837329333</v>
       </c>
       <c r="F6" t="n">
         <v>19.66506386261032</v>
@@ -6323,64 +6323,64 @@
         <v>29.15370338951404</v>
       </c>
       <c r="I6" t="n">
-        <v>29.24948697340544</v>
+        <v>29.24948697340542</v>
       </c>
       <c r="J6" t="n">
-        <v>32.13250913023075</v>
+        <v>32.13250913023072</v>
       </c>
       <c r="K6" t="n">
-        <v>29.66272165682437</v>
+        <v>29.6627216568244</v>
       </c>
       <c r="L6" t="n">
-        <v>29.4841075950549</v>
+        <v>29.48410759505489</v>
       </c>
       <c r="M6" t="n">
-        <v>30.497346857144</v>
+        <v>30.49734685714396</v>
       </c>
       <c r="N6" t="n">
-        <v>47.35781243703475</v>
+        <v>29.63849520171796</v>
       </c>
       <c r="O6" t="n">
         <v>31.01438116973086</v>
       </c>
       <c r="P6" t="n">
-        <v>32.86155206855813</v>
+        <v>32.86155206855811</v>
       </c>
       <c r="Q6" t="n">
-        <v>30.01267539546685</v>
+        <v>30.01267539546684</v>
       </c>
       <c r="R6" t="n">
-        <v>29.18600409076615</v>
+        <v>29.18600409076614</v>
       </c>
       <c r="S6" t="n">
-        <v>29.49712559623816</v>
+        <v>29.49712559623812</v>
       </c>
       <c r="T6" t="n">
-        <v>28.81989822039512</v>
+        <v>28.8198982203951</v>
       </c>
       <c r="U6" t="n">
-        <v>29.66370800976069</v>
+        <v>29.66370800976068</v>
       </c>
       <c r="V6" t="n">
-        <v>33.85691367689994</v>
+        <v>33.85691367689993</v>
       </c>
       <c r="W6" t="n">
-        <v>30.91530572545615</v>
+        <v>30.91530572545612</v>
       </c>
       <c r="X6" t="n">
-        <v>31.58586707098542</v>
+        <v>31.58586707098545</v>
       </c>
       <c r="Y6" t="n">
-        <v>34.62561966002828</v>
+        <v>34.62561966002826</v>
       </c>
       <c r="Z6" t="n">
-        <v>27.24740836453695</v>
+        <v>27.24740836453698</v>
       </c>
       <c r="AA6" t="n">
-        <v>29.40825287624158</v>
+        <v>29.4082528762416</v>
       </c>
       <c r="AB6" t="n">
-        <v>37.66961878707346</v>
+        <v>37.66961878707343</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ecotoxicity freshwater results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.14224171820514</v>
+        <v>22.39032690857972</v>
       </c>
       <c r="C3" t="n">
-        <v>16.25553831415238</v>
+        <v>15.86511945185627</v>
       </c>
       <c r="D3" t="n">
-        <v>22.74020697306093</v>
+        <v>22.05769903226832</v>
       </c>
       <c r="E3" t="n">
-        <v>16.64150953691766</v>
+        <v>16.36874312778667</v>
       </c>
       <c r="F3" t="n">
-        <v>23.24072848851326</v>
+        <v>22.38725504168707</v>
       </c>
       <c r="G3" t="n">
-        <v>30.13296949566783</v>
+        <v>27.33274047104177</v>
       </c>
       <c r="H3" t="n">
-        <v>21.99061920566681</v>
+        <v>21.52912497342541</v>
       </c>
       <c r="I3" t="n">
-        <v>23.05833473725859</v>
+        <v>22.27043001008921</v>
       </c>
       <c r="J3" t="n">
-        <v>26.24036083173975</v>
+        <v>24.54386265489297</v>
       </c>
       <c r="K3" t="n">
-        <v>22.92618237125767</v>
+        <v>22.18930734405421</v>
       </c>
       <c r="L3" t="n">
-        <v>22.57690379492382</v>
+        <v>21.96780707454485</v>
       </c>
       <c r="M3" t="n">
-        <v>34.38757245763765</v>
+        <v>29.98240326035653</v>
       </c>
       <c r="N3" t="n">
-        <v>22.73556255758706</v>
+        <v>22.06634102777741</v>
       </c>
       <c r="O3" t="n">
-        <v>31.15795010260706</v>
+        <v>30.21233649989526</v>
       </c>
       <c r="P3" t="n">
-        <v>24.80190802327237</v>
+        <v>23.56816348358268</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.20604428208497</v>
+        <v>21.69619353064628</v>
       </c>
       <c r="R3" t="n">
-        <v>22.01453779880177</v>
+        <v>21.55222163868974</v>
       </c>
       <c r="S3" t="n">
-        <v>24.13791595730353</v>
+        <v>23.08298115913052</v>
       </c>
       <c r="T3" t="n">
-        <v>22.32738293677017</v>
+        <v>21.7726870852873</v>
       </c>
       <c r="U3" t="n">
-        <v>28.97872086479471</v>
+        <v>27.49764645379441</v>
       </c>
       <c r="V3" t="n">
-        <v>22.95470466321627</v>
+        <v>22.2494060074666</v>
       </c>
       <c r="W3" t="n">
-        <v>29.7913813350798</v>
+        <v>28.69424659598645</v>
       </c>
       <c r="X3" t="n">
-        <v>23.24642600841173</v>
+        <v>22.41109367040954</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.39298050644614</v>
+        <v>23.2273872707286</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.38232044630526</v>
+        <v>29.36656715281897</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.6302324143913</v>
+        <v>23.39085417054129</v>
       </c>
       <c r="AB3" t="n">
-        <v>34.65414647799553</v>
+        <v>30.11419024434435</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.18798823156275</v>
+        <v>20.72818389142824</v>
       </c>
       <c r="C3" t="n">
-        <v>14.86577840821052</v>
+        <v>14.60580620309618</v>
       </c>
       <c r="D3" t="n">
-        <v>20.55272701372235</v>
+        <v>20.2527235851384</v>
       </c>
       <c r="E3" t="n">
-        <v>15.26704098198984</v>
+        <v>15.149629310311</v>
       </c>
       <c r="F3" t="n">
-        <v>20.6654558973676</v>
+        <v>20.33162907741931</v>
       </c>
       <c r="G3" t="n">
-        <v>21.05605811237451</v>
+        <v>20.62911853783469</v>
       </c>
       <c r="H3" t="n">
-        <v>21.03143862488368</v>
+        <v>20.5754773024601</v>
       </c>
       <c r="I3" t="n">
-        <v>21.31640930573857</v>
+        <v>20.7825144303326</v>
       </c>
       <c r="J3" t="n">
-        <v>20.98565140598658</v>
+        <v>20.57003800111012</v>
       </c>
       <c r="K3" t="n">
-        <v>21.13426009617802</v>
+        <v>20.66375455160625</v>
       </c>
       <c r="L3" t="n">
-        <v>20.87158838581789</v>
+        <v>20.48799221837352</v>
       </c>
       <c r="M3" t="n">
-        <v>20.76712808617194</v>
+        <v>20.35558031708366</v>
       </c>
       <c r="N3" t="n">
-        <v>20.8297865122313</v>
+        <v>20.45579557536268</v>
       </c>
       <c r="O3" t="n">
-        <v>27.65134421448422</v>
+        <v>27.27108316808907</v>
       </c>
       <c r="P3" t="n">
-        <v>21.00933438568123</v>
+        <v>20.601649922661</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.03659573468335</v>
+        <v>20.60331066156148</v>
       </c>
       <c r="R3" t="n">
-        <v>21.19351496984895</v>
+        <v>20.69296364329229</v>
       </c>
       <c r="S3" t="n">
-        <v>20.93163667865544</v>
+        <v>20.54191053100244</v>
       </c>
       <c r="T3" t="n">
-        <v>20.58985025525544</v>
+        <v>20.28312687888211</v>
       </c>
       <c r="U3" t="n">
-        <v>24.32583252879328</v>
+        <v>23.87863989266392</v>
       </c>
       <c r="V3" t="n">
-        <v>20.96011393746966</v>
+        <v>20.55797501840697</v>
       </c>
       <c r="W3" t="n">
-        <v>27.22339661322875</v>
+        <v>26.53999729179133</v>
       </c>
       <c r="X3" t="n">
-        <v>22.76202752037205</v>
+        <v>21.8131215410952</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.55541232905469</v>
+        <v>21.65753663174071</v>
       </c>
       <c r="Z3" t="n">
-        <v>26.91088786307446</v>
+        <v>26.57735794022729</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.4118223264736</v>
+        <v>20.86447542936768</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.7057792993554</v>
+        <v>20.35220035311007</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.03388262849475</v>
+        <v>22.28823130967821</v>
       </c>
       <c r="C3" t="n">
-        <v>15.78467893988396</v>
+        <v>15.5045156036652</v>
       </c>
       <c r="D3" t="n">
-        <v>23.41310314350937</v>
+        <v>22.4909902649329</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46383499954863</v>
+        <v>16.22189611632286</v>
       </c>
       <c r="F3" t="n">
-        <v>22.90035926716999</v>
+        <v>22.13179147908049</v>
       </c>
       <c r="G3" t="n">
-        <v>29.74727125513714</v>
+        <v>27.04799384938033</v>
       </c>
       <c r="H3" t="n">
-        <v>21.47041588327418</v>
+        <v>21.14585822824414</v>
       </c>
       <c r="I3" t="n">
-        <v>22.08374844626802</v>
+        <v>21.57398201268426</v>
       </c>
       <c r="J3" t="n">
-        <v>26.26743158497754</v>
+        <v>24.53785865276817</v>
       </c>
       <c r="K3" t="n">
-        <v>22.82258427913983</v>
+        <v>22.09927139829803</v>
       </c>
       <c r="L3" t="n">
-        <v>22.24026923950319</v>
+        <v>21.70452792540182</v>
       </c>
       <c r="M3" t="n">
-        <v>33.37198710911608</v>
+        <v>29.27103582689119</v>
       </c>
       <c r="N3" t="n">
-        <v>22.46070063557785</v>
+        <v>21.84735496021904</v>
       </c>
       <c r="O3" t="n">
-        <v>30.79121652998711</v>
+        <v>29.90834199898708</v>
       </c>
       <c r="P3" t="n">
-        <v>25.4365856292063</v>
+        <v>23.99419714213503</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.20311055006176</v>
+        <v>21.66629084811148</v>
       </c>
       <c r="R3" t="n">
-        <v>21.62673908014364</v>
+        <v>21.25830551109257</v>
       </c>
       <c r="S3" t="n">
-        <v>23.99953727089731</v>
+        <v>22.96265025002371</v>
       </c>
       <c r="T3" t="n">
-        <v>22.08826979904298</v>
+        <v>21.57941289635145</v>
       </c>
       <c r="U3" t="n">
-        <v>28.11683384904522</v>
+        <v>26.84661835324696</v>
       </c>
       <c r="V3" t="n">
-        <v>22.33368885742324</v>
+        <v>21.78187370761459</v>
       </c>
       <c r="W3" t="n">
-        <v>29.42599939802803</v>
+        <v>28.39130571123191</v>
       </c>
       <c r="X3" t="n">
-        <v>23.28242736298611</v>
+        <v>22.40887866959013</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.05519213039003</v>
+        <v>22.96836626478507</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.77598527883753</v>
+        <v>28.89549034324467</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.00102837038901</v>
+        <v>22.2303808991986</v>
       </c>
       <c r="AB3" t="n">
-        <v>34.1877620527432</v>
+        <v>29.76597561601773</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.97560952763384</v>
+        <v>22.23062704989467</v>
       </c>
       <c r="C3" t="n">
-        <v>15.72615866897508</v>
+        <v>15.4455259591194</v>
       </c>
       <c r="D3" t="n">
-        <v>23.76706635704</v>
+        <v>22.72463914112924</v>
       </c>
       <c r="E3" t="n">
-        <v>16.34861615094141</v>
+        <v>16.13033479461667</v>
       </c>
       <c r="F3" t="n">
-        <v>23.57162609492394</v>
+        <v>22.58646636191706</v>
       </c>
       <c r="G3" t="n">
-        <v>29.12627586408509</v>
+        <v>26.61900982407808</v>
       </c>
       <c r="H3" t="n">
-        <v>21.43745594460213</v>
+        <v>21.11096832337942</v>
       </c>
       <c r="I3" t="n">
-        <v>22.87237406022711</v>
+        <v>22.10128652130788</v>
       </c>
       <c r="J3" t="n">
-        <v>25.9460573067763</v>
+        <v>24.30485124076036</v>
       </c>
       <c r="K3" t="n">
-        <v>23.00208384221284</v>
+        <v>22.2232717209824</v>
       </c>
       <c r="L3" t="n">
-        <v>22.04972222634861</v>
+        <v>21.55858735647582</v>
       </c>
       <c r="M3" t="n">
-        <v>31.8096681140074</v>
+        <v>28.18205862414136</v>
       </c>
       <c r="N3" t="n">
-        <v>22.10157722216281</v>
+        <v>21.58512739494909</v>
       </c>
       <c r="O3" t="n">
-        <v>30.43690937087486</v>
+        <v>29.62783117709558</v>
       </c>
       <c r="P3" t="n">
-        <v>25.30656942248542</v>
+        <v>23.89843579994557</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.33367099479674</v>
+        <v>21.74745511758677</v>
       </c>
       <c r="R3" t="n">
-        <v>21.479541695793</v>
+        <v>21.14451199290819</v>
       </c>
       <c r="S3" t="n">
-        <v>23.73581070202393</v>
+        <v>22.76722708393697</v>
       </c>
       <c r="T3" t="n">
-        <v>22.05057070571133</v>
+        <v>21.54035641624699</v>
       </c>
       <c r="U3" t="n">
-        <v>26.10967123437838</v>
+        <v>25.40866449231418</v>
       </c>
       <c r="V3" t="n">
-        <v>22.67371416897405</v>
+        <v>22.01752356652824</v>
       </c>
       <c r="W3" t="n">
-        <v>28.97255277899711</v>
+        <v>28.04728010831418</v>
       </c>
       <c r="X3" t="n">
-        <v>23.72130911698338</v>
+        <v>22.70139276600509</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.10244919171468</v>
+        <v>24.3861166015876</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.68453983005663</v>
+        <v>28.83775941127422</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.48119935997435</v>
+        <v>21.85471984786827</v>
       </c>
       <c r="AB3" t="n">
-        <v>33.25660531101775</v>
+        <v>29.11168407020732</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.85239349642213</v>
+        <v>22.13592502260412</v>
       </c>
       <c r="C3" t="n">
-        <v>15.8023829975829</v>
+        <v>15.48360364363889</v>
       </c>
       <c r="D3" t="n">
-        <v>23.06073868447785</v>
+        <v>22.23202649813852</v>
       </c>
       <c r="E3" t="n">
-        <v>16.10804346351736</v>
+        <v>15.93845559670189</v>
       </c>
       <c r="F3" t="n">
-        <v>23.94071735697687</v>
+        <v>22.83004777166595</v>
       </c>
       <c r="G3" t="n">
-        <v>27.96478174033834</v>
+        <v>25.81824165802192</v>
       </c>
       <c r="H3" t="n">
-        <v>21.47376229332998</v>
+        <v>21.11936615231372</v>
       </c>
       <c r="I3" t="n">
-        <v>23.07166146924427</v>
+        <v>22.22622817771327</v>
       </c>
       <c r="J3" t="n">
-        <v>25.32757981566959</v>
+        <v>23.8723651048368</v>
       </c>
       <c r="K3" t="n">
-        <v>23.14490765228086</v>
+        <v>22.31120441629097</v>
       </c>
       <c r="L3" t="n">
-        <v>22.02648210229212</v>
+        <v>21.52745173803894</v>
       </c>
       <c r="M3" t="n">
-        <v>29.92805490284038</v>
+        <v>26.95074466030864</v>
       </c>
       <c r="N3" t="n">
-        <v>21.85147062170815</v>
+        <v>21.39572041484709</v>
       </c>
       <c r="O3" t="n">
-        <v>29.69590809742503</v>
+        <v>29.05312173777094</v>
       </c>
       <c r="P3" t="n">
-        <v>24.81953109198625</v>
+        <v>23.55799113103192</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.132177192407</v>
+        <v>21.5951154067726</v>
       </c>
       <c r="R3" t="n">
-        <v>22.18046611856409</v>
+        <v>21.60597329846885</v>
       </c>
       <c r="S3" t="n">
-        <v>23.54542355652281</v>
+        <v>22.62271380395408</v>
       </c>
       <c r="T3" t="n">
-        <v>22.24166226542915</v>
+        <v>21.65546188414066</v>
       </c>
       <c r="U3" t="n">
-        <v>25.56799851289754</v>
+        <v>25.01063469108146</v>
       </c>
       <c r="V3" t="n">
-        <v>23.25842614504882</v>
+        <v>22.42964767247573</v>
       </c>
       <c r="W3" t="n">
-        <v>28.87708946856099</v>
+        <v>27.96094353114082</v>
       </c>
       <c r="X3" t="n">
-        <v>23.81576347986672</v>
+        <v>22.76582069466789</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.52120925185949</v>
+        <v>26.03392052736283</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.30084913418109</v>
+        <v>28.55835752956236</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.59630191040002</v>
+        <v>21.91864976369457</v>
       </c>
       <c r="AB3" t="n">
-        <v>32.01524077597279</v>
+        <v>28.28750781042329</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.48652770777196</v>
+        <v>20.99244945509545</v>
       </c>
       <c r="C3" t="n">
-        <v>14.96268639901478</v>
+        <v>14.73089058504683</v>
       </c>
       <c r="D3" t="n">
-        <v>20.95579117724213</v>
+        <v>20.59174063346111</v>
       </c>
       <c r="E3" t="n">
-        <v>15.75283582358187</v>
+        <v>15.54888630655782</v>
       </c>
       <c r="F3" t="n">
-        <v>20.89905152968327</v>
+        <v>20.54799297931238</v>
       </c>
       <c r="G3" t="n">
-        <v>22.79516006184298</v>
+        <v>21.94579703945733</v>
       </c>
       <c r="H3" t="n">
-        <v>21.57876751144688</v>
+        <v>21.00512540457249</v>
       </c>
       <c r="I3" t="n">
-        <v>21.10720860538045</v>
+        <v>20.69360653429078</v>
       </c>
       <c r="J3" t="n">
-        <v>22.14899571993423</v>
+        <v>21.46069635760243</v>
       </c>
       <c r="K3" t="n">
-        <v>21.5617154808942</v>
+        <v>21.01729577249426</v>
       </c>
       <c r="L3" t="n">
-        <v>21.57859037778982</v>
+        <v>21.04678958382691</v>
       </c>
       <c r="M3" t="n">
-        <v>24.29162575372451</v>
+        <v>22.90090580513673</v>
       </c>
       <c r="N3" t="n">
-        <v>21.40261892731752</v>
+        <v>20.91231533402729</v>
       </c>
       <c r="O3" t="n">
-        <v>28.18223953097599</v>
+        <v>27.72830822509555</v>
       </c>
       <c r="P3" t="n">
-        <v>22.09039532659412</v>
+        <v>21.42361371669751</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.52047922251416</v>
+        <v>20.99477596335765</v>
       </c>
       <c r="R3" t="n">
-        <v>21.00036859643179</v>
+        <v>20.61813648400523</v>
       </c>
       <c r="S3" t="n">
-        <v>21.62971694074219</v>
+        <v>21.10511640154262</v>
       </c>
       <c r="T3" t="n">
-        <v>20.99465569501384</v>
+        <v>20.6145340854945</v>
       </c>
       <c r="U3" t="n">
-        <v>24.85019913780761</v>
+        <v>24.31080761070807</v>
       </c>
       <c r="V3" t="n">
-        <v>21.0790369394796</v>
+        <v>20.69262101611266</v>
       </c>
       <c r="W3" t="n">
-        <v>28.1645031600235</v>
+        <v>27.26267118695289</v>
       </c>
       <c r="X3" t="n">
-        <v>21.6790453649692</v>
+        <v>21.09575739641028</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.3701860589358</v>
+        <v>20.88900268875728</v>
       </c>
       <c r="Z3" t="n">
-        <v>28.01591934933561</v>
+        <v>27.44202475213289</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.33508709104577</v>
+        <v>20.86579995045053</v>
       </c>
       <c r="AB3" t="n">
-        <v>23.73031047238522</v>
+        <v>22.485352903871</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.21272566014108</v>
+        <v>20.74147347374728</v>
       </c>
       <c r="C3" t="n">
-        <v>14.89999039452142</v>
+        <v>14.62594723361097</v>
       </c>
       <c r="D3" t="n">
-        <v>20.42406607089493</v>
+        <v>20.15676386200952</v>
       </c>
       <c r="E3" t="n">
-        <v>15.31876950493675</v>
+        <v>15.19376426462082</v>
       </c>
       <c r="F3" t="n">
-        <v>20.65453266317322</v>
+        <v>20.32066689751471</v>
       </c>
       <c r="G3" t="n">
-        <v>20.94954042244082</v>
+        <v>20.54633856224036</v>
       </c>
       <c r="H3" t="n">
-        <v>21.1487857550457</v>
+        <v>20.65216012055482</v>
       </c>
       <c r="I3" t="n">
-        <v>20.92609013422718</v>
+        <v>20.50874724107149</v>
       </c>
       <c r="J3" t="n">
-        <v>20.96574216341116</v>
+        <v>20.55382936934023</v>
       </c>
       <c r="K3" t="n">
-        <v>20.89935802469216</v>
+        <v>20.49166646960789</v>
       </c>
       <c r="L3" t="n">
-        <v>20.72170003659455</v>
+        <v>20.3670856259002</v>
       </c>
       <c r="M3" t="n">
-        <v>20.5439719913873</v>
+        <v>20.18645208809825</v>
       </c>
       <c r="N3" t="n">
-        <v>21.01600069775793</v>
+        <v>20.5865705034887</v>
       </c>
       <c r="O3" t="n">
-        <v>28.20259825076113</v>
+        <v>27.6730885381084</v>
       </c>
       <c r="P3" t="n">
-        <v>20.97444545606482</v>
+        <v>20.57323663444567</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.04485245960105</v>
+        <v>20.61183416679954</v>
       </c>
       <c r="R3" t="n">
-        <v>20.8172088731294</v>
+        <v>20.43080604018645</v>
       </c>
       <c r="S3" t="n">
-        <v>20.90818280527684</v>
+        <v>20.52389713188899</v>
       </c>
       <c r="T3" t="n">
-        <v>20.49518094397783</v>
+        <v>20.20549608667973</v>
       </c>
       <c r="U3" t="n">
-        <v>24.04077399482342</v>
+        <v>23.65600188599977</v>
       </c>
       <c r="V3" t="n">
-        <v>21.03588856292963</v>
+        <v>20.60922538810393</v>
       </c>
       <c r="W3" t="n">
-        <v>27.01549213283397</v>
+        <v>26.3859009968003</v>
       </c>
       <c r="X3" t="n">
-        <v>22.58503156047711</v>
+        <v>21.68916144877645</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.6193786963868</v>
+        <v>21.00536706891052</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.27661023842126</v>
+        <v>26.84414698052847</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.10117927832104</v>
+        <v>20.64510893919134</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.62734500018378</v>
+        <v>20.2950409404935</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.86514613685304</v>
+        <v>20.48093764285402</v>
       </c>
       <c r="C3" t="n">
-        <v>14.75248372640726</v>
+        <v>14.5111624201792</v>
       </c>
       <c r="D3" t="n">
-        <v>20.49477057060223</v>
+        <v>20.19657913771131</v>
       </c>
       <c r="E3" t="n">
-        <v>15.36041440531578</v>
+        <v>15.20617965105979</v>
       </c>
       <c r="F3" t="n">
-        <v>20.55732244120972</v>
+        <v>20.2400246820225</v>
       </c>
       <c r="G3" t="n">
-        <v>20.7404164539715</v>
+        <v>20.38514861683397</v>
       </c>
       <c r="H3" t="n">
-        <v>20.91913002761023</v>
+        <v>20.48139476039455</v>
       </c>
       <c r="I3" t="n">
-        <v>21.12659814038221</v>
+        <v>20.63441011721776</v>
       </c>
       <c r="J3" t="n">
-        <v>20.78544437392586</v>
+        <v>20.41149527242062</v>
       </c>
       <c r="K3" t="n">
-        <v>20.7739906670776</v>
+        <v>20.39229787837758</v>
       </c>
       <c r="L3" t="n">
-        <v>20.59682670333889</v>
+        <v>20.27009136065978</v>
       </c>
       <c r="M3" t="n">
-        <v>20.51214413948752</v>
+        <v>20.15946529360135</v>
       </c>
       <c r="N3" t="n">
-        <v>20.67433406011036</v>
+        <v>20.33237876708228</v>
       </c>
       <c r="O3" t="n">
-        <v>27.96812799590841</v>
+        <v>27.48186797847568</v>
       </c>
       <c r="P3" t="n">
-        <v>20.94312561034597</v>
+        <v>20.5388263609799</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.66134745630809</v>
+        <v>20.32215758638136</v>
       </c>
       <c r="R3" t="n">
-        <v>21.18865413444775</v>
+        <v>20.67273622835621</v>
       </c>
       <c r="S3" t="n">
-        <v>20.74413852476877</v>
+        <v>20.39165165533573</v>
       </c>
       <c r="T3" t="n">
-        <v>20.46574602466128</v>
+        <v>20.17690400984635</v>
       </c>
       <c r="U3" t="n">
-        <v>23.91993229558071</v>
+        <v>23.55401670919623</v>
       </c>
       <c r="V3" t="n">
-        <v>20.90305930126304</v>
+        <v>20.50194517004388</v>
       </c>
       <c r="W3" t="n">
-        <v>26.76720105629384</v>
+        <v>26.18927289005762</v>
       </c>
       <c r="X3" t="n">
-        <v>22.94841499926999</v>
+        <v>21.94036694311146</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.37668219993478</v>
+        <v>20.82183138453754</v>
       </c>
       <c r="Z3" t="n">
-        <v>26.78358039437642</v>
+        <v>26.46427231243377</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.15147139849058</v>
+        <v>20.66696688723202</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.63741418124295</v>
+        <v>20.28862767523676</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.41964292634579</v>
+        <v>21.81179363687318</v>
       </c>
       <c r="C3" t="n">
-        <v>15.65722635298462</v>
+        <v>15.37459794599441</v>
       </c>
       <c r="D3" t="n">
-        <v>22.22991919274362</v>
+        <v>21.63627483218389</v>
       </c>
       <c r="E3" t="n">
-        <v>16.37946415723687</v>
+        <v>16.13039632802352</v>
       </c>
       <c r="F3" t="n">
-        <v>22.09000985046519</v>
+        <v>21.53503124289468</v>
       </c>
       <c r="G3" t="n">
-        <v>29.11653004737438</v>
+        <v>26.62823445192898</v>
       </c>
       <c r="H3" t="n">
-        <v>21.45881696464059</v>
+        <v>21.09498916292917</v>
       </c>
       <c r="I3" t="n">
-        <v>22.00781935257255</v>
+        <v>21.47993640282869</v>
       </c>
       <c r="J3" t="n">
-        <v>25.59781798826339</v>
+        <v>24.06791335081729</v>
       </c>
       <c r="K3" t="n">
-        <v>22.48986572825321</v>
+        <v>21.82975628898512</v>
       </c>
       <c r="L3" t="n">
-        <v>22.21297768598931</v>
+        <v>21.64693890273847</v>
       </c>
       <c r="M3" t="n">
-        <v>32.55120393325728</v>
+        <v>28.85615779317659</v>
       </c>
       <c r="N3" t="n">
-        <v>22.49456537748593</v>
+        <v>21.83018234858036</v>
       </c>
       <c r="O3" t="n">
-        <v>29.6164246308951</v>
+        <v>28.9779451766271</v>
       </c>
       <c r="P3" t="n">
-        <v>24.42513600073502</v>
+        <v>23.23712726762349</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.4332338684962</v>
+        <v>21.78994136507026</v>
       </c>
       <c r="R3" t="n">
-        <v>21.65525505610413</v>
+        <v>21.23525645443888</v>
       </c>
       <c r="S3" t="n">
-        <v>23.08390603882036</v>
+        <v>22.29421510517786</v>
       </c>
       <c r="T3" t="n">
-        <v>21.80782038489946</v>
+        <v>21.344867403435</v>
       </c>
       <c r="U3" t="n">
-        <v>26.68826804267884</v>
+        <v>25.77814409938738</v>
       </c>
       <c r="V3" t="n">
-        <v>21.96930133979404</v>
+        <v>21.4821769448691</v>
       </c>
       <c r="W3" t="n">
-        <v>28.88545840179649</v>
+        <v>27.94584865719583</v>
       </c>
       <c r="X3" t="n">
-        <v>23.20953210915918</v>
+        <v>22.31763019595723</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.80143254122618</v>
+        <v>22.75205309516166</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.40585360344376</v>
+        <v>28.59083535911083</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.56631433079794</v>
+        <v>21.88690287895897</v>
       </c>
       <c r="AB3" t="n">
-        <v>32.28675777640419</v>
+        <v>28.44324772314426</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.67764878421558</v>
+        <v>21.18722196890109</v>
       </c>
       <c r="C3" t="n">
-        <v>15.39409603318979</v>
+        <v>15.09368822467701</v>
       </c>
       <c r="D3" t="n">
-        <v>21.01997105232929</v>
+        <v>20.69835851007119</v>
       </c>
       <c r="E3" t="n">
-        <v>15.81395696855713</v>
+        <v>15.64960700403724</v>
       </c>
       <c r="F3" t="n">
-        <v>20.89399193457771</v>
+        <v>20.60821134114713</v>
       </c>
       <c r="G3" t="n">
-        <v>26.94127826349714</v>
+        <v>25.01839021948092</v>
       </c>
       <c r="H3" t="n">
-        <v>21.1824397504773</v>
+        <v>20.80340002284303</v>
       </c>
       <c r="I3" t="n">
-        <v>21.23775487096115</v>
+        <v>20.84897748670939</v>
       </c>
       <c r="J3" t="n">
-        <v>23.18653718053771</v>
+        <v>22.27363554925901</v>
       </c>
       <c r="K3" t="n">
-        <v>21.52819525461542</v>
+        <v>21.05295606088537</v>
       </c>
       <c r="L3" t="n">
-        <v>21.38164665321432</v>
+        <v>20.9616414483108</v>
       </c>
       <c r="M3" t="n">
-        <v>21.98585155167933</v>
+        <v>21.32727663715095</v>
       </c>
       <c r="N3" t="n">
-        <v>21.49893320313393</v>
+        <v>21.03925044271157</v>
       </c>
       <c r="O3" t="n">
-        <v>28.40827726122826</v>
+        <v>27.96632932289764</v>
       </c>
       <c r="P3" t="n">
-        <v>22.57677604363011</v>
+        <v>21.8343285900913</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.74609373034597</v>
+        <v>21.22205283352314</v>
       </c>
       <c r="R3" t="n">
-        <v>21.19655201284246</v>
+        <v>20.81813664080706</v>
       </c>
       <c r="S3" t="n">
-        <v>21.36936288540928</v>
+        <v>20.96511797889345</v>
       </c>
       <c r="T3" t="n">
-        <v>20.92726350089194</v>
+        <v>20.63560636905054</v>
       </c>
       <c r="U3" t="n">
-        <v>24.74509800577231</v>
+        <v>24.2942020069929</v>
       </c>
       <c r="V3" t="n">
-        <v>21.38150161909925</v>
+        <v>20.96795175130129</v>
       </c>
       <c r="W3" t="n">
-        <v>27.78359644064076</v>
+        <v>27.05859594885974</v>
       </c>
       <c r="X3" t="n">
-        <v>22.88340814402431</v>
+        <v>22.00332388056819</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.01519094608269</v>
+        <v>23.50310265720051</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.62532036215615</v>
+        <v>27.20084470220584</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.32810743764967</v>
+        <v>20.92426763751236</v>
       </c>
       <c r="AB3" t="n">
-        <v>27.38442505851065</v>
+        <v>25.04262547442107</v>
       </c>
     </row>
     <row r="4">
